--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260723-00034</v>
       </c>
       <c r="B2" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -476,16 +476,16 @@
         <v>2026-07-23 20:39:50</v>
       </c>
       <c r="N2" s="1">
-        <v/>
+        <v>180000</v>
       </c>
       <c r="O2" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P2" t="str">
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R2" t="str">
         <v>(주)위니온로지스</v>
@@ -496,7 +496,7 @@
         <v>T260723-00033</v>
       </c>
       <c r="B3" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -532,16 +532,16 @@
         <v>2026-07-23 20:39:30</v>
       </c>
       <c r="N3" s="1">
-        <v/>
+        <v>180000</v>
       </c>
       <c r="O3" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P3" t="str">
         <v/>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R3" t="str">
         <v>(주)위니온로지스</v>
@@ -552,7 +552,7 @@
         <v>T260723-00032</v>
       </c>
       <c r="B4" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -588,16 +588,16 @@
         <v>2026-07-23 20:38:54</v>
       </c>
       <c r="N4" s="1">
-        <v/>
+        <v>190000</v>
       </c>
       <c r="O4" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P4" t="str">
         <v/>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R4" t="str">
         <v>(주)위니온로지스</v>
@@ -608,7 +608,7 @@
         <v>T260723-00031</v>
       </c>
       <c r="B5" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -644,16 +644,16 @@
         <v>2026-07-23 20:38:24</v>
       </c>
       <c r="N5" s="1">
-        <v/>
+        <v>90000</v>
       </c>
       <c r="O5" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P5" t="str">
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R5" t="str">
         <v>(주)위니온로지스</v>
@@ -664,7 +664,7 @@
         <v>T260723-00030</v>
       </c>
       <c r="B6" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -700,16 +700,16 @@
         <v>2026-07-23 20:35:58</v>
       </c>
       <c r="N6" s="1">
-        <v/>
+        <v>170000</v>
       </c>
       <c r="O6" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P6" t="str">
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R6" t="str">
         <v>(주)위니온로지스</v>
@@ -720,7 +720,7 @@
         <v>T260723-00029</v>
       </c>
       <c r="B7" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -756,16 +756,16 @@
         <v>2026-07-23 20:35:24</v>
       </c>
       <c r="N7" s="1">
-        <v/>
+        <v>250000</v>
       </c>
       <c r="O7" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P7" t="str">
         <v/>
       </c>
       <c r="Q7" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R7" t="str">
         <v>(주)위니온로지스</v>
@@ -776,7 +776,7 @@
         <v>T260723-00028</v>
       </c>
       <c r="B8" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -812,16 +812,16 @@
         <v>2026-07-23 20:35:04</v>
       </c>
       <c r="N8" s="1">
-        <v/>
+        <v>200000</v>
       </c>
       <c r="O8" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P8" t="str">
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R8" t="str">
         <v>(주)위니온로지스</v>
@@ -832,7 +832,7 @@
         <v>T260723-00027</v>
       </c>
       <c r="B9" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -868,16 +868,16 @@
         <v>2026-07-23 20:34:33</v>
       </c>
       <c r="N9" s="1">
-        <v/>
+        <v>180000</v>
       </c>
       <c r="O9" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P9" t="str">
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R9" t="str">
         <v>(주)위니온로지스</v>
@@ -888,7 +888,7 @@
         <v>T260723-00026</v>
       </c>
       <c r="B10" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -924,16 +924,16 @@
         <v>2026-07-23 20:34:06</v>
       </c>
       <c r="N10" s="1">
-        <v/>
+        <v>240000</v>
       </c>
       <c r="O10" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P10" t="str">
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R10" t="str">
         <v>(주)위니온로지스</v>
@@ -944,7 +944,7 @@
         <v>T260723-00025</v>
       </c>
       <c r="B11" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -980,16 +980,16 @@
         <v>2026-07-23 20:33:51</v>
       </c>
       <c r="N11" s="1">
-        <v/>
+        <v>250000</v>
       </c>
       <c r="O11" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P11" t="str">
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R11" t="str">
         <v>(주)위니온로지스</v>
@@ -1000,7 +1000,7 @@
         <v>T260723-00024</v>
       </c>
       <c r="B12" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1036,16 +1036,16 @@
         <v>2026-07-23 20:33:35</v>
       </c>
       <c r="N12" s="1">
-        <v/>
+        <v>200000</v>
       </c>
       <c r="O12" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P12" t="str">
         <v/>
       </c>
       <c r="Q12" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R12" t="str">
         <v>(주)위니온로지스</v>
@@ -1056,7 +1056,7 @@
         <v>T260723-00023</v>
       </c>
       <c r="B13" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1092,16 +1092,16 @@
         <v>2026-07-23 20:33:18</v>
       </c>
       <c r="N13" s="1">
-        <v/>
+        <v>310000</v>
       </c>
       <c r="O13" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P13" t="str">
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R13" t="str">
         <v>(주)위니온로지스</v>
@@ -1112,7 +1112,7 @@
         <v>T260723-00022</v>
       </c>
       <c r="B14" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1148,16 +1148,16 @@
         <v>2026-07-23 20:33:02</v>
       </c>
       <c r="N14" s="1">
-        <v/>
+        <v>280000</v>
       </c>
       <c r="O14" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P14" t="str">
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R14" t="str">
         <v>(주)위니온로지스</v>
@@ -1168,7 +1168,7 @@
         <v>T260723-00021</v>
       </c>
       <c r="B15" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1204,16 +1204,16 @@
         <v>2026-07-23 20:32:44</v>
       </c>
       <c r="N15" s="1">
-        <v/>
+        <v>260000</v>
       </c>
       <c r="O15" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P15" t="str">
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R15" t="str">
         <v>(주)위니온로지스</v>
@@ -1224,7 +1224,7 @@
         <v>T260723-00020</v>
       </c>
       <c r="B16" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1248,7 +1248,7 @@
         <v>2026-07-23 22:00</v>
       </c>
       <c r="J16" t="str">
-        <v>11톤 윙바디</v>
+        <v>5톤 윙바디</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1260,16 +1260,16 @@
         <v>2026-07-23 20:32:26</v>
       </c>
       <c r="N16" s="1">
-        <v/>
+        <v>290000</v>
       </c>
       <c r="O16" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P16" t="str">
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R16" t="str">
         <v>(주)위니온로지스</v>
@@ -1280,7 +1280,7 @@
         <v>T260723-00019</v>
       </c>
       <c r="B17" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1316,16 +1316,16 @@
         <v>2026-07-23 20:32:02</v>
       </c>
       <c r="N17" s="1">
-        <v/>
+        <v>780000</v>
       </c>
       <c r="O17" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P17" t="str">
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R17" t="str">
         <v>(주)위니온로지스</v>
@@ -1336,7 +1336,7 @@
         <v>T260723-00018</v>
       </c>
       <c r="B18" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1372,16 +1372,16 @@
         <v>2026-07-23 20:31:26</v>
       </c>
       <c r="N18" s="1">
-        <v/>
+        <v>250000</v>
       </c>
       <c r="O18" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P18" t="str">
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R18" t="str">
         <v>(주)위니온로지스</v>
@@ -1392,7 +1392,7 @@
         <v>T260723-00017</v>
       </c>
       <c r="B19" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1428,16 +1428,16 @@
         <v>2026-07-23 20:31:11</v>
       </c>
       <c r="N19" s="1">
-        <v/>
+        <v>260000</v>
       </c>
       <c r="O19" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P19" t="str">
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R19" t="str">
         <v>(주)위니온로지스</v>
@@ -1448,7 +1448,7 @@
         <v>T260723-00016</v>
       </c>
       <c r="B20" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1484,16 +1484,16 @@
         <v>2026-07-23 20:30:57</v>
       </c>
       <c r="N20" s="1">
-        <v/>
+        <v>420000</v>
       </c>
       <c r="O20" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P20" t="str">
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R20" t="str">
         <v>(주)위니온로지스</v>
@@ -1504,7 +1504,7 @@
         <v>T260723-00015</v>
       </c>
       <c r="B21" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1540,16 +1540,16 @@
         <v>2026-07-23 20:30:39</v>
       </c>
       <c r="N21" s="1">
-        <v/>
+        <v>200000</v>
       </c>
       <c r="O21" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P21" t="str">
         <v/>
       </c>
       <c r="Q21" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R21" t="str">
         <v>(주)위니온로지스</v>
@@ -1560,7 +1560,7 @@
         <v>T260723-00014</v>
       </c>
       <c r="B22" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1596,16 +1596,16 @@
         <v>2026-07-23 20:30:23</v>
       </c>
       <c r="N22" s="1">
-        <v/>
+        <v>520000</v>
       </c>
       <c r="O22" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P22" t="str">
         <v/>
       </c>
       <c r="Q22" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R22" t="str">
         <v>(주)위니온로지스</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -496,7 +496,7 @@
         <v>T260723-00034</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260723-00033</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260723-00032</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260723-00031</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260723-00030</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260723-00029</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260723-00028</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260723-00027</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260723-00026</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260723-00025</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260723-00024</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260723-00023</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260723-00022</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260723-00021</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260723-00020</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260723-00019</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260723-00018</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260723-00017</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260723-00016</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260723-00015</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1616,7 +1616,7 @@
         <v>T260723-00014</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>안성FC</v>
@@ -1672,7 +1672,7 @@
         <v>T260723-00013</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>안성FC</v>
@@ -1728,7 +1728,7 @@
         <v>T260723-00012</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>라꾸스토리</v>
@@ -1784,7 +1784,7 @@
         <v>T260723-00011</v>
       </c>
       <c r="B26" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C26" t="str">
         <v>청주ARC</v>
@@ -1840,7 +1840,7 @@
         <v>T260723-00010</v>
       </c>
       <c r="B27" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C27" t="str">
         <v>곤지암FDC</v>
@@ -1896,7 +1896,7 @@
         <v>T260723-00009</v>
       </c>
       <c r="B28" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C28" t="str">
         <v>샤오미</v>
@@ -1952,7 +1952,7 @@
         <v>T260723-00008</v>
       </c>
       <c r="B29" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C29" t="str">
         <v>듀오백(화성)</v>
@@ -2008,7 +2008,7 @@
         <v>T260723-00007</v>
       </c>
       <c r="B30" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C30" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260724-00026</v>
       </c>
       <c r="B2" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -476,16 +476,16 @@
         <v>2026-07-24 19:59:08</v>
       </c>
       <c r="N2" s="1">
-        <v/>
+        <v>130000</v>
       </c>
       <c r="O2" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P2" t="str">
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R2" t="str">
         <v>(주)위니온로지스</v>
@@ -496,7 +496,7 @@
         <v>T260724-00025</v>
       </c>
       <c r="B3" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -532,16 +532,16 @@
         <v>2026-07-24 19:58:40</v>
       </c>
       <c r="N3" s="1">
-        <v/>
+        <v>160000</v>
       </c>
       <c r="O3" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P3" t="str">
         <v/>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R3" t="str">
         <v>(주)위니온로지스</v>
@@ -552,7 +552,7 @@
         <v>T260724-00024</v>
       </c>
       <c r="B4" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -588,16 +588,16 @@
         <v>2026-07-24 19:58:23</v>
       </c>
       <c r="N4" s="1">
-        <v/>
+        <v>200000</v>
       </c>
       <c r="O4" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P4" t="str">
         <v/>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R4" t="str">
         <v>(주)위니온로지스</v>
@@ -608,7 +608,7 @@
         <v>T260724-00023</v>
       </c>
       <c r="B5" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -644,16 +644,16 @@
         <v>2026-07-24 19:57:56</v>
       </c>
       <c r="N5" s="1">
-        <v/>
+        <v>80000</v>
       </c>
       <c r="O5" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P5" t="str">
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R5" t="str">
         <v>(주)위니온로지스</v>
@@ -720,7 +720,7 @@
         <v>T260724-00021</v>
       </c>
       <c r="B7" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -756,16 +756,16 @@
         <v>2026-07-24 19:57:20</v>
       </c>
       <c r="N7" s="1">
-        <v/>
+        <v>120000</v>
       </c>
       <c r="O7" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P7" t="str">
         <v/>
       </c>
       <c r="Q7" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R7" t="str">
         <v>(주)위니온로지스</v>
@@ -776,7 +776,7 @@
         <v>T260724-00020</v>
       </c>
       <c r="B8" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -812,16 +812,16 @@
         <v>2026-07-24 19:57:03</v>
       </c>
       <c r="N8" s="1">
-        <v/>
+        <v>320000</v>
       </c>
       <c r="O8" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P8" t="str">
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R8" t="str">
         <v>(주)위니온로지스</v>
@@ -832,7 +832,7 @@
         <v>T260724-00019</v>
       </c>
       <c r="B9" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -868,16 +868,16 @@
         <v>2026-07-24 19:55:58</v>
       </c>
       <c r="N9" s="1">
-        <v/>
+        <v>140000</v>
       </c>
       <c r="O9" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P9" t="str">
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R9" t="str">
         <v>(주)위니온로지스</v>
@@ -888,7 +888,7 @@
         <v>T260724-00018</v>
       </c>
       <c r="B10" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -924,16 +924,16 @@
         <v>2026-07-24 19:55:35</v>
       </c>
       <c r="N10" s="1">
-        <v/>
+        <v>190000</v>
       </c>
       <c r="O10" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P10" t="str">
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R10" t="str">
         <v>(주)위니온로지스</v>
@@ -944,7 +944,7 @@
         <v>T260724-00017</v>
       </c>
       <c r="B11" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -980,16 +980,16 @@
         <v>2026-07-24 19:55:08</v>
       </c>
       <c r="N11" s="1">
-        <v/>
+        <v>250000</v>
       </c>
       <c r="O11" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P11" t="str">
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R11" t="str">
         <v>(주)위니온로지스</v>
@@ -1000,7 +1000,7 @@
         <v>T260724-00016</v>
       </c>
       <c r="B12" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1036,16 +1036,16 @@
         <v>2026-07-24 19:54:03</v>
       </c>
       <c r="N12" s="1">
-        <v/>
+        <v>240000</v>
       </c>
       <c r="O12" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P12" t="str">
         <v/>
       </c>
       <c r="Q12" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R12" t="str">
         <v>(주)위니온로지스</v>
@@ -1056,7 +1056,7 @@
         <v>T260724-00015</v>
       </c>
       <c r="B13" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1092,16 +1092,16 @@
         <v>2026-07-24 19:53:45</v>
       </c>
       <c r="N13" s="1">
-        <v/>
+        <v>350000</v>
       </c>
       <c r="O13" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P13" t="str">
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R13" t="str">
         <v>(주)위니온로지스</v>
@@ -1112,7 +1112,7 @@
         <v>T260724-00014</v>
       </c>
       <c r="B14" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1148,16 +1148,16 @@
         <v>2026-07-24 19:53:23</v>
       </c>
       <c r="N14" s="1">
-        <v/>
+        <v>590000</v>
       </c>
       <c r="O14" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P14" t="str">
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R14" t="str">
         <v>(주)위니온로지스</v>
@@ -1168,7 +1168,7 @@
         <v>T260724-00013</v>
       </c>
       <c r="B15" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1204,16 +1204,16 @@
         <v>2026-07-24 19:53:01</v>
       </c>
       <c r="N15" s="1">
-        <v/>
+        <v>260000</v>
       </c>
       <c r="O15" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P15" t="str">
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R15" t="str">
         <v>(주)위니온로지스</v>
@@ -1224,7 +1224,7 @@
         <v>T260724-00012</v>
       </c>
       <c r="B16" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1260,16 +1260,16 @@
         <v>2026-07-24 19:52:39</v>
       </c>
       <c r="N16" s="1">
-        <v/>
+        <v>280000</v>
       </c>
       <c r="O16" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P16" t="str">
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R16" t="str">
         <v>(주)위니온로지스</v>
@@ -1280,7 +1280,7 @@
         <v>T260724-00011</v>
       </c>
       <c r="B17" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1316,16 +1316,16 @@
         <v>2026-07-24 19:52:22</v>
       </c>
       <c r="N17" s="1">
-        <v/>
+        <v>290000</v>
       </c>
       <c r="O17" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P17" t="str">
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R17" t="str">
         <v>(주)위니온로지스</v>
@@ -1392,7 +1392,7 @@
         <v>T260724-00009</v>
       </c>
       <c r="B19" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1428,16 +1428,16 @@
         <v>2026-07-24 19:51:37</v>
       </c>
       <c r="N19" s="1">
-        <v/>
+        <v>250000</v>
       </c>
       <c r="O19" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P19" t="str">
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R19" t="str">
         <v>(주)위니온로지스</v>
@@ -1448,7 +1448,7 @@
         <v>T260724-00008</v>
       </c>
       <c r="B20" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1484,16 +1484,16 @@
         <v>2026-07-24 19:51:21</v>
       </c>
       <c r="N20" s="1">
-        <v/>
+        <v>370000</v>
       </c>
       <c r="O20" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P20" t="str">
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R20" t="str">
         <v>(주)위니온로지스</v>
@@ -1504,7 +1504,7 @@
         <v>T260724-00007</v>
       </c>
       <c r="B21" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1540,16 +1540,16 @@
         <v>2026-07-24 19:50:59</v>
       </c>
       <c r="N21" s="1">
-        <v/>
+        <v>420000</v>
       </c>
       <c r="O21" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P21" t="str">
         <v/>
       </c>
       <c r="Q21" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R21" t="str">
         <v>(주)위니온로지스</v>
@@ -1560,7 +1560,7 @@
         <v>T260724-00006</v>
       </c>
       <c r="B22" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1596,16 +1596,16 @@
         <v>2026-07-24 19:50:17</v>
       </c>
       <c r="N22" s="1">
-        <v/>
+        <v>200000</v>
       </c>
       <c r="O22" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P22" t="str">
         <v/>
       </c>
       <c r="Q22" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R22" t="str">
         <v>(주)위니온로지스</v>
@@ -1616,7 +1616,7 @@
         <v>T260724-00005</v>
       </c>
       <c r="B23" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C23" t="str">
         <v>안성FC</v>
@@ -1652,16 +1652,16 @@
         <v>2026-07-24 19:49:25</v>
       </c>
       <c r="N23" s="1">
-        <v/>
+        <v>520000</v>
       </c>
       <c r="O23" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P23" t="str">
         <v/>
       </c>
       <c r="Q23" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R23" t="str">
         <v>(주)위니온로지스</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -664,7 +664,7 @@
         <v>T260724-00022</v>
       </c>
       <c r="B6" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -700,16 +700,16 @@
         <v>2026-07-24 19:57:39</v>
       </c>
       <c r="N6" s="1">
-        <v/>
+        <v>450000</v>
       </c>
       <c r="O6" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P6" t="str">
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R6" t="str">
         <v>(주)위니온로지스</v>
@@ -1336,7 +1336,7 @@
         <v>T260724-00010</v>
       </c>
       <c r="B18" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1360,7 +1360,7 @@
         <v>2026-07-24 23:00</v>
       </c>
       <c r="J18" t="str">
-        <v>5톤축 윙바디</v>
+        <v>11톤 윙바디</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -1372,16 +1372,16 @@
         <v>2026-07-24 19:52:00</v>
       </c>
       <c r="N18" s="1">
-        <v/>
+        <v>490000</v>
       </c>
       <c r="O18" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P18" t="str">
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R18" t="str">
         <v>(주)위니온로지스</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260724-00026</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260724-00025</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260724-00024</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260724-00023</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260724-00022</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260724-00021</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260724-00020</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260724-00019</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260724-00018</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260724-00017</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260724-00016</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260724-00015</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260724-00014</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260724-00013</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260724-00012</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260724-00011</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260724-00010</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260724-00009</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260724-00008</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260724-00007</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260724-00006</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1616,7 +1616,7 @@
         <v>T260724-00005</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>안성FC</v>
@@ -1672,7 +1672,7 @@
         <v>T260724-00004</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>안성FC</v>
@@ -1728,7 +1728,7 @@
         <v>T260724-00003</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>듀오백(화성)</v>
@@ -1784,7 +1784,7 @@
         <v>T260724-00002</v>
       </c>
       <c r="B26" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C26" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -944,7 +944,7 @@
         <v>T260728-00023</v>
       </c>
       <c r="B11" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -968,7 +968,7 @@
         <v>2026-07-28 23:00</v>
       </c>
       <c r="J11" t="str">
-        <v>3.5톤 윙바디</v>
+        <v>5톤 윙바디</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -980,16 +980,16 @@
         <v>2026-07-28 20:53:41</v>
       </c>
       <c r="N11" s="1">
-        <v/>
+        <v>360000</v>
       </c>
       <c r="O11" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P11" t="str">
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R11" t="str">
         <v>(주)위니온로지스</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -776,7 +776,7 @@
         <v>T260728-00032</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260728-00031</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260728-00030</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260728-00029</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260728-00028</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260728-00027</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260728-00026</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260728-00025</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260728-00024</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260728-00023</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260728-00022</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260728-00021</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260728-00020</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260728-00019</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260728-00018</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1616,7 +1616,7 @@
         <v>T260728-00017</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>안성FC</v>
@@ -1672,7 +1672,7 @@
         <v>T260728-00016</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>안성FC</v>
@@ -1728,7 +1728,7 @@
         <v>T260728-00015</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>안성FC</v>
@@ -1784,7 +1784,7 @@
         <v>T260728-00014</v>
       </c>
       <c r="B26" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C26" t="str">
         <v>안성FC</v>
@@ -1840,7 +1840,7 @@
         <v>T260728-00013</v>
       </c>
       <c r="B27" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C27" t="str">
         <v>듀오백(화성)</v>
@@ -1896,7 +1896,7 @@
         <v>T260728-00012</v>
       </c>
       <c r="B28" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C28" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260729-00033</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260729-00032</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260729-00031</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260729-00030</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260729-00029</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260729-00028</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260729-00027</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260729-00026</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260729-00025</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260729-00024</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260729-00023</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260729-00022</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260729-00021</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260729-00020</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260729-00019</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260729-00018</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260729-00017</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260729-00016</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260729-00015</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260729-00014</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260729-00013</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1616,7 +1616,7 @@
         <v>T260729-00012</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>안성FC</v>
@@ -1672,7 +1672,7 @@
         <v>T260729-00011</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>안성FC</v>
@@ -1728,7 +1728,7 @@
         <v>T260729-00010</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>샤오미</v>
@@ -1784,7 +1784,7 @@
         <v>T260729-00009</v>
       </c>
       <c r="B26" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C26" t="str">
         <v>듀오백(화성)</v>
@@ -1840,7 +1840,7 @@
         <v>T260729-00008</v>
       </c>
       <c r="B27" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C27" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260731-00034</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260731-00033</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260731-00032</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260731-00031</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260731-00030</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260731-00029</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260731-00028</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260731-00027</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260731-00026</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260731-00025</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260731-00024</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260731-00023</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260731-00022</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260731-00021</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260731-00020</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260731-00019</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260731-00017</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260731-00016</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260731-00015</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260731-00014</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260731-00013</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1616,7 +1616,7 @@
         <v>T260731-00012</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>안성FC</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R711"/>
+  <dimension ref="A1:R685"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38740,1465 +38740,9 @@
         <v>패스트레인코리아</v>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="str">
-        <v>T260701-00026</v>
-      </c>
-      <c r="B686" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C686" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D686" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E686" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F686">
-        <v>1</v>
-      </c>
-      <c r="G686" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H686" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I686" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J686" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K686">
-        <v>1</v>
-      </c>
-      <c r="L686" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M686" t="str">
-        <v>2026-07-01 19:47:13</v>
-      </c>
-      <c r="N686" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O686" s="1">
-        <v>0</v>
-      </c>
-      <c r="P686" t="str">
-        <v/>
-      </c>
-      <c r="Q686" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R686" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="str">
-        <v>T260701-00025</v>
-      </c>
-      <c r="B687" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C687" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D687" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E687" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F687">
-        <v>2</v>
-      </c>
-      <c r="G687" t="str">
-        <v>원주ACP</v>
-      </c>
-      <c r="H687" t="str">
-        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
-      </c>
-      <c r="I687" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J687" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K687">
-        <v>1</v>
-      </c>
-      <c r="L687" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M687" t="str">
-        <v>2026-07-01 19:46:48</v>
-      </c>
-      <c r="N687" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O687" s="1">
-        <v>0</v>
-      </c>
-      <c r="P687" t="str">
-        <v/>
-      </c>
-      <c r="Q687" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R687" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="str">
-        <v>T260701-00024</v>
-      </c>
-      <c r="B688" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C688" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D688" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E688" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F688">
-        <v>1</v>
-      </c>
-      <c r="G688" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H688" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I688" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J688" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K688">
-        <v>1</v>
-      </c>
-      <c r="L688" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M688" t="str">
-        <v>2026-07-01 19:46:12</v>
-      </c>
-      <c r="N688" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O688" s="1">
-        <v>0</v>
-      </c>
-      <c r="P688" t="str">
-        <v/>
-      </c>
-      <c r="Q688" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R688" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="str">
-        <v>T260701-00023</v>
-      </c>
-      <c r="B689" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C689" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D689" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E689" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F689">
-        <v>3</v>
-      </c>
-      <c r="G689" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H689" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I689" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J689" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K689">
-        <v>1</v>
-      </c>
-      <c r="L689" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M689" t="str">
-        <v>2026-07-01 19:45:40</v>
-      </c>
-      <c r="N689" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O689" s="1">
-        <v>0</v>
-      </c>
-      <c r="P689" t="str">
-        <v/>
-      </c>
-      <c r="Q689" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R689" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="str">
-        <v>T260701-00022</v>
-      </c>
-      <c r="B690" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C690" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D690" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E690" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F690">
-        <v>0</v>
-      </c>
-      <c r="G690" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H690" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I690" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J690" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K690">
-        <v>1</v>
-      </c>
-      <c r="L690" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M690" t="str">
-        <v>2026-07-01 19:44:56</v>
-      </c>
-      <c r="N690" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O690" s="1">
-        <v>0</v>
-      </c>
-      <c r="P690" t="str">
-        <v/>
-      </c>
-      <c r="Q690" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R690" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="str">
-        <v>T260701-00021</v>
-      </c>
-      <c r="B691" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C691" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D691" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E691" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F691">
-        <v>1</v>
-      </c>
-      <c r="G691" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H691" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I691" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J691" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K691">
-        <v>1</v>
-      </c>
-      <c r="L691" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M691" t="str">
-        <v>2026-07-01 19:44:37</v>
-      </c>
-      <c r="N691" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O691" s="1">
-        <v>0</v>
-      </c>
-      <c r="P691" t="str">
-        <v/>
-      </c>
-      <c r="Q691" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R691" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="str">
-        <v>T260701-00020</v>
-      </c>
-      <c r="B692" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C692" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D692" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E692" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F692">
-        <v>2</v>
-      </c>
-      <c r="G692" t="str">
-        <v>속초ACP</v>
-      </c>
-      <c r="H692" t="str">
-        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
-      </c>
-      <c r="I692" t="str">
-        <v>2026-07-02 06:00</v>
-      </c>
-      <c r="J692" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K692">
-        <v>1</v>
-      </c>
-      <c r="L692" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M692" t="str">
-        <v>2026-07-01 19:44:05</v>
-      </c>
-      <c r="N692" s="1">
-        <v>320000</v>
-      </c>
-      <c r="O692" s="1">
-        <v>0</v>
-      </c>
-      <c r="P692" t="str">
-        <v/>
-      </c>
-      <c r="Q692" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R692" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="str">
-        <v>T260701-00019</v>
-      </c>
-      <c r="B693" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C693" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D693" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E693" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F693">
-        <v>0</v>
-      </c>
-      <c r="G693" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H693" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I693" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J693" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K693">
-        <v>1</v>
-      </c>
-      <c r="L693" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M693" t="str">
-        <v>2026-07-01 19:43:22</v>
-      </c>
-      <c r="N693" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O693" s="1">
-        <v>0</v>
-      </c>
-      <c r="P693" t="str">
-        <v/>
-      </c>
-      <c r="Q693" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R693" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="str">
-        <v>T260701-00018</v>
-      </c>
-      <c r="B694" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C694" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D694" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E694" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F694">
-        <v>1</v>
-      </c>
-      <c r="G694" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H694" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I694" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J694" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K694">
-        <v>1</v>
-      </c>
-      <c r="L694" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M694" t="str">
-        <v>2026-07-01 19:43:03</v>
-      </c>
-      <c r="N694" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O694" s="1">
-        <v>0</v>
-      </c>
-      <c r="P694" t="str">
-        <v/>
-      </c>
-      <c r="Q694" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R694" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="str">
-        <v>T260701-00017</v>
-      </c>
-      <c r="B695" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C695" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D695" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E695" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F695">
-        <v>0</v>
-      </c>
-      <c r="G695" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H695" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I695" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J695" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K695">
-        <v>1</v>
-      </c>
-      <c r="L695" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M695" t="str">
-        <v>2026-07-01 19:42:39</v>
-      </c>
-      <c r="N695" s="1">
-        <v>310000</v>
-      </c>
-      <c r="O695" s="1">
-        <v>0</v>
-      </c>
-      <c r="P695" t="str">
-        <v/>
-      </c>
-      <c r="Q695" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R695" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="str">
-        <v>T260701-00016</v>
-      </c>
-      <c r="B696" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C696" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D696" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E696" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F696">
-        <v>0</v>
-      </c>
-      <c r="G696" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H696" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I696" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J696" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K696">
-        <v>1</v>
-      </c>
-      <c r="L696" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M696" t="str">
-        <v>2026-07-01 19:42:17</v>
-      </c>
-      <c r="N696" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O696" s="1">
-        <v>0</v>
-      </c>
-      <c r="P696" t="str">
-        <v/>
-      </c>
-      <c r="Q696" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R696" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="str">
-        <v>T260701-00015</v>
-      </c>
-      <c r="B697" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C697" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D697" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E697" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F697">
-        <v>1</v>
-      </c>
-      <c r="G697" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H697" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I697" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J697" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K697">
-        <v>1</v>
-      </c>
-      <c r="L697" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M697" t="str">
-        <v>2026-07-01 19:42:02</v>
-      </c>
-      <c r="N697" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O697" s="1">
-        <v>0</v>
-      </c>
-      <c r="P697" t="str">
-        <v/>
-      </c>
-      <c r="Q697" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R697" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="str">
-        <v>T260701-00014</v>
-      </c>
-      <c r="B698" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C698" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D698" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E698" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F698">
-        <v>1</v>
-      </c>
-      <c r="G698" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H698" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I698" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J698" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K698">
-        <v>1</v>
-      </c>
-      <c r="L698" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M698" t="str">
-        <v>2026-07-01 19:41:41</v>
-      </c>
-      <c r="N698" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O698" s="1">
-        <v>0</v>
-      </c>
-      <c r="P698" t="str">
-        <v/>
-      </c>
-      <c r="Q698" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R698" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="str">
-        <v>T260701-00013</v>
-      </c>
-      <c r="B699" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C699" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D699" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E699" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F699">
-        <v>1</v>
-      </c>
-      <c r="G699" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H699" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I699" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J699" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K699">
-        <v>1</v>
-      </c>
-      <c r="L699" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M699" t="str">
-        <v>2026-07-01 19:41:08</v>
-      </c>
-      <c r="N699" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O699" s="1">
-        <v>0</v>
-      </c>
-      <c r="P699" t="str">
-        <v/>
-      </c>
-      <c r="Q699" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R699" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="str">
-        <v>T260701-00012</v>
-      </c>
-      <c r="B700" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C700" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D700" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E700" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F700">
-        <v>1</v>
-      </c>
-      <c r="G700" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H700" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I700" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J700" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K700">
-        <v>1</v>
-      </c>
-      <c r="L700" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M700" t="str">
-        <v>2026-07-01 19:40:45</v>
-      </c>
-      <c r="N700" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O700" s="1">
-        <v>0</v>
-      </c>
-      <c r="P700" t="str">
-        <v/>
-      </c>
-      <c r="Q700" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R700" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="str">
-        <v>T260701-00011</v>
-      </c>
-      <c r="B701" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C701" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D701" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E701" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F701">
-        <v>0</v>
-      </c>
-      <c r="G701" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H701" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I701" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J701" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K701">
-        <v>1</v>
-      </c>
-      <c r="L701" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M701" t="str">
-        <v>2026-07-01 19:40:21</v>
-      </c>
-      <c r="N701" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O701" s="1">
-        <v>0</v>
-      </c>
-      <c r="P701" t="str">
-        <v/>
-      </c>
-      <c r="Q701" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R701" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="str">
-        <v>T260701-00010</v>
-      </c>
-      <c r="B702" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C702" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D702" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E702" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F702">
-        <v>1</v>
-      </c>
-      <c r="G702" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H702" t="str">
-        <v>경산시 해오름길114-2 경산FDC</v>
-      </c>
-      <c r="I702" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J702" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K702">
-        <v>1</v>
-      </c>
-      <c r="L702" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M702" t="str">
-        <v>2026-07-01 19:40:04</v>
-      </c>
-      <c r="N702" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O702" s="1">
-        <v>0</v>
-      </c>
-      <c r="P702" t="str">
-        <v/>
-      </c>
-      <c r="Q702" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R702" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="str">
-        <v>T260701-00009</v>
-      </c>
-      <c r="B703" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C703" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D703" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E703" t="str">
-        <v>2026-07-01 17:30</v>
-      </c>
-      <c r="F703">
-        <v>0</v>
-      </c>
-      <c r="G703" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H703" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I703" t="str">
-        <v>2026-07-01 18:30</v>
-      </c>
-      <c r="J703" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K703">
-        <v>1</v>
-      </c>
-      <c r="L703" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M703" t="str">
-        <v>2026-07-01 19:31:35</v>
-      </c>
-      <c r="N703" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O703" s="1">
-        <v>0</v>
-      </c>
-      <c r="P703" t="str">
-        <v/>
-      </c>
-      <c r="Q703" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R703" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="str">
-        <v>T260701-00008</v>
-      </c>
-      <c r="B704" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C704" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D704" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E704" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="F704">
-        <v>0</v>
-      </c>
-      <c r="G704" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H704" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I704" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="J704" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K704">
-        <v>1</v>
-      </c>
-      <c r="L704" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M704" t="str">
-        <v>2026-07-01 19:31:02</v>
-      </c>
-      <c r="N704" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O704" s="1">
-        <v>0</v>
-      </c>
-      <c r="P704" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q704" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R704" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="str">
-        <v>T260701-00007</v>
-      </c>
-      <c r="B705" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C705" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D705" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E705" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F705">
-        <v>0</v>
-      </c>
-      <c r="G705" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H705" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I705" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="J705" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K705">
-        <v>1</v>
-      </c>
-      <c r="L705" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M705" t="str">
-        <v>2026-07-01 19:29:27</v>
-      </c>
-      <c r="N705" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O705" s="1">
-        <v>0</v>
-      </c>
-      <c r="P705" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q705" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R705" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="str">
-        <v>T260701-00006</v>
-      </c>
-      <c r="B706" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C706" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D706" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E706" t="str">
-        <v>2026-07-01 16:30</v>
-      </c>
-      <c r="F706">
-        <v>0</v>
-      </c>
-      <c r="G706" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H706" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I706" t="str">
-        <v>2026-07-01 18:00</v>
-      </c>
-      <c r="J706" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K706">
-        <v>1</v>
-      </c>
-      <c r="L706" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M706" t="str">
-        <v>2026-07-01 16:09:24</v>
-      </c>
-      <c r="N706" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O706" s="1">
-        <v>0</v>
-      </c>
-      <c r="P706" t="str">
-        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q706" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R706" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="str">
-        <v>T260701-00005</v>
-      </c>
-      <c r="B707" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C707" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D707" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E707" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="F707">
-        <v>0</v>
-      </c>
-      <c r="G707" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H707" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I707" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J707" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K707">
-        <v>1</v>
-      </c>
-      <c r="L707" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M707" t="str">
-        <v>2026-07-01 14:58:37</v>
-      </c>
-      <c r="N707" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O707" s="1">
-        <v>0</v>
-      </c>
-      <c r="P707" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q707" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R707" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="str">
-        <v>T260701-00004</v>
-      </c>
-      <c r="B708" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C708" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D708" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E708" t="str">
-        <v>2026-07-01 15:20</v>
-      </c>
-      <c r="F708">
-        <v>0</v>
-      </c>
-      <c r="G708" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H708" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I708" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J708" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K708">
-        <v>1</v>
-      </c>
-      <c r="L708" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M708" t="str">
-        <v>2026-07-01 14:53:20</v>
-      </c>
-      <c r="N708" s="1">
-        <v>440000</v>
-      </c>
-      <c r="O708" s="1">
-        <v>0</v>
-      </c>
-      <c r="P708" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q708" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R708" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="str">
-        <v>T260701-00003</v>
-      </c>
-      <c r="B709" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C709" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D709" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E709" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F709">
-        <v>0</v>
-      </c>
-      <c r="G709" t="str">
-        <v>하이얼(이천다코넷)</v>
-      </c>
-      <c r="H709" t="str">
-        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
-      </c>
-      <c r="I709" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J709" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K709">
-        <v>1</v>
-      </c>
-      <c r="L709" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M709" t="str">
-        <v>2026-07-01 10:15:38</v>
-      </c>
-      <c r="N709" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O709" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P709" t="str">
-        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
-      </c>
-      <c r="Q709" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R709" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="str">
-        <v>T260701-00002</v>
-      </c>
-      <c r="B710" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C710" t="str">
-        <v>청주ARC(디지탈태양)</v>
-      </c>
-      <c r="D710" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
-      </c>
-      <c r="E710" t="str">
-        <v>2026-07-01 08:30</v>
-      </c>
-      <c r="F710">
-        <v>0</v>
-      </c>
-      <c r="G710" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H710" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="I710" t="str">
-        <v>2026-07-01 10:30</v>
-      </c>
-      <c r="J710" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K710">
-        <v>1</v>
-      </c>
-      <c r="L710" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M710" t="str">
-        <v>2026-07-01 10:13:39</v>
-      </c>
-      <c r="N710" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O710" s="1">
-        <v>0</v>
-      </c>
-      <c r="P710" t="str">
-        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
-      </c>
-      <c r="Q710" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R710" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="str">
-        <v>T260701-00001</v>
-      </c>
-      <c r="B711" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C711" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D711" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E711" t="str">
-        <v>2026-07-01 09:00</v>
-      </c>
-      <c r="F711">
-        <v>0</v>
-      </c>
-      <c r="G711" t="str">
-        <v>현대클러스터 한강미사3차</v>
-      </c>
-      <c r="H711" t="str">
-        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
-      </c>
-      <c r="I711" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J711" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K711">
-        <v>1</v>
-      </c>
-      <c r="L711" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M711" t="str">
-        <v>2026-07-01 09:07:09</v>
-      </c>
-      <c r="N711" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O711" s="1">
-        <v>0</v>
-      </c>
-      <c r="P711" t="str">
-        <v>스마트윈드 출하</v>
-      </c>
-      <c r="Q711" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R711" t="str">
-        <v>스마트윈드</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R711"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R685"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R685"/>
+  <dimension ref="A1:R711"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38740,9 +38740,1465 @@
         <v>패스트레인코리아</v>
       </c>
     </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>T260701-00026</v>
+      </c>
+      <c r="B686" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C686" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D686" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E686" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F686">
+        <v>1</v>
+      </c>
+      <c r="G686" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H686" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I686" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J686" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K686">
+        <v>1</v>
+      </c>
+      <c r="L686" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M686" t="str">
+        <v>2026-07-01 19:47:13</v>
+      </c>
+      <c r="N686" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O686" s="1">
+        <v>0</v>
+      </c>
+      <c r="P686" t="str">
+        <v/>
+      </c>
+      <c r="Q686" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R686" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>T260701-00025</v>
+      </c>
+      <c r="B687" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C687" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D687" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E687" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F687">
+        <v>2</v>
+      </c>
+      <c r="G687" t="str">
+        <v>원주ACP</v>
+      </c>
+      <c r="H687" t="str">
+        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
+      </c>
+      <c r="I687" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J687" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K687">
+        <v>1</v>
+      </c>
+      <c r="L687" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M687" t="str">
+        <v>2026-07-01 19:46:48</v>
+      </c>
+      <c r="N687" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O687" s="1">
+        <v>0</v>
+      </c>
+      <c r="P687" t="str">
+        <v/>
+      </c>
+      <c r="Q687" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R687" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>T260701-00024</v>
+      </c>
+      <c r="B688" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C688" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D688" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E688" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F688">
+        <v>1</v>
+      </c>
+      <c r="G688" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H688" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I688" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J688" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K688">
+        <v>1</v>
+      </c>
+      <c r="L688" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M688" t="str">
+        <v>2026-07-01 19:46:12</v>
+      </c>
+      <c r="N688" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O688" s="1">
+        <v>0</v>
+      </c>
+      <c r="P688" t="str">
+        <v/>
+      </c>
+      <c r="Q688" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R688" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>T260701-00023</v>
+      </c>
+      <c r="B689" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C689" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D689" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E689" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F689">
+        <v>3</v>
+      </c>
+      <c r="G689" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H689" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I689" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J689" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K689">
+        <v>1</v>
+      </c>
+      <c r="L689" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M689" t="str">
+        <v>2026-07-01 19:45:40</v>
+      </c>
+      <c r="N689" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O689" s="1">
+        <v>0</v>
+      </c>
+      <c r="P689" t="str">
+        <v/>
+      </c>
+      <c r="Q689" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R689" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>T260701-00022</v>
+      </c>
+      <c r="B690" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C690" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D690" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E690" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F690">
+        <v>0</v>
+      </c>
+      <c r="G690" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H690" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I690" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J690" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K690">
+        <v>1</v>
+      </c>
+      <c r="L690" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M690" t="str">
+        <v>2026-07-01 19:44:56</v>
+      </c>
+      <c r="N690" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O690" s="1">
+        <v>0</v>
+      </c>
+      <c r="P690" t="str">
+        <v/>
+      </c>
+      <c r="Q690" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R690" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>T260701-00021</v>
+      </c>
+      <c r="B691" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C691" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D691" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E691" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F691">
+        <v>1</v>
+      </c>
+      <c r="G691" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H691" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I691" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J691" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K691">
+        <v>1</v>
+      </c>
+      <c r="L691" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M691" t="str">
+        <v>2026-07-01 19:44:37</v>
+      </c>
+      <c r="N691" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O691" s="1">
+        <v>0</v>
+      </c>
+      <c r="P691" t="str">
+        <v/>
+      </c>
+      <c r="Q691" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R691" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>T260701-00020</v>
+      </c>
+      <c r="B692" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C692" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D692" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E692" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F692">
+        <v>2</v>
+      </c>
+      <c r="G692" t="str">
+        <v>속초ACP</v>
+      </c>
+      <c r="H692" t="str">
+        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
+      </c>
+      <c r="I692" t="str">
+        <v>2026-07-02 06:00</v>
+      </c>
+      <c r="J692" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K692">
+        <v>1</v>
+      </c>
+      <c r="L692" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M692" t="str">
+        <v>2026-07-01 19:44:05</v>
+      </c>
+      <c r="N692" s="1">
+        <v>320000</v>
+      </c>
+      <c r="O692" s="1">
+        <v>0</v>
+      </c>
+      <c r="P692" t="str">
+        <v/>
+      </c>
+      <c r="Q692" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R692" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
+        <v>T260701-00019</v>
+      </c>
+      <c r="B693" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C693" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D693" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E693" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F693">
+        <v>0</v>
+      </c>
+      <c r="G693" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H693" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I693" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J693" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K693">
+        <v>1</v>
+      </c>
+      <c r="L693" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M693" t="str">
+        <v>2026-07-01 19:43:22</v>
+      </c>
+      <c r="N693" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O693" s="1">
+        <v>0</v>
+      </c>
+      <c r="P693" t="str">
+        <v/>
+      </c>
+      <c r="Q693" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R693" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>T260701-00018</v>
+      </c>
+      <c r="B694" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C694" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D694" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E694" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F694">
+        <v>1</v>
+      </c>
+      <c r="G694" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H694" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I694" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J694" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K694">
+        <v>1</v>
+      </c>
+      <c r="L694" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M694" t="str">
+        <v>2026-07-01 19:43:03</v>
+      </c>
+      <c r="N694" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O694" s="1">
+        <v>0</v>
+      </c>
+      <c r="P694" t="str">
+        <v/>
+      </c>
+      <c r="Q694" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R694" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>T260701-00017</v>
+      </c>
+      <c r="B695" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C695" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D695" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E695" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F695">
+        <v>0</v>
+      </c>
+      <c r="G695" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H695" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I695" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J695" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K695">
+        <v>1</v>
+      </c>
+      <c r="L695" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M695" t="str">
+        <v>2026-07-01 19:42:39</v>
+      </c>
+      <c r="N695" s="1">
+        <v>310000</v>
+      </c>
+      <c r="O695" s="1">
+        <v>0</v>
+      </c>
+      <c r="P695" t="str">
+        <v/>
+      </c>
+      <c r="Q695" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R695" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>T260701-00016</v>
+      </c>
+      <c r="B696" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C696" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D696" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E696" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F696">
+        <v>0</v>
+      </c>
+      <c r="G696" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H696" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I696" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J696" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K696">
+        <v>1</v>
+      </c>
+      <c r="L696" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M696" t="str">
+        <v>2026-07-01 19:42:17</v>
+      </c>
+      <c r="N696" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O696" s="1">
+        <v>0</v>
+      </c>
+      <c r="P696" t="str">
+        <v/>
+      </c>
+      <c r="Q696" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R696" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>T260701-00015</v>
+      </c>
+      <c r="B697" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C697" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D697" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E697" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F697">
+        <v>1</v>
+      </c>
+      <c r="G697" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H697" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I697" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J697" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K697">
+        <v>1</v>
+      </c>
+      <c r="L697" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M697" t="str">
+        <v>2026-07-01 19:42:02</v>
+      </c>
+      <c r="N697" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O697" s="1">
+        <v>0</v>
+      </c>
+      <c r="P697" t="str">
+        <v/>
+      </c>
+      <c r="Q697" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R697" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>T260701-00014</v>
+      </c>
+      <c r="B698" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C698" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D698" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E698" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F698">
+        <v>1</v>
+      </c>
+      <c r="G698" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H698" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I698" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J698" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K698">
+        <v>1</v>
+      </c>
+      <c r="L698" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M698" t="str">
+        <v>2026-07-01 19:41:41</v>
+      </c>
+      <c r="N698" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O698" s="1">
+        <v>0</v>
+      </c>
+      <c r="P698" t="str">
+        <v/>
+      </c>
+      <c r="Q698" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R698" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>T260701-00013</v>
+      </c>
+      <c r="B699" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C699" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D699" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E699" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F699">
+        <v>1</v>
+      </c>
+      <c r="G699" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H699" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I699" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J699" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K699">
+        <v>1</v>
+      </c>
+      <c r="L699" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M699" t="str">
+        <v>2026-07-01 19:41:08</v>
+      </c>
+      <c r="N699" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O699" s="1">
+        <v>0</v>
+      </c>
+      <c r="P699" t="str">
+        <v/>
+      </c>
+      <c r="Q699" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R699" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
+        <v>T260701-00012</v>
+      </c>
+      <c r="B700" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C700" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D700" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E700" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F700">
+        <v>1</v>
+      </c>
+      <c r="G700" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H700" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I700" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J700" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K700">
+        <v>1</v>
+      </c>
+      <c r="L700" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M700" t="str">
+        <v>2026-07-01 19:40:45</v>
+      </c>
+      <c r="N700" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O700" s="1">
+        <v>0</v>
+      </c>
+      <c r="P700" t="str">
+        <v/>
+      </c>
+      <c r="Q700" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R700" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>T260701-00011</v>
+      </c>
+      <c r="B701" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C701" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D701" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E701" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F701">
+        <v>0</v>
+      </c>
+      <c r="G701" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H701" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I701" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J701" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K701">
+        <v>1</v>
+      </c>
+      <c r="L701" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M701" t="str">
+        <v>2026-07-01 19:40:21</v>
+      </c>
+      <c r="N701" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O701" s="1">
+        <v>0</v>
+      </c>
+      <c r="P701" t="str">
+        <v/>
+      </c>
+      <c r="Q701" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R701" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>T260701-00010</v>
+      </c>
+      <c r="B702" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C702" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D702" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E702" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F702">
+        <v>1</v>
+      </c>
+      <c r="G702" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H702" t="str">
+        <v>경산시 해오름길114-2 경산FDC</v>
+      </c>
+      <c r="I702" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J702" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K702">
+        <v>1</v>
+      </c>
+      <c r="L702" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M702" t="str">
+        <v>2026-07-01 19:40:04</v>
+      </c>
+      <c r="N702" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O702" s="1">
+        <v>0</v>
+      </c>
+      <c r="P702" t="str">
+        <v/>
+      </c>
+      <c r="Q702" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R702" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>T260701-00009</v>
+      </c>
+      <c r="B703" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C703" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D703" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E703" t="str">
+        <v>2026-07-01 17:30</v>
+      </c>
+      <c r="F703">
+        <v>0</v>
+      </c>
+      <c r="G703" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H703" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I703" t="str">
+        <v>2026-07-01 18:30</v>
+      </c>
+      <c r="J703" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K703">
+        <v>1</v>
+      </c>
+      <c r="L703" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M703" t="str">
+        <v>2026-07-01 19:31:35</v>
+      </c>
+      <c r="N703" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O703" s="1">
+        <v>0</v>
+      </c>
+      <c r="P703" t="str">
+        <v/>
+      </c>
+      <c r="Q703" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R703" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>T260701-00008</v>
+      </c>
+      <c r="B704" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C704" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D704" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E704" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="F704">
+        <v>0</v>
+      </c>
+      <c r="G704" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H704" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I704" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="J704" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K704">
+        <v>1</v>
+      </c>
+      <c r="L704" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M704" t="str">
+        <v>2026-07-01 19:31:02</v>
+      </c>
+      <c r="N704" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O704" s="1">
+        <v>0</v>
+      </c>
+      <c r="P704" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q704" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R704" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
+        <v>T260701-00007</v>
+      </c>
+      <c r="B705" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C705" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D705" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E705" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F705">
+        <v>0</v>
+      </c>
+      <c r="G705" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H705" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I705" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="J705" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K705">
+        <v>1</v>
+      </c>
+      <c r="L705" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M705" t="str">
+        <v>2026-07-01 19:29:27</v>
+      </c>
+      <c r="N705" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O705" s="1">
+        <v>0</v>
+      </c>
+      <c r="P705" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q705" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R705" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
+        <v>T260701-00006</v>
+      </c>
+      <c r="B706" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C706" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D706" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E706" t="str">
+        <v>2026-07-01 16:30</v>
+      </c>
+      <c r="F706">
+        <v>0</v>
+      </c>
+      <c r="G706" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H706" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I706" t="str">
+        <v>2026-07-01 18:00</v>
+      </c>
+      <c r="J706" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K706">
+        <v>1</v>
+      </c>
+      <c r="L706" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M706" t="str">
+        <v>2026-07-01 16:09:24</v>
+      </c>
+      <c r="N706" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O706" s="1">
+        <v>0</v>
+      </c>
+      <c r="P706" t="str">
+        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q706" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R706" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
+        <v>T260701-00005</v>
+      </c>
+      <c r="B707" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C707" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D707" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E707" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="F707">
+        <v>0</v>
+      </c>
+      <c r="G707" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H707" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I707" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J707" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K707">
+        <v>1</v>
+      </c>
+      <c r="L707" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M707" t="str">
+        <v>2026-07-01 14:58:37</v>
+      </c>
+      <c r="N707" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O707" s="1">
+        <v>0</v>
+      </c>
+      <c r="P707" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q707" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R707" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="str">
+        <v>T260701-00004</v>
+      </c>
+      <c r="B708" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C708" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D708" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E708" t="str">
+        <v>2026-07-01 15:20</v>
+      </c>
+      <c r="F708">
+        <v>0</v>
+      </c>
+      <c r="G708" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H708" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I708" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J708" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K708">
+        <v>1</v>
+      </c>
+      <c r="L708" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M708" t="str">
+        <v>2026-07-01 14:53:20</v>
+      </c>
+      <c r="N708" s="1">
+        <v>440000</v>
+      </c>
+      <c r="O708" s="1">
+        <v>0</v>
+      </c>
+      <c r="P708" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q708" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R708" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="str">
+        <v>T260701-00003</v>
+      </c>
+      <c r="B709" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C709" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D709" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E709" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F709">
+        <v>0</v>
+      </c>
+      <c r="G709" t="str">
+        <v>하이얼(이천다코넷)</v>
+      </c>
+      <c r="H709" t="str">
+        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
+      </c>
+      <c r="I709" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J709" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K709">
+        <v>1</v>
+      </c>
+      <c r="L709" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M709" t="str">
+        <v>2026-07-01 10:15:38</v>
+      </c>
+      <c r="N709" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O709" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P709" t="str">
+        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
+      </c>
+      <c r="Q709" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R709" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="str">
+        <v>T260701-00002</v>
+      </c>
+      <c r="B710" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C710" t="str">
+        <v>청주ARC(디지탈태양)</v>
+      </c>
+      <c r="D710" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
+      </c>
+      <c r="E710" t="str">
+        <v>2026-07-01 08:30</v>
+      </c>
+      <c r="F710">
+        <v>0</v>
+      </c>
+      <c r="G710" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H710" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="I710" t="str">
+        <v>2026-07-01 10:30</v>
+      </c>
+      <c r="J710" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K710">
+        <v>1</v>
+      </c>
+      <c r="L710" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M710" t="str">
+        <v>2026-07-01 10:13:39</v>
+      </c>
+      <c r="N710" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O710" s="1">
+        <v>0</v>
+      </c>
+      <c r="P710" t="str">
+        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
+      </c>
+      <c r="Q710" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R710" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="str">
+        <v>T260701-00001</v>
+      </c>
+      <c r="B711" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C711" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D711" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E711" t="str">
+        <v>2026-07-01 09:00</v>
+      </c>
+      <c r="F711">
+        <v>0</v>
+      </c>
+      <c r="G711" t="str">
+        <v>현대클러스터 한강미사3차</v>
+      </c>
+      <c r="H711" t="str">
+        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
+      </c>
+      <c r="I711" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J711" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K711">
+        <v>1</v>
+      </c>
+      <c r="L711" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M711" t="str">
+        <v>2026-07-01 09:07:09</v>
+      </c>
+      <c r="N711" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O711" s="1">
+        <v>0</v>
+      </c>
+      <c r="P711" t="str">
+        <v>스마트윈드 출하</v>
+      </c>
+      <c r="Q711" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R711" t="str">
+        <v>스마트윈드</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R685"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R711"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R711"/>
+  <dimension ref="A1:R658"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -37228,2977 +37228,9 @@
         <v>일코전자</v>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="str">
-        <v>T260702-00027</v>
-      </c>
-      <c r="B659" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C659" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D659" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E659" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F659">
-        <v>1</v>
-      </c>
-      <c r="G659" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H659" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I659" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J659" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K659">
-        <v>1</v>
-      </c>
-      <c r="L659" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M659" t="str">
-        <v>2026-07-02 20:54:21</v>
-      </c>
-      <c r="N659" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O659" s="1">
-        <v>0</v>
-      </c>
-      <c r="P659" t="str">
-        <v/>
-      </c>
-      <c r="Q659" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R659" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="str">
-        <v>T260702-00026</v>
-      </c>
-      <c r="B660" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C660" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D660" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E660" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F660">
-        <v>1</v>
-      </c>
-      <c r="G660" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H660" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I660" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J660" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K660">
-        <v>1</v>
-      </c>
-      <c r="L660" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M660" t="str">
-        <v>2026-07-02 20:53:56</v>
-      </c>
-      <c r="N660" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O660" s="1">
-        <v>0</v>
-      </c>
-      <c r="P660" t="str">
-        <v/>
-      </c>
-      <c r="Q660" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R660" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="str">
-        <v>T260702-00025</v>
-      </c>
-      <c r="B661" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C661" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D661" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E661" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F661">
-        <v>3</v>
-      </c>
-      <c r="G661" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H661" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I661" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J661" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K661">
-        <v>1</v>
-      </c>
-      <c r="L661" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M661" t="str">
-        <v>2026-07-02 20:53:28</v>
-      </c>
-      <c r="N661" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O661" s="1">
-        <v>0</v>
-      </c>
-      <c r="P661" t="str">
-        <v/>
-      </c>
-      <c r="Q661" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R661" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="str">
-        <v>T260702-00024</v>
-      </c>
-      <c r="B662" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C662" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D662" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E662" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F662">
-        <v>0</v>
-      </c>
-      <c r="G662" t="str">
-        <v>용인ACP</v>
-      </c>
-      <c r="H662" t="str">
-        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
-      </c>
-      <c r="I662" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J662" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K662">
-        <v>1</v>
-      </c>
-      <c r="L662" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M662" t="str">
-        <v>2026-07-02 20:52:18</v>
-      </c>
-      <c r="N662" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O662" s="1">
-        <v>0</v>
-      </c>
-      <c r="P662" t="str">
-        <v/>
-      </c>
-      <c r="Q662" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R662" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="str">
-        <v>T260702-00023</v>
-      </c>
-      <c r="B663" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C663" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D663" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E663" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F663">
-        <v>1</v>
-      </c>
-      <c r="G663" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H663" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I663" t="str">
-        <v>2026-07-03 07:00</v>
-      </c>
-      <c r="J663" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K663">
-        <v>1</v>
-      </c>
-      <c r="L663" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M663" t="str">
-        <v>2026-07-02 20:51:59</v>
-      </c>
-      <c r="N663" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O663" s="1">
-        <v>0</v>
-      </c>
-      <c r="P663" t="str">
-        <v/>
-      </c>
-      <c r="Q663" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R663" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="str">
-        <v>T260702-00022</v>
-      </c>
-      <c r="B664" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C664" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D664" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E664" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F664">
-        <v>0</v>
-      </c>
-      <c r="G664" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H664" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I664" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J664" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K664">
-        <v>1</v>
-      </c>
-      <c r="L664" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M664" t="str">
-        <v>2026-07-02 20:51:32</v>
-      </c>
-      <c r="N664" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O664" s="1">
-        <v>0</v>
-      </c>
-      <c r="P664" t="str">
-        <v/>
-      </c>
-      <c r="Q664" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R664" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="str">
-        <v>T260702-00021</v>
-      </c>
-      <c r="B665" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C665" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D665" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E665" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F665">
-        <v>1</v>
-      </c>
-      <c r="G665" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H665" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I665" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J665" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K665">
-        <v>1</v>
-      </c>
-      <c r="L665" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M665" t="str">
-        <v>2026-07-02 20:51:14</v>
-      </c>
-      <c r="N665" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O665" s="1">
-        <v>0</v>
-      </c>
-      <c r="P665" t="str">
-        <v/>
-      </c>
-      <c r="Q665" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R665" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="str">
-        <v>T260702-00020</v>
-      </c>
-      <c r="B666" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C666" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D666" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E666" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F666">
-        <v>0</v>
-      </c>
-      <c r="G666" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="H666" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="I666" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J666" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K666">
-        <v>1</v>
-      </c>
-      <c r="L666" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M666" t="str">
-        <v>2026-07-02 20:50:54</v>
-      </c>
-      <c r="N666" s="1">
-        <v>280000</v>
-      </c>
-      <c r="O666" s="1">
-        <v>0</v>
-      </c>
-      <c r="P666" t="str">
-        <v/>
-      </c>
-      <c r="Q666" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R666" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="str">
-        <v>T260702-00019</v>
-      </c>
-      <c r="B667" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C667" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D667" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E667" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F667">
-        <v>0</v>
-      </c>
-      <c r="G667" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H667" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I667" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J667" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K667">
-        <v>1</v>
-      </c>
-      <c r="L667" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M667" t="str">
-        <v>2026-07-02 20:50:36</v>
-      </c>
-      <c r="N667" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O667" s="1">
-        <v>0</v>
-      </c>
-      <c r="P667" t="str">
-        <v/>
-      </c>
-      <c r="Q667" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R667" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="str">
-        <v>T260702-00018</v>
-      </c>
-      <c r="B668" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C668" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D668" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E668" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F668">
-        <v>1</v>
-      </c>
-      <c r="G668" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H668" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I668" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J668" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K668">
-        <v>1</v>
-      </c>
-      <c r="L668" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M668" t="str">
-        <v>2026-07-02 20:50:19</v>
-      </c>
-      <c r="N668" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O668" s="1">
-        <v>0</v>
-      </c>
-      <c r="P668" t="str">
-        <v/>
-      </c>
-      <c r="Q668" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R668" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="str">
-        <v>T260702-00017</v>
-      </c>
-      <c r="B669" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C669" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D669" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E669" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F669">
-        <v>1</v>
-      </c>
-      <c r="G669" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H669" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I669" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J669" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K669">
-        <v>1</v>
-      </c>
-      <c r="L669" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M669" t="str">
-        <v>2026-07-02 20:49:56</v>
-      </c>
-      <c r="N669" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O669" s="1">
-        <v>0</v>
-      </c>
-      <c r="P669" t="str">
-        <v/>
-      </c>
-      <c r="Q669" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R669" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="str">
-        <v>T260702-00016</v>
-      </c>
-      <c r="B670" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C670" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D670" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E670" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F670">
-        <v>0</v>
-      </c>
-      <c r="G670" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H670" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I670" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J670" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K670">
-        <v>1</v>
-      </c>
-      <c r="L670" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M670" t="str">
-        <v>2026-07-02 20:49:25</v>
-      </c>
-      <c r="N670" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O670" s="1">
-        <v>0</v>
-      </c>
-      <c r="P670" t="str">
-        <v/>
-      </c>
-      <c r="Q670" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R670" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="str">
-        <v>T260702-00015</v>
-      </c>
-      <c r="B671" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C671" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D671" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E671" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F671">
-        <v>1</v>
-      </c>
-      <c r="G671" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H671" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I671" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J671" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K671">
-        <v>1</v>
-      </c>
-      <c r="L671" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M671" t="str">
-        <v>2026-07-02 20:48:50</v>
-      </c>
-      <c r="N671" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O671" s="1">
-        <v>0</v>
-      </c>
-      <c r="P671" t="str">
-        <v/>
-      </c>
-      <c r="Q671" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R671" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="str">
-        <v>T260702-00014</v>
-      </c>
-      <c r="B672" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C672" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D672" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E672" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F672">
-        <v>0</v>
-      </c>
-      <c r="G672" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H672" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I672" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J672" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K672">
-        <v>1</v>
-      </c>
-      <c r="L672" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M672" t="str">
-        <v>2026-07-02 20:48:25</v>
-      </c>
-      <c r="N672" s="1">
-        <v>420000</v>
-      </c>
-      <c r="O672" s="1">
-        <v>0</v>
-      </c>
-      <c r="P672" t="str">
-        <v/>
-      </c>
-      <c r="Q672" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R672" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="str">
-        <v>T260702-00013</v>
-      </c>
-      <c r="B673" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C673" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D673" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E673" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F673">
-        <v>0</v>
-      </c>
-      <c r="G673" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H673" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I673" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J673" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K673">
-        <v>1</v>
-      </c>
-      <c r="L673" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M673" t="str">
-        <v>2026-07-02 20:48:09</v>
-      </c>
-      <c r="N673" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O673" s="1">
-        <v>0</v>
-      </c>
-      <c r="P673" t="str">
-        <v/>
-      </c>
-      <c r="Q673" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R673" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="str">
-        <v>T260702-00012</v>
-      </c>
-      <c r="B674" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C674" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D674" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E674" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F674">
-        <v>2</v>
-      </c>
-      <c r="G674" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H674" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I674" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J674" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K674">
-        <v>1</v>
-      </c>
-      <c r="L674" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M674" t="str">
-        <v>2026-07-02 20:47:49</v>
-      </c>
-      <c r="N674" s="1">
-        <v>680000</v>
-      </c>
-      <c r="O674" s="1">
-        <v>0</v>
-      </c>
-      <c r="P674" t="str">
-        <v/>
-      </c>
-      <c r="Q674" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R674" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="str">
-        <v>T260702-00011</v>
-      </c>
-      <c r="B675" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C675" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D675" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E675" t="str">
-        <v>2026-07-02 17:50</v>
-      </c>
-      <c r="F675">
-        <v>0</v>
-      </c>
-      <c r="G675" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H675" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I675" t="str">
-        <v>2026-07-02 18:50</v>
-      </c>
-      <c r="J675" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K675">
-        <v>1</v>
-      </c>
-      <c r="L675" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M675" t="str">
-        <v>2026-07-02 20:44:59</v>
-      </c>
-      <c r="N675" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O675" s="1">
-        <v>0</v>
-      </c>
-      <c r="P675" t="str">
-        <v/>
-      </c>
-      <c r="Q675" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R675" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="str">
-        <v>T260702-00010</v>
-      </c>
-      <c r="B676" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C676" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D676" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E676" t="str">
-        <v>2026-07-02 13:30</v>
-      </c>
-      <c r="F676">
-        <v>0</v>
-      </c>
-      <c r="G676" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H676" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I676" t="str">
-        <v>2026-07-02 15:40</v>
-      </c>
-      <c r="J676" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K676">
-        <v>1</v>
-      </c>
-      <c r="L676" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M676" t="str">
-        <v>2026-07-02 20:44:26</v>
-      </c>
-      <c r="N676" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O676" s="1">
-        <v>0</v>
-      </c>
-      <c r="P676" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q676" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R676" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="str">
-        <v>T260702-00009</v>
-      </c>
-      <c r="B677" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C677" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D677" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E677" t="str">
-        <v>2026-07-02 10:00</v>
-      </c>
-      <c r="F677">
-        <v>0</v>
-      </c>
-      <c r="G677" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H677" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I677" t="str">
-        <v>2026-07-02 13:40</v>
-      </c>
-      <c r="J677" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K677">
-        <v>1</v>
-      </c>
-      <c r="L677" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M677" t="str">
-        <v>2026-07-02 20:43:37</v>
-      </c>
-      <c r="N677" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O677" s="1">
-        <v>0</v>
-      </c>
-      <c r="P677" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q677" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R677" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="str">
-        <v>T260702-00008</v>
-      </c>
-      <c r="B678" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C678" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D678" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E678" t="str">
-        <v>2026-07-02 17:00</v>
-      </c>
-      <c r="F678">
-        <v>0</v>
-      </c>
-      <c r="G678" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="H678" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="I678" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J678" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K678">
-        <v>1</v>
-      </c>
-      <c r="L678" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M678" t="str">
-        <v>2026-07-02 16:38:23</v>
-      </c>
-      <c r="N678" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O678" s="1">
-        <v>0</v>
-      </c>
-      <c r="P678" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="Q678" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R678" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="str">
-        <v>T260702-00007</v>
-      </c>
-      <c r="B679" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C679" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D679" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E679" t="str">
-        <v>2026-07-02 16:30</v>
-      </c>
-      <c r="F679">
-        <v>0</v>
-      </c>
-      <c r="G679" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H679" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I679" t="str">
-        <v>2026-07-02 18:00</v>
-      </c>
-      <c r="J679" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K679">
-        <v>1</v>
-      </c>
-      <c r="L679" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M679" t="str">
-        <v>2026-07-02 16:34:35</v>
-      </c>
-      <c r="N679" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O679" s="1">
-        <v>0</v>
-      </c>
-      <c r="P679" t="str">
-        <v>20260702/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q679" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R679" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="str">
-        <v>T260702-00006</v>
-      </c>
-      <c r="B680" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C680" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D680" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E680" t="str">
-        <v>2026-07-02 16:00</v>
-      </c>
-      <c r="F680">
-        <v>0</v>
-      </c>
-      <c r="G680" t="str">
-        <v>광주 하이마트 물류</v>
-      </c>
-      <c r="H680" t="str">
-        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
-      </c>
-      <c r="I680" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J680" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K680">
-        <v>1</v>
-      </c>
-      <c r="L680" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M680" t="str">
-        <v>2026-07-02 15:30:55</v>
-      </c>
-      <c r="N680" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O680" s="1">
-        <v>0</v>
-      </c>
-      <c r="P680" t="str">
-        <v>일코 광주 하이마트 물류</v>
-      </c>
-      <c r="Q680" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R680" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="str">
-        <v>T260702-00005</v>
-      </c>
-      <c r="B681" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C681" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D681" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E681" t="str">
-        <v>2026-07-02 14:30</v>
-      </c>
-      <c r="F681">
-        <v>0</v>
-      </c>
-      <c r="G681" t="str">
-        <v>마산 하이마트 물류</v>
-      </c>
-      <c r="H681" t="str">
-        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
-      </c>
-      <c r="I681" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J681" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K681">
-        <v>1</v>
-      </c>
-      <c r="L681" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M681" t="str">
-        <v>2026-07-02 13:44:41</v>
-      </c>
-      <c r="N681" s="1">
-        <v>380000</v>
-      </c>
-      <c r="O681" s="1">
-        <v>0</v>
-      </c>
-      <c r="P681" t="str">
-        <v>일코 마산 하이마트 물류</v>
-      </c>
-      <c r="Q681" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R681" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="str">
-        <v>T260702-00004</v>
-      </c>
-      <c r="B682" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C682" t="str">
-        <v>강릉 하이마트 물류</v>
-      </c>
-      <c r="D682" t="str">
-        <v>강원특별자치도 강릉시 연곡면 동해대로 4100-36 강릉 하이마트 물류</v>
-      </c>
-      <c r="E682" t="str">
-        <v>2026-07-02 13:30</v>
-      </c>
-      <c r="F682">
-        <v>0</v>
-      </c>
-      <c r="G682" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H682" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I682" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J682" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K682">
-        <v>1</v>
-      </c>
-      <c r="L682" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M682" t="str">
-        <v>2026-07-02 12:00:10</v>
-      </c>
-      <c r="N682" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O682" s="1">
-        <v>0</v>
-      </c>
-      <c r="P682" t="str">
-        <v>일코전자 강릉 하이마트 물류</v>
-      </c>
-      <c r="Q682" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R682" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="str">
-        <v>T260702-00003</v>
-      </c>
-      <c r="B683" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C683" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D683" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E683" t="str">
-        <v>2026-07-02 14:30</v>
-      </c>
-      <c r="F683">
-        <v>0</v>
-      </c>
-      <c r="G683" t="str">
-        <v>대구 하이마트 물류</v>
-      </c>
-      <c r="H683" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="I683" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J683" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K683">
-        <v>1</v>
-      </c>
-      <c r="L683" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M683" t="str">
-        <v>2026-07-02 11:59:32</v>
-      </c>
-      <c r="N683" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O683" s="1">
-        <v>0</v>
-      </c>
-      <c r="P683" t="str">
-        <v>일코전자 대구 하이마트 물류</v>
-      </c>
-      <c r="Q683" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R683" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="str">
-        <v>T260702-00002</v>
-      </c>
-      <c r="B684" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C684" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D684" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E684" t="str">
-        <v>2026-07-02 09:30</v>
-      </c>
-      <c r="F684">
-        <v>1</v>
-      </c>
-      <c r="G684" t="str">
-        <v>하이얼(대구2착)</v>
-      </c>
-      <c r="H684" t="str">
-        <v>대구 남구 양지로 25 대명자이 아파트</v>
-      </c>
-      <c r="I684" t="str">
-        <v>2026-07-02 15:00</v>
-      </c>
-      <c r="J684" t="str">
-        <v>1.5톤 윙바디</v>
-      </c>
-      <c r="K684">
-        <v>1</v>
-      </c>
-      <c r="L684" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M684" t="str">
-        <v>2026-07-02 09:20:07</v>
-      </c>
-      <c r="N684" s="1">
-        <v>220000</v>
-      </c>
-      <c r="O684" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P684" t="str">
-        <v>20260702/하이얼_대구 착지 2곳_벌크_출하</v>
-      </c>
-      <c r="Q684" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R684" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="str">
-        <v>T260702-00001</v>
-      </c>
-      <c r="B685" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C685" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D685" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E685" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="F685">
-        <v>0</v>
-      </c>
-      <c r="G685" t="str">
-        <v>로지스밸리인천포트(Logisvalley)</v>
-      </c>
-      <c r="H685" t="str">
-        <v>인천 연수구 인천타워대로599번길 60 로지스밸리인천포트(Logisvalley) 1층 13번(HTC)</v>
-      </c>
-      <c r="I685" t="str">
-        <v>2026-07-02 11:00</v>
-      </c>
-      <c r="J685" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K685">
-        <v>1</v>
-      </c>
-      <c r="L685" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M685" t="str">
-        <v>2026-07-02 09:17:29</v>
-      </c>
-      <c r="N685" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O685" s="1">
-        <v>0</v>
-      </c>
-      <c r="P685" t="str">
-        <v>패스트레인 출하</v>
-      </c>
-      <c r="Q685" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R685" t="str">
-        <v>패스트레인코리아</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="str">
-        <v>T260701-00026</v>
-      </c>
-      <c r="B686" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C686" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D686" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E686" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F686">
-        <v>1</v>
-      </c>
-      <c r="G686" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H686" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I686" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J686" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K686">
-        <v>1</v>
-      </c>
-      <c r="L686" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M686" t="str">
-        <v>2026-07-01 19:47:13</v>
-      </c>
-      <c r="N686" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O686" s="1">
-        <v>0</v>
-      </c>
-      <c r="P686" t="str">
-        <v/>
-      </c>
-      <c r="Q686" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R686" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="str">
-        <v>T260701-00025</v>
-      </c>
-      <c r="B687" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C687" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D687" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E687" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F687">
-        <v>2</v>
-      </c>
-      <c r="G687" t="str">
-        <v>원주ACP</v>
-      </c>
-      <c r="H687" t="str">
-        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
-      </c>
-      <c r="I687" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J687" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K687">
-        <v>1</v>
-      </c>
-      <c r="L687" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M687" t="str">
-        <v>2026-07-01 19:46:48</v>
-      </c>
-      <c r="N687" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O687" s="1">
-        <v>0</v>
-      </c>
-      <c r="P687" t="str">
-        <v/>
-      </c>
-      <c r="Q687" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R687" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="str">
-        <v>T260701-00024</v>
-      </c>
-      <c r="B688" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C688" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D688" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E688" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F688">
-        <v>1</v>
-      </c>
-      <c r="G688" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H688" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I688" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J688" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K688">
-        <v>1</v>
-      </c>
-      <c r="L688" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M688" t="str">
-        <v>2026-07-01 19:46:12</v>
-      </c>
-      <c r="N688" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O688" s="1">
-        <v>0</v>
-      </c>
-      <c r="P688" t="str">
-        <v/>
-      </c>
-      <c r="Q688" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R688" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="str">
-        <v>T260701-00023</v>
-      </c>
-      <c r="B689" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C689" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D689" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E689" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F689">
-        <v>3</v>
-      </c>
-      <c r="G689" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H689" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I689" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J689" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K689">
-        <v>1</v>
-      </c>
-      <c r="L689" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M689" t="str">
-        <v>2026-07-01 19:45:40</v>
-      </c>
-      <c r="N689" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O689" s="1">
-        <v>0</v>
-      </c>
-      <c r="P689" t="str">
-        <v/>
-      </c>
-      <c r="Q689" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R689" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="str">
-        <v>T260701-00022</v>
-      </c>
-      <c r="B690" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C690" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D690" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E690" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F690">
-        <v>0</v>
-      </c>
-      <c r="G690" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H690" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I690" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J690" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K690">
-        <v>1</v>
-      </c>
-      <c r="L690" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M690" t="str">
-        <v>2026-07-01 19:44:56</v>
-      </c>
-      <c r="N690" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O690" s="1">
-        <v>0</v>
-      </c>
-      <c r="P690" t="str">
-        <v/>
-      </c>
-      <c r="Q690" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R690" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="str">
-        <v>T260701-00021</v>
-      </c>
-      <c r="B691" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C691" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D691" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E691" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F691">
-        <v>1</v>
-      </c>
-      <c r="G691" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H691" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I691" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J691" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K691">
-        <v>1</v>
-      </c>
-      <c r="L691" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M691" t="str">
-        <v>2026-07-01 19:44:37</v>
-      </c>
-      <c r="N691" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O691" s="1">
-        <v>0</v>
-      </c>
-      <c r="P691" t="str">
-        <v/>
-      </c>
-      <c r="Q691" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R691" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="str">
-        <v>T260701-00020</v>
-      </c>
-      <c r="B692" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C692" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D692" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E692" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F692">
-        <v>2</v>
-      </c>
-      <c r="G692" t="str">
-        <v>속초ACP</v>
-      </c>
-      <c r="H692" t="str">
-        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
-      </c>
-      <c r="I692" t="str">
-        <v>2026-07-02 06:00</v>
-      </c>
-      <c r="J692" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K692">
-        <v>1</v>
-      </c>
-      <c r="L692" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M692" t="str">
-        <v>2026-07-01 19:44:05</v>
-      </c>
-      <c r="N692" s="1">
-        <v>320000</v>
-      </c>
-      <c r="O692" s="1">
-        <v>0</v>
-      </c>
-      <c r="P692" t="str">
-        <v/>
-      </c>
-      <c r="Q692" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R692" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="str">
-        <v>T260701-00019</v>
-      </c>
-      <c r="B693" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C693" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D693" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E693" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F693">
-        <v>0</v>
-      </c>
-      <c r="G693" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H693" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I693" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J693" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K693">
-        <v>1</v>
-      </c>
-      <c r="L693" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M693" t="str">
-        <v>2026-07-01 19:43:22</v>
-      </c>
-      <c r="N693" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O693" s="1">
-        <v>0</v>
-      </c>
-      <c r="P693" t="str">
-        <v/>
-      </c>
-      <c r="Q693" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R693" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="str">
-        <v>T260701-00018</v>
-      </c>
-      <c r="B694" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C694" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D694" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E694" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F694">
-        <v>1</v>
-      </c>
-      <c r="G694" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H694" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I694" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J694" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K694">
-        <v>1</v>
-      </c>
-      <c r="L694" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M694" t="str">
-        <v>2026-07-01 19:43:03</v>
-      </c>
-      <c r="N694" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O694" s="1">
-        <v>0</v>
-      </c>
-      <c r="P694" t="str">
-        <v/>
-      </c>
-      <c r="Q694" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R694" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="str">
-        <v>T260701-00017</v>
-      </c>
-      <c r="B695" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C695" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D695" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E695" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F695">
-        <v>0</v>
-      </c>
-      <c r="G695" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H695" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I695" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J695" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K695">
-        <v>1</v>
-      </c>
-      <c r="L695" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M695" t="str">
-        <v>2026-07-01 19:42:39</v>
-      </c>
-      <c r="N695" s="1">
-        <v>310000</v>
-      </c>
-      <c r="O695" s="1">
-        <v>0</v>
-      </c>
-      <c r="P695" t="str">
-        <v/>
-      </c>
-      <c r="Q695" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R695" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="str">
-        <v>T260701-00016</v>
-      </c>
-      <c r="B696" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C696" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D696" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E696" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F696">
-        <v>0</v>
-      </c>
-      <c r="G696" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H696" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I696" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J696" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K696">
-        <v>1</v>
-      </c>
-      <c r="L696" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M696" t="str">
-        <v>2026-07-01 19:42:17</v>
-      </c>
-      <c r="N696" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O696" s="1">
-        <v>0</v>
-      </c>
-      <c r="P696" t="str">
-        <v/>
-      </c>
-      <c r="Q696" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R696" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="str">
-        <v>T260701-00015</v>
-      </c>
-      <c r="B697" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C697" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D697" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E697" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F697">
-        <v>1</v>
-      </c>
-      <c r="G697" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H697" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I697" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J697" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K697">
-        <v>1</v>
-      </c>
-      <c r="L697" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M697" t="str">
-        <v>2026-07-01 19:42:02</v>
-      </c>
-      <c r="N697" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O697" s="1">
-        <v>0</v>
-      </c>
-      <c r="P697" t="str">
-        <v/>
-      </c>
-      <c r="Q697" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R697" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="str">
-        <v>T260701-00014</v>
-      </c>
-      <c r="B698" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C698" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D698" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E698" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F698">
-        <v>1</v>
-      </c>
-      <c r="G698" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H698" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I698" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J698" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K698">
-        <v>1</v>
-      </c>
-      <c r="L698" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M698" t="str">
-        <v>2026-07-01 19:41:41</v>
-      </c>
-      <c r="N698" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O698" s="1">
-        <v>0</v>
-      </c>
-      <c r="P698" t="str">
-        <v/>
-      </c>
-      <c r="Q698" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R698" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="str">
-        <v>T260701-00013</v>
-      </c>
-      <c r="B699" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C699" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D699" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E699" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F699">
-        <v>1</v>
-      </c>
-      <c r="G699" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H699" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I699" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J699" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K699">
-        <v>1</v>
-      </c>
-      <c r="L699" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M699" t="str">
-        <v>2026-07-01 19:41:08</v>
-      </c>
-      <c r="N699" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O699" s="1">
-        <v>0</v>
-      </c>
-      <c r="P699" t="str">
-        <v/>
-      </c>
-      <c r="Q699" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R699" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="str">
-        <v>T260701-00012</v>
-      </c>
-      <c r="B700" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C700" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D700" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E700" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F700">
-        <v>1</v>
-      </c>
-      <c r="G700" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H700" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I700" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J700" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K700">
-        <v>1</v>
-      </c>
-      <c r="L700" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M700" t="str">
-        <v>2026-07-01 19:40:45</v>
-      </c>
-      <c r="N700" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O700" s="1">
-        <v>0</v>
-      </c>
-      <c r="P700" t="str">
-        <v/>
-      </c>
-      <c r="Q700" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R700" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="str">
-        <v>T260701-00011</v>
-      </c>
-      <c r="B701" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C701" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D701" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E701" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F701">
-        <v>0</v>
-      </c>
-      <c r="G701" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H701" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I701" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J701" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K701">
-        <v>1</v>
-      </c>
-      <c r="L701" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M701" t="str">
-        <v>2026-07-01 19:40:21</v>
-      </c>
-      <c r="N701" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O701" s="1">
-        <v>0</v>
-      </c>
-      <c r="P701" t="str">
-        <v/>
-      </c>
-      <c r="Q701" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R701" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="str">
-        <v>T260701-00010</v>
-      </c>
-      <c r="B702" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C702" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D702" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E702" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F702">
-        <v>1</v>
-      </c>
-      <c r="G702" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H702" t="str">
-        <v>경산시 해오름길114-2 경산FDC</v>
-      </c>
-      <c r="I702" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J702" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K702">
-        <v>1</v>
-      </c>
-      <c r="L702" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M702" t="str">
-        <v>2026-07-01 19:40:04</v>
-      </c>
-      <c r="N702" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O702" s="1">
-        <v>0</v>
-      </c>
-      <c r="P702" t="str">
-        <v/>
-      </c>
-      <c r="Q702" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R702" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="str">
-        <v>T260701-00009</v>
-      </c>
-      <c r="B703" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C703" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D703" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E703" t="str">
-        <v>2026-07-01 17:30</v>
-      </c>
-      <c r="F703">
-        <v>0</v>
-      </c>
-      <c r="G703" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H703" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I703" t="str">
-        <v>2026-07-01 18:30</v>
-      </c>
-      <c r="J703" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K703">
-        <v>1</v>
-      </c>
-      <c r="L703" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M703" t="str">
-        <v>2026-07-01 19:31:35</v>
-      </c>
-      <c r="N703" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O703" s="1">
-        <v>0</v>
-      </c>
-      <c r="P703" t="str">
-        <v/>
-      </c>
-      <c r="Q703" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R703" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="str">
-        <v>T260701-00008</v>
-      </c>
-      <c r="B704" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C704" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D704" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E704" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="F704">
-        <v>0</v>
-      </c>
-      <c r="G704" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H704" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I704" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="J704" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K704">
-        <v>1</v>
-      </c>
-      <c r="L704" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M704" t="str">
-        <v>2026-07-01 19:31:02</v>
-      </c>
-      <c r="N704" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O704" s="1">
-        <v>0</v>
-      </c>
-      <c r="P704" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q704" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R704" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="str">
-        <v>T260701-00007</v>
-      </c>
-      <c r="B705" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C705" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D705" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E705" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F705">
-        <v>0</v>
-      </c>
-      <c r="G705" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H705" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I705" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="J705" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K705">
-        <v>1</v>
-      </c>
-      <c r="L705" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M705" t="str">
-        <v>2026-07-01 19:29:27</v>
-      </c>
-      <c r="N705" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O705" s="1">
-        <v>0</v>
-      </c>
-      <c r="P705" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q705" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R705" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="str">
-        <v>T260701-00006</v>
-      </c>
-      <c r="B706" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C706" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D706" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E706" t="str">
-        <v>2026-07-01 16:30</v>
-      </c>
-      <c r="F706">
-        <v>0</v>
-      </c>
-      <c r="G706" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H706" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I706" t="str">
-        <v>2026-07-01 18:00</v>
-      </c>
-      <c r="J706" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K706">
-        <v>1</v>
-      </c>
-      <c r="L706" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M706" t="str">
-        <v>2026-07-01 16:09:24</v>
-      </c>
-      <c r="N706" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O706" s="1">
-        <v>0</v>
-      </c>
-      <c r="P706" t="str">
-        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q706" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R706" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="str">
-        <v>T260701-00005</v>
-      </c>
-      <c r="B707" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C707" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D707" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E707" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="F707">
-        <v>0</v>
-      </c>
-      <c r="G707" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H707" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I707" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J707" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K707">
-        <v>1</v>
-      </c>
-      <c r="L707" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M707" t="str">
-        <v>2026-07-01 14:58:37</v>
-      </c>
-      <c r="N707" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O707" s="1">
-        <v>0</v>
-      </c>
-      <c r="P707" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q707" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R707" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="str">
-        <v>T260701-00004</v>
-      </c>
-      <c r="B708" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C708" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D708" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E708" t="str">
-        <v>2026-07-01 15:20</v>
-      </c>
-      <c r="F708">
-        <v>0</v>
-      </c>
-      <c r="G708" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H708" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I708" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J708" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K708">
-        <v>1</v>
-      </c>
-      <c r="L708" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M708" t="str">
-        <v>2026-07-01 14:53:20</v>
-      </c>
-      <c r="N708" s="1">
-        <v>440000</v>
-      </c>
-      <c r="O708" s="1">
-        <v>0</v>
-      </c>
-      <c r="P708" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q708" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R708" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="str">
-        <v>T260701-00003</v>
-      </c>
-      <c r="B709" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C709" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D709" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E709" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F709">
-        <v>0</v>
-      </c>
-      <c r="G709" t="str">
-        <v>하이얼(이천다코넷)</v>
-      </c>
-      <c r="H709" t="str">
-        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
-      </c>
-      <c r="I709" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J709" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K709">
-        <v>1</v>
-      </c>
-      <c r="L709" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M709" t="str">
-        <v>2026-07-01 10:15:38</v>
-      </c>
-      <c r="N709" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O709" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P709" t="str">
-        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
-      </c>
-      <c r="Q709" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R709" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="str">
-        <v>T260701-00002</v>
-      </c>
-      <c r="B710" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C710" t="str">
-        <v>청주ARC(디지탈태양)</v>
-      </c>
-      <c r="D710" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
-      </c>
-      <c r="E710" t="str">
-        <v>2026-07-01 08:30</v>
-      </c>
-      <c r="F710">
-        <v>0</v>
-      </c>
-      <c r="G710" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H710" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="I710" t="str">
-        <v>2026-07-01 10:30</v>
-      </c>
-      <c r="J710" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K710">
-        <v>1</v>
-      </c>
-      <c r="L710" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M710" t="str">
-        <v>2026-07-01 10:13:39</v>
-      </c>
-      <c r="N710" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O710" s="1">
-        <v>0</v>
-      </c>
-      <c r="P710" t="str">
-        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
-      </c>
-      <c r="Q710" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R710" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="str">
-        <v>T260701-00001</v>
-      </c>
-      <c r="B711" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C711" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D711" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E711" t="str">
-        <v>2026-07-01 09:00</v>
-      </c>
-      <c r="F711">
-        <v>0</v>
-      </c>
-      <c r="G711" t="str">
-        <v>현대클러스터 한강미사3차</v>
-      </c>
-      <c r="H711" t="str">
-        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
-      </c>
-      <c r="I711" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J711" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K711">
-        <v>1</v>
-      </c>
-      <c r="L711" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M711" t="str">
-        <v>2026-07-01 09:07:09</v>
-      </c>
-      <c r="N711" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O711" s="1">
-        <v>0</v>
-      </c>
-      <c r="P711" t="str">
-        <v>스마트윈드 출하</v>
-      </c>
-      <c r="Q711" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R711" t="str">
-        <v>스마트윈드</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R711"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R658"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R742"/>
+  <dimension ref="A1:R689"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38964,2977 +38964,9 @@
         <v>일코전자</v>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="str">
-        <v>T260702-00027</v>
-      </c>
-      <c r="B690" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C690" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D690" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E690" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F690">
-        <v>1</v>
-      </c>
-      <c r="G690" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H690" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I690" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J690" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K690">
-        <v>1</v>
-      </c>
-      <c r="L690" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M690" t="str">
-        <v>2026-07-02 20:54:21</v>
-      </c>
-      <c r="N690" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O690" s="1">
-        <v>0</v>
-      </c>
-      <c r="P690" t="str">
-        <v/>
-      </c>
-      <c r="Q690" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R690" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="str">
-        <v>T260702-00026</v>
-      </c>
-      <c r="B691" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C691" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D691" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E691" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F691">
-        <v>1</v>
-      </c>
-      <c r="G691" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H691" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I691" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J691" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K691">
-        <v>1</v>
-      </c>
-      <c r="L691" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M691" t="str">
-        <v>2026-07-02 20:53:56</v>
-      </c>
-      <c r="N691" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O691" s="1">
-        <v>0</v>
-      </c>
-      <c r="P691" t="str">
-        <v/>
-      </c>
-      <c r="Q691" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R691" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="str">
-        <v>T260702-00025</v>
-      </c>
-      <c r="B692" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C692" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D692" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E692" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F692">
-        <v>3</v>
-      </c>
-      <c r="G692" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H692" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I692" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J692" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K692">
-        <v>1</v>
-      </c>
-      <c r="L692" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M692" t="str">
-        <v>2026-07-02 20:53:28</v>
-      </c>
-      <c r="N692" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O692" s="1">
-        <v>0</v>
-      </c>
-      <c r="P692" t="str">
-        <v/>
-      </c>
-      <c r="Q692" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R692" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="str">
-        <v>T260702-00024</v>
-      </c>
-      <c r="B693" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C693" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D693" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E693" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F693">
-        <v>0</v>
-      </c>
-      <c r="G693" t="str">
-        <v>용인ACP</v>
-      </c>
-      <c r="H693" t="str">
-        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
-      </c>
-      <c r="I693" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J693" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K693">
-        <v>1</v>
-      </c>
-      <c r="L693" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M693" t="str">
-        <v>2026-07-02 20:52:18</v>
-      </c>
-      <c r="N693" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O693" s="1">
-        <v>0</v>
-      </c>
-      <c r="P693" t="str">
-        <v/>
-      </c>
-      <c r="Q693" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R693" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="str">
-        <v>T260702-00023</v>
-      </c>
-      <c r="B694" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C694" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D694" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E694" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F694">
-        <v>1</v>
-      </c>
-      <c r="G694" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H694" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I694" t="str">
-        <v>2026-07-03 07:00</v>
-      </c>
-      <c r="J694" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K694">
-        <v>1</v>
-      </c>
-      <c r="L694" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M694" t="str">
-        <v>2026-07-02 20:51:59</v>
-      </c>
-      <c r="N694" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O694" s="1">
-        <v>0</v>
-      </c>
-      <c r="P694" t="str">
-        <v/>
-      </c>
-      <c r="Q694" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R694" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="str">
-        <v>T260702-00022</v>
-      </c>
-      <c r="B695" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C695" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D695" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E695" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F695">
-        <v>0</v>
-      </c>
-      <c r="G695" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H695" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I695" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J695" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K695">
-        <v>1</v>
-      </c>
-      <c r="L695" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M695" t="str">
-        <v>2026-07-02 20:51:32</v>
-      </c>
-      <c r="N695" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O695" s="1">
-        <v>0</v>
-      </c>
-      <c r="P695" t="str">
-        <v/>
-      </c>
-      <c r="Q695" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R695" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="str">
-        <v>T260702-00021</v>
-      </c>
-      <c r="B696" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C696" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D696" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E696" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F696">
-        <v>1</v>
-      </c>
-      <c r="G696" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H696" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I696" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J696" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K696">
-        <v>1</v>
-      </c>
-      <c r="L696" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M696" t="str">
-        <v>2026-07-02 20:51:14</v>
-      </c>
-      <c r="N696" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O696" s="1">
-        <v>0</v>
-      </c>
-      <c r="P696" t="str">
-        <v/>
-      </c>
-      <c r="Q696" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R696" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="str">
-        <v>T260702-00020</v>
-      </c>
-      <c r="B697" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C697" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D697" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E697" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F697">
-        <v>0</v>
-      </c>
-      <c r="G697" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="H697" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="I697" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J697" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K697">
-        <v>1</v>
-      </c>
-      <c r="L697" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M697" t="str">
-        <v>2026-07-02 20:50:54</v>
-      </c>
-      <c r="N697" s="1">
-        <v>280000</v>
-      </c>
-      <c r="O697" s="1">
-        <v>0</v>
-      </c>
-      <c r="P697" t="str">
-        <v/>
-      </c>
-      <c r="Q697" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R697" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="str">
-        <v>T260702-00019</v>
-      </c>
-      <c r="B698" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C698" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D698" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E698" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F698">
-        <v>0</v>
-      </c>
-      <c r="G698" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H698" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I698" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J698" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K698">
-        <v>1</v>
-      </c>
-      <c r="L698" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M698" t="str">
-        <v>2026-07-02 20:50:36</v>
-      </c>
-      <c r="N698" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O698" s="1">
-        <v>0</v>
-      </c>
-      <c r="P698" t="str">
-        <v/>
-      </c>
-      <c r="Q698" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R698" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="str">
-        <v>T260702-00018</v>
-      </c>
-      <c r="B699" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C699" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D699" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E699" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F699">
-        <v>1</v>
-      </c>
-      <c r="G699" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H699" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I699" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J699" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K699">
-        <v>1</v>
-      </c>
-      <c r="L699" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M699" t="str">
-        <v>2026-07-02 20:50:19</v>
-      </c>
-      <c r="N699" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O699" s="1">
-        <v>0</v>
-      </c>
-      <c r="P699" t="str">
-        <v/>
-      </c>
-      <c r="Q699" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R699" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="str">
-        <v>T260702-00017</v>
-      </c>
-      <c r="B700" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C700" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D700" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E700" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F700">
-        <v>1</v>
-      </c>
-      <c r="G700" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H700" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I700" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J700" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K700">
-        <v>1</v>
-      </c>
-      <c r="L700" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M700" t="str">
-        <v>2026-07-02 20:49:56</v>
-      </c>
-      <c r="N700" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O700" s="1">
-        <v>0</v>
-      </c>
-      <c r="P700" t="str">
-        <v/>
-      </c>
-      <c r="Q700" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R700" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="str">
-        <v>T260702-00016</v>
-      </c>
-      <c r="B701" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C701" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D701" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E701" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F701">
-        <v>0</v>
-      </c>
-      <c r="G701" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H701" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I701" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J701" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K701">
-        <v>1</v>
-      </c>
-      <c r="L701" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M701" t="str">
-        <v>2026-07-02 20:49:25</v>
-      </c>
-      <c r="N701" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O701" s="1">
-        <v>0</v>
-      </c>
-      <c r="P701" t="str">
-        <v/>
-      </c>
-      <c r="Q701" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R701" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="str">
-        <v>T260702-00015</v>
-      </c>
-      <c r="B702" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C702" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D702" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E702" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F702">
-        <v>1</v>
-      </c>
-      <c r="G702" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H702" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I702" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J702" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K702">
-        <v>1</v>
-      </c>
-      <c r="L702" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M702" t="str">
-        <v>2026-07-02 20:48:50</v>
-      </c>
-      <c r="N702" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O702" s="1">
-        <v>0</v>
-      </c>
-      <c r="P702" t="str">
-        <v/>
-      </c>
-      <c r="Q702" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R702" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="str">
-        <v>T260702-00014</v>
-      </c>
-      <c r="B703" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C703" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D703" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E703" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F703">
-        <v>0</v>
-      </c>
-      <c r="G703" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H703" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I703" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J703" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K703">
-        <v>1</v>
-      </c>
-      <c r="L703" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M703" t="str">
-        <v>2026-07-02 20:48:25</v>
-      </c>
-      <c r="N703" s="1">
-        <v>420000</v>
-      </c>
-      <c r="O703" s="1">
-        <v>0</v>
-      </c>
-      <c r="P703" t="str">
-        <v/>
-      </c>
-      <c r="Q703" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R703" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="str">
-        <v>T260702-00013</v>
-      </c>
-      <c r="B704" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C704" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D704" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E704" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F704">
-        <v>0</v>
-      </c>
-      <c r="G704" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H704" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I704" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J704" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K704">
-        <v>1</v>
-      </c>
-      <c r="L704" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M704" t="str">
-        <v>2026-07-02 20:48:09</v>
-      </c>
-      <c r="N704" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O704" s="1">
-        <v>0</v>
-      </c>
-      <c r="P704" t="str">
-        <v/>
-      </c>
-      <c r="Q704" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R704" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="str">
-        <v>T260702-00012</v>
-      </c>
-      <c r="B705" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C705" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D705" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E705" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F705">
-        <v>2</v>
-      </c>
-      <c r="G705" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H705" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I705" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J705" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K705">
-        <v>1</v>
-      </c>
-      <c r="L705" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M705" t="str">
-        <v>2026-07-02 20:47:49</v>
-      </c>
-      <c r="N705" s="1">
-        <v>680000</v>
-      </c>
-      <c r="O705" s="1">
-        <v>0</v>
-      </c>
-      <c r="P705" t="str">
-        <v/>
-      </c>
-      <c r="Q705" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R705" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="str">
-        <v>T260702-00011</v>
-      </c>
-      <c r="B706" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C706" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D706" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E706" t="str">
-        <v>2026-07-02 17:50</v>
-      </c>
-      <c r="F706">
-        <v>0</v>
-      </c>
-      <c r="G706" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H706" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I706" t="str">
-        <v>2026-07-02 18:50</v>
-      </c>
-      <c r="J706" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K706">
-        <v>1</v>
-      </c>
-      <c r="L706" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M706" t="str">
-        <v>2026-07-02 20:44:59</v>
-      </c>
-      <c r="N706" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O706" s="1">
-        <v>0</v>
-      </c>
-      <c r="P706" t="str">
-        <v/>
-      </c>
-      <c r="Q706" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R706" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="str">
-        <v>T260702-00010</v>
-      </c>
-      <c r="B707" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C707" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D707" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E707" t="str">
-        <v>2026-07-02 13:30</v>
-      </c>
-      <c r="F707">
-        <v>0</v>
-      </c>
-      <c r="G707" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H707" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I707" t="str">
-        <v>2026-07-02 15:40</v>
-      </c>
-      <c r="J707" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K707">
-        <v>1</v>
-      </c>
-      <c r="L707" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M707" t="str">
-        <v>2026-07-02 20:44:26</v>
-      </c>
-      <c r="N707" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O707" s="1">
-        <v>0</v>
-      </c>
-      <c r="P707" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q707" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R707" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="str">
-        <v>T260702-00009</v>
-      </c>
-      <c r="B708" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C708" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D708" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E708" t="str">
-        <v>2026-07-02 10:00</v>
-      </c>
-      <c r="F708">
-        <v>0</v>
-      </c>
-      <c r="G708" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H708" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I708" t="str">
-        <v>2026-07-02 13:40</v>
-      </c>
-      <c r="J708" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K708">
-        <v>1</v>
-      </c>
-      <c r="L708" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M708" t="str">
-        <v>2026-07-02 20:43:37</v>
-      </c>
-      <c r="N708" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O708" s="1">
-        <v>0</v>
-      </c>
-      <c r="P708" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q708" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R708" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="str">
-        <v>T260702-00008</v>
-      </c>
-      <c r="B709" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C709" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D709" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E709" t="str">
-        <v>2026-07-02 17:00</v>
-      </c>
-      <c r="F709">
-        <v>0</v>
-      </c>
-      <c r="G709" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="H709" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="I709" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J709" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K709">
-        <v>1</v>
-      </c>
-      <c r="L709" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M709" t="str">
-        <v>2026-07-02 16:38:23</v>
-      </c>
-      <c r="N709" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O709" s="1">
-        <v>0</v>
-      </c>
-      <c r="P709" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="Q709" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R709" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="str">
-        <v>T260702-00007</v>
-      </c>
-      <c r="B710" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C710" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D710" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E710" t="str">
-        <v>2026-07-02 16:30</v>
-      </c>
-      <c r="F710">
-        <v>0</v>
-      </c>
-      <c r="G710" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H710" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I710" t="str">
-        <v>2026-07-02 18:00</v>
-      </c>
-      <c r="J710" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K710">
-        <v>1</v>
-      </c>
-      <c r="L710" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M710" t="str">
-        <v>2026-07-02 16:34:35</v>
-      </c>
-      <c r="N710" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O710" s="1">
-        <v>0</v>
-      </c>
-      <c r="P710" t="str">
-        <v>20260702/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q710" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R710" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="str">
-        <v>T260702-00006</v>
-      </c>
-      <c r="B711" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C711" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D711" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E711" t="str">
-        <v>2026-07-02 16:00</v>
-      </c>
-      <c r="F711">
-        <v>0</v>
-      </c>
-      <c r="G711" t="str">
-        <v>광주 하이마트 물류</v>
-      </c>
-      <c r="H711" t="str">
-        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
-      </c>
-      <c r="I711" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J711" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K711">
-        <v>1</v>
-      </c>
-      <c r="L711" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M711" t="str">
-        <v>2026-07-02 15:30:55</v>
-      </c>
-      <c r="N711" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O711" s="1">
-        <v>0</v>
-      </c>
-      <c r="P711" t="str">
-        <v>일코 광주 하이마트 물류</v>
-      </c>
-      <c r="Q711" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R711" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="str">
-        <v>T260702-00005</v>
-      </c>
-      <c r="B712" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C712" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D712" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E712" t="str">
-        <v>2026-07-02 14:30</v>
-      </c>
-      <c r="F712">
-        <v>0</v>
-      </c>
-      <c r="G712" t="str">
-        <v>마산 하이마트 물류</v>
-      </c>
-      <c r="H712" t="str">
-        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
-      </c>
-      <c r="I712" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J712" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K712">
-        <v>1</v>
-      </c>
-      <c r="L712" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M712" t="str">
-        <v>2026-07-02 13:44:41</v>
-      </c>
-      <c r="N712" s="1">
-        <v>380000</v>
-      </c>
-      <c r="O712" s="1">
-        <v>0</v>
-      </c>
-      <c r="P712" t="str">
-        <v>일코 마산 하이마트 물류</v>
-      </c>
-      <c r="Q712" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R712" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="str">
-        <v>T260702-00004</v>
-      </c>
-      <c r="B713" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C713" t="str">
-        <v>강릉 하이마트 물류</v>
-      </c>
-      <c r="D713" t="str">
-        <v>강원특별자치도 강릉시 연곡면 동해대로 4100-36 강릉 하이마트 물류</v>
-      </c>
-      <c r="E713" t="str">
-        <v>2026-07-02 13:30</v>
-      </c>
-      <c r="F713">
-        <v>0</v>
-      </c>
-      <c r="G713" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H713" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I713" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J713" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K713">
-        <v>1</v>
-      </c>
-      <c r="L713" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M713" t="str">
-        <v>2026-07-02 12:00:10</v>
-      </c>
-      <c r="N713" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O713" s="1">
-        <v>0</v>
-      </c>
-      <c r="P713" t="str">
-        <v>일코전자 강릉 하이마트 물류</v>
-      </c>
-      <c r="Q713" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R713" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="str">
-        <v>T260702-00003</v>
-      </c>
-      <c r="B714" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C714" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D714" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E714" t="str">
-        <v>2026-07-02 14:30</v>
-      </c>
-      <c r="F714">
-        <v>0</v>
-      </c>
-      <c r="G714" t="str">
-        <v>대구 하이마트 물류</v>
-      </c>
-      <c r="H714" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="I714" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J714" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K714">
-        <v>1</v>
-      </c>
-      <c r="L714" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M714" t="str">
-        <v>2026-07-02 11:59:32</v>
-      </c>
-      <c r="N714" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O714" s="1">
-        <v>0</v>
-      </c>
-      <c r="P714" t="str">
-        <v>일코전자 대구 하이마트 물류</v>
-      </c>
-      <c r="Q714" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R714" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="str">
-        <v>T260702-00002</v>
-      </c>
-      <c r="B715" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C715" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D715" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E715" t="str">
-        <v>2026-07-02 09:30</v>
-      </c>
-      <c r="F715">
-        <v>1</v>
-      </c>
-      <c r="G715" t="str">
-        <v>하이얼(대구2착)</v>
-      </c>
-      <c r="H715" t="str">
-        <v>대구 남구 양지로 25 대명자이 아파트</v>
-      </c>
-      <c r="I715" t="str">
-        <v>2026-07-02 15:00</v>
-      </c>
-      <c r="J715" t="str">
-        <v>1.5톤 윙바디</v>
-      </c>
-      <c r="K715">
-        <v>1</v>
-      </c>
-      <c r="L715" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M715" t="str">
-        <v>2026-07-02 09:20:07</v>
-      </c>
-      <c r="N715" s="1">
-        <v>220000</v>
-      </c>
-      <c r="O715" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P715" t="str">
-        <v>20260702/하이얼_대구 착지 2곳_벌크_출하</v>
-      </c>
-      <c r="Q715" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R715" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="str">
-        <v>T260702-00001</v>
-      </c>
-      <c r="B716" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C716" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D716" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E716" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="F716">
-        <v>0</v>
-      </c>
-      <c r="G716" t="str">
-        <v>로지스밸리인천포트(Logisvalley)</v>
-      </c>
-      <c r="H716" t="str">
-        <v>인천 연수구 인천타워대로599번길 60 로지스밸리인천포트(Logisvalley) 1층 13번(HTC)</v>
-      </c>
-      <c r="I716" t="str">
-        <v>2026-07-02 11:00</v>
-      </c>
-      <c r="J716" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K716">
-        <v>1</v>
-      </c>
-      <c r="L716" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M716" t="str">
-        <v>2026-07-02 09:17:29</v>
-      </c>
-      <c r="N716" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O716" s="1">
-        <v>0</v>
-      </c>
-      <c r="P716" t="str">
-        <v>패스트레인 출하</v>
-      </c>
-      <c r="Q716" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R716" t="str">
-        <v>패스트레인코리아</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="str">
-        <v>T260701-00026</v>
-      </c>
-      <c r="B717" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C717" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D717" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E717" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F717">
-        <v>1</v>
-      </c>
-      <c r="G717" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H717" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I717" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J717" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K717">
-        <v>1</v>
-      </c>
-      <c r="L717" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M717" t="str">
-        <v>2026-07-01 19:47:13</v>
-      </c>
-      <c r="N717" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O717" s="1">
-        <v>0</v>
-      </c>
-      <c r="P717" t="str">
-        <v/>
-      </c>
-      <c r="Q717" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R717" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="str">
-        <v>T260701-00025</v>
-      </c>
-      <c r="B718" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C718" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D718" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E718" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F718">
-        <v>2</v>
-      </c>
-      <c r="G718" t="str">
-        <v>원주ACP</v>
-      </c>
-      <c r="H718" t="str">
-        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
-      </c>
-      <c r="I718" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J718" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K718">
-        <v>1</v>
-      </c>
-      <c r="L718" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M718" t="str">
-        <v>2026-07-01 19:46:48</v>
-      </c>
-      <c r="N718" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O718" s="1">
-        <v>0</v>
-      </c>
-      <c r="P718" t="str">
-        <v/>
-      </c>
-      <c r="Q718" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R718" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="str">
-        <v>T260701-00024</v>
-      </c>
-      <c r="B719" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C719" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D719" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E719" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F719">
-        <v>1</v>
-      </c>
-      <c r="G719" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H719" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I719" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J719" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K719">
-        <v>1</v>
-      </c>
-      <c r="L719" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M719" t="str">
-        <v>2026-07-01 19:46:12</v>
-      </c>
-      <c r="N719" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O719" s="1">
-        <v>0</v>
-      </c>
-      <c r="P719" t="str">
-        <v/>
-      </c>
-      <c r="Q719" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R719" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="str">
-        <v>T260701-00023</v>
-      </c>
-      <c r="B720" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C720" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D720" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E720" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F720">
-        <v>3</v>
-      </c>
-      <c r="G720" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H720" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I720" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J720" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K720">
-        <v>1</v>
-      </c>
-      <c r="L720" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M720" t="str">
-        <v>2026-07-01 19:45:40</v>
-      </c>
-      <c r="N720" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O720" s="1">
-        <v>0</v>
-      </c>
-      <c r="P720" t="str">
-        <v/>
-      </c>
-      <c r="Q720" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R720" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="str">
-        <v>T260701-00022</v>
-      </c>
-      <c r="B721" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C721" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D721" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E721" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F721">
-        <v>0</v>
-      </c>
-      <c r="G721" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H721" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I721" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J721" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K721">
-        <v>1</v>
-      </c>
-      <c r="L721" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M721" t="str">
-        <v>2026-07-01 19:44:56</v>
-      </c>
-      <c r="N721" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O721" s="1">
-        <v>0</v>
-      </c>
-      <c r="P721" t="str">
-        <v/>
-      </c>
-      <c r="Q721" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R721" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="str">
-        <v>T260701-00021</v>
-      </c>
-      <c r="B722" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C722" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D722" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E722" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F722">
-        <v>1</v>
-      </c>
-      <c r="G722" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H722" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I722" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J722" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K722">
-        <v>1</v>
-      </c>
-      <c r="L722" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M722" t="str">
-        <v>2026-07-01 19:44:37</v>
-      </c>
-      <c r="N722" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O722" s="1">
-        <v>0</v>
-      </c>
-      <c r="P722" t="str">
-        <v/>
-      </c>
-      <c r="Q722" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R722" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="str">
-        <v>T260701-00020</v>
-      </c>
-      <c r="B723" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C723" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D723" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E723" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F723">
-        <v>2</v>
-      </c>
-      <c r="G723" t="str">
-        <v>속초ACP</v>
-      </c>
-      <c r="H723" t="str">
-        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
-      </c>
-      <c r="I723" t="str">
-        <v>2026-07-02 06:00</v>
-      </c>
-      <c r="J723" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K723">
-        <v>1</v>
-      </c>
-      <c r="L723" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M723" t="str">
-        <v>2026-07-01 19:44:05</v>
-      </c>
-      <c r="N723" s="1">
-        <v>320000</v>
-      </c>
-      <c r="O723" s="1">
-        <v>0</v>
-      </c>
-      <c r="P723" t="str">
-        <v/>
-      </c>
-      <c r="Q723" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R723" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="str">
-        <v>T260701-00019</v>
-      </c>
-      <c r="B724" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C724" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D724" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E724" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F724">
-        <v>0</v>
-      </c>
-      <c r="G724" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H724" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I724" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J724" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K724">
-        <v>1</v>
-      </c>
-      <c r="L724" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M724" t="str">
-        <v>2026-07-01 19:43:22</v>
-      </c>
-      <c r="N724" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O724" s="1">
-        <v>0</v>
-      </c>
-      <c r="P724" t="str">
-        <v/>
-      </c>
-      <c r="Q724" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R724" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="str">
-        <v>T260701-00018</v>
-      </c>
-      <c r="B725" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C725" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D725" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E725" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F725">
-        <v>1</v>
-      </c>
-      <c r="G725" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H725" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I725" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J725" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K725">
-        <v>1</v>
-      </c>
-      <c r="L725" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M725" t="str">
-        <v>2026-07-01 19:43:03</v>
-      </c>
-      <c r="N725" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O725" s="1">
-        <v>0</v>
-      </c>
-      <c r="P725" t="str">
-        <v/>
-      </c>
-      <c r="Q725" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R725" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="str">
-        <v>T260701-00017</v>
-      </c>
-      <c r="B726" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C726" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D726" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E726" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F726">
-        <v>0</v>
-      </c>
-      <c r="G726" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H726" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I726" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J726" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K726">
-        <v>1</v>
-      </c>
-      <c r="L726" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M726" t="str">
-        <v>2026-07-01 19:42:39</v>
-      </c>
-      <c r="N726" s="1">
-        <v>310000</v>
-      </c>
-      <c r="O726" s="1">
-        <v>0</v>
-      </c>
-      <c r="P726" t="str">
-        <v/>
-      </c>
-      <c r="Q726" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R726" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="str">
-        <v>T260701-00016</v>
-      </c>
-      <c r="B727" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C727" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D727" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E727" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F727">
-        <v>0</v>
-      </c>
-      <c r="G727" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H727" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I727" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J727" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K727">
-        <v>1</v>
-      </c>
-      <c r="L727" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M727" t="str">
-        <v>2026-07-01 19:42:17</v>
-      </c>
-      <c r="N727" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O727" s="1">
-        <v>0</v>
-      </c>
-      <c r="P727" t="str">
-        <v/>
-      </c>
-      <c r="Q727" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R727" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="str">
-        <v>T260701-00015</v>
-      </c>
-      <c r="B728" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C728" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D728" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E728" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F728">
-        <v>1</v>
-      </c>
-      <c r="G728" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H728" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I728" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J728" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K728">
-        <v>1</v>
-      </c>
-      <c r="L728" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M728" t="str">
-        <v>2026-07-01 19:42:02</v>
-      </c>
-      <c r="N728" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O728" s="1">
-        <v>0</v>
-      </c>
-      <c r="P728" t="str">
-        <v/>
-      </c>
-      <c r="Q728" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R728" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="str">
-        <v>T260701-00014</v>
-      </c>
-      <c r="B729" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C729" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D729" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E729" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F729">
-        <v>1</v>
-      </c>
-      <c r="G729" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H729" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I729" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J729" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K729">
-        <v>1</v>
-      </c>
-      <c r="L729" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M729" t="str">
-        <v>2026-07-01 19:41:41</v>
-      </c>
-      <c r="N729" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O729" s="1">
-        <v>0</v>
-      </c>
-      <c r="P729" t="str">
-        <v/>
-      </c>
-      <c r="Q729" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R729" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="str">
-        <v>T260701-00013</v>
-      </c>
-      <c r="B730" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C730" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D730" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E730" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F730">
-        <v>1</v>
-      </c>
-      <c r="G730" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H730" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I730" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J730" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K730">
-        <v>1</v>
-      </c>
-      <c r="L730" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M730" t="str">
-        <v>2026-07-01 19:41:08</v>
-      </c>
-      <c r="N730" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O730" s="1">
-        <v>0</v>
-      </c>
-      <c r="P730" t="str">
-        <v/>
-      </c>
-      <c r="Q730" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R730" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="str">
-        <v>T260701-00012</v>
-      </c>
-      <c r="B731" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C731" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D731" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E731" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F731">
-        <v>1</v>
-      </c>
-      <c r="G731" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H731" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I731" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J731" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K731">
-        <v>1</v>
-      </c>
-      <c r="L731" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M731" t="str">
-        <v>2026-07-01 19:40:45</v>
-      </c>
-      <c r="N731" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O731" s="1">
-        <v>0</v>
-      </c>
-      <c r="P731" t="str">
-        <v/>
-      </c>
-      <c r="Q731" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R731" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="str">
-        <v>T260701-00011</v>
-      </c>
-      <c r="B732" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C732" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D732" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E732" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F732">
-        <v>0</v>
-      </c>
-      <c r="G732" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H732" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I732" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J732" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K732">
-        <v>1</v>
-      </c>
-      <c r="L732" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M732" t="str">
-        <v>2026-07-01 19:40:21</v>
-      </c>
-      <c r="N732" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O732" s="1">
-        <v>0</v>
-      </c>
-      <c r="P732" t="str">
-        <v/>
-      </c>
-      <c r="Q732" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R732" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="str">
-        <v>T260701-00010</v>
-      </c>
-      <c r="B733" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C733" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D733" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E733" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F733">
-        <v>1</v>
-      </c>
-      <c r="G733" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H733" t="str">
-        <v>경산시 해오름길114-2 경산FDC</v>
-      </c>
-      <c r="I733" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J733" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K733">
-        <v>1</v>
-      </c>
-      <c r="L733" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M733" t="str">
-        <v>2026-07-01 19:40:04</v>
-      </c>
-      <c r="N733" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O733" s="1">
-        <v>0</v>
-      </c>
-      <c r="P733" t="str">
-        <v/>
-      </c>
-      <c r="Q733" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R733" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="str">
-        <v>T260701-00009</v>
-      </c>
-      <c r="B734" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C734" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D734" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E734" t="str">
-        <v>2026-07-01 17:30</v>
-      </c>
-      <c r="F734">
-        <v>0</v>
-      </c>
-      <c r="G734" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H734" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I734" t="str">
-        <v>2026-07-01 18:30</v>
-      </c>
-      <c r="J734" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K734">
-        <v>1</v>
-      </c>
-      <c r="L734" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M734" t="str">
-        <v>2026-07-01 19:31:35</v>
-      </c>
-      <c r="N734" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O734" s="1">
-        <v>0</v>
-      </c>
-      <c r="P734" t="str">
-        <v/>
-      </c>
-      <c r="Q734" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R734" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="str">
-        <v>T260701-00008</v>
-      </c>
-      <c r="B735" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C735" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D735" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E735" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="F735">
-        <v>0</v>
-      </c>
-      <c r="G735" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H735" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I735" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="J735" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K735">
-        <v>1</v>
-      </c>
-      <c r="L735" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M735" t="str">
-        <v>2026-07-01 19:31:02</v>
-      </c>
-      <c r="N735" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O735" s="1">
-        <v>0</v>
-      </c>
-      <c r="P735" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q735" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R735" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="str">
-        <v>T260701-00007</v>
-      </c>
-      <c r="B736" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C736" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D736" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E736" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F736">
-        <v>0</v>
-      </c>
-      <c r="G736" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H736" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I736" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="J736" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K736">
-        <v>1</v>
-      </c>
-      <c r="L736" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M736" t="str">
-        <v>2026-07-01 19:29:27</v>
-      </c>
-      <c r="N736" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O736" s="1">
-        <v>0</v>
-      </c>
-      <c r="P736" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q736" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R736" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="str">
-        <v>T260701-00006</v>
-      </c>
-      <c r="B737" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C737" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D737" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E737" t="str">
-        <v>2026-07-01 16:30</v>
-      </c>
-      <c r="F737">
-        <v>0</v>
-      </c>
-      <c r="G737" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H737" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I737" t="str">
-        <v>2026-07-01 18:00</v>
-      </c>
-      <c r="J737" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K737">
-        <v>1</v>
-      </c>
-      <c r="L737" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M737" t="str">
-        <v>2026-07-01 16:09:24</v>
-      </c>
-      <c r="N737" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O737" s="1">
-        <v>0</v>
-      </c>
-      <c r="P737" t="str">
-        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q737" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R737" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="str">
-        <v>T260701-00005</v>
-      </c>
-      <c r="B738" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C738" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D738" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E738" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="F738">
-        <v>0</v>
-      </c>
-      <c r="G738" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H738" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I738" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J738" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K738">
-        <v>1</v>
-      </c>
-      <c r="L738" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M738" t="str">
-        <v>2026-07-01 14:58:37</v>
-      </c>
-      <c r="N738" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O738" s="1">
-        <v>0</v>
-      </c>
-      <c r="P738" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q738" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R738" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="str">
-        <v>T260701-00004</v>
-      </c>
-      <c r="B739" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C739" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D739" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E739" t="str">
-        <v>2026-07-01 15:20</v>
-      </c>
-      <c r="F739">
-        <v>0</v>
-      </c>
-      <c r="G739" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H739" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I739" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J739" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K739">
-        <v>1</v>
-      </c>
-      <c r="L739" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M739" t="str">
-        <v>2026-07-01 14:53:20</v>
-      </c>
-      <c r="N739" s="1">
-        <v>440000</v>
-      </c>
-      <c r="O739" s="1">
-        <v>0</v>
-      </c>
-      <c r="P739" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q739" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R739" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="str">
-        <v>T260701-00003</v>
-      </c>
-      <c r="B740" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C740" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D740" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E740" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F740">
-        <v>0</v>
-      </c>
-      <c r="G740" t="str">
-        <v>하이얼(이천다코넷)</v>
-      </c>
-      <c r="H740" t="str">
-        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
-      </c>
-      <c r="I740" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J740" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K740">
-        <v>1</v>
-      </c>
-      <c r="L740" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M740" t="str">
-        <v>2026-07-01 10:15:38</v>
-      </c>
-      <c r="N740" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O740" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P740" t="str">
-        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
-      </c>
-      <c r="Q740" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R740" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="str">
-        <v>T260701-00002</v>
-      </c>
-      <c r="B741" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C741" t="str">
-        <v>청주ARC(디지탈태양)</v>
-      </c>
-      <c r="D741" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
-      </c>
-      <c r="E741" t="str">
-        <v>2026-07-01 08:30</v>
-      </c>
-      <c r="F741">
-        <v>0</v>
-      </c>
-      <c r="G741" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H741" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="I741" t="str">
-        <v>2026-07-01 10:30</v>
-      </c>
-      <c r="J741" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K741">
-        <v>1</v>
-      </c>
-      <c r="L741" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M741" t="str">
-        <v>2026-07-01 10:13:39</v>
-      </c>
-      <c r="N741" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O741" s="1">
-        <v>0</v>
-      </c>
-      <c r="P741" t="str">
-        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
-      </c>
-      <c r="Q741" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R741" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="str">
-        <v>T260701-00001</v>
-      </c>
-      <c r="B742" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C742" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D742" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E742" t="str">
-        <v>2026-07-01 09:00</v>
-      </c>
-      <c r="F742">
-        <v>0</v>
-      </c>
-      <c r="G742" t="str">
-        <v>현대클러스터 한강미사3차</v>
-      </c>
-      <c r="H742" t="str">
-        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
-      </c>
-      <c r="I742" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J742" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K742">
-        <v>1</v>
-      </c>
-      <c r="L742" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M742" t="str">
-        <v>2026-07-01 09:07:09</v>
-      </c>
-      <c r="N742" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O742" s="1">
-        <v>0</v>
-      </c>
-      <c r="P742" t="str">
-        <v>스마트윈드 출하</v>
-      </c>
-      <c r="Q742" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R742" t="str">
-        <v>스마트윈드</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R742"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R689"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R689"/>
+  <dimension ref="A1:R742"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38964,9 +38964,2977 @@
         <v>일코전자</v>
       </c>
     </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>T260702-00027</v>
+      </c>
+      <c r="B690" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C690" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D690" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E690" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F690">
+        <v>1</v>
+      </c>
+      <c r="G690" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H690" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I690" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J690" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K690">
+        <v>1</v>
+      </c>
+      <c r="L690" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M690" t="str">
+        <v>2026-07-02 20:54:21</v>
+      </c>
+      <c r="N690" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O690" s="1">
+        <v>0</v>
+      </c>
+      <c r="P690" t="str">
+        <v/>
+      </c>
+      <c r="Q690" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R690" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>T260702-00026</v>
+      </c>
+      <c r="B691" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C691" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D691" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E691" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F691">
+        <v>1</v>
+      </c>
+      <c r="G691" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H691" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I691" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J691" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K691">
+        <v>1</v>
+      </c>
+      <c r="L691" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M691" t="str">
+        <v>2026-07-02 20:53:56</v>
+      </c>
+      <c r="N691" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O691" s="1">
+        <v>0</v>
+      </c>
+      <c r="P691" t="str">
+        <v/>
+      </c>
+      <c r="Q691" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R691" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>T260702-00025</v>
+      </c>
+      <c r="B692" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C692" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D692" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E692" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F692">
+        <v>3</v>
+      </c>
+      <c r="G692" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H692" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I692" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J692" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K692">
+        <v>1</v>
+      </c>
+      <c r="L692" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M692" t="str">
+        <v>2026-07-02 20:53:28</v>
+      </c>
+      <c r="N692" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O692" s="1">
+        <v>0</v>
+      </c>
+      <c r="P692" t="str">
+        <v/>
+      </c>
+      <c r="Q692" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R692" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
+        <v>T260702-00024</v>
+      </c>
+      <c r="B693" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C693" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D693" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E693" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F693">
+        <v>0</v>
+      </c>
+      <c r="G693" t="str">
+        <v>용인ACP</v>
+      </c>
+      <c r="H693" t="str">
+        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
+      </c>
+      <c r="I693" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J693" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K693">
+        <v>1</v>
+      </c>
+      <c r="L693" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M693" t="str">
+        <v>2026-07-02 20:52:18</v>
+      </c>
+      <c r="N693" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O693" s="1">
+        <v>0</v>
+      </c>
+      <c r="P693" t="str">
+        <v/>
+      </c>
+      <c r="Q693" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R693" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>T260702-00023</v>
+      </c>
+      <c r="B694" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C694" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D694" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E694" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F694">
+        <v>1</v>
+      </c>
+      <c r="G694" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H694" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I694" t="str">
+        <v>2026-07-03 07:00</v>
+      </c>
+      <c r="J694" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K694">
+        <v>1</v>
+      </c>
+      <c r="L694" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M694" t="str">
+        <v>2026-07-02 20:51:59</v>
+      </c>
+      <c r="N694" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O694" s="1">
+        <v>0</v>
+      </c>
+      <c r="P694" t="str">
+        <v/>
+      </c>
+      <c r="Q694" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R694" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>T260702-00022</v>
+      </c>
+      <c r="B695" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C695" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D695" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E695" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F695">
+        <v>0</v>
+      </c>
+      <c r="G695" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H695" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I695" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J695" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K695">
+        <v>1</v>
+      </c>
+      <c r="L695" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M695" t="str">
+        <v>2026-07-02 20:51:32</v>
+      </c>
+      <c r="N695" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O695" s="1">
+        <v>0</v>
+      </c>
+      <c r="P695" t="str">
+        <v/>
+      </c>
+      <c r="Q695" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R695" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>T260702-00021</v>
+      </c>
+      <c r="B696" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C696" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D696" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E696" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F696">
+        <v>1</v>
+      </c>
+      <c r="G696" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H696" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I696" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J696" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K696">
+        <v>1</v>
+      </c>
+      <c r="L696" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M696" t="str">
+        <v>2026-07-02 20:51:14</v>
+      </c>
+      <c r="N696" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O696" s="1">
+        <v>0</v>
+      </c>
+      <c r="P696" t="str">
+        <v/>
+      </c>
+      <c r="Q696" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R696" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>T260702-00020</v>
+      </c>
+      <c r="B697" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C697" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D697" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E697" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F697">
+        <v>0</v>
+      </c>
+      <c r="G697" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H697" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I697" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J697" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K697">
+        <v>1</v>
+      </c>
+      <c r="L697" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M697" t="str">
+        <v>2026-07-02 20:50:54</v>
+      </c>
+      <c r="N697" s="1">
+        <v>280000</v>
+      </c>
+      <c r="O697" s="1">
+        <v>0</v>
+      </c>
+      <c r="P697" t="str">
+        <v/>
+      </c>
+      <c r="Q697" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R697" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>T260702-00019</v>
+      </c>
+      <c r="B698" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C698" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D698" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E698" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F698">
+        <v>0</v>
+      </c>
+      <c r="G698" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H698" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I698" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J698" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K698">
+        <v>1</v>
+      </c>
+      <c r="L698" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M698" t="str">
+        <v>2026-07-02 20:50:36</v>
+      </c>
+      <c r="N698" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O698" s="1">
+        <v>0</v>
+      </c>
+      <c r="P698" t="str">
+        <v/>
+      </c>
+      <c r="Q698" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R698" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>T260702-00018</v>
+      </c>
+      <c r="B699" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C699" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D699" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E699" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F699">
+        <v>1</v>
+      </c>
+      <c r="G699" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H699" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I699" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J699" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K699">
+        <v>1</v>
+      </c>
+      <c r="L699" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M699" t="str">
+        <v>2026-07-02 20:50:19</v>
+      </c>
+      <c r="N699" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O699" s="1">
+        <v>0</v>
+      </c>
+      <c r="P699" t="str">
+        <v/>
+      </c>
+      <c r="Q699" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R699" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
+        <v>T260702-00017</v>
+      </c>
+      <c r="B700" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C700" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D700" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E700" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F700">
+        <v>1</v>
+      </c>
+      <c r="G700" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H700" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I700" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J700" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K700">
+        <v>1</v>
+      </c>
+      <c r="L700" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M700" t="str">
+        <v>2026-07-02 20:49:56</v>
+      </c>
+      <c r="N700" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O700" s="1">
+        <v>0</v>
+      </c>
+      <c r="P700" t="str">
+        <v/>
+      </c>
+      <c r="Q700" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R700" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>T260702-00016</v>
+      </c>
+      <c r="B701" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C701" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D701" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E701" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F701">
+        <v>0</v>
+      </c>
+      <c r="G701" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H701" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I701" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J701" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K701">
+        <v>1</v>
+      </c>
+      <c r="L701" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M701" t="str">
+        <v>2026-07-02 20:49:25</v>
+      </c>
+      <c r="N701" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O701" s="1">
+        <v>0</v>
+      </c>
+      <c r="P701" t="str">
+        <v/>
+      </c>
+      <c r="Q701" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R701" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>T260702-00015</v>
+      </c>
+      <c r="B702" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C702" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D702" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E702" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F702">
+        <v>1</v>
+      </c>
+      <c r="G702" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H702" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I702" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J702" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K702">
+        <v>1</v>
+      </c>
+      <c r="L702" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M702" t="str">
+        <v>2026-07-02 20:48:50</v>
+      </c>
+      <c r="N702" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O702" s="1">
+        <v>0</v>
+      </c>
+      <c r="P702" t="str">
+        <v/>
+      </c>
+      <c r="Q702" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R702" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>T260702-00014</v>
+      </c>
+      <c r="B703" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C703" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D703" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E703" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F703">
+        <v>0</v>
+      </c>
+      <c r="G703" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H703" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I703" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J703" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K703">
+        <v>1</v>
+      </c>
+      <c r="L703" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M703" t="str">
+        <v>2026-07-02 20:48:25</v>
+      </c>
+      <c r="N703" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O703" s="1">
+        <v>0</v>
+      </c>
+      <c r="P703" t="str">
+        <v/>
+      </c>
+      <c r="Q703" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R703" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>T260702-00013</v>
+      </c>
+      <c r="B704" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C704" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D704" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E704" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F704">
+        <v>0</v>
+      </c>
+      <c r="G704" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H704" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I704" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J704" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K704">
+        <v>1</v>
+      </c>
+      <c r="L704" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M704" t="str">
+        <v>2026-07-02 20:48:09</v>
+      </c>
+      <c r="N704" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O704" s="1">
+        <v>0</v>
+      </c>
+      <c r="P704" t="str">
+        <v/>
+      </c>
+      <c r="Q704" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R704" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
+        <v>T260702-00012</v>
+      </c>
+      <c r="B705" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C705" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D705" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E705" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F705">
+        <v>2</v>
+      </c>
+      <c r="G705" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H705" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I705" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J705" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K705">
+        <v>1</v>
+      </c>
+      <c r="L705" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M705" t="str">
+        <v>2026-07-02 20:47:49</v>
+      </c>
+      <c r="N705" s="1">
+        <v>680000</v>
+      </c>
+      <c r="O705" s="1">
+        <v>0</v>
+      </c>
+      <c r="P705" t="str">
+        <v/>
+      </c>
+      <c r="Q705" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R705" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
+        <v>T260702-00011</v>
+      </c>
+      <c r="B706" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C706" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D706" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E706" t="str">
+        <v>2026-07-02 17:50</v>
+      </c>
+      <c r="F706">
+        <v>0</v>
+      </c>
+      <c r="G706" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H706" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I706" t="str">
+        <v>2026-07-02 18:50</v>
+      </c>
+      <c r="J706" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K706">
+        <v>1</v>
+      </c>
+      <c r="L706" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M706" t="str">
+        <v>2026-07-02 20:44:59</v>
+      </c>
+      <c r="N706" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O706" s="1">
+        <v>0</v>
+      </c>
+      <c r="P706" t="str">
+        <v/>
+      </c>
+      <c r="Q706" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R706" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
+        <v>T260702-00010</v>
+      </c>
+      <c r="B707" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C707" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D707" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E707" t="str">
+        <v>2026-07-02 13:30</v>
+      </c>
+      <c r="F707">
+        <v>0</v>
+      </c>
+      <c r="G707" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H707" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I707" t="str">
+        <v>2026-07-02 15:40</v>
+      </c>
+      <c r="J707" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K707">
+        <v>1</v>
+      </c>
+      <c r="L707" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M707" t="str">
+        <v>2026-07-02 20:44:26</v>
+      </c>
+      <c r="N707" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O707" s="1">
+        <v>0</v>
+      </c>
+      <c r="P707" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q707" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R707" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="str">
+        <v>T260702-00009</v>
+      </c>
+      <c r="B708" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C708" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D708" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E708" t="str">
+        <v>2026-07-02 10:00</v>
+      </c>
+      <c r="F708">
+        <v>0</v>
+      </c>
+      <c r="G708" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H708" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I708" t="str">
+        <v>2026-07-02 13:40</v>
+      </c>
+      <c r="J708" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K708">
+        <v>1</v>
+      </c>
+      <c r="L708" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M708" t="str">
+        <v>2026-07-02 20:43:37</v>
+      </c>
+      <c r="N708" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O708" s="1">
+        <v>0</v>
+      </c>
+      <c r="P708" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q708" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R708" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="str">
+        <v>T260702-00008</v>
+      </c>
+      <c r="B709" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C709" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D709" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E709" t="str">
+        <v>2026-07-02 17:00</v>
+      </c>
+      <c r="F709">
+        <v>0</v>
+      </c>
+      <c r="G709" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="H709" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="I709" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J709" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K709">
+        <v>1</v>
+      </c>
+      <c r="L709" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M709" t="str">
+        <v>2026-07-02 16:38:23</v>
+      </c>
+      <c r="N709" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O709" s="1">
+        <v>0</v>
+      </c>
+      <c r="P709" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="Q709" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R709" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="str">
+        <v>T260702-00007</v>
+      </c>
+      <c r="B710" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C710" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D710" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E710" t="str">
+        <v>2026-07-02 16:30</v>
+      </c>
+      <c r="F710">
+        <v>0</v>
+      </c>
+      <c r="G710" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H710" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I710" t="str">
+        <v>2026-07-02 18:00</v>
+      </c>
+      <c r="J710" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K710">
+        <v>1</v>
+      </c>
+      <c r="L710" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M710" t="str">
+        <v>2026-07-02 16:34:35</v>
+      </c>
+      <c r="N710" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O710" s="1">
+        <v>0</v>
+      </c>
+      <c r="P710" t="str">
+        <v>20260702/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q710" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R710" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="str">
+        <v>T260702-00006</v>
+      </c>
+      <c r="B711" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C711" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D711" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E711" t="str">
+        <v>2026-07-02 16:00</v>
+      </c>
+      <c r="F711">
+        <v>0</v>
+      </c>
+      <c r="G711" t="str">
+        <v>광주 하이마트 물류</v>
+      </c>
+      <c r="H711" t="str">
+        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
+      </c>
+      <c r="I711" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J711" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K711">
+        <v>1</v>
+      </c>
+      <c r="L711" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M711" t="str">
+        <v>2026-07-02 15:30:55</v>
+      </c>
+      <c r="N711" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O711" s="1">
+        <v>0</v>
+      </c>
+      <c r="P711" t="str">
+        <v>일코 광주 하이마트 물류</v>
+      </c>
+      <c r="Q711" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R711" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="str">
+        <v>T260702-00005</v>
+      </c>
+      <c r="B712" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C712" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D712" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E712" t="str">
+        <v>2026-07-02 14:30</v>
+      </c>
+      <c r="F712">
+        <v>0</v>
+      </c>
+      <c r="G712" t="str">
+        <v>마산 하이마트 물류</v>
+      </c>
+      <c r="H712" t="str">
+        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
+      </c>
+      <c r="I712" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J712" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K712">
+        <v>1</v>
+      </c>
+      <c r="L712" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M712" t="str">
+        <v>2026-07-02 13:44:41</v>
+      </c>
+      <c r="N712" s="1">
+        <v>380000</v>
+      </c>
+      <c r="O712" s="1">
+        <v>0</v>
+      </c>
+      <c r="P712" t="str">
+        <v>일코 마산 하이마트 물류</v>
+      </c>
+      <c r="Q712" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R712" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="str">
+        <v>T260702-00004</v>
+      </c>
+      <c r="B713" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C713" t="str">
+        <v>강릉 하이마트 물류</v>
+      </c>
+      <c r="D713" t="str">
+        <v>강원특별자치도 강릉시 연곡면 동해대로 4100-36 강릉 하이마트 물류</v>
+      </c>
+      <c r="E713" t="str">
+        <v>2026-07-02 13:30</v>
+      </c>
+      <c r="F713">
+        <v>0</v>
+      </c>
+      <c r="G713" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H713" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I713" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J713" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K713">
+        <v>1</v>
+      </c>
+      <c r="L713" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M713" t="str">
+        <v>2026-07-02 12:00:10</v>
+      </c>
+      <c r="N713" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O713" s="1">
+        <v>0</v>
+      </c>
+      <c r="P713" t="str">
+        <v>일코전자 강릉 하이마트 물류</v>
+      </c>
+      <c r="Q713" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R713" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="str">
+        <v>T260702-00003</v>
+      </c>
+      <c r="B714" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C714" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D714" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E714" t="str">
+        <v>2026-07-02 14:30</v>
+      </c>
+      <c r="F714">
+        <v>0</v>
+      </c>
+      <c r="G714" t="str">
+        <v>대구 하이마트 물류</v>
+      </c>
+      <c r="H714" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="I714" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J714" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K714">
+        <v>1</v>
+      </c>
+      <c r="L714" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M714" t="str">
+        <v>2026-07-02 11:59:32</v>
+      </c>
+      <c r="N714" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O714" s="1">
+        <v>0</v>
+      </c>
+      <c r="P714" t="str">
+        <v>일코전자 대구 하이마트 물류</v>
+      </c>
+      <c r="Q714" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R714" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="str">
+        <v>T260702-00002</v>
+      </c>
+      <c r="B715" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C715" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D715" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E715" t="str">
+        <v>2026-07-02 09:30</v>
+      </c>
+      <c r="F715">
+        <v>1</v>
+      </c>
+      <c r="G715" t="str">
+        <v>하이얼(대구2착)</v>
+      </c>
+      <c r="H715" t="str">
+        <v>대구 남구 양지로 25 대명자이 아파트</v>
+      </c>
+      <c r="I715" t="str">
+        <v>2026-07-02 15:00</v>
+      </c>
+      <c r="J715" t="str">
+        <v>1.5톤 윙바디</v>
+      </c>
+      <c r="K715">
+        <v>1</v>
+      </c>
+      <c r="L715" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M715" t="str">
+        <v>2026-07-02 09:20:07</v>
+      </c>
+      <c r="N715" s="1">
+        <v>220000</v>
+      </c>
+      <c r="O715" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P715" t="str">
+        <v>20260702/하이얼_대구 착지 2곳_벌크_출하</v>
+      </c>
+      <c r="Q715" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R715" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="str">
+        <v>T260702-00001</v>
+      </c>
+      <c r="B716" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C716" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D716" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E716" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="F716">
+        <v>0</v>
+      </c>
+      <c r="G716" t="str">
+        <v>로지스밸리인천포트(Logisvalley)</v>
+      </c>
+      <c r="H716" t="str">
+        <v>인천 연수구 인천타워대로599번길 60 로지스밸리인천포트(Logisvalley) 1층 13번(HTC)</v>
+      </c>
+      <c r="I716" t="str">
+        <v>2026-07-02 11:00</v>
+      </c>
+      <c r="J716" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K716">
+        <v>1</v>
+      </c>
+      <c r="L716" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M716" t="str">
+        <v>2026-07-02 09:17:29</v>
+      </c>
+      <c r="N716" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O716" s="1">
+        <v>0</v>
+      </c>
+      <c r="P716" t="str">
+        <v>패스트레인 출하</v>
+      </c>
+      <c r="Q716" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R716" t="str">
+        <v>패스트레인코리아</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="str">
+        <v>T260701-00026</v>
+      </c>
+      <c r="B717" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C717" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D717" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E717" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F717">
+        <v>1</v>
+      </c>
+      <c r="G717" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H717" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I717" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J717" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K717">
+        <v>1</v>
+      </c>
+      <c r="L717" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M717" t="str">
+        <v>2026-07-01 19:47:13</v>
+      </c>
+      <c r="N717" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O717" s="1">
+        <v>0</v>
+      </c>
+      <c r="P717" t="str">
+        <v/>
+      </c>
+      <c r="Q717" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R717" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="str">
+        <v>T260701-00025</v>
+      </c>
+      <c r="B718" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C718" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D718" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E718" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F718">
+        <v>2</v>
+      </c>
+      <c r="G718" t="str">
+        <v>원주ACP</v>
+      </c>
+      <c r="H718" t="str">
+        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
+      </c>
+      <c r="I718" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J718" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K718">
+        <v>1</v>
+      </c>
+      <c r="L718" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M718" t="str">
+        <v>2026-07-01 19:46:48</v>
+      </c>
+      <c r="N718" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O718" s="1">
+        <v>0</v>
+      </c>
+      <c r="P718" t="str">
+        <v/>
+      </c>
+      <c r="Q718" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R718" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="str">
+        <v>T260701-00024</v>
+      </c>
+      <c r="B719" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C719" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D719" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E719" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F719">
+        <v>1</v>
+      </c>
+      <c r="G719" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H719" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I719" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J719" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K719">
+        <v>1</v>
+      </c>
+      <c r="L719" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M719" t="str">
+        <v>2026-07-01 19:46:12</v>
+      </c>
+      <c r="N719" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O719" s="1">
+        <v>0</v>
+      </c>
+      <c r="P719" t="str">
+        <v/>
+      </c>
+      <c r="Q719" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R719" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="str">
+        <v>T260701-00023</v>
+      </c>
+      <c r="B720" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C720" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D720" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E720" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F720">
+        <v>3</v>
+      </c>
+      <c r="G720" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H720" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I720" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J720" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K720">
+        <v>1</v>
+      </c>
+      <c r="L720" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M720" t="str">
+        <v>2026-07-01 19:45:40</v>
+      </c>
+      <c r="N720" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O720" s="1">
+        <v>0</v>
+      </c>
+      <c r="P720" t="str">
+        <v/>
+      </c>
+      <c r="Q720" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R720" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="str">
+        <v>T260701-00022</v>
+      </c>
+      <c r="B721" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C721" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D721" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E721" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F721">
+        <v>0</v>
+      </c>
+      <c r="G721" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H721" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I721" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J721" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K721">
+        <v>1</v>
+      </c>
+      <c r="L721" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M721" t="str">
+        <v>2026-07-01 19:44:56</v>
+      </c>
+      <c r="N721" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O721" s="1">
+        <v>0</v>
+      </c>
+      <c r="P721" t="str">
+        <v/>
+      </c>
+      <c r="Q721" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R721" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="str">
+        <v>T260701-00021</v>
+      </c>
+      <c r="B722" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C722" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D722" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E722" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F722">
+        <v>1</v>
+      </c>
+      <c r="G722" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H722" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I722" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J722" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K722">
+        <v>1</v>
+      </c>
+      <c r="L722" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M722" t="str">
+        <v>2026-07-01 19:44:37</v>
+      </c>
+      <c r="N722" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O722" s="1">
+        <v>0</v>
+      </c>
+      <c r="P722" t="str">
+        <v/>
+      </c>
+      <c r="Q722" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R722" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="str">
+        <v>T260701-00020</v>
+      </c>
+      <c r="B723" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C723" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D723" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E723" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F723">
+        <v>2</v>
+      </c>
+      <c r="G723" t="str">
+        <v>속초ACP</v>
+      </c>
+      <c r="H723" t="str">
+        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
+      </c>
+      <c r="I723" t="str">
+        <v>2026-07-02 06:00</v>
+      </c>
+      <c r="J723" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K723">
+        <v>1</v>
+      </c>
+      <c r="L723" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M723" t="str">
+        <v>2026-07-01 19:44:05</v>
+      </c>
+      <c r="N723" s="1">
+        <v>320000</v>
+      </c>
+      <c r="O723" s="1">
+        <v>0</v>
+      </c>
+      <c r="P723" t="str">
+        <v/>
+      </c>
+      <c r="Q723" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R723" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="str">
+        <v>T260701-00019</v>
+      </c>
+      <c r="B724" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C724" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D724" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E724" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F724">
+        <v>0</v>
+      </c>
+      <c r="G724" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H724" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I724" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J724" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K724">
+        <v>1</v>
+      </c>
+      <c r="L724" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M724" t="str">
+        <v>2026-07-01 19:43:22</v>
+      </c>
+      <c r="N724" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O724" s="1">
+        <v>0</v>
+      </c>
+      <c r="P724" t="str">
+        <v/>
+      </c>
+      <c r="Q724" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R724" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="str">
+        <v>T260701-00018</v>
+      </c>
+      <c r="B725" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C725" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D725" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E725" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F725">
+        <v>1</v>
+      </c>
+      <c r="G725" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H725" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I725" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J725" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K725">
+        <v>1</v>
+      </c>
+      <c r="L725" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M725" t="str">
+        <v>2026-07-01 19:43:03</v>
+      </c>
+      <c r="N725" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O725" s="1">
+        <v>0</v>
+      </c>
+      <c r="P725" t="str">
+        <v/>
+      </c>
+      <c r="Q725" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R725" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="str">
+        <v>T260701-00017</v>
+      </c>
+      <c r="B726" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C726" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D726" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E726" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F726">
+        <v>0</v>
+      </c>
+      <c r="G726" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H726" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I726" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J726" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K726">
+        <v>1</v>
+      </c>
+      <c r="L726" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M726" t="str">
+        <v>2026-07-01 19:42:39</v>
+      </c>
+      <c r="N726" s="1">
+        <v>310000</v>
+      </c>
+      <c r="O726" s="1">
+        <v>0</v>
+      </c>
+      <c r="P726" t="str">
+        <v/>
+      </c>
+      <c r="Q726" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R726" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="str">
+        <v>T260701-00016</v>
+      </c>
+      <c r="B727" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C727" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D727" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E727" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F727">
+        <v>0</v>
+      </c>
+      <c r="G727" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H727" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I727" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J727" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K727">
+        <v>1</v>
+      </c>
+      <c r="L727" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M727" t="str">
+        <v>2026-07-01 19:42:17</v>
+      </c>
+      <c r="N727" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O727" s="1">
+        <v>0</v>
+      </c>
+      <c r="P727" t="str">
+        <v/>
+      </c>
+      <c r="Q727" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R727" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="str">
+        <v>T260701-00015</v>
+      </c>
+      <c r="B728" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C728" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D728" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E728" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F728">
+        <v>1</v>
+      </c>
+      <c r="G728" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H728" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I728" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J728" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K728">
+        <v>1</v>
+      </c>
+      <c r="L728" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M728" t="str">
+        <v>2026-07-01 19:42:02</v>
+      </c>
+      <c r="N728" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O728" s="1">
+        <v>0</v>
+      </c>
+      <c r="P728" t="str">
+        <v/>
+      </c>
+      <c r="Q728" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R728" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="str">
+        <v>T260701-00014</v>
+      </c>
+      <c r="B729" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C729" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D729" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E729" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F729">
+        <v>1</v>
+      </c>
+      <c r="G729" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H729" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I729" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J729" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K729">
+        <v>1</v>
+      </c>
+      <c r="L729" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M729" t="str">
+        <v>2026-07-01 19:41:41</v>
+      </c>
+      <c r="N729" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O729" s="1">
+        <v>0</v>
+      </c>
+      <c r="P729" t="str">
+        <v/>
+      </c>
+      <c r="Q729" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R729" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="str">
+        <v>T260701-00013</v>
+      </c>
+      <c r="B730" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C730" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D730" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E730" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F730">
+        <v>1</v>
+      </c>
+      <c r="G730" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H730" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I730" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J730" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K730">
+        <v>1</v>
+      </c>
+      <c r="L730" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M730" t="str">
+        <v>2026-07-01 19:41:08</v>
+      </c>
+      <c r="N730" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O730" s="1">
+        <v>0</v>
+      </c>
+      <c r="P730" t="str">
+        <v/>
+      </c>
+      <c r="Q730" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R730" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="str">
+        <v>T260701-00012</v>
+      </c>
+      <c r="B731" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C731" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D731" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E731" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F731">
+        <v>1</v>
+      </c>
+      <c r="G731" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H731" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I731" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J731" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K731">
+        <v>1</v>
+      </c>
+      <c r="L731" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M731" t="str">
+        <v>2026-07-01 19:40:45</v>
+      </c>
+      <c r="N731" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O731" s="1">
+        <v>0</v>
+      </c>
+      <c r="P731" t="str">
+        <v/>
+      </c>
+      <c r="Q731" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R731" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="str">
+        <v>T260701-00011</v>
+      </c>
+      <c r="B732" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C732" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D732" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E732" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F732">
+        <v>0</v>
+      </c>
+      <c r="G732" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H732" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I732" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J732" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K732">
+        <v>1</v>
+      </c>
+      <c r="L732" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M732" t="str">
+        <v>2026-07-01 19:40:21</v>
+      </c>
+      <c r="N732" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O732" s="1">
+        <v>0</v>
+      </c>
+      <c r="P732" t="str">
+        <v/>
+      </c>
+      <c r="Q732" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R732" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="str">
+        <v>T260701-00010</v>
+      </c>
+      <c r="B733" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C733" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D733" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E733" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F733">
+        <v>1</v>
+      </c>
+      <c r="G733" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H733" t="str">
+        <v>경산시 해오름길114-2 경산FDC</v>
+      </c>
+      <c r="I733" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J733" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K733">
+        <v>1</v>
+      </c>
+      <c r="L733" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M733" t="str">
+        <v>2026-07-01 19:40:04</v>
+      </c>
+      <c r="N733" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O733" s="1">
+        <v>0</v>
+      </c>
+      <c r="P733" t="str">
+        <v/>
+      </c>
+      <c r="Q733" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R733" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="str">
+        <v>T260701-00009</v>
+      </c>
+      <c r="B734" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C734" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D734" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E734" t="str">
+        <v>2026-07-01 17:30</v>
+      </c>
+      <c r="F734">
+        <v>0</v>
+      </c>
+      <c r="G734" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H734" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I734" t="str">
+        <v>2026-07-01 18:30</v>
+      </c>
+      <c r="J734" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K734">
+        <v>1</v>
+      </c>
+      <c r="L734" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M734" t="str">
+        <v>2026-07-01 19:31:35</v>
+      </c>
+      <c r="N734" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O734" s="1">
+        <v>0</v>
+      </c>
+      <c r="P734" t="str">
+        <v/>
+      </c>
+      <c r="Q734" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R734" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="str">
+        <v>T260701-00008</v>
+      </c>
+      <c r="B735" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C735" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D735" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E735" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="F735">
+        <v>0</v>
+      </c>
+      <c r="G735" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H735" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I735" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="J735" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K735">
+        <v>1</v>
+      </c>
+      <c r="L735" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M735" t="str">
+        <v>2026-07-01 19:31:02</v>
+      </c>
+      <c r="N735" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O735" s="1">
+        <v>0</v>
+      </c>
+      <c r="P735" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q735" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R735" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="str">
+        <v>T260701-00007</v>
+      </c>
+      <c r="B736" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C736" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D736" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E736" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F736">
+        <v>0</v>
+      </c>
+      <c r="G736" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H736" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I736" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="J736" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K736">
+        <v>1</v>
+      </c>
+      <c r="L736" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M736" t="str">
+        <v>2026-07-01 19:29:27</v>
+      </c>
+      <c r="N736" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O736" s="1">
+        <v>0</v>
+      </c>
+      <c r="P736" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q736" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R736" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="str">
+        <v>T260701-00006</v>
+      </c>
+      <c r="B737" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C737" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D737" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E737" t="str">
+        <v>2026-07-01 16:30</v>
+      </c>
+      <c r="F737">
+        <v>0</v>
+      </c>
+      <c r="G737" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H737" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I737" t="str">
+        <v>2026-07-01 18:00</v>
+      </c>
+      <c r="J737" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K737">
+        <v>1</v>
+      </c>
+      <c r="L737" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M737" t="str">
+        <v>2026-07-01 16:09:24</v>
+      </c>
+      <c r="N737" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O737" s="1">
+        <v>0</v>
+      </c>
+      <c r="P737" t="str">
+        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q737" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R737" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="str">
+        <v>T260701-00005</v>
+      </c>
+      <c r="B738" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C738" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D738" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E738" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="F738">
+        <v>0</v>
+      </c>
+      <c r="G738" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H738" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I738" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J738" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K738">
+        <v>1</v>
+      </c>
+      <c r="L738" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M738" t="str">
+        <v>2026-07-01 14:58:37</v>
+      </c>
+      <c r="N738" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O738" s="1">
+        <v>0</v>
+      </c>
+      <c r="P738" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q738" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R738" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="str">
+        <v>T260701-00004</v>
+      </c>
+      <c r="B739" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C739" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D739" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E739" t="str">
+        <v>2026-07-01 15:20</v>
+      </c>
+      <c r="F739">
+        <v>0</v>
+      </c>
+      <c r="G739" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H739" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I739" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J739" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K739">
+        <v>1</v>
+      </c>
+      <c r="L739" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M739" t="str">
+        <v>2026-07-01 14:53:20</v>
+      </c>
+      <c r="N739" s="1">
+        <v>440000</v>
+      </c>
+      <c r="O739" s="1">
+        <v>0</v>
+      </c>
+      <c r="P739" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q739" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R739" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="str">
+        <v>T260701-00003</v>
+      </c>
+      <c r="B740" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C740" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D740" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E740" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F740">
+        <v>0</v>
+      </c>
+      <c r="G740" t="str">
+        <v>하이얼(이천다코넷)</v>
+      </c>
+      <c r="H740" t="str">
+        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
+      </c>
+      <c r="I740" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J740" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K740">
+        <v>1</v>
+      </c>
+      <c r="L740" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M740" t="str">
+        <v>2026-07-01 10:15:38</v>
+      </c>
+      <c r="N740" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O740" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P740" t="str">
+        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
+      </c>
+      <c r="Q740" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R740" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="str">
+        <v>T260701-00002</v>
+      </c>
+      <c r="B741" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C741" t="str">
+        <v>청주ARC(디지탈태양)</v>
+      </c>
+      <c r="D741" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
+      </c>
+      <c r="E741" t="str">
+        <v>2026-07-01 08:30</v>
+      </c>
+      <c r="F741">
+        <v>0</v>
+      </c>
+      <c r="G741" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H741" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="I741" t="str">
+        <v>2026-07-01 10:30</v>
+      </c>
+      <c r="J741" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K741">
+        <v>1</v>
+      </c>
+      <c r="L741" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M741" t="str">
+        <v>2026-07-01 10:13:39</v>
+      </c>
+      <c r="N741" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O741" s="1">
+        <v>0</v>
+      </c>
+      <c r="P741" t="str">
+        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
+      </c>
+      <c r="Q741" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R741" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="str">
+        <v>T260701-00001</v>
+      </c>
+      <c r="B742" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C742" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D742" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E742" t="str">
+        <v>2026-07-01 09:00</v>
+      </c>
+      <c r="F742">
+        <v>0</v>
+      </c>
+      <c r="G742" t="str">
+        <v>현대클러스터 한강미사3차</v>
+      </c>
+      <c r="H742" t="str">
+        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
+      </c>
+      <c r="I742" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J742" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K742">
+        <v>1</v>
+      </c>
+      <c r="L742" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M742" t="str">
+        <v>2026-07-01 09:07:09</v>
+      </c>
+      <c r="N742" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O742" s="1">
+        <v>0</v>
+      </c>
+      <c r="P742" t="str">
+        <v>스마트윈드 출하</v>
+      </c>
+      <c r="Q742" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R742" t="str">
+        <v>스마트윈드</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R689"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R742"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260803-00031</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260803-00030</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260803-00029</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260803-00028</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260803-00027</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260803-00026</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260803-00025</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260803-00024</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260803-00023</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260803-00022</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260803-00021</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260803-00020</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260803-00019</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260803-00018</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260803-00017</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260803-00016</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260803-00015</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260803-00014</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260803-00013</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260803-00012</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260803-00011</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1616,7 +1616,7 @@
         <v>T260803-00010</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>안성FC</v>
@@ -1672,7 +1672,7 @@
         <v>T260803-00009</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>안성FC</v>
@@ -1728,7 +1728,7 @@
         <v>T260803-00008</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>안성FC</v>
@@ -1784,7 +1784,7 @@
         <v>T260803-00007</v>
       </c>
       <c r="B26" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C26" t="str">
         <v>안성FC</v>
@@ -1840,7 +1840,7 @@
         <v>T260803-00006</v>
       </c>
       <c r="B27" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C27" t="str">
         <v>안성FC</v>
@@ -1896,7 +1896,7 @@
         <v>T260803-00005</v>
       </c>
       <c r="B28" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C28" t="str">
         <v>안성FC</v>
@@ -1952,7 +1952,7 @@
         <v>T260803-00004</v>
       </c>
       <c r="B29" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C29" t="str">
         <v>샤오미</v>
@@ -2008,7 +2008,7 @@
         <v>T260803-00003</v>
       </c>
       <c r="B30" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C30" t="str">
         <v>아이베</v>
@@ -2064,7 +2064,7 @@
         <v>T260803-00002</v>
       </c>
       <c r="B31" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C31" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R767"/>
+  <dimension ref="A1:R680"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38460,4881 +38460,9 @@
         <v>세상담기</v>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="str">
-        <v>T260703-00034</v>
-      </c>
-      <c r="B681" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C681" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D681" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E681" t="str">
-        <v>2026-07-03 19:01</v>
-      </c>
-      <c r="F681">
-        <v>0</v>
-      </c>
-      <c r="G681" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H681" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I681" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J681" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K681">
-        <v>1</v>
-      </c>
-      <c r="L681" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M681" t="str">
-        <v>2026-07-03 20:43:25</v>
-      </c>
-      <c r="N681" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O681" s="1">
-        <v>0</v>
-      </c>
-      <c r="P681" t="str">
-        <v/>
-      </c>
-      <c r="Q681" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R681" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="str">
-        <v>T260703-00033</v>
-      </c>
-      <c r="B682" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C682" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D682" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E682" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F682">
-        <v>1</v>
-      </c>
-      <c r="G682" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H682" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I682" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J682" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K682">
-        <v>1</v>
-      </c>
-      <c r="L682" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M682" t="str">
-        <v>2026-07-03 20:42:58</v>
-      </c>
-      <c r="N682" s="1">
-        <v>170000</v>
-      </c>
-      <c r="O682" s="1">
-        <v>0</v>
-      </c>
-      <c r="P682" t="str">
-        <v/>
-      </c>
-      <c r="Q682" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R682" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="str">
-        <v>T260703-00032</v>
-      </c>
-      <c r="B683" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C683" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D683" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E683" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F683">
-        <v>1</v>
-      </c>
-      <c r="G683" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H683" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I683" t="str">
-        <v>2026-07-04 08:00</v>
-      </c>
-      <c r="J683" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K683">
-        <v>1</v>
-      </c>
-      <c r="L683" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M683" t="str">
-        <v>2026-07-03 20:42:34</v>
-      </c>
-      <c r="N683" s="1">
-        <v>170000</v>
-      </c>
-      <c r="O683" s="1">
-        <v>0</v>
-      </c>
-      <c r="P683" t="str">
-        <v/>
-      </c>
-      <c r="Q683" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R683" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="str">
-        <v>T260703-00031</v>
-      </c>
-      <c r="B684" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C684" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D684" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E684" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F684">
-        <v>0</v>
-      </c>
-      <c r="G684" t="str">
-        <v>시흥ACP</v>
-      </c>
-      <c r="H684" t="str">
-        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
-      </c>
-      <c r="I684" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J684" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K684">
-        <v>1</v>
-      </c>
-      <c r="L684" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M684" t="str">
-        <v>2026-07-03 20:41:59</v>
-      </c>
-      <c r="N684" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O684" s="1">
-        <v>0</v>
-      </c>
-      <c r="P684" t="str">
-        <v/>
-      </c>
-      <c r="Q684" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R684" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="str">
-        <v>T260703-00030</v>
-      </c>
-      <c r="B685" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C685" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D685" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E685" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F685">
-        <v>3</v>
-      </c>
-      <c r="G685" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H685" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I685" t="str">
-        <v>2026-07-04 08:00</v>
-      </c>
-      <c r="J685" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K685">
-        <v>1</v>
-      </c>
-      <c r="L685" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M685" t="str">
-        <v>2026-07-03 20:41:34</v>
-      </c>
-      <c r="N685" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O685" s="1">
-        <v>0</v>
-      </c>
-      <c r="P685" t="str">
-        <v/>
-      </c>
-      <c r="Q685" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R685" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="str">
-        <v>T260703-00029</v>
-      </c>
-      <c r="B686" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C686" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D686" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E686" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F686">
-        <v>0</v>
-      </c>
-      <c r="G686" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H686" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I686" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J686" t="str">
-        <v>1톤 기타차량</v>
-      </c>
-      <c r="K686">
-        <v>1</v>
-      </c>
-      <c r="L686" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M686" t="str">
-        <v>2026-07-03 20:40:56</v>
-      </c>
-      <c r="N686" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O686" s="1">
-        <v>0</v>
-      </c>
-      <c r="P686" t="str">
-        <v/>
-      </c>
-      <c r="Q686" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R686" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="str">
-        <v>T260703-00028</v>
-      </c>
-      <c r="B687" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C687" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D687" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E687" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F687">
-        <v>0</v>
-      </c>
-      <c r="G687" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="H687" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="I687" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J687" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K687">
-        <v>1</v>
-      </c>
-      <c r="L687" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M687" t="str">
-        <v>2026-07-03 20:40:32</v>
-      </c>
-      <c r="N687" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O687" s="1">
-        <v>0</v>
-      </c>
-      <c r="P687" t="str">
-        <v/>
-      </c>
-      <c r="Q687" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R687" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="str">
-        <v>T260703-00027</v>
-      </c>
-      <c r="B688" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C688" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D688" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E688" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F688">
-        <v>3</v>
-      </c>
-      <c r="G688" t="str">
-        <v>인제ACP</v>
-      </c>
-      <c r="H688" t="str">
-        <v>강원특별자치도 속초시 만천6길 13 인제ACP</v>
-      </c>
-      <c r="I688" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J688" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K688">
-        <v>1</v>
-      </c>
-      <c r="L688" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M688" t="str">
-        <v>2026-07-03 20:40:07</v>
-      </c>
-      <c r="N688" s="1">
-        <v>390000</v>
-      </c>
-      <c r="O688" s="1">
-        <v>0</v>
-      </c>
-      <c r="P688" t="str">
-        <v/>
-      </c>
-      <c r="Q688" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R688" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="str">
-        <v>T260703-00026</v>
-      </c>
-      <c r="B689" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C689" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D689" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E689" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F689">
-        <v>0</v>
-      </c>
-      <c r="G689" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H689" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I689" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J689" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K689">
-        <v>1</v>
-      </c>
-      <c r="L689" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M689" t="str">
-        <v>2026-07-03 20:39:21</v>
-      </c>
-      <c r="N689" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O689" s="1">
-        <v>0</v>
-      </c>
-      <c r="P689" t="str">
-        <v/>
-      </c>
-      <c r="Q689" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R689" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="str">
-        <v>T260703-00025</v>
-      </c>
-      <c r="B690" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C690" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D690" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E690" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F690">
-        <v>1</v>
-      </c>
-      <c r="G690" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H690" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I690" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J690" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K690">
-        <v>1</v>
-      </c>
-      <c r="L690" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M690" t="str">
-        <v>2026-07-03 20:39:06</v>
-      </c>
-      <c r="N690" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O690" s="1">
-        <v>0</v>
-      </c>
-      <c r="P690" t="str">
-        <v/>
-      </c>
-      <c r="Q690" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R690" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="str">
-        <v>T260703-00024</v>
-      </c>
-      <c r="B691" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C691" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D691" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E691" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F691">
-        <v>1</v>
-      </c>
-      <c r="G691" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H691" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I691" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J691" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K691">
-        <v>1</v>
-      </c>
-      <c r="L691" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M691" t="str">
-        <v>2026-07-03 20:38:48</v>
-      </c>
-      <c r="N691" s="1">
-        <v>530000</v>
-      </c>
-      <c r="O691" s="1">
-        <v>0</v>
-      </c>
-      <c r="P691" t="str">
-        <v/>
-      </c>
-      <c r="Q691" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R691" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="str">
-        <v>T260703-00023</v>
-      </c>
-      <c r="B692" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C692" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D692" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E692" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F692">
-        <v>0</v>
-      </c>
-      <c r="G692" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="H692" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="I692" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J692" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K692">
-        <v>1</v>
-      </c>
-      <c r="L692" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M692" t="str">
-        <v>2026-07-03 20:38:28</v>
-      </c>
-      <c r="N692" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O692" s="1">
-        <v>0</v>
-      </c>
-      <c r="P692" t="str">
-        <v/>
-      </c>
-      <c r="Q692" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R692" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="str">
-        <v>T260703-00022</v>
-      </c>
-      <c r="B693" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C693" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D693" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E693" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F693">
-        <v>0</v>
-      </c>
-      <c r="G693" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H693" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I693" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J693" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K693">
-        <v>1</v>
-      </c>
-      <c r="L693" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M693" t="str">
-        <v>2026-07-03 20:38:14</v>
-      </c>
-      <c r="N693" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O693" s="1">
-        <v>0</v>
-      </c>
-      <c r="P693" t="str">
-        <v/>
-      </c>
-      <c r="Q693" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R693" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="str">
-        <v>T260703-00021</v>
-      </c>
-      <c r="B694" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C694" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D694" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E694" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F694">
-        <v>1</v>
-      </c>
-      <c r="G694" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H694" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I694" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J694" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K694">
-        <v>1</v>
-      </c>
-      <c r="L694" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M694" t="str">
-        <v>2026-07-03 20:37:59</v>
-      </c>
-      <c r="N694" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O694" s="1">
-        <v>0</v>
-      </c>
-      <c r="P694" t="str">
-        <v/>
-      </c>
-      <c r="Q694" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R694" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="str">
-        <v>T260703-00020</v>
-      </c>
-      <c r="B695" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C695" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D695" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E695" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F695">
-        <v>0</v>
-      </c>
-      <c r="G695" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H695" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I695" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J695" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K695">
-        <v>1</v>
-      </c>
-      <c r="L695" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M695" t="str">
-        <v>2026-07-03 20:37:40</v>
-      </c>
-      <c r="N695" s="1">
-        <v>490000</v>
-      </c>
-      <c r="O695" s="1">
-        <v>0</v>
-      </c>
-      <c r="P695" t="str">
-        <v/>
-      </c>
-      <c r="Q695" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R695" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="str">
-        <v>T260703-00019</v>
-      </c>
-      <c r="B696" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C696" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D696" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E696" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F696">
-        <v>0</v>
-      </c>
-      <c r="G696" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H696" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I696" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J696" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K696">
-        <v>1</v>
-      </c>
-      <c r="L696" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M696" t="str">
-        <v>2026-07-03 20:37:26</v>
-      </c>
-      <c r="N696" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O696" s="1">
-        <v>0</v>
-      </c>
-      <c r="P696" t="str">
-        <v/>
-      </c>
-      <c r="Q696" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R696" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="str">
-        <v>T260703-00018</v>
-      </c>
-      <c r="B697" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C697" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D697" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E697" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F697">
-        <v>0</v>
-      </c>
-      <c r="G697" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H697" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I697" t="str">
-        <v>2026-07-03 20:00</v>
-      </c>
-      <c r="J697" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K697">
-        <v>1</v>
-      </c>
-      <c r="L697" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M697" t="str">
-        <v>2026-07-03 20:37:11</v>
-      </c>
-      <c r="N697" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O697" s="1">
-        <v>0</v>
-      </c>
-      <c r="P697" t="str">
-        <v/>
-      </c>
-      <c r="Q697" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R697" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="str">
-        <v>T260703-00017</v>
-      </c>
-      <c r="B698" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C698" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D698" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E698" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F698">
-        <v>0</v>
-      </c>
-      <c r="G698" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H698" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I698" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J698" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K698">
-        <v>1</v>
-      </c>
-      <c r="L698" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M698" t="str">
-        <v>2026-07-03 20:36:55</v>
-      </c>
-      <c r="N698" s="1">
-        <v>420000</v>
-      </c>
-      <c r="O698" s="1">
-        <v>0</v>
-      </c>
-      <c r="P698" t="str">
-        <v/>
-      </c>
-      <c r="Q698" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R698" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="str">
-        <v>T260703-00016</v>
-      </c>
-      <c r="B699" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C699" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D699" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E699" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F699">
-        <v>0</v>
-      </c>
-      <c r="G699" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H699" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I699" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J699" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K699">
-        <v>1</v>
-      </c>
-      <c r="L699" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M699" t="str">
-        <v>2026-07-03 20:36:37</v>
-      </c>
-      <c r="N699" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O699" s="1">
-        <v>0</v>
-      </c>
-      <c r="P699" t="str">
-        <v/>
-      </c>
-      <c r="Q699" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R699" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="str">
-        <v>T260703-00015</v>
-      </c>
-      <c r="B700" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C700" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D700" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E700" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F700">
-        <v>0</v>
-      </c>
-      <c r="G700" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H700" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I700" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J700" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K700">
-        <v>1</v>
-      </c>
-      <c r="L700" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M700" t="str">
-        <v>2026-07-03 20:36:15</v>
-      </c>
-      <c r="N700" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O700" s="1">
-        <v>0</v>
-      </c>
-      <c r="P700" t="str">
-        <v/>
-      </c>
-      <c r="Q700" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R700" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="str">
-        <v>T260703-00014</v>
-      </c>
-      <c r="B701" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C701" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D701" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E701" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F701">
-        <v>1</v>
-      </c>
-      <c r="G701" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H701" t="str">
-        <v>경산시 해오름길114-2 경산FDC</v>
-      </c>
-      <c r="I701" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J701" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K701">
-        <v>1</v>
-      </c>
-      <c r="L701" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M701" t="str">
-        <v>2026-07-03 20:35:55</v>
-      </c>
-      <c r="N701" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O701" s="1">
-        <v>0</v>
-      </c>
-      <c r="P701" t="str">
-        <v/>
-      </c>
-      <c r="Q701" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R701" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="str">
-        <v>T260703-00013</v>
-      </c>
-      <c r="B702" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C702" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D702" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E702" t="str">
-        <v>2026-07-03 17:30</v>
-      </c>
-      <c r="F702">
-        <v>0</v>
-      </c>
-      <c r="G702" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H702" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I702" t="str">
-        <v>2026-07-03 18:30</v>
-      </c>
-      <c r="J702" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K702">
-        <v>1</v>
-      </c>
-      <c r="L702" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M702" t="str">
-        <v>2026-07-03 20:31:55</v>
-      </c>
-      <c r="N702" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O702" s="1">
-        <v>0</v>
-      </c>
-      <c r="P702" t="str">
-        <v/>
-      </c>
-      <c r="Q702" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R702" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="str">
-        <v>T260703-00012</v>
-      </c>
-      <c r="B703" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C703" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="D703" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="E703" t="str">
-        <v>2026-07-03 08:30</v>
-      </c>
-      <c r="F703">
-        <v>0</v>
-      </c>
-      <c r="G703" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="H703" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="I703" t="str">
-        <v>2026-07-03 11:30</v>
-      </c>
-      <c r="J703" t="str">
-        <v>3.5톤 카고</v>
-      </c>
-      <c r="K703">
-        <v>1</v>
-      </c>
-      <c r="L703" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M703" t="str">
-        <v>2026-07-03 20:31:21</v>
-      </c>
-      <c r="N703" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O703" s="1">
-        <v>0</v>
-      </c>
-      <c r="P703" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="Q703" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R703" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="str">
-        <v>T260703-00011</v>
-      </c>
-      <c r="B704" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C704" t="str">
-        <v>샤오미</v>
-      </c>
-      <c r="D704" t="str">
-        <v>경기 이천시 대월면 부필리 309 샤오미</v>
-      </c>
-      <c r="E704" t="str">
-        <v>2026-07-03 11:30</v>
-      </c>
-      <c r="F704">
-        <v>0</v>
-      </c>
-      <c r="G704" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H704" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I704" t="str">
-        <v>2026-07-03 13:30</v>
-      </c>
-      <c r="J704" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K704">
-        <v>1</v>
-      </c>
-      <c r="L704" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M704" t="str">
-        <v>2026-07-03 20:30:39</v>
-      </c>
-      <c r="N704" s="1">
-        <v>80000</v>
-      </c>
-      <c r="O704" s="1">
-        <v>0</v>
-      </c>
-      <c r="P704" t="str">
-        <v>거래처비용청구(1대)</v>
-      </c>
-      <c r="Q704" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R704" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="str">
-        <v>T260703-00010</v>
-      </c>
-      <c r="B705" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C705" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D705" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E705" t="str">
-        <v>2026-07-03 13:30</v>
-      </c>
-      <c r="F705">
-        <v>0</v>
-      </c>
-      <c r="G705" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H705" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I705" t="str">
-        <v>2026-07-03 15:30</v>
-      </c>
-      <c r="J705" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K705">
-        <v>1</v>
-      </c>
-      <c r="L705" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M705" t="str">
-        <v>2026-07-03 20:29:47</v>
-      </c>
-      <c r="N705" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O705" s="1">
-        <v>0</v>
-      </c>
-      <c r="P705" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q705" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R705" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="str">
-        <v>T260703-00009</v>
-      </c>
-      <c r="B706" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C706" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D706" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E706" t="str">
-        <v>2026-07-03 10:00</v>
-      </c>
-      <c r="F706">
-        <v>0</v>
-      </c>
-      <c r="G706" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H706" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I706" t="str">
-        <v>2026-07-03 13:30</v>
-      </c>
-      <c r="J706" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K706">
-        <v>1</v>
-      </c>
-      <c r="L706" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M706" t="str">
-        <v>2026-07-03 20:29:05</v>
-      </c>
-      <c r="N706" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O706" s="1">
-        <v>0</v>
-      </c>
-      <c r="P706" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q706" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R706" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="str">
-        <v>T260703-00008</v>
-      </c>
-      <c r="B707" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C707" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D707" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E707" t="str">
-        <v>2026-07-03 16:30</v>
-      </c>
-      <c r="F707">
-        <v>0</v>
-      </c>
-      <c r="G707" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H707" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I707" t="str">
-        <v>2026-07-03 18:00</v>
-      </c>
-      <c r="J707" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K707">
-        <v>1</v>
-      </c>
-      <c r="L707" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M707" t="str">
-        <v>2026-07-03 18:39:34</v>
-      </c>
-      <c r="N707" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O707" s="1">
-        <v>0</v>
-      </c>
-      <c r="P707" t="str">
-        <v>20260703/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q707" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R707" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="str">
-        <v>T260703-00007</v>
-      </c>
-      <c r="B708" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C708" t="str">
-        <v>청주ARC(공파렛트 이동)</v>
-      </c>
-      <c r="D708" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(공파렛트 이동)</v>
-      </c>
-      <c r="E708" t="str">
-        <v>2026-07-03 11:40</v>
-      </c>
-      <c r="F708">
-        <v>0</v>
-      </c>
-      <c r="G708" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H708" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="I708" t="str">
-        <v>2026-07-03 13:00</v>
-      </c>
-      <c r="J708" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K708">
-        <v>1</v>
-      </c>
-      <c r="L708" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M708" t="str">
-        <v>2026-07-03 11:28:01</v>
-      </c>
-      <c r="N708" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O708" s="1">
-        <v>0</v>
-      </c>
-      <c r="P708" t="str">
-        <v>20260703청주-&gt; 안성FC/공파렛트이동</v>
-      </c>
-      <c r="Q708" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R708" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="str">
-        <v>T260703-00006</v>
-      </c>
-      <c r="B709" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C709" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D709" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E709" t="str">
-        <v>2026-07-03 11:55</v>
-      </c>
-      <c r="F709">
-        <v>0</v>
-      </c>
-      <c r="G709" t="str">
-        <v>하이얼(서울 벌크 출하)</v>
-      </c>
-      <c r="H709" t="str">
-        <v>서울 강남구 선릉로92길 38 도파민</v>
-      </c>
-      <c r="I709" t="str">
-        <v>2026-07-03 13:00</v>
-      </c>
-      <c r="J709" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K709">
-        <v>1</v>
-      </c>
-      <c r="L709" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M709" t="str">
-        <v>2026-07-03 11:26:22</v>
-      </c>
-      <c r="N709" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O709" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P709" t="str">
-        <v>20260703/하이얼_서울_벌크_출하</v>
-      </c>
-      <c r="Q709" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R709" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="str">
-        <v>T260703-00005</v>
-      </c>
-      <c r="B710" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C710" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D710" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E710" t="str">
-        <v>2026-07-03 11:00</v>
-      </c>
-      <c r="F710">
-        <v>0</v>
-      </c>
-      <c r="G710" t="str">
-        <v>파주 하이마트 물류</v>
-      </c>
-      <c r="H710" t="str">
-        <v>경기 파주시 탄현면 월롱산로 296 파주 하이마트 물류</v>
-      </c>
-      <c r="I710" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J710" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K710">
-        <v>1</v>
-      </c>
-      <c r="L710" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M710" t="str">
-        <v>2026-07-03 11:22:28</v>
-      </c>
-      <c r="N710" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O710" s="1">
-        <v>0</v>
-      </c>
-      <c r="P710" t="str">
-        <v>일코전자 파주 하이마트 물류</v>
-      </c>
-      <c r="Q710" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R710" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="str">
-        <v>T260703-00004</v>
-      </c>
-      <c r="B711" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C711" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D711" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지  안성FC</v>
-      </c>
-      <c r="E711" t="str">
-        <v>2026-07-03 09:30</v>
-      </c>
-      <c r="F711">
-        <v>0</v>
-      </c>
-      <c r="G711" t="str">
-        <v>TCL다코넷</v>
-      </c>
-      <c r="H711" t="str">
-        <v>경기 평택시 포승읍 희곡리 847 평택 켄달스퀘어 3층, 다코넷 37번 도크</v>
-      </c>
-      <c r="I711" t="str">
-        <v>2026-07-03 11:30</v>
-      </c>
-      <c r="J711" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K711">
-        <v>1</v>
-      </c>
-      <c r="L711" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M711" t="str">
-        <v>2026-07-03 11:21:17</v>
-      </c>
-      <c r="N711" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O711" s="1">
-        <v>0</v>
-      </c>
-      <c r="P711" t="str">
-        <v>TCL 다코넷</v>
-      </c>
-      <c r="Q711" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R711" t="str">
-        <v>TCL</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="str">
-        <v>T260703-00003</v>
-      </c>
-      <c r="B712" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C712" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D712" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E712" t="str">
-        <v>2026-07-03 13:00</v>
-      </c>
-      <c r="F712">
-        <v>0</v>
-      </c>
-      <c r="G712" t="str">
-        <v>이천 하이마트 물류</v>
-      </c>
-      <c r="H712" t="str">
-        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 물류</v>
-      </c>
-      <c r="I712" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J712" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K712">
-        <v>1</v>
-      </c>
-      <c r="L712" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M712" t="str">
-        <v>2026-07-03 11:19:40</v>
-      </c>
-      <c r="N712" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O712" s="1">
-        <v>0</v>
-      </c>
-      <c r="P712" t="str">
-        <v>일코전자 이천 하이마트 물류</v>
-      </c>
-      <c r="Q712" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R712" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="str">
-        <v>T260703-00002</v>
-      </c>
-      <c r="B713" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C713" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D713" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E713" t="str">
-        <v>2026-07-03 10:00</v>
-      </c>
-      <c r="F713">
-        <v>0</v>
-      </c>
-      <c r="G713" t="str">
-        <v>화성 하이마트 물류</v>
-      </c>
-      <c r="H713" t="str">
-        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 물류</v>
-      </c>
-      <c r="I713" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J713" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K713">
-        <v>1</v>
-      </c>
-      <c r="L713" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M713" t="str">
-        <v>2026-07-03 11:18:03</v>
-      </c>
-      <c r="N713" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O713" s="1">
-        <v>0</v>
-      </c>
-      <c r="P713" t="str">
-        <v>일코전자 화성 하이마트 물류</v>
-      </c>
-      <c r="Q713" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R713" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="str">
-        <v>T260703-00001</v>
-      </c>
-      <c r="B714" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C714" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D714" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E714" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="F714">
-        <v>0</v>
-      </c>
-      <c r="G714" t="str">
-        <v>인천 하이마트 물류</v>
-      </c>
-      <c r="H714" t="str">
-        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
-      </c>
-      <c r="I714" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J714" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K714">
-        <v>1</v>
-      </c>
-      <c r="L714" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M714" t="str">
-        <v>2026-07-03 11:16:52</v>
-      </c>
-      <c r="N714" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O714" s="1">
-        <v>0</v>
-      </c>
-      <c r="P714" t="str">
-        <v>일코전자 인천 하이마트 물류</v>
-      </c>
-      <c r="Q714" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R714" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="str">
-        <v>T260702-00027</v>
-      </c>
-      <c r="B715" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C715" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D715" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E715" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F715">
-        <v>1</v>
-      </c>
-      <c r="G715" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H715" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I715" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J715" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K715">
-        <v>1</v>
-      </c>
-      <c r="L715" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M715" t="str">
-        <v>2026-07-02 20:54:21</v>
-      </c>
-      <c r="N715" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O715" s="1">
-        <v>0</v>
-      </c>
-      <c r="P715" t="str">
-        <v/>
-      </c>
-      <c r="Q715" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R715" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="str">
-        <v>T260702-00026</v>
-      </c>
-      <c r="B716" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C716" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D716" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E716" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F716">
-        <v>1</v>
-      </c>
-      <c r="G716" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H716" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I716" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J716" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K716">
-        <v>1</v>
-      </c>
-      <c r="L716" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M716" t="str">
-        <v>2026-07-02 20:53:56</v>
-      </c>
-      <c r="N716" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O716" s="1">
-        <v>0</v>
-      </c>
-      <c r="P716" t="str">
-        <v/>
-      </c>
-      <c r="Q716" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R716" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="str">
-        <v>T260702-00025</v>
-      </c>
-      <c r="B717" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C717" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D717" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E717" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F717">
-        <v>3</v>
-      </c>
-      <c r="G717" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H717" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I717" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J717" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K717">
-        <v>1</v>
-      </c>
-      <c r="L717" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M717" t="str">
-        <v>2026-07-02 20:53:28</v>
-      </c>
-      <c r="N717" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O717" s="1">
-        <v>0</v>
-      </c>
-      <c r="P717" t="str">
-        <v/>
-      </c>
-      <c r="Q717" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R717" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="str">
-        <v>T260702-00024</v>
-      </c>
-      <c r="B718" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C718" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D718" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E718" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F718">
-        <v>0</v>
-      </c>
-      <c r="G718" t="str">
-        <v>용인ACP</v>
-      </c>
-      <c r="H718" t="str">
-        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
-      </c>
-      <c r="I718" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J718" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K718">
-        <v>1</v>
-      </c>
-      <c r="L718" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M718" t="str">
-        <v>2026-07-02 20:52:18</v>
-      </c>
-      <c r="N718" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O718" s="1">
-        <v>0</v>
-      </c>
-      <c r="P718" t="str">
-        <v/>
-      </c>
-      <c r="Q718" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R718" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="str">
-        <v>T260702-00023</v>
-      </c>
-      <c r="B719" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C719" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D719" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E719" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F719">
-        <v>1</v>
-      </c>
-      <c r="G719" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H719" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I719" t="str">
-        <v>2026-07-03 07:00</v>
-      </c>
-      <c r="J719" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K719">
-        <v>1</v>
-      </c>
-      <c r="L719" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M719" t="str">
-        <v>2026-07-02 20:51:59</v>
-      </c>
-      <c r="N719" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O719" s="1">
-        <v>0</v>
-      </c>
-      <c r="P719" t="str">
-        <v/>
-      </c>
-      <c r="Q719" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R719" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="str">
-        <v>T260702-00022</v>
-      </c>
-      <c r="B720" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C720" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D720" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E720" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F720">
-        <v>0</v>
-      </c>
-      <c r="G720" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H720" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I720" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J720" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K720">
-        <v>1</v>
-      </c>
-      <c r="L720" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M720" t="str">
-        <v>2026-07-02 20:51:32</v>
-      </c>
-      <c r="N720" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O720" s="1">
-        <v>0</v>
-      </c>
-      <c r="P720" t="str">
-        <v/>
-      </c>
-      <c r="Q720" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R720" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="str">
-        <v>T260702-00021</v>
-      </c>
-      <c r="B721" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C721" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D721" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E721" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F721">
-        <v>1</v>
-      </c>
-      <c r="G721" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H721" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I721" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J721" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K721">
-        <v>1</v>
-      </c>
-      <c r="L721" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M721" t="str">
-        <v>2026-07-02 20:51:14</v>
-      </c>
-      <c r="N721" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O721" s="1">
-        <v>0</v>
-      </c>
-      <c r="P721" t="str">
-        <v/>
-      </c>
-      <c r="Q721" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R721" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="str">
-        <v>T260702-00020</v>
-      </c>
-      <c r="B722" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C722" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D722" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E722" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F722">
-        <v>0</v>
-      </c>
-      <c r="G722" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="H722" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="I722" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J722" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K722">
-        <v>1</v>
-      </c>
-      <c r="L722" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M722" t="str">
-        <v>2026-07-02 20:50:54</v>
-      </c>
-      <c r="N722" s="1">
-        <v>280000</v>
-      </c>
-      <c r="O722" s="1">
-        <v>0</v>
-      </c>
-      <c r="P722" t="str">
-        <v/>
-      </c>
-      <c r="Q722" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R722" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="str">
-        <v>T260702-00019</v>
-      </c>
-      <c r="B723" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C723" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D723" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E723" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F723">
-        <v>0</v>
-      </c>
-      <c r="G723" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H723" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I723" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J723" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K723">
-        <v>1</v>
-      </c>
-      <c r="L723" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M723" t="str">
-        <v>2026-07-02 20:50:36</v>
-      </c>
-      <c r="N723" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O723" s="1">
-        <v>0</v>
-      </c>
-      <c r="P723" t="str">
-        <v/>
-      </c>
-      <c r="Q723" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R723" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="str">
-        <v>T260702-00018</v>
-      </c>
-      <c r="B724" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C724" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D724" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E724" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F724">
-        <v>1</v>
-      </c>
-      <c r="G724" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H724" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I724" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J724" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K724">
-        <v>1</v>
-      </c>
-      <c r="L724" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M724" t="str">
-        <v>2026-07-02 20:50:19</v>
-      </c>
-      <c r="N724" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O724" s="1">
-        <v>0</v>
-      </c>
-      <c r="P724" t="str">
-        <v/>
-      </c>
-      <c r="Q724" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R724" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="str">
-        <v>T260702-00017</v>
-      </c>
-      <c r="B725" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C725" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D725" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E725" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F725">
-        <v>1</v>
-      </c>
-      <c r="G725" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H725" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I725" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J725" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K725">
-        <v>1</v>
-      </c>
-      <c r="L725" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M725" t="str">
-        <v>2026-07-02 20:49:56</v>
-      </c>
-      <c r="N725" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O725" s="1">
-        <v>0</v>
-      </c>
-      <c r="P725" t="str">
-        <v/>
-      </c>
-      <c r="Q725" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R725" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="str">
-        <v>T260702-00016</v>
-      </c>
-      <c r="B726" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C726" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D726" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E726" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F726">
-        <v>0</v>
-      </c>
-      <c r="G726" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H726" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I726" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J726" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K726">
-        <v>1</v>
-      </c>
-      <c r="L726" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M726" t="str">
-        <v>2026-07-02 20:49:25</v>
-      </c>
-      <c r="N726" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O726" s="1">
-        <v>0</v>
-      </c>
-      <c r="P726" t="str">
-        <v/>
-      </c>
-      <c r="Q726" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R726" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="str">
-        <v>T260702-00015</v>
-      </c>
-      <c r="B727" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C727" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D727" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E727" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F727">
-        <v>1</v>
-      </c>
-      <c r="G727" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H727" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I727" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J727" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K727">
-        <v>1</v>
-      </c>
-      <c r="L727" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M727" t="str">
-        <v>2026-07-02 20:48:50</v>
-      </c>
-      <c r="N727" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O727" s="1">
-        <v>0</v>
-      </c>
-      <c r="P727" t="str">
-        <v/>
-      </c>
-      <c r="Q727" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R727" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="str">
-        <v>T260702-00014</v>
-      </c>
-      <c r="B728" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C728" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D728" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E728" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F728">
-        <v>0</v>
-      </c>
-      <c r="G728" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H728" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I728" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J728" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K728">
-        <v>1</v>
-      </c>
-      <c r="L728" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M728" t="str">
-        <v>2026-07-02 20:48:25</v>
-      </c>
-      <c r="N728" s="1">
-        <v>420000</v>
-      </c>
-      <c r="O728" s="1">
-        <v>0</v>
-      </c>
-      <c r="P728" t="str">
-        <v/>
-      </c>
-      <c r="Q728" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R728" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="str">
-        <v>T260702-00013</v>
-      </c>
-      <c r="B729" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C729" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D729" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E729" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F729">
-        <v>0</v>
-      </c>
-      <c r="G729" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H729" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I729" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J729" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K729">
-        <v>1</v>
-      </c>
-      <c r="L729" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M729" t="str">
-        <v>2026-07-02 20:48:09</v>
-      </c>
-      <c r="N729" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O729" s="1">
-        <v>0</v>
-      </c>
-      <c r="P729" t="str">
-        <v/>
-      </c>
-      <c r="Q729" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R729" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="str">
-        <v>T260702-00012</v>
-      </c>
-      <c r="B730" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C730" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D730" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E730" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F730">
-        <v>2</v>
-      </c>
-      <c r="G730" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H730" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I730" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J730" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K730">
-        <v>1</v>
-      </c>
-      <c r="L730" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M730" t="str">
-        <v>2026-07-02 20:47:49</v>
-      </c>
-      <c r="N730" s="1">
-        <v>680000</v>
-      </c>
-      <c r="O730" s="1">
-        <v>0</v>
-      </c>
-      <c r="P730" t="str">
-        <v/>
-      </c>
-      <c r="Q730" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R730" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="str">
-        <v>T260702-00011</v>
-      </c>
-      <c r="B731" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C731" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D731" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E731" t="str">
-        <v>2026-07-02 17:50</v>
-      </c>
-      <c r="F731">
-        <v>0</v>
-      </c>
-      <c r="G731" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H731" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I731" t="str">
-        <v>2026-07-02 18:50</v>
-      </c>
-      <c r="J731" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K731">
-        <v>1</v>
-      </c>
-      <c r="L731" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M731" t="str">
-        <v>2026-07-02 20:44:59</v>
-      </c>
-      <c r="N731" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O731" s="1">
-        <v>0</v>
-      </c>
-      <c r="P731" t="str">
-        <v/>
-      </c>
-      <c r="Q731" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R731" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="str">
-        <v>T260702-00010</v>
-      </c>
-      <c r="B732" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C732" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D732" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E732" t="str">
-        <v>2026-07-02 13:30</v>
-      </c>
-      <c r="F732">
-        <v>0</v>
-      </c>
-      <c r="G732" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H732" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I732" t="str">
-        <v>2026-07-02 15:40</v>
-      </c>
-      <c r="J732" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K732">
-        <v>1</v>
-      </c>
-      <c r="L732" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M732" t="str">
-        <v>2026-07-02 20:44:26</v>
-      </c>
-      <c r="N732" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O732" s="1">
-        <v>0</v>
-      </c>
-      <c r="P732" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q732" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R732" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="str">
-        <v>T260702-00009</v>
-      </c>
-      <c r="B733" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C733" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D733" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E733" t="str">
-        <v>2026-07-02 10:00</v>
-      </c>
-      <c r="F733">
-        <v>0</v>
-      </c>
-      <c r="G733" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H733" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I733" t="str">
-        <v>2026-07-02 13:40</v>
-      </c>
-      <c r="J733" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K733">
-        <v>1</v>
-      </c>
-      <c r="L733" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M733" t="str">
-        <v>2026-07-02 20:43:37</v>
-      </c>
-      <c r="N733" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O733" s="1">
-        <v>0</v>
-      </c>
-      <c r="P733" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q733" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R733" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="str">
-        <v>T260702-00008</v>
-      </c>
-      <c r="B734" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C734" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D734" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E734" t="str">
-        <v>2026-07-02 17:00</v>
-      </c>
-      <c r="F734">
-        <v>0</v>
-      </c>
-      <c r="G734" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="H734" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="I734" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J734" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K734">
-        <v>1</v>
-      </c>
-      <c r="L734" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M734" t="str">
-        <v>2026-07-02 16:38:23</v>
-      </c>
-      <c r="N734" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O734" s="1">
-        <v>0</v>
-      </c>
-      <c r="P734" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="Q734" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R734" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="str">
-        <v>T260702-00007</v>
-      </c>
-      <c r="B735" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C735" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D735" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E735" t="str">
-        <v>2026-07-02 16:30</v>
-      </c>
-      <c r="F735">
-        <v>0</v>
-      </c>
-      <c r="G735" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H735" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I735" t="str">
-        <v>2026-07-02 18:00</v>
-      </c>
-      <c r="J735" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K735">
-        <v>1</v>
-      </c>
-      <c r="L735" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M735" t="str">
-        <v>2026-07-02 16:34:35</v>
-      </c>
-      <c r="N735" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O735" s="1">
-        <v>0</v>
-      </c>
-      <c r="P735" t="str">
-        <v>20260702/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q735" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R735" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="str">
-        <v>T260702-00006</v>
-      </c>
-      <c r="B736" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C736" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D736" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E736" t="str">
-        <v>2026-07-02 16:00</v>
-      </c>
-      <c r="F736">
-        <v>0</v>
-      </c>
-      <c r="G736" t="str">
-        <v>광주 하이마트 물류</v>
-      </c>
-      <c r="H736" t="str">
-        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
-      </c>
-      <c r="I736" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J736" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K736">
-        <v>1</v>
-      </c>
-      <c r="L736" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M736" t="str">
-        <v>2026-07-02 15:30:55</v>
-      </c>
-      <c r="N736" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O736" s="1">
-        <v>0</v>
-      </c>
-      <c r="P736" t="str">
-        <v>일코 광주 하이마트 물류</v>
-      </c>
-      <c r="Q736" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R736" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="str">
-        <v>T260702-00005</v>
-      </c>
-      <c r="B737" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C737" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D737" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E737" t="str">
-        <v>2026-07-02 14:30</v>
-      </c>
-      <c r="F737">
-        <v>0</v>
-      </c>
-      <c r="G737" t="str">
-        <v>마산 하이마트 물류</v>
-      </c>
-      <c r="H737" t="str">
-        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
-      </c>
-      <c r="I737" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J737" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K737">
-        <v>1</v>
-      </c>
-      <c r="L737" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M737" t="str">
-        <v>2026-07-02 13:44:41</v>
-      </c>
-      <c r="N737" s="1">
-        <v>380000</v>
-      </c>
-      <c r="O737" s="1">
-        <v>0</v>
-      </c>
-      <c r="P737" t="str">
-        <v>일코 마산 하이마트 물류</v>
-      </c>
-      <c r="Q737" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R737" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="str">
-        <v>T260702-00004</v>
-      </c>
-      <c r="B738" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C738" t="str">
-        <v>강릉 하이마트 물류</v>
-      </c>
-      <c r="D738" t="str">
-        <v>강원특별자치도 강릉시 연곡면 동해대로 4100-36 강릉 하이마트 물류</v>
-      </c>
-      <c r="E738" t="str">
-        <v>2026-07-02 13:30</v>
-      </c>
-      <c r="F738">
-        <v>0</v>
-      </c>
-      <c r="G738" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H738" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I738" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J738" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K738">
-        <v>1</v>
-      </c>
-      <c r="L738" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M738" t="str">
-        <v>2026-07-02 12:00:10</v>
-      </c>
-      <c r="N738" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O738" s="1">
-        <v>0</v>
-      </c>
-      <c r="P738" t="str">
-        <v>일코전자 강릉 하이마트 물류</v>
-      </c>
-      <c r="Q738" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R738" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="str">
-        <v>T260702-00003</v>
-      </c>
-      <c r="B739" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C739" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D739" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E739" t="str">
-        <v>2026-07-02 14:30</v>
-      </c>
-      <c r="F739">
-        <v>0</v>
-      </c>
-      <c r="G739" t="str">
-        <v>대구 하이마트 물류</v>
-      </c>
-      <c r="H739" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="I739" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J739" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K739">
-        <v>1</v>
-      </c>
-      <c r="L739" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M739" t="str">
-        <v>2026-07-02 11:59:32</v>
-      </c>
-      <c r="N739" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O739" s="1">
-        <v>0</v>
-      </c>
-      <c r="P739" t="str">
-        <v>일코전자 대구 하이마트 물류</v>
-      </c>
-      <c r="Q739" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R739" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="str">
-        <v>T260702-00002</v>
-      </c>
-      <c r="B740" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C740" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D740" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E740" t="str">
-        <v>2026-07-02 09:30</v>
-      </c>
-      <c r="F740">
-        <v>1</v>
-      </c>
-      <c r="G740" t="str">
-        <v>하이얼(대구2착)</v>
-      </c>
-      <c r="H740" t="str">
-        <v>대구 남구 양지로 25 대명자이 아파트</v>
-      </c>
-      <c r="I740" t="str">
-        <v>2026-07-02 15:00</v>
-      </c>
-      <c r="J740" t="str">
-        <v>1.5톤 윙바디</v>
-      </c>
-      <c r="K740">
-        <v>1</v>
-      </c>
-      <c r="L740" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M740" t="str">
-        <v>2026-07-02 09:20:07</v>
-      </c>
-      <c r="N740" s="1">
-        <v>220000</v>
-      </c>
-      <c r="O740" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P740" t="str">
-        <v>20260702/하이얼_대구 착지 2곳_벌크_출하</v>
-      </c>
-      <c r="Q740" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R740" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="str">
-        <v>T260702-00001</v>
-      </c>
-      <c r="B741" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C741" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D741" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E741" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="F741">
-        <v>0</v>
-      </c>
-      <c r="G741" t="str">
-        <v>로지스밸리인천포트(Logisvalley)</v>
-      </c>
-      <c r="H741" t="str">
-        <v>인천 연수구 인천타워대로599번길 60 로지스밸리인천포트(Logisvalley) 1층 13번(HTC)</v>
-      </c>
-      <c r="I741" t="str">
-        <v>2026-07-02 11:00</v>
-      </c>
-      <c r="J741" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K741">
-        <v>1</v>
-      </c>
-      <c r="L741" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M741" t="str">
-        <v>2026-07-02 09:17:29</v>
-      </c>
-      <c r="N741" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O741" s="1">
-        <v>0</v>
-      </c>
-      <c r="P741" t="str">
-        <v>패스트레인 출하</v>
-      </c>
-      <c r="Q741" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R741" t="str">
-        <v>패스트레인코리아</v>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="str">
-        <v>T260701-00026</v>
-      </c>
-      <c r="B742" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C742" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D742" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E742" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F742">
-        <v>1</v>
-      </c>
-      <c r="G742" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H742" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I742" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J742" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K742">
-        <v>1</v>
-      </c>
-      <c r="L742" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M742" t="str">
-        <v>2026-07-01 19:47:13</v>
-      </c>
-      <c r="N742" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O742" s="1">
-        <v>0</v>
-      </c>
-      <c r="P742" t="str">
-        <v/>
-      </c>
-      <c r="Q742" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R742" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="str">
-        <v>T260701-00025</v>
-      </c>
-      <c r="B743" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C743" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D743" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E743" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F743">
-        <v>2</v>
-      </c>
-      <c r="G743" t="str">
-        <v>원주ACP</v>
-      </c>
-      <c r="H743" t="str">
-        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
-      </c>
-      <c r="I743" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J743" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K743">
-        <v>1</v>
-      </c>
-      <c r="L743" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M743" t="str">
-        <v>2026-07-01 19:46:48</v>
-      </c>
-      <c r="N743" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O743" s="1">
-        <v>0</v>
-      </c>
-      <c r="P743" t="str">
-        <v/>
-      </c>
-      <c r="Q743" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R743" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="str">
-        <v>T260701-00024</v>
-      </c>
-      <c r="B744" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C744" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D744" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E744" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F744">
-        <v>1</v>
-      </c>
-      <c r="G744" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H744" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I744" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J744" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K744">
-        <v>1</v>
-      </c>
-      <c r="L744" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M744" t="str">
-        <v>2026-07-01 19:46:12</v>
-      </c>
-      <c r="N744" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O744" s="1">
-        <v>0</v>
-      </c>
-      <c r="P744" t="str">
-        <v/>
-      </c>
-      <c r="Q744" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R744" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="str">
-        <v>T260701-00023</v>
-      </c>
-      <c r="B745" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C745" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D745" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E745" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F745">
-        <v>3</v>
-      </c>
-      <c r="G745" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H745" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I745" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J745" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K745">
-        <v>1</v>
-      </c>
-      <c r="L745" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M745" t="str">
-        <v>2026-07-01 19:45:40</v>
-      </c>
-      <c r="N745" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O745" s="1">
-        <v>0</v>
-      </c>
-      <c r="P745" t="str">
-        <v/>
-      </c>
-      <c r="Q745" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R745" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="str">
-        <v>T260701-00022</v>
-      </c>
-      <c r="B746" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C746" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D746" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E746" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F746">
-        <v>0</v>
-      </c>
-      <c r="G746" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H746" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I746" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J746" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K746">
-        <v>1</v>
-      </c>
-      <c r="L746" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M746" t="str">
-        <v>2026-07-01 19:44:56</v>
-      </c>
-      <c r="N746" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O746" s="1">
-        <v>0</v>
-      </c>
-      <c r="P746" t="str">
-        <v/>
-      </c>
-      <c r="Q746" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R746" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="str">
-        <v>T260701-00021</v>
-      </c>
-      <c r="B747" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C747" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D747" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E747" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F747">
-        <v>1</v>
-      </c>
-      <c r="G747" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H747" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I747" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J747" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K747">
-        <v>1</v>
-      </c>
-      <c r="L747" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M747" t="str">
-        <v>2026-07-01 19:44:37</v>
-      </c>
-      <c r="N747" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O747" s="1">
-        <v>0</v>
-      </c>
-      <c r="P747" t="str">
-        <v/>
-      </c>
-      <c r="Q747" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R747" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="str">
-        <v>T260701-00020</v>
-      </c>
-      <c r="B748" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C748" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D748" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E748" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F748">
-        <v>2</v>
-      </c>
-      <c r="G748" t="str">
-        <v>속초ACP</v>
-      </c>
-      <c r="H748" t="str">
-        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
-      </c>
-      <c r="I748" t="str">
-        <v>2026-07-02 06:00</v>
-      </c>
-      <c r="J748" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K748">
-        <v>1</v>
-      </c>
-      <c r="L748" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M748" t="str">
-        <v>2026-07-01 19:44:05</v>
-      </c>
-      <c r="N748" s="1">
-        <v>320000</v>
-      </c>
-      <c r="O748" s="1">
-        <v>0</v>
-      </c>
-      <c r="P748" t="str">
-        <v/>
-      </c>
-      <c r="Q748" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R748" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" t="str">
-        <v>T260701-00019</v>
-      </c>
-      <c r="B749" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C749" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D749" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E749" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F749">
-        <v>0</v>
-      </c>
-      <c r="G749" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H749" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I749" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J749" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K749">
-        <v>1</v>
-      </c>
-      <c r="L749" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M749" t="str">
-        <v>2026-07-01 19:43:22</v>
-      </c>
-      <c r="N749" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O749" s="1">
-        <v>0</v>
-      </c>
-      <c r="P749" t="str">
-        <v/>
-      </c>
-      <c r="Q749" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R749" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="str">
-        <v>T260701-00018</v>
-      </c>
-      <c r="B750" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C750" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D750" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E750" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F750">
-        <v>1</v>
-      </c>
-      <c r="G750" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H750" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I750" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J750" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K750">
-        <v>1</v>
-      </c>
-      <c r="L750" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M750" t="str">
-        <v>2026-07-01 19:43:03</v>
-      </c>
-      <c r="N750" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O750" s="1">
-        <v>0</v>
-      </c>
-      <c r="P750" t="str">
-        <v/>
-      </c>
-      <c r="Q750" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R750" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="str">
-        <v>T260701-00017</v>
-      </c>
-      <c r="B751" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C751" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D751" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E751" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F751">
-        <v>0</v>
-      </c>
-      <c r="G751" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H751" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I751" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J751" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K751">
-        <v>1</v>
-      </c>
-      <c r="L751" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M751" t="str">
-        <v>2026-07-01 19:42:39</v>
-      </c>
-      <c r="N751" s="1">
-        <v>310000</v>
-      </c>
-      <c r="O751" s="1">
-        <v>0</v>
-      </c>
-      <c r="P751" t="str">
-        <v/>
-      </c>
-      <c r="Q751" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R751" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="str">
-        <v>T260701-00016</v>
-      </c>
-      <c r="B752" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C752" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D752" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E752" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F752">
-        <v>0</v>
-      </c>
-      <c r="G752" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H752" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I752" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J752" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K752">
-        <v>1</v>
-      </c>
-      <c r="L752" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M752" t="str">
-        <v>2026-07-01 19:42:17</v>
-      </c>
-      <c r="N752" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O752" s="1">
-        <v>0</v>
-      </c>
-      <c r="P752" t="str">
-        <v/>
-      </c>
-      <c r="Q752" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R752" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="str">
-        <v>T260701-00015</v>
-      </c>
-      <c r="B753" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C753" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D753" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E753" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F753">
-        <v>1</v>
-      </c>
-      <c r="G753" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H753" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I753" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J753" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K753">
-        <v>1</v>
-      </c>
-      <c r="L753" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M753" t="str">
-        <v>2026-07-01 19:42:02</v>
-      </c>
-      <c r="N753" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O753" s="1">
-        <v>0</v>
-      </c>
-      <c r="P753" t="str">
-        <v/>
-      </c>
-      <c r="Q753" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R753" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="str">
-        <v>T260701-00014</v>
-      </c>
-      <c r="B754" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C754" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D754" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E754" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F754">
-        <v>1</v>
-      </c>
-      <c r="G754" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H754" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I754" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J754" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K754">
-        <v>1</v>
-      </c>
-      <c r="L754" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M754" t="str">
-        <v>2026-07-01 19:41:41</v>
-      </c>
-      <c r="N754" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O754" s="1">
-        <v>0</v>
-      </c>
-      <c r="P754" t="str">
-        <v/>
-      </c>
-      <c r="Q754" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R754" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="str">
-        <v>T260701-00013</v>
-      </c>
-      <c r="B755" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C755" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D755" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E755" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F755">
-        <v>1</v>
-      </c>
-      <c r="G755" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H755" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I755" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J755" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K755">
-        <v>1</v>
-      </c>
-      <c r="L755" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M755" t="str">
-        <v>2026-07-01 19:41:08</v>
-      </c>
-      <c r="N755" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O755" s="1">
-        <v>0</v>
-      </c>
-      <c r="P755" t="str">
-        <v/>
-      </c>
-      <c r="Q755" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R755" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="str">
-        <v>T260701-00012</v>
-      </c>
-      <c r="B756" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C756" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D756" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E756" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F756">
-        <v>1</v>
-      </c>
-      <c r="G756" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H756" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I756" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J756" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K756">
-        <v>1</v>
-      </c>
-      <c r="L756" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M756" t="str">
-        <v>2026-07-01 19:40:45</v>
-      </c>
-      <c r="N756" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O756" s="1">
-        <v>0</v>
-      </c>
-      <c r="P756" t="str">
-        <v/>
-      </c>
-      <c r="Q756" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R756" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="str">
-        <v>T260701-00011</v>
-      </c>
-      <c r="B757" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C757" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D757" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E757" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F757">
-        <v>0</v>
-      </c>
-      <c r="G757" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H757" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I757" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J757" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K757">
-        <v>1</v>
-      </c>
-      <c r="L757" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M757" t="str">
-        <v>2026-07-01 19:40:21</v>
-      </c>
-      <c r="N757" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O757" s="1">
-        <v>0</v>
-      </c>
-      <c r="P757" t="str">
-        <v/>
-      </c>
-      <c r="Q757" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R757" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="str">
-        <v>T260701-00010</v>
-      </c>
-      <c r="B758" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C758" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D758" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E758" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F758">
-        <v>1</v>
-      </c>
-      <c r="G758" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H758" t="str">
-        <v>경산시 해오름길114-2 경산FDC</v>
-      </c>
-      <c r="I758" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J758" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K758">
-        <v>1</v>
-      </c>
-      <c r="L758" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M758" t="str">
-        <v>2026-07-01 19:40:04</v>
-      </c>
-      <c r="N758" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O758" s="1">
-        <v>0</v>
-      </c>
-      <c r="P758" t="str">
-        <v/>
-      </c>
-      <c r="Q758" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R758" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="str">
-        <v>T260701-00009</v>
-      </c>
-      <c r="B759" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C759" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D759" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E759" t="str">
-        <v>2026-07-01 17:30</v>
-      </c>
-      <c r="F759">
-        <v>0</v>
-      </c>
-      <c r="G759" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H759" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I759" t="str">
-        <v>2026-07-01 18:30</v>
-      </c>
-      <c r="J759" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K759">
-        <v>1</v>
-      </c>
-      <c r="L759" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M759" t="str">
-        <v>2026-07-01 19:31:35</v>
-      </c>
-      <c r="N759" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O759" s="1">
-        <v>0</v>
-      </c>
-      <c r="P759" t="str">
-        <v/>
-      </c>
-      <c r="Q759" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R759" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="760">
-      <c r="A760" t="str">
-        <v>T260701-00008</v>
-      </c>
-      <c r="B760" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C760" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D760" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E760" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="F760">
-        <v>0</v>
-      </c>
-      <c r="G760" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H760" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I760" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="J760" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K760">
-        <v>1</v>
-      </c>
-      <c r="L760" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M760" t="str">
-        <v>2026-07-01 19:31:02</v>
-      </c>
-      <c r="N760" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O760" s="1">
-        <v>0</v>
-      </c>
-      <c r="P760" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q760" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R760" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" t="str">
-        <v>T260701-00007</v>
-      </c>
-      <c r="B761" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C761" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D761" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E761" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F761">
-        <v>0</v>
-      </c>
-      <c r="G761" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H761" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I761" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="J761" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K761">
-        <v>1</v>
-      </c>
-      <c r="L761" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M761" t="str">
-        <v>2026-07-01 19:29:27</v>
-      </c>
-      <c r="N761" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O761" s="1">
-        <v>0</v>
-      </c>
-      <c r="P761" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q761" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R761" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="762">
-      <c r="A762" t="str">
-        <v>T260701-00006</v>
-      </c>
-      <c r="B762" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C762" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D762" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E762" t="str">
-        <v>2026-07-01 16:30</v>
-      </c>
-      <c r="F762">
-        <v>0</v>
-      </c>
-      <c r="G762" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H762" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I762" t="str">
-        <v>2026-07-01 18:00</v>
-      </c>
-      <c r="J762" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K762">
-        <v>1</v>
-      </c>
-      <c r="L762" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M762" t="str">
-        <v>2026-07-01 16:09:24</v>
-      </c>
-      <c r="N762" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O762" s="1">
-        <v>0</v>
-      </c>
-      <c r="P762" t="str">
-        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q762" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R762" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="763">
-      <c r="A763" t="str">
-        <v>T260701-00005</v>
-      </c>
-      <c r="B763" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C763" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D763" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E763" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="F763">
-        <v>0</v>
-      </c>
-      <c r="G763" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H763" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I763" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J763" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K763">
-        <v>1</v>
-      </c>
-      <c r="L763" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M763" t="str">
-        <v>2026-07-01 14:58:37</v>
-      </c>
-      <c r="N763" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O763" s="1">
-        <v>0</v>
-      </c>
-      <c r="P763" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q763" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R763" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="764">
-      <c r="A764" t="str">
-        <v>T260701-00004</v>
-      </c>
-      <c r="B764" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C764" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D764" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E764" t="str">
-        <v>2026-07-01 15:20</v>
-      </c>
-      <c r="F764">
-        <v>0</v>
-      </c>
-      <c r="G764" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H764" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I764" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J764" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K764">
-        <v>1</v>
-      </c>
-      <c r="L764" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M764" t="str">
-        <v>2026-07-01 14:53:20</v>
-      </c>
-      <c r="N764" s="1">
-        <v>440000</v>
-      </c>
-      <c r="O764" s="1">
-        <v>0</v>
-      </c>
-      <c r="P764" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q764" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R764" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" t="str">
-        <v>T260701-00003</v>
-      </c>
-      <c r="B765" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C765" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D765" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E765" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F765">
-        <v>0</v>
-      </c>
-      <c r="G765" t="str">
-        <v>하이얼(이천다코넷)</v>
-      </c>
-      <c r="H765" t="str">
-        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
-      </c>
-      <c r="I765" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J765" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K765">
-        <v>1</v>
-      </c>
-      <c r="L765" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M765" t="str">
-        <v>2026-07-01 10:15:38</v>
-      </c>
-      <c r="N765" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O765" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P765" t="str">
-        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
-      </c>
-      <c r="Q765" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R765" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" t="str">
-        <v>T260701-00002</v>
-      </c>
-      <c r="B766" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C766" t="str">
-        <v>청주ARC(디지탈태양)</v>
-      </c>
-      <c r="D766" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
-      </c>
-      <c r="E766" t="str">
-        <v>2026-07-01 08:30</v>
-      </c>
-      <c r="F766">
-        <v>0</v>
-      </c>
-      <c r="G766" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H766" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="I766" t="str">
-        <v>2026-07-01 10:30</v>
-      </c>
-      <c r="J766" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K766">
-        <v>1</v>
-      </c>
-      <c r="L766" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M766" t="str">
-        <v>2026-07-01 10:13:39</v>
-      </c>
-      <c r="N766" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O766" s="1">
-        <v>0</v>
-      </c>
-      <c r="P766" t="str">
-        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
-      </c>
-      <c r="Q766" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R766" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" t="str">
-        <v>T260701-00001</v>
-      </c>
-      <c r="B767" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C767" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D767" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E767" t="str">
-        <v>2026-07-01 09:00</v>
-      </c>
-      <c r="F767">
-        <v>0</v>
-      </c>
-      <c r="G767" t="str">
-        <v>현대클러스터 한강미사3차</v>
-      </c>
-      <c r="H767" t="str">
-        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
-      </c>
-      <c r="I767" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J767" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K767">
-        <v>1</v>
-      </c>
-      <c r="L767" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M767" t="str">
-        <v>2026-07-01 09:07:09</v>
-      </c>
-      <c r="N767" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O767" s="1">
-        <v>0</v>
-      </c>
-      <c r="P767" t="str">
-        <v>스마트윈드 출하</v>
-      </c>
-      <c r="Q767" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R767" t="str">
-        <v>스마트윈드</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R767"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R680"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R680"/>
+  <dimension ref="A1:R767"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38460,9 +38460,4881 @@
         <v>세상담기</v>
       </c>
     </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>T260703-00034</v>
+      </c>
+      <c r="B681" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C681" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D681" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E681" t="str">
+        <v>2026-07-03 19:01</v>
+      </c>
+      <c r="F681">
+        <v>0</v>
+      </c>
+      <c r="G681" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H681" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I681" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J681" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K681">
+        <v>1</v>
+      </c>
+      <c r="L681" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M681" t="str">
+        <v>2026-07-03 20:43:25</v>
+      </c>
+      <c r="N681" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O681" s="1">
+        <v>0</v>
+      </c>
+      <c r="P681" t="str">
+        <v/>
+      </c>
+      <c r="Q681" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R681" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>T260703-00033</v>
+      </c>
+      <c r="B682" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C682" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D682" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E682" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F682">
+        <v>1</v>
+      </c>
+      <c r="G682" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H682" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I682" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J682" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K682">
+        <v>1</v>
+      </c>
+      <c r="L682" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M682" t="str">
+        <v>2026-07-03 20:42:58</v>
+      </c>
+      <c r="N682" s="1">
+        <v>170000</v>
+      </c>
+      <c r="O682" s="1">
+        <v>0</v>
+      </c>
+      <c r="P682" t="str">
+        <v/>
+      </c>
+      <c r="Q682" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R682" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>T260703-00032</v>
+      </c>
+      <c r="B683" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C683" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D683" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E683" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F683">
+        <v>1</v>
+      </c>
+      <c r="G683" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H683" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I683" t="str">
+        <v>2026-07-04 08:00</v>
+      </c>
+      <c r="J683" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K683">
+        <v>1</v>
+      </c>
+      <c r="L683" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M683" t="str">
+        <v>2026-07-03 20:42:34</v>
+      </c>
+      <c r="N683" s="1">
+        <v>170000</v>
+      </c>
+      <c r="O683" s="1">
+        <v>0</v>
+      </c>
+      <c r="P683" t="str">
+        <v/>
+      </c>
+      <c r="Q683" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R683" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>T260703-00031</v>
+      </c>
+      <c r="B684" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C684" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D684" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E684" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F684">
+        <v>0</v>
+      </c>
+      <c r="G684" t="str">
+        <v>시흥ACP</v>
+      </c>
+      <c r="H684" t="str">
+        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
+      </c>
+      <c r="I684" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J684" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K684">
+        <v>1</v>
+      </c>
+      <c r="L684" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M684" t="str">
+        <v>2026-07-03 20:41:59</v>
+      </c>
+      <c r="N684" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O684" s="1">
+        <v>0</v>
+      </c>
+      <c r="P684" t="str">
+        <v/>
+      </c>
+      <c r="Q684" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R684" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>T260703-00030</v>
+      </c>
+      <c r="B685" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C685" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D685" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E685" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F685">
+        <v>3</v>
+      </c>
+      <c r="G685" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H685" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I685" t="str">
+        <v>2026-07-04 08:00</v>
+      </c>
+      <c r="J685" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K685">
+        <v>1</v>
+      </c>
+      <c r="L685" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M685" t="str">
+        <v>2026-07-03 20:41:34</v>
+      </c>
+      <c r="N685" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O685" s="1">
+        <v>0</v>
+      </c>
+      <c r="P685" t="str">
+        <v/>
+      </c>
+      <c r="Q685" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R685" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>T260703-00029</v>
+      </c>
+      <c r="B686" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C686" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D686" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E686" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F686">
+        <v>0</v>
+      </c>
+      <c r="G686" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H686" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I686" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J686" t="str">
+        <v>1톤 기타차량</v>
+      </c>
+      <c r="K686">
+        <v>1</v>
+      </c>
+      <c r="L686" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M686" t="str">
+        <v>2026-07-03 20:40:56</v>
+      </c>
+      <c r="N686" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O686" s="1">
+        <v>0</v>
+      </c>
+      <c r="P686" t="str">
+        <v/>
+      </c>
+      <c r="Q686" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R686" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>T260703-00028</v>
+      </c>
+      <c r="B687" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C687" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D687" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E687" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F687">
+        <v>0</v>
+      </c>
+      <c r="G687" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H687" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I687" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J687" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K687">
+        <v>1</v>
+      </c>
+      <c r="L687" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M687" t="str">
+        <v>2026-07-03 20:40:32</v>
+      </c>
+      <c r="N687" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O687" s="1">
+        <v>0</v>
+      </c>
+      <c r="P687" t="str">
+        <v/>
+      </c>
+      <c r="Q687" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R687" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>T260703-00027</v>
+      </c>
+      <c r="B688" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C688" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D688" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E688" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F688">
+        <v>3</v>
+      </c>
+      <c r="G688" t="str">
+        <v>인제ACP</v>
+      </c>
+      <c r="H688" t="str">
+        <v>강원특별자치도 속초시 만천6길 13 인제ACP</v>
+      </c>
+      <c r="I688" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J688" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K688">
+        <v>1</v>
+      </c>
+      <c r="L688" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M688" t="str">
+        <v>2026-07-03 20:40:07</v>
+      </c>
+      <c r="N688" s="1">
+        <v>390000</v>
+      </c>
+      <c r="O688" s="1">
+        <v>0</v>
+      </c>
+      <c r="P688" t="str">
+        <v/>
+      </c>
+      <c r="Q688" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R688" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>T260703-00026</v>
+      </c>
+      <c r="B689" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C689" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D689" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E689" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F689">
+        <v>0</v>
+      </c>
+      <c r="G689" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H689" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I689" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J689" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K689">
+        <v>1</v>
+      </c>
+      <c r="L689" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M689" t="str">
+        <v>2026-07-03 20:39:21</v>
+      </c>
+      <c r="N689" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O689" s="1">
+        <v>0</v>
+      </c>
+      <c r="P689" t="str">
+        <v/>
+      </c>
+      <c r="Q689" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R689" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>T260703-00025</v>
+      </c>
+      <c r="B690" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C690" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D690" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E690" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F690">
+        <v>1</v>
+      </c>
+      <c r="G690" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H690" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I690" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J690" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K690">
+        <v>1</v>
+      </c>
+      <c r="L690" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M690" t="str">
+        <v>2026-07-03 20:39:06</v>
+      </c>
+      <c r="N690" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O690" s="1">
+        <v>0</v>
+      </c>
+      <c r="P690" t="str">
+        <v/>
+      </c>
+      <c r="Q690" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R690" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>T260703-00024</v>
+      </c>
+      <c r="B691" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C691" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D691" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E691" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F691">
+        <v>1</v>
+      </c>
+      <c r="G691" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H691" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I691" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J691" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K691">
+        <v>1</v>
+      </c>
+      <c r="L691" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M691" t="str">
+        <v>2026-07-03 20:38:48</v>
+      </c>
+      <c r="N691" s="1">
+        <v>530000</v>
+      </c>
+      <c r="O691" s="1">
+        <v>0</v>
+      </c>
+      <c r="P691" t="str">
+        <v/>
+      </c>
+      <c r="Q691" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R691" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>T260703-00023</v>
+      </c>
+      <c r="B692" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C692" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D692" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E692" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F692">
+        <v>0</v>
+      </c>
+      <c r="G692" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H692" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I692" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J692" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K692">
+        <v>1</v>
+      </c>
+      <c r="L692" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M692" t="str">
+        <v>2026-07-03 20:38:28</v>
+      </c>
+      <c r="N692" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O692" s="1">
+        <v>0</v>
+      </c>
+      <c r="P692" t="str">
+        <v/>
+      </c>
+      <c r="Q692" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R692" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
+        <v>T260703-00022</v>
+      </c>
+      <c r="B693" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C693" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D693" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E693" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F693">
+        <v>0</v>
+      </c>
+      <c r="G693" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H693" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I693" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J693" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K693">
+        <v>1</v>
+      </c>
+      <c r="L693" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M693" t="str">
+        <v>2026-07-03 20:38:14</v>
+      </c>
+      <c r="N693" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O693" s="1">
+        <v>0</v>
+      </c>
+      <c r="P693" t="str">
+        <v/>
+      </c>
+      <c r="Q693" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R693" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>T260703-00021</v>
+      </c>
+      <c r="B694" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C694" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D694" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E694" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F694">
+        <v>1</v>
+      </c>
+      <c r="G694" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H694" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I694" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J694" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K694">
+        <v>1</v>
+      </c>
+      <c r="L694" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M694" t="str">
+        <v>2026-07-03 20:37:59</v>
+      </c>
+      <c r="N694" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O694" s="1">
+        <v>0</v>
+      </c>
+      <c r="P694" t="str">
+        <v/>
+      </c>
+      <c r="Q694" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R694" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>T260703-00020</v>
+      </c>
+      <c r="B695" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C695" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D695" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E695" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F695">
+        <v>0</v>
+      </c>
+      <c r="G695" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H695" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I695" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J695" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K695">
+        <v>1</v>
+      </c>
+      <c r="L695" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M695" t="str">
+        <v>2026-07-03 20:37:40</v>
+      </c>
+      <c r="N695" s="1">
+        <v>490000</v>
+      </c>
+      <c r="O695" s="1">
+        <v>0</v>
+      </c>
+      <c r="P695" t="str">
+        <v/>
+      </c>
+      <c r="Q695" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R695" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>T260703-00019</v>
+      </c>
+      <c r="B696" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C696" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D696" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E696" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F696">
+        <v>0</v>
+      </c>
+      <c r="G696" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H696" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I696" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J696" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K696">
+        <v>1</v>
+      </c>
+      <c r="L696" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M696" t="str">
+        <v>2026-07-03 20:37:26</v>
+      </c>
+      <c r="N696" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O696" s="1">
+        <v>0</v>
+      </c>
+      <c r="P696" t="str">
+        <v/>
+      </c>
+      <c r="Q696" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R696" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>T260703-00018</v>
+      </c>
+      <c r="B697" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C697" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D697" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E697" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F697">
+        <v>0</v>
+      </c>
+      <c r="G697" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H697" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I697" t="str">
+        <v>2026-07-03 20:00</v>
+      </c>
+      <c r="J697" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K697">
+        <v>1</v>
+      </c>
+      <c r="L697" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M697" t="str">
+        <v>2026-07-03 20:37:11</v>
+      </c>
+      <c r="N697" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O697" s="1">
+        <v>0</v>
+      </c>
+      <c r="P697" t="str">
+        <v/>
+      </c>
+      <c r="Q697" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R697" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>T260703-00017</v>
+      </c>
+      <c r="B698" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C698" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D698" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E698" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F698">
+        <v>0</v>
+      </c>
+      <c r="G698" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H698" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I698" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J698" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K698">
+        <v>1</v>
+      </c>
+      <c r="L698" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M698" t="str">
+        <v>2026-07-03 20:36:55</v>
+      </c>
+      <c r="N698" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O698" s="1">
+        <v>0</v>
+      </c>
+      <c r="P698" t="str">
+        <v/>
+      </c>
+      <c r="Q698" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R698" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>T260703-00016</v>
+      </c>
+      <c r="B699" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C699" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D699" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E699" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F699">
+        <v>0</v>
+      </c>
+      <c r="G699" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H699" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I699" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J699" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K699">
+        <v>1</v>
+      </c>
+      <c r="L699" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M699" t="str">
+        <v>2026-07-03 20:36:37</v>
+      </c>
+      <c r="N699" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O699" s="1">
+        <v>0</v>
+      </c>
+      <c r="P699" t="str">
+        <v/>
+      </c>
+      <c r="Q699" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R699" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
+        <v>T260703-00015</v>
+      </c>
+      <c r="B700" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C700" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D700" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E700" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F700">
+        <v>0</v>
+      </c>
+      <c r="G700" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H700" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I700" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J700" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K700">
+        <v>1</v>
+      </c>
+      <c r="L700" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M700" t="str">
+        <v>2026-07-03 20:36:15</v>
+      </c>
+      <c r="N700" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O700" s="1">
+        <v>0</v>
+      </c>
+      <c r="P700" t="str">
+        <v/>
+      </c>
+      <c r="Q700" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R700" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>T260703-00014</v>
+      </c>
+      <c r="B701" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C701" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D701" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E701" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F701">
+        <v>1</v>
+      </c>
+      <c r="G701" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H701" t="str">
+        <v>경산시 해오름길114-2 경산FDC</v>
+      </c>
+      <c r="I701" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J701" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K701">
+        <v>1</v>
+      </c>
+      <c r="L701" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M701" t="str">
+        <v>2026-07-03 20:35:55</v>
+      </c>
+      <c r="N701" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O701" s="1">
+        <v>0</v>
+      </c>
+      <c r="P701" t="str">
+        <v/>
+      </c>
+      <c r="Q701" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R701" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>T260703-00013</v>
+      </c>
+      <c r="B702" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C702" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D702" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E702" t="str">
+        <v>2026-07-03 17:30</v>
+      </c>
+      <c r="F702">
+        <v>0</v>
+      </c>
+      <c r="G702" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H702" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I702" t="str">
+        <v>2026-07-03 18:30</v>
+      </c>
+      <c r="J702" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K702">
+        <v>1</v>
+      </c>
+      <c r="L702" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M702" t="str">
+        <v>2026-07-03 20:31:55</v>
+      </c>
+      <c r="N702" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O702" s="1">
+        <v>0</v>
+      </c>
+      <c r="P702" t="str">
+        <v/>
+      </c>
+      <c r="Q702" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R702" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>T260703-00012</v>
+      </c>
+      <c r="B703" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C703" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="D703" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="E703" t="str">
+        <v>2026-07-03 08:30</v>
+      </c>
+      <c r="F703">
+        <v>0</v>
+      </c>
+      <c r="G703" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="H703" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="I703" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="J703" t="str">
+        <v>3.5톤 카고</v>
+      </c>
+      <c r="K703">
+        <v>1</v>
+      </c>
+      <c r="L703" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M703" t="str">
+        <v>2026-07-03 20:31:21</v>
+      </c>
+      <c r="N703" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O703" s="1">
+        <v>0</v>
+      </c>
+      <c r="P703" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="Q703" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R703" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>T260703-00011</v>
+      </c>
+      <c r="B704" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C704" t="str">
+        <v>샤오미</v>
+      </c>
+      <c r="D704" t="str">
+        <v>경기 이천시 대월면 부필리 309 샤오미</v>
+      </c>
+      <c r="E704" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="F704">
+        <v>0</v>
+      </c>
+      <c r="G704" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H704" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I704" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="J704" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K704">
+        <v>1</v>
+      </c>
+      <c r="L704" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M704" t="str">
+        <v>2026-07-03 20:30:39</v>
+      </c>
+      <c r="N704" s="1">
+        <v>80000</v>
+      </c>
+      <c r="O704" s="1">
+        <v>0</v>
+      </c>
+      <c r="P704" t="str">
+        <v>거래처비용청구(1대)</v>
+      </c>
+      <c r="Q704" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R704" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
+        <v>T260703-00010</v>
+      </c>
+      <c r="B705" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C705" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D705" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E705" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="F705">
+        <v>0</v>
+      </c>
+      <c r="G705" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H705" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I705" t="str">
+        <v>2026-07-03 15:30</v>
+      </c>
+      <c r="J705" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K705">
+        <v>1</v>
+      </c>
+      <c r="L705" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M705" t="str">
+        <v>2026-07-03 20:29:47</v>
+      </c>
+      <c r="N705" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O705" s="1">
+        <v>0</v>
+      </c>
+      <c r="P705" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q705" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R705" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
+        <v>T260703-00009</v>
+      </c>
+      <c r="B706" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C706" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D706" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E706" t="str">
+        <v>2026-07-03 10:00</v>
+      </c>
+      <c r="F706">
+        <v>0</v>
+      </c>
+      <c r="G706" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H706" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I706" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="J706" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K706">
+        <v>1</v>
+      </c>
+      <c r="L706" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M706" t="str">
+        <v>2026-07-03 20:29:05</v>
+      </c>
+      <c r="N706" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O706" s="1">
+        <v>0</v>
+      </c>
+      <c r="P706" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q706" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R706" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
+        <v>T260703-00008</v>
+      </c>
+      <c r="B707" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C707" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D707" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E707" t="str">
+        <v>2026-07-03 16:30</v>
+      </c>
+      <c r="F707">
+        <v>0</v>
+      </c>
+      <c r="G707" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H707" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I707" t="str">
+        <v>2026-07-03 18:00</v>
+      </c>
+      <c r="J707" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K707">
+        <v>1</v>
+      </c>
+      <c r="L707" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M707" t="str">
+        <v>2026-07-03 18:39:34</v>
+      </c>
+      <c r="N707" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O707" s="1">
+        <v>0</v>
+      </c>
+      <c r="P707" t="str">
+        <v>20260703/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q707" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R707" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="str">
+        <v>T260703-00007</v>
+      </c>
+      <c r="B708" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C708" t="str">
+        <v>청주ARC(공파렛트 이동)</v>
+      </c>
+      <c r="D708" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(공파렛트 이동)</v>
+      </c>
+      <c r="E708" t="str">
+        <v>2026-07-03 11:40</v>
+      </c>
+      <c r="F708">
+        <v>0</v>
+      </c>
+      <c r="G708" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H708" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="I708" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="J708" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K708">
+        <v>1</v>
+      </c>
+      <c r="L708" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M708" t="str">
+        <v>2026-07-03 11:28:01</v>
+      </c>
+      <c r="N708" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O708" s="1">
+        <v>0</v>
+      </c>
+      <c r="P708" t="str">
+        <v>20260703청주-&gt; 안성FC/공파렛트이동</v>
+      </c>
+      <c r="Q708" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R708" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="str">
+        <v>T260703-00006</v>
+      </c>
+      <c r="B709" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C709" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D709" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E709" t="str">
+        <v>2026-07-03 11:55</v>
+      </c>
+      <c r="F709">
+        <v>0</v>
+      </c>
+      <c r="G709" t="str">
+        <v>하이얼(서울 벌크 출하)</v>
+      </c>
+      <c r="H709" t="str">
+        <v>서울 강남구 선릉로92길 38 도파민</v>
+      </c>
+      <c r="I709" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="J709" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K709">
+        <v>1</v>
+      </c>
+      <c r="L709" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M709" t="str">
+        <v>2026-07-03 11:26:22</v>
+      </c>
+      <c r="N709" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O709" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P709" t="str">
+        <v>20260703/하이얼_서울_벌크_출하</v>
+      </c>
+      <c r="Q709" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R709" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="str">
+        <v>T260703-00005</v>
+      </c>
+      <c r="B710" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C710" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D710" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E710" t="str">
+        <v>2026-07-03 11:00</v>
+      </c>
+      <c r="F710">
+        <v>0</v>
+      </c>
+      <c r="G710" t="str">
+        <v>파주 하이마트 물류</v>
+      </c>
+      <c r="H710" t="str">
+        <v>경기 파주시 탄현면 월롱산로 296 파주 하이마트 물류</v>
+      </c>
+      <c r="I710" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J710" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K710">
+        <v>1</v>
+      </c>
+      <c r="L710" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M710" t="str">
+        <v>2026-07-03 11:22:28</v>
+      </c>
+      <c r="N710" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O710" s="1">
+        <v>0</v>
+      </c>
+      <c r="P710" t="str">
+        <v>일코전자 파주 하이마트 물류</v>
+      </c>
+      <c r="Q710" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R710" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="str">
+        <v>T260703-00004</v>
+      </c>
+      <c r="B711" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C711" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D711" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지  안성FC</v>
+      </c>
+      <c r="E711" t="str">
+        <v>2026-07-03 09:30</v>
+      </c>
+      <c r="F711">
+        <v>0</v>
+      </c>
+      <c r="G711" t="str">
+        <v>TCL다코넷</v>
+      </c>
+      <c r="H711" t="str">
+        <v>경기 평택시 포승읍 희곡리 847 평택 켄달스퀘어 3층, 다코넷 37번 도크</v>
+      </c>
+      <c r="I711" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="J711" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K711">
+        <v>1</v>
+      </c>
+      <c r="L711" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M711" t="str">
+        <v>2026-07-03 11:21:17</v>
+      </c>
+      <c r="N711" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O711" s="1">
+        <v>0</v>
+      </c>
+      <c r="P711" t="str">
+        <v>TCL 다코넷</v>
+      </c>
+      <c r="Q711" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R711" t="str">
+        <v>TCL</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="str">
+        <v>T260703-00003</v>
+      </c>
+      <c r="B712" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C712" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D712" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E712" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="F712">
+        <v>0</v>
+      </c>
+      <c r="G712" t="str">
+        <v>이천 하이마트 물류</v>
+      </c>
+      <c r="H712" t="str">
+        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 물류</v>
+      </c>
+      <c r="I712" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J712" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K712">
+        <v>1</v>
+      </c>
+      <c r="L712" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M712" t="str">
+        <v>2026-07-03 11:19:40</v>
+      </c>
+      <c r="N712" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O712" s="1">
+        <v>0</v>
+      </c>
+      <c r="P712" t="str">
+        <v>일코전자 이천 하이마트 물류</v>
+      </c>
+      <c r="Q712" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R712" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="str">
+        <v>T260703-00002</v>
+      </c>
+      <c r="B713" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C713" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D713" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E713" t="str">
+        <v>2026-07-03 10:00</v>
+      </c>
+      <c r="F713">
+        <v>0</v>
+      </c>
+      <c r="G713" t="str">
+        <v>화성 하이마트 물류</v>
+      </c>
+      <c r="H713" t="str">
+        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 물류</v>
+      </c>
+      <c r="I713" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J713" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K713">
+        <v>1</v>
+      </c>
+      <c r="L713" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M713" t="str">
+        <v>2026-07-03 11:18:03</v>
+      </c>
+      <c r="N713" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O713" s="1">
+        <v>0</v>
+      </c>
+      <c r="P713" t="str">
+        <v>일코전자 화성 하이마트 물류</v>
+      </c>
+      <c r="Q713" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R713" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="str">
+        <v>T260703-00001</v>
+      </c>
+      <c r="B714" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C714" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D714" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E714" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="F714">
+        <v>0</v>
+      </c>
+      <c r="G714" t="str">
+        <v>인천 하이마트 물류</v>
+      </c>
+      <c r="H714" t="str">
+        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
+      </c>
+      <c r="I714" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J714" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K714">
+        <v>1</v>
+      </c>
+      <c r="L714" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M714" t="str">
+        <v>2026-07-03 11:16:52</v>
+      </c>
+      <c r="N714" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O714" s="1">
+        <v>0</v>
+      </c>
+      <c r="P714" t="str">
+        <v>일코전자 인천 하이마트 물류</v>
+      </c>
+      <c r="Q714" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R714" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="str">
+        <v>T260702-00027</v>
+      </c>
+      <c r="B715" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C715" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D715" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E715" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F715">
+        <v>1</v>
+      </c>
+      <c r="G715" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H715" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I715" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J715" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K715">
+        <v>1</v>
+      </c>
+      <c r="L715" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M715" t="str">
+        <v>2026-07-02 20:54:21</v>
+      </c>
+      <c r="N715" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O715" s="1">
+        <v>0</v>
+      </c>
+      <c r="P715" t="str">
+        <v/>
+      </c>
+      <c r="Q715" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R715" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="str">
+        <v>T260702-00026</v>
+      </c>
+      <c r="B716" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C716" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D716" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E716" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F716">
+        <v>1</v>
+      </c>
+      <c r="G716" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H716" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I716" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J716" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K716">
+        <v>1</v>
+      </c>
+      <c r="L716" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M716" t="str">
+        <v>2026-07-02 20:53:56</v>
+      </c>
+      <c r="N716" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O716" s="1">
+        <v>0</v>
+      </c>
+      <c r="P716" t="str">
+        <v/>
+      </c>
+      <c r="Q716" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R716" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="str">
+        <v>T260702-00025</v>
+      </c>
+      <c r="B717" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C717" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D717" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E717" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F717">
+        <v>3</v>
+      </c>
+      <c r="G717" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H717" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I717" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J717" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K717">
+        <v>1</v>
+      </c>
+      <c r="L717" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M717" t="str">
+        <v>2026-07-02 20:53:28</v>
+      </c>
+      <c r="N717" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O717" s="1">
+        <v>0</v>
+      </c>
+      <c r="P717" t="str">
+        <v/>
+      </c>
+      <c r="Q717" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R717" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="str">
+        <v>T260702-00024</v>
+      </c>
+      <c r="B718" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C718" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D718" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E718" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F718">
+        <v>0</v>
+      </c>
+      <c r="G718" t="str">
+        <v>용인ACP</v>
+      </c>
+      <c r="H718" t="str">
+        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
+      </c>
+      <c r="I718" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J718" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K718">
+        <v>1</v>
+      </c>
+      <c r="L718" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M718" t="str">
+        <v>2026-07-02 20:52:18</v>
+      </c>
+      <c r="N718" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O718" s="1">
+        <v>0</v>
+      </c>
+      <c r="P718" t="str">
+        <v/>
+      </c>
+      <c r="Q718" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R718" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="str">
+        <v>T260702-00023</v>
+      </c>
+      <c r="B719" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C719" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D719" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E719" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F719">
+        <v>1</v>
+      </c>
+      <c r="G719" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H719" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I719" t="str">
+        <v>2026-07-03 07:00</v>
+      </c>
+      <c r="J719" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K719">
+        <v>1</v>
+      </c>
+      <c r="L719" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M719" t="str">
+        <v>2026-07-02 20:51:59</v>
+      </c>
+      <c r="N719" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O719" s="1">
+        <v>0</v>
+      </c>
+      <c r="P719" t="str">
+        <v/>
+      </c>
+      <c r="Q719" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R719" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="str">
+        <v>T260702-00022</v>
+      </c>
+      <c r="B720" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C720" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D720" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E720" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F720">
+        <v>0</v>
+      </c>
+      <c r="G720" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H720" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I720" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J720" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K720">
+        <v>1</v>
+      </c>
+      <c r="L720" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M720" t="str">
+        <v>2026-07-02 20:51:32</v>
+      </c>
+      <c r="N720" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O720" s="1">
+        <v>0</v>
+      </c>
+      <c r="P720" t="str">
+        <v/>
+      </c>
+      <c r="Q720" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R720" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="str">
+        <v>T260702-00021</v>
+      </c>
+      <c r="B721" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C721" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D721" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E721" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F721">
+        <v>1</v>
+      </c>
+      <c r="G721" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H721" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I721" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J721" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K721">
+        <v>1</v>
+      </c>
+      <c r="L721" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M721" t="str">
+        <v>2026-07-02 20:51:14</v>
+      </c>
+      <c r="N721" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O721" s="1">
+        <v>0</v>
+      </c>
+      <c r="P721" t="str">
+        <v/>
+      </c>
+      <c r="Q721" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R721" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="str">
+        <v>T260702-00020</v>
+      </c>
+      <c r="B722" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C722" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D722" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E722" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F722">
+        <v>0</v>
+      </c>
+      <c r="G722" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H722" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I722" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J722" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K722">
+        <v>1</v>
+      </c>
+      <c r="L722" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M722" t="str">
+        <v>2026-07-02 20:50:54</v>
+      </c>
+      <c r="N722" s="1">
+        <v>280000</v>
+      </c>
+      <c r="O722" s="1">
+        <v>0</v>
+      </c>
+      <c r="P722" t="str">
+        <v/>
+      </c>
+      <c r="Q722" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R722" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="str">
+        <v>T260702-00019</v>
+      </c>
+      <c r="B723" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C723" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D723" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E723" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F723">
+        <v>0</v>
+      </c>
+      <c r="G723" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H723" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I723" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J723" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K723">
+        <v>1</v>
+      </c>
+      <c r="L723" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M723" t="str">
+        <v>2026-07-02 20:50:36</v>
+      </c>
+      <c r="N723" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O723" s="1">
+        <v>0</v>
+      </c>
+      <c r="P723" t="str">
+        <v/>
+      </c>
+      <c r="Q723" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R723" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="str">
+        <v>T260702-00018</v>
+      </c>
+      <c r="B724" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C724" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D724" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E724" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F724">
+        <v>1</v>
+      </c>
+      <c r="G724" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H724" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I724" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J724" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K724">
+        <v>1</v>
+      </c>
+      <c r="L724" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M724" t="str">
+        <v>2026-07-02 20:50:19</v>
+      </c>
+      <c r="N724" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O724" s="1">
+        <v>0</v>
+      </c>
+      <c r="P724" t="str">
+        <v/>
+      </c>
+      <c r="Q724" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R724" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="str">
+        <v>T260702-00017</v>
+      </c>
+      <c r="B725" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C725" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D725" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E725" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F725">
+        <v>1</v>
+      </c>
+      <c r="G725" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H725" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I725" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J725" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K725">
+        <v>1</v>
+      </c>
+      <c r="L725" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M725" t="str">
+        <v>2026-07-02 20:49:56</v>
+      </c>
+      <c r="N725" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O725" s="1">
+        <v>0</v>
+      </c>
+      <c r="P725" t="str">
+        <v/>
+      </c>
+      <c r="Q725" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R725" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="str">
+        <v>T260702-00016</v>
+      </c>
+      <c r="B726" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C726" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D726" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E726" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F726">
+        <v>0</v>
+      </c>
+      <c r="G726" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H726" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I726" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J726" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K726">
+        <v>1</v>
+      </c>
+      <c r="L726" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M726" t="str">
+        <v>2026-07-02 20:49:25</v>
+      </c>
+      <c r="N726" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O726" s="1">
+        <v>0</v>
+      </c>
+      <c r="P726" t="str">
+        <v/>
+      </c>
+      <c r="Q726" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R726" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="str">
+        <v>T260702-00015</v>
+      </c>
+      <c r="B727" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C727" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D727" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E727" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F727">
+        <v>1</v>
+      </c>
+      <c r="G727" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H727" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I727" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J727" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K727">
+        <v>1</v>
+      </c>
+      <c r="L727" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M727" t="str">
+        <v>2026-07-02 20:48:50</v>
+      </c>
+      <c r="N727" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O727" s="1">
+        <v>0</v>
+      </c>
+      <c r="P727" t="str">
+        <v/>
+      </c>
+      <c r="Q727" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R727" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="str">
+        <v>T260702-00014</v>
+      </c>
+      <c r="B728" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C728" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D728" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E728" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F728">
+        <v>0</v>
+      </c>
+      <c r="G728" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H728" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I728" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J728" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K728">
+        <v>1</v>
+      </c>
+      <c r="L728" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M728" t="str">
+        <v>2026-07-02 20:48:25</v>
+      </c>
+      <c r="N728" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O728" s="1">
+        <v>0</v>
+      </c>
+      <c r="P728" t="str">
+        <v/>
+      </c>
+      <c r="Q728" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R728" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="str">
+        <v>T260702-00013</v>
+      </c>
+      <c r="B729" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C729" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D729" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E729" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F729">
+        <v>0</v>
+      </c>
+      <c r="G729" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H729" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I729" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J729" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K729">
+        <v>1</v>
+      </c>
+      <c r="L729" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M729" t="str">
+        <v>2026-07-02 20:48:09</v>
+      </c>
+      <c r="N729" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O729" s="1">
+        <v>0</v>
+      </c>
+      <c r="P729" t="str">
+        <v/>
+      </c>
+      <c r="Q729" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R729" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="str">
+        <v>T260702-00012</v>
+      </c>
+      <c r="B730" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C730" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D730" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E730" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F730">
+        <v>2</v>
+      </c>
+      <c r="G730" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H730" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I730" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J730" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K730">
+        <v>1</v>
+      </c>
+      <c r="L730" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M730" t="str">
+        <v>2026-07-02 20:47:49</v>
+      </c>
+      <c r="N730" s="1">
+        <v>680000</v>
+      </c>
+      <c r="O730" s="1">
+        <v>0</v>
+      </c>
+      <c r="P730" t="str">
+        <v/>
+      </c>
+      <c r="Q730" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R730" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="str">
+        <v>T260702-00011</v>
+      </c>
+      <c r="B731" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C731" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D731" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E731" t="str">
+        <v>2026-07-02 17:50</v>
+      </c>
+      <c r="F731">
+        <v>0</v>
+      </c>
+      <c r="G731" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H731" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I731" t="str">
+        <v>2026-07-02 18:50</v>
+      </c>
+      <c r="J731" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K731">
+        <v>1</v>
+      </c>
+      <c r="L731" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M731" t="str">
+        <v>2026-07-02 20:44:59</v>
+      </c>
+      <c r="N731" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O731" s="1">
+        <v>0</v>
+      </c>
+      <c r="P731" t="str">
+        <v/>
+      </c>
+      <c r="Q731" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R731" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="str">
+        <v>T260702-00010</v>
+      </c>
+      <c r="B732" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C732" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D732" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E732" t="str">
+        <v>2026-07-02 13:30</v>
+      </c>
+      <c r="F732">
+        <v>0</v>
+      </c>
+      <c r="G732" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H732" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I732" t="str">
+        <v>2026-07-02 15:40</v>
+      </c>
+      <c r="J732" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K732">
+        <v>1</v>
+      </c>
+      <c r="L732" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M732" t="str">
+        <v>2026-07-02 20:44:26</v>
+      </c>
+      <c r="N732" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O732" s="1">
+        <v>0</v>
+      </c>
+      <c r="P732" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q732" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R732" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="str">
+        <v>T260702-00009</v>
+      </c>
+      <c r="B733" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C733" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D733" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E733" t="str">
+        <v>2026-07-02 10:00</v>
+      </c>
+      <c r="F733">
+        <v>0</v>
+      </c>
+      <c r="G733" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H733" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I733" t="str">
+        <v>2026-07-02 13:40</v>
+      </c>
+      <c r="J733" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K733">
+        <v>1</v>
+      </c>
+      <c r="L733" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M733" t="str">
+        <v>2026-07-02 20:43:37</v>
+      </c>
+      <c r="N733" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O733" s="1">
+        <v>0</v>
+      </c>
+      <c r="P733" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q733" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R733" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="str">
+        <v>T260702-00008</v>
+      </c>
+      <c r="B734" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C734" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D734" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E734" t="str">
+        <v>2026-07-02 17:00</v>
+      </c>
+      <c r="F734">
+        <v>0</v>
+      </c>
+      <c r="G734" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="H734" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="I734" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J734" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K734">
+        <v>1</v>
+      </c>
+      <c r="L734" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M734" t="str">
+        <v>2026-07-02 16:38:23</v>
+      </c>
+      <c r="N734" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O734" s="1">
+        <v>0</v>
+      </c>
+      <c r="P734" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="Q734" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R734" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="str">
+        <v>T260702-00007</v>
+      </c>
+      <c r="B735" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C735" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D735" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E735" t="str">
+        <v>2026-07-02 16:30</v>
+      </c>
+      <c r="F735">
+        <v>0</v>
+      </c>
+      <c r="G735" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H735" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I735" t="str">
+        <v>2026-07-02 18:00</v>
+      </c>
+      <c r="J735" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K735">
+        <v>1</v>
+      </c>
+      <c r="L735" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M735" t="str">
+        <v>2026-07-02 16:34:35</v>
+      </c>
+      <c r="N735" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O735" s="1">
+        <v>0</v>
+      </c>
+      <c r="P735" t="str">
+        <v>20260702/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q735" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R735" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="str">
+        <v>T260702-00006</v>
+      </c>
+      <c r="B736" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C736" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D736" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E736" t="str">
+        <v>2026-07-02 16:00</v>
+      </c>
+      <c r="F736">
+        <v>0</v>
+      </c>
+      <c r="G736" t="str">
+        <v>광주 하이마트 물류</v>
+      </c>
+      <c r="H736" t="str">
+        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
+      </c>
+      <c r="I736" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J736" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K736">
+        <v>1</v>
+      </c>
+      <c r="L736" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M736" t="str">
+        <v>2026-07-02 15:30:55</v>
+      </c>
+      <c r="N736" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O736" s="1">
+        <v>0</v>
+      </c>
+      <c r="P736" t="str">
+        <v>일코 광주 하이마트 물류</v>
+      </c>
+      <c r="Q736" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R736" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="str">
+        <v>T260702-00005</v>
+      </c>
+      <c r="B737" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C737" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D737" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E737" t="str">
+        <v>2026-07-02 14:30</v>
+      </c>
+      <c r="F737">
+        <v>0</v>
+      </c>
+      <c r="G737" t="str">
+        <v>마산 하이마트 물류</v>
+      </c>
+      <c r="H737" t="str">
+        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
+      </c>
+      <c r="I737" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J737" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K737">
+        <v>1</v>
+      </c>
+      <c r="L737" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M737" t="str">
+        <v>2026-07-02 13:44:41</v>
+      </c>
+      <c r="N737" s="1">
+        <v>380000</v>
+      </c>
+      <c r="O737" s="1">
+        <v>0</v>
+      </c>
+      <c r="P737" t="str">
+        <v>일코 마산 하이마트 물류</v>
+      </c>
+      <c r="Q737" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R737" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="str">
+        <v>T260702-00004</v>
+      </c>
+      <c r="B738" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C738" t="str">
+        <v>강릉 하이마트 물류</v>
+      </c>
+      <c r="D738" t="str">
+        <v>강원특별자치도 강릉시 연곡면 동해대로 4100-36 강릉 하이마트 물류</v>
+      </c>
+      <c r="E738" t="str">
+        <v>2026-07-02 13:30</v>
+      </c>
+      <c r="F738">
+        <v>0</v>
+      </c>
+      <c r="G738" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H738" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I738" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J738" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K738">
+        <v>1</v>
+      </c>
+      <c r="L738" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M738" t="str">
+        <v>2026-07-02 12:00:10</v>
+      </c>
+      <c r="N738" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O738" s="1">
+        <v>0</v>
+      </c>
+      <c r="P738" t="str">
+        <v>일코전자 강릉 하이마트 물류</v>
+      </c>
+      <c r="Q738" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R738" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="str">
+        <v>T260702-00003</v>
+      </c>
+      <c r="B739" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C739" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D739" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E739" t="str">
+        <v>2026-07-02 14:30</v>
+      </c>
+      <c r="F739">
+        <v>0</v>
+      </c>
+      <c r="G739" t="str">
+        <v>대구 하이마트 물류</v>
+      </c>
+      <c r="H739" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="I739" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J739" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K739">
+        <v>1</v>
+      </c>
+      <c r="L739" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M739" t="str">
+        <v>2026-07-02 11:59:32</v>
+      </c>
+      <c r="N739" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O739" s="1">
+        <v>0</v>
+      </c>
+      <c r="P739" t="str">
+        <v>일코전자 대구 하이마트 물류</v>
+      </c>
+      <c r="Q739" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R739" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="str">
+        <v>T260702-00002</v>
+      </c>
+      <c r="B740" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C740" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D740" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E740" t="str">
+        <v>2026-07-02 09:30</v>
+      </c>
+      <c r="F740">
+        <v>1</v>
+      </c>
+      <c r="G740" t="str">
+        <v>하이얼(대구2착)</v>
+      </c>
+      <c r="H740" t="str">
+        <v>대구 남구 양지로 25 대명자이 아파트</v>
+      </c>
+      <c r="I740" t="str">
+        <v>2026-07-02 15:00</v>
+      </c>
+      <c r="J740" t="str">
+        <v>1.5톤 윙바디</v>
+      </c>
+      <c r="K740">
+        <v>1</v>
+      </c>
+      <c r="L740" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M740" t="str">
+        <v>2026-07-02 09:20:07</v>
+      </c>
+      <c r="N740" s="1">
+        <v>220000</v>
+      </c>
+      <c r="O740" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P740" t="str">
+        <v>20260702/하이얼_대구 착지 2곳_벌크_출하</v>
+      </c>
+      <c r="Q740" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R740" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="str">
+        <v>T260702-00001</v>
+      </c>
+      <c r="B741" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C741" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D741" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E741" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="F741">
+        <v>0</v>
+      </c>
+      <c r="G741" t="str">
+        <v>로지스밸리인천포트(Logisvalley)</v>
+      </c>
+      <c r="H741" t="str">
+        <v>인천 연수구 인천타워대로599번길 60 로지스밸리인천포트(Logisvalley) 1층 13번(HTC)</v>
+      </c>
+      <c r="I741" t="str">
+        <v>2026-07-02 11:00</v>
+      </c>
+      <c r="J741" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K741">
+        <v>1</v>
+      </c>
+      <c r="L741" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M741" t="str">
+        <v>2026-07-02 09:17:29</v>
+      </c>
+      <c r="N741" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O741" s="1">
+        <v>0</v>
+      </c>
+      <c r="P741" t="str">
+        <v>패스트레인 출하</v>
+      </c>
+      <c r="Q741" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R741" t="str">
+        <v>패스트레인코리아</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="str">
+        <v>T260701-00026</v>
+      </c>
+      <c r="B742" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C742" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D742" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E742" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F742">
+        <v>1</v>
+      </c>
+      <c r="G742" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H742" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I742" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J742" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K742">
+        <v>1</v>
+      </c>
+      <c r="L742" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M742" t="str">
+        <v>2026-07-01 19:47:13</v>
+      </c>
+      <c r="N742" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O742" s="1">
+        <v>0</v>
+      </c>
+      <c r="P742" t="str">
+        <v/>
+      </c>
+      <c r="Q742" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R742" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="str">
+        <v>T260701-00025</v>
+      </c>
+      <c r="B743" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C743" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D743" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E743" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F743">
+        <v>2</v>
+      </c>
+      <c r="G743" t="str">
+        <v>원주ACP</v>
+      </c>
+      <c r="H743" t="str">
+        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
+      </c>
+      <c r="I743" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J743" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K743">
+        <v>1</v>
+      </c>
+      <c r="L743" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M743" t="str">
+        <v>2026-07-01 19:46:48</v>
+      </c>
+      <c r="N743" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O743" s="1">
+        <v>0</v>
+      </c>
+      <c r="P743" t="str">
+        <v/>
+      </c>
+      <c r="Q743" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R743" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="str">
+        <v>T260701-00024</v>
+      </c>
+      <c r="B744" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C744" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D744" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E744" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F744">
+        <v>1</v>
+      </c>
+      <c r="G744" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H744" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I744" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J744" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K744">
+        <v>1</v>
+      </c>
+      <c r="L744" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M744" t="str">
+        <v>2026-07-01 19:46:12</v>
+      </c>
+      <c r="N744" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O744" s="1">
+        <v>0</v>
+      </c>
+      <c r="P744" t="str">
+        <v/>
+      </c>
+      <c r="Q744" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R744" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="str">
+        <v>T260701-00023</v>
+      </c>
+      <c r="B745" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C745" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D745" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E745" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F745">
+        <v>3</v>
+      </c>
+      <c r="G745" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H745" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I745" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J745" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K745">
+        <v>1</v>
+      </c>
+      <c r="L745" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M745" t="str">
+        <v>2026-07-01 19:45:40</v>
+      </c>
+      <c r="N745" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O745" s="1">
+        <v>0</v>
+      </c>
+      <c r="P745" t="str">
+        <v/>
+      </c>
+      <c r="Q745" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R745" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="str">
+        <v>T260701-00022</v>
+      </c>
+      <c r="B746" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C746" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D746" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E746" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F746">
+        <v>0</v>
+      </c>
+      <c r="G746" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H746" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I746" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J746" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K746">
+        <v>1</v>
+      </c>
+      <c r="L746" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M746" t="str">
+        <v>2026-07-01 19:44:56</v>
+      </c>
+      <c r="N746" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O746" s="1">
+        <v>0</v>
+      </c>
+      <c r="P746" t="str">
+        <v/>
+      </c>
+      <c r="Q746" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R746" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="str">
+        <v>T260701-00021</v>
+      </c>
+      <c r="B747" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C747" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D747" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E747" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F747">
+        <v>1</v>
+      </c>
+      <c r="G747" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H747" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I747" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J747" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K747">
+        <v>1</v>
+      </c>
+      <c r="L747" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M747" t="str">
+        <v>2026-07-01 19:44:37</v>
+      </c>
+      <c r="N747" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O747" s="1">
+        <v>0</v>
+      </c>
+      <c r="P747" t="str">
+        <v/>
+      </c>
+      <c r="Q747" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R747" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="str">
+        <v>T260701-00020</v>
+      </c>
+      <c r="B748" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C748" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D748" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E748" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F748">
+        <v>2</v>
+      </c>
+      <c r="G748" t="str">
+        <v>속초ACP</v>
+      </c>
+      <c r="H748" t="str">
+        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
+      </c>
+      <c r="I748" t="str">
+        <v>2026-07-02 06:00</v>
+      </c>
+      <c r="J748" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K748">
+        <v>1</v>
+      </c>
+      <c r="L748" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M748" t="str">
+        <v>2026-07-01 19:44:05</v>
+      </c>
+      <c r="N748" s="1">
+        <v>320000</v>
+      </c>
+      <c r="O748" s="1">
+        <v>0</v>
+      </c>
+      <c r="P748" t="str">
+        <v/>
+      </c>
+      <c r="Q748" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R748" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="str">
+        <v>T260701-00019</v>
+      </c>
+      <c r="B749" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C749" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D749" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E749" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F749">
+        <v>0</v>
+      </c>
+      <c r="G749" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H749" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I749" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J749" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K749">
+        <v>1</v>
+      </c>
+      <c r="L749" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M749" t="str">
+        <v>2026-07-01 19:43:22</v>
+      </c>
+      <c r="N749" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O749" s="1">
+        <v>0</v>
+      </c>
+      <c r="P749" t="str">
+        <v/>
+      </c>
+      <c r="Q749" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R749" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="str">
+        <v>T260701-00018</v>
+      </c>
+      <c r="B750" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C750" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D750" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E750" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F750">
+        <v>1</v>
+      </c>
+      <c r="G750" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H750" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I750" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J750" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K750">
+        <v>1</v>
+      </c>
+      <c r="L750" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M750" t="str">
+        <v>2026-07-01 19:43:03</v>
+      </c>
+      <c r="N750" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O750" s="1">
+        <v>0</v>
+      </c>
+      <c r="P750" t="str">
+        <v/>
+      </c>
+      <c r="Q750" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R750" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="str">
+        <v>T260701-00017</v>
+      </c>
+      <c r="B751" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C751" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D751" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E751" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F751">
+        <v>0</v>
+      </c>
+      <c r="G751" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H751" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I751" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J751" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K751">
+        <v>1</v>
+      </c>
+      <c r="L751" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M751" t="str">
+        <v>2026-07-01 19:42:39</v>
+      </c>
+      <c r="N751" s="1">
+        <v>310000</v>
+      </c>
+      <c r="O751" s="1">
+        <v>0</v>
+      </c>
+      <c r="P751" t="str">
+        <v/>
+      </c>
+      <c r="Q751" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R751" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="str">
+        <v>T260701-00016</v>
+      </c>
+      <c r="B752" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C752" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D752" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E752" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F752">
+        <v>0</v>
+      </c>
+      <c r="G752" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H752" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I752" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J752" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K752">
+        <v>1</v>
+      </c>
+      <c r="L752" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M752" t="str">
+        <v>2026-07-01 19:42:17</v>
+      </c>
+      <c r="N752" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O752" s="1">
+        <v>0</v>
+      </c>
+      <c r="P752" t="str">
+        <v/>
+      </c>
+      <c r="Q752" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R752" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="str">
+        <v>T260701-00015</v>
+      </c>
+      <c r="B753" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C753" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D753" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E753" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F753">
+        <v>1</v>
+      </c>
+      <c r="G753" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H753" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I753" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J753" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K753">
+        <v>1</v>
+      </c>
+      <c r="L753" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M753" t="str">
+        <v>2026-07-01 19:42:02</v>
+      </c>
+      <c r="N753" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O753" s="1">
+        <v>0</v>
+      </c>
+      <c r="P753" t="str">
+        <v/>
+      </c>
+      <c r="Q753" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R753" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="str">
+        <v>T260701-00014</v>
+      </c>
+      <c r="B754" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C754" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D754" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E754" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F754">
+        <v>1</v>
+      </c>
+      <c r="G754" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H754" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I754" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J754" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K754">
+        <v>1</v>
+      </c>
+      <c r="L754" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M754" t="str">
+        <v>2026-07-01 19:41:41</v>
+      </c>
+      <c r="N754" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O754" s="1">
+        <v>0</v>
+      </c>
+      <c r="P754" t="str">
+        <v/>
+      </c>
+      <c r="Q754" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R754" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="str">
+        <v>T260701-00013</v>
+      </c>
+      <c r="B755" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C755" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D755" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E755" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F755">
+        <v>1</v>
+      </c>
+      <c r="G755" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H755" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I755" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J755" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K755">
+        <v>1</v>
+      </c>
+      <c r="L755" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M755" t="str">
+        <v>2026-07-01 19:41:08</v>
+      </c>
+      <c r="N755" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O755" s="1">
+        <v>0</v>
+      </c>
+      <c r="P755" t="str">
+        <v/>
+      </c>
+      <c r="Q755" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R755" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="str">
+        <v>T260701-00012</v>
+      </c>
+      <c r="B756" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C756" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D756" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E756" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F756">
+        <v>1</v>
+      </c>
+      <c r="G756" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H756" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I756" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J756" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K756">
+        <v>1</v>
+      </c>
+      <c r="L756" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M756" t="str">
+        <v>2026-07-01 19:40:45</v>
+      </c>
+      <c r="N756" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O756" s="1">
+        <v>0</v>
+      </c>
+      <c r="P756" t="str">
+        <v/>
+      </c>
+      <c r="Q756" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R756" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="str">
+        <v>T260701-00011</v>
+      </c>
+      <c r="B757" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C757" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D757" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E757" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F757">
+        <v>0</v>
+      </c>
+      <c r="G757" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H757" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I757" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J757" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K757">
+        <v>1</v>
+      </c>
+      <c r="L757" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M757" t="str">
+        <v>2026-07-01 19:40:21</v>
+      </c>
+      <c r="N757" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O757" s="1">
+        <v>0</v>
+      </c>
+      <c r="P757" t="str">
+        <v/>
+      </c>
+      <c r="Q757" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R757" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="str">
+        <v>T260701-00010</v>
+      </c>
+      <c r="B758" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C758" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D758" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E758" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F758">
+        <v>1</v>
+      </c>
+      <c r="G758" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H758" t="str">
+        <v>경산시 해오름길114-2 경산FDC</v>
+      </c>
+      <c r="I758" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J758" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K758">
+        <v>1</v>
+      </c>
+      <c r="L758" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M758" t="str">
+        <v>2026-07-01 19:40:04</v>
+      </c>
+      <c r="N758" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O758" s="1">
+        <v>0</v>
+      </c>
+      <c r="P758" t="str">
+        <v/>
+      </c>
+      <c r="Q758" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R758" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="str">
+        <v>T260701-00009</v>
+      </c>
+      <c r="B759" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C759" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D759" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E759" t="str">
+        <v>2026-07-01 17:30</v>
+      </c>
+      <c r="F759">
+        <v>0</v>
+      </c>
+      <c r="G759" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H759" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I759" t="str">
+        <v>2026-07-01 18:30</v>
+      </c>
+      <c r="J759" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K759">
+        <v>1</v>
+      </c>
+      <c r="L759" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M759" t="str">
+        <v>2026-07-01 19:31:35</v>
+      </c>
+      <c r="N759" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O759" s="1">
+        <v>0</v>
+      </c>
+      <c r="P759" t="str">
+        <v/>
+      </c>
+      <c r="Q759" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R759" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="str">
+        <v>T260701-00008</v>
+      </c>
+      <c r="B760" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C760" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D760" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E760" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="F760">
+        <v>0</v>
+      </c>
+      <c r="G760" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H760" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I760" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="J760" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K760">
+        <v>1</v>
+      </c>
+      <c r="L760" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M760" t="str">
+        <v>2026-07-01 19:31:02</v>
+      </c>
+      <c r="N760" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O760" s="1">
+        <v>0</v>
+      </c>
+      <c r="P760" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q760" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R760" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="str">
+        <v>T260701-00007</v>
+      </c>
+      <c r="B761" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C761" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D761" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E761" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F761">
+        <v>0</v>
+      </c>
+      <c r="G761" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H761" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I761" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="J761" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K761">
+        <v>1</v>
+      </c>
+      <c r="L761" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M761" t="str">
+        <v>2026-07-01 19:29:27</v>
+      </c>
+      <c r="N761" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O761" s="1">
+        <v>0</v>
+      </c>
+      <c r="P761" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q761" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R761" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="str">
+        <v>T260701-00006</v>
+      </c>
+      <c r="B762" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C762" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D762" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E762" t="str">
+        <v>2026-07-01 16:30</v>
+      </c>
+      <c r="F762">
+        <v>0</v>
+      </c>
+      <c r="G762" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H762" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I762" t="str">
+        <v>2026-07-01 18:00</v>
+      </c>
+      <c r="J762" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K762">
+        <v>1</v>
+      </c>
+      <c r="L762" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M762" t="str">
+        <v>2026-07-01 16:09:24</v>
+      </c>
+      <c r="N762" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O762" s="1">
+        <v>0</v>
+      </c>
+      <c r="P762" t="str">
+        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q762" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R762" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="str">
+        <v>T260701-00005</v>
+      </c>
+      <c r="B763" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C763" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D763" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E763" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="F763">
+        <v>0</v>
+      </c>
+      <c r="G763" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H763" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I763" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J763" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K763">
+        <v>1</v>
+      </c>
+      <c r="L763" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M763" t="str">
+        <v>2026-07-01 14:58:37</v>
+      </c>
+      <c r="N763" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O763" s="1">
+        <v>0</v>
+      </c>
+      <c r="P763" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q763" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R763" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="str">
+        <v>T260701-00004</v>
+      </c>
+      <c r="B764" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C764" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D764" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E764" t="str">
+        <v>2026-07-01 15:20</v>
+      </c>
+      <c r="F764">
+        <v>0</v>
+      </c>
+      <c r="G764" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H764" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I764" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J764" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K764">
+        <v>1</v>
+      </c>
+      <c r="L764" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M764" t="str">
+        <v>2026-07-01 14:53:20</v>
+      </c>
+      <c r="N764" s="1">
+        <v>440000</v>
+      </c>
+      <c r="O764" s="1">
+        <v>0</v>
+      </c>
+      <c r="P764" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q764" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R764" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="str">
+        <v>T260701-00003</v>
+      </c>
+      <c r="B765" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C765" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D765" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E765" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F765">
+        <v>0</v>
+      </c>
+      <c r="G765" t="str">
+        <v>하이얼(이천다코넷)</v>
+      </c>
+      <c r="H765" t="str">
+        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
+      </c>
+      <c r="I765" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J765" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K765">
+        <v>1</v>
+      </c>
+      <c r="L765" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M765" t="str">
+        <v>2026-07-01 10:15:38</v>
+      </c>
+      <c r="N765" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O765" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P765" t="str">
+        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
+      </c>
+      <c r="Q765" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R765" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="str">
+        <v>T260701-00002</v>
+      </c>
+      <c r="B766" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C766" t="str">
+        <v>청주ARC(디지탈태양)</v>
+      </c>
+      <c r="D766" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
+      </c>
+      <c r="E766" t="str">
+        <v>2026-07-01 08:30</v>
+      </c>
+      <c r="F766">
+        <v>0</v>
+      </c>
+      <c r="G766" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H766" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="I766" t="str">
+        <v>2026-07-01 10:30</v>
+      </c>
+      <c r="J766" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K766">
+        <v>1</v>
+      </c>
+      <c r="L766" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M766" t="str">
+        <v>2026-07-01 10:13:39</v>
+      </c>
+      <c r="N766" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O766" s="1">
+        <v>0</v>
+      </c>
+      <c r="P766" t="str">
+        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
+      </c>
+      <c r="Q766" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R766" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="str">
+        <v>T260701-00001</v>
+      </c>
+      <c r="B767" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C767" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D767" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E767" t="str">
+        <v>2026-07-01 09:00</v>
+      </c>
+      <c r="F767">
+        <v>0</v>
+      </c>
+      <c r="G767" t="str">
+        <v>현대클러스터 한강미사3차</v>
+      </c>
+      <c r="H767" t="str">
+        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
+      </c>
+      <c r="I767" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J767" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K767">
+        <v>1</v>
+      </c>
+      <c r="L767" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M767" t="str">
+        <v>2026-07-01 09:07:09</v>
+      </c>
+      <c r="N767" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O767" s="1">
+        <v>0</v>
+      </c>
+      <c r="P767" t="str">
+        <v>스마트윈드 출하</v>
+      </c>
+      <c r="Q767" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R767" t="str">
+        <v>스마트윈드</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R680"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R767"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R813"/>
+  <dimension ref="A1:R726"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -41036,4881 +41036,9 @@
         <v>세상담기</v>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" t="str">
-        <v>T260703-00034</v>
-      </c>
-      <c r="B727" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C727" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D727" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E727" t="str">
-        <v>2026-07-03 19:01</v>
-      </c>
-      <c r="F727">
-        <v>0</v>
-      </c>
-      <c r="G727" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H727" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I727" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J727" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K727">
-        <v>1</v>
-      </c>
-      <c r="L727" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M727" t="str">
-        <v>2026-07-03 20:43:25</v>
-      </c>
-      <c r="N727" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O727" s="1">
-        <v>0</v>
-      </c>
-      <c r="P727" t="str">
-        <v/>
-      </c>
-      <c r="Q727" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R727" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="str">
-        <v>T260703-00033</v>
-      </c>
-      <c r="B728" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C728" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D728" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E728" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F728">
-        <v>1</v>
-      </c>
-      <c r="G728" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H728" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I728" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J728" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K728">
-        <v>1</v>
-      </c>
-      <c r="L728" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M728" t="str">
-        <v>2026-07-03 20:42:58</v>
-      </c>
-      <c r="N728" s="1">
-        <v>170000</v>
-      </c>
-      <c r="O728" s="1">
-        <v>0</v>
-      </c>
-      <c r="P728" t="str">
-        <v/>
-      </c>
-      <c r="Q728" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R728" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="str">
-        <v>T260703-00032</v>
-      </c>
-      <c r="B729" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C729" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D729" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E729" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F729">
-        <v>1</v>
-      </c>
-      <c r="G729" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H729" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I729" t="str">
-        <v>2026-07-04 08:00</v>
-      </c>
-      <c r="J729" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K729">
-        <v>1</v>
-      </c>
-      <c r="L729" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M729" t="str">
-        <v>2026-07-03 20:42:34</v>
-      </c>
-      <c r="N729" s="1">
-        <v>170000</v>
-      </c>
-      <c r="O729" s="1">
-        <v>0</v>
-      </c>
-      <c r="P729" t="str">
-        <v/>
-      </c>
-      <c r="Q729" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R729" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="str">
-        <v>T260703-00031</v>
-      </c>
-      <c r="B730" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C730" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D730" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E730" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F730">
-        <v>0</v>
-      </c>
-      <c r="G730" t="str">
-        <v>시흥ACP</v>
-      </c>
-      <c r="H730" t="str">
-        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
-      </c>
-      <c r="I730" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J730" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K730">
-        <v>1</v>
-      </c>
-      <c r="L730" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M730" t="str">
-        <v>2026-07-03 20:41:59</v>
-      </c>
-      <c r="N730" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O730" s="1">
-        <v>0</v>
-      </c>
-      <c r="P730" t="str">
-        <v/>
-      </c>
-      <c r="Q730" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R730" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="str">
-        <v>T260703-00030</v>
-      </c>
-      <c r="B731" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C731" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D731" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E731" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F731">
-        <v>3</v>
-      </c>
-      <c r="G731" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H731" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I731" t="str">
-        <v>2026-07-04 08:00</v>
-      </c>
-      <c r="J731" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K731">
-        <v>1</v>
-      </c>
-      <c r="L731" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M731" t="str">
-        <v>2026-07-03 20:41:34</v>
-      </c>
-      <c r="N731" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O731" s="1">
-        <v>0</v>
-      </c>
-      <c r="P731" t="str">
-        <v/>
-      </c>
-      <c r="Q731" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R731" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="str">
-        <v>T260703-00029</v>
-      </c>
-      <c r="B732" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C732" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D732" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E732" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F732">
-        <v>0</v>
-      </c>
-      <c r="G732" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H732" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I732" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J732" t="str">
-        <v>1톤 기타차량</v>
-      </c>
-      <c r="K732">
-        <v>1</v>
-      </c>
-      <c r="L732" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M732" t="str">
-        <v>2026-07-03 20:40:56</v>
-      </c>
-      <c r="N732" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O732" s="1">
-        <v>0</v>
-      </c>
-      <c r="P732" t="str">
-        <v/>
-      </c>
-      <c r="Q732" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R732" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="str">
-        <v>T260703-00028</v>
-      </c>
-      <c r="B733" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C733" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D733" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E733" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F733">
-        <v>0</v>
-      </c>
-      <c r="G733" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="H733" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="I733" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J733" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K733">
-        <v>1</v>
-      </c>
-      <c r="L733" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M733" t="str">
-        <v>2026-07-03 20:40:32</v>
-      </c>
-      <c r="N733" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O733" s="1">
-        <v>0</v>
-      </c>
-      <c r="P733" t="str">
-        <v/>
-      </c>
-      <c r="Q733" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R733" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="str">
-        <v>T260703-00027</v>
-      </c>
-      <c r="B734" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C734" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D734" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E734" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F734">
-        <v>3</v>
-      </c>
-      <c r="G734" t="str">
-        <v>인제ACP</v>
-      </c>
-      <c r="H734" t="str">
-        <v>강원특별자치도 속초시 만천6길 13 인제ACP</v>
-      </c>
-      <c r="I734" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J734" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K734">
-        <v>1</v>
-      </c>
-      <c r="L734" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M734" t="str">
-        <v>2026-07-03 20:40:07</v>
-      </c>
-      <c r="N734" s="1">
-        <v>390000</v>
-      </c>
-      <c r="O734" s="1">
-        <v>0</v>
-      </c>
-      <c r="P734" t="str">
-        <v/>
-      </c>
-      <c r="Q734" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R734" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="str">
-        <v>T260703-00026</v>
-      </c>
-      <c r="B735" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C735" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D735" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E735" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F735">
-        <v>0</v>
-      </c>
-      <c r="G735" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H735" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I735" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J735" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K735">
-        <v>1</v>
-      </c>
-      <c r="L735" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M735" t="str">
-        <v>2026-07-03 20:39:21</v>
-      </c>
-      <c r="N735" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O735" s="1">
-        <v>0</v>
-      </c>
-      <c r="P735" t="str">
-        <v/>
-      </c>
-      <c r="Q735" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R735" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="str">
-        <v>T260703-00025</v>
-      </c>
-      <c r="B736" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C736" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D736" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E736" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F736">
-        <v>1</v>
-      </c>
-      <c r="G736" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H736" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I736" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J736" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K736">
-        <v>1</v>
-      </c>
-      <c r="L736" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M736" t="str">
-        <v>2026-07-03 20:39:06</v>
-      </c>
-      <c r="N736" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O736" s="1">
-        <v>0</v>
-      </c>
-      <c r="P736" t="str">
-        <v/>
-      </c>
-      <c r="Q736" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R736" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="str">
-        <v>T260703-00024</v>
-      </c>
-      <c r="B737" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C737" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D737" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E737" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F737">
-        <v>1</v>
-      </c>
-      <c r="G737" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H737" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I737" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J737" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K737">
-        <v>1</v>
-      </c>
-      <c r="L737" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M737" t="str">
-        <v>2026-07-03 20:38:48</v>
-      </c>
-      <c r="N737" s="1">
-        <v>530000</v>
-      </c>
-      <c r="O737" s="1">
-        <v>0</v>
-      </c>
-      <c r="P737" t="str">
-        <v/>
-      </c>
-      <c r="Q737" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R737" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="str">
-        <v>T260703-00023</v>
-      </c>
-      <c r="B738" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C738" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D738" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E738" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F738">
-        <v>0</v>
-      </c>
-      <c r="G738" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="H738" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="I738" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J738" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K738">
-        <v>1</v>
-      </c>
-      <c r="L738" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M738" t="str">
-        <v>2026-07-03 20:38:28</v>
-      </c>
-      <c r="N738" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O738" s="1">
-        <v>0</v>
-      </c>
-      <c r="P738" t="str">
-        <v/>
-      </c>
-      <c r="Q738" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R738" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="str">
-        <v>T260703-00022</v>
-      </c>
-      <c r="B739" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C739" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D739" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E739" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F739">
-        <v>0</v>
-      </c>
-      <c r="G739" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H739" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I739" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J739" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K739">
-        <v>1</v>
-      </c>
-      <c r="L739" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M739" t="str">
-        <v>2026-07-03 20:38:14</v>
-      </c>
-      <c r="N739" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O739" s="1">
-        <v>0</v>
-      </c>
-      <c r="P739" t="str">
-        <v/>
-      </c>
-      <c r="Q739" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R739" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="str">
-        <v>T260703-00021</v>
-      </c>
-      <c r="B740" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C740" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D740" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E740" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F740">
-        <v>1</v>
-      </c>
-      <c r="G740" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H740" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I740" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J740" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K740">
-        <v>1</v>
-      </c>
-      <c r="L740" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M740" t="str">
-        <v>2026-07-03 20:37:59</v>
-      </c>
-      <c r="N740" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O740" s="1">
-        <v>0</v>
-      </c>
-      <c r="P740" t="str">
-        <v/>
-      </c>
-      <c r="Q740" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R740" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="str">
-        <v>T260703-00020</v>
-      </c>
-      <c r="B741" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C741" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D741" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E741" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F741">
-        <v>0</v>
-      </c>
-      <c r="G741" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H741" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I741" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J741" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K741">
-        <v>1</v>
-      </c>
-      <c r="L741" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M741" t="str">
-        <v>2026-07-03 20:37:40</v>
-      </c>
-      <c r="N741" s="1">
-        <v>490000</v>
-      </c>
-      <c r="O741" s="1">
-        <v>0</v>
-      </c>
-      <c r="P741" t="str">
-        <v/>
-      </c>
-      <c r="Q741" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R741" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="str">
-        <v>T260703-00019</v>
-      </c>
-      <c r="B742" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C742" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D742" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E742" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F742">
-        <v>0</v>
-      </c>
-      <c r="G742" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H742" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I742" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J742" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K742">
-        <v>1</v>
-      </c>
-      <c r="L742" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M742" t="str">
-        <v>2026-07-03 20:37:26</v>
-      </c>
-      <c r="N742" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O742" s="1">
-        <v>0</v>
-      </c>
-      <c r="P742" t="str">
-        <v/>
-      </c>
-      <c r="Q742" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R742" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="str">
-        <v>T260703-00018</v>
-      </c>
-      <c r="B743" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C743" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D743" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E743" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F743">
-        <v>0</v>
-      </c>
-      <c r="G743" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H743" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I743" t="str">
-        <v>2026-07-03 20:00</v>
-      </c>
-      <c r="J743" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K743">
-        <v>1</v>
-      </c>
-      <c r="L743" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M743" t="str">
-        <v>2026-07-03 20:37:11</v>
-      </c>
-      <c r="N743" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O743" s="1">
-        <v>0</v>
-      </c>
-      <c r="P743" t="str">
-        <v/>
-      </c>
-      <c r="Q743" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R743" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="str">
-        <v>T260703-00017</v>
-      </c>
-      <c r="B744" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C744" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D744" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E744" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F744">
-        <v>0</v>
-      </c>
-      <c r="G744" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H744" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I744" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J744" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K744">
-        <v>1</v>
-      </c>
-      <c r="L744" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M744" t="str">
-        <v>2026-07-03 20:36:55</v>
-      </c>
-      <c r="N744" s="1">
-        <v>420000</v>
-      </c>
-      <c r="O744" s="1">
-        <v>0</v>
-      </c>
-      <c r="P744" t="str">
-        <v/>
-      </c>
-      <c r="Q744" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R744" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="str">
-        <v>T260703-00016</v>
-      </c>
-      <c r="B745" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C745" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D745" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E745" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F745">
-        <v>0</v>
-      </c>
-      <c r="G745" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H745" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I745" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J745" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K745">
-        <v>1</v>
-      </c>
-      <c r="L745" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M745" t="str">
-        <v>2026-07-03 20:36:37</v>
-      </c>
-      <c r="N745" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O745" s="1">
-        <v>0</v>
-      </c>
-      <c r="P745" t="str">
-        <v/>
-      </c>
-      <c r="Q745" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R745" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="str">
-        <v>T260703-00015</v>
-      </c>
-      <c r="B746" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C746" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D746" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E746" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F746">
-        <v>0</v>
-      </c>
-      <c r="G746" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H746" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I746" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J746" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K746">
-        <v>1</v>
-      </c>
-      <c r="L746" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M746" t="str">
-        <v>2026-07-03 20:36:15</v>
-      </c>
-      <c r="N746" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O746" s="1">
-        <v>0</v>
-      </c>
-      <c r="P746" t="str">
-        <v/>
-      </c>
-      <c r="Q746" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R746" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="str">
-        <v>T260703-00014</v>
-      </c>
-      <c r="B747" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C747" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D747" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E747" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F747">
-        <v>1</v>
-      </c>
-      <c r="G747" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H747" t="str">
-        <v>경산시 해오름길114-2 경산FDC</v>
-      </c>
-      <c r="I747" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J747" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K747">
-        <v>1</v>
-      </c>
-      <c r="L747" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M747" t="str">
-        <v>2026-07-03 20:35:55</v>
-      </c>
-      <c r="N747" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O747" s="1">
-        <v>0</v>
-      </c>
-      <c r="P747" t="str">
-        <v/>
-      </c>
-      <c r="Q747" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R747" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="str">
-        <v>T260703-00013</v>
-      </c>
-      <c r="B748" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C748" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D748" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E748" t="str">
-        <v>2026-07-03 17:30</v>
-      </c>
-      <c r="F748">
-        <v>0</v>
-      </c>
-      <c r="G748" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H748" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I748" t="str">
-        <v>2026-07-03 18:30</v>
-      </c>
-      <c r="J748" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K748">
-        <v>1</v>
-      </c>
-      <c r="L748" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M748" t="str">
-        <v>2026-07-03 20:31:55</v>
-      </c>
-      <c r="N748" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O748" s="1">
-        <v>0</v>
-      </c>
-      <c r="P748" t="str">
-        <v/>
-      </c>
-      <c r="Q748" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R748" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" t="str">
-        <v>T260703-00012</v>
-      </c>
-      <c r="B749" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C749" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="D749" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="E749" t="str">
-        <v>2026-07-03 08:30</v>
-      </c>
-      <c r="F749">
-        <v>0</v>
-      </c>
-      <c r="G749" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="H749" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="I749" t="str">
-        <v>2026-07-03 11:30</v>
-      </c>
-      <c r="J749" t="str">
-        <v>3.5톤 카고</v>
-      </c>
-      <c r="K749">
-        <v>1</v>
-      </c>
-      <c r="L749" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M749" t="str">
-        <v>2026-07-03 20:31:21</v>
-      </c>
-      <c r="N749" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O749" s="1">
-        <v>0</v>
-      </c>
-      <c r="P749" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="Q749" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R749" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="str">
-        <v>T260703-00011</v>
-      </c>
-      <c r="B750" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C750" t="str">
-        <v>샤오미</v>
-      </c>
-      <c r="D750" t="str">
-        <v>경기 이천시 대월면 부필리 309 샤오미</v>
-      </c>
-      <c r="E750" t="str">
-        <v>2026-07-03 11:30</v>
-      </c>
-      <c r="F750">
-        <v>0</v>
-      </c>
-      <c r="G750" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H750" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I750" t="str">
-        <v>2026-07-03 13:30</v>
-      </c>
-      <c r="J750" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K750">
-        <v>1</v>
-      </c>
-      <c r="L750" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M750" t="str">
-        <v>2026-07-03 20:30:39</v>
-      </c>
-      <c r="N750" s="1">
-        <v>80000</v>
-      </c>
-      <c r="O750" s="1">
-        <v>0</v>
-      </c>
-      <c r="P750" t="str">
-        <v>거래처비용청구(1대)</v>
-      </c>
-      <c r="Q750" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R750" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="str">
-        <v>T260703-00010</v>
-      </c>
-      <c r="B751" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C751" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D751" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E751" t="str">
-        <v>2026-07-03 13:30</v>
-      </c>
-      <c r="F751">
-        <v>0</v>
-      </c>
-      <c r="G751" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H751" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I751" t="str">
-        <v>2026-07-03 15:30</v>
-      </c>
-      <c r="J751" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K751">
-        <v>1</v>
-      </c>
-      <c r="L751" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M751" t="str">
-        <v>2026-07-03 20:29:47</v>
-      </c>
-      <c r="N751" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O751" s="1">
-        <v>0</v>
-      </c>
-      <c r="P751" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q751" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R751" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="str">
-        <v>T260703-00009</v>
-      </c>
-      <c r="B752" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C752" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D752" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E752" t="str">
-        <v>2026-07-03 10:00</v>
-      </c>
-      <c r="F752">
-        <v>0</v>
-      </c>
-      <c r="G752" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H752" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I752" t="str">
-        <v>2026-07-03 13:30</v>
-      </c>
-      <c r="J752" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K752">
-        <v>1</v>
-      </c>
-      <c r="L752" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M752" t="str">
-        <v>2026-07-03 20:29:05</v>
-      </c>
-      <c r="N752" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O752" s="1">
-        <v>0</v>
-      </c>
-      <c r="P752" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q752" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R752" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="str">
-        <v>T260703-00008</v>
-      </c>
-      <c r="B753" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C753" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D753" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E753" t="str">
-        <v>2026-07-03 16:30</v>
-      </c>
-      <c r="F753">
-        <v>0</v>
-      </c>
-      <c r="G753" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H753" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I753" t="str">
-        <v>2026-07-03 18:00</v>
-      </c>
-      <c r="J753" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K753">
-        <v>1</v>
-      </c>
-      <c r="L753" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M753" t="str">
-        <v>2026-07-03 18:39:34</v>
-      </c>
-      <c r="N753" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O753" s="1">
-        <v>0</v>
-      </c>
-      <c r="P753" t="str">
-        <v>20260703/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q753" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R753" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="str">
-        <v>T260703-00007</v>
-      </c>
-      <c r="B754" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C754" t="str">
-        <v>청주ARC(공파렛트 이동)</v>
-      </c>
-      <c r="D754" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(공파렛트 이동)</v>
-      </c>
-      <c r="E754" t="str">
-        <v>2026-07-03 11:40</v>
-      </c>
-      <c r="F754">
-        <v>0</v>
-      </c>
-      <c r="G754" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H754" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="I754" t="str">
-        <v>2026-07-03 13:00</v>
-      </c>
-      <c r="J754" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K754">
-        <v>1</v>
-      </c>
-      <c r="L754" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M754" t="str">
-        <v>2026-07-03 11:28:01</v>
-      </c>
-      <c r="N754" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O754" s="1">
-        <v>0</v>
-      </c>
-      <c r="P754" t="str">
-        <v>20260703청주-&gt; 안성FC/공파렛트이동</v>
-      </c>
-      <c r="Q754" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R754" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="str">
-        <v>T260703-00006</v>
-      </c>
-      <c r="B755" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C755" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D755" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E755" t="str">
-        <v>2026-07-03 11:55</v>
-      </c>
-      <c r="F755">
-        <v>0</v>
-      </c>
-      <c r="G755" t="str">
-        <v>하이얼(서울 벌크 출하)</v>
-      </c>
-      <c r="H755" t="str">
-        <v>서울 강남구 선릉로92길 38 도파민</v>
-      </c>
-      <c r="I755" t="str">
-        <v>2026-07-03 13:00</v>
-      </c>
-      <c r="J755" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K755">
-        <v>1</v>
-      </c>
-      <c r="L755" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M755" t="str">
-        <v>2026-07-03 11:26:22</v>
-      </c>
-      <c r="N755" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O755" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P755" t="str">
-        <v>20260703/하이얼_서울_벌크_출하</v>
-      </c>
-      <c r="Q755" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R755" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="str">
-        <v>T260703-00005</v>
-      </c>
-      <c r="B756" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C756" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D756" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E756" t="str">
-        <v>2026-07-03 11:00</v>
-      </c>
-      <c r="F756">
-        <v>0</v>
-      </c>
-      <c r="G756" t="str">
-        <v>파주 하이마트 물류</v>
-      </c>
-      <c r="H756" t="str">
-        <v>경기 파주시 탄현면 월롱산로 296 파주 하이마트 물류</v>
-      </c>
-      <c r="I756" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J756" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K756">
-        <v>1</v>
-      </c>
-      <c r="L756" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M756" t="str">
-        <v>2026-07-03 11:22:28</v>
-      </c>
-      <c r="N756" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O756" s="1">
-        <v>0</v>
-      </c>
-      <c r="P756" t="str">
-        <v>일코전자 파주 하이마트 물류</v>
-      </c>
-      <c r="Q756" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R756" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="str">
-        <v>T260703-00004</v>
-      </c>
-      <c r="B757" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C757" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D757" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지  안성FC</v>
-      </c>
-      <c r="E757" t="str">
-        <v>2026-07-03 09:30</v>
-      </c>
-      <c r="F757">
-        <v>0</v>
-      </c>
-      <c r="G757" t="str">
-        <v>TCL다코넷</v>
-      </c>
-      <c r="H757" t="str">
-        <v>경기 평택시 포승읍 희곡리 847 평택 켄달스퀘어 3층, 다코넷 37번 도크</v>
-      </c>
-      <c r="I757" t="str">
-        <v>2026-07-03 11:30</v>
-      </c>
-      <c r="J757" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K757">
-        <v>1</v>
-      </c>
-      <c r="L757" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M757" t="str">
-        <v>2026-07-03 11:21:17</v>
-      </c>
-      <c r="N757" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O757" s="1">
-        <v>0</v>
-      </c>
-      <c r="P757" t="str">
-        <v>TCL 다코넷</v>
-      </c>
-      <c r="Q757" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R757" t="str">
-        <v>TCL</v>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="str">
-        <v>T260703-00003</v>
-      </c>
-      <c r="B758" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C758" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D758" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E758" t="str">
-        <v>2026-07-03 13:00</v>
-      </c>
-      <c r="F758">
-        <v>0</v>
-      </c>
-      <c r="G758" t="str">
-        <v>이천 하이마트 물류</v>
-      </c>
-      <c r="H758" t="str">
-        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 물류</v>
-      </c>
-      <c r="I758" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J758" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K758">
-        <v>1</v>
-      </c>
-      <c r="L758" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M758" t="str">
-        <v>2026-07-03 11:19:40</v>
-      </c>
-      <c r="N758" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O758" s="1">
-        <v>0</v>
-      </c>
-      <c r="P758" t="str">
-        <v>일코전자 이천 하이마트 물류</v>
-      </c>
-      <c r="Q758" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R758" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="str">
-        <v>T260703-00002</v>
-      </c>
-      <c r="B759" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C759" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D759" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E759" t="str">
-        <v>2026-07-03 10:00</v>
-      </c>
-      <c r="F759">
-        <v>0</v>
-      </c>
-      <c r="G759" t="str">
-        <v>화성 하이마트 물류</v>
-      </c>
-      <c r="H759" t="str">
-        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 물류</v>
-      </c>
-      <c r="I759" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J759" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K759">
-        <v>1</v>
-      </c>
-      <c r="L759" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M759" t="str">
-        <v>2026-07-03 11:18:03</v>
-      </c>
-      <c r="N759" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O759" s="1">
-        <v>0</v>
-      </c>
-      <c r="P759" t="str">
-        <v>일코전자 화성 하이마트 물류</v>
-      </c>
-      <c r="Q759" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R759" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="760">
-      <c r="A760" t="str">
-        <v>T260703-00001</v>
-      </c>
-      <c r="B760" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C760" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D760" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E760" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="F760">
-        <v>0</v>
-      </c>
-      <c r="G760" t="str">
-        <v>인천 하이마트 물류</v>
-      </c>
-      <c r="H760" t="str">
-        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
-      </c>
-      <c r="I760" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J760" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K760">
-        <v>1</v>
-      </c>
-      <c r="L760" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M760" t="str">
-        <v>2026-07-03 11:16:52</v>
-      </c>
-      <c r="N760" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O760" s="1">
-        <v>0</v>
-      </c>
-      <c r="P760" t="str">
-        <v>일코전자 인천 하이마트 물류</v>
-      </c>
-      <c r="Q760" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R760" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" t="str">
-        <v>T260702-00027</v>
-      </c>
-      <c r="B761" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C761" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D761" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E761" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F761">
-        <v>1</v>
-      </c>
-      <c r="G761" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H761" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I761" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J761" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K761">
-        <v>1</v>
-      </c>
-      <c r="L761" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M761" t="str">
-        <v>2026-07-02 20:54:21</v>
-      </c>
-      <c r="N761" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O761" s="1">
-        <v>0</v>
-      </c>
-      <c r="P761" t="str">
-        <v/>
-      </c>
-      <c r="Q761" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R761" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="762">
-      <c r="A762" t="str">
-        <v>T260702-00026</v>
-      </c>
-      <c r="B762" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C762" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D762" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E762" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F762">
-        <v>1</v>
-      </c>
-      <c r="G762" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H762" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I762" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J762" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K762">
-        <v>1</v>
-      </c>
-      <c r="L762" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M762" t="str">
-        <v>2026-07-02 20:53:56</v>
-      </c>
-      <c r="N762" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O762" s="1">
-        <v>0</v>
-      </c>
-      <c r="P762" t="str">
-        <v/>
-      </c>
-      <c r="Q762" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R762" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="763">
-      <c r="A763" t="str">
-        <v>T260702-00025</v>
-      </c>
-      <c r="B763" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C763" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D763" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E763" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F763">
-        <v>3</v>
-      </c>
-      <c r="G763" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H763" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I763" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J763" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K763">
-        <v>1</v>
-      </c>
-      <c r="L763" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M763" t="str">
-        <v>2026-07-02 20:53:28</v>
-      </c>
-      <c r="N763" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O763" s="1">
-        <v>0</v>
-      </c>
-      <c r="P763" t="str">
-        <v/>
-      </c>
-      <c r="Q763" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R763" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="764">
-      <c r="A764" t="str">
-        <v>T260702-00024</v>
-      </c>
-      <c r="B764" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C764" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D764" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E764" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F764">
-        <v>0</v>
-      </c>
-      <c r="G764" t="str">
-        <v>용인ACP</v>
-      </c>
-      <c r="H764" t="str">
-        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
-      </c>
-      <c r="I764" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J764" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K764">
-        <v>1</v>
-      </c>
-      <c r="L764" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M764" t="str">
-        <v>2026-07-02 20:52:18</v>
-      </c>
-      <c r="N764" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O764" s="1">
-        <v>0</v>
-      </c>
-      <c r="P764" t="str">
-        <v/>
-      </c>
-      <c r="Q764" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R764" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" t="str">
-        <v>T260702-00023</v>
-      </c>
-      <c r="B765" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C765" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D765" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E765" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F765">
-        <v>1</v>
-      </c>
-      <c r="G765" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H765" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I765" t="str">
-        <v>2026-07-03 07:00</v>
-      </c>
-      <c r="J765" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K765">
-        <v>1</v>
-      </c>
-      <c r="L765" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M765" t="str">
-        <v>2026-07-02 20:51:59</v>
-      </c>
-      <c r="N765" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O765" s="1">
-        <v>0</v>
-      </c>
-      <c r="P765" t="str">
-        <v/>
-      </c>
-      <c r="Q765" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R765" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" t="str">
-        <v>T260702-00022</v>
-      </c>
-      <c r="B766" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C766" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D766" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E766" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F766">
-        <v>0</v>
-      </c>
-      <c r="G766" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H766" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I766" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J766" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K766">
-        <v>1</v>
-      </c>
-      <c r="L766" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M766" t="str">
-        <v>2026-07-02 20:51:32</v>
-      </c>
-      <c r="N766" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O766" s="1">
-        <v>0</v>
-      </c>
-      <c r="P766" t="str">
-        <v/>
-      </c>
-      <c r="Q766" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R766" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" t="str">
-        <v>T260702-00021</v>
-      </c>
-      <c r="B767" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C767" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D767" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E767" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F767">
-        <v>1</v>
-      </c>
-      <c r="G767" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H767" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I767" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J767" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K767">
-        <v>1</v>
-      </c>
-      <c r="L767" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M767" t="str">
-        <v>2026-07-02 20:51:14</v>
-      </c>
-      <c r="N767" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O767" s="1">
-        <v>0</v>
-      </c>
-      <c r="P767" t="str">
-        <v/>
-      </c>
-      <c r="Q767" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R767" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="768">
-      <c r="A768" t="str">
-        <v>T260702-00020</v>
-      </c>
-      <c r="B768" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C768" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D768" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E768" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F768">
-        <v>0</v>
-      </c>
-      <c r="G768" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="H768" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="I768" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J768" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K768">
-        <v>1</v>
-      </c>
-      <c r="L768" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M768" t="str">
-        <v>2026-07-02 20:50:54</v>
-      </c>
-      <c r="N768" s="1">
-        <v>280000</v>
-      </c>
-      <c r="O768" s="1">
-        <v>0</v>
-      </c>
-      <c r="P768" t="str">
-        <v/>
-      </c>
-      <c r="Q768" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R768" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="769">
-      <c r="A769" t="str">
-        <v>T260702-00019</v>
-      </c>
-      <c r="B769" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C769" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D769" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E769" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F769">
-        <v>0</v>
-      </c>
-      <c r="G769" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H769" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I769" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J769" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K769">
-        <v>1</v>
-      </c>
-      <c r="L769" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M769" t="str">
-        <v>2026-07-02 20:50:36</v>
-      </c>
-      <c r="N769" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O769" s="1">
-        <v>0</v>
-      </c>
-      <c r="P769" t="str">
-        <v/>
-      </c>
-      <c r="Q769" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R769" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="770">
-      <c r="A770" t="str">
-        <v>T260702-00018</v>
-      </c>
-      <c r="B770" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C770" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D770" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E770" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F770">
-        <v>1</v>
-      </c>
-      <c r="G770" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H770" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I770" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J770" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K770">
-        <v>1</v>
-      </c>
-      <c r="L770" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M770" t="str">
-        <v>2026-07-02 20:50:19</v>
-      </c>
-      <c r="N770" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O770" s="1">
-        <v>0</v>
-      </c>
-      <c r="P770" t="str">
-        <v/>
-      </c>
-      <c r="Q770" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R770" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="771">
-      <c r="A771" t="str">
-        <v>T260702-00017</v>
-      </c>
-      <c r="B771" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C771" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D771" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E771" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F771">
-        <v>1</v>
-      </c>
-      <c r="G771" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H771" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I771" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J771" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K771">
-        <v>1</v>
-      </c>
-      <c r="L771" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M771" t="str">
-        <v>2026-07-02 20:49:56</v>
-      </c>
-      <c r="N771" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O771" s="1">
-        <v>0</v>
-      </c>
-      <c r="P771" t="str">
-        <v/>
-      </c>
-      <c r="Q771" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R771" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="772">
-      <c r="A772" t="str">
-        <v>T260702-00016</v>
-      </c>
-      <c r="B772" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C772" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D772" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E772" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F772">
-        <v>0</v>
-      </c>
-      <c r="G772" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H772" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I772" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J772" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K772">
-        <v>1</v>
-      </c>
-      <c r="L772" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M772" t="str">
-        <v>2026-07-02 20:49:25</v>
-      </c>
-      <c r="N772" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O772" s="1">
-        <v>0</v>
-      </c>
-      <c r="P772" t="str">
-        <v/>
-      </c>
-      <c r="Q772" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R772" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="773">
-      <c r="A773" t="str">
-        <v>T260702-00015</v>
-      </c>
-      <c r="B773" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C773" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D773" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E773" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F773">
-        <v>1</v>
-      </c>
-      <c r="G773" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H773" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I773" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J773" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K773">
-        <v>1</v>
-      </c>
-      <c r="L773" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M773" t="str">
-        <v>2026-07-02 20:48:50</v>
-      </c>
-      <c r="N773" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O773" s="1">
-        <v>0</v>
-      </c>
-      <c r="P773" t="str">
-        <v/>
-      </c>
-      <c r="Q773" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R773" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="774">
-      <c r="A774" t="str">
-        <v>T260702-00014</v>
-      </c>
-      <c r="B774" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C774" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D774" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E774" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F774">
-        <v>0</v>
-      </c>
-      <c r="G774" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H774" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I774" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J774" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K774">
-        <v>1</v>
-      </c>
-      <c r="L774" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M774" t="str">
-        <v>2026-07-02 20:48:25</v>
-      </c>
-      <c r="N774" s="1">
-        <v>420000</v>
-      </c>
-      <c r="O774" s="1">
-        <v>0</v>
-      </c>
-      <c r="P774" t="str">
-        <v/>
-      </c>
-      <c r="Q774" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R774" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="775">
-      <c r="A775" t="str">
-        <v>T260702-00013</v>
-      </c>
-      <c r="B775" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C775" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D775" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E775" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F775">
-        <v>0</v>
-      </c>
-      <c r="G775" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H775" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I775" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J775" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K775">
-        <v>1</v>
-      </c>
-      <c r="L775" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M775" t="str">
-        <v>2026-07-02 20:48:09</v>
-      </c>
-      <c r="N775" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O775" s="1">
-        <v>0</v>
-      </c>
-      <c r="P775" t="str">
-        <v/>
-      </c>
-      <c r="Q775" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R775" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="776">
-      <c r="A776" t="str">
-        <v>T260702-00012</v>
-      </c>
-      <c r="B776" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C776" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D776" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E776" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F776">
-        <v>2</v>
-      </c>
-      <c r="G776" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H776" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I776" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J776" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K776">
-        <v>1</v>
-      </c>
-      <c r="L776" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M776" t="str">
-        <v>2026-07-02 20:47:49</v>
-      </c>
-      <c r="N776" s="1">
-        <v>680000</v>
-      </c>
-      <c r="O776" s="1">
-        <v>0</v>
-      </c>
-      <c r="P776" t="str">
-        <v/>
-      </c>
-      <c r="Q776" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R776" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="777">
-      <c r="A777" t="str">
-        <v>T260702-00011</v>
-      </c>
-      <c r="B777" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C777" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D777" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E777" t="str">
-        <v>2026-07-02 17:50</v>
-      </c>
-      <c r="F777">
-        <v>0</v>
-      </c>
-      <c r="G777" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H777" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I777" t="str">
-        <v>2026-07-02 18:50</v>
-      </c>
-      <c r="J777" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K777">
-        <v>1</v>
-      </c>
-      <c r="L777" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M777" t="str">
-        <v>2026-07-02 20:44:59</v>
-      </c>
-      <c r="N777" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O777" s="1">
-        <v>0</v>
-      </c>
-      <c r="P777" t="str">
-        <v/>
-      </c>
-      <c r="Q777" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R777" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="778">
-      <c r="A778" t="str">
-        <v>T260702-00010</v>
-      </c>
-      <c r="B778" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C778" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D778" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E778" t="str">
-        <v>2026-07-02 13:30</v>
-      </c>
-      <c r="F778">
-        <v>0</v>
-      </c>
-      <c r="G778" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H778" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I778" t="str">
-        <v>2026-07-02 15:40</v>
-      </c>
-      <c r="J778" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K778">
-        <v>1</v>
-      </c>
-      <c r="L778" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M778" t="str">
-        <v>2026-07-02 20:44:26</v>
-      </c>
-      <c r="N778" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O778" s="1">
-        <v>0</v>
-      </c>
-      <c r="P778" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q778" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R778" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="779">
-      <c r="A779" t="str">
-        <v>T260702-00009</v>
-      </c>
-      <c r="B779" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C779" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D779" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E779" t="str">
-        <v>2026-07-02 10:00</v>
-      </c>
-      <c r="F779">
-        <v>0</v>
-      </c>
-      <c r="G779" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H779" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I779" t="str">
-        <v>2026-07-02 13:40</v>
-      </c>
-      <c r="J779" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K779">
-        <v>1</v>
-      </c>
-      <c r="L779" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M779" t="str">
-        <v>2026-07-02 20:43:37</v>
-      </c>
-      <c r="N779" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O779" s="1">
-        <v>0</v>
-      </c>
-      <c r="P779" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q779" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R779" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="780">
-      <c r="A780" t="str">
-        <v>T260702-00008</v>
-      </c>
-      <c r="B780" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C780" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D780" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E780" t="str">
-        <v>2026-07-02 17:00</v>
-      </c>
-      <c r="F780">
-        <v>0</v>
-      </c>
-      <c r="G780" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="H780" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="I780" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J780" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K780">
-        <v>1</v>
-      </c>
-      <c r="L780" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M780" t="str">
-        <v>2026-07-02 16:38:23</v>
-      </c>
-      <c r="N780" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O780" s="1">
-        <v>0</v>
-      </c>
-      <c r="P780" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="Q780" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R780" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="781">
-      <c r="A781" t="str">
-        <v>T260702-00007</v>
-      </c>
-      <c r="B781" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C781" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D781" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E781" t="str">
-        <v>2026-07-02 16:30</v>
-      </c>
-      <c r="F781">
-        <v>0</v>
-      </c>
-      <c r="G781" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H781" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I781" t="str">
-        <v>2026-07-02 18:00</v>
-      </c>
-      <c r="J781" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K781">
-        <v>1</v>
-      </c>
-      <c r="L781" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M781" t="str">
-        <v>2026-07-02 16:34:35</v>
-      </c>
-      <c r="N781" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O781" s="1">
-        <v>0</v>
-      </c>
-      <c r="P781" t="str">
-        <v>20260702/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q781" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R781" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="782">
-      <c r="A782" t="str">
-        <v>T260702-00006</v>
-      </c>
-      <c r="B782" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C782" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D782" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E782" t="str">
-        <v>2026-07-02 16:00</v>
-      </c>
-      <c r="F782">
-        <v>0</v>
-      </c>
-      <c r="G782" t="str">
-        <v>광주 하이마트 물류</v>
-      </c>
-      <c r="H782" t="str">
-        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
-      </c>
-      <c r="I782" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J782" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K782">
-        <v>1</v>
-      </c>
-      <c r="L782" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M782" t="str">
-        <v>2026-07-02 15:30:55</v>
-      </c>
-      <c r="N782" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O782" s="1">
-        <v>0</v>
-      </c>
-      <c r="P782" t="str">
-        <v>일코 광주 하이마트 물류</v>
-      </c>
-      <c r="Q782" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R782" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="783">
-      <c r="A783" t="str">
-        <v>T260702-00005</v>
-      </c>
-      <c r="B783" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C783" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D783" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E783" t="str">
-        <v>2026-07-02 14:30</v>
-      </c>
-      <c r="F783">
-        <v>0</v>
-      </c>
-      <c r="G783" t="str">
-        <v>마산 하이마트 물류</v>
-      </c>
-      <c r="H783" t="str">
-        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
-      </c>
-      <c r="I783" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J783" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K783">
-        <v>1</v>
-      </c>
-      <c r="L783" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M783" t="str">
-        <v>2026-07-02 13:44:41</v>
-      </c>
-      <c r="N783" s="1">
-        <v>380000</v>
-      </c>
-      <c r="O783" s="1">
-        <v>0</v>
-      </c>
-      <c r="P783" t="str">
-        <v>일코 마산 하이마트 물류</v>
-      </c>
-      <c r="Q783" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R783" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="784">
-      <c r="A784" t="str">
-        <v>T260702-00004</v>
-      </c>
-      <c r="B784" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C784" t="str">
-        <v>강릉 하이마트 물류</v>
-      </c>
-      <c r="D784" t="str">
-        <v>강원특별자치도 강릉시 연곡면 동해대로 4100-36 강릉 하이마트 물류</v>
-      </c>
-      <c r="E784" t="str">
-        <v>2026-07-02 13:30</v>
-      </c>
-      <c r="F784">
-        <v>0</v>
-      </c>
-      <c r="G784" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H784" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I784" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J784" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K784">
-        <v>1</v>
-      </c>
-      <c r="L784" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M784" t="str">
-        <v>2026-07-02 12:00:10</v>
-      </c>
-      <c r="N784" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O784" s="1">
-        <v>0</v>
-      </c>
-      <c r="P784" t="str">
-        <v>일코전자 강릉 하이마트 물류</v>
-      </c>
-      <c r="Q784" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R784" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="785">
-      <c r="A785" t="str">
-        <v>T260702-00003</v>
-      </c>
-      <c r="B785" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C785" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D785" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E785" t="str">
-        <v>2026-07-02 14:30</v>
-      </c>
-      <c r="F785">
-        <v>0</v>
-      </c>
-      <c r="G785" t="str">
-        <v>대구 하이마트 물류</v>
-      </c>
-      <c r="H785" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="I785" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J785" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K785">
-        <v>1</v>
-      </c>
-      <c r="L785" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M785" t="str">
-        <v>2026-07-02 11:59:32</v>
-      </c>
-      <c r="N785" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O785" s="1">
-        <v>0</v>
-      </c>
-      <c r="P785" t="str">
-        <v>일코전자 대구 하이마트 물류</v>
-      </c>
-      <c r="Q785" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R785" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="786">
-      <c r="A786" t="str">
-        <v>T260702-00002</v>
-      </c>
-      <c r="B786" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C786" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D786" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E786" t="str">
-        <v>2026-07-02 09:30</v>
-      </c>
-      <c r="F786">
-        <v>1</v>
-      </c>
-      <c r="G786" t="str">
-        <v>하이얼(대구2착)</v>
-      </c>
-      <c r="H786" t="str">
-        <v>대구 남구 양지로 25 대명자이 아파트</v>
-      </c>
-      <c r="I786" t="str">
-        <v>2026-07-02 15:00</v>
-      </c>
-      <c r="J786" t="str">
-        <v>1.5톤 윙바디</v>
-      </c>
-      <c r="K786">
-        <v>1</v>
-      </c>
-      <c r="L786" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M786" t="str">
-        <v>2026-07-02 09:20:07</v>
-      </c>
-      <c r="N786" s="1">
-        <v>220000</v>
-      </c>
-      <c r="O786" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P786" t="str">
-        <v>20260702/하이얼_대구 착지 2곳_벌크_출하</v>
-      </c>
-      <c r="Q786" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R786" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="787">
-      <c r="A787" t="str">
-        <v>T260702-00001</v>
-      </c>
-      <c r="B787" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C787" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D787" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E787" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="F787">
-        <v>0</v>
-      </c>
-      <c r="G787" t="str">
-        <v>로지스밸리인천포트(Logisvalley)</v>
-      </c>
-      <c r="H787" t="str">
-        <v>인천 연수구 인천타워대로599번길 60 로지스밸리인천포트(Logisvalley) 1층 13번(HTC)</v>
-      </c>
-      <c r="I787" t="str">
-        <v>2026-07-02 11:00</v>
-      </c>
-      <c r="J787" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K787">
-        <v>1</v>
-      </c>
-      <c r="L787" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M787" t="str">
-        <v>2026-07-02 09:17:29</v>
-      </c>
-      <c r="N787" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O787" s="1">
-        <v>0</v>
-      </c>
-      <c r="P787" t="str">
-        <v>패스트레인 출하</v>
-      </c>
-      <c r="Q787" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R787" t="str">
-        <v>패스트레인코리아</v>
-      </c>
-    </row>
-    <row r="788">
-      <c r="A788" t="str">
-        <v>T260701-00026</v>
-      </c>
-      <c r="B788" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C788" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D788" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E788" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F788">
-        <v>1</v>
-      </c>
-      <c r="G788" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H788" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I788" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J788" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K788">
-        <v>1</v>
-      </c>
-      <c r="L788" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M788" t="str">
-        <v>2026-07-01 19:47:13</v>
-      </c>
-      <c r="N788" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O788" s="1">
-        <v>0</v>
-      </c>
-      <c r="P788" t="str">
-        <v/>
-      </c>
-      <c r="Q788" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R788" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="789">
-      <c r="A789" t="str">
-        <v>T260701-00025</v>
-      </c>
-      <c r="B789" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C789" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D789" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E789" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F789">
-        <v>2</v>
-      </c>
-      <c r="G789" t="str">
-        <v>원주ACP</v>
-      </c>
-      <c r="H789" t="str">
-        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
-      </c>
-      <c r="I789" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J789" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K789">
-        <v>1</v>
-      </c>
-      <c r="L789" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M789" t="str">
-        <v>2026-07-01 19:46:48</v>
-      </c>
-      <c r="N789" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O789" s="1">
-        <v>0</v>
-      </c>
-      <c r="P789" t="str">
-        <v/>
-      </c>
-      <c r="Q789" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R789" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="790">
-      <c r="A790" t="str">
-        <v>T260701-00024</v>
-      </c>
-      <c r="B790" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C790" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D790" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E790" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F790">
-        <v>1</v>
-      </c>
-      <c r="G790" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H790" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I790" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J790" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K790">
-        <v>1</v>
-      </c>
-      <c r="L790" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M790" t="str">
-        <v>2026-07-01 19:46:12</v>
-      </c>
-      <c r="N790" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O790" s="1">
-        <v>0</v>
-      </c>
-      <c r="P790" t="str">
-        <v/>
-      </c>
-      <c r="Q790" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R790" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="791">
-      <c r="A791" t="str">
-        <v>T260701-00023</v>
-      </c>
-      <c r="B791" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C791" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D791" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E791" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F791">
-        <v>3</v>
-      </c>
-      <c r="G791" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H791" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I791" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J791" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K791">
-        <v>1</v>
-      </c>
-      <c r="L791" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M791" t="str">
-        <v>2026-07-01 19:45:40</v>
-      </c>
-      <c r="N791" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O791" s="1">
-        <v>0</v>
-      </c>
-      <c r="P791" t="str">
-        <v/>
-      </c>
-      <c r="Q791" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R791" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="792">
-      <c r="A792" t="str">
-        <v>T260701-00022</v>
-      </c>
-      <c r="B792" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C792" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D792" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E792" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F792">
-        <v>0</v>
-      </c>
-      <c r="G792" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H792" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I792" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J792" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K792">
-        <v>1</v>
-      </c>
-      <c r="L792" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M792" t="str">
-        <v>2026-07-01 19:44:56</v>
-      </c>
-      <c r="N792" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O792" s="1">
-        <v>0</v>
-      </c>
-      <c r="P792" t="str">
-        <v/>
-      </c>
-      <c r="Q792" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R792" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="793">
-      <c r="A793" t="str">
-        <v>T260701-00021</v>
-      </c>
-      <c r="B793" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C793" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D793" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E793" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F793">
-        <v>1</v>
-      </c>
-      <c r="G793" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H793" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I793" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J793" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K793">
-        <v>1</v>
-      </c>
-      <c r="L793" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M793" t="str">
-        <v>2026-07-01 19:44:37</v>
-      </c>
-      <c r="N793" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O793" s="1">
-        <v>0</v>
-      </c>
-      <c r="P793" t="str">
-        <v/>
-      </c>
-      <c r="Q793" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R793" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" t="str">
-        <v>T260701-00020</v>
-      </c>
-      <c r="B794" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C794" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D794" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E794" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F794">
-        <v>2</v>
-      </c>
-      <c r="G794" t="str">
-        <v>속초ACP</v>
-      </c>
-      <c r="H794" t="str">
-        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
-      </c>
-      <c r="I794" t="str">
-        <v>2026-07-02 06:00</v>
-      </c>
-      <c r="J794" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K794">
-        <v>1</v>
-      </c>
-      <c r="L794" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M794" t="str">
-        <v>2026-07-01 19:44:05</v>
-      </c>
-      <c r="N794" s="1">
-        <v>320000</v>
-      </c>
-      <c r="O794" s="1">
-        <v>0</v>
-      </c>
-      <c r="P794" t="str">
-        <v/>
-      </c>
-      <c r="Q794" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R794" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="795">
-      <c r="A795" t="str">
-        <v>T260701-00019</v>
-      </c>
-      <c r="B795" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C795" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D795" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E795" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F795">
-        <v>0</v>
-      </c>
-      <c r="G795" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H795" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I795" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J795" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K795">
-        <v>1</v>
-      </c>
-      <c r="L795" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M795" t="str">
-        <v>2026-07-01 19:43:22</v>
-      </c>
-      <c r="N795" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O795" s="1">
-        <v>0</v>
-      </c>
-      <c r="P795" t="str">
-        <v/>
-      </c>
-      <c r="Q795" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R795" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="796">
-      <c r="A796" t="str">
-        <v>T260701-00018</v>
-      </c>
-      <c r="B796" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C796" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D796" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E796" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F796">
-        <v>1</v>
-      </c>
-      <c r="G796" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H796" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I796" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J796" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K796">
-        <v>1</v>
-      </c>
-      <c r="L796" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M796" t="str">
-        <v>2026-07-01 19:43:03</v>
-      </c>
-      <c r="N796" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O796" s="1">
-        <v>0</v>
-      </c>
-      <c r="P796" t="str">
-        <v/>
-      </c>
-      <c r="Q796" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R796" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="797">
-      <c r="A797" t="str">
-        <v>T260701-00017</v>
-      </c>
-      <c r="B797" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C797" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D797" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E797" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F797">
-        <v>0</v>
-      </c>
-      <c r="G797" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H797" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I797" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J797" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K797">
-        <v>1</v>
-      </c>
-      <c r="L797" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M797" t="str">
-        <v>2026-07-01 19:42:39</v>
-      </c>
-      <c r="N797" s="1">
-        <v>310000</v>
-      </c>
-      <c r="O797" s="1">
-        <v>0</v>
-      </c>
-      <c r="P797" t="str">
-        <v/>
-      </c>
-      <c r="Q797" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R797" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="798">
-      <c r="A798" t="str">
-        <v>T260701-00016</v>
-      </c>
-      <c r="B798" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C798" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D798" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E798" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F798">
-        <v>0</v>
-      </c>
-      <c r="G798" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H798" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I798" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J798" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K798">
-        <v>1</v>
-      </c>
-      <c r="L798" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M798" t="str">
-        <v>2026-07-01 19:42:17</v>
-      </c>
-      <c r="N798" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O798" s="1">
-        <v>0</v>
-      </c>
-      <c r="P798" t="str">
-        <v/>
-      </c>
-      <c r="Q798" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R798" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="799">
-      <c r="A799" t="str">
-        <v>T260701-00015</v>
-      </c>
-      <c r="B799" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C799" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D799" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E799" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F799">
-        <v>1</v>
-      </c>
-      <c r="G799" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H799" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I799" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J799" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K799">
-        <v>1</v>
-      </c>
-      <c r="L799" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M799" t="str">
-        <v>2026-07-01 19:42:02</v>
-      </c>
-      <c r="N799" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O799" s="1">
-        <v>0</v>
-      </c>
-      <c r="P799" t="str">
-        <v/>
-      </c>
-      <c r="Q799" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R799" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="800">
-      <c r="A800" t="str">
-        <v>T260701-00014</v>
-      </c>
-      <c r="B800" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C800" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D800" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E800" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F800">
-        <v>1</v>
-      </c>
-      <c r="G800" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H800" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I800" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J800" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K800">
-        <v>1</v>
-      </c>
-      <c r="L800" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M800" t="str">
-        <v>2026-07-01 19:41:41</v>
-      </c>
-      <c r="N800" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O800" s="1">
-        <v>0</v>
-      </c>
-      <c r="P800" t="str">
-        <v/>
-      </c>
-      <c r="Q800" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R800" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="801">
-      <c r="A801" t="str">
-        <v>T260701-00013</v>
-      </c>
-      <c r="B801" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C801" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D801" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E801" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F801">
-        <v>1</v>
-      </c>
-      <c r="G801" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H801" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I801" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J801" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K801">
-        <v>1</v>
-      </c>
-      <c r="L801" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M801" t="str">
-        <v>2026-07-01 19:41:08</v>
-      </c>
-      <c r="N801" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O801" s="1">
-        <v>0</v>
-      </c>
-      <c r="P801" t="str">
-        <v/>
-      </c>
-      <c r="Q801" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R801" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="802">
-      <c r="A802" t="str">
-        <v>T260701-00012</v>
-      </c>
-      <c r="B802" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C802" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D802" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E802" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F802">
-        <v>1</v>
-      </c>
-      <c r="G802" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H802" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I802" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J802" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K802">
-        <v>1</v>
-      </c>
-      <c r="L802" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M802" t="str">
-        <v>2026-07-01 19:40:45</v>
-      </c>
-      <c r="N802" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O802" s="1">
-        <v>0</v>
-      </c>
-      <c r="P802" t="str">
-        <v/>
-      </c>
-      <c r="Q802" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R802" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="803">
-      <c r="A803" t="str">
-        <v>T260701-00011</v>
-      </c>
-      <c r="B803" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C803" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D803" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E803" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F803">
-        <v>0</v>
-      </c>
-      <c r="G803" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H803" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I803" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J803" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K803">
-        <v>1</v>
-      </c>
-      <c r="L803" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M803" t="str">
-        <v>2026-07-01 19:40:21</v>
-      </c>
-      <c r="N803" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O803" s="1">
-        <v>0</v>
-      </c>
-      <c r="P803" t="str">
-        <v/>
-      </c>
-      <c r="Q803" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R803" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="804">
-      <c r="A804" t="str">
-        <v>T260701-00010</v>
-      </c>
-      <c r="B804" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C804" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D804" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E804" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F804">
-        <v>1</v>
-      </c>
-      <c r="G804" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H804" t="str">
-        <v>경산시 해오름길114-2 경산FDC</v>
-      </c>
-      <c r="I804" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J804" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K804">
-        <v>1</v>
-      </c>
-      <c r="L804" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M804" t="str">
-        <v>2026-07-01 19:40:04</v>
-      </c>
-      <c r="N804" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O804" s="1">
-        <v>0</v>
-      </c>
-      <c r="P804" t="str">
-        <v/>
-      </c>
-      <c r="Q804" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R804" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="805">
-      <c r="A805" t="str">
-        <v>T260701-00009</v>
-      </c>
-      <c r="B805" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C805" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D805" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E805" t="str">
-        <v>2026-07-01 17:30</v>
-      </c>
-      <c r="F805">
-        <v>0</v>
-      </c>
-      <c r="G805" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H805" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I805" t="str">
-        <v>2026-07-01 18:30</v>
-      </c>
-      <c r="J805" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K805">
-        <v>1</v>
-      </c>
-      <c r="L805" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M805" t="str">
-        <v>2026-07-01 19:31:35</v>
-      </c>
-      <c r="N805" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O805" s="1">
-        <v>0</v>
-      </c>
-      <c r="P805" t="str">
-        <v/>
-      </c>
-      <c r="Q805" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R805" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="806">
-      <c r="A806" t="str">
-        <v>T260701-00008</v>
-      </c>
-      <c r="B806" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C806" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D806" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E806" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="F806">
-        <v>0</v>
-      </c>
-      <c r="G806" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H806" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I806" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="J806" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K806">
-        <v>1</v>
-      </c>
-      <c r="L806" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M806" t="str">
-        <v>2026-07-01 19:31:02</v>
-      </c>
-      <c r="N806" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O806" s="1">
-        <v>0</v>
-      </c>
-      <c r="P806" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q806" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R806" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="807">
-      <c r="A807" t="str">
-        <v>T260701-00007</v>
-      </c>
-      <c r="B807" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C807" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D807" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E807" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F807">
-        <v>0</v>
-      </c>
-      <c r="G807" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H807" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I807" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="J807" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K807">
-        <v>1</v>
-      </c>
-      <c r="L807" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M807" t="str">
-        <v>2026-07-01 19:29:27</v>
-      </c>
-      <c r="N807" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O807" s="1">
-        <v>0</v>
-      </c>
-      <c r="P807" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q807" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R807" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="808">
-      <c r="A808" t="str">
-        <v>T260701-00006</v>
-      </c>
-      <c r="B808" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C808" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D808" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E808" t="str">
-        <v>2026-07-01 16:30</v>
-      </c>
-      <c r="F808">
-        <v>0</v>
-      </c>
-      <c r="G808" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H808" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I808" t="str">
-        <v>2026-07-01 18:00</v>
-      </c>
-      <c r="J808" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K808">
-        <v>1</v>
-      </c>
-      <c r="L808" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M808" t="str">
-        <v>2026-07-01 16:09:24</v>
-      </c>
-      <c r="N808" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O808" s="1">
-        <v>0</v>
-      </c>
-      <c r="P808" t="str">
-        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q808" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R808" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="809">
-      <c r="A809" t="str">
-        <v>T260701-00005</v>
-      </c>
-      <c r="B809" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C809" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D809" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E809" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="F809">
-        <v>0</v>
-      </c>
-      <c r="G809" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H809" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I809" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J809" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K809">
-        <v>1</v>
-      </c>
-      <c r="L809" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M809" t="str">
-        <v>2026-07-01 14:58:37</v>
-      </c>
-      <c r="N809" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O809" s="1">
-        <v>0</v>
-      </c>
-      <c r="P809" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q809" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R809" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="810">
-      <c r="A810" t="str">
-        <v>T260701-00004</v>
-      </c>
-      <c r="B810" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C810" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D810" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E810" t="str">
-        <v>2026-07-01 15:20</v>
-      </c>
-      <c r="F810">
-        <v>0</v>
-      </c>
-      <c r="G810" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H810" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I810" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J810" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K810">
-        <v>1</v>
-      </c>
-      <c r="L810" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M810" t="str">
-        <v>2026-07-01 14:53:20</v>
-      </c>
-      <c r="N810" s="1">
-        <v>440000</v>
-      </c>
-      <c r="O810" s="1">
-        <v>0</v>
-      </c>
-      <c r="P810" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q810" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R810" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="811">
-      <c r="A811" t="str">
-        <v>T260701-00003</v>
-      </c>
-      <c r="B811" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C811" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D811" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E811" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F811">
-        <v>0</v>
-      </c>
-      <c r="G811" t="str">
-        <v>하이얼(이천다코넷)</v>
-      </c>
-      <c r="H811" t="str">
-        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
-      </c>
-      <c r="I811" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J811" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K811">
-        <v>1</v>
-      </c>
-      <c r="L811" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M811" t="str">
-        <v>2026-07-01 10:15:38</v>
-      </c>
-      <c r="N811" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O811" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P811" t="str">
-        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
-      </c>
-      <c r="Q811" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R811" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="812">
-      <c r="A812" t="str">
-        <v>T260701-00002</v>
-      </c>
-      <c r="B812" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C812" t="str">
-        <v>청주ARC(디지탈태양)</v>
-      </c>
-      <c r="D812" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
-      </c>
-      <c r="E812" t="str">
-        <v>2026-07-01 08:30</v>
-      </c>
-      <c r="F812">
-        <v>0</v>
-      </c>
-      <c r="G812" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H812" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="I812" t="str">
-        <v>2026-07-01 10:30</v>
-      </c>
-      <c r="J812" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K812">
-        <v>1</v>
-      </c>
-      <c r="L812" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M812" t="str">
-        <v>2026-07-01 10:13:39</v>
-      </c>
-      <c r="N812" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O812" s="1">
-        <v>0</v>
-      </c>
-      <c r="P812" t="str">
-        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
-      </c>
-      <c r="Q812" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R812" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="813">
-      <c r="A813" t="str">
-        <v>T260701-00001</v>
-      </c>
-      <c r="B813" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C813" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D813" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E813" t="str">
-        <v>2026-07-01 09:00</v>
-      </c>
-      <c r="F813">
-        <v>0</v>
-      </c>
-      <c r="G813" t="str">
-        <v>현대클러스터 한강미사3차</v>
-      </c>
-      <c r="H813" t="str">
-        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
-      </c>
-      <c r="I813" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J813" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K813">
-        <v>1</v>
-      </c>
-      <c r="L813" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M813" t="str">
-        <v>2026-07-01 09:07:09</v>
-      </c>
-      <c r="N813" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O813" s="1">
-        <v>0</v>
-      </c>
-      <c r="P813" t="str">
-        <v>스마트윈드 출하</v>
-      </c>
-      <c r="Q813" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R813" t="str">
-        <v>스마트윈드</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R813"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R726"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R726"/>
+  <dimension ref="A1:R813"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -41036,9 +41036,4881 @@
         <v>세상담기</v>
       </c>
     </row>
+    <row r="727">
+      <c r="A727" t="str">
+        <v>T260703-00034</v>
+      </c>
+      <c r="B727" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C727" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D727" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E727" t="str">
+        <v>2026-07-03 19:01</v>
+      </c>
+      <c r="F727">
+        <v>0</v>
+      </c>
+      <c r="G727" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H727" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I727" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J727" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K727">
+        <v>1</v>
+      </c>
+      <c r="L727" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M727" t="str">
+        <v>2026-07-03 20:43:25</v>
+      </c>
+      <c r="N727" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O727" s="1">
+        <v>0</v>
+      </c>
+      <c r="P727" t="str">
+        <v/>
+      </c>
+      <c r="Q727" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R727" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="str">
+        <v>T260703-00033</v>
+      </c>
+      <c r="B728" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C728" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D728" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E728" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F728">
+        <v>1</v>
+      </c>
+      <c r="G728" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H728" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I728" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J728" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K728">
+        <v>1</v>
+      </c>
+      <c r="L728" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M728" t="str">
+        <v>2026-07-03 20:42:58</v>
+      </c>
+      <c r="N728" s="1">
+        <v>170000</v>
+      </c>
+      <c r="O728" s="1">
+        <v>0</v>
+      </c>
+      <c r="P728" t="str">
+        <v/>
+      </c>
+      <c r="Q728" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R728" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="str">
+        <v>T260703-00032</v>
+      </c>
+      <c r="B729" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C729" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D729" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E729" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F729">
+        <v>1</v>
+      </c>
+      <c r="G729" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H729" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I729" t="str">
+        <v>2026-07-04 08:00</v>
+      </c>
+      <c r="J729" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K729">
+        <v>1</v>
+      </c>
+      <c r="L729" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M729" t="str">
+        <v>2026-07-03 20:42:34</v>
+      </c>
+      <c r="N729" s="1">
+        <v>170000</v>
+      </c>
+      <c r="O729" s="1">
+        <v>0</v>
+      </c>
+      <c r="P729" t="str">
+        <v/>
+      </c>
+      <c r="Q729" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R729" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="str">
+        <v>T260703-00031</v>
+      </c>
+      <c r="B730" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C730" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D730" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E730" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F730">
+        <v>0</v>
+      </c>
+      <c r="G730" t="str">
+        <v>시흥ACP</v>
+      </c>
+      <c r="H730" t="str">
+        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
+      </c>
+      <c r="I730" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J730" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K730">
+        <v>1</v>
+      </c>
+      <c r="L730" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M730" t="str">
+        <v>2026-07-03 20:41:59</v>
+      </c>
+      <c r="N730" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O730" s="1">
+        <v>0</v>
+      </c>
+      <c r="P730" t="str">
+        <v/>
+      </c>
+      <c r="Q730" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R730" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="str">
+        <v>T260703-00030</v>
+      </c>
+      <c r="B731" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C731" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D731" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E731" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F731">
+        <v>3</v>
+      </c>
+      <c r="G731" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H731" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I731" t="str">
+        <v>2026-07-04 08:00</v>
+      </c>
+      <c r="J731" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K731">
+        <v>1</v>
+      </c>
+      <c r="L731" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M731" t="str">
+        <v>2026-07-03 20:41:34</v>
+      </c>
+      <c r="N731" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O731" s="1">
+        <v>0</v>
+      </c>
+      <c r="P731" t="str">
+        <v/>
+      </c>
+      <c r="Q731" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R731" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="str">
+        <v>T260703-00029</v>
+      </c>
+      <c r="B732" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C732" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D732" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E732" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F732">
+        <v>0</v>
+      </c>
+      <c r="G732" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H732" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I732" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J732" t="str">
+        <v>1톤 기타차량</v>
+      </c>
+      <c r="K732">
+        <v>1</v>
+      </c>
+      <c r="L732" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M732" t="str">
+        <v>2026-07-03 20:40:56</v>
+      </c>
+      <c r="N732" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O732" s="1">
+        <v>0</v>
+      </c>
+      <c r="P732" t="str">
+        <v/>
+      </c>
+      <c r="Q732" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R732" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="str">
+        <v>T260703-00028</v>
+      </c>
+      <c r="B733" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C733" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D733" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E733" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F733">
+        <v>0</v>
+      </c>
+      <c r="G733" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H733" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I733" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J733" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K733">
+        <v>1</v>
+      </c>
+      <c r="L733" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M733" t="str">
+        <v>2026-07-03 20:40:32</v>
+      </c>
+      <c r="N733" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O733" s="1">
+        <v>0</v>
+      </c>
+      <c r="P733" t="str">
+        <v/>
+      </c>
+      <c r="Q733" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R733" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="str">
+        <v>T260703-00027</v>
+      </c>
+      <c r="B734" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C734" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D734" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E734" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F734">
+        <v>3</v>
+      </c>
+      <c r="G734" t="str">
+        <v>인제ACP</v>
+      </c>
+      <c r="H734" t="str">
+        <v>강원특별자치도 속초시 만천6길 13 인제ACP</v>
+      </c>
+      <c r="I734" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J734" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K734">
+        <v>1</v>
+      </c>
+      <c r="L734" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M734" t="str">
+        <v>2026-07-03 20:40:07</v>
+      </c>
+      <c r="N734" s="1">
+        <v>390000</v>
+      </c>
+      <c r="O734" s="1">
+        <v>0</v>
+      </c>
+      <c r="P734" t="str">
+        <v/>
+      </c>
+      <c r="Q734" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R734" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="str">
+        <v>T260703-00026</v>
+      </c>
+      <c r="B735" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C735" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D735" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E735" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F735">
+        <v>0</v>
+      </c>
+      <c r="G735" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H735" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I735" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J735" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K735">
+        <v>1</v>
+      </c>
+      <c r="L735" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M735" t="str">
+        <v>2026-07-03 20:39:21</v>
+      </c>
+      <c r="N735" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O735" s="1">
+        <v>0</v>
+      </c>
+      <c r="P735" t="str">
+        <v/>
+      </c>
+      <c r="Q735" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R735" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="str">
+        <v>T260703-00025</v>
+      </c>
+      <c r="B736" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C736" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D736" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E736" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F736">
+        <v>1</v>
+      </c>
+      <c r="G736" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H736" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I736" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J736" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K736">
+        <v>1</v>
+      </c>
+      <c r="L736" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M736" t="str">
+        <v>2026-07-03 20:39:06</v>
+      </c>
+      <c r="N736" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O736" s="1">
+        <v>0</v>
+      </c>
+      <c r="P736" t="str">
+        <v/>
+      </c>
+      <c r="Q736" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R736" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="str">
+        <v>T260703-00024</v>
+      </c>
+      <c r="B737" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C737" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D737" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E737" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F737">
+        <v>1</v>
+      </c>
+      <c r="G737" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H737" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I737" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J737" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K737">
+        <v>1</v>
+      </c>
+      <c r="L737" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M737" t="str">
+        <v>2026-07-03 20:38:48</v>
+      </c>
+      <c r="N737" s="1">
+        <v>530000</v>
+      </c>
+      <c r="O737" s="1">
+        <v>0</v>
+      </c>
+      <c r="P737" t="str">
+        <v/>
+      </c>
+      <c r="Q737" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R737" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="str">
+        <v>T260703-00023</v>
+      </c>
+      <c r="B738" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C738" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D738" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E738" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F738">
+        <v>0</v>
+      </c>
+      <c r="G738" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H738" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I738" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J738" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K738">
+        <v>1</v>
+      </c>
+      <c r="L738" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M738" t="str">
+        <v>2026-07-03 20:38:28</v>
+      </c>
+      <c r="N738" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O738" s="1">
+        <v>0</v>
+      </c>
+      <c r="P738" t="str">
+        <v/>
+      </c>
+      <c r="Q738" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R738" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="str">
+        <v>T260703-00022</v>
+      </c>
+      <c r="B739" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C739" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D739" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E739" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F739">
+        <v>0</v>
+      </c>
+      <c r="G739" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H739" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I739" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J739" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K739">
+        <v>1</v>
+      </c>
+      <c r="L739" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M739" t="str">
+        <v>2026-07-03 20:38:14</v>
+      </c>
+      <c r="N739" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O739" s="1">
+        <v>0</v>
+      </c>
+      <c r="P739" t="str">
+        <v/>
+      </c>
+      <c r="Q739" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R739" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="str">
+        <v>T260703-00021</v>
+      </c>
+      <c r="B740" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C740" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D740" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E740" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F740">
+        <v>1</v>
+      </c>
+      <c r="G740" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H740" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I740" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J740" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K740">
+        <v>1</v>
+      </c>
+      <c r="L740" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M740" t="str">
+        <v>2026-07-03 20:37:59</v>
+      </c>
+      <c r="N740" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O740" s="1">
+        <v>0</v>
+      </c>
+      <c r="P740" t="str">
+        <v/>
+      </c>
+      <c r="Q740" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R740" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="str">
+        <v>T260703-00020</v>
+      </c>
+      <c r="B741" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C741" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D741" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E741" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F741">
+        <v>0</v>
+      </c>
+      <c r="G741" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H741" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I741" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J741" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K741">
+        <v>1</v>
+      </c>
+      <c r="L741" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M741" t="str">
+        <v>2026-07-03 20:37:40</v>
+      </c>
+      <c r="N741" s="1">
+        <v>490000</v>
+      </c>
+      <c r="O741" s="1">
+        <v>0</v>
+      </c>
+      <c r="P741" t="str">
+        <v/>
+      </c>
+      <c r="Q741" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R741" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="str">
+        <v>T260703-00019</v>
+      </c>
+      <c r="B742" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C742" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D742" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E742" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F742">
+        <v>0</v>
+      </c>
+      <c r="G742" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H742" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I742" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J742" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K742">
+        <v>1</v>
+      </c>
+      <c r="L742" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M742" t="str">
+        <v>2026-07-03 20:37:26</v>
+      </c>
+      <c r="N742" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O742" s="1">
+        <v>0</v>
+      </c>
+      <c r="P742" t="str">
+        <v/>
+      </c>
+      <c r="Q742" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R742" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="str">
+        <v>T260703-00018</v>
+      </c>
+      <c r="B743" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C743" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D743" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E743" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F743">
+        <v>0</v>
+      </c>
+      <c r="G743" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H743" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I743" t="str">
+        <v>2026-07-03 20:00</v>
+      </c>
+      <c r="J743" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K743">
+        <v>1</v>
+      </c>
+      <c r="L743" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M743" t="str">
+        <v>2026-07-03 20:37:11</v>
+      </c>
+      <c r="N743" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O743" s="1">
+        <v>0</v>
+      </c>
+      <c r="P743" t="str">
+        <v/>
+      </c>
+      <c r="Q743" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R743" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="str">
+        <v>T260703-00017</v>
+      </c>
+      <c r="B744" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C744" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D744" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E744" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F744">
+        <v>0</v>
+      </c>
+      <c r="G744" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H744" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I744" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J744" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K744">
+        <v>1</v>
+      </c>
+      <c r="L744" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M744" t="str">
+        <v>2026-07-03 20:36:55</v>
+      </c>
+      <c r="N744" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O744" s="1">
+        <v>0</v>
+      </c>
+      <c r="P744" t="str">
+        <v/>
+      </c>
+      <c r="Q744" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R744" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="str">
+        <v>T260703-00016</v>
+      </c>
+      <c r="B745" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C745" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D745" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E745" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F745">
+        <v>0</v>
+      </c>
+      <c r="G745" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H745" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I745" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J745" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K745">
+        <v>1</v>
+      </c>
+      <c r="L745" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M745" t="str">
+        <v>2026-07-03 20:36:37</v>
+      </c>
+      <c r="N745" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O745" s="1">
+        <v>0</v>
+      </c>
+      <c r="P745" t="str">
+        <v/>
+      </c>
+      <c r="Q745" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R745" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="str">
+        <v>T260703-00015</v>
+      </c>
+      <c r="B746" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C746" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D746" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E746" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F746">
+        <v>0</v>
+      </c>
+      <c r="G746" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H746" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I746" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J746" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K746">
+        <v>1</v>
+      </c>
+      <c r="L746" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M746" t="str">
+        <v>2026-07-03 20:36:15</v>
+      </c>
+      <c r="N746" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O746" s="1">
+        <v>0</v>
+      </c>
+      <c r="P746" t="str">
+        <v/>
+      </c>
+      <c r="Q746" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R746" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="str">
+        <v>T260703-00014</v>
+      </c>
+      <c r="B747" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C747" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D747" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E747" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F747">
+        <v>1</v>
+      </c>
+      <c r="G747" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H747" t="str">
+        <v>경산시 해오름길114-2 경산FDC</v>
+      </c>
+      <c r="I747" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J747" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K747">
+        <v>1</v>
+      </c>
+      <c r="L747" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M747" t="str">
+        <v>2026-07-03 20:35:55</v>
+      </c>
+      <c r="N747" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O747" s="1">
+        <v>0</v>
+      </c>
+      <c r="P747" t="str">
+        <v/>
+      </c>
+      <c r="Q747" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R747" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="str">
+        <v>T260703-00013</v>
+      </c>
+      <c r="B748" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C748" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D748" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E748" t="str">
+        <v>2026-07-03 17:30</v>
+      </c>
+      <c r="F748">
+        <v>0</v>
+      </c>
+      <c r="G748" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H748" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I748" t="str">
+        <v>2026-07-03 18:30</v>
+      </c>
+      <c r="J748" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K748">
+        <v>1</v>
+      </c>
+      <c r="L748" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M748" t="str">
+        <v>2026-07-03 20:31:55</v>
+      </c>
+      <c r="N748" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O748" s="1">
+        <v>0</v>
+      </c>
+      <c r="P748" t="str">
+        <v/>
+      </c>
+      <c r="Q748" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R748" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="str">
+        <v>T260703-00012</v>
+      </c>
+      <c r="B749" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C749" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="D749" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="E749" t="str">
+        <v>2026-07-03 08:30</v>
+      </c>
+      <c r="F749">
+        <v>0</v>
+      </c>
+      <c r="G749" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="H749" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="I749" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="J749" t="str">
+        <v>3.5톤 카고</v>
+      </c>
+      <c r="K749">
+        <v>1</v>
+      </c>
+      <c r="L749" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M749" t="str">
+        <v>2026-07-03 20:31:21</v>
+      </c>
+      <c r="N749" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O749" s="1">
+        <v>0</v>
+      </c>
+      <c r="P749" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="Q749" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R749" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="str">
+        <v>T260703-00011</v>
+      </c>
+      <c r="B750" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C750" t="str">
+        <v>샤오미</v>
+      </c>
+      <c r="D750" t="str">
+        <v>경기 이천시 대월면 부필리 309 샤오미</v>
+      </c>
+      <c r="E750" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="F750">
+        <v>0</v>
+      </c>
+      <c r="G750" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H750" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I750" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="J750" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K750">
+        <v>1</v>
+      </c>
+      <c r="L750" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M750" t="str">
+        <v>2026-07-03 20:30:39</v>
+      </c>
+      <c r="N750" s="1">
+        <v>80000</v>
+      </c>
+      <c r="O750" s="1">
+        <v>0</v>
+      </c>
+      <c r="P750" t="str">
+        <v>거래처비용청구(1대)</v>
+      </c>
+      <c r="Q750" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R750" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="str">
+        <v>T260703-00010</v>
+      </c>
+      <c r="B751" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C751" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D751" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E751" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="F751">
+        <v>0</v>
+      </c>
+      <c r="G751" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H751" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I751" t="str">
+        <v>2026-07-03 15:30</v>
+      </c>
+      <c r="J751" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K751">
+        <v>1</v>
+      </c>
+      <c r="L751" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M751" t="str">
+        <v>2026-07-03 20:29:47</v>
+      </c>
+      <c r="N751" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O751" s="1">
+        <v>0</v>
+      </c>
+      <c r="P751" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q751" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R751" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="str">
+        <v>T260703-00009</v>
+      </c>
+      <c r="B752" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C752" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D752" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E752" t="str">
+        <v>2026-07-03 10:00</v>
+      </c>
+      <c r="F752">
+        <v>0</v>
+      </c>
+      <c r="G752" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H752" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I752" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="J752" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K752">
+        <v>1</v>
+      </c>
+      <c r="L752" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M752" t="str">
+        <v>2026-07-03 20:29:05</v>
+      </c>
+      <c r="N752" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O752" s="1">
+        <v>0</v>
+      </c>
+      <c r="P752" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q752" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R752" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="str">
+        <v>T260703-00008</v>
+      </c>
+      <c r="B753" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C753" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D753" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E753" t="str">
+        <v>2026-07-03 16:30</v>
+      </c>
+      <c r="F753">
+        <v>0</v>
+      </c>
+      <c r="G753" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H753" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I753" t="str">
+        <v>2026-07-03 18:00</v>
+      </c>
+      <c r="J753" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K753">
+        <v>1</v>
+      </c>
+      <c r="L753" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M753" t="str">
+        <v>2026-07-03 18:39:34</v>
+      </c>
+      <c r="N753" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O753" s="1">
+        <v>0</v>
+      </c>
+      <c r="P753" t="str">
+        <v>20260703/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q753" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R753" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="str">
+        <v>T260703-00007</v>
+      </c>
+      <c r="B754" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C754" t="str">
+        <v>청주ARC(공파렛트 이동)</v>
+      </c>
+      <c r="D754" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(공파렛트 이동)</v>
+      </c>
+      <c r="E754" t="str">
+        <v>2026-07-03 11:40</v>
+      </c>
+      <c r="F754">
+        <v>0</v>
+      </c>
+      <c r="G754" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H754" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="I754" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="J754" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K754">
+        <v>1</v>
+      </c>
+      <c r="L754" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M754" t="str">
+        <v>2026-07-03 11:28:01</v>
+      </c>
+      <c r="N754" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O754" s="1">
+        <v>0</v>
+      </c>
+      <c r="P754" t="str">
+        <v>20260703청주-&gt; 안성FC/공파렛트이동</v>
+      </c>
+      <c r="Q754" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R754" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="str">
+        <v>T260703-00006</v>
+      </c>
+      <c r="B755" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C755" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D755" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E755" t="str">
+        <v>2026-07-03 11:55</v>
+      </c>
+      <c r="F755">
+        <v>0</v>
+      </c>
+      <c r="G755" t="str">
+        <v>하이얼(서울 벌크 출하)</v>
+      </c>
+      <c r="H755" t="str">
+        <v>서울 강남구 선릉로92길 38 도파민</v>
+      </c>
+      <c r="I755" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="J755" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K755">
+        <v>1</v>
+      </c>
+      <c r="L755" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M755" t="str">
+        <v>2026-07-03 11:26:22</v>
+      </c>
+      <c r="N755" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O755" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P755" t="str">
+        <v>20260703/하이얼_서울_벌크_출하</v>
+      </c>
+      <c r="Q755" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R755" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="str">
+        <v>T260703-00005</v>
+      </c>
+      <c r="B756" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C756" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D756" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E756" t="str">
+        <v>2026-07-03 11:00</v>
+      </c>
+      <c r="F756">
+        <v>0</v>
+      </c>
+      <c r="G756" t="str">
+        <v>파주 하이마트 물류</v>
+      </c>
+      <c r="H756" t="str">
+        <v>경기 파주시 탄현면 월롱산로 296 파주 하이마트 물류</v>
+      </c>
+      <c r="I756" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J756" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K756">
+        <v>1</v>
+      </c>
+      <c r="L756" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M756" t="str">
+        <v>2026-07-03 11:22:28</v>
+      </c>
+      <c r="N756" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O756" s="1">
+        <v>0</v>
+      </c>
+      <c r="P756" t="str">
+        <v>일코전자 파주 하이마트 물류</v>
+      </c>
+      <c r="Q756" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R756" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="str">
+        <v>T260703-00004</v>
+      </c>
+      <c r="B757" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C757" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D757" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지  안성FC</v>
+      </c>
+      <c r="E757" t="str">
+        <v>2026-07-03 09:30</v>
+      </c>
+      <c r="F757">
+        <v>0</v>
+      </c>
+      <c r="G757" t="str">
+        <v>TCL다코넷</v>
+      </c>
+      <c r="H757" t="str">
+        <v>경기 평택시 포승읍 희곡리 847 평택 켄달스퀘어 3층, 다코넷 37번 도크</v>
+      </c>
+      <c r="I757" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="J757" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K757">
+        <v>1</v>
+      </c>
+      <c r="L757" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M757" t="str">
+        <v>2026-07-03 11:21:17</v>
+      </c>
+      <c r="N757" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O757" s="1">
+        <v>0</v>
+      </c>
+      <c r="P757" t="str">
+        <v>TCL 다코넷</v>
+      </c>
+      <c r="Q757" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R757" t="str">
+        <v>TCL</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="str">
+        <v>T260703-00003</v>
+      </c>
+      <c r="B758" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C758" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D758" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E758" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="F758">
+        <v>0</v>
+      </c>
+      <c r="G758" t="str">
+        <v>이천 하이마트 물류</v>
+      </c>
+      <c r="H758" t="str">
+        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 물류</v>
+      </c>
+      <c r="I758" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J758" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K758">
+        <v>1</v>
+      </c>
+      <c r="L758" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M758" t="str">
+        <v>2026-07-03 11:19:40</v>
+      </c>
+      <c r="N758" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O758" s="1">
+        <v>0</v>
+      </c>
+      <c r="P758" t="str">
+        <v>일코전자 이천 하이마트 물류</v>
+      </c>
+      <c r="Q758" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R758" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="str">
+        <v>T260703-00002</v>
+      </c>
+      <c r="B759" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C759" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D759" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E759" t="str">
+        <v>2026-07-03 10:00</v>
+      </c>
+      <c r="F759">
+        <v>0</v>
+      </c>
+      <c r="G759" t="str">
+        <v>화성 하이마트 물류</v>
+      </c>
+      <c r="H759" t="str">
+        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 물류</v>
+      </c>
+      <c r="I759" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J759" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K759">
+        <v>1</v>
+      </c>
+      <c r="L759" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M759" t="str">
+        <v>2026-07-03 11:18:03</v>
+      </c>
+      <c r="N759" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O759" s="1">
+        <v>0</v>
+      </c>
+      <c r="P759" t="str">
+        <v>일코전자 화성 하이마트 물류</v>
+      </c>
+      <c r="Q759" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R759" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="str">
+        <v>T260703-00001</v>
+      </c>
+      <c r="B760" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C760" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D760" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E760" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="F760">
+        <v>0</v>
+      </c>
+      <c r="G760" t="str">
+        <v>인천 하이마트 물류</v>
+      </c>
+      <c r="H760" t="str">
+        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
+      </c>
+      <c r="I760" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J760" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K760">
+        <v>1</v>
+      </c>
+      <c r="L760" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M760" t="str">
+        <v>2026-07-03 11:16:52</v>
+      </c>
+      <c r="N760" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O760" s="1">
+        <v>0</v>
+      </c>
+      <c r="P760" t="str">
+        <v>일코전자 인천 하이마트 물류</v>
+      </c>
+      <c r="Q760" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R760" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="str">
+        <v>T260702-00027</v>
+      </c>
+      <c r="B761" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C761" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D761" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E761" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F761">
+        <v>1</v>
+      </c>
+      <c r="G761" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H761" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I761" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J761" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K761">
+        <v>1</v>
+      </c>
+      <c r="L761" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M761" t="str">
+        <v>2026-07-02 20:54:21</v>
+      </c>
+      <c r="N761" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O761" s="1">
+        <v>0</v>
+      </c>
+      <c r="P761" t="str">
+        <v/>
+      </c>
+      <c r="Q761" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R761" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="str">
+        <v>T260702-00026</v>
+      </c>
+      <c r="B762" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C762" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D762" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E762" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F762">
+        <v>1</v>
+      </c>
+      <c r="G762" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H762" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I762" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J762" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K762">
+        <v>1</v>
+      </c>
+      <c r="L762" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M762" t="str">
+        <v>2026-07-02 20:53:56</v>
+      </c>
+      <c r="N762" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O762" s="1">
+        <v>0</v>
+      </c>
+      <c r="P762" t="str">
+        <v/>
+      </c>
+      <c r="Q762" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R762" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="str">
+        <v>T260702-00025</v>
+      </c>
+      <c r="B763" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C763" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D763" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E763" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F763">
+        <v>3</v>
+      </c>
+      <c r="G763" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H763" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I763" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J763" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K763">
+        <v>1</v>
+      </c>
+      <c r="L763" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M763" t="str">
+        <v>2026-07-02 20:53:28</v>
+      </c>
+      <c r="N763" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O763" s="1">
+        <v>0</v>
+      </c>
+      <c r="P763" t="str">
+        <v/>
+      </c>
+      <c r="Q763" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R763" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="str">
+        <v>T260702-00024</v>
+      </c>
+      <c r="B764" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C764" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D764" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E764" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F764">
+        <v>0</v>
+      </c>
+      <c r="G764" t="str">
+        <v>용인ACP</v>
+      </c>
+      <c r="H764" t="str">
+        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
+      </c>
+      <c r="I764" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J764" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K764">
+        <v>1</v>
+      </c>
+      <c r="L764" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M764" t="str">
+        <v>2026-07-02 20:52:18</v>
+      </c>
+      <c r="N764" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O764" s="1">
+        <v>0</v>
+      </c>
+      <c r="P764" t="str">
+        <v/>
+      </c>
+      <c r="Q764" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R764" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="str">
+        <v>T260702-00023</v>
+      </c>
+      <c r="B765" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C765" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D765" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E765" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F765">
+        <v>1</v>
+      </c>
+      <c r="G765" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H765" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I765" t="str">
+        <v>2026-07-03 07:00</v>
+      </c>
+      <c r="J765" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K765">
+        <v>1</v>
+      </c>
+      <c r="L765" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M765" t="str">
+        <v>2026-07-02 20:51:59</v>
+      </c>
+      <c r="N765" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O765" s="1">
+        <v>0</v>
+      </c>
+      <c r="P765" t="str">
+        <v/>
+      </c>
+      <c r="Q765" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R765" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="str">
+        <v>T260702-00022</v>
+      </c>
+      <c r="B766" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C766" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D766" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E766" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F766">
+        <v>0</v>
+      </c>
+      <c r="G766" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H766" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I766" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J766" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K766">
+        <v>1</v>
+      </c>
+      <c r="L766" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M766" t="str">
+        <v>2026-07-02 20:51:32</v>
+      </c>
+      <c r="N766" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O766" s="1">
+        <v>0</v>
+      </c>
+      <c r="P766" t="str">
+        <v/>
+      </c>
+      <c r="Q766" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R766" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="str">
+        <v>T260702-00021</v>
+      </c>
+      <c r="B767" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C767" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D767" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E767" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F767">
+        <v>1</v>
+      </c>
+      <c r="G767" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H767" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I767" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J767" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K767">
+        <v>1</v>
+      </c>
+      <c r="L767" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M767" t="str">
+        <v>2026-07-02 20:51:14</v>
+      </c>
+      <c r="N767" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O767" s="1">
+        <v>0</v>
+      </c>
+      <c r="P767" t="str">
+        <v/>
+      </c>
+      <c r="Q767" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R767" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="str">
+        <v>T260702-00020</v>
+      </c>
+      <c r="B768" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C768" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D768" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E768" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F768">
+        <v>0</v>
+      </c>
+      <c r="G768" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H768" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I768" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J768" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K768">
+        <v>1</v>
+      </c>
+      <c r="L768" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M768" t="str">
+        <v>2026-07-02 20:50:54</v>
+      </c>
+      <c r="N768" s="1">
+        <v>280000</v>
+      </c>
+      <c r="O768" s="1">
+        <v>0</v>
+      </c>
+      <c r="P768" t="str">
+        <v/>
+      </c>
+      <c r="Q768" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R768" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="str">
+        <v>T260702-00019</v>
+      </c>
+      <c r="B769" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C769" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D769" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E769" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F769">
+        <v>0</v>
+      </c>
+      <c r="G769" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H769" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I769" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J769" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K769">
+        <v>1</v>
+      </c>
+      <c r="L769" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M769" t="str">
+        <v>2026-07-02 20:50:36</v>
+      </c>
+      <c r="N769" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O769" s="1">
+        <v>0</v>
+      </c>
+      <c r="P769" t="str">
+        <v/>
+      </c>
+      <c r="Q769" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R769" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="str">
+        <v>T260702-00018</v>
+      </c>
+      <c r="B770" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C770" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D770" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E770" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F770">
+        <v>1</v>
+      </c>
+      <c r="G770" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H770" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I770" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J770" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K770">
+        <v>1</v>
+      </c>
+      <c r="L770" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M770" t="str">
+        <v>2026-07-02 20:50:19</v>
+      </c>
+      <c r="N770" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O770" s="1">
+        <v>0</v>
+      </c>
+      <c r="P770" t="str">
+        <v/>
+      </c>
+      <c r="Q770" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R770" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="str">
+        <v>T260702-00017</v>
+      </c>
+      <c r="B771" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C771" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D771" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E771" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F771">
+        <v>1</v>
+      </c>
+      <c r="G771" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H771" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I771" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J771" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K771">
+        <v>1</v>
+      </c>
+      <c r="L771" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M771" t="str">
+        <v>2026-07-02 20:49:56</v>
+      </c>
+      <c r="N771" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O771" s="1">
+        <v>0</v>
+      </c>
+      <c r="P771" t="str">
+        <v/>
+      </c>
+      <c r="Q771" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R771" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="str">
+        <v>T260702-00016</v>
+      </c>
+      <c r="B772" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C772" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D772" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E772" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F772">
+        <v>0</v>
+      </c>
+      <c r="G772" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H772" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I772" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J772" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K772">
+        <v>1</v>
+      </c>
+      <c r="L772" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M772" t="str">
+        <v>2026-07-02 20:49:25</v>
+      </c>
+      <c r="N772" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O772" s="1">
+        <v>0</v>
+      </c>
+      <c r="P772" t="str">
+        <v/>
+      </c>
+      <c r="Q772" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R772" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="str">
+        <v>T260702-00015</v>
+      </c>
+      <c r="B773" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C773" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D773" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E773" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F773">
+        <v>1</v>
+      </c>
+      <c r="G773" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H773" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I773" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J773" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K773">
+        <v>1</v>
+      </c>
+      <c r="L773" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M773" t="str">
+        <v>2026-07-02 20:48:50</v>
+      </c>
+      <c r="N773" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O773" s="1">
+        <v>0</v>
+      </c>
+      <c r="P773" t="str">
+        <v/>
+      </c>
+      <c r="Q773" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R773" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="str">
+        <v>T260702-00014</v>
+      </c>
+      <c r="B774" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C774" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D774" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E774" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F774">
+        <v>0</v>
+      </c>
+      <c r="G774" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H774" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I774" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J774" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K774">
+        <v>1</v>
+      </c>
+      <c r="L774" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M774" t="str">
+        <v>2026-07-02 20:48:25</v>
+      </c>
+      <c r="N774" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O774" s="1">
+        <v>0</v>
+      </c>
+      <c r="P774" t="str">
+        <v/>
+      </c>
+      <c r="Q774" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R774" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="str">
+        <v>T260702-00013</v>
+      </c>
+      <c r="B775" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C775" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D775" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E775" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F775">
+        <v>0</v>
+      </c>
+      <c r="G775" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H775" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I775" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J775" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K775">
+        <v>1</v>
+      </c>
+      <c r="L775" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M775" t="str">
+        <v>2026-07-02 20:48:09</v>
+      </c>
+      <c r="N775" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O775" s="1">
+        <v>0</v>
+      </c>
+      <c r="P775" t="str">
+        <v/>
+      </c>
+      <c r="Q775" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R775" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="str">
+        <v>T260702-00012</v>
+      </c>
+      <c r="B776" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C776" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D776" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E776" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F776">
+        <v>2</v>
+      </c>
+      <c r="G776" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H776" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I776" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J776" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K776">
+        <v>1</v>
+      </c>
+      <c r="L776" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M776" t="str">
+        <v>2026-07-02 20:47:49</v>
+      </c>
+      <c r="N776" s="1">
+        <v>680000</v>
+      </c>
+      <c r="O776" s="1">
+        <v>0</v>
+      </c>
+      <c r="P776" t="str">
+        <v/>
+      </c>
+      <c r="Q776" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R776" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="str">
+        <v>T260702-00011</v>
+      </c>
+      <c r="B777" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C777" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D777" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E777" t="str">
+        <v>2026-07-02 17:50</v>
+      </c>
+      <c r="F777">
+        <v>0</v>
+      </c>
+      <c r="G777" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H777" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I777" t="str">
+        <v>2026-07-02 18:50</v>
+      </c>
+      <c r="J777" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K777">
+        <v>1</v>
+      </c>
+      <c r="L777" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M777" t="str">
+        <v>2026-07-02 20:44:59</v>
+      </c>
+      <c r="N777" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O777" s="1">
+        <v>0</v>
+      </c>
+      <c r="P777" t="str">
+        <v/>
+      </c>
+      <c r="Q777" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R777" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="str">
+        <v>T260702-00010</v>
+      </c>
+      <c r="B778" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C778" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D778" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E778" t="str">
+        <v>2026-07-02 13:30</v>
+      </c>
+      <c r="F778">
+        <v>0</v>
+      </c>
+      <c r="G778" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H778" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I778" t="str">
+        <v>2026-07-02 15:40</v>
+      </c>
+      <c r="J778" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K778">
+        <v>1</v>
+      </c>
+      <c r="L778" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M778" t="str">
+        <v>2026-07-02 20:44:26</v>
+      </c>
+      <c r="N778" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O778" s="1">
+        <v>0</v>
+      </c>
+      <c r="P778" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q778" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R778" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="str">
+        <v>T260702-00009</v>
+      </c>
+      <c r="B779" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C779" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D779" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E779" t="str">
+        <v>2026-07-02 10:00</v>
+      </c>
+      <c r="F779">
+        <v>0</v>
+      </c>
+      <c r="G779" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H779" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I779" t="str">
+        <v>2026-07-02 13:40</v>
+      </c>
+      <c r="J779" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K779">
+        <v>1</v>
+      </c>
+      <c r="L779" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M779" t="str">
+        <v>2026-07-02 20:43:37</v>
+      </c>
+      <c r="N779" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O779" s="1">
+        <v>0</v>
+      </c>
+      <c r="P779" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q779" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R779" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="str">
+        <v>T260702-00008</v>
+      </c>
+      <c r="B780" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C780" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D780" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E780" t="str">
+        <v>2026-07-02 17:00</v>
+      </c>
+      <c r="F780">
+        <v>0</v>
+      </c>
+      <c r="G780" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="H780" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="I780" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J780" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K780">
+        <v>1</v>
+      </c>
+      <c r="L780" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M780" t="str">
+        <v>2026-07-02 16:38:23</v>
+      </c>
+      <c r="N780" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O780" s="1">
+        <v>0</v>
+      </c>
+      <c r="P780" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="Q780" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R780" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="str">
+        <v>T260702-00007</v>
+      </c>
+      <c r="B781" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C781" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D781" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E781" t="str">
+        <v>2026-07-02 16:30</v>
+      </c>
+      <c r="F781">
+        <v>0</v>
+      </c>
+      <c r="G781" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H781" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I781" t="str">
+        <v>2026-07-02 18:00</v>
+      </c>
+      <c r="J781" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K781">
+        <v>1</v>
+      </c>
+      <c r="L781" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M781" t="str">
+        <v>2026-07-02 16:34:35</v>
+      </c>
+      <c r="N781" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O781" s="1">
+        <v>0</v>
+      </c>
+      <c r="P781" t="str">
+        <v>20260702/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q781" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R781" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="str">
+        <v>T260702-00006</v>
+      </c>
+      <c r="B782" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C782" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D782" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E782" t="str">
+        <v>2026-07-02 16:00</v>
+      </c>
+      <c r="F782">
+        <v>0</v>
+      </c>
+      <c r="G782" t="str">
+        <v>광주 하이마트 물류</v>
+      </c>
+      <c r="H782" t="str">
+        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
+      </c>
+      <c r="I782" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J782" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K782">
+        <v>1</v>
+      </c>
+      <c r="L782" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M782" t="str">
+        <v>2026-07-02 15:30:55</v>
+      </c>
+      <c r="N782" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O782" s="1">
+        <v>0</v>
+      </c>
+      <c r="P782" t="str">
+        <v>일코 광주 하이마트 물류</v>
+      </c>
+      <c r="Q782" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R782" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="str">
+        <v>T260702-00005</v>
+      </c>
+      <c r="B783" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C783" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D783" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E783" t="str">
+        <v>2026-07-02 14:30</v>
+      </c>
+      <c r="F783">
+        <v>0</v>
+      </c>
+      <c r="G783" t="str">
+        <v>마산 하이마트 물류</v>
+      </c>
+      <c r="H783" t="str">
+        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
+      </c>
+      <c r="I783" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J783" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K783">
+        <v>1</v>
+      </c>
+      <c r="L783" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M783" t="str">
+        <v>2026-07-02 13:44:41</v>
+      </c>
+      <c r="N783" s="1">
+        <v>380000</v>
+      </c>
+      <c r="O783" s="1">
+        <v>0</v>
+      </c>
+      <c r="P783" t="str">
+        <v>일코 마산 하이마트 물류</v>
+      </c>
+      <c r="Q783" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R783" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="str">
+        <v>T260702-00004</v>
+      </c>
+      <c r="B784" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C784" t="str">
+        <v>강릉 하이마트 물류</v>
+      </c>
+      <c r="D784" t="str">
+        <v>강원특별자치도 강릉시 연곡면 동해대로 4100-36 강릉 하이마트 물류</v>
+      </c>
+      <c r="E784" t="str">
+        <v>2026-07-02 13:30</v>
+      </c>
+      <c r="F784">
+        <v>0</v>
+      </c>
+      <c r="G784" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H784" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I784" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J784" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K784">
+        <v>1</v>
+      </c>
+      <c r="L784" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M784" t="str">
+        <v>2026-07-02 12:00:10</v>
+      </c>
+      <c r="N784" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O784" s="1">
+        <v>0</v>
+      </c>
+      <c r="P784" t="str">
+        <v>일코전자 강릉 하이마트 물류</v>
+      </c>
+      <c r="Q784" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R784" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="str">
+        <v>T260702-00003</v>
+      </c>
+      <c r="B785" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C785" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D785" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E785" t="str">
+        <v>2026-07-02 14:30</v>
+      </c>
+      <c r="F785">
+        <v>0</v>
+      </c>
+      <c r="G785" t="str">
+        <v>대구 하이마트 물류</v>
+      </c>
+      <c r="H785" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="I785" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J785" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K785">
+        <v>1</v>
+      </c>
+      <c r="L785" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M785" t="str">
+        <v>2026-07-02 11:59:32</v>
+      </c>
+      <c r="N785" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O785" s="1">
+        <v>0</v>
+      </c>
+      <c r="P785" t="str">
+        <v>일코전자 대구 하이마트 물류</v>
+      </c>
+      <c r="Q785" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R785" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="str">
+        <v>T260702-00002</v>
+      </c>
+      <c r="B786" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C786" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D786" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E786" t="str">
+        <v>2026-07-02 09:30</v>
+      </c>
+      <c r="F786">
+        <v>1</v>
+      </c>
+      <c r="G786" t="str">
+        <v>하이얼(대구2착)</v>
+      </c>
+      <c r="H786" t="str">
+        <v>대구 남구 양지로 25 대명자이 아파트</v>
+      </c>
+      <c r="I786" t="str">
+        <v>2026-07-02 15:00</v>
+      </c>
+      <c r="J786" t="str">
+        <v>1.5톤 윙바디</v>
+      </c>
+      <c r="K786">
+        <v>1</v>
+      </c>
+      <c r="L786" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M786" t="str">
+        <v>2026-07-02 09:20:07</v>
+      </c>
+      <c r="N786" s="1">
+        <v>220000</v>
+      </c>
+      <c r="O786" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P786" t="str">
+        <v>20260702/하이얼_대구 착지 2곳_벌크_출하</v>
+      </c>
+      <c r="Q786" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R786" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="str">
+        <v>T260702-00001</v>
+      </c>
+      <c r="B787" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C787" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D787" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E787" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="F787">
+        <v>0</v>
+      </c>
+      <c r="G787" t="str">
+        <v>로지스밸리인천포트(Logisvalley)</v>
+      </c>
+      <c r="H787" t="str">
+        <v>인천 연수구 인천타워대로599번길 60 로지스밸리인천포트(Logisvalley) 1층 13번(HTC)</v>
+      </c>
+      <c r="I787" t="str">
+        <v>2026-07-02 11:00</v>
+      </c>
+      <c r="J787" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K787">
+        <v>1</v>
+      </c>
+      <c r="L787" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M787" t="str">
+        <v>2026-07-02 09:17:29</v>
+      </c>
+      <c r="N787" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O787" s="1">
+        <v>0</v>
+      </c>
+      <c r="P787" t="str">
+        <v>패스트레인 출하</v>
+      </c>
+      <c r="Q787" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R787" t="str">
+        <v>패스트레인코리아</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="str">
+        <v>T260701-00026</v>
+      </c>
+      <c r="B788" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C788" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D788" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E788" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F788">
+        <v>1</v>
+      </c>
+      <c r="G788" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H788" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I788" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J788" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K788">
+        <v>1</v>
+      </c>
+      <c r="L788" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M788" t="str">
+        <v>2026-07-01 19:47:13</v>
+      </c>
+      <c r="N788" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O788" s="1">
+        <v>0</v>
+      </c>
+      <c r="P788" t="str">
+        <v/>
+      </c>
+      <c r="Q788" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R788" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="str">
+        <v>T260701-00025</v>
+      </c>
+      <c r="B789" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C789" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D789" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E789" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F789">
+        <v>2</v>
+      </c>
+      <c r="G789" t="str">
+        <v>원주ACP</v>
+      </c>
+      <c r="H789" t="str">
+        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
+      </c>
+      <c r="I789" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J789" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K789">
+        <v>1</v>
+      </c>
+      <c r="L789" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M789" t="str">
+        <v>2026-07-01 19:46:48</v>
+      </c>
+      <c r="N789" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O789" s="1">
+        <v>0</v>
+      </c>
+      <c r="P789" t="str">
+        <v/>
+      </c>
+      <c r="Q789" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R789" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="str">
+        <v>T260701-00024</v>
+      </c>
+      <c r="B790" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C790" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D790" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E790" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F790">
+        <v>1</v>
+      </c>
+      <c r="G790" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H790" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I790" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J790" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K790">
+        <v>1</v>
+      </c>
+      <c r="L790" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M790" t="str">
+        <v>2026-07-01 19:46:12</v>
+      </c>
+      <c r="N790" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O790" s="1">
+        <v>0</v>
+      </c>
+      <c r="P790" t="str">
+        <v/>
+      </c>
+      <c r="Q790" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R790" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="str">
+        <v>T260701-00023</v>
+      </c>
+      <c r="B791" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C791" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D791" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E791" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F791">
+        <v>3</v>
+      </c>
+      <c r="G791" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H791" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I791" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J791" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K791">
+        <v>1</v>
+      </c>
+      <c r="L791" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M791" t="str">
+        <v>2026-07-01 19:45:40</v>
+      </c>
+      <c r="N791" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O791" s="1">
+        <v>0</v>
+      </c>
+      <c r="P791" t="str">
+        <v/>
+      </c>
+      <c r="Q791" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R791" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="str">
+        <v>T260701-00022</v>
+      </c>
+      <c r="B792" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C792" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D792" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E792" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F792">
+        <v>0</v>
+      </c>
+      <c r="G792" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H792" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I792" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J792" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K792">
+        <v>1</v>
+      </c>
+      <c r="L792" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M792" t="str">
+        <v>2026-07-01 19:44:56</v>
+      </c>
+      <c r="N792" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O792" s="1">
+        <v>0</v>
+      </c>
+      <c r="P792" t="str">
+        <v/>
+      </c>
+      <c r="Q792" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R792" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="str">
+        <v>T260701-00021</v>
+      </c>
+      <c r="B793" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C793" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D793" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E793" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F793">
+        <v>1</v>
+      </c>
+      <c r="G793" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H793" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I793" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J793" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K793">
+        <v>1</v>
+      </c>
+      <c r="L793" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M793" t="str">
+        <v>2026-07-01 19:44:37</v>
+      </c>
+      <c r="N793" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O793" s="1">
+        <v>0</v>
+      </c>
+      <c r="P793" t="str">
+        <v/>
+      </c>
+      <c r="Q793" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R793" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="str">
+        <v>T260701-00020</v>
+      </c>
+      <c r="B794" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C794" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D794" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E794" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F794">
+        <v>2</v>
+      </c>
+      <c r="G794" t="str">
+        <v>속초ACP</v>
+      </c>
+      <c r="H794" t="str">
+        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
+      </c>
+      <c r="I794" t="str">
+        <v>2026-07-02 06:00</v>
+      </c>
+      <c r="J794" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K794">
+        <v>1</v>
+      </c>
+      <c r="L794" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M794" t="str">
+        <v>2026-07-01 19:44:05</v>
+      </c>
+      <c r="N794" s="1">
+        <v>320000</v>
+      </c>
+      <c r="O794" s="1">
+        <v>0</v>
+      </c>
+      <c r="P794" t="str">
+        <v/>
+      </c>
+      <c r="Q794" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R794" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="str">
+        <v>T260701-00019</v>
+      </c>
+      <c r="B795" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C795" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D795" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E795" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F795">
+        <v>0</v>
+      </c>
+      <c r="G795" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H795" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I795" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J795" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K795">
+        <v>1</v>
+      </c>
+      <c r="L795" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M795" t="str">
+        <v>2026-07-01 19:43:22</v>
+      </c>
+      <c r="N795" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O795" s="1">
+        <v>0</v>
+      </c>
+      <c r="P795" t="str">
+        <v/>
+      </c>
+      <c r="Q795" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R795" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="str">
+        <v>T260701-00018</v>
+      </c>
+      <c r="B796" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C796" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D796" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E796" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F796">
+        <v>1</v>
+      </c>
+      <c r="G796" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H796" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I796" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J796" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K796">
+        <v>1</v>
+      </c>
+      <c r="L796" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M796" t="str">
+        <v>2026-07-01 19:43:03</v>
+      </c>
+      <c r="N796" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O796" s="1">
+        <v>0</v>
+      </c>
+      <c r="P796" t="str">
+        <v/>
+      </c>
+      <c r="Q796" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R796" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="str">
+        <v>T260701-00017</v>
+      </c>
+      <c r="B797" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C797" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D797" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E797" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F797">
+        <v>0</v>
+      </c>
+      <c r="G797" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H797" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I797" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J797" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K797">
+        <v>1</v>
+      </c>
+      <c r="L797" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M797" t="str">
+        <v>2026-07-01 19:42:39</v>
+      </c>
+      <c r="N797" s="1">
+        <v>310000</v>
+      </c>
+      <c r="O797" s="1">
+        <v>0</v>
+      </c>
+      <c r="P797" t="str">
+        <v/>
+      </c>
+      <c r="Q797" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R797" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="str">
+        <v>T260701-00016</v>
+      </c>
+      <c r="B798" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C798" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D798" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E798" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F798">
+        <v>0</v>
+      </c>
+      <c r="G798" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H798" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I798" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J798" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K798">
+        <v>1</v>
+      </c>
+      <c r="L798" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M798" t="str">
+        <v>2026-07-01 19:42:17</v>
+      </c>
+      <c r="N798" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O798" s="1">
+        <v>0</v>
+      </c>
+      <c r="P798" t="str">
+        <v/>
+      </c>
+      <c r="Q798" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R798" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="str">
+        <v>T260701-00015</v>
+      </c>
+      <c r="B799" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C799" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D799" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E799" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F799">
+        <v>1</v>
+      </c>
+      <c r="G799" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H799" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I799" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J799" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K799">
+        <v>1</v>
+      </c>
+      <c r="L799" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M799" t="str">
+        <v>2026-07-01 19:42:02</v>
+      </c>
+      <c r="N799" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O799" s="1">
+        <v>0</v>
+      </c>
+      <c r="P799" t="str">
+        <v/>
+      </c>
+      <c r="Q799" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R799" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="str">
+        <v>T260701-00014</v>
+      </c>
+      <c r="B800" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C800" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D800" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E800" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F800">
+        <v>1</v>
+      </c>
+      <c r="G800" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H800" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I800" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J800" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K800">
+        <v>1</v>
+      </c>
+      <c r="L800" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M800" t="str">
+        <v>2026-07-01 19:41:41</v>
+      </c>
+      <c r="N800" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O800" s="1">
+        <v>0</v>
+      </c>
+      <c r="P800" t="str">
+        <v/>
+      </c>
+      <c r="Q800" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R800" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="str">
+        <v>T260701-00013</v>
+      </c>
+      <c r="B801" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C801" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D801" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E801" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F801">
+        <v>1</v>
+      </c>
+      <c r="G801" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H801" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I801" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J801" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K801">
+        <v>1</v>
+      </c>
+      <c r="L801" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M801" t="str">
+        <v>2026-07-01 19:41:08</v>
+      </c>
+      <c r="N801" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O801" s="1">
+        <v>0</v>
+      </c>
+      <c r="P801" t="str">
+        <v/>
+      </c>
+      <c r="Q801" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R801" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="str">
+        <v>T260701-00012</v>
+      </c>
+      <c r="B802" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C802" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D802" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E802" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F802">
+        <v>1</v>
+      </c>
+      <c r="G802" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H802" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I802" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J802" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K802">
+        <v>1</v>
+      </c>
+      <c r="L802" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M802" t="str">
+        <v>2026-07-01 19:40:45</v>
+      </c>
+      <c r="N802" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O802" s="1">
+        <v>0</v>
+      </c>
+      <c r="P802" t="str">
+        <v/>
+      </c>
+      <c r="Q802" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R802" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="str">
+        <v>T260701-00011</v>
+      </c>
+      <c r="B803" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C803" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D803" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E803" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F803">
+        <v>0</v>
+      </c>
+      <c r="G803" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H803" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I803" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J803" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K803">
+        <v>1</v>
+      </c>
+      <c r="L803" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M803" t="str">
+        <v>2026-07-01 19:40:21</v>
+      </c>
+      <c r="N803" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O803" s="1">
+        <v>0</v>
+      </c>
+      <c r="P803" t="str">
+        <v/>
+      </c>
+      <c r="Q803" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R803" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="str">
+        <v>T260701-00010</v>
+      </c>
+      <c r="B804" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C804" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D804" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E804" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F804">
+        <v>1</v>
+      </c>
+      <c r="G804" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H804" t="str">
+        <v>경산시 해오름길114-2 경산FDC</v>
+      </c>
+      <c r="I804" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J804" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K804">
+        <v>1</v>
+      </c>
+      <c r="L804" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M804" t="str">
+        <v>2026-07-01 19:40:04</v>
+      </c>
+      <c r="N804" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O804" s="1">
+        <v>0</v>
+      </c>
+      <c r="P804" t="str">
+        <v/>
+      </c>
+      <c r="Q804" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R804" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="str">
+        <v>T260701-00009</v>
+      </c>
+      <c r="B805" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C805" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D805" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E805" t="str">
+        <v>2026-07-01 17:30</v>
+      </c>
+      <c r="F805">
+        <v>0</v>
+      </c>
+      <c r="G805" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H805" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I805" t="str">
+        <v>2026-07-01 18:30</v>
+      </c>
+      <c r="J805" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K805">
+        <v>1</v>
+      </c>
+      <c r="L805" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M805" t="str">
+        <v>2026-07-01 19:31:35</v>
+      </c>
+      <c r="N805" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O805" s="1">
+        <v>0</v>
+      </c>
+      <c r="P805" t="str">
+        <v/>
+      </c>
+      <c r="Q805" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R805" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="str">
+        <v>T260701-00008</v>
+      </c>
+      <c r="B806" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C806" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D806" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E806" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="F806">
+        <v>0</v>
+      </c>
+      <c r="G806" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H806" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I806" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="J806" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K806">
+        <v>1</v>
+      </c>
+      <c r="L806" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M806" t="str">
+        <v>2026-07-01 19:31:02</v>
+      </c>
+      <c r="N806" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O806" s="1">
+        <v>0</v>
+      </c>
+      <c r="P806" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q806" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R806" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="str">
+        <v>T260701-00007</v>
+      </c>
+      <c r="B807" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C807" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D807" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E807" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F807">
+        <v>0</v>
+      </c>
+      <c r="G807" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H807" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I807" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="J807" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K807">
+        <v>1</v>
+      </c>
+      <c r="L807" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M807" t="str">
+        <v>2026-07-01 19:29:27</v>
+      </c>
+      <c r="N807" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O807" s="1">
+        <v>0</v>
+      </c>
+      <c r="P807" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q807" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R807" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="str">
+        <v>T260701-00006</v>
+      </c>
+      <c r="B808" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C808" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D808" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E808" t="str">
+        <v>2026-07-01 16:30</v>
+      </c>
+      <c r="F808">
+        <v>0</v>
+      </c>
+      <c r="G808" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H808" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I808" t="str">
+        <v>2026-07-01 18:00</v>
+      </c>
+      <c r="J808" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K808">
+        <v>1</v>
+      </c>
+      <c r="L808" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M808" t="str">
+        <v>2026-07-01 16:09:24</v>
+      </c>
+      <c r="N808" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O808" s="1">
+        <v>0</v>
+      </c>
+      <c r="P808" t="str">
+        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q808" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R808" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="str">
+        <v>T260701-00005</v>
+      </c>
+      <c r="B809" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C809" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D809" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E809" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="F809">
+        <v>0</v>
+      </c>
+      <c r="G809" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H809" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I809" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J809" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K809">
+        <v>1</v>
+      </c>
+      <c r="L809" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M809" t="str">
+        <v>2026-07-01 14:58:37</v>
+      </c>
+      <c r="N809" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O809" s="1">
+        <v>0</v>
+      </c>
+      <c r="P809" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q809" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R809" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="str">
+        <v>T260701-00004</v>
+      </c>
+      <c r="B810" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C810" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D810" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E810" t="str">
+        <v>2026-07-01 15:20</v>
+      </c>
+      <c r="F810">
+        <v>0</v>
+      </c>
+      <c r="G810" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H810" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I810" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J810" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K810">
+        <v>1</v>
+      </c>
+      <c r="L810" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M810" t="str">
+        <v>2026-07-01 14:53:20</v>
+      </c>
+      <c r="N810" s="1">
+        <v>440000</v>
+      </c>
+      <c r="O810" s="1">
+        <v>0</v>
+      </c>
+      <c r="P810" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q810" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R810" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="str">
+        <v>T260701-00003</v>
+      </c>
+      <c r="B811" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C811" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D811" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E811" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F811">
+        <v>0</v>
+      </c>
+      <c r="G811" t="str">
+        <v>하이얼(이천다코넷)</v>
+      </c>
+      <c r="H811" t="str">
+        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
+      </c>
+      <c r="I811" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J811" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K811">
+        <v>1</v>
+      </c>
+      <c r="L811" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M811" t="str">
+        <v>2026-07-01 10:15:38</v>
+      </c>
+      <c r="N811" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O811" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P811" t="str">
+        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
+      </c>
+      <c r="Q811" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R811" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="str">
+        <v>T260701-00002</v>
+      </c>
+      <c r="B812" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C812" t="str">
+        <v>청주ARC(디지탈태양)</v>
+      </c>
+      <c r="D812" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
+      </c>
+      <c r="E812" t="str">
+        <v>2026-07-01 08:30</v>
+      </c>
+      <c r="F812">
+        <v>0</v>
+      </c>
+      <c r="G812" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H812" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="I812" t="str">
+        <v>2026-07-01 10:30</v>
+      </c>
+      <c r="J812" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K812">
+        <v>1</v>
+      </c>
+      <c r="L812" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M812" t="str">
+        <v>2026-07-01 10:13:39</v>
+      </c>
+      <c r="N812" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O812" s="1">
+        <v>0</v>
+      </c>
+      <c r="P812" t="str">
+        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
+      </c>
+      <c r="Q812" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R812" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="str">
+        <v>T260701-00001</v>
+      </c>
+      <c r="B813" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C813" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D813" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E813" t="str">
+        <v>2026-07-01 09:00</v>
+      </c>
+      <c r="F813">
+        <v>0</v>
+      </c>
+      <c r="G813" t="str">
+        <v>현대클러스터 한강미사3차</v>
+      </c>
+      <c r="H813" t="str">
+        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
+      </c>
+      <c r="I813" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J813" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K813">
+        <v>1</v>
+      </c>
+      <c r="L813" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M813" t="str">
+        <v>2026-07-01 09:07:09</v>
+      </c>
+      <c r="N813" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O813" s="1">
+        <v>0</v>
+      </c>
+      <c r="P813" t="str">
+        <v>스마트윈드 출하</v>
+      </c>
+      <c r="Q813" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R813" t="str">
+        <v>스마트윈드</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R726"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R813"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R740"/>
+  <dimension ref="A1:R858"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -41820,9 +41820,6617 @@
         <v>명경전자</v>
       </c>
     </row>
+    <row r="741">
+      <c r="A741" t="str">
+        <v>T260706-00031</v>
+      </c>
+      <c r="B741" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C741" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D741" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E741" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F741">
+        <v>0</v>
+      </c>
+      <c r="G741" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H741" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I741" t="str">
+        <v>2026-07-07 07:00</v>
+      </c>
+      <c r="J741" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K741">
+        <v>1</v>
+      </c>
+      <c r="L741" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M741" t="str">
+        <v>2026-07-06 20:43:10</v>
+      </c>
+      <c r="N741" s="1">
+        <v>130000</v>
+      </c>
+      <c r="O741" s="1">
+        <v>0</v>
+      </c>
+      <c r="P741" t="str">
+        <v/>
+      </c>
+      <c r="Q741" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R741" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="str">
+        <v>T260706-00030</v>
+      </c>
+      <c r="B742" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C742" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D742" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E742" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F742">
+        <v>1</v>
+      </c>
+      <c r="G742" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H742" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I742" t="str">
+        <v>2026-07-07 08:00</v>
+      </c>
+      <c r="J742" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K742">
+        <v>1</v>
+      </c>
+      <c r="L742" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M742" t="str">
+        <v>2026-07-06 20:42:49</v>
+      </c>
+      <c r="N742" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O742" s="1">
+        <v>0</v>
+      </c>
+      <c r="P742" t="str">
+        <v/>
+      </c>
+      <c r="Q742" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R742" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="str">
+        <v>T260706-00029</v>
+      </c>
+      <c r="B743" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C743" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D743" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E743" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F743">
+        <v>2</v>
+      </c>
+      <c r="G743" t="str">
+        <v>원주ACP</v>
+      </c>
+      <c r="H743" t="str">
+        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
+      </c>
+      <c r="I743" t="str">
+        <v>2026-07-07 07:00</v>
+      </c>
+      <c r="J743" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K743">
+        <v>1</v>
+      </c>
+      <c r="L743" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M743" t="str">
+        <v>2026-07-06 20:42:20</v>
+      </c>
+      <c r="N743" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O743" s="1">
+        <v>0</v>
+      </c>
+      <c r="P743" t="str">
+        <v/>
+      </c>
+      <c r="Q743" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R743" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="str">
+        <v>T260706-00028</v>
+      </c>
+      <c r="B744" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C744" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D744" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E744" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F744">
+        <v>1</v>
+      </c>
+      <c r="G744" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H744" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I744" t="str">
+        <v>2026-07-07 08:00</v>
+      </c>
+      <c r="J744" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K744">
+        <v>1</v>
+      </c>
+      <c r="L744" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M744" t="str">
+        <v>2026-07-06 20:41:21</v>
+      </c>
+      <c r="N744" s="1">
+        <v>170000</v>
+      </c>
+      <c r="O744" s="1">
+        <v>0</v>
+      </c>
+      <c r="P744" t="str">
+        <v/>
+      </c>
+      <c r="Q744" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R744" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="str">
+        <v>T260706-00027</v>
+      </c>
+      <c r="B745" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C745" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D745" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E745" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F745">
+        <v>1</v>
+      </c>
+      <c r="G745" t="str">
+        <v>속초ACP</v>
+      </c>
+      <c r="H745" t="str">
+        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
+      </c>
+      <c r="I745" t="str">
+        <v>2026-07-07 08:00</v>
+      </c>
+      <c r="J745" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K745">
+        <v>1</v>
+      </c>
+      <c r="L745" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M745" t="str">
+        <v>2026-07-06 20:40:49</v>
+      </c>
+      <c r="N745" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O745" s="1">
+        <v>0</v>
+      </c>
+      <c r="P745" t="str">
+        <v/>
+      </c>
+      <c r="Q745" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R745" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="str">
+        <v>T260706-00026</v>
+      </c>
+      <c r="B746" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C746" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D746" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E746" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F746">
+        <v>3</v>
+      </c>
+      <c r="G746" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H746" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I746" t="str">
+        <v>2026-07-07 07:00</v>
+      </c>
+      <c r="J746" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K746">
+        <v>1</v>
+      </c>
+      <c r="L746" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M746" t="str">
+        <v>2026-07-06 20:40:12</v>
+      </c>
+      <c r="N746" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O746" s="1">
+        <v>0</v>
+      </c>
+      <c r="P746" t="str">
+        <v/>
+      </c>
+      <c r="Q746" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R746" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="str">
+        <v>T260706-00025</v>
+      </c>
+      <c r="B747" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C747" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D747" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E747" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F747">
+        <v>0</v>
+      </c>
+      <c r="G747" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H747" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I747" t="str">
+        <v>2026-07-06 22:00</v>
+      </c>
+      <c r="J747" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K747">
+        <v>1</v>
+      </c>
+      <c r="L747" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M747" t="str">
+        <v>2026-07-06 20:39:25</v>
+      </c>
+      <c r="N747" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O747" s="1">
+        <v>0</v>
+      </c>
+      <c r="P747" t="str">
+        <v/>
+      </c>
+      <c r="Q747" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R747" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="str">
+        <v>T260706-00024</v>
+      </c>
+      <c r="B748" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C748" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D748" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E748" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F748">
+        <v>0</v>
+      </c>
+      <c r="G748" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H748" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I748" t="str">
+        <v>2026-07-07 07:00</v>
+      </c>
+      <c r="J748" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K748">
+        <v>1</v>
+      </c>
+      <c r="L748" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M748" t="str">
+        <v>2026-07-06 20:39:07</v>
+      </c>
+      <c r="N748" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O748" s="1">
+        <v>0</v>
+      </c>
+      <c r="P748" t="str">
+        <v/>
+      </c>
+      <c r="Q748" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R748" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="str">
+        <v>T260706-00023</v>
+      </c>
+      <c r="B749" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C749" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D749" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E749" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F749">
+        <v>0</v>
+      </c>
+      <c r="G749" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H749" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I749" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J749" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K749">
+        <v>1</v>
+      </c>
+      <c r="L749" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M749" t="str">
+        <v>2026-07-06 20:38:47</v>
+      </c>
+      <c r="N749" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O749" s="1">
+        <v>0</v>
+      </c>
+      <c r="P749" t="str">
+        <v/>
+      </c>
+      <c r="Q749" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R749" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="str">
+        <v>T260706-00022</v>
+      </c>
+      <c r="B750" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C750" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D750" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E750" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F750">
+        <v>0</v>
+      </c>
+      <c r="G750" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H750" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I750" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J750" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K750">
+        <v>1</v>
+      </c>
+      <c r="L750" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M750" t="str">
+        <v>2026-07-06 20:38:33</v>
+      </c>
+      <c r="N750" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O750" s="1">
+        <v>0</v>
+      </c>
+      <c r="P750" t="str">
+        <v/>
+      </c>
+      <c r="Q750" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R750" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="str">
+        <v>T260706-00021</v>
+      </c>
+      <c r="B751" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C751" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D751" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E751" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F751">
+        <v>0</v>
+      </c>
+      <c r="G751" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="H751" t="str">
+        <v>충청남도 아산시 음봉면 월암로 265-16 가동 천안FDC</v>
+      </c>
+      <c r="I751" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J751" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K751">
+        <v>1</v>
+      </c>
+      <c r="L751" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M751" t="str">
+        <v>2026-07-06 20:38:16</v>
+      </c>
+      <c r="N751" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O751" s="1">
+        <v>0</v>
+      </c>
+      <c r="P751" t="str">
+        <v/>
+      </c>
+      <c r="Q751" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R751" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="str">
+        <v>T260706-00020</v>
+      </c>
+      <c r="B752" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C752" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D752" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E752" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F752">
+        <v>1</v>
+      </c>
+      <c r="G752" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H752" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I752" t="str">
+        <v>2026-07-06 23:00</v>
+      </c>
+      <c r="J752" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K752">
+        <v>1</v>
+      </c>
+      <c r="L752" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M752" t="str">
+        <v>2026-07-06 20:37:59</v>
+      </c>
+      <c r="N752" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O752" s="1">
+        <v>0</v>
+      </c>
+      <c r="P752" t="str">
+        <v/>
+      </c>
+      <c r="Q752" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R752" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="str">
+        <v>T260706-00019</v>
+      </c>
+      <c r="B753" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C753" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D753" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E753" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F753">
+        <v>0</v>
+      </c>
+      <c r="G753" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H753" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I753" t="str">
+        <v>2026-07-06 22:00</v>
+      </c>
+      <c r="J753" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K753">
+        <v>1</v>
+      </c>
+      <c r="L753" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M753" t="str">
+        <v>2026-07-06 20:37:38</v>
+      </c>
+      <c r="N753" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O753" s="1">
+        <v>0</v>
+      </c>
+      <c r="P753" t="str">
+        <v/>
+      </c>
+      <c r="Q753" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R753" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="str">
+        <v>T260706-00018</v>
+      </c>
+      <c r="B754" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C754" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D754" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E754" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F754">
+        <v>1</v>
+      </c>
+      <c r="G754" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H754" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I754" t="str">
+        <v>2026-07-06 22:00</v>
+      </c>
+      <c r="J754" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K754">
+        <v>1</v>
+      </c>
+      <c r="L754" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M754" t="str">
+        <v>2026-07-06 20:37:22</v>
+      </c>
+      <c r="N754" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O754" s="1">
+        <v>0</v>
+      </c>
+      <c r="P754" t="str">
+        <v/>
+      </c>
+      <c r="Q754" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R754" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="str">
+        <v>T260706-00017</v>
+      </c>
+      <c r="B755" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C755" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D755" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E755" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F755">
+        <v>0</v>
+      </c>
+      <c r="G755" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H755" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I755" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J755" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K755">
+        <v>1</v>
+      </c>
+      <c r="L755" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M755" t="str">
+        <v>2026-07-06 20:36:54</v>
+      </c>
+      <c r="N755" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O755" s="1">
+        <v>0</v>
+      </c>
+      <c r="P755" t="str">
+        <v/>
+      </c>
+      <c r="Q755" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R755" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="str">
+        <v>T260706-00016</v>
+      </c>
+      <c r="B756" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C756" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D756" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E756" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F756">
+        <v>1</v>
+      </c>
+      <c r="G756" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H756" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I756" t="str">
+        <v>2026-07-06 22:00</v>
+      </c>
+      <c r="J756" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K756">
+        <v>1</v>
+      </c>
+      <c r="L756" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M756" t="str">
+        <v>2026-07-06 20:35:29</v>
+      </c>
+      <c r="N756" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O756" s="1">
+        <v>0</v>
+      </c>
+      <c r="P756" t="str">
+        <v/>
+      </c>
+      <c r="Q756" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R756" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="str">
+        <v>T260706-00015</v>
+      </c>
+      <c r="B757" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C757" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D757" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E757" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F757">
+        <v>0</v>
+      </c>
+      <c r="G757" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H757" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I757" t="str">
+        <v>2026-07-06 23:00</v>
+      </c>
+      <c r="J757" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K757">
+        <v>1</v>
+      </c>
+      <c r="L757" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M757" t="str">
+        <v>2026-07-06 20:35:06</v>
+      </c>
+      <c r="N757" s="1">
+        <v>480000</v>
+      </c>
+      <c r="O757" s="1">
+        <v>0</v>
+      </c>
+      <c r="P757" t="str">
+        <v/>
+      </c>
+      <c r="Q757" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R757" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="str">
+        <v>T260706-00014</v>
+      </c>
+      <c r="B758" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C758" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D758" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E758" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F758">
+        <v>0</v>
+      </c>
+      <c r="G758" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H758" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I758" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J758" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K758">
+        <v>1</v>
+      </c>
+      <c r="L758" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M758" t="str">
+        <v>2026-07-06 20:34:46</v>
+      </c>
+      <c r="N758" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O758" s="1">
+        <v>0</v>
+      </c>
+      <c r="P758" t="str">
+        <v/>
+      </c>
+      <c r="Q758" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R758" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="str">
+        <v>T260706-00013</v>
+      </c>
+      <c r="B759" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C759" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D759" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E759" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F759">
+        <v>0</v>
+      </c>
+      <c r="G759" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H759" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I759" t="str">
+        <v>2026-07-07 06:00</v>
+      </c>
+      <c r="J759" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K759">
+        <v>1</v>
+      </c>
+      <c r="L759" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M759" t="str">
+        <v>2026-07-06 20:34:27</v>
+      </c>
+      <c r="N759" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O759" s="1">
+        <v>0</v>
+      </c>
+      <c r="P759" t="str">
+        <v/>
+      </c>
+      <c r="Q759" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R759" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="str">
+        <v>T260706-00012</v>
+      </c>
+      <c r="B760" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C760" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D760" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E760" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F760">
+        <v>0</v>
+      </c>
+      <c r="G760" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H760" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I760" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J760" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K760">
+        <v>1</v>
+      </c>
+      <c r="L760" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M760" t="str">
+        <v>2026-07-06 20:33:52</v>
+      </c>
+      <c r="N760" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O760" s="1">
+        <v>0</v>
+      </c>
+      <c r="P760" t="str">
+        <v/>
+      </c>
+      <c r="Q760" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R760" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="str">
+        <v>T260706-00011</v>
+      </c>
+      <c r="B761" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C761" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D761" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E761" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F761">
+        <v>0</v>
+      </c>
+      <c r="G761" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H761" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I761" t="str">
+        <v>2026-07-06 23:00</v>
+      </c>
+      <c r="J761" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K761">
+        <v>1</v>
+      </c>
+      <c r="L761" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M761" t="str">
+        <v>2026-07-06 20:33:32</v>
+      </c>
+      <c r="N761" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O761" s="1">
+        <v>0</v>
+      </c>
+      <c r="P761" t="str">
+        <v/>
+      </c>
+      <c r="Q761" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R761" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="str">
+        <v>T260706-00010</v>
+      </c>
+      <c r="B762" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C762" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D762" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E762" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F762">
+        <v>0</v>
+      </c>
+      <c r="G762" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H762" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I762" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J762" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K762">
+        <v>1</v>
+      </c>
+      <c r="L762" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M762" t="str">
+        <v>2026-07-06 20:33:02</v>
+      </c>
+      <c r="N762" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O762" s="1">
+        <v>0</v>
+      </c>
+      <c r="P762" t="str">
+        <v/>
+      </c>
+      <c r="Q762" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R762" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="str">
+        <v>T260706-00009</v>
+      </c>
+      <c r="B763" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C763" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D763" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E763" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F763">
+        <v>1</v>
+      </c>
+      <c r="G763" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H763" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="I763" t="str">
+        <v>2026-07-06 23:00</v>
+      </c>
+      <c r="J763" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K763">
+        <v>1</v>
+      </c>
+      <c r="L763" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M763" t="str">
+        <v>2026-07-06 20:32:45</v>
+      </c>
+      <c r="N763" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O763" s="1">
+        <v>0</v>
+      </c>
+      <c r="P763" t="str">
+        <v/>
+      </c>
+      <c r="Q763" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R763" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="str">
+        <v>T260706-00008</v>
+      </c>
+      <c r="B764" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C764" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D764" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E764" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F764">
+        <v>1</v>
+      </c>
+      <c r="G764" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="H764" t="str">
+        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="I764" t="str">
+        <v>2026-07-06 23:00</v>
+      </c>
+      <c r="J764" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K764">
+        <v>1</v>
+      </c>
+      <c r="L764" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M764" t="str">
+        <v>2026-07-06 20:32:23</v>
+      </c>
+      <c r="N764" s="1">
+        <v>330000</v>
+      </c>
+      <c r="O764" s="1">
+        <v>0</v>
+      </c>
+      <c r="P764" t="str">
+        <v/>
+      </c>
+      <c r="Q764" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R764" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="str">
+        <v>T260706-00007</v>
+      </c>
+      <c r="B765" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C765" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D765" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E765" t="str">
+        <v>2026-07-06 17:30</v>
+      </c>
+      <c r="F765">
+        <v>0</v>
+      </c>
+      <c r="G765" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H765" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I765" t="str">
+        <v>2026-07-06 18:30</v>
+      </c>
+      <c r="J765" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K765">
+        <v>1</v>
+      </c>
+      <c r="L765" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M765" t="str">
+        <v>2026-07-06 20:29:06</v>
+      </c>
+      <c r="N765" s="1">
+        <v>130000</v>
+      </c>
+      <c r="O765" s="1">
+        <v>0</v>
+      </c>
+      <c r="P765" t="str">
+        <v/>
+      </c>
+      <c r="Q765" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R765" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="str">
+        <v>T260706-00006</v>
+      </c>
+      <c r="B766" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C766" t="str">
+        <v>라꾸스토리</v>
+      </c>
+      <c r="D766" t="str">
+        <v>충북 옥천군 군서면 동평리 130 라꾸스토리</v>
+      </c>
+      <c r="E766" t="str">
+        <v>2026-07-06 13:30</v>
+      </c>
+      <c r="F766">
+        <v>0</v>
+      </c>
+      <c r="G766" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H766" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I766" t="str">
+        <v>2026-07-06 15:30</v>
+      </c>
+      <c r="J766" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K766">
+        <v>1</v>
+      </c>
+      <c r="L766" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M766" t="str">
+        <v>2026-07-06 20:28:33</v>
+      </c>
+      <c r="N766" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O766" s="1">
+        <v>0</v>
+      </c>
+      <c r="P766" t="str">
+        <v>거래처비용청구</v>
+      </c>
+      <c r="Q766" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R766" t="str">
+        <v>라꾸스토리</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="str">
+        <v>T260706-00005</v>
+      </c>
+      <c r="B767" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C767" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="D767" t="str">
+        <v>강원특별자치도 강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="E767" t="str">
+        <v>2026-07-06 08:00</v>
+      </c>
+      <c r="F767">
+        <v>0</v>
+      </c>
+      <c r="G767" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="H767" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="I767" t="str">
+        <v>2026-07-06 11:30</v>
+      </c>
+      <c r="J767" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K767">
+        <v>1</v>
+      </c>
+      <c r="L767" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M767" t="str">
+        <v>2026-07-06 20:27:47</v>
+      </c>
+      <c r="N767" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O767" s="1">
+        <v>0</v>
+      </c>
+      <c r="P767" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="Q767" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R767" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="str">
+        <v>T260706-00004</v>
+      </c>
+      <c r="B768" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C768" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D768" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E768" t="str">
+        <v>2026-07-06 13:30</v>
+      </c>
+      <c r="F768">
+        <v>0</v>
+      </c>
+      <c r="G768" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H768" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I768" t="str">
+        <v>2026-07-06 15:30</v>
+      </c>
+      <c r="J768" t="str">
+        <v>1.5톤 윙바디</v>
+      </c>
+      <c r="K768">
+        <v>1</v>
+      </c>
+      <c r="L768" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M768" t="str">
+        <v>2026-07-06 20:26:56</v>
+      </c>
+      <c r="N768" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O768" s="1">
+        <v>0</v>
+      </c>
+      <c r="P768" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q768" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R768" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="str">
+        <v>T260706-00003</v>
+      </c>
+      <c r="B769" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C769" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D769" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E769" t="str">
+        <v>2026-07-06 10:00</v>
+      </c>
+      <c r="F769">
+        <v>0</v>
+      </c>
+      <c r="G769" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H769" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I769" t="str">
+        <v>2026-07-06 13:30</v>
+      </c>
+      <c r="J769" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K769">
+        <v>1</v>
+      </c>
+      <c r="L769" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M769" t="str">
+        <v>2026-07-06 20:25:59</v>
+      </c>
+      <c r="N769" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O769" s="1">
+        <v>0</v>
+      </c>
+      <c r="P769" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q769" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R769" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="str">
+        <v>T260706-00002</v>
+      </c>
+      <c r="B770" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C770" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D770" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E770" t="str">
+        <v>2026-07-06 16:30</v>
+      </c>
+      <c r="F770">
+        <v>0</v>
+      </c>
+      <c r="G770" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H770" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I770" t="str">
+        <v>2026-07-06 18:00</v>
+      </c>
+      <c r="J770" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K770">
+        <v>1</v>
+      </c>
+      <c r="L770" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M770" t="str">
+        <v>2026-07-06 15:56:39</v>
+      </c>
+      <c r="N770" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O770" s="1">
+        <v>0</v>
+      </c>
+      <c r="P770" t="str">
+        <v>20260706/경동택배_남이가마258 영업소_파렛트 출하</v>
+      </c>
+      <c r="Q770" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R770" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="str">
+        <v>T260706-00001</v>
+      </c>
+      <c r="B771" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C771" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D771" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E771" t="str">
+        <v>2026-07-06 09:00</v>
+      </c>
+      <c r="F771">
+        <v>0</v>
+      </c>
+      <c r="G771" t="str">
+        <v>세상담기(14대 서울 벌크 출하)</v>
+      </c>
+      <c r="H771" t="str">
+        <v>서울 서대문구 이화여대길 50-8 2층 문 앞</v>
+      </c>
+      <c r="I771" t="str">
+        <v>2026-07-06 11:50</v>
+      </c>
+      <c r="J771" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K771">
+        <v>1</v>
+      </c>
+      <c r="L771" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M771" t="str">
+        <v>2026-07-06 10:32:22</v>
+      </c>
+      <c r="N771" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O771" s="1">
+        <v>0</v>
+      </c>
+      <c r="P771" t="str">
+        <v>20260706/세상담기_서울 벌크_출하(14대 2층 운반 건)</v>
+      </c>
+      <c r="Q771" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R771" t="str">
+        <v>세상담기</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="str">
+        <v>T260703-00034</v>
+      </c>
+      <c r="B772" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C772" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D772" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E772" t="str">
+        <v>2026-07-03 19:01</v>
+      </c>
+      <c r="F772">
+        <v>0</v>
+      </c>
+      <c r="G772" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H772" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I772" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J772" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K772">
+        <v>1</v>
+      </c>
+      <c r="L772" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M772" t="str">
+        <v>2026-07-03 20:43:25</v>
+      </c>
+      <c r="N772" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O772" s="1">
+        <v>0</v>
+      </c>
+      <c r="P772" t="str">
+        <v/>
+      </c>
+      <c r="Q772" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R772" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="str">
+        <v>T260703-00033</v>
+      </c>
+      <c r="B773" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C773" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D773" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E773" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F773">
+        <v>1</v>
+      </c>
+      <c r="G773" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H773" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I773" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J773" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K773">
+        <v>1</v>
+      </c>
+      <c r="L773" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M773" t="str">
+        <v>2026-07-03 20:42:58</v>
+      </c>
+      <c r="N773" s="1">
+        <v>170000</v>
+      </c>
+      <c r="O773" s="1">
+        <v>0</v>
+      </c>
+      <c r="P773" t="str">
+        <v/>
+      </c>
+      <c r="Q773" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R773" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="str">
+        <v>T260703-00032</v>
+      </c>
+      <c r="B774" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C774" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D774" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E774" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F774">
+        <v>1</v>
+      </c>
+      <c r="G774" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H774" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I774" t="str">
+        <v>2026-07-04 08:00</v>
+      </c>
+      <c r="J774" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K774">
+        <v>1</v>
+      </c>
+      <c r="L774" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M774" t="str">
+        <v>2026-07-03 20:42:34</v>
+      </c>
+      <c r="N774" s="1">
+        <v>170000</v>
+      </c>
+      <c r="O774" s="1">
+        <v>0</v>
+      </c>
+      <c r="P774" t="str">
+        <v/>
+      </c>
+      <c r="Q774" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R774" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="str">
+        <v>T260703-00031</v>
+      </c>
+      <c r="B775" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C775" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D775" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E775" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F775">
+        <v>0</v>
+      </c>
+      <c r="G775" t="str">
+        <v>시흥ACP</v>
+      </c>
+      <c r="H775" t="str">
+        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
+      </c>
+      <c r="I775" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J775" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K775">
+        <v>1</v>
+      </c>
+      <c r="L775" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M775" t="str">
+        <v>2026-07-03 20:41:59</v>
+      </c>
+      <c r="N775" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O775" s="1">
+        <v>0</v>
+      </c>
+      <c r="P775" t="str">
+        <v/>
+      </c>
+      <c r="Q775" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R775" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="str">
+        <v>T260703-00030</v>
+      </c>
+      <c r="B776" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C776" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D776" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E776" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F776">
+        <v>3</v>
+      </c>
+      <c r="G776" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H776" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I776" t="str">
+        <v>2026-07-04 08:00</v>
+      </c>
+      <c r="J776" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K776">
+        <v>1</v>
+      </c>
+      <c r="L776" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M776" t="str">
+        <v>2026-07-03 20:41:34</v>
+      </c>
+      <c r="N776" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O776" s="1">
+        <v>0</v>
+      </c>
+      <c r="P776" t="str">
+        <v/>
+      </c>
+      <c r="Q776" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R776" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="str">
+        <v>T260703-00029</v>
+      </c>
+      <c r="B777" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C777" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D777" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E777" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F777">
+        <v>0</v>
+      </c>
+      <c r="G777" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H777" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I777" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J777" t="str">
+        <v>1톤 기타차량</v>
+      </c>
+      <c r="K777">
+        <v>1</v>
+      </c>
+      <c r="L777" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M777" t="str">
+        <v>2026-07-03 20:40:56</v>
+      </c>
+      <c r="N777" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O777" s="1">
+        <v>0</v>
+      </c>
+      <c r="P777" t="str">
+        <v/>
+      </c>
+      <c r="Q777" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R777" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="str">
+        <v>T260703-00028</v>
+      </c>
+      <c r="B778" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C778" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D778" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E778" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F778">
+        <v>0</v>
+      </c>
+      <c r="G778" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H778" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I778" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J778" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K778">
+        <v>1</v>
+      </c>
+      <c r="L778" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M778" t="str">
+        <v>2026-07-03 20:40:32</v>
+      </c>
+      <c r="N778" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O778" s="1">
+        <v>0</v>
+      </c>
+      <c r="P778" t="str">
+        <v/>
+      </c>
+      <c r="Q778" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R778" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="str">
+        <v>T260703-00027</v>
+      </c>
+      <c r="B779" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C779" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D779" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E779" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F779">
+        <v>3</v>
+      </c>
+      <c r="G779" t="str">
+        <v>인제ACP</v>
+      </c>
+      <c r="H779" t="str">
+        <v>강원특별자치도 속초시 만천6길 13 인제ACP</v>
+      </c>
+      <c r="I779" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J779" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K779">
+        <v>1</v>
+      </c>
+      <c r="L779" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M779" t="str">
+        <v>2026-07-03 20:40:07</v>
+      </c>
+      <c r="N779" s="1">
+        <v>390000</v>
+      </c>
+      <c r="O779" s="1">
+        <v>0</v>
+      </c>
+      <c r="P779" t="str">
+        <v/>
+      </c>
+      <c r="Q779" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R779" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="str">
+        <v>T260703-00026</v>
+      </c>
+      <c r="B780" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C780" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D780" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E780" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F780">
+        <v>0</v>
+      </c>
+      <c r="G780" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H780" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I780" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J780" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K780">
+        <v>1</v>
+      </c>
+      <c r="L780" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M780" t="str">
+        <v>2026-07-03 20:39:21</v>
+      </c>
+      <c r="N780" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O780" s="1">
+        <v>0</v>
+      </c>
+      <c r="P780" t="str">
+        <v/>
+      </c>
+      <c r="Q780" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R780" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="str">
+        <v>T260703-00025</v>
+      </c>
+      <c r="B781" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C781" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D781" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E781" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F781">
+        <v>1</v>
+      </c>
+      <c r="G781" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H781" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I781" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J781" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K781">
+        <v>1</v>
+      </c>
+      <c r="L781" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M781" t="str">
+        <v>2026-07-03 20:39:06</v>
+      </c>
+      <c r="N781" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O781" s="1">
+        <v>0</v>
+      </c>
+      <c r="P781" t="str">
+        <v/>
+      </c>
+      <c r="Q781" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R781" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="str">
+        <v>T260703-00024</v>
+      </c>
+      <c r="B782" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C782" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D782" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E782" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F782">
+        <v>1</v>
+      </c>
+      <c r="G782" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H782" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I782" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J782" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K782">
+        <v>1</v>
+      </c>
+      <c r="L782" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M782" t="str">
+        <v>2026-07-03 20:38:48</v>
+      </c>
+      <c r="N782" s="1">
+        <v>530000</v>
+      </c>
+      <c r="O782" s="1">
+        <v>0</v>
+      </c>
+      <c r="P782" t="str">
+        <v/>
+      </c>
+      <c r="Q782" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R782" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="str">
+        <v>T260703-00023</v>
+      </c>
+      <c r="B783" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C783" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D783" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E783" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F783">
+        <v>0</v>
+      </c>
+      <c r="G783" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H783" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I783" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J783" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K783">
+        <v>1</v>
+      </c>
+      <c r="L783" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M783" t="str">
+        <v>2026-07-03 20:38:28</v>
+      </c>
+      <c r="N783" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O783" s="1">
+        <v>0</v>
+      </c>
+      <c r="P783" t="str">
+        <v/>
+      </c>
+      <c r="Q783" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R783" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="str">
+        <v>T260703-00022</v>
+      </c>
+      <c r="B784" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C784" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D784" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E784" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F784">
+        <v>0</v>
+      </c>
+      <c r="G784" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H784" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I784" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J784" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K784">
+        <v>1</v>
+      </c>
+      <c r="L784" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M784" t="str">
+        <v>2026-07-03 20:38:14</v>
+      </c>
+      <c r="N784" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O784" s="1">
+        <v>0</v>
+      </c>
+      <c r="P784" t="str">
+        <v/>
+      </c>
+      <c r="Q784" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R784" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="str">
+        <v>T260703-00021</v>
+      </c>
+      <c r="B785" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C785" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D785" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E785" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F785">
+        <v>1</v>
+      </c>
+      <c r="G785" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H785" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I785" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J785" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K785">
+        <v>1</v>
+      </c>
+      <c r="L785" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M785" t="str">
+        <v>2026-07-03 20:37:59</v>
+      </c>
+      <c r="N785" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O785" s="1">
+        <v>0</v>
+      </c>
+      <c r="P785" t="str">
+        <v/>
+      </c>
+      <c r="Q785" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R785" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="str">
+        <v>T260703-00020</v>
+      </c>
+      <c r="B786" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C786" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D786" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E786" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F786">
+        <v>0</v>
+      </c>
+      <c r="G786" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H786" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I786" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J786" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K786">
+        <v>1</v>
+      </c>
+      <c r="L786" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M786" t="str">
+        <v>2026-07-03 20:37:40</v>
+      </c>
+      <c r="N786" s="1">
+        <v>490000</v>
+      </c>
+      <c r="O786" s="1">
+        <v>0</v>
+      </c>
+      <c r="P786" t="str">
+        <v/>
+      </c>
+      <c r="Q786" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R786" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="str">
+        <v>T260703-00019</v>
+      </c>
+      <c r="B787" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C787" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D787" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E787" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F787">
+        <v>0</v>
+      </c>
+      <c r="G787" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H787" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I787" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J787" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K787">
+        <v>1</v>
+      </c>
+      <c r="L787" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M787" t="str">
+        <v>2026-07-03 20:37:26</v>
+      </c>
+      <c r="N787" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O787" s="1">
+        <v>0</v>
+      </c>
+      <c r="P787" t="str">
+        <v/>
+      </c>
+      <c r="Q787" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R787" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="str">
+        <v>T260703-00018</v>
+      </c>
+      <c r="B788" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C788" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D788" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E788" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F788">
+        <v>0</v>
+      </c>
+      <c r="G788" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H788" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I788" t="str">
+        <v>2026-07-03 20:00</v>
+      </c>
+      <c r="J788" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K788">
+        <v>1</v>
+      </c>
+      <c r="L788" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M788" t="str">
+        <v>2026-07-03 20:37:11</v>
+      </c>
+      <c r="N788" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O788" s="1">
+        <v>0</v>
+      </c>
+      <c r="P788" t="str">
+        <v/>
+      </c>
+      <c r="Q788" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R788" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="str">
+        <v>T260703-00017</v>
+      </c>
+      <c r="B789" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C789" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D789" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E789" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F789">
+        <v>0</v>
+      </c>
+      <c r="G789" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H789" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I789" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J789" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K789">
+        <v>1</v>
+      </c>
+      <c r="L789" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M789" t="str">
+        <v>2026-07-03 20:36:55</v>
+      </c>
+      <c r="N789" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O789" s="1">
+        <v>0</v>
+      </c>
+      <c r="P789" t="str">
+        <v/>
+      </c>
+      <c r="Q789" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R789" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="str">
+        <v>T260703-00016</v>
+      </c>
+      <c r="B790" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C790" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D790" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E790" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F790">
+        <v>0</v>
+      </c>
+      <c r="G790" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H790" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I790" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J790" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K790">
+        <v>1</v>
+      </c>
+      <c r="L790" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M790" t="str">
+        <v>2026-07-03 20:36:37</v>
+      </c>
+      <c r="N790" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O790" s="1">
+        <v>0</v>
+      </c>
+      <c r="P790" t="str">
+        <v/>
+      </c>
+      <c r="Q790" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R790" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="str">
+        <v>T260703-00015</v>
+      </c>
+      <c r="B791" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C791" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D791" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E791" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F791">
+        <v>0</v>
+      </c>
+      <c r="G791" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H791" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I791" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J791" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K791">
+        <v>1</v>
+      </c>
+      <c r="L791" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M791" t="str">
+        <v>2026-07-03 20:36:15</v>
+      </c>
+      <c r="N791" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O791" s="1">
+        <v>0</v>
+      </c>
+      <c r="P791" t="str">
+        <v/>
+      </c>
+      <c r="Q791" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R791" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="str">
+        <v>T260703-00014</v>
+      </c>
+      <c r="B792" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C792" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D792" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E792" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F792">
+        <v>1</v>
+      </c>
+      <c r="G792" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H792" t="str">
+        <v>경산시 해오름길114-2 경산FDC</v>
+      </c>
+      <c r="I792" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J792" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K792">
+        <v>1</v>
+      </c>
+      <c r="L792" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M792" t="str">
+        <v>2026-07-03 20:35:55</v>
+      </c>
+      <c r="N792" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O792" s="1">
+        <v>0</v>
+      </c>
+      <c r="P792" t="str">
+        <v/>
+      </c>
+      <c r="Q792" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R792" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="str">
+        <v>T260703-00013</v>
+      </c>
+      <c r="B793" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C793" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D793" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E793" t="str">
+        <v>2026-07-03 17:30</v>
+      </c>
+      <c r="F793">
+        <v>0</v>
+      </c>
+      <c r="G793" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H793" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I793" t="str">
+        <v>2026-07-03 18:30</v>
+      </c>
+      <c r="J793" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K793">
+        <v>1</v>
+      </c>
+      <c r="L793" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M793" t="str">
+        <v>2026-07-03 20:31:55</v>
+      </c>
+      <c r="N793" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O793" s="1">
+        <v>0</v>
+      </c>
+      <c r="P793" t="str">
+        <v/>
+      </c>
+      <c r="Q793" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R793" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="str">
+        <v>T260703-00012</v>
+      </c>
+      <c r="B794" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C794" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="D794" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="E794" t="str">
+        <v>2026-07-03 08:30</v>
+      </c>
+      <c r="F794">
+        <v>0</v>
+      </c>
+      <c r="G794" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="H794" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="I794" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="J794" t="str">
+        <v>3.5톤 카고</v>
+      </c>
+      <c r="K794">
+        <v>1</v>
+      </c>
+      <c r="L794" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M794" t="str">
+        <v>2026-07-03 20:31:21</v>
+      </c>
+      <c r="N794" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O794" s="1">
+        <v>0</v>
+      </c>
+      <c r="P794" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="Q794" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R794" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="str">
+        <v>T260703-00011</v>
+      </c>
+      <c r="B795" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C795" t="str">
+        <v>샤오미</v>
+      </c>
+      <c r="D795" t="str">
+        <v>경기 이천시 대월면 부필리 309 샤오미</v>
+      </c>
+      <c r="E795" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="F795">
+        <v>0</v>
+      </c>
+      <c r="G795" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H795" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I795" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="J795" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K795">
+        <v>1</v>
+      </c>
+      <c r="L795" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M795" t="str">
+        <v>2026-07-03 20:30:39</v>
+      </c>
+      <c r="N795" s="1">
+        <v>80000</v>
+      </c>
+      <c r="O795" s="1">
+        <v>0</v>
+      </c>
+      <c r="P795" t="str">
+        <v>거래처비용청구(1대)</v>
+      </c>
+      <c r="Q795" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R795" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="str">
+        <v>T260703-00010</v>
+      </c>
+      <c r="B796" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C796" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D796" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E796" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="F796">
+        <v>0</v>
+      </c>
+      <c r="G796" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H796" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I796" t="str">
+        <v>2026-07-03 15:30</v>
+      </c>
+      <c r="J796" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K796">
+        <v>1</v>
+      </c>
+      <c r="L796" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M796" t="str">
+        <v>2026-07-03 20:29:47</v>
+      </c>
+      <c r="N796" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O796" s="1">
+        <v>0</v>
+      </c>
+      <c r="P796" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q796" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R796" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="str">
+        <v>T260703-00009</v>
+      </c>
+      <c r="B797" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C797" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D797" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E797" t="str">
+        <v>2026-07-03 10:00</v>
+      </c>
+      <c r="F797">
+        <v>0</v>
+      </c>
+      <c r="G797" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H797" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I797" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="J797" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K797">
+        <v>1</v>
+      </c>
+      <c r="L797" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M797" t="str">
+        <v>2026-07-03 20:29:05</v>
+      </c>
+      <c r="N797" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O797" s="1">
+        <v>0</v>
+      </c>
+      <c r="P797" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q797" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R797" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="str">
+        <v>T260703-00008</v>
+      </c>
+      <c r="B798" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C798" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D798" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E798" t="str">
+        <v>2026-07-03 16:30</v>
+      </c>
+      <c r="F798">
+        <v>0</v>
+      </c>
+      <c r="G798" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H798" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I798" t="str">
+        <v>2026-07-03 18:00</v>
+      </c>
+      <c r="J798" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K798">
+        <v>1</v>
+      </c>
+      <c r="L798" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M798" t="str">
+        <v>2026-07-03 18:39:34</v>
+      </c>
+      <c r="N798" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O798" s="1">
+        <v>0</v>
+      </c>
+      <c r="P798" t="str">
+        <v>20260703/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q798" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R798" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="str">
+        <v>T260703-00007</v>
+      </c>
+      <c r="B799" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C799" t="str">
+        <v>청주ARC(공파렛트 이동)</v>
+      </c>
+      <c r="D799" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(공파렛트 이동)</v>
+      </c>
+      <c r="E799" t="str">
+        <v>2026-07-03 11:40</v>
+      </c>
+      <c r="F799">
+        <v>0</v>
+      </c>
+      <c r="G799" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H799" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="I799" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="J799" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K799">
+        <v>1</v>
+      </c>
+      <c r="L799" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M799" t="str">
+        <v>2026-07-03 11:28:01</v>
+      </c>
+      <c r="N799" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O799" s="1">
+        <v>0</v>
+      </c>
+      <c r="P799" t="str">
+        <v>20260703청주-&gt; 안성FC/공파렛트이동</v>
+      </c>
+      <c r="Q799" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R799" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="str">
+        <v>T260703-00006</v>
+      </c>
+      <c r="B800" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C800" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D800" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E800" t="str">
+        <v>2026-07-03 11:55</v>
+      </c>
+      <c r="F800">
+        <v>0</v>
+      </c>
+      <c r="G800" t="str">
+        <v>하이얼(서울 벌크 출하)</v>
+      </c>
+      <c r="H800" t="str">
+        <v>서울 강남구 선릉로92길 38 도파민</v>
+      </c>
+      <c r="I800" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="J800" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K800">
+        <v>1</v>
+      </c>
+      <c r="L800" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M800" t="str">
+        <v>2026-07-03 11:26:22</v>
+      </c>
+      <c r="N800" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O800" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P800" t="str">
+        <v>20260703/하이얼_서울_벌크_출하</v>
+      </c>
+      <c r="Q800" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R800" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="str">
+        <v>T260703-00005</v>
+      </c>
+      <c r="B801" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C801" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D801" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E801" t="str">
+        <v>2026-07-03 11:00</v>
+      </c>
+      <c r="F801">
+        <v>0</v>
+      </c>
+      <c r="G801" t="str">
+        <v>파주 하이마트 물류</v>
+      </c>
+      <c r="H801" t="str">
+        <v>경기 파주시 탄현면 월롱산로 296 파주 하이마트 물류</v>
+      </c>
+      <c r="I801" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J801" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K801">
+        <v>1</v>
+      </c>
+      <c r="L801" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M801" t="str">
+        <v>2026-07-03 11:22:28</v>
+      </c>
+      <c r="N801" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O801" s="1">
+        <v>0</v>
+      </c>
+      <c r="P801" t="str">
+        <v>일코전자 파주 하이마트 물류</v>
+      </c>
+      <c r="Q801" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R801" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="str">
+        <v>T260703-00004</v>
+      </c>
+      <c r="B802" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C802" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D802" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지  안성FC</v>
+      </c>
+      <c r="E802" t="str">
+        <v>2026-07-03 09:30</v>
+      </c>
+      <c r="F802">
+        <v>0</v>
+      </c>
+      <c r="G802" t="str">
+        <v>TCL다코넷</v>
+      </c>
+      <c r="H802" t="str">
+        <v>경기 평택시 포승읍 희곡리 847 평택 켄달스퀘어 3층, 다코넷 37번 도크</v>
+      </c>
+      <c r="I802" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="J802" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K802">
+        <v>1</v>
+      </c>
+      <c r="L802" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M802" t="str">
+        <v>2026-07-03 11:21:17</v>
+      </c>
+      <c r="N802" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O802" s="1">
+        <v>0</v>
+      </c>
+      <c r="P802" t="str">
+        <v>TCL 다코넷</v>
+      </c>
+      <c r="Q802" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R802" t="str">
+        <v>TCL</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="str">
+        <v>T260703-00003</v>
+      </c>
+      <c r="B803" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C803" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D803" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E803" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="F803">
+        <v>0</v>
+      </c>
+      <c r="G803" t="str">
+        <v>이천 하이마트 물류</v>
+      </c>
+      <c r="H803" t="str">
+        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 물류</v>
+      </c>
+      <c r="I803" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J803" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K803">
+        <v>1</v>
+      </c>
+      <c r="L803" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M803" t="str">
+        <v>2026-07-03 11:19:40</v>
+      </c>
+      <c r="N803" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O803" s="1">
+        <v>0</v>
+      </c>
+      <c r="P803" t="str">
+        <v>일코전자 이천 하이마트 물류</v>
+      </c>
+      <c r="Q803" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R803" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="str">
+        <v>T260703-00002</v>
+      </c>
+      <c r="B804" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C804" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D804" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E804" t="str">
+        <v>2026-07-03 10:00</v>
+      </c>
+      <c r="F804">
+        <v>0</v>
+      </c>
+      <c r="G804" t="str">
+        <v>화성 하이마트 물류</v>
+      </c>
+      <c r="H804" t="str">
+        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 물류</v>
+      </c>
+      <c r="I804" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J804" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K804">
+        <v>1</v>
+      </c>
+      <c r="L804" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M804" t="str">
+        <v>2026-07-03 11:18:03</v>
+      </c>
+      <c r="N804" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O804" s="1">
+        <v>0</v>
+      </c>
+      <c r="P804" t="str">
+        <v>일코전자 화성 하이마트 물류</v>
+      </c>
+      <c r="Q804" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R804" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="str">
+        <v>T260703-00001</v>
+      </c>
+      <c r="B805" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C805" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D805" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E805" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="F805">
+        <v>0</v>
+      </c>
+      <c r="G805" t="str">
+        <v>인천 하이마트 물류</v>
+      </c>
+      <c r="H805" t="str">
+        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
+      </c>
+      <c r="I805" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J805" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K805">
+        <v>1</v>
+      </c>
+      <c r="L805" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M805" t="str">
+        <v>2026-07-03 11:16:52</v>
+      </c>
+      <c r="N805" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O805" s="1">
+        <v>0</v>
+      </c>
+      <c r="P805" t="str">
+        <v>일코전자 인천 하이마트 물류</v>
+      </c>
+      <c r="Q805" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R805" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="str">
+        <v>T260702-00027</v>
+      </c>
+      <c r="B806" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C806" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D806" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E806" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F806">
+        <v>1</v>
+      </c>
+      <c r="G806" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H806" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I806" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J806" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K806">
+        <v>1</v>
+      </c>
+      <c r="L806" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M806" t="str">
+        <v>2026-07-02 20:54:21</v>
+      </c>
+      <c r="N806" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O806" s="1">
+        <v>0</v>
+      </c>
+      <c r="P806" t="str">
+        <v/>
+      </c>
+      <c r="Q806" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R806" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="str">
+        <v>T260702-00026</v>
+      </c>
+      <c r="B807" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C807" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D807" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E807" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F807">
+        <v>1</v>
+      </c>
+      <c r="G807" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H807" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I807" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J807" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K807">
+        <v>1</v>
+      </c>
+      <c r="L807" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M807" t="str">
+        <v>2026-07-02 20:53:56</v>
+      </c>
+      <c r="N807" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O807" s="1">
+        <v>0</v>
+      </c>
+      <c r="P807" t="str">
+        <v/>
+      </c>
+      <c r="Q807" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R807" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="str">
+        <v>T260702-00025</v>
+      </c>
+      <c r="B808" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C808" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D808" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E808" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F808">
+        <v>3</v>
+      </c>
+      <c r="G808" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H808" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I808" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J808" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K808">
+        <v>1</v>
+      </c>
+      <c r="L808" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M808" t="str">
+        <v>2026-07-02 20:53:28</v>
+      </c>
+      <c r="N808" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O808" s="1">
+        <v>0</v>
+      </c>
+      <c r="P808" t="str">
+        <v/>
+      </c>
+      <c r="Q808" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R808" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="str">
+        <v>T260702-00024</v>
+      </c>
+      <c r="B809" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C809" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D809" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E809" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F809">
+        <v>0</v>
+      </c>
+      <c r="G809" t="str">
+        <v>용인ACP</v>
+      </c>
+      <c r="H809" t="str">
+        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
+      </c>
+      <c r="I809" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J809" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K809">
+        <v>1</v>
+      </c>
+      <c r="L809" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M809" t="str">
+        <v>2026-07-02 20:52:18</v>
+      </c>
+      <c r="N809" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O809" s="1">
+        <v>0</v>
+      </c>
+      <c r="P809" t="str">
+        <v/>
+      </c>
+      <c r="Q809" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R809" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="str">
+        <v>T260702-00023</v>
+      </c>
+      <c r="B810" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C810" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D810" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E810" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F810">
+        <v>1</v>
+      </c>
+      <c r="G810" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H810" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I810" t="str">
+        <v>2026-07-03 07:00</v>
+      </c>
+      <c r="J810" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K810">
+        <v>1</v>
+      </c>
+      <c r="L810" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M810" t="str">
+        <v>2026-07-02 20:51:59</v>
+      </c>
+      <c r="N810" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O810" s="1">
+        <v>0</v>
+      </c>
+      <c r="P810" t="str">
+        <v/>
+      </c>
+      <c r="Q810" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R810" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="str">
+        <v>T260702-00022</v>
+      </c>
+      <c r="B811" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C811" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D811" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E811" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F811">
+        <v>0</v>
+      </c>
+      <c r="G811" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H811" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I811" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J811" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K811">
+        <v>1</v>
+      </c>
+      <c r="L811" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M811" t="str">
+        <v>2026-07-02 20:51:32</v>
+      </c>
+      <c r="N811" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O811" s="1">
+        <v>0</v>
+      </c>
+      <c r="P811" t="str">
+        <v/>
+      </c>
+      <c r="Q811" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R811" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="str">
+        <v>T260702-00021</v>
+      </c>
+      <c r="B812" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C812" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D812" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E812" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F812">
+        <v>1</v>
+      </c>
+      <c r="G812" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H812" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I812" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J812" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K812">
+        <v>1</v>
+      </c>
+      <c r="L812" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M812" t="str">
+        <v>2026-07-02 20:51:14</v>
+      </c>
+      <c r="N812" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O812" s="1">
+        <v>0</v>
+      </c>
+      <c r="P812" t="str">
+        <v/>
+      </c>
+      <c r="Q812" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R812" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="str">
+        <v>T260702-00020</v>
+      </c>
+      <c r="B813" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C813" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D813" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E813" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F813">
+        <v>0</v>
+      </c>
+      <c r="G813" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H813" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I813" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J813" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K813">
+        <v>1</v>
+      </c>
+      <c r="L813" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M813" t="str">
+        <v>2026-07-02 20:50:54</v>
+      </c>
+      <c r="N813" s="1">
+        <v>280000</v>
+      </c>
+      <c r="O813" s="1">
+        <v>0</v>
+      </c>
+      <c r="P813" t="str">
+        <v/>
+      </c>
+      <c r="Q813" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R813" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="str">
+        <v>T260702-00019</v>
+      </c>
+      <c r="B814" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C814" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D814" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E814" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F814">
+        <v>0</v>
+      </c>
+      <c r="G814" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H814" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I814" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J814" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K814">
+        <v>1</v>
+      </c>
+      <c r="L814" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M814" t="str">
+        <v>2026-07-02 20:50:36</v>
+      </c>
+      <c r="N814" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O814" s="1">
+        <v>0</v>
+      </c>
+      <c r="P814" t="str">
+        <v/>
+      </c>
+      <c r="Q814" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R814" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="str">
+        <v>T260702-00018</v>
+      </c>
+      <c r="B815" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C815" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D815" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E815" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F815">
+        <v>1</v>
+      </c>
+      <c r="G815" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H815" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I815" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J815" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K815">
+        <v>1</v>
+      </c>
+      <c r="L815" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M815" t="str">
+        <v>2026-07-02 20:50:19</v>
+      </c>
+      <c r="N815" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O815" s="1">
+        <v>0</v>
+      </c>
+      <c r="P815" t="str">
+        <v/>
+      </c>
+      <c r="Q815" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R815" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="str">
+        <v>T260702-00017</v>
+      </c>
+      <c r="B816" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C816" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D816" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E816" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F816">
+        <v>1</v>
+      </c>
+      <c r="G816" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H816" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I816" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J816" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K816">
+        <v>1</v>
+      </c>
+      <c r="L816" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M816" t="str">
+        <v>2026-07-02 20:49:56</v>
+      </c>
+      <c r="N816" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O816" s="1">
+        <v>0</v>
+      </c>
+      <c r="P816" t="str">
+        <v/>
+      </c>
+      <c r="Q816" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R816" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="str">
+        <v>T260702-00016</v>
+      </c>
+      <c r="B817" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C817" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D817" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E817" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F817">
+        <v>0</v>
+      </c>
+      <c r="G817" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H817" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I817" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J817" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K817">
+        <v>1</v>
+      </c>
+      <c r="L817" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M817" t="str">
+        <v>2026-07-02 20:49:25</v>
+      </c>
+      <c r="N817" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O817" s="1">
+        <v>0</v>
+      </c>
+      <c r="P817" t="str">
+        <v/>
+      </c>
+      <c r="Q817" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R817" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="str">
+        <v>T260702-00015</v>
+      </c>
+      <c r="B818" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C818" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D818" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E818" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F818">
+        <v>1</v>
+      </c>
+      <c r="G818" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H818" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I818" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J818" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K818">
+        <v>1</v>
+      </c>
+      <c r="L818" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M818" t="str">
+        <v>2026-07-02 20:48:50</v>
+      </c>
+      <c r="N818" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O818" s="1">
+        <v>0</v>
+      </c>
+      <c r="P818" t="str">
+        <v/>
+      </c>
+      <c r="Q818" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R818" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="str">
+        <v>T260702-00014</v>
+      </c>
+      <c r="B819" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C819" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D819" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E819" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F819">
+        <v>0</v>
+      </c>
+      <c r="G819" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H819" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I819" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J819" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K819">
+        <v>1</v>
+      </c>
+      <c r="L819" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M819" t="str">
+        <v>2026-07-02 20:48:25</v>
+      </c>
+      <c r="N819" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O819" s="1">
+        <v>0</v>
+      </c>
+      <c r="P819" t="str">
+        <v/>
+      </c>
+      <c r="Q819" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R819" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="str">
+        <v>T260702-00013</v>
+      </c>
+      <c r="B820" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C820" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D820" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E820" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F820">
+        <v>0</v>
+      </c>
+      <c r="G820" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H820" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I820" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J820" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K820">
+        <v>1</v>
+      </c>
+      <c r="L820" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M820" t="str">
+        <v>2026-07-02 20:48:09</v>
+      </c>
+      <c r="N820" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O820" s="1">
+        <v>0</v>
+      </c>
+      <c r="P820" t="str">
+        <v/>
+      </c>
+      <c r="Q820" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R820" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="str">
+        <v>T260702-00012</v>
+      </c>
+      <c r="B821" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C821" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D821" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E821" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F821">
+        <v>2</v>
+      </c>
+      <c r="G821" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H821" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I821" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J821" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K821">
+        <v>1</v>
+      </c>
+      <c r="L821" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M821" t="str">
+        <v>2026-07-02 20:47:49</v>
+      </c>
+      <c r="N821" s="1">
+        <v>680000</v>
+      </c>
+      <c r="O821" s="1">
+        <v>0</v>
+      </c>
+      <c r="P821" t="str">
+        <v/>
+      </c>
+      <c r="Q821" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R821" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="str">
+        <v>T260702-00011</v>
+      </c>
+      <c r="B822" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C822" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D822" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E822" t="str">
+        <v>2026-07-02 17:50</v>
+      </c>
+      <c r="F822">
+        <v>0</v>
+      </c>
+      <c r="G822" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H822" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I822" t="str">
+        <v>2026-07-02 18:50</v>
+      </c>
+      <c r="J822" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K822">
+        <v>1</v>
+      </c>
+      <c r="L822" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M822" t="str">
+        <v>2026-07-02 20:44:59</v>
+      </c>
+      <c r="N822" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O822" s="1">
+        <v>0</v>
+      </c>
+      <c r="P822" t="str">
+        <v/>
+      </c>
+      <c r="Q822" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R822" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="str">
+        <v>T260702-00010</v>
+      </c>
+      <c r="B823" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C823" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D823" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E823" t="str">
+        <v>2026-07-02 13:30</v>
+      </c>
+      <c r="F823">
+        <v>0</v>
+      </c>
+      <c r="G823" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H823" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I823" t="str">
+        <v>2026-07-02 15:40</v>
+      </c>
+      <c r="J823" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K823">
+        <v>1</v>
+      </c>
+      <c r="L823" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M823" t="str">
+        <v>2026-07-02 20:44:26</v>
+      </c>
+      <c r="N823" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O823" s="1">
+        <v>0</v>
+      </c>
+      <c r="P823" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q823" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R823" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="str">
+        <v>T260702-00009</v>
+      </c>
+      <c r="B824" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C824" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D824" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E824" t="str">
+        <v>2026-07-02 10:00</v>
+      </c>
+      <c r="F824">
+        <v>0</v>
+      </c>
+      <c r="G824" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H824" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I824" t="str">
+        <v>2026-07-02 13:40</v>
+      </c>
+      <c r="J824" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K824">
+        <v>1</v>
+      </c>
+      <c r="L824" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M824" t="str">
+        <v>2026-07-02 20:43:37</v>
+      </c>
+      <c r="N824" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O824" s="1">
+        <v>0</v>
+      </c>
+      <c r="P824" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q824" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R824" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="str">
+        <v>T260702-00008</v>
+      </c>
+      <c r="B825" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C825" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D825" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E825" t="str">
+        <v>2026-07-02 17:00</v>
+      </c>
+      <c r="F825">
+        <v>0</v>
+      </c>
+      <c r="G825" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="H825" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="I825" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J825" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K825">
+        <v>1</v>
+      </c>
+      <c r="L825" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M825" t="str">
+        <v>2026-07-02 16:38:23</v>
+      </c>
+      <c r="N825" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O825" s="1">
+        <v>0</v>
+      </c>
+      <c r="P825" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="Q825" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R825" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="str">
+        <v>T260702-00007</v>
+      </c>
+      <c r="B826" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C826" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D826" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E826" t="str">
+        <v>2026-07-02 16:30</v>
+      </c>
+      <c r="F826">
+        <v>0</v>
+      </c>
+      <c r="G826" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H826" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I826" t="str">
+        <v>2026-07-02 18:00</v>
+      </c>
+      <c r="J826" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K826">
+        <v>1</v>
+      </c>
+      <c r="L826" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M826" t="str">
+        <v>2026-07-02 16:34:35</v>
+      </c>
+      <c r="N826" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O826" s="1">
+        <v>0</v>
+      </c>
+      <c r="P826" t="str">
+        <v>20260702/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q826" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R826" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="str">
+        <v>T260702-00006</v>
+      </c>
+      <c r="B827" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C827" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D827" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E827" t="str">
+        <v>2026-07-02 16:00</v>
+      </c>
+      <c r="F827">
+        <v>0</v>
+      </c>
+      <c r="G827" t="str">
+        <v>광주 하이마트 물류</v>
+      </c>
+      <c r="H827" t="str">
+        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
+      </c>
+      <c r="I827" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J827" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K827">
+        <v>1</v>
+      </c>
+      <c r="L827" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M827" t="str">
+        <v>2026-07-02 15:30:55</v>
+      </c>
+      <c r="N827" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O827" s="1">
+        <v>0</v>
+      </c>
+      <c r="P827" t="str">
+        <v>일코 광주 하이마트 물류</v>
+      </c>
+      <c r="Q827" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R827" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="str">
+        <v>T260702-00005</v>
+      </c>
+      <c r="B828" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C828" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D828" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E828" t="str">
+        <v>2026-07-02 14:30</v>
+      </c>
+      <c r="F828">
+        <v>0</v>
+      </c>
+      <c r="G828" t="str">
+        <v>마산 하이마트 물류</v>
+      </c>
+      <c r="H828" t="str">
+        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
+      </c>
+      <c r="I828" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J828" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K828">
+        <v>1</v>
+      </c>
+      <c r="L828" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M828" t="str">
+        <v>2026-07-02 13:44:41</v>
+      </c>
+      <c r="N828" s="1">
+        <v>380000</v>
+      </c>
+      <c r="O828" s="1">
+        <v>0</v>
+      </c>
+      <c r="P828" t="str">
+        <v>일코 마산 하이마트 물류</v>
+      </c>
+      <c r="Q828" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R828" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="str">
+        <v>T260702-00004</v>
+      </c>
+      <c r="B829" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C829" t="str">
+        <v>강릉 하이마트 물류</v>
+      </c>
+      <c r="D829" t="str">
+        <v>강원특별자치도 강릉시 연곡면 동해대로 4100-36 강릉 하이마트 물류</v>
+      </c>
+      <c r="E829" t="str">
+        <v>2026-07-02 13:30</v>
+      </c>
+      <c r="F829">
+        <v>0</v>
+      </c>
+      <c r="G829" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H829" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I829" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J829" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K829">
+        <v>1</v>
+      </c>
+      <c r="L829" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M829" t="str">
+        <v>2026-07-02 12:00:10</v>
+      </c>
+      <c r="N829" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O829" s="1">
+        <v>0</v>
+      </c>
+      <c r="P829" t="str">
+        <v>일코전자 강릉 하이마트 물류</v>
+      </c>
+      <c r="Q829" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R829" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="str">
+        <v>T260702-00003</v>
+      </c>
+      <c r="B830" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C830" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D830" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E830" t="str">
+        <v>2026-07-02 14:30</v>
+      </c>
+      <c r="F830">
+        <v>0</v>
+      </c>
+      <c r="G830" t="str">
+        <v>대구 하이마트 물류</v>
+      </c>
+      <c r="H830" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="I830" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J830" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K830">
+        <v>1</v>
+      </c>
+      <c r="L830" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M830" t="str">
+        <v>2026-07-02 11:59:32</v>
+      </c>
+      <c r="N830" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O830" s="1">
+        <v>0</v>
+      </c>
+      <c r="P830" t="str">
+        <v>일코전자 대구 하이마트 물류</v>
+      </c>
+      <c r="Q830" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R830" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="str">
+        <v>T260702-00002</v>
+      </c>
+      <c r="B831" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C831" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D831" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E831" t="str">
+        <v>2026-07-02 09:30</v>
+      </c>
+      <c r="F831">
+        <v>1</v>
+      </c>
+      <c r="G831" t="str">
+        <v>하이얼(대구2착)</v>
+      </c>
+      <c r="H831" t="str">
+        <v>대구 남구 양지로 25 대명자이 아파트</v>
+      </c>
+      <c r="I831" t="str">
+        <v>2026-07-02 15:00</v>
+      </c>
+      <c r="J831" t="str">
+        <v>1.5톤 윙바디</v>
+      </c>
+      <c r="K831">
+        <v>1</v>
+      </c>
+      <c r="L831" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M831" t="str">
+        <v>2026-07-02 09:20:07</v>
+      </c>
+      <c r="N831" s="1">
+        <v>220000</v>
+      </c>
+      <c r="O831" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P831" t="str">
+        <v>20260702/하이얼_대구 착지 2곳_벌크_출하</v>
+      </c>
+      <c r="Q831" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R831" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="str">
+        <v>T260702-00001</v>
+      </c>
+      <c r="B832" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C832" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D832" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E832" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="F832">
+        <v>0</v>
+      </c>
+      <c r="G832" t="str">
+        <v>로지스밸리인천포트(Logisvalley)</v>
+      </c>
+      <c r="H832" t="str">
+        <v>인천 연수구 인천타워대로599번길 60 로지스밸리인천포트(Logisvalley) 1층 13번(HTC)</v>
+      </c>
+      <c r="I832" t="str">
+        <v>2026-07-02 11:00</v>
+      </c>
+      <c r="J832" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K832">
+        <v>1</v>
+      </c>
+      <c r="L832" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M832" t="str">
+        <v>2026-07-02 09:17:29</v>
+      </c>
+      <c r="N832" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O832" s="1">
+        <v>0</v>
+      </c>
+      <c r="P832" t="str">
+        <v>패스트레인 출하</v>
+      </c>
+      <c r="Q832" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R832" t="str">
+        <v>패스트레인코리아</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="str">
+        <v>T260701-00026</v>
+      </c>
+      <c r="B833" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C833" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D833" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E833" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F833">
+        <v>1</v>
+      </c>
+      <c r="G833" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H833" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I833" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J833" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K833">
+        <v>1</v>
+      </c>
+      <c r="L833" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M833" t="str">
+        <v>2026-07-01 19:47:13</v>
+      </c>
+      <c r="N833" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O833" s="1">
+        <v>0</v>
+      </c>
+      <c r="P833" t="str">
+        <v/>
+      </c>
+      <c r="Q833" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R833" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="str">
+        <v>T260701-00025</v>
+      </c>
+      <c r="B834" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C834" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D834" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E834" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F834">
+        <v>2</v>
+      </c>
+      <c r="G834" t="str">
+        <v>원주ACP</v>
+      </c>
+      <c r="H834" t="str">
+        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
+      </c>
+      <c r="I834" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J834" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K834">
+        <v>1</v>
+      </c>
+      <c r="L834" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M834" t="str">
+        <v>2026-07-01 19:46:48</v>
+      </c>
+      <c r="N834" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O834" s="1">
+        <v>0</v>
+      </c>
+      <c r="P834" t="str">
+        <v/>
+      </c>
+      <c r="Q834" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R834" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="str">
+        <v>T260701-00024</v>
+      </c>
+      <c r="B835" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C835" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D835" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E835" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F835">
+        <v>1</v>
+      </c>
+      <c r="G835" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H835" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I835" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J835" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K835">
+        <v>1</v>
+      </c>
+      <c r="L835" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M835" t="str">
+        <v>2026-07-01 19:46:12</v>
+      </c>
+      <c r="N835" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O835" s="1">
+        <v>0</v>
+      </c>
+      <c r="P835" t="str">
+        <v/>
+      </c>
+      <c r="Q835" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R835" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="str">
+        <v>T260701-00023</v>
+      </c>
+      <c r="B836" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C836" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D836" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E836" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F836">
+        <v>3</v>
+      </c>
+      <c r="G836" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H836" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I836" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J836" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K836">
+        <v>1</v>
+      </c>
+      <c r="L836" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M836" t="str">
+        <v>2026-07-01 19:45:40</v>
+      </c>
+      <c r="N836" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O836" s="1">
+        <v>0</v>
+      </c>
+      <c r="P836" t="str">
+        <v/>
+      </c>
+      <c r="Q836" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R836" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="str">
+        <v>T260701-00022</v>
+      </c>
+      <c r="B837" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C837" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D837" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E837" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F837">
+        <v>0</v>
+      </c>
+      <c r="G837" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H837" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I837" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J837" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K837">
+        <v>1</v>
+      </c>
+      <c r="L837" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M837" t="str">
+        <v>2026-07-01 19:44:56</v>
+      </c>
+      <c r="N837" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O837" s="1">
+        <v>0</v>
+      </c>
+      <c r="P837" t="str">
+        <v/>
+      </c>
+      <c r="Q837" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R837" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="str">
+        <v>T260701-00021</v>
+      </c>
+      <c r="B838" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C838" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D838" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E838" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F838">
+        <v>1</v>
+      </c>
+      <c r="G838" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H838" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I838" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J838" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K838">
+        <v>1</v>
+      </c>
+      <c r="L838" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M838" t="str">
+        <v>2026-07-01 19:44:37</v>
+      </c>
+      <c r="N838" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O838" s="1">
+        <v>0</v>
+      </c>
+      <c r="P838" t="str">
+        <v/>
+      </c>
+      <c r="Q838" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R838" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="str">
+        <v>T260701-00020</v>
+      </c>
+      <c r="B839" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C839" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D839" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E839" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F839">
+        <v>2</v>
+      </c>
+      <c r="G839" t="str">
+        <v>속초ACP</v>
+      </c>
+      <c r="H839" t="str">
+        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
+      </c>
+      <c r="I839" t="str">
+        <v>2026-07-02 06:00</v>
+      </c>
+      <c r="J839" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K839">
+        <v>1</v>
+      </c>
+      <c r="L839" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M839" t="str">
+        <v>2026-07-01 19:44:05</v>
+      </c>
+      <c r="N839" s="1">
+        <v>320000</v>
+      </c>
+      <c r="O839" s="1">
+        <v>0</v>
+      </c>
+      <c r="P839" t="str">
+        <v/>
+      </c>
+      <c r="Q839" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R839" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="str">
+        <v>T260701-00019</v>
+      </c>
+      <c r="B840" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C840" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D840" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E840" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F840">
+        <v>0</v>
+      </c>
+      <c r="G840" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H840" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I840" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J840" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K840">
+        <v>1</v>
+      </c>
+      <c r="L840" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M840" t="str">
+        <v>2026-07-01 19:43:22</v>
+      </c>
+      <c r="N840" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O840" s="1">
+        <v>0</v>
+      </c>
+      <c r="P840" t="str">
+        <v/>
+      </c>
+      <c r="Q840" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R840" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="str">
+        <v>T260701-00018</v>
+      </c>
+      <c r="B841" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C841" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D841" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E841" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F841">
+        <v>1</v>
+      </c>
+      <c r="G841" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H841" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I841" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J841" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K841">
+        <v>1</v>
+      </c>
+      <c r="L841" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M841" t="str">
+        <v>2026-07-01 19:43:03</v>
+      </c>
+      <c r="N841" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O841" s="1">
+        <v>0</v>
+      </c>
+      <c r="P841" t="str">
+        <v/>
+      </c>
+      <c r="Q841" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R841" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="str">
+        <v>T260701-00017</v>
+      </c>
+      <c r="B842" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C842" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D842" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E842" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F842">
+        <v>0</v>
+      </c>
+      <c r="G842" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H842" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I842" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J842" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K842">
+        <v>1</v>
+      </c>
+      <c r="L842" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M842" t="str">
+        <v>2026-07-01 19:42:39</v>
+      </c>
+      <c r="N842" s="1">
+        <v>310000</v>
+      </c>
+      <c r="O842" s="1">
+        <v>0</v>
+      </c>
+      <c r="P842" t="str">
+        <v/>
+      </c>
+      <c r="Q842" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R842" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="str">
+        <v>T260701-00016</v>
+      </c>
+      <c r="B843" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C843" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D843" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E843" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F843">
+        <v>0</v>
+      </c>
+      <c r="G843" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H843" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I843" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J843" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K843">
+        <v>1</v>
+      </c>
+      <c r="L843" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M843" t="str">
+        <v>2026-07-01 19:42:17</v>
+      </c>
+      <c r="N843" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O843" s="1">
+        <v>0</v>
+      </c>
+      <c r="P843" t="str">
+        <v/>
+      </c>
+      <c r="Q843" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R843" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="str">
+        <v>T260701-00015</v>
+      </c>
+      <c r="B844" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C844" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D844" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E844" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F844">
+        <v>1</v>
+      </c>
+      <c r="G844" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H844" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I844" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J844" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K844">
+        <v>1</v>
+      </c>
+      <c r="L844" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M844" t="str">
+        <v>2026-07-01 19:42:02</v>
+      </c>
+      <c r="N844" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O844" s="1">
+        <v>0</v>
+      </c>
+      <c r="P844" t="str">
+        <v/>
+      </c>
+      <c r="Q844" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R844" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="str">
+        <v>T260701-00014</v>
+      </c>
+      <c r="B845" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C845" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D845" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E845" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F845">
+        <v>1</v>
+      </c>
+      <c r="G845" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H845" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I845" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J845" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K845">
+        <v>1</v>
+      </c>
+      <c r="L845" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M845" t="str">
+        <v>2026-07-01 19:41:41</v>
+      </c>
+      <c r="N845" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O845" s="1">
+        <v>0</v>
+      </c>
+      <c r="P845" t="str">
+        <v/>
+      </c>
+      <c r="Q845" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R845" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="str">
+        <v>T260701-00013</v>
+      </c>
+      <c r="B846" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C846" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D846" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E846" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F846">
+        <v>1</v>
+      </c>
+      <c r="G846" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H846" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I846" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J846" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K846">
+        <v>1</v>
+      </c>
+      <c r="L846" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M846" t="str">
+        <v>2026-07-01 19:41:08</v>
+      </c>
+      <c r="N846" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O846" s="1">
+        <v>0</v>
+      </c>
+      <c r="P846" t="str">
+        <v/>
+      </c>
+      <c r="Q846" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R846" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="str">
+        <v>T260701-00012</v>
+      </c>
+      <c r="B847" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C847" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D847" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E847" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F847">
+        <v>1</v>
+      </c>
+      <c r="G847" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H847" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I847" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J847" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K847">
+        <v>1</v>
+      </c>
+      <c r="L847" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M847" t="str">
+        <v>2026-07-01 19:40:45</v>
+      </c>
+      <c r="N847" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O847" s="1">
+        <v>0</v>
+      </c>
+      <c r="P847" t="str">
+        <v/>
+      </c>
+      <c r="Q847" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R847" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="str">
+        <v>T260701-00011</v>
+      </c>
+      <c r="B848" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C848" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D848" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E848" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F848">
+        <v>0</v>
+      </c>
+      <c r="G848" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H848" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I848" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J848" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K848">
+        <v>1</v>
+      </c>
+      <c r="L848" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M848" t="str">
+        <v>2026-07-01 19:40:21</v>
+      </c>
+      <c r="N848" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O848" s="1">
+        <v>0</v>
+      </c>
+      <c r="P848" t="str">
+        <v/>
+      </c>
+      <c r="Q848" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R848" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="str">
+        <v>T260701-00010</v>
+      </c>
+      <c r="B849" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C849" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D849" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E849" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F849">
+        <v>1</v>
+      </c>
+      <c r="G849" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H849" t="str">
+        <v>경산시 해오름길114-2 경산FDC</v>
+      </c>
+      <c r="I849" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J849" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K849">
+        <v>1</v>
+      </c>
+      <c r="L849" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M849" t="str">
+        <v>2026-07-01 19:40:04</v>
+      </c>
+      <c r="N849" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O849" s="1">
+        <v>0</v>
+      </c>
+      <c r="P849" t="str">
+        <v/>
+      </c>
+      <c r="Q849" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R849" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="str">
+        <v>T260701-00009</v>
+      </c>
+      <c r="B850" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C850" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D850" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E850" t="str">
+        <v>2026-07-01 17:30</v>
+      </c>
+      <c r="F850">
+        <v>0</v>
+      </c>
+      <c r="G850" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H850" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I850" t="str">
+        <v>2026-07-01 18:30</v>
+      </c>
+      <c r="J850" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K850">
+        <v>1</v>
+      </c>
+      <c r="L850" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M850" t="str">
+        <v>2026-07-01 19:31:35</v>
+      </c>
+      <c r="N850" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O850" s="1">
+        <v>0</v>
+      </c>
+      <c r="P850" t="str">
+        <v/>
+      </c>
+      <c r="Q850" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R850" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="str">
+        <v>T260701-00008</v>
+      </c>
+      <c r="B851" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C851" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D851" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E851" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="F851">
+        <v>0</v>
+      </c>
+      <c r="G851" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H851" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I851" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="J851" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K851">
+        <v>1</v>
+      </c>
+      <c r="L851" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M851" t="str">
+        <v>2026-07-01 19:31:02</v>
+      </c>
+      <c r="N851" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O851" s="1">
+        <v>0</v>
+      </c>
+      <c r="P851" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q851" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R851" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="str">
+        <v>T260701-00007</v>
+      </c>
+      <c r="B852" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C852" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D852" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E852" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F852">
+        <v>0</v>
+      </c>
+      <c r="G852" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H852" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I852" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="J852" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K852">
+        <v>1</v>
+      </c>
+      <c r="L852" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M852" t="str">
+        <v>2026-07-01 19:29:27</v>
+      </c>
+      <c r="N852" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O852" s="1">
+        <v>0</v>
+      </c>
+      <c r="P852" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q852" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R852" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="str">
+        <v>T260701-00006</v>
+      </c>
+      <c r="B853" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C853" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D853" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E853" t="str">
+        <v>2026-07-01 16:30</v>
+      </c>
+      <c r="F853">
+        <v>0</v>
+      </c>
+      <c r="G853" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H853" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I853" t="str">
+        <v>2026-07-01 18:00</v>
+      </c>
+      <c r="J853" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K853">
+        <v>1</v>
+      </c>
+      <c r="L853" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M853" t="str">
+        <v>2026-07-01 16:09:24</v>
+      </c>
+      <c r="N853" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O853" s="1">
+        <v>0</v>
+      </c>
+      <c r="P853" t="str">
+        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q853" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R853" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="str">
+        <v>T260701-00005</v>
+      </c>
+      <c r="B854" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C854" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D854" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E854" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="F854">
+        <v>0</v>
+      </c>
+      <c r="G854" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H854" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I854" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J854" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K854">
+        <v>1</v>
+      </c>
+      <c r="L854" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M854" t="str">
+        <v>2026-07-01 14:58:37</v>
+      </c>
+      <c r="N854" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O854" s="1">
+        <v>0</v>
+      </c>
+      <c r="P854" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q854" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R854" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="str">
+        <v>T260701-00004</v>
+      </c>
+      <c r="B855" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C855" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D855" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E855" t="str">
+        <v>2026-07-01 15:20</v>
+      </c>
+      <c r="F855">
+        <v>0</v>
+      </c>
+      <c r="G855" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H855" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I855" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J855" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K855">
+        <v>1</v>
+      </c>
+      <c r="L855" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M855" t="str">
+        <v>2026-07-01 14:53:20</v>
+      </c>
+      <c r="N855" s="1">
+        <v>440000</v>
+      </c>
+      <c r="O855" s="1">
+        <v>0</v>
+      </c>
+      <c r="P855" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q855" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R855" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="str">
+        <v>T260701-00003</v>
+      </c>
+      <c r="B856" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C856" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D856" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E856" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F856">
+        <v>0</v>
+      </c>
+      <c r="G856" t="str">
+        <v>하이얼(이천다코넷)</v>
+      </c>
+      <c r="H856" t="str">
+        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
+      </c>
+      <c r="I856" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J856" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K856">
+        <v>1</v>
+      </c>
+      <c r="L856" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M856" t="str">
+        <v>2026-07-01 10:15:38</v>
+      </c>
+      <c r="N856" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O856" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P856" t="str">
+        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
+      </c>
+      <c r="Q856" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R856" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="str">
+        <v>T260701-00002</v>
+      </c>
+      <c r="B857" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C857" t="str">
+        <v>청주ARC(디지탈태양)</v>
+      </c>
+      <c r="D857" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
+      </c>
+      <c r="E857" t="str">
+        <v>2026-07-01 08:30</v>
+      </c>
+      <c r="F857">
+        <v>0</v>
+      </c>
+      <c r="G857" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H857" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="I857" t="str">
+        <v>2026-07-01 10:30</v>
+      </c>
+      <c r="J857" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K857">
+        <v>1</v>
+      </c>
+      <c r="L857" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M857" t="str">
+        <v>2026-07-01 10:13:39</v>
+      </c>
+      <c r="N857" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O857" s="1">
+        <v>0</v>
+      </c>
+      <c r="P857" t="str">
+        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
+      </c>
+      <c r="Q857" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R857" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="str">
+        <v>T260701-00001</v>
+      </c>
+      <c r="B858" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C858" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D858" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E858" t="str">
+        <v>2026-07-01 09:00</v>
+      </c>
+      <c r="F858">
+        <v>0</v>
+      </c>
+      <c r="G858" t="str">
+        <v>현대클러스터 한강미사3차</v>
+      </c>
+      <c r="H858" t="str">
+        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
+      </c>
+      <c r="I858" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J858" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K858">
+        <v>1</v>
+      </c>
+      <c r="L858" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M858" t="str">
+        <v>2026-07-01 09:07:09</v>
+      </c>
+      <c r="N858" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O858" s="1">
+        <v>0</v>
+      </c>
+      <c r="P858" t="str">
+        <v>스마트윈드 출하</v>
+      </c>
+      <c r="Q858" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R858" t="str">
+        <v>스마트윈드</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R740"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R858"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R894"/>
+  <dimension ref="A1:R746"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -42156,8297 +42156,9 @@
         <v>고카트</v>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="str">
-        <v>T260707-00030</v>
-      </c>
-      <c r="B747" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C747" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D747" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E747" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F747">
-        <v>1</v>
-      </c>
-      <c r="G747" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H747" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I747" t="str">
-        <v>2026-07-08 08:00</v>
-      </c>
-      <c r="J747" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K747">
-        <v>1</v>
-      </c>
-      <c r="L747" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M747" t="str">
-        <v>2026-07-07 20:49:37</v>
-      </c>
-      <c r="N747" s="1">
-        <v>220000</v>
-      </c>
-      <c r="O747" s="1">
-        <v>0</v>
-      </c>
-      <c r="P747" t="str">
-        <v/>
-      </c>
-      <c r="Q747" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R747" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="str">
-        <v>T260707-00029</v>
-      </c>
-      <c r="B748" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C748" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D748" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E748" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F748">
-        <v>0</v>
-      </c>
-      <c r="G748" t="str">
-        <v>용인ACP</v>
-      </c>
-      <c r="H748" t="str">
-        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
-      </c>
-      <c r="I748" t="str">
-        <v>2026-07-08 07:00</v>
-      </c>
-      <c r="J748" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K748">
-        <v>1</v>
-      </c>
-      <c r="L748" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M748" t="str">
-        <v>2026-07-07 20:49:13</v>
-      </c>
-      <c r="N748" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O748" s="1">
-        <v>0</v>
-      </c>
-      <c r="P748" t="str">
-        <v/>
-      </c>
-      <c r="Q748" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R748" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" t="str">
-        <v>T260707-00028</v>
-      </c>
-      <c r="B749" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C749" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D749" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E749" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F749">
-        <v>1</v>
-      </c>
-      <c r="G749" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H749" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I749" t="str">
-        <v>2026-07-08 08:00</v>
-      </c>
-      <c r="J749" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K749">
-        <v>1</v>
-      </c>
-      <c r="L749" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M749" t="str">
-        <v>2026-07-07 20:48:56</v>
-      </c>
-      <c r="N749" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O749" s="1">
-        <v>0</v>
-      </c>
-      <c r="P749" t="str">
-        <v/>
-      </c>
-      <c r="Q749" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R749" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="str">
-        <v>T260707-00027</v>
-      </c>
-      <c r="B750" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C750" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D750" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E750" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F750">
-        <v>0</v>
-      </c>
-      <c r="G750" t="str">
-        <v>시흥ACP</v>
-      </c>
-      <c r="H750" t="str">
-        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
-      </c>
-      <c r="I750" t="str">
-        <v>2026-07-08 07:00</v>
-      </c>
-      <c r="J750" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K750">
-        <v>1</v>
-      </c>
-      <c r="L750" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M750" t="str">
-        <v>2026-07-07 20:48:32</v>
-      </c>
-      <c r="N750" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O750" s="1">
-        <v>0</v>
-      </c>
-      <c r="P750" t="str">
-        <v/>
-      </c>
-      <c r="Q750" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R750" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="str">
-        <v>T260707-00026</v>
-      </c>
-      <c r="B751" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C751" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D751" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E751" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F751">
-        <v>3</v>
-      </c>
-      <c r="G751" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H751" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I751" t="str">
-        <v>2026-07-08 07:00</v>
-      </c>
-      <c r="J751" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K751">
-        <v>1</v>
-      </c>
-      <c r="L751" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M751" t="str">
-        <v>2026-07-07 20:48:12</v>
-      </c>
-      <c r="N751" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O751" s="1">
-        <v>0</v>
-      </c>
-      <c r="P751" t="str">
-        <v/>
-      </c>
-      <c r="Q751" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R751" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="str">
-        <v>T260707-00025</v>
-      </c>
-      <c r="B752" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C752" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D752" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E752" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F752">
-        <v>0</v>
-      </c>
-      <c r="G752" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="H752" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="I752" t="str">
-        <v>2026-07-08 07:00</v>
-      </c>
-      <c r="J752" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K752">
-        <v>1</v>
-      </c>
-      <c r="L752" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M752" t="str">
-        <v>2026-07-07 20:47:33</v>
-      </c>
-      <c r="N752" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O752" s="1">
-        <v>0</v>
-      </c>
-      <c r="P752" t="str">
-        <v/>
-      </c>
-      <c r="Q752" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R752" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="str">
-        <v>T260707-00024</v>
-      </c>
-      <c r="B753" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C753" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D753" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E753" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F753">
-        <v>0</v>
-      </c>
-      <c r="G753" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H753" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I753" t="str">
-        <v>2026-07-07 21:00</v>
-      </c>
-      <c r="J753" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K753">
-        <v>1</v>
-      </c>
-      <c r="L753" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M753" t="str">
-        <v>2026-07-07 20:47:14</v>
-      </c>
-      <c r="N753" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O753" s="1">
-        <v>0</v>
-      </c>
-      <c r="P753" t="str">
-        <v/>
-      </c>
-      <c r="Q753" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R753" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="str">
-        <v>T260707-00023</v>
-      </c>
-      <c r="B754" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C754" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D754" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E754" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F754">
-        <v>0</v>
-      </c>
-      <c r="G754" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H754" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I754" t="str">
-        <v>2026-07-07 21:00</v>
-      </c>
-      <c r="J754" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K754">
-        <v>1</v>
-      </c>
-      <c r="L754" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M754" t="str">
-        <v>2026-07-07 20:47:00</v>
-      </c>
-      <c r="N754" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O754" s="1">
-        <v>0</v>
-      </c>
-      <c r="P754" t="str">
-        <v/>
-      </c>
-      <c r="Q754" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R754" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="str">
-        <v>T260707-00022</v>
-      </c>
-      <c r="B755" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C755" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D755" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E755" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F755">
-        <v>0</v>
-      </c>
-      <c r="G755" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="H755" t="str">
-        <v>충청남도 아산시 음봉면 월암로 265-16 가동 천안FDC</v>
-      </c>
-      <c r="I755" t="str">
-        <v>2026-07-07 21:00</v>
-      </c>
-      <c r="J755" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K755">
-        <v>1</v>
-      </c>
-      <c r="L755" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M755" t="str">
-        <v>2026-07-07 20:46:43</v>
-      </c>
-      <c r="N755" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O755" s="1">
-        <v>0</v>
-      </c>
-      <c r="P755" t="str">
-        <v/>
-      </c>
-      <c r="Q755" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R755" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="str">
-        <v>T260707-00021</v>
-      </c>
-      <c r="B756" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C756" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D756" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E756" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F756">
-        <v>0</v>
-      </c>
-      <c r="G756" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H756" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I756" t="str">
-        <v>2026-07-07 23:00</v>
-      </c>
-      <c r="J756" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K756">
-        <v>1</v>
-      </c>
-      <c r="L756" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M756" t="str">
-        <v>2026-07-07 20:46:28</v>
-      </c>
-      <c r="N756" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O756" s="1">
-        <v>0</v>
-      </c>
-      <c r="P756" t="str">
-        <v/>
-      </c>
-      <c r="Q756" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R756" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="str">
-        <v>T260707-00020</v>
-      </c>
-      <c r="B757" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C757" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D757" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E757" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F757">
-        <v>0</v>
-      </c>
-      <c r="G757" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H757" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I757" t="str">
-        <v>2026-07-07 21:00</v>
-      </c>
-      <c r="J757" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K757">
-        <v>1</v>
-      </c>
-      <c r="L757" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M757" t="str">
-        <v>2026-07-07 20:46:14</v>
-      </c>
-      <c r="N757" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O757" s="1">
-        <v>0</v>
-      </c>
-      <c r="P757" t="str">
-        <v/>
-      </c>
-      <c r="Q757" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R757" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="str">
-        <v>T260707-00019</v>
-      </c>
-      <c r="B758" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C758" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D758" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E758" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F758">
-        <v>1</v>
-      </c>
-      <c r="G758" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H758" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I758" t="str">
-        <v>2026-07-07 22:00</v>
-      </c>
-      <c r="J758" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K758">
-        <v>1</v>
-      </c>
-      <c r="L758" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M758" t="str">
-        <v>2026-07-07 20:45:57</v>
-      </c>
-      <c r="N758" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O758" s="1">
-        <v>0</v>
-      </c>
-      <c r="P758" t="str">
-        <v/>
-      </c>
-      <c r="Q758" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R758" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="str">
-        <v>T260707-00018</v>
-      </c>
-      <c r="B759" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C759" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D759" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E759" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F759">
-        <v>1</v>
-      </c>
-      <c r="G759" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H759" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I759" t="str">
-        <v>2026-07-07 23:00</v>
-      </c>
-      <c r="J759" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K759">
-        <v>1</v>
-      </c>
-      <c r="L759" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M759" t="str">
-        <v>2026-07-07 20:45:38</v>
-      </c>
-      <c r="N759" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O759" s="1">
-        <v>0</v>
-      </c>
-      <c r="P759" t="str">
-        <v/>
-      </c>
-      <c r="Q759" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R759" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="760">
-      <c r="A760" t="str">
-        <v>T260707-00017</v>
-      </c>
-      <c r="B760" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C760" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D760" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E760" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F760">
-        <v>0</v>
-      </c>
-      <c r="G760" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H760" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I760" t="str">
-        <v>2026-07-07 21:00</v>
-      </c>
-      <c r="J760" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K760">
-        <v>1</v>
-      </c>
-      <c r="L760" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M760" t="str">
-        <v>2026-07-07 20:45:15</v>
-      </c>
-      <c r="N760" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O760" s="1">
-        <v>0</v>
-      </c>
-      <c r="P760" t="str">
-        <v/>
-      </c>
-      <c r="Q760" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R760" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" t="str">
-        <v>T260707-00016</v>
-      </c>
-      <c r="B761" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C761" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D761" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E761" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F761">
-        <v>0</v>
-      </c>
-      <c r="G761" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H761" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I761" t="str">
-        <v>2026-07-07 21:00</v>
-      </c>
-      <c r="J761" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K761">
-        <v>1</v>
-      </c>
-      <c r="L761" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M761" t="str">
-        <v>2026-07-07 20:45:00</v>
-      </c>
-      <c r="N761" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O761" s="1">
-        <v>0</v>
-      </c>
-      <c r="P761" t="str">
-        <v/>
-      </c>
-      <c r="Q761" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R761" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="762">
-      <c r="A762" t="str">
-        <v>T260707-00015</v>
-      </c>
-      <c r="B762" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C762" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D762" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E762" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F762">
-        <v>1</v>
-      </c>
-      <c r="G762" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H762" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I762" t="str">
-        <v>2026-07-07 23:00</v>
-      </c>
-      <c r="J762" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K762">
-        <v>1</v>
-      </c>
-      <c r="L762" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M762" t="str">
-        <v>2026-07-07 20:44:42</v>
-      </c>
-      <c r="N762" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O762" s="1">
-        <v>0</v>
-      </c>
-      <c r="P762" t="str">
-        <v/>
-      </c>
-      <c r="Q762" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R762" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="763">
-      <c r="A763" t="str">
-        <v>T260707-00014</v>
-      </c>
-      <c r="B763" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C763" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D763" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E763" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F763">
-        <v>0</v>
-      </c>
-      <c r="G763" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H763" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I763" t="str">
-        <v>2026-07-07 21:00</v>
-      </c>
-      <c r="J763" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K763">
-        <v>1</v>
-      </c>
-      <c r="L763" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M763" t="str">
-        <v>2026-07-07 20:44:21</v>
-      </c>
-      <c r="N763" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O763" s="1">
-        <v>0</v>
-      </c>
-      <c r="P763" t="str">
-        <v/>
-      </c>
-      <c r="Q763" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R763" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="764">
-      <c r="A764" t="str">
-        <v>T260707-00013</v>
-      </c>
-      <c r="B764" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C764" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D764" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E764" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F764">
-        <v>1</v>
-      </c>
-      <c r="G764" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H764" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="I764" t="str">
-        <v>2026-07-07 23:00</v>
-      </c>
-      <c r="J764" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K764">
-        <v>1</v>
-      </c>
-      <c r="L764" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M764" t="str">
-        <v>2026-07-07 20:44:05</v>
-      </c>
-      <c r="N764" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O764" s="1">
-        <v>0</v>
-      </c>
-      <c r="P764" t="str">
-        <v/>
-      </c>
-      <c r="Q764" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R764" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" t="str">
-        <v>T260707-00012</v>
-      </c>
-      <c r="B765" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C765" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D765" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E765" t="str">
-        <v>2026-07-07 19:00</v>
-      </c>
-      <c r="F765">
-        <v>0</v>
-      </c>
-      <c r="G765" t="str">
-        <v>강릉FDC</v>
-      </c>
-      <c r="H765" t="str">
-        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
-      </c>
-      <c r="I765" t="str">
-        <v>2026-07-07 22:00</v>
-      </c>
-      <c r="J765" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K765">
-        <v>1</v>
-      </c>
-      <c r="L765" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M765" t="str">
-        <v>2026-07-07 20:43:44</v>
-      </c>
-      <c r="N765" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O765" s="1">
-        <v>0</v>
-      </c>
-      <c r="P765" t="str">
-        <v/>
-      </c>
-      <c r="Q765" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R765" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" t="str">
-        <v>T260707-00011</v>
-      </c>
-      <c r="B766" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C766" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D766" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E766" t="str">
-        <v>2026-07-07 17:40</v>
-      </c>
-      <c r="F766">
-        <v>0</v>
-      </c>
-      <c r="G766" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H766" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I766" t="str">
-        <v>2026-07-07 18:40</v>
-      </c>
-      <c r="J766" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K766">
-        <v>1</v>
-      </c>
-      <c r="L766" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M766" t="str">
-        <v>2026-07-07 20:41:08</v>
-      </c>
-      <c r="N766" s="1">
-        <v>130000</v>
-      </c>
-      <c r="O766" s="1">
-        <v>0</v>
-      </c>
-      <c r="P766" t="str">
-        <v/>
-      </c>
-      <c r="Q766" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R766" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" t="str">
-        <v>T260707-00010</v>
-      </c>
-      <c r="B767" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C767" t="str">
-        <v>화성FDC</v>
-      </c>
-      <c r="D767" t="str">
-        <v>경기 화성시 장안면 3.1만세로 506-21 화성FDC</v>
-      </c>
-      <c r="E767" t="str">
-        <v>2026-07-07 12:40</v>
-      </c>
-      <c r="F767">
-        <v>0</v>
-      </c>
-      <c r="G767" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="H767" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="I767" t="str">
-        <v>2026-07-07 14:40</v>
-      </c>
-      <c r="J767" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K767">
-        <v>1</v>
-      </c>
-      <c r="L767" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M767" t="str">
-        <v>2026-07-07 20:40:36</v>
-      </c>
-      <c r="N767" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O767" s="1">
-        <v>0</v>
-      </c>
-      <c r="P767" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="Q767" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R767" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="768">
-      <c r="A768" t="str">
-        <v>T260707-00009</v>
-      </c>
-      <c r="B768" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C768" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="D768" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5 김포FDC</v>
-      </c>
-      <c r="E768" t="str">
-        <v>2026-07-07 21:40</v>
-      </c>
-      <c r="F768">
-        <v>0</v>
-      </c>
-      <c r="G768" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="H768" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="I768" t="str">
-        <v>2026-07-08 08:40</v>
-      </c>
-      <c r="J768" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K768">
-        <v>1</v>
-      </c>
-      <c r="L768" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M768" t="str">
-        <v>2026-07-07 20:39:57</v>
-      </c>
-      <c r="N768" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O768" s="1">
-        <v>0</v>
-      </c>
-      <c r="P768" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="Q768" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R768" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="769">
-      <c r="A769" t="str">
-        <v>T260707-00008</v>
-      </c>
-      <c r="B769" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C769" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D769" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E769" t="str">
-        <v>2026-07-07 13:40</v>
-      </c>
-      <c r="F769">
-        <v>0</v>
-      </c>
-      <c r="G769" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H769" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I769" t="str">
-        <v>2026-07-07 15:40</v>
-      </c>
-      <c r="J769" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K769">
-        <v>1</v>
-      </c>
-      <c r="L769" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M769" t="str">
-        <v>2026-07-07 20:39:13</v>
-      </c>
-      <c r="N769" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O769" s="1">
-        <v>0</v>
-      </c>
-      <c r="P769" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q769" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R769" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="770">
-      <c r="A770" t="str">
-        <v>T260707-00007</v>
-      </c>
-      <c r="B770" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C770" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D770" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E770" t="str">
-        <v>2026-07-07 10:00</v>
-      </c>
-      <c r="F770">
-        <v>0</v>
-      </c>
-      <c r="G770" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H770" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I770" t="str">
-        <v>2026-07-07 13:40</v>
-      </c>
-      <c r="J770" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K770">
-        <v>1</v>
-      </c>
-      <c r="L770" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M770" t="str">
-        <v>2026-07-07 20:38:35</v>
-      </c>
-      <c r="N770" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O770" s="1">
-        <v>0</v>
-      </c>
-      <c r="P770" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q770" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R770" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="771">
-      <c r="A771" t="str">
-        <v>T260707-00006</v>
-      </c>
-      <c r="B771" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C771" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D771" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E771" t="str">
-        <v>2026-07-07 16:30</v>
-      </c>
-      <c r="F771">
-        <v>0</v>
-      </c>
-      <c r="G771" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H771" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I771" t="str">
-        <v>2026-07-07 18:00</v>
-      </c>
-      <c r="J771" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K771">
-        <v>1</v>
-      </c>
-      <c r="L771" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M771" t="str">
-        <v>2026-07-07 15:57:50</v>
-      </c>
-      <c r="N771" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O771" s="1">
-        <v>0</v>
-      </c>
-      <c r="P771" t="str">
-        <v>20260707/경동택배_남이가마258 영업소_파렛트 출하</v>
-      </c>
-      <c r="Q771" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R771" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="772">
-      <c r="A772" t="str">
-        <v>T260707-00005</v>
-      </c>
-      <c r="B772" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C772" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D772" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E772" t="str">
-        <v>2026-07-07 11:40</v>
-      </c>
-      <c r="F772">
-        <v>0</v>
-      </c>
-      <c r="G772" t="str">
-        <v>캐리어 신양지 물류</v>
-      </c>
-      <c r="H772" t="str">
-        <v>경기 용인시 처인구 원삼면 죽양대로1626번길 42 캐리어 신양지 물류</v>
-      </c>
-      <c r="I772" t="str">
-        <v>2026-07-07 14:00</v>
-      </c>
-      <c r="J772" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K772">
-        <v>1</v>
-      </c>
-      <c r="L772" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M772" t="str">
-        <v>2026-07-07 10:57:56</v>
-      </c>
-      <c r="N772" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O772" s="1">
-        <v>0</v>
-      </c>
-      <c r="P772" t="str">
-        <v>명경전자 캐리어 신양지 물류</v>
-      </c>
-      <c r="Q772" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R772" t="str">
-        <v>명경전자</v>
-      </c>
-    </row>
-    <row r="773">
-      <c r="A773" t="str">
-        <v>T260707-00004</v>
-      </c>
-      <c r="B773" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C773" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D773" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E773" t="str">
-        <v>2026-07-07 11:20</v>
-      </c>
-      <c r="F773">
-        <v>0</v>
-      </c>
-      <c r="G773" t="str">
-        <v>캐리어 신양지 물류</v>
-      </c>
-      <c r="H773" t="str">
-        <v>경기 용인시 처인구 원삼면 죽양대로1626번길 42 캐리어 신양지 물류</v>
-      </c>
-      <c r="I773" t="str">
-        <v>2026-07-07 01:20</v>
-      </c>
-      <c r="J773" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K773">
-        <v>1</v>
-      </c>
-      <c r="L773" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M773" t="str">
-        <v>2026-07-07 10:20:11</v>
-      </c>
-      <c r="N773" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O773" s="1">
-        <v>0</v>
-      </c>
-      <c r="P773" t="str">
-        <v>명경전자 캐리어 신양지 물류</v>
-      </c>
-      <c r="Q773" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R773" t="str">
-        <v>명경전자</v>
-      </c>
-    </row>
-    <row r="774">
-      <c r="A774" t="str">
-        <v>T260707-00003</v>
-      </c>
-      <c r="B774" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C774" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D774" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E774" t="str">
-        <v>2026-07-07 10:20</v>
-      </c>
-      <c r="F774">
-        <v>0</v>
-      </c>
-      <c r="G774" t="str">
-        <v>캐리어 신양지 물류</v>
-      </c>
-      <c r="H774" t="str">
-        <v>경기 용인시 처인구 원삼면 죽양대로1626번길 42 캐리어 신양지 물류</v>
-      </c>
-      <c r="I774" t="str">
-        <v>2026-07-07 01:20</v>
-      </c>
-      <c r="J774" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K774">
-        <v>1</v>
-      </c>
-      <c r="L774" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M774" t="str">
-        <v>2026-07-07 10:19:53</v>
-      </c>
-      <c r="N774" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O774" s="1">
-        <v>0</v>
-      </c>
-      <c r="P774" t="str">
-        <v>명경전자 캐리어 신양지 물류</v>
-      </c>
-      <c r="Q774" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R774" t="str">
-        <v>명경전자</v>
-      </c>
-    </row>
-    <row r="775">
-      <c r="A775" t="str">
-        <v>T260707-00002</v>
-      </c>
-      <c r="B775" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C775" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D775" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E775" t="str">
-        <v>2026-07-07 09:20</v>
-      </c>
-      <c r="F775">
-        <v>0</v>
-      </c>
-      <c r="G775" t="str">
-        <v>캐리어 신양지 물류</v>
-      </c>
-      <c r="H775" t="str">
-        <v>경기 용인시 처인구 원삼면 죽양대로1626번길 42 캐리어 신양지 물류</v>
-      </c>
-      <c r="I775" t="str">
-        <v>2026-07-07 11:20</v>
-      </c>
-      <c r="J775" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K775">
-        <v>1</v>
-      </c>
-      <c r="L775" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M775" t="str">
-        <v>2026-07-07 10:19:33</v>
-      </c>
-      <c r="N775" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O775" s="1">
-        <v>0</v>
-      </c>
-      <c r="P775" t="str">
-        <v>명경전자 캐리어 신양지 물류</v>
-      </c>
-      <c r="Q775" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R775" t="str">
-        <v>명경전자</v>
-      </c>
-    </row>
-    <row r="776">
-      <c r="A776" t="str">
-        <v>T260707-00001</v>
-      </c>
-      <c r="B776" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C776" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D776" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E776" t="str">
-        <v>2026-07-07 09:00</v>
-      </c>
-      <c r="F776">
-        <v>0</v>
-      </c>
-      <c r="G776" t="str">
-        <v>캐리어 신양지 물류</v>
-      </c>
-      <c r="H776" t="str">
-        <v>경기 용인시 처인구 원삼면 죽양대로1626번길 42 캐리어 신양지 물류</v>
-      </c>
-      <c r="I776" t="str">
-        <v>2026-07-07 11:00</v>
-      </c>
-      <c r="J776" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K776">
-        <v>1</v>
-      </c>
-      <c r="L776" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M776" t="str">
-        <v>2026-07-07 09:21:00</v>
-      </c>
-      <c r="N776" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O776" s="1">
-        <v>0</v>
-      </c>
-      <c r="P776" t="str">
-        <v>명경전자 캐리어 신양지 물류</v>
-      </c>
-      <c r="Q776" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R776" t="str">
-        <v>명경전자</v>
-      </c>
-    </row>
-    <row r="777">
-      <c r="A777" t="str">
-        <v>T260706-00031</v>
-      </c>
-      <c r="B777" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C777" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D777" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E777" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F777">
-        <v>0</v>
-      </c>
-      <c r="G777" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H777" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I777" t="str">
-        <v>2026-07-07 07:00</v>
-      </c>
-      <c r="J777" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K777">
-        <v>1</v>
-      </c>
-      <c r="L777" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M777" t="str">
-        <v>2026-07-06 20:43:10</v>
-      </c>
-      <c r="N777" s="1">
-        <v>130000</v>
-      </c>
-      <c r="O777" s="1">
-        <v>0</v>
-      </c>
-      <c r="P777" t="str">
-        <v/>
-      </c>
-      <c r="Q777" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R777" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="778">
-      <c r="A778" t="str">
-        <v>T260706-00030</v>
-      </c>
-      <c r="B778" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C778" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D778" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E778" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F778">
-        <v>1</v>
-      </c>
-      <c r="G778" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H778" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I778" t="str">
-        <v>2026-07-07 08:00</v>
-      </c>
-      <c r="J778" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K778">
-        <v>1</v>
-      </c>
-      <c r="L778" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M778" t="str">
-        <v>2026-07-06 20:42:49</v>
-      </c>
-      <c r="N778" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O778" s="1">
-        <v>0</v>
-      </c>
-      <c r="P778" t="str">
-        <v/>
-      </c>
-      <c r="Q778" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R778" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="779">
-      <c r="A779" t="str">
-        <v>T260706-00029</v>
-      </c>
-      <c r="B779" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C779" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D779" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E779" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F779">
-        <v>2</v>
-      </c>
-      <c r="G779" t="str">
-        <v>원주ACP</v>
-      </c>
-      <c r="H779" t="str">
-        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
-      </c>
-      <c r="I779" t="str">
-        <v>2026-07-07 07:00</v>
-      </c>
-      <c r="J779" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K779">
-        <v>1</v>
-      </c>
-      <c r="L779" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M779" t="str">
-        <v>2026-07-06 20:42:20</v>
-      </c>
-      <c r="N779" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O779" s="1">
-        <v>0</v>
-      </c>
-      <c r="P779" t="str">
-        <v/>
-      </c>
-      <c r="Q779" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R779" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="780">
-      <c r="A780" t="str">
-        <v>T260706-00028</v>
-      </c>
-      <c r="B780" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C780" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D780" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E780" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F780">
-        <v>1</v>
-      </c>
-      <c r="G780" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H780" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I780" t="str">
-        <v>2026-07-07 08:00</v>
-      </c>
-      <c r="J780" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K780">
-        <v>1</v>
-      </c>
-      <c r="L780" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M780" t="str">
-        <v>2026-07-06 20:41:21</v>
-      </c>
-      <c r="N780" s="1">
-        <v>170000</v>
-      </c>
-      <c r="O780" s="1">
-        <v>0</v>
-      </c>
-      <c r="P780" t="str">
-        <v/>
-      </c>
-      <c r="Q780" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R780" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="781">
-      <c r="A781" t="str">
-        <v>T260706-00027</v>
-      </c>
-      <c r="B781" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C781" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D781" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E781" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F781">
-        <v>1</v>
-      </c>
-      <c r="G781" t="str">
-        <v>속초ACP</v>
-      </c>
-      <c r="H781" t="str">
-        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
-      </c>
-      <c r="I781" t="str">
-        <v>2026-07-07 08:00</v>
-      </c>
-      <c r="J781" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K781">
-        <v>1</v>
-      </c>
-      <c r="L781" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M781" t="str">
-        <v>2026-07-06 20:40:49</v>
-      </c>
-      <c r="N781" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O781" s="1">
-        <v>0</v>
-      </c>
-      <c r="P781" t="str">
-        <v/>
-      </c>
-      <c r="Q781" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R781" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="782">
-      <c r="A782" t="str">
-        <v>T260706-00026</v>
-      </c>
-      <c r="B782" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C782" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D782" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E782" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F782">
-        <v>3</v>
-      </c>
-      <c r="G782" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H782" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I782" t="str">
-        <v>2026-07-07 07:00</v>
-      </c>
-      <c r="J782" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K782">
-        <v>1</v>
-      </c>
-      <c r="L782" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M782" t="str">
-        <v>2026-07-06 20:40:12</v>
-      </c>
-      <c r="N782" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O782" s="1">
-        <v>0</v>
-      </c>
-      <c r="P782" t="str">
-        <v/>
-      </c>
-      <c r="Q782" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R782" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="783">
-      <c r="A783" t="str">
-        <v>T260706-00025</v>
-      </c>
-      <c r="B783" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C783" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D783" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E783" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F783">
-        <v>0</v>
-      </c>
-      <c r="G783" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H783" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I783" t="str">
-        <v>2026-07-06 22:00</v>
-      </c>
-      <c r="J783" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K783">
-        <v>1</v>
-      </c>
-      <c r="L783" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M783" t="str">
-        <v>2026-07-06 20:39:25</v>
-      </c>
-      <c r="N783" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O783" s="1">
-        <v>0</v>
-      </c>
-      <c r="P783" t="str">
-        <v/>
-      </c>
-      <c r="Q783" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R783" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="784">
-      <c r="A784" t="str">
-        <v>T260706-00024</v>
-      </c>
-      <c r="B784" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C784" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D784" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E784" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F784">
-        <v>0</v>
-      </c>
-      <c r="G784" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="H784" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="I784" t="str">
-        <v>2026-07-07 07:00</v>
-      </c>
-      <c r="J784" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K784">
-        <v>1</v>
-      </c>
-      <c r="L784" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M784" t="str">
-        <v>2026-07-06 20:39:07</v>
-      </c>
-      <c r="N784" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O784" s="1">
-        <v>0</v>
-      </c>
-      <c r="P784" t="str">
-        <v/>
-      </c>
-      <c r="Q784" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R784" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="785">
-      <c r="A785" t="str">
-        <v>T260706-00023</v>
-      </c>
-      <c r="B785" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C785" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D785" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E785" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F785">
-        <v>0</v>
-      </c>
-      <c r="G785" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H785" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I785" t="str">
-        <v>2026-07-06 21:00</v>
-      </c>
-      <c r="J785" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K785">
-        <v>1</v>
-      </c>
-      <c r="L785" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M785" t="str">
-        <v>2026-07-06 20:38:47</v>
-      </c>
-      <c r="N785" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O785" s="1">
-        <v>0</v>
-      </c>
-      <c r="P785" t="str">
-        <v/>
-      </c>
-      <c r="Q785" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R785" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="786">
-      <c r="A786" t="str">
-        <v>T260706-00022</v>
-      </c>
-      <c r="B786" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C786" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D786" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E786" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F786">
-        <v>0</v>
-      </c>
-      <c r="G786" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H786" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I786" t="str">
-        <v>2026-07-06 21:00</v>
-      </c>
-      <c r="J786" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K786">
-        <v>1</v>
-      </c>
-      <c r="L786" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M786" t="str">
-        <v>2026-07-06 20:38:33</v>
-      </c>
-      <c r="N786" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O786" s="1">
-        <v>0</v>
-      </c>
-      <c r="P786" t="str">
-        <v/>
-      </c>
-      <c r="Q786" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R786" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="787">
-      <c r="A787" t="str">
-        <v>T260706-00021</v>
-      </c>
-      <c r="B787" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C787" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D787" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E787" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F787">
-        <v>0</v>
-      </c>
-      <c r="G787" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="H787" t="str">
-        <v>충청남도 아산시 음봉면 월암로 265-16 가동 천안FDC</v>
-      </c>
-      <c r="I787" t="str">
-        <v>2026-07-06 21:00</v>
-      </c>
-      <c r="J787" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K787">
-        <v>1</v>
-      </c>
-      <c r="L787" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M787" t="str">
-        <v>2026-07-06 20:38:16</v>
-      </c>
-      <c r="N787" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O787" s="1">
-        <v>0</v>
-      </c>
-      <c r="P787" t="str">
-        <v/>
-      </c>
-      <c r="Q787" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R787" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="788">
-      <c r="A788" t="str">
-        <v>T260706-00020</v>
-      </c>
-      <c r="B788" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C788" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D788" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E788" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F788">
-        <v>1</v>
-      </c>
-      <c r="G788" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H788" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I788" t="str">
-        <v>2026-07-06 23:00</v>
-      </c>
-      <c r="J788" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K788">
-        <v>1</v>
-      </c>
-      <c r="L788" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M788" t="str">
-        <v>2026-07-06 20:37:59</v>
-      </c>
-      <c r="N788" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O788" s="1">
-        <v>0</v>
-      </c>
-      <c r="P788" t="str">
-        <v/>
-      </c>
-      <c r="Q788" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R788" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="789">
-      <c r="A789" t="str">
-        <v>T260706-00019</v>
-      </c>
-      <c r="B789" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C789" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D789" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E789" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F789">
-        <v>0</v>
-      </c>
-      <c r="G789" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="H789" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="I789" t="str">
-        <v>2026-07-06 22:00</v>
-      </c>
-      <c r="J789" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K789">
-        <v>1</v>
-      </c>
-      <c r="L789" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M789" t="str">
-        <v>2026-07-06 20:37:38</v>
-      </c>
-      <c r="N789" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O789" s="1">
-        <v>0</v>
-      </c>
-      <c r="P789" t="str">
-        <v/>
-      </c>
-      <c r="Q789" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R789" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="790">
-      <c r="A790" t="str">
-        <v>T260706-00018</v>
-      </c>
-      <c r="B790" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C790" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D790" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E790" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F790">
-        <v>1</v>
-      </c>
-      <c r="G790" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H790" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I790" t="str">
-        <v>2026-07-06 22:00</v>
-      </c>
-      <c r="J790" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K790">
-        <v>1</v>
-      </c>
-      <c r="L790" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M790" t="str">
-        <v>2026-07-06 20:37:22</v>
-      </c>
-      <c r="N790" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O790" s="1">
-        <v>0</v>
-      </c>
-      <c r="P790" t="str">
-        <v/>
-      </c>
-      <c r="Q790" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R790" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="791">
-      <c r="A791" t="str">
-        <v>T260706-00017</v>
-      </c>
-      <c r="B791" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C791" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D791" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E791" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F791">
-        <v>0</v>
-      </c>
-      <c r="G791" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H791" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I791" t="str">
-        <v>2026-07-06 21:00</v>
-      </c>
-      <c r="J791" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K791">
-        <v>1</v>
-      </c>
-      <c r="L791" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M791" t="str">
-        <v>2026-07-06 20:36:54</v>
-      </c>
-      <c r="N791" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O791" s="1">
-        <v>0</v>
-      </c>
-      <c r="P791" t="str">
-        <v/>
-      </c>
-      <c r="Q791" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R791" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="792">
-      <c r="A792" t="str">
-        <v>T260706-00016</v>
-      </c>
-      <c r="B792" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C792" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D792" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E792" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F792">
-        <v>1</v>
-      </c>
-      <c r="G792" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H792" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I792" t="str">
-        <v>2026-07-06 22:00</v>
-      </c>
-      <c r="J792" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K792">
-        <v>1</v>
-      </c>
-      <c r="L792" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M792" t="str">
-        <v>2026-07-06 20:35:29</v>
-      </c>
-      <c r="N792" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O792" s="1">
-        <v>0</v>
-      </c>
-      <c r="P792" t="str">
-        <v/>
-      </c>
-      <c r="Q792" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R792" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="793">
-      <c r="A793" t="str">
-        <v>T260706-00015</v>
-      </c>
-      <c r="B793" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C793" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D793" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E793" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F793">
-        <v>0</v>
-      </c>
-      <c r="G793" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H793" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I793" t="str">
-        <v>2026-07-06 23:00</v>
-      </c>
-      <c r="J793" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K793">
-        <v>1</v>
-      </c>
-      <c r="L793" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M793" t="str">
-        <v>2026-07-06 20:35:06</v>
-      </c>
-      <c r="N793" s="1">
-        <v>480000</v>
-      </c>
-      <c r="O793" s="1">
-        <v>0</v>
-      </c>
-      <c r="P793" t="str">
-        <v/>
-      </c>
-      <c r="Q793" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R793" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" t="str">
-        <v>T260706-00014</v>
-      </c>
-      <c r="B794" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C794" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D794" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E794" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F794">
-        <v>0</v>
-      </c>
-      <c r="G794" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H794" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I794" t="str">
-        <v>2026-07-06 21:00</v>
-      </c>
-      <c r="J794" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K794">
-        <v>1</v>
-      </c>
-      <c r="L794" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M794" t="str">
-        <v>2026-07-06 20:34:46</v>
-      </c>
-      <c r="N794" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O794" s="1">
-        <v>0</v>
-      </c>
-      <c r="P794" t="str">
-        <v/>
-      </c>
-      <c r="Q794" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R794" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="795">
-      <c r="A795" t="str">
-        <v>T260706-00013</v>
-      </c>
-      <c r="B795" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C795" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D795" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E795" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F795">
-        <v>0</v>
-      </c>
-      <c r="G795" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H795" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I795" t="str">
-        <v>2026-07-07 06:00</v>
-      </c>
-      <c r="J795" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K795">
-        <v>1</v>
-      </c>
-      <c r="L795" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M795" t="str">
-        <v>2026-07-06 20:34:27</v>
-      </c>
-      <c r="N795" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O795" s="1">
-        <v>0</v>
-      </c>
-      <c r="P795" t="str">
-        <v/>
-      </c>
-      <c r="Q795" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R795" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="796">
-      <c r="A796" t="str">
-        <v>T260706-00012</v>
-      </c>
-      <c r="B796" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C796" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D796" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E796" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F796">
-        <v>0</v>
-      </c>
-      <c r="G796" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H796" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I796" t="str">
-        <v>2026-07-06 21:00</v>
-      </c>
-      <c r="J796" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K796">
-        <v>1</v>
-      </c>
-      <c r="L796" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M796" t="str">
-        <v>2026-07-06 20:33:52</v>
-      </c>
-      <c r="N796" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O796" s="1">
-        <v>0</v>
-      </c>
-      <c r="P796" t="str">
-        <v/>
-      </c>
-      <c r="Q796" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R796" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="797">
-      <c r="A797" t="str">
-        <v>T260706-00011</v>
-      </c>
-      <c r="B797" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C797" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D797" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E797" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F797">
-        <v>0</v>
-      </c>
-      <c r="G797" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H797" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I797" t="str">
-        <v>2026-07-06 23:00</v>
-      </c>
-      <c r="J797" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K797">
-        <v>1</v>
-      </c>
-      <c r="L797" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M797" t="str">
-        <v>2026-07-06 20:33:32</v>
-      </c>
-      <c r="N797" s="1">
-        <v>420000</v>
-      </c>
-      <c r="O797" s="1">
-        <v>0</v>
-      </c>
-      <c r="P797" t="str">
-        <v/>
-      </c>
-      <c r="Q797" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R797" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="798">
-      <c r="A798" t="str">
-        <v>T260706-00010</v>
-      </c>
-      <c r="B798" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C798" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D798" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E798" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F798">
-        <v>0</v>
-      </c>
-      <c r="G798" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H798" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I798" t="str">
-        <v>2026-07-06 21:00</v>
-      </c>
-      <c r="J798" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K798">
-        <v>1</v>
-      </c>
-      <c r="L798" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M798" t="str">
-        <v>2026-07-06 20:33:02</v>
-      </c>
-      <c r="N798" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O798" s="1">
-        <v>0</v>
-      </c>
-      <c r="P798" t="str">
-        <v/>
-      </c>
-      <c r="Q798" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R798" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="799">
-      <c r="A799" t="str">
-        <v>T260706-00009</v>
-      </c>
-      <c r="B799" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C799" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D799" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E799" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F799">
-        <v>1</v>
-      </c>
-      <c r="G799" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H799" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="I799" t="str">
-        <v>2026-07-06 23:00</v>
-      </c>
-      <c r="J799" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K799">
-        <v>1</v>
-      </c>
-      <c r="L799" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M799" t="str">
-        <v>2026-07-06 20:32:45</v>
-      </c>
-      <c r="N799" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O799" s="1">
-        <v>0</v>
-      </c>
-      <c r="P799" t="str">
-        <v/>
-      </c>
-      <c r="Q799" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R799" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="800">
-      <c r="A800" t="str">
-        <v>T260706-00008</v>
-      </c>
-      <c r="B800" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C800" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D800" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E800" t="str">
-        <v>2026-07-06 19:00</v>
-      </c>
-      <c r="F800">
-        <v>1</v>
-      </c>
-      <c r="G800" t="str">
-        <v>강릉FDC</v>
-      </c>
-      <c r="H800" t="str">
-        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
-      </c>
-      <c r="I800" t="str">
-        <v>2026-07-06 23:00</v>
-      </c>
-      <c r="J800" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K800">
-        <v>1</v>
-      </c>
-      <c r="L800" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M800" t="str">
-        <v>2026-07-06 20:32:23</v>
-      </c>
-      <c r="N800" s="1">
-        <v>330000</v>
-      </c>
-      <c r="O800" s="1">
-        <v>0</v>
-      </c>
-      <c r="P800" t="str">
-        <v/>
-      </c>
-      <c r="Q800" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R800" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="801">
-      <c r="A801" t="str">
-        <v>T260706-00007</v>
-      </c>
-      <c r="B801" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C801" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D801" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E801" t="str">
-        <v>2026-07-06 17:30</v>
-      </c>
-      <c r="F801">
-        <v>0</v>
-      </c>
-      <c r="G801" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H801" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I801" t="str">
-        <v>2026-07-06 18:30</v>
-      </c>
-      <c r="J801" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K801">
-        <v>1</v>
-      </c>
-      <c r="L801" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M801" t="str">
-        <v>2026-07-06 20:29:06</v>
-      </c>
-      <c r="N801" s="1">
-        <v>130000</v>
-      </c>
-      <c r="O801" s="1">
-        <v>0</v>
-      </c>
-      <c r="P801" t="str">
-        <v/>
-      </c>
-      <c r="Q801" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R801" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="802">
-      <c r="A802" t="str">
-        <v>T260706-00006</v>
-      </c>
-      <c r="B802" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C802" t="str">
-        <v>라꾸스토리</v>
-      </c>
-      <c r="D802" t="str">
-        <v>충북 옥천군 군서면 동평리 130 라꾸스토리</v>
-      </c>
-      <c r="E802" t="str">
-        <v>2026-07-06 13:30</v>
-      </c>
-      <c r="F802">
-        <v>0</v>
-      </c>
-      <c r="G802" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H802" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I802" t="str">
-        <v>2026-07-06 15:30</v>
-      </c>
-      <c r="J802" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K802">
-        <v>1</v>
-      </c>
-      <c r="L802" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M802" t="str">
-        <v>2026-07-06 20:28:33</v>
-      </c>
-      <c r="N802" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O802" s="1">
-        <v>0</v>
-      </c>
-      <c r="P802" t="str">
-        <v>거래처비용청구</v>
-      </c>
-      <c r="Q802" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R802" t="str">
-        <v>라꾸스토리</v>
-      </c>
-    </row>
-    <row r="803">
-      <c r="A803" t="str">
-        <v>T260706-00005</v>
-      </c>
-      <c r="B803" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C803" t="str">
-        <v>강릉FDC</v>
-      </c>
-      <c r="D803" t="str">
-        <v>강원특별자치도 강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
-      </c>
-      <c r="E803" t="str">
-        <v>2026-07-06 08:00</v>
-      </c>
-      <c r="F803">
-        <v>0</v>
-      </c>
-      <c r="G803" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="H803" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="I803" t="str">
-        <v>2026-07-06 11:30</v>
-      </c>
-      <c r="J803" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K803">
-        <v>1</v>
-      </c>
-      <c r="L803" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M803" t="str">
-        <v>2026-07-06 20:27:47</v>
-      </c>
-      <c r="N803" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O803" s="1">
-        <v>0</v>
-      </c>
-      <c r="P803" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="Q803" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R803" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="804">
-      <c r="A804" t="str">
-        <v>T260706-00004</v>
-      </c>
-      <c r="B804" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C804" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D804" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E804" t="str">
-        <v>2026-07-06 13:30</v>
-      </c>
-      <c r="F804">
-        <v>0</v>
-      </c>
-      <c r="G804" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H804" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I804" t="str">
-        <v>2026-07-06 15:30</v>
-      </c>
-      <c r="J804" t="str">
-        <v>1.5톤 윙바디</v>
-      </c>
-      <c r="K804">
-        <v>1</v>
-      </c>
-      <c r="L804" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M804" t="str">
-        <v>2026-07-06 20:26:56</v>
-      </c>
-      <c r="N804" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O804" s="1">
-        <v>0</v>
-      </c>
-      <c r="P804" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q804" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R804" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="805">
-      <c r="A805" t="str">
-        <v>T260706-00003</v>
-      </c>
-      <c r="B805" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C805" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D805" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E805" t="str">
-        <v>2026-07-06 10:00</v>
-      </c>
-      <c r="F805">
-        <v>0</v>
-      </c>
-      <c r="G805" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H805" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I805" t="str">
-        <v>2026-07-06 13:30</v>
-      </c>
-      <c r="J805" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K805">
-        <v>1</v>
-      </c>
-      <c r="L805" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M805" t="str">
-        <v>2026-07-06 20:25:59</v>
-      </c>
-      <c r="N805" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O805" s="1">
-        <v>0</v>
-      </c>
-      <c r="P805" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q805" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R805" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="806">
-      <c r="A806" t="str">
-        <v>T260706-00002</v>
-      </c>
-      <c r="B806" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C806" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D806" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E806" t="str">
-        <v>2026-07-06 16:30</v>
-      </c>
-      <c r="F806">
-        <v>0</v>
-      </c>
-      <c r="G806" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H806" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I806" t="str">
-        <v>2026-07-06 18:00</v>
-      </c>
-      <c r="J806" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K806">
-        <v>1</v>
-      </c>
-      <c r="L806" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M806" t="str">
-        <v>2026-07-06 15:56:39</v>
-      </c>
-      <c r="N806" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O806" s="1">
-        <v>0</v>
-      </c>
-      <c r="P806" t="str">
-        <v>20260706/경동택배_남이가마258 영업소_파렛트 출하</v>
-      </c>
-      <c r="Q806" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R806" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="807">
-      <c r="A807" t="str">
-        <v>T260706-00001</v>
-      </c>
-      <c r="B807" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C807" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D807" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E807" t="str">
-        <v>2026-07-06 09:00</v>
-      </c>
-      <c r="F807">
-        <v>0</v>
-      </c>
-      <c r="G807" t="str">
-        <v>세상담기(14대 서울 벌크 출하)</v>
-      </c>
-      <c r="H807" t="str">
-        <v>서울 서대문구 이화여대길 50-8 2층 문 앞</v>
-      </c>
-      <c r="I807" t="str">
-        <v>2026-07-06 11:50</v>
-      </c>
-      <c r="J807" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K807">
-        <v>1</v>
-      </c>
-      <c r="L807" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M807" t="str">
-        <v>2026-07-06 10:32:22</v>
-      </c>
-      <c r="N807" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O807" s="1">
-        <v>0</v>
-      </c>
-      <c r="P807" t="str">
-        <v>20260706/세상담기_서울 벌크_출하(14대 2층 운반 건)</v>
-      </c>
-      <c r="Q807" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R807" t="str">
-        <v>세상담기</v>
-      </c>
-    </row>
-    <row r="808">
-      <c r="A808" t="str">
-        <v>T260703-00034</v>
-      </c>
-      <c r="B808" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C808" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D808" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E808" t="str">
-        <v>2026-07-03 19:01</v>
-      </c>
-      <c r="F808">
-        <v>0</v>
-      </c>
-      <c r="G808" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H808" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I808" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J808" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K808">
-        <v>1</v>
-      </c>
-      <c r="L808" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M808" t="str">
-        <v>2026-07-03 20:43:25</v>
-      </c>
-      <c r="N808" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O808" s="1">
-        <v>0</v>
-      </c>
-      <c r="P808" t="str">
-        <v/>
-      </c>
-      <c r="Q808" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R808" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="809">
-      <c r="A809" t="str">
-        <v>T260703-00033</v>
-      </c>
-      <c r="B809" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C809" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D809" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E809" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F809">
-        <v>1</v>
-      </c>
-      <c r="G809" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H809" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I809" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J809" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K809">
-        <v>1</v>
-      </c>
-      <c r="L809" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M809" t="str">
-        <v>2026-07-03 20:42:58</v>
-      </c>
-      <c r="N809" s="1">
-        <v>170000</v>
-      </c>
-      <c r="O809" s="1">
-        <v>0</v>
-      </c>
-      <c r="P809" t="str">
-        <v/>
-      </c>
-      <c r="Q809" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R809" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="810">
-      <c r="A810" t="str">
-        <v>T260703-00032</v>
-      </c>
-      <c r="B810" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C810" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D810" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E810" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F810">
-        <v>1</v>
-      </c>
-      <c r="G810" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H810" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I810" t="str">
-        <v>2026-07-04 08:00</v>
-      </c>
-      <c r="J810" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K810">
-        <v>1</v>
-      </c>
-      <c r="L810" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M810" t="str">
-        <v>2026-07-03 20:42:34</v>
-      </c>
-      <c r="N810" s="1">
-        <v>170000</v>
-      </c>
-      <c r="O810" s="1">
-        <v>0</v>
-      </c>
-      <c r="P810" t="str">
-        <v/>
-      </c>
-      <c r="Q810" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R810" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="811">
-      <c r="A811" t="str">
-        <v>T260703-00031</v>
-      </c>
-      <c r="B811" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C811" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D811" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E811" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F811">
-        <v>0</v>
-      </c>
-      <c r="G811" t="str">
-        <v>시흥ACP</v>
-      </c>
-      <c r="H811" t="str">
-        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
-      </c>
-      <c r="I811" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J811" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K811">
-        <v>1</v>
-      </c>
-      <c r="L811" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M811" t="str">
-        <v>2026-07-03 20:41:59</v>
-      </c>
-      <c r="N811" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O811" s="1">
-        <v>0</v>
-      </c>
-      <c r="P811" t="str">
-        <v/>
-      </c>
-      <c r="Q811" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R811" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="812">
-      <c r="A812" t="str">
-        <v>T260703-00030</v>
-      </c>
-      <c r="B812" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C812" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D812" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E812" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F812">
-        <v>3</v>
-      </c>
-      <c r="G812" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H812" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I812" t="str">
-        <v>2026-07-04 08:00</v>
-      </c>
-      <c r="J812" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K812">
-        <v>1</v>
-      </c>
-      <c r="L812" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M812" t="str">
-        <v>2026-07-03 20:41:34</v>
-      </c>
-      <c r="N812" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O812" s="1">
-        <v>0</v>
-      </c>
-      <c r="P812" t="str">
-        <v/>
-      </c>
-      <c r="Q812" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R812" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="813">
-      <c r="A813" t="str">
-        <v>T260703-00029</v>
-      </c>
-      <c r="B813" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C813" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D813" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E813" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F813">
-        <v>0</v>
-      </c>
-      <c r="G813" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H813" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I813" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J813" t="str">
-        <v>1톤 기타차량</v>
-      </c>
-      <c r="K813">
-        <v>1</v>
-      </c>
-      <c r="L813" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M813" t="str">
-        <v>2026-07-03 20:40:56</v>
-      </c>
-      <c r="N813" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O813" s="1">
-        <v>0</v>
-      </c>
-      <c r="P813" t="str">
-        <v/>
-      </c>
-      <c r="Q813" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R813" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="814">
-      <c r="A814" t="str">
-        <v>T260703-00028</v>
-      </c>
-      <c r="B814" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C814" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D814" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E814" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F814">
-        <v>0</v>
-      </c>
-      <c r="G814" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="H814" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="I814" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J814" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K814">
-        <v>1</v>
-      </c>
-      <c r="L814" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M814" t="str">
-        <v>2026-07-03 20:40:32</v>
-      </c>
-      <c r="N814" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O814" s="1">
-        <v>0</v>
-      </c>
-      <c r="P814" t="str">
-        <v/>
-      </c>
-      <c r="Q814" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R814" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="815">
-      <c r="A815" t="str">
-        <v>T260703-00027</v>
-      </c>
-      <c r="B815" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C815" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D815" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E815" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F815">
-        <v>3</v>
-      </c>
-      <c r="G815" t="str">
-        <v>인제ACP</v>
-      </c>
-      <c r="H815" t="str">
-        <v>강원특별자치도 속초시 만천6길 13 인제ACP</v>
-      </c>
-      <c r="I815" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J815" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K815">
-        <v>1</v>
-      </c>
-      <c r="L815" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M815" t="str">
-        <v>2026-07-03 20:40:07</v>
-      </c>
-      <c r="N815" s="1">
-        <v>390000</v>
-      </c>
-      <c r="O815" s="1">
-        <v>0</v>
-      </c>
-      <c r="P815" t="str">
-        <v/>
-      </c>
-      <c r="Q815" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R815" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="816">
-      <c r="A816" t="str">
-        <v>T260703-00026</v>
-      </c>
-      <c r="B816" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C816" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D816" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E816" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F816">
-        <v>0</v>
-      </c>
-      <c r="G816" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H816" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I816" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J816" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K816">
-        <v>1</v>
-      </c>
-      <c r="L816" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M816" t="str">
-        <v>2026-07-03 20:39:21</v>
-      </c>
-      <c r="N816" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O816" s="1">
-        <v>0</v>
-      </c>
-      <c r="P816" t="str">
-        <v/>
-      </c>
-      <c r="Q816" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R816" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="817">
-      <c r="A817" t="str">
-        <v>T260703-00025</v>
-      </c>
-      <c r="B817" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C817" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D817" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E817" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F817">
-        <v>1</v>
-      </c>
-      <c r="G817" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H817" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I817" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J817" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K817">
-        <v>1</v>
-      </c>
-      <c r="L817" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M817" t="str">
-        <v>2026-07-03 20:39:06</v>
-      </c>
-      <c r="N817" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O817" s="1">
-        <v>0</v>
-      </c>
-      <c r="P817" t="str">
-        <v/>
-      </c>
-      <c r="Q817" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R817" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="818">
-      <c r="A818" t="str">
-        <v>T260703-00024</v>
-      </c>
-      <c r="B818" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C818" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D818" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E818" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F818">
-        <v>1</v>
-      </c>
-      <c r="G818" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H818" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I818" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J818" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K818">
-        <v>1</v>
-      </c>
-      <c r="L818" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M818" t="str">
-        <v>2026-07-03 20:38:48</v>
-      </c>
-      <c r="N818" s="1">
-        <v>530000</v>
-      </c>
-      <c r="O818" s="1">
-        <v>0</v>
-      </c>
-      <c r="P818" t="str">
-        <v/>
-      </c>
-      <c r="Q818" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R818" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="819">
-      <c r="A819" t="str">
-        <v>T260703-00023</v>
-      </c>
-      <c r="B819" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C819" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D819" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E819" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F819">
-        <v>0</v>
-      </c>
-      <c r="G819" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="H819" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="I819" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J819" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K819">
-        <v>1</v>
-      </c>
-      <c r="L819" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M819" t="str">
-        <v>2026-07-03 20:38:28</v>
-      </c>
-      <c r="N819" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O819" s="1">
-        <v>0</v>
-      </c>
-      <c r="P819" t="str">
-        <v/>
-      </c>
-      <c r="Q819" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R819" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="820">
-      <c r="A820" t="str">
-        <v>T260703-00022</v>
-      </c>
-      <c r="B820" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C820" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D820" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E820" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F820">
-        <v>0</v>
-      </c>
-      <c r="G820" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H820" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I820" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J820" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K820">
-        <v>1</v>
-      </c>
-      <c r="L820" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M820" t="str">
-        <v>2026-07-03 20:38:14</v>
-      </c>
-      <c r="N820" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O820" s="1">
-        <v>0</v>
-      </c>
-      <c r="P820" t="str">
-        <v/>
-      </c>
-      <c r="Q820" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R820" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="821">
-      <c r="A821" t="str">
-        <v>T260703-00021</v>
-      </c>
-      <c r="B821" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C821" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D821" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E821" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F821">
-        <v>1</v>
-      </c>
-      <c r="G821" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H821" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I821" t="str">
-        <v>2026-07-03 22:00</v>
-      </c>
-      <c r="J821" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K821">
-        <v>1</v>
-      </c>
-      <c r="L821" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M821" t="str">
-        <v>2026-07-03 20:37:59</v>
-      </c>
-      <c r="N821" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O821" s="1">
-        <v>0</v>
-      </c>
-      <c r="P821" t="str">
-        <v/>
-      </c>
-      <c r="Q821" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R821" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="822">
-      <c r="A822" t="str">
-        <v>T260703-00020</v>
-      </c>
-      <c r="B822" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C822" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D822" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E822" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F822">
-        <v>0</v>
-      </c>
-      <c r="G822" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H822" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I822" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J822" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K822">
-        <v>1</v>
-      </c>
-      <c r="L822" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M822" t="str">
-        <v>2026-07-03 20:37:40</v>
-      </c>
-      <c r="N822" s="1">
-        <v>490000</v>
-      </c>
-      <c r="O822" s="1">
-        <v>0</v>
-      </c>
-      <c r="P822" t="str">
-        <v/>
-      </c>
-      <c r="Q822" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R822" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="823">
-      <c r="A823" t="str">
-        <v>T260703-00019</v>
-      </c>
-      <c r="B823" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C823" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D823" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E823" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F823">
-        <v>0</v>
-      </c>
-      <c r="G823" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H823" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I823" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J823" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K823">
-        <v>1</v>
-      </c>
-      <c r="L823" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M823" t="str">
-        <v>2026-07-03 20:37:26</v>
-      </c>
-      <c r="N823" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O823" s="1">
-        <v>0</v>
-      </c>
-      <c r="P823" t="str">
-        <v/>
-      </c>
-      <c r="Q823" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R823" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="824">
-      <c r="A824" t="str">
-        <v>T260703-00018</v>
-      </c>
-      <c r="B824" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C824" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D824" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E824" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F824">
-        <v>0</v>
-      </c>
-      <c r="G824" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H824" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I824" t="str">
-        <v>2026-07-03 20:00</v>
-      </c>
-      <c r="J824" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K824">
-        <v>1</v>
-      </c>
-      <c r="L824" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M824" t="str">
-        <v>2026-07-03 20:37:11</v>
-      </c>
-      <c r="N824" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O824" s="1">
-        <v>0</v>
-      </c>
-      <c r="P824" t="str">
-        <v/>
-      </c>
-      <c r="Q824" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R824" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="825">
-      <c r="A825" t="str">
-        <v>T260703-00017</v>
-      </c>
-      <c r="B825" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C825" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D825" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E825" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F825">
-        <v>0</v>
-      </c>
-      <c r="G825" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H825" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I825" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J825" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K825">
-        <v>1</v>
-      </c>
-      <c r="L825" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M825" t="str">
-        <v>2026-07-03 20:36:55</v>
-      </c>
-      <c r="N825" s="1">
-        <v>420000</v>
-      </c>
-      <c r="O825" s="1">
-        <v>0</v>
-      </c>
-      <c r="P825" t="str">
-        <v/>
-      </c>
-      <c r="Q825" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R825" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="826">
-      <c r="A826" t="str">
-        <v>T260703-00016</v>
-      </c>
-      <c r="B826" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C826" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D826" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E826" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F826">
-        <v>0</v>
-      </c>
-      <c r="G826" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H826" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I826" t="str">
-        <v>2026-07-03 21:00</v>
-      </c>
-      <c r="J826" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K826">
-        <v>1</v>
-      </c>
-      <c r="L826" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M826" t="str">
-        <v>2026-07-03 20:36:37</v>
-      </c>
-      <c r="N826" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O826" s="1">
-        <v>0</v>
-      </c>
-      <c r="P826" t="str">
-        <v/>
-      </c>
-      <c r="Q826" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R826" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="827">
-      <c r="A827" t="str">
-        <v>T260703-00015</v>
-      </c>
-      <c r="B827" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C827" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D827" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E827" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F827">
-        <v>0</v>
-      </c>
-      <c r="G827" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H827" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I827" t="str">
-        <v>2026-07-04 07:00</v>
-      </c>
-      <c r="J827" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K827">
-        <v>1</v>
-      </c>
-      <c r="L827" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M827" t="str">
-        <v>2026-07-03 20:36:15</v>
-      </c>
-      <c r="N827" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O827" s="1">
-        <v>0</v>
-      </c>
-      <c r="P827" t="str">
-        <v/>
-      </c>
-      <c r="Q827" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R827" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="828">
-      <c r="A828" t="str">
-        <v>T260703-00014</v>
-      </c>
-      <c r="B828" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C828" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D828" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E828" t="str">
-        <v>2026-07-03 19:00</v>
-      </c>
-      <c r="F828">
-        <v>1</v>
-      </c>
-      <c r="G828" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H828" t="str">
-        <v>경산시 해오름길114-2 경산FDC</v>
-      </c>
-      <c r="I828" t="str">
-        <v>2026-07-03 23:00</v>
-      </c>
-      <c r="J828" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K828">
-        <v>1</v>
-      </c>
-      <c r="L828" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M828" t="str">
-        <v>2026-07-03 20:35:55</v>
-      </c>
-      <c r="N828" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O828" s="1">
-        <v>0</v>
-      </c>
-      <c r="P828" t="str">
-        <v/>
-      </c>
-      <c r="Q828" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R828" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="829">
-      <c r="A829" t="str">
-        <v>T260703-00013</v>
-      </c>
-      <c r="B829" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C829" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D829" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E829" t="str">
-        <v>2026-07-03 17:30</v>
-      </c>
-      <c r="F829">
-        <v>0</v>
-      </c>
-      <c r="G829" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H829" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I829" t="str">
-        <v>2026-07-03 18:30</v>
-      </c>
-      <c r="J829" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K829">
-        <v>1</v>
-      </c>
-      <c r="L829" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M829" t="str">
-        <v>2026-07-03 20:31:55</v>
-      </c>
-      <c r="N829" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O829" s="1">
-        <v>0</v>
-      </c>
-      <c r="P829" t="str">
-        <v/>
-      </c>
-      <c r="Q829" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R829" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="830">
-      <c r="A830" t="str">
-        <v>T260703-00012</v>
-      </c>
-      <c r="B830" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C830" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="D830" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="E830" t="str">
-        <v>2026-07-03 08:30</v>
-      </c>
-      <c r="F830">
-        <v>0</v>
-      </c>
-      <c r="G830" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="H830" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="I830" t="str">
-        <v>2026-07-03 11:30</v>
-      </c>
-      <c r="J830" t="str">
-        <v>3.5톤 카고</v>
-      </c>
-      <c r="K830">
-        <v>1</v>
-      </c>
-      <c r="L830" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M830" t="str">
-        <v>2026-07-03 20:31:21</v>
-      </c>
-      <c r="N830" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O830" s="1">
-        <v>0</v>
-      </c>
-      <c r="P830" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="Q830" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R830" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="831">
-      <c r="A831" t="str">
-        <v>T260703-00011</v>
-      </c>
-      <c r="B831" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C831" t="str">
-        <v>샤오미</v>
-      </c>
-      <c r="D831" t="str">
-        <v>경기 이천시 대월면 부필리 309 샤오미</v>
-      </c>
-      <c r="E831" t="str">
-        <v>2026-07-03 11:30</v>
-      </c>
-      <c r="F831">
-        <v>0</v>
-      </c>
-      <c r="G831" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H831" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I831" t="str">
-        <v>2026-07-03 13:30</v>
-      </c>
-      <c r="J831" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K831">
-        <v>1</v>
-      </c>
-      <c r="L831" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M831" t="str">
-        <v>2026-07-03 20:30:39</v>
-      </c>
-      <c r="N831" s="1">
-        <v>80000</v>
-      </c>
-      <c r="O831" s="1">
-        <v>0</v>
-      </c>
-      <c r="P831" t="str">
-        <v>거래처비용청구(1대)</v>
-      </c>
-      <c r="Q831" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R831" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="832">
-      <c r="A832" t="str">
-        <v>T260703-00010</v>
-      </c>
-      <c r="B832" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C832" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D832" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E832" t="str">
-        <v>2026-07-03 13:30</v>
-      </c>
-      <c r="F832">
-        <v>0</v>
-      </c>
-      <c r="G832" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H832" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I832" t="str">
-        <v>2026-07-03 15:30</v>
-      </c>
-      <c r="J832" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K832">
-        <v>1</v>
-      </c>
-      <c r="L832" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M832" t="str">
-        <v>2026-07-03 20:29:47</v>
-      </c>
-      <c r="N832" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O832" s="1">
-        <v>0</v>
-      </c>
-      <c r="P832" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q832" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R832" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="833">
-      <c r="A833" t="str">
-        <v>T260703-00009</v>
-      </c>
-      <c r="B833" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C833" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D833" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E833" t="str">
-        <v>2026-07-03 10:00</v>
-      </c>
-      <c r="F833">
-        <v>0</v>
-      </c>
-      <c r="G833" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H833" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I833" t="str">
-        <v>2026-07-03 13:30</v>
-      </c>
-      <c r="J833" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K833">
-        <v>1</v>
-      </c>
-      <c r="L833" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M833" t="str">
-        <v>2026-07-03 20:29:05</v>
-      </c>
-      <c r="N833" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O833" s="1">
-        <v>0</v>
-      </c>
-      <c r="P833" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q833" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R833" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="834">
-      <c r="A834" t="str">
-        <v>T260703-00008</v>
-      </c>
-      <c r="B834" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C834" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D834" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E834" t="str">
-        <v>2026-07-03 16:30</v>
-      </c>
-      <c r="F834">
-        <v>0</v>
-      </c>
-      <c r="G834" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H834" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I834" t="str">
-        <v>2026-07-03 18:00</v>
-      </c>
-      <c r="J834" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K834">
-        <v>1</v>
-      </c>
-      <c r="L834" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M834" t="str">
-        <v>2026-07-03 18:39:34</v>
-      </c>
-      <c r="N834" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O834" s="1">
-        <v>0</v>
-      </c>
-      <c r="P834" t="str">
-        <v>20260703/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q834" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R834" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="835">
-      <c r="A835" t="str">
-        <v>T260703-00007</v>
-      </c>
-      <c r="B835" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C835" t="str">
-        <v>청주ARC(공파렛트 이동)</v>
-      </c>
-      <c r="D835" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(공파렛트 이동)</v>
-      </c>
-      <c r="E835" t="str">
-        <v>2026-07-03 11:40</v>
-      </c>
-      <c r="F835">
-        <v>0</v>
-      </c>
-      <c r="G835" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H835" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="I835" t="str">
-        <v>2026-07-03 13:00</v>
-      </c>
-      <c r="J835" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K835">
-        <v>1</v>
-      </c>
-      <c r="L835" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M835" t="str">
-        <v>2026-07-03 11:28:01</v>
-      </c>
-      <c r="N835" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O835" s="1">
-        <v>0</v>
-      </c>
-      <c r="P835" t="str">
-        <v>20260703청주-&gt; 안성FC/공파렛트이동</v>
-      </c>
-      <c r="Q835" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R835" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="836">
-      <c r="A836" t="str">
-        <v>T260703-00006</v>
-      </c>
-      <c r="B836" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C836" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D836" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E836" t="str">
-        <v>2026-07-03 11:55</v>
-      </c>
-      <c r="F836">
-        <v>0</v>
-      </c>
-      <c r="G836" t="str">
-        <v>하이얼(서울 벌크 출하)</v>
-      </c>
-      <c r="H836" t="str">
-        <v>서울 강남구 선릉로92길 38 도파민</v>
-      </c>
-      <c r="I836" t="str">
-        <v>2026-07-03 13:00</v>
-      </c>
-      <c r="J836" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K836">
-        <v>1</v>
-      </c>
-      <c r="L836" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M836" t="str">
-        <v>2026-07-03 11:26:22</v>
-      </c>
-      <c r="N836" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O836" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P836" t="str">
-        <v>20260703/하이얼_서울_벌크_출하</v>
-      </c>
-      <c r="Q836" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R836" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="837">
-      <c r="A837" t="str">
-        <v>T260703-00005</v>
-      </c>
-      <c r="B837" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C837" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D837" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E837" t="str">
-        <v>2026-07-03 11:00</v>
-      </c>
-      <c r="F837">
-        <v>0</v>
-      </c>
-      <c r="G837" t="str">
-        <v>파주 하이마트 물류</v>
-      </c>
-      <c r="H837" t="str">
-        <v>경기 파주시 탄현면 월롱산로 296 파주 하이마트 물류</v>
-      </c>
-      <c r="I837" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J837" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K837">
-        <v>1</v>
-      </c>
-      <c r="L837" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M837" t="str">
-        <v>2026-07-03 11:22:28</v>
-      </c>
-      <c r="N837" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O837" s="1">
-        <v>0</v>
-      </c>
-      <c r="P837" t="str">
-        <v>일코전자 파주 하이마트 물류</v>
-      </c>
-      <c r="Q837" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R837" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="838">
-      <c r="A838" t="str">
-        <v>T260703-00004</v>
-      </c>
-      <c r="B838" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C838" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D838" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지  안성FC</v>
-      </c>
-      <c r="E838" t="str">
-        <v>2026-07-03 09:30</v>
-      </c>
-      <c r="F838">
-        <v>0</v>
-      </c>
-      <c r="G838" t="str">
-        <v>TCL다코넷</v>
-      </c>
-      <c r="H838" t="str">
-        <v>경기 평택시 포승읍 희곡리 847 평택 켄달스퀘어 3층, 다코넷 37번 도크</v>
-      </c>
-      <c r="I838" t="str">
-        <v>2026-07-03 11:30</v>
-      </c>
-      <c r="J838" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K838">
-        <v>1</v>
-      </c>
-      <c r="L838" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M838" t="str">
-        <v>2026-07-03 11:21:17</v>
-      </c>
-      <c r="N838" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O838" s="1">
-        <v>0</v>
-      </c>
-      <c r="P838" t="str">
-        <v>TCL 다코넷</v>
-      </c>
-      <c r="Q838" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R838" t="str">
-        <v>TCL</v>
-      </c>
-    </row>
-    <row r="839">
-      <c r="A839" t="str">
-        <v>T260703-00003</v>
-      </c>
-      <c r="B839" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C839" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D839" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E839" t="str">
-        <v>2026-07-03 13:00</v>
-      </c>
-      <c r="F839">
-        <v>0</v>
-      </c>
-      <c r="G839" t="str">
-        <v>이천 하이마트 물류</v>
-      </c>
-      <c r="H839" t="str">
-        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 물류</v>
-      </c>
-      <c r="I839" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J839" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K839">
-        <v>1</v>
-      </c>
-      <c r="L839" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M839" t="str">
-        <v>2026-07-03 11:19:40</v>
-      </c>
-      <c r="N839" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O839" s="1">
-        <v>0</v>
-      </c>
-      <c r="P839" t="str">
-        <v>일코전자 이천 하이마트 물류</v>
-      </c>
-      <c r="Q839" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R839" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="840">
-      <c r="A840" t="str">
-        <v>T260703-00002</v>
-      </c>
-      <c r="B840" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C840" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D840" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E840" t="str">
-        <v>2026-07-03 10:00</v>
-      </c>
-      <c r="F840">
-        <v>0</v>
-      </c>
-      <c r="G840" t="str">
-        <v>화성 하이마트 물류</v>
-      </c>
-      <c r="H840" t="str">
-        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 물류</v>
-      </c>
-      <c r="I840" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J840" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K840">
-        <v>1</v>
-      </c>
-      <c r="L840" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M840" t="str">
-        <v>2026-07-03 11:18:03</v>
-      </c>
-      <c r="N840" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O840" s="1">
-        <v>0</v>
-      </c>
-      <c r="P840" t="str">
-        <v>일코전자 화성 하이마트 물류</v>
-      </c>
-      <c r="Q840" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R840" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="841">
-      <c r="A841" t="str">
-        <v>T260703-00001</v>
-      </c>
-      <c r="B841" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C841" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D841" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E841" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="F841">
-        <v>0</v>
-      </c>
-      <c r="G841" t="str">
-        <v>인천 하이마트 물류</v>
-      </c>
-      <c r="H841" t="str">
-        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
-      </c>
-      <c r="I841" t="str">
-        <v>2026-07-03 15:00</v>
-      </c>
-      <c r="J841" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K841">
-        <v>1</v>
-      </c>
-      <c r="L841" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M841" t="str">
-        <v>2026-07-03 11:16:52</v>
-      </c>
-      <c r="N841" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O841" s="1">
-        <v>0</v>
-      </c>
-      <c r="P841" t="str">
-        <v>일코전자 인천 하이마트 물류</v>
-      </c>
-      <c r="Q841" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R841" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="842">
-      <c r="A842" t="str">
-        <v>T260702-00027</v>
-      </c>
-      <c r="B842" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C842" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D842" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E842" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F842">
-        <v>1</v>
-      </c>
-      <c r="G842" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H842" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I842" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J842" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K842">
-        <v>1</v>
-      </c>
-      <c r="L842" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M842" t="str">
-        <v>2026-07-02 20:54:21</v>
-      </c>
-      <c r="N842" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O842" s="1">
-        <v>0</v>
-      </c>
-      <c r="P842" t="str">
-        <v/>
-      </c>
-      <c r="Q842" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R842" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="843">
-      <c r="A843" t="str">
-        <v>T260702-00026</v>
-      </c>
-      <c r="B843" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C843" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D843" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E843" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F843">
-        <v>1</v>
-      </c>
-      <c r="G843" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H843" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I843" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J843" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K843">
-        <v>1</v>
-      </c>
-      <c r="L843" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M843" t="str">
-        <v>2026-07-02 20:53:56</v>
-      </c>
-      <c r="N843" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O843" s="1">
-        <v>0</v>
-      </c>
-      <c r="P843" t="str">
-        <v/>
-      </c>
-      <c r="Q843" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R843" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="844">
-      <c r="A844" t="str">
-        <v>T260702-00025</v>
-      </c>
-      <c r="B844" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C844" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D844" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E844" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F844">
-        <v>3</v>
-      </c>
-      <c r="G844" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H844" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I844" t="str">
-        <v>2026-07-03 08:00</v>
-      </c>
-      <c r="J844" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K844">
-        <v>1</v>
-      </c>
-      <c r="L844" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M844" t="str">
-        <v>2026-07-02 20:53:28</v>
-      </c>
-      <c r="N844" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O844" s="1">
-        <v>0</v>
-      </c>
-      <c r="P844" t="str">
-        <v/>
-      </c>
-      <c r="Q844" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R844" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="845">
-      <c r="A845" t="str">
-        <v>T260702-00024</v>
-      </c>
-      <c r="B845" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C845" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D845" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E845" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F845">
-        <v>0</v>
-      </c>
-      <c r="G845" t="str">
-        <v>용인ACP</v>
-      </c>
-      <c r="H845" t="str">
-        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
-      </c>
-      <c r="I845" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J845" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K845">
-        <v>1</v>
-      </c>
-      <c r="L845" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M845" t="str">
-        <v>2026-07-02 20:52:18</v>
-      </c>
-      <c r="N845" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O845" s="1">
-        <v>0</v>
-      </c>
-      <c r="P845" t="str">
-        <v/>
-      </c>
-      <c r="Q845" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R845" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="846">
-      <c r="A846" t="str">
-        <v>T260702-00023</v>
-      </c>
-      <c r="B846" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C846" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D846" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E846" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F846">
-        <v>1</v>
-      </c>
-      <c r="G846" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H846" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I846" t="str">
-        <v>2026-07-03 07:00</v>
-      </c>
-      <c r="J846" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K846">
-        <v>1</v>
-      </c>
-      <c r="L846" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M846" t="str">
-        <v>2026-07-02 20:51:59</v>
-      </c>
-      <c r="N846" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O846" s="1">
-        <v>0</v>
-      </c>
-      <c r="P846" t="str">
-        <v/>
-      </c>
-      <c r="Q846" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R846" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="847">
-      <c r="A847" t="str">
-        <v>T260702-00022</v>
-      </c>
-      <c r="B847" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C847" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D847" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E847" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F847">
-        <v>0</v>
-      </c>
-      <c r="G847" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H847" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I847" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J847" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K847">
-        <v>1</v>
-      </c>
-      <c r="L847" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M847" t="str">
-        <v>2026-07-02 20:51:32</v>
-      </c>
-      <c r="N847" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O847" s="1">
-        <v>0</v>
-      </c>
-      <c r="P847" t="str">
-        <v/>
-      </c>
-      <c r="Q847" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R847" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="848">
-      <c r="A848" t="str">
-        <v>T260702-00021</v>
-      </c>
-      <c r="B848" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C848" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D848" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E848" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F848">
-        <v>1</v>
-      </c>
-      <c r="G848" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H848" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I848" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J848" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K848">
-        <v>1</v>
-      </c>
-      <c r="L848" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M848" t="str">
-        <v>2026-07-02 20:51:14</v>
-      </c>
-      <c r="N848" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O848" s="1">
-        <v>0</v>
-      </c>
-      <c r="P848" t="str">
-        <v/>
-      </c>
-      <c r="Q848" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R848" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="849">
-      <c r="A849" t="str">
-        <v>T260702-00020</v>
-      </c>
-      <c r="B849" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C849" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D849" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E849" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F849">
-        <v>0</v>
-      </c>
-      <c r="G849" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="H849" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="I849" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J849" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K849">
-        <v>1</v>
-      </c>
-      <c r="L849" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M849" t="str">
-        <v>2026-07-02 20:50:54</v>
-      </c>
-      <c r="N849" s="1">
-        <v>280000</v>
-      </c>
-      <c r="O849" s="1">
-        <v>0</v>
-      </c>
-      <c r="P849" t="str">
-        <v/>
-      </c>
-      <c r="Q849" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R849" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="850">
-      <c r="A850" t="str">
-        <v>T260702-00019</v>
-      </c>
-      <c r="B850" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C850" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D850" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E850" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F850">
-        <v>0</v>
-      </c>
-      <c r="G850" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H850" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I850" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J850" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K850">
-        <v>1</v>
-      </c>
-      <c r="L850" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M850" t="str">
-        <v>2026-07-02 20:50:36</v>
-      </c>
-      <c r="N850" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O850" s="1">
-        <v>0</v>
-      </c>
-      <c r="P850" t="str">
-        <v/>
-      </c>
-      <c r="Q850" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R850" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="851">
-      <c r="A851" t="str">
-        <v>T260702-00018</v>
-      </c>
-      <c r="B851" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C851" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D851" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E851" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F851">
-        <v>1</v>
-      </c>
-      <c r="G851" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H851" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I851" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J851" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K851">
-        <v>1</v>
-      </c>
-      <c r="L851" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M851" t="str">
-        <v>2026-07-02 20:50:19</v>
-      </c>
-      <c r="N851" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O851" s="1">
-        <v>0</v>
-      </c>
-      <c r="P851" t="str">
-        <v/>
-      </c>
-      <c r="Q851" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R851" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="852">
-      <c r="A852" t="str">
-        <v>T260702-00017</v>
-      </c>
-      <c r="B852" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C852" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D852" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E852" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F852">
-        <v>1</v>
-      </c>
-      <c r="G852" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H852" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I852" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J852" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K852">
-        <v>1</v>
-      </c>
-      <c r="L852" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M852" t="str">
-        <v>2026-07-02 20:49:56</v>
-      </c>
-      <c r="N852" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O852" s="1">
-        <v>0</v>
-      </c>
-      <c r="P852" t="str">
-        <v/>
-      </c>
-      <c r="Q852" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R852" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="853">
-      <c r="A853" t="str">
-        <v>T260702-00016</v>
-      </c>
-      <c r="B853" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C853" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D853" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E853" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F853">
-        <v>0</v>
-      </c>
-      <c r="G853" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H853" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I853" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J853" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K853">
-        <v>1</v>
-      </c>
-      <c r="L853" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M853" t="str">
-        <v>2026-07-02 20:49:25</v>
-      </c>
-      <c r="N853" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O853" s="1">
-        <v>0</v>
-      </c>
-      <c r="P853" t="str">
-        <v/>
-      </c>
-      <c r="Q853" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R853" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="854">
-      <c r="A854" t="str">
-        <v>T260702-00015</v>
-      </c>
-      <c r="B854" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C854" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D854" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E854" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F854">
-        <v>1</v>
-      </c>
-      <c r="G854" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H854" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I854" t="str">
-        <v>2026-07-02 22:00</v>
-      </c>
-      <c r="J854" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K854">
-        <v>1</v>
-      </c>
-      <c r="L854" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M854" t="str">
-        <v>2026-07-02 20:48:50</v>
-      </c>
-      <c r="N854" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O854" s="1">
-        <v>0</v>
-      </c>
-      <c r="P854" t="str">
-        <v/>
-      </c>
-      <c r="Q854" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R854" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="855">
-      <c r="A855" t="str">
-        <v>T260702-00014</v>
-      </c>
-      <c r="B855" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C855" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D855" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E855" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F855">
-        <v>0</v>
-      </c>
-      <c r="G855" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H855" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I855" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J855" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K855">
-        <v>1</v>
-      </c>
-      <c r="L855" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M855" t="str">
-        <v>2026-07-02 20:48:25</v>
-      </c>
-      <c r="N855" s="1">
-        <v>420000</v>
-      </c>
-      <c r="O855" s="1">
-        <v>0</v>
-      </c>
-      <c r="P855" t="str">
-        <v/>
-      </c>
-      <c r="Q855" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R855" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="856">
-      <c r="A856" t="str">
-        <v>T260702-00013</v>
-      </c>
-      <c r="B856" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C856" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D856" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E856" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F856">
-        <v>0</v>
-      </c>
-      <c r="G856" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H856" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I856" t="str">
-        <v>2026-07-02 21:00</v>
-      </c>
-      <c r="J856" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K856">
-        <v>1</v>
-      </c>
-      <c r="L856" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M856" t="str">
-        <v>2026-07-02 20:48:09</v>
-      </c>
-      <c r="N856" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O856" s="1">
-        <v>0</v>
-      </c>
-      <c r="P856" t="str">
-        <v/>
-      </c>
-      <c r="Q856" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R856" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="857">
-      <c r="A857" t="str">
-        <v>T260702-00012</v>
-      </c>
-      <c r="B857" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C857" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D857" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E857" t="str">
-        <v>2026-07-02 19:00</v>
-      </c>
-      <c r="F857">
-        <v>2</v>
-      </c>
-      <c r="G857" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H857" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I857" t="str">
-        <v>2026-07-02 23:00</v>
-      </c>
-      <c r="J857" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K857">
-        <v>1</v>
-      </c>
-      <c r="L857" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M857" t="str">
-        <v>2026-07-02 20:47:49</v>
-      </c>
-      <c r="N857" s="1">
-        <v>680000</v>
-      </c>
-      <c r="O857" s="1">
-        <v>0</v>
-      </c>
-      <c r="P857" t="str">
-        <v/>
-      </c>
-      <c r="Q857" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R857" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="858">
-      <c r="A858" t="str">
-        <v>T260702-00011</v>
-      </c>
-      <c r="B858" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C858" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D858" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E858" t="str">
-        <v>2026-07-02 17:50</v>
-      </c>
-      <c r="F858">
-        <v>0</v>
-      </c>
-      <c r="G858" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H858" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I858" t="str">
-        <v>2026-07-02 18:50</v>
-      </c>
-      <c r="J858" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K858">
-        <v>1</v>
-      </c>
-      <c r="L858" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M858" t="str">
-        <v>2026-07-02 20:44:59</v>
-      </c>
-      <c r="N858" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O858" s="1">
-        <v>0</v>
-      </c>
-      <c r="P858" t="str">
-        <v/>
-      </c>
-      <c r="Q858" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R858" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="859">
-      <c r="A859" t="str">
-        <v>T260702-00010</v>
-      </c>
-      <c r="B859" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C859" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D859" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E859" t="str">
-        <v>2026-07-02 13:30</v>
-      </c>
-      <c r="F859">
-        <v>0</v>
-      </c>
-      <c r="G859" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H859" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I859" t="str">
-        <v>2026-07-02 15:40</v>
-      </c>
-      <c r="J859" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K859">
-        <v>1</v>
-      </c>
-      <c r="L859" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M859" t="str">
-        <v>2026-07-02 20:44:26</v>
-      </c>
-      <c r="N859" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O859" s="1">
-        <v>0</v>
-      </c>
-      <c r="P859" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q859" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R859" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="860">
-      <c r="A860" t="str">
-        <v>T260702-00009</v>
-      </c>
-      <c r="B860" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C860" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D860" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E860" t="str">
-        <v>2026-07-02 10:00</v>
-      </c>
-      <c r="F860">
-        <v>0</v>
-      </c>
-      <c r="G860" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H860" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I860" t="str">
-        <v>2026-07-02 13:40</v>
-      </c>
-      <c r="J860" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K860">
-        <v>1</v>
-      </c>
-      <c r="L860" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M860" t="str">
-        <v>2026-07-02 20:43:37</v>
-      </c>
-      <c r="N860" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O860" s="1">
-        <v>0</v>
-      </c>
-      <c r="P860" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q860" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R860" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="861">
-      <c r="A861" t="str">
-        <v>T260702-00008</v>
-      </c>
-      <c r="B861" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C861" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D861" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E861" t="str">
-        <v>2026-07-02 17:00</v>
-      </c>
-      <c r="F861">
-        <v>0</v>
-      </c>
-      <c r="G861" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="H861" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="I861" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J861" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K861">
-        <v>1</v>
-      </c>
-      <c r="L861" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M861" t="str">
-        <v>2026-07-02 16:38:23</v>
-      </c>
-      <c r="N861" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O861" s="1">
-        <v>0</v>
-      </c>
-      <c r="P861" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="Q861" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R861" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="862">
-      <c r="A862" t="str">
-        <v>T260702-00007</v>
-      </c>
-      <c r="B862" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C862" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D862" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E862" t="str">
-        <v>2026-07-02 16:30</v>
-      </c>
-      <c r="F862">
-        <v>0</v>
-      </c>
-      <c r="G862" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H862" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I862" t="str">
-        <v>2026-07-02 18:00</v>
-      </c>
-      <c r="J862" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K862">
-        <v>1</v>
-      </c>
-      <c r="L862" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M862" t="str">
-        <v>2026-07-02 16:34:35</v>
-      </c>
-      <c r="N862" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O862" s="1">
-        <v>0</v>
-      </c>
-      <c r="P862" t="str">
-        <v>20260702/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q862" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R862" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="863">
-      <c r="A863" t="str">
-        <v>T260702-00006</v>
-      </c>
-      <c r="B863" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C863" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D863" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E863" t="str">
-        <v>2026-07-02 16:00</v>
-      </c>
-      <c r="F863">
-        <v>0</v>
-      </c>
-      <c r="G863" t="str">
-        <v>광주 하이마트 물류</v>
-      </c>
-      <c r="H863" t="str">
-        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
-      </c>
-      <c r="I863" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J863" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K863">
-        <v>1</v>
-      </c>
-      <c r="L863" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M863" t="str">
-        <v>2026-07-02 15:30:55</v>
-      </c>
-      <c r="N863" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O863" s="1">
-        <v>0</v>
-      </c>
-      <c r="P863" t="str">
-        <v>일코 광주 하이마트 물류</v>
-      </c>
-      <c r="Q863" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R863" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="864">
-      <c r="A864" t="str">
-        <v>T260702-00005</v>
-      </c>
-      <c r="B864" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C864" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D864" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E864" t="str">
-        <v>2026-07-02 14:30</v>
-      </c>
-      <c r="F864">
-        <v>0</v>
-      </c>
-      <c r="G864" t="str">
-        <v>마산 하이마트 물류</v>
-      </c>
-      <c r="H864" t="str">
-        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
-      </c>
-      <c r="I864" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J864" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K864">
-        <v>1</v>
-      </c>
-      <c r="L864" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M864" t="str">
-        <v>2026-07-02 13:44:41</v>
-      </c>
-      <c r="N864" s="1">
-        <v>380000</v>
-      </c>
-      <c r="O864" s="1">
-        <v>0</v>
-      </c>
-      <c r="P864" t="str">
-        <v>일코 마산 하이마트 물류</v>
-      </c>
-      <c r="Q864" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R864" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="865">
-      <c r="A865" t="str">
-        <v>T260702-00004</v>
-      </c>
-      <c r="B865" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C865" t="str">
-        <v>강릉 하이마트 물류</v>
-      </c>
-      <c r="D865" t="str">
-        <v>강원특별자치도 강릉시 연곡면 동해대로 4100-36 강릉 하이마트 물류</v>
-      </c>
-      <c r="E865" t="str">
-        <v>2026-07-02 13:30</v>
-      </c>
-      <c r="F865">
-        <v>0</v>
-      </c>
-      <c r="G865" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H865" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I865" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J865" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K865">
-        <v>1</v>
-      </c>
-      <c r="L865" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M865" t="str">
-        <v>2026-07-02 12:00:10</v>
-      </c>
-      <c r="N865" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O865" s="1">
-        <v>0</v>
-      </c>
-      <c r="P865" t="str">
-        <v>일코전자 강릉 하이마트 물류</v>
-      </c>
-      <c r="Q865" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R865" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="866">
-      <c r="A866" t="str">
-        <v>T260702-00003</v>
-      </c>
-      <c r="B866" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C866" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D866" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E866" t="str">
-        <v>2026-07-02 14:30</v>
-      </c>
-      <c r="F866">
-        <v>0</v>
-      </c>
-      <c r="G866" t="str">
-        <v>대구 하이마트 물류</v>
-      </c>
-      <c r="H866" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="I866" t="str">
-        <v>2026-07-03 09:00</v>
-      </c>
-      <c r="J866" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K866">
-        <v>1</v>
-      </c>
-      <c r="L866" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M866" t="str">
-        <v>2026-07-02 11:59:32</v>
-      </c>
-      <c r="N866" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O866" s="1">
-        <v>0</v>
-      </c>
-      <c r="P866" t="str">
-        <v>일코전자 대구 하이마트 물류</v>
-      </c>
-      <c r="Q866" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R866" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="867">
-      <c r="A867" t="str">
-        <v>T260702-00002</v>
-      </c>
-      <c r="B867" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C867" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D867" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E867" t="str">
-        <v>2026-07-02 09:30</v>
-      </c>
-      <c r="F867">
-        <v>1</v>
-      </c>
-      <c r="G867" t="str">
-        <v>하이얼(대구2착)</v>
-      </c>
-      <c r="H867" t="str">
-        <v>대구 남구 양지로 25 대명자이 아파트</v>
-      </c>
-      <c r="I867" t="str">
-        <v>2026-07-02 15:00</v>
-      </c>
-      <c r="J867" t="str">
-        <v>1.5톤 윙바디</v>
-      </c>
-      <c r="K867">
-        <v>1</v>
-      </c>
-      <c r="L867" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M867" t="str">
-        <v>2026-07-02 09:20:07</v>
-      </c>
-      <c r="N867" s="1">
-        <v>220000</v>
-      </c>
-      <c r="O867" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P867" t="str">
-        <v>20260702/하이얼_대구 착지 2곳_벌크_출하</v>
-      </c>
-      <c r="Q867" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R867" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="868">
-      <c r="A868" t="str">
-        <v>T260702-00001</v>
-      </c>
-      <c r="B868" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C868" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D868" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E868" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="F868">
-        <v>0</v>
-      </c>
-      <c r="G868" t="str">
-        <v>로지스밸리인천포트(Logisvalley)</v>
-      </c>
-      <c r="H868" t="str">
-        <v>인천 연수구 인천타워대로599번길 60 로지스밸리인천포트(Logisvalley) 1층 13번(HTC)</v>
-      </c>
-      <c r="I868" t="str">
-        <v>2026-07-02 11:00</v>
-      </c>
-      <c r="J868" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K868">
-        <v>1</v>
-      </c>
-      <c r="L868" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M868" t="str">
-        <v>2026-07-02 09:17:29</v>
-      </c>
-      <c r="N868" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O868" s="1">
-        <v>0</v>
-      </c>
-      <c r="P868" t="str">
-        <v>패스트레인 출하</v>
-      </c>
-      <c r="Q868" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R868" t="str">
-        <v>패스트레인코리아</v>
-      </c>
-    </row>
-    <row r="869">
-      <c r="A869" t="str">
-        <v>T260701-00026</v>
-      </c>
-      <c r="B869" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C869" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D869" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E869" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F869">
-        <v>1</v>
-      </c>
-      <c r="G869" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H869" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I869" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J869" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K869">
-        <v>1</v>
-      </c>
-      <c r="L869" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M869" t="str">
-        <v>2026-07-01 19:47:13</v>
-      </c>
-      <c r="N869" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O869" s="1">
-        <v>0</v>
-      </c>
-      <c r="P869" t="str">
-        <v/>
-      </c>
-      <c r="Q869" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R869" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="870">
-      <c r="A870" t="str">
-        <v>T260701-00025</v>
-      </c>
-      <c r="B870" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C870" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D870" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E870" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F870">
-        <v>2</v>
-      </c>
-      <c r="G870" t="str">
-        <v>원주ACP</v>
-      </c>
-      <c r="H870" t="str">
-        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
-      </c>
-      <c r="I870" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J870" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K870">
-        <v>1</v>
-      </c>
-      <c r="L870" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M870" t="str">
-        <v>2026-07-01 19:46:48</v>
-      </c>
-      <c r="N870" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O870" s="1">
-        <v>0</v>
-      </c>
-      <c r="P870" t="str">
-        <v/>
-      </c>
-      <c r="Q870" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R870" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="871">
-      <c r="A871" t="str">
-        <v>T260701-00024</v>
-      </c>
-      <c r="B871" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C871" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D871" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E871" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F871">
-        <v>1</v>
-      </c>
-      <c r="G871" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H871" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I871" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J871" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K871">
-        <v>1</v>
-      </c>
-      <c r="L871" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M871" t="str">
-        <v>2026-07-01 19:46:12</v>
-      </c>
-      <c r="N871" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O871" s="1">
-        <v>0</v>
-      </c>
-      <c r="P871" t="str">
-        <v/>
-      </c>
-      <c r="Q871" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R871" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="872">
-      <c r="A872" t="str">
-        <v>T260701-00023</v>
-      </c>
-      <c r="B872" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C872" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D872" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E872" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F872">
-        <v>3</v>
-      </c>
-      <c r="G872" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H872" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I872" t="str">
-        <v>2026-07-02 07:00</v>
-      </c>
-      <c r="J872" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K872">
-        <v>1</v>
-      </c>
-      <c r="L872" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M872" t="str">
-        <v>2026-07-01 19:45:40</v>
-      </c>
-      <c r="N872" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O872" s="1">
-        <v>0</v>
-      </c>
-      <c r="P872" t="str">
-        <v/>
-      </c>
-      <c r="Q872" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R872" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="873">
-      <c r="A873" t="str">
-        <v>T260701-00022</v>
-      </c>
-      <c r="B873" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C873" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D873" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E873" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F873">
-        <v>0</v>
-      </c>
-      <c r="G873" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H873" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I873" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J873" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K873">
-        <v>1</v>
-      </c>
-      <c r="L873" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M873" t="str">
-        <v>2026-07-01 19:44:56</v>
-      </c>
-      <c r="N873" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O873" s="1">
-        <v>0</v>
-      </c>
-      <c r="P873" t="str">
-        <v/>
-      </c>
-      <c r="Q873" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R873" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="874">
-      <c r="A874" t="str">
-        <v>T260701-00021</v>
-      </c>
-      <c r="B874" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C874" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D874" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E874" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F874">
-        <v>1</v>
-      </c>
-      <c r="G874" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H874" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I874" t="str">
-        <v>2026-07-02 08:00</v>
-      </c>
-      <c r="J874" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K874">
-        <v>1</v>
-      </c>
-      <c r="L874" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M874" t="str">
-        <v>2026-07-01 19:44:37</v>
-      </c>
-      <c r="N874" s="1">
-        <v>190000</v>
-      </c>
-      <c r="O874" s="1">
-        <v>0</v>
-      </c>
-      <c r="P874" t="str">
-        <v/>
-      </c>
-      <c r="Q874" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R874" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="875">
-      <c r="A875" t="str">
-        <v>T260701-00020</v>
-      </c>
-      <c r="B875" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C875" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D875" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E875" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F875">
-        <v>2</v>
-      </c>
-      <c r="G875" t="str">
-        <v>속초ACP</v>
-      </c>
-      <c r="H875" t="str">
-        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
-      </c>
-      <c r="I875" t="str">
-        <v>2026-07-02 06:00</v>
-      </c>
-      <c r="J875" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K875">
-        <v>1</v>
-      </c>
-      <c r="L875" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M875" t="str">
-        <v>2026-07-01 19:44:05</v>
-      </c>
-      <c r="N875" s="1">
-        <v>320000</v>
-      </c>
-      <c r="O875" s="1">
-        <v>0</v>
-      </c>
-      <c r="P875" t="str">
-        <v/>
-      </c>
-      <c r="Q875" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R875" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="876">
-      <c r="A876" t="str">
-        <v>T260701-00019</v>
-      </c>
-      <c r="B876" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C876" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D876" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E876" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F876">
-        <v>0</v>
-      </c>
-      <c r="G876" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H876" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I876" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J876" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K876">
-        <v>1</v>
-      </c>
-      <c r="L876" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M876" t="str">
-        <v>2026-07-01 19:43:22</v>
-      </c>
-      <c r="N876" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O876" s="1">
-        <v>0</v>
-      </c>
-      <c r="P876" t="str">
-        <v/>
-      </c>
-      <c r="Q876" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R876" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="877">
-      <c r="A877" t="str">
-        <v>T260701-00018</v>
-      </c>
-      <c r="B877" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C877" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D877" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E877" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F877">
-        <v>1</v>
-      </c>
-      <c r="G877" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H877" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I877" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J877" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K877">
-        <v>1</v>
-      </c>
-      <c r="L877" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M877" t="str">
-        <v>2026-07-01 19:43:03</v>
-      </c>
-      <c r="N877" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O877" s="1">
-        <v>0</v>
-      </c>
-      <c r="P877" t="str">
-        <v/>
-      </c>
-      <c r="Q877" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R877" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="878">
-      <c r="A878" t="str">
-        <v>T260701-00017</v>
-      </c>
-      <c r="B878" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C878" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D878" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E878" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F878">
-        <v>0</v>
-      </c>
-      <c r="G878" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H878" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I878" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J878" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K878">
-        <v>1</v>
-      </c>
-      <c r="L878" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M878" t="str">
-        <v>2026-07-01 19:42:39</v>
-      </c>
-      <c r="N878" s="1">
-        <v>310000</v>
-      </c>
-      <c r="O878" s="1">
-        <v>0</v>
-      </c>
-      <c r="P878" t="str">
-        <v/>
-      </c>
-      <c r="Q878" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R878" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="879">
-      <c r="A879" t="str">
-        <v>T260701-00016</v>
-      </c>
-      <c r="B879" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C879" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D879" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E879" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F879">
-        <v>0</v>
-      </c>
-      <c r="G879" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H879" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I879" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J879" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K879">
-        <v>1</v>
-      </c>
-      <c r="L879" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M879" t="str">
-        <v>2026-07-01 19:42:17</v>
-      </c>
-      <c r="N879" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O879" s="1">
-        <v>0</v>
-      </c>
-      <c r="P879" t="str">
-        <v/>
-      </c>
-      <c r="Q879" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R879" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="880">
-      <c r="A880" t="str">
-        <v>T260701-00015</v>
-      </c>
-      <c r="B880" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C880" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D880" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E880" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F880">
-        <v>1</v>
-      </c>
-      <c r="G880" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H880" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I880" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J880" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K880">
-        <v>1</v>
-      </c>
-      <c r="L880" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M880" t="str">
-        <v>2026-07-01 19:42:02</v>
-      </c>
-      <c r="N880" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O880" s="1">
-        <v>0</v>
-      </c>
-      <c r="P880" t="str">
-        <v/>
-      </c>
-      <c r="Q880" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R880" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="881">
-      <c r="A881" t="str">
-        <v>T260701-00014</v>
-      </c>
-      <c r="B881" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C881" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D881" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E881" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F881">
-        <v>1</v>
-      </c>
-      <c r="G881" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H881" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I881" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J881" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K881">
-        <v>1</v>
-      </c>
-      <c r="L881" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M881" t="str">
-        <v>2026-07-01 19:41:41</v>
-      </c>
-      <c r="N881" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O881" s="1">
-        <v>0</v>
-      </c>
-      <c r="P881" t="str">
-        <v/>
-      </c>
-      <c r="Q881" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R881" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="882">
-      <c r="A882" t="str">
-        <v>T260701-00013</v>
-      </c>
-      <c r="B882" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C882" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D882" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E882" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F882">
-        <v>1</v>
-      </c>
-      <c r="G882" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H882" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I882" t="str">
-        <v>2026-07-01 22:00</v>
-      </c>
-      <c r="J882" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K882">
-        <v>1</v>
-      </c>
-      <c r="L882" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M882" t="str">
-        <v>2026-07-01 19:41:08</v>
-      </c>
-      <c r="N882" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O882" s="1">
-        <v>0</v>
-      </c>
-      <c r="P882" t="str">
-        <v/>
-      </c>
-      <c r="Q882" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R882" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="883">
-      <c r="A883" t="str">
-        <v>T260701-00012</v>
-      </c>
-      <c r="B883" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C883" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D883" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E883" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F883">
-        <v>1</v>
-      </c>
-      <c r="G883" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H883" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I883" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J883" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K883">
-        <v>1</v>
-      </c>
-      <c r="L883" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M883" t="str">
-        <v>2026-07-01 19:40:45</v>
-      </c>
-      <c r="N883" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O883" s="1">
-        <v>0</v>
-      </c>
-      <c r="P883" t="str">
-        <v/>
-      </c>
-      <c r="Q883" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R883" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="884">
-      <c r="A884" t="str">
-        <v>T260701-00011</v>
-      </c>
-      <c r="B884" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C884" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D884" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E884" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F884">
-        <v>0</v>
-      </c>
-      <c r="G884" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H884" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I884" t="str">
-        <v>2026-07-01 21:00</v>
-      </c>
-      <c r="J884" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K884">
-        <v>1</v>
-      </c>
-      <c r="L884" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M884" t="str">
-        <v>2026-07-01 19:40:21</v>
-      </c>
-      <c r="N884" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O884" s="1">
-        <v>0</v>
-      </c>
-      <c r="P884" t="str">
-        <v/>
-      </c>
-      <c r="Q884" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R884" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="885">
-      <c r="A885" t="str">
-        <v>T260701-00010</v>
-      </c>
-      <c r="B885" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C885" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D885" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E885" t="str">
-        <v>2026-07-01 19:00</v>
-      </c>
-      <c r="F885">
-        <v>1</v>
-      </c>
-      <c r="G885" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H885" t="str">
-        <v>경산시 해오름길114-2 경산FDC</v>
-      </c>
-      <c r="I885" t="str">
-        <v>2026-07-01 23:00</v>
-      </c>
-      <c r="J885" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K885">
-        <v>1</v>
-      </c>
-      <c r="L885" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M885" t="str">
-        <v>2026-07-01 19:40:04</v>
-      </c>
-      <c r="N885" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O885" s="1">
-        <v>0</v>
-      </c>
-      <c r="P885" t="str">
-        <v/>
-      </c>
-      <c r="Q885" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R885" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="886">
-      <c r="A886" t="str">
-        <v>T260701-00009</v>
-      </c>
-      <c r="B886" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C886" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D886" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E886" t="str">
-        <v>2026-07-01 17:30</v>
-      </c>
-      <c r="F886">
-        <v>0</v>
-      </c>
-      <c r="G886" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H886" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I886" t="str">
-        <v>2026-07-01 18:30</v>
-      </c>
-      <c r="J886" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K886">
-        <v>1</v>
-      </c>
-      <c r="L886" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M886" t="str">
-        <v>2026-07-01 19:31:35</v>
-      </c>
-      <c r="N886" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O886" s="1">
-        <v>0</v>
-      </c>
-      <c r="P886" t="str">
-        <v/>
-      </c>
-      <c r="Q886" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R886" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="887">
-      <c r="A887" t="str">
-        <v>T260701-00008</v>
-      </c>
-      <c r="B887" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C887" t="str">
-        <v>듀오백(화성)</v>
-      </c>
-      <c r="D887" t="str">
-        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
-      </c>
-      <c r="E887" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="F887">
-        <v>0</v>
-      </c>
-      <c r="G887" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H887" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I887" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="J887" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K887">
-        <v>1</v>
-      </c>
-      <c r="L887" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M887" t="str">
-        <v>2026-07-01 19:31:02</v>
-      </c>
-      <c r="N887" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O887" s="1">
-        <v>0</v>
-      </c>
-      <c r="P887" t="str">
-        <v>듀오백(화성) 외주사입고</v>
-      </c>
-      <c r="Q887" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R887" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="888">
-      <c r="A888" t="str">
-        <v>T260701-00007</v>
-      </c>
-      <c r="B888" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C888" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D888" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E888" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F888">
-        <v>0</v>
-      </c>
-      <c r="G888" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H888" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I888" t="str">
-        <v>2026-07-01 13:30</v>
-      </c>
-      <c r="J888" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K888">
-        <v>1</v>
-      </c>
-      <c r="L888" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M888" t="str">
-        <v>2026-07-01 19:29:27</v>
-      </c>
-      <c r="N888" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O888" s="1">
-        <v>0</v>
-      </c>
-      <c r="P888" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q888" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R888" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="889">
-      <c r="A889" t="str">
-        <v>T260701-00006</v>
-      </c>
-      <c r="B889" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C889" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D889" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E889" t="str">
-        <v>2026-07-01 16:30</v>
-      </c>
-      <c r="F889">
-        <v>0</v>
-      </c>
-      <c r="G889" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H889" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I889" t="str">
-        <v>2026-07-01 18:00</v>
-      </c>
-      <c r="J889" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K889">
-        <v>1</v>
-      </c>
-      <c r="L889" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M889" t="str">
-        <v>2026-07-01 16:09:24</v>
-      </c>
-      <c r="N889" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O889" s="1">
-        <v>0</v>
-      </c>
-      <c r="P889" t="str">
-        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
-      </c>
-      <c r="Q889" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R889" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="890">
-      <c r="A890" t="str">
-        <v>T260701-00005</v>
-      </c>
-      <c r="B890" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C890" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D890" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E890" t="str">
-        <v>2026-07-01 15:30</v>
-      </c>
-      <c r="F890">
-        <v>0</v>
-      </c>
-      <c r="G890" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H890" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I890" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J890" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K890">
-        <v>1</v>
-      </c>
-      <c r="L890" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M890" t="str">
-        <v>2026-07-01 14:58:37</v>
-      </c>
-      <c r="N890" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O890" s="1">
-        <v>0</v>
-      </c>
-      <c r="P890" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q890" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R890" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="891">
-      <c r="A891" t="str">
-        <v>T260701-00004</v>
-      </c>
-      <c r="B891" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C891" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D891" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E891" t="str">
-        <v>2026-07-01 15:20</v>
-      </c>
-      <c r="F891">
-        <v>0</v>
-      </c>
-      <c r="G891" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H891" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I891" t="str">
-        <v>2026-07-02 09:00</v>
-      </c>
-      <c r="J891" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K891">
-        <v>1</v>
-      </c>
-      <c r="L891" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M891" t="str">
-        <v>2026-07-01 14:53:20</v>
-      </c>
-      <c r="N891" s="1">
-        <v>440000</v>
-      </c>
-      <c r="O891" s="1">
-        <v>0</v>
-      </c>
-      <c r="P891" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q891" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R891" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="892">
-      <c r="A892" t="str">
-        <v>T260701-00003</v>
-      </c>
-      <c r="B892" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C892" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D892" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E892" t="str">
-        <v>2026-07-01 10:00</v>
-      </c>
-      <c r="F892">
-        <v>0</v>
-      </c>
-      <c r="G892" t="str">
-        <v>하이얼(이천다코넷)</v>
-      </c>
-      <c r="H892" t="str">
-        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
-      </c>
-      <c r="I892" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J892" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K892">
-        <v>1</v>
-      </c>
-      <c r="L892" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M892" t="str">
-        <v>2026-07-01 10:15:38</v>
-      </c>
-      <c r="N892" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O892" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P892" t="str">
-        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
-      </c>
-      <c r="Q892" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R892" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="893">
-      <c r="A893" t="str">
-        <v>T260701-00002</v>
-      </c>
-      <c r="B893" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C893" t="str">
-        <v>청주ARC(디지탈태양)</v>
-      </c>
-      <c r="D893" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
-      </c>
-      <c r="E893" t="str">
-        <v>2026-07-01 08:30</v>
-      </c>
-      <c r="F893">
-        <v>0</v>
-      </c>
-      <c r="G893" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H893" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="I893" t="str">
-        <v>2026-07-01 10:30</v>
-      </c>
-      <c r="J893" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K893">
-        <v>1</v>
-      </c>
-      <c r="L893" t="str">
-        <v>신소라</v>
-      </c>
-      <c r="M893" t="str">
-        <v>2026-07-01 10:13:39</v>
-      </c>
-      <c r="N893" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O893" s="1">
-        <v>0</v>
-      </c>
-      <c r="P893" t="str">
-        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
-      </c>
-      <c r="Q893" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R893" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="894">
-      <c r="A894" t="str">
-        <v>T260701-00001</v>
-      </c>
-      <c r="B894" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C894" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D894" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E894" t="str">
-        <v>2026-07-01 09:00</v>
-      </c>
-      <c r="F894">
-        <v>0</v>
-      </c>
-      <c r="G894" t="str">
-        <v>현대클러스터 한강미사3차</v>
-      </c>
-      <c r="H894" t="str">
-        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
-      </c>
-      <c r="I894" t="str">
-        <v>2026-07-01 11:00</v>
-      </c>
-      <c r="J894" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K894">
-        <v>1</v>
-      </c>
-      <c r="L894" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M894" t="str">
-        <v>2026-07-01 09:07:09</v>
-      </c>
-      <c r="N894" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O894" s="1">
-        <v>0</v>
-      </c>
-      <c r="P894" t="str">
-        <v>스마트윈드 출하</v>
-      </c>
-      <c r="Q894" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R894" t="str">
-        <v>스마트윈드</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R894"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R746"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R746"/>
+  <dimension ref="A1:R894"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -42156,9 +42156,8297 @@
         <v>고카트</v>
       </c>
     </row>
+    <row r="747">
+      <c r="A747" t="str">
+        <v>T260707-00030</v>
+      </c>
+      <c r="B747" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C747" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D747" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E747" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F747">
+        <v>1</v>
+      </c>
+      <c r="G747" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H747" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I747" t="str">
+        <v>2026-07-08 08:00</v>
+      </c>
+      <c r="J747" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K747">
+        <v>1</v>
+      </c>
+      <c r="L747" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M747" t="str">
+        <v>2026-07-07 20:49:37</v>
+      </c>
+      <c r="N747" s="1">
+        <v>220000</v>
+      </c>
+      <c r="O747" s="1">
+        <v>0</v>
+      </c>
+      <c r="P747" t="str">
+        <v/>
+      </c>
+      <c r="Q747" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R747" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="str">
+        <v>T260707-00029</v>
+      </c>
+      <c r="B748" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C748" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D748" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E748" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F748">
+        <v>0</v>
+      </c>
+      <c r="G748" t="str">
+        <v>용인ACP</v>
+      </c>
+      <c r="H748" t="str">
+        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
+      </c>
+      <c r="I748" t="str">
+        <v>2026-07-08 07:00</v>
+      </c>
+      <c r="J748" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K748">
+        <v>1</v>
+      </c>
+      <c r="L748" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M748" t="str">
+        <v>2026-07-07 20:49:13</v>
+      </c>
+      <c r="N748" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O748" s="1">
+        <v>0</v>
+      </c>
+      <c r="P748" t="str">
+        <v/>
+      </c>
+      <c r="Q748" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R748" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="str">
+        <v>T260707-00028</v>
+      </c>
+      <c r="B749" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C749" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D749" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E749" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F749">
+        <v>1</v>
+      </c>
+      <c r="G749" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H749" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I749" t="str">
+        <v>2026-07-08 08:00</v>
+      </c>
+      <c r="J749" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K749">
+        <v>1</v>
+      </c>
+      <c r="L749" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M749" t="str">
+        <v>2026-07-07 20:48:56</v>
+      </c>
+      <c r="N749" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O749" s="1">
+        <v>0</v>
+      </c>
+      <c r="P749" t="str">
+        <v/>
+      </c>
+      <c r="Q749" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R749" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="str">
+        <v>T260707-00027</v>
+      </c>
+      <c r="B750" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C750" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D750" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E750" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F750">
+        <v>0</v>
+      </c>
+      <c r="G750" t="str">
+        <v>시흥ACP</v>
+      </c>
+      <c r="H750" t="str">
+        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
+      </c>
+      <c r="I750" t="str">
+        <v>2026-07-08 07:00</v>
+      </c>
+      <c r="J750" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K750">
+        <v>1</v>
+      </c>
+      <c r="L750" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M750" t="str">
+        <v>2026-07-07 20:48:32</v>
+      </c>
+      <c r="N750" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O750" s="1">
+        <v>0</v>
+      </c>
+      <c r="P750" t="str">
+        <v/>
+      </c>
+      <c r="Q750" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R750" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="str">
+        <v>T260707-00026</v>
+      </c>
+      <c r="B751" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C751" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D751" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E751" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F751">
+        <v>3</v>
+      </c>
+      <c r="G751" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H751" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I751" t="str">
+        <v>2026-07-08 07:00</v>
+      </c>
+      <c r="J751" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K751">
+        <v>1</v>
+      </c>
+      <c r="L751" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M751" t="str">
+        <v>2026-07-07 20:48:12</v>
+      </c>
+      <c r="N751" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O751" s="1">
+        <v>0</v>
+      </c>
+      <c r="P751" t="str">
+        <v/>
+      </c>
+      <c r="Q751" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R751" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="str">
+        <v>T260707-00025</v>
+      </c>
+      <c r="B752" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C752" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D752" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E752" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F752">
+        <v>0</v>
+      </c>
+      <c r="G752" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H752" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I752" t="str">
+        <v>2026-07-08 07:00</v>
+      </c>
+      <c r="J752" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K752">
+        <v>1</v>
+      </c>
+      <c r="L752" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M752" t="str">
+        <v>2026-07-07 20:47:33</v>
+      </c>
+      <c r="N752" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O752" s="1">
+        <v>0</v>
+      </c>
+      <c r="P752" t="str">
+        <v/>
+      </c>
+      <c r="Q752" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R752" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="str">
+        <v>T260707-00024</v>
+      </c>
+      <c r="B753" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C753" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D753" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E753" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F753">
+        <v>0</v>
+      </c>
+      <c r="G753" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H753" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I753" t="str">
+        <v>2026-07-07 21:00</v>
+      </c>
+      <c r="J753" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K753">
+        <v>1</v>
+      </c>
+      <c r="L753" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M753" t="str">
+        <v>2026-07-07 20:47:14</v>
+      </c>
+      <c r="N753" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O753" s="1">
+        <v>0</v>
+      </c>
+      <c r="P753" t="str">
+        <v/>
+      </c>
+      <c r="Q753" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R753" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="str">
+        <v>T260707-00023</v>
+      </c>
+      <c r="B754" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C754" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D754" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E754" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F754">
+        <v>0</v>
+      </c>
+      <c r="G754" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H754" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I754" t="str">
+        <v>2026-07-07 21:00</v>
+      </c>
+      <c r="J754" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K754">
+        <v>1</v>
+      </c>
+      <c r="L754" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M754" t="str">
+        <v>2026-07-07 20:47:00</v>
+      </c>
+      <c r="N754" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O754" s="1">
+        <v>0</v>
+      </c>
+      <c r="P754" t="str">
+        <v/>
+      </c>
+      <c r="Q754" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R754" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="str">
+        <v>T260707-00022</v>
+      </c>
+      <c r="B755" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C755" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D755" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E755" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F755">
+        <v>0</v>
+      </c>
+      <c r="G755" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="H755" t="str">
+        <v>충청남도 아산시 음봉면 월암로 265-16 가동 천안FDC</v>
+      </c>
+      <c r="I755" t="str">
+        <v>2026-07-07 21:00</v>
+      </c>
+      <c r="J755" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K755">
+        <v>1</v>
+      </c>
+      <c r="L755" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M755" t="str">
+        <v>2026-07-07 20:46:43</v>
+      </c>
+      <c r="N755" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O755" s="1">
+        <v>0</v>
+      </c>
+      <c r="P755" t="str">
+        <v/>
+      </c>
+      <c r="Q755" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R755" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="str">
+        <v>T260707-00021</v>
+      </c>
+      <c r="B756" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C756" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D756" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E756" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F756">
+        <v>0</v>
+      </c>
+      <c r="G756" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H756" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I756" t="str">
+        <v>2026-07-07 23:00</v>
+      </c>
+      <c r="J756" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K756">
+        <v>1</v>
+      </c>
+      <c r="L756" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M756" t="str">
+        <v>2026-07-07 20:46:28</v>
+      </c>
+      <c r="N756" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O756" s="1">
+        <v>0</v>
+      </c>
+      <c r="P756" t="str">
+        <v/>
+      </c>
+      <c r="Q756" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R756" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="str">
+        <v>T260707-00020</v>
+      </c>
+      <c r="B757" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C757" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D757" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E757" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F757">
+        <v>0</v>
+      </c>
+      <c r="G757" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H757" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I757" t="str">
+        <v>2026-07-07 21:00</v>
+      </c>
+      <c r="J757" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K757">
+        <v>1</v>
+      </c>
+      <c r="L757" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M757" t="str">
+        <v>2026-07-07 20:46:14</v>
+      </c>
+      <c r="N757" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O757" s="1">
+        <v>0</v>
+      </c>
+      <c r="P757" t="str">
+        <v/>
+      </c>
+      <c r="Q757" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R757" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="str">
+        <v>T260707-00019</v>
+      </c>
+      <c r="B758" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C758" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D758" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E758" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F758">
+        <v>1</v>
+      </c>
+      <c r="G758" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H758" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I758" t="str">
+        <v>2026-07-07 22:00</v>
+      </c>
+      <c r="J758" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K758">
+        <v>1</v>
+      </c>
+      <c r="L758" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M758" t="str">
+        <v>2026-07-07 20:45:57</v>
+      </c>
+      <c r="N758" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O758" s="1">
+        <v>0</v>
+      </c>
+      <c r="P758" t="str">
+        <v/>
+      </c>
+      <c r="Q758" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R758" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="str">
+        <v>T260707-00018</v>
+      </c>
+      <c r="B759" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C759" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D759" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E759" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F759">
+        <v>1</v>
+      </c>
+      <c r="G759" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H759" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I759" t="str">
+        <v>2026-07-07 23:00</v>
+      </c>
+      <c r="J759" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K759">
+        <v>1</v>
+      </c>
+      <c r="L759" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M759" t="str">
+        <v>2026-07-07 20:45:38</v>
+      </c>
+      <c r="N759" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O759" s="1">
+        <v>0</v>
+      </c>
+      <c r="P759" t="str">
+        <v/>
+      </c>
+      <c r="Q759" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R759" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="str">
+        <v>T260707-00017</v>
+      </c>
+      <c r="B760" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C760" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D760" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E760" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F760">
+        <v>0</v>
+      </c>
+      <c r="G760" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H760" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I760" t="str">
+        <v>2026-07-07 21:00</v>
+      </c>
+      <c r="J760" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K760">
+        <v>1</v>
+      </c>
+      <c r="L760" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M760" t="str">
+        <v>2026-07-07 20:45:15</v>
+      </c>
+      <c r="N760" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O760" s="1">
+        <v>0</v>
+      </c>
+      <c r="P760" t="str">
+        <v/>
+      </c>
+      <c r="Q760" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R760" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="str">
+        <v>T260707-00016</v>
+      </c>
+      <c r="B761" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C761" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D761" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E761" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F761">
+        <v>0</v>
+      </c>
+      <c r="G761" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H761" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I761" t="str">
+        <v>2026-07-07 21:00</v>
+      </c>
+      <c r="J761" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K761">
+        <v>1</v>
+      </c>
+      <c r="L761" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M761" t="str">
+        <v>2026-07-07 20:45:00</v>
+      </c>
+      <c r="N761" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O761" s="1">
+        <v>0</v>
+      </c>
+      <c r="P761" t="str">
+        <v/>
+      </c>
+      <c r="Q761" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R761" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="str">
+        <v>T260707-00015</v>
+      </c>
+      <c r="B762" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C762" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D762" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E762" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F762">
+        <v>1</v>
+      </c>
+      <c r="G762" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H762" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I762" t="str">
+        <v>2026-07-07 23:00</v>
+      </c>
+      <c r="J762" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K762">
+        <v>1</v>
+      </c>
+      <c r="L762" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M762" t="str">
+        <v>2026-07-07 20:44:42</v>
+      </c>
+      <c r="N762" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O762" s="1">
+        <v>0</v>
+      </c>
+      <c r="P762" t="str">
+        <v/>
+      </c>
+      <c r="Q762" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R762" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="str">
+        <v>T260707-00014</v>
+      </c>
+      <c r="B763" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C763" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D763" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E763" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F763">
+        <v>0</v>
+      </c>
+      <c r="G763" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H763" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I763" t="str">
+        <v>2026-07-07 21:00</v>
+      </c>
+      <c r="J763" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K763">
+        <v>1</v>
+      </c>
+      <c r="L763" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M763" t="str">
+        <v>2026-07-07 20:44:21</v>
+      </c>
+      <c r="N763" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O763" s="1">
+        <v>0</v>
+      </c>
+      <c r="P763" t="str">
+        <v/>
+      </c>
+      <c r="Q763" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R763" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="str">
+        <v>T260707-00013</v>
+      </c>
+      <c r="B764" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C764" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D764" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E764" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F764">
+        <v>1</v>
+      </c>
+      <c r="G764" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H764" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="I764" t="str">
+        <v>2026-07-07 23:00</v>
+      </c>
+      <c r="J764" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K764">
+        <v>1</v>
+      </c>
+      <c r="L764" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M764" t="str">
+        <v>2026-07-07 20:44:05</v>
+      </c>
+      <c r="N764" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O764" s="1">
+        <v>0</v>
+      </c>
+      <c r="P764" t="str">
+        <v/>
+      </c>
+      <c r="Q764" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R764" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="str">
+        <v>T260707-00012</v>
+      </c>
+      <c r="B765" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C765" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D765" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E765" t="str">
+        <v>2026-07-07 19:00</v>
+      </c>
+      <c r="F765">
+        <v>0</v>
+      </c>
+      <c r="G765" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="H765" t="str">
+        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="I765" t="str">
+        <v>2026-07-07 22:00</v>
+      </c>
+      <c r="J765" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K765">
+        <v>1</v>
+      </c>
+      <c r="L765" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M765" t="str">
+        <v>2026-07-07 20:43:44</v>
+      </c>
+      <c r="N765" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O765" s="1">
+        <v>0</v>
+      </c>
+      <c r="P765" t="str">
+        <v/>
+      </c>
+      <c r="Q765" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R765" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="str">
+        <v>T260707-00011</v>
+      </c>
+      <c r="B766" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C766" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D766" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E766" t="str">
+        <v>2026-07-07 17:40</v>
+      </c>
+      <c r="F766">
+        <v>0</v>
+      </c>
+      <c r="G766" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H766" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I766" t="str">
+        <v>2026-07-07 18:40</v>
+      </c>
+      <c r="J766" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K766">
+        <v>1</v>
+      </c>
+      <c r="L766" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M766" t="str">
+        <v>2026-07-07 20:41:08</v>
+      </c>
+      <c r="N766" s="1">
+        <v>130000</v>
+      </c>
+      <c r="O766" s="1">
+        <v>0</v>
+      </c>
+      <c r="P766" t="str">
+        <v/>
+      </c>
+      <c r="Q766" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R766" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="str">
+        <v>T260707-00010</v>
+      </c>
+      <c r="B767" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C767" t="str">
+        <v>화성FDC</v>
+      </c>
+      <c r="D767" t="str">
+        <v>경기 화성시 장안면 3.1만세로 506-21 화성FDC</v>
+      </c>
+      <c r="E767" t="str">
+        <v>2026-07-07 12:40</v>
+      </c>
+      <c r="F767">
+        <v>0</v>
+      </c>
+      <c r="G767" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="H767" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="I767" t="str">
+        <v>2026-07-07 14:40</v>
+      </c>
+      <c r="J767" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K767">
+        <v>1</v>
+      </c>
+      <c r="L767" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M767" t="str">
+        <v>2026-07-07 20:40:36</v>
+      </c>
+      <c r="N767" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O767" s="1">
+        <v>0</v>
+      </c>
+      <c r="P767" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="Q767" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R767" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="str">
+        <v>T260707-00009</v>
+      </c>
+      <c r="B768" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C768" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="D768" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5 김포FDC</v>
+      </c>
+      <c r="E768" t="str">
+        <v>2026-07-07 21:40</v>
+      </c>
+      <c r="F768">
+        <v>0</v>
+      </c>
+      <c r="G768" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="H768" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="I768" t="str">
+        <v>2026-07-08 08:40</v>
+      </c>
+      <c r="J768" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K768">
+        <v>1</v>
+      </c>
+      <c r="L768" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M768" t="str">
+        <v>2026-07-07 20:39:57</v>
+      </c>
+      <c r="N768" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O768" s="1">
+        <v>0</v>
+      </c>
+      <c r="P768" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="Q768" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R768" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="str">
+        <v>T260707-00008</v>
+      </c>
+      <c r="B769" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C769" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D769" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E769" t="str">
+        <v>2026-07-07 13:40</v>
+      </c>
+      <c r="F769">
+        <v>0</v>
+      </c>
+      <c r="G769" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H769" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I769" t="str">
+        <v>2026-07-07 15:40</v>
+      </c>
+      <c r="J769" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K769">
+        <v>1</v>
+      </c>
+      <c r="L769" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M769" t="str">
+        <v>2026-07-07 20:39:13</v>
+      </c>
+      <c r="N769" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O769" s="1">
+        <v>0</v>
+      </c>
+      <c r="P769" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q769" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R769" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="str">
+        <v>T260707-00007</v>
+      </c>
+      <c r="B770" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C770" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D770" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E770" t="str">
+        <v>2026-07-07 10:00</v>
+      </c>
+      <c r="F770">
+        <v>0</v>
+      </c>
+      <c r="G770" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H770" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I770" t="str">
+        <v>2026-07-07 13:40</v>
+      </c>
+      <c r="J770" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K770">
+        <v>1</v>
+      </c>
+      <c r="L770" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M770" t="str">
+        <v>2026-07-07 20:38:35</v>
+      </c>
+      <c r="N770" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O770" s="1">
+        <v>0</v>
+      </c>
+      <c r="P770" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q770" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R770" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="str">
+        <v>T260707-00006</v>
+      </c>
+      <c r="B771" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C771" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D771" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E771" t="str">
+        <v>2026-07-07 16:30</v>
+      </c>
+      <c r="F771">
+        <v>0</v>
+      </c>
+      <c r="G771" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H771" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I771" t="str">
+        <v>2026-07-07 18:00</v>
+      </c>
+      <c r="J771" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K771">
+        <v>1</v>
+      </c>
+      <c r="L771" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M771" t="str">
+        <v>2026-07-07 15:57:50</v>
+      </c>
+      <c r="N771" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O771" s="1">
+        <v>0</v>
+      </c>
+      <c r="P771" t="str">
+        <v>20260707/경동택배_남이가마258 영업소_파렛트 출하</v>
+      </c>
+      <c r="Q771" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R771" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="str">
+        <v>T260707-00005</v>
+      </c>
+      <c r="B772" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C772" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D772" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E772" t="str">
+        <v>2026-07-07 11:40</v>
+      </c>
+      <c r="F772">
+        <v>0</v>
+      </c>
+      <c r="G772" t="str">
+        <v>캐리어 신양지 물류</v>
+      </c>
+      <c r="H772" t="str">
+        <v>경기 용인시 처인구 원삼면 죽양대로1626번길 42 캐리어 신양지 물류</v>
+      </c>
+      <c r="I772" t="str">
+        <v>2026-07-07 14:00</v>
+      </c>
+      <c r="J772" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K772">
+        <v>1</v>
+      </c>
+      <c r="L772" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M772" t="str">
+        <v>2026-07-07 10:57:56</v>
+      </c>
+      <c r="N772" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O772" s="1">
+        <v>0</v>
+      </c>
+      <c r="P772" t="str">
+        <v>명경전자 캐리어 신양지 물류</v>
+      </c>
+      <c r="Q772" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R772" t="str">
+        <v>명경전자</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="str">
+        <v>T260707-00004</v>
+      </c>
+      <c r="B773" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C773" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D773" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E773" t="str">
+        <v>2026-07-07 11:20</v>
+      </c>
+      <c r="F773">
+        <v>0</v>
+      </c>
+      <c r="G773" t="str">
+        <v>캐리어 신양지 물류</v>
+      </c>
+      <c r="H773" t="str">
+        <v>경기 용인시 처인구 원삼면 죽양대로1626번길 42 캐리어 신양지 물류</v>
+      </c>
+      <c r="I773" t="str">
+        <v>2026-07-07 01:20</v>
+      </c>
+      <c r="J773" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K773">
+        <v>1</v>
+      </c>
+      <c r="L773" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M773" t="str">
+        <v>2026-07-07 10:20:11</v>
+      </c>
+      <c r="N773" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O773" s="1">
+        <v>0</v>
+      </c>
+      <c r="P773" t="str">
+        <v>명경전자 캐리어 신양지 물류</v>
+      </c>
+      <c r="Q773" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R773" t="str">
+        <v>명경전자</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="str">
+        <v>T260707-00003</v>
+      </c>
+      <c r="B774" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C774" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D774" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E774" t="str">
+        <v>2026-07-07 10:20</v>
+      </c>
+      <c r="F774">
+        <v>0</v>
+      </c>
+      <c r="G774" t="str">
+        <v>캐리어 신양지 물류</v>
+      </c>
+      <c r="H774" t="str">
+        <v>경기 용인시 처인구 원삼면 죽양대로1626번길 42 캐리어 신양지 물류</v>
+      </c>
+      <c r="I774" t="str">
+        <v>2026-07-07 01:20</v>
+      </c>
+      <c r="J774" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K774">
+        <v>1</v>
+      </c>
+      <c r="L774" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M774" t="str">
+        <v>2026-07-07 10:19:53</v>
+      </c>
+      <c r="N774" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O774" s="1">
+        <v>0</v>
+      </c>
+      <c r="P774" t="str">
+        <v>명경전자 캐리어 신양지 물류</v>
+      </c>
+      <c r="Q774" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R774" t="str">
+        <v>명경전자</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="str">
+        <v>T260707-00002</v>
+      </c>
+      <c r="B775" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C775" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D775" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E775" t="str">
+        <v>2026-07-07 09:20</v>
+      </c>
+      <c r="F775">
+        <v>0</v>
+      </c>
+      <c r="G775" t="str">
+        <v>캐리어 신양지 물류</v>
+      </c>
+      <c r="H775" t="str">
+        <v>경기 용인시 처인구 원삼면 죽양대로1626번길 42 캐리어 신양지 물류</v>
+      </c>
+      <c r="I775" t="str">
+        <v>2026-07-07 11:20</v>
+      </c>
+      <c r="J775" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K775">
+        <v>1</v>
+      </c>
+      <c r="L775" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M775" t="str">
+        <v>2026-07-07 10:19:33</v>
+      </c>
+      <c r="N775" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O775" s="1">
+        <v>0</v>
+      </c>
+      <c r="P775" t="str">
+        <v>명경전자 캐리어 신양지 물류</v>
+      </c>
+      <c r="Q775" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R775" t="str">
+        <v>명경전자</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="str">
+        <v>T260707-00001</v>
+      </c>
+      <c r="B776" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C776" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D776" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E776" t="str">
+        <v>2026-07-07 09:00</v>
+      </c>
+      <c r="F776">
+        <v>0</v>
+      </c>
+      <c r="G776" t="str">
+        <v>캐리어 신양지 물류</v>
+      </c>
+      <c r="H776" t="str">
+        <v>경기 용인시 처인구 원삼면 죽양대로1626번길 42 캐리어 신양지 물류</v>
+      </c>
+      <c r="I776" t="str">
+        <v>2026-07-07 11:00</v>
+      </c>
+      <c r="J776" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K776">
+        <v>1</v>
+      </c>
+      <c r="L776" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M776" t="str">
+        <v>2026-07-07 09:21:00</v>
+      </c>
+      <c r="N776" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O776" s="1">
+        <v>0</v>
+      </c>
+      <c r="P776" t="str">
+        <v>명경전자 캐리어 신양지 물류</v>
+      </c>
+      <c r="Q776" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R776" t="str">
+        <v>명경전자</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="str">
+        <v>T260706-00031</v>
+      </c>
+      <c r="B777" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C777" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D777" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E777" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F777">
+        <v>0</v>
+      </c>
+      <c r="G777" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H777" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I777" t="str">
+        <v>2026-07-07 07:00</v>
+      </c>
+      <c r="J777" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K777">
+        <v>1</v>
+      </c>
+      <c r="L777" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M777" t="str">
+        <v>2026-07-06 20:43:10</v>
+      </c>
+      <c r="N777" s="1">
+        <v>130000</v>
+      </c>
+      <c r="O777" s="1">
+        <v>0</v>
+      </c>
+      <c r="P777" t="str">
+        <v/>
+      </c>
+      <c r="Q777" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R777" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="str">
+        <v>T260706-00030</v>
+      </c>
+      <c r="B778" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C778" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D778" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E778" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F778">
+        <v>1</v>
+      </c>
+      <c r="G778" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H778" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I778" t="str">
+        <v>2026-07-07 08:00</v>
+      </c>
+      <c r="J778" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K778">
+        <v>1</v>
+      </c>
+      <c r="L778" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M778" t="str">
+        <v>2026-07-06 20:42:49</v>
+      </c>
+      <c r="N778" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O778" s="1">
+        <v>0</v>
+      </c>
+      <c r="P778" t="str">
+        <v/>
+      </c>
+      <c r="Q778" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R778" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="str">
+        <v>T260706-00029</v>
+      </c>
+      <c r="B779" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C779" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D779" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E779" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F779">
+        <v>2</v>
+      </c>
+      <c r="G779" t="str">
+        <v>원주ACP</v>
+      </c>
+      <c r="H779" t="str">
+        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
+      </c>
+      <c r="I779" t="str">
+        <v>2026-07-07 07:00</v>
+      </c>
+      <c r="J779" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K779">
+        <v>1</v>
+      </c>
+      <c r="L779" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M779" t="str">
+        <v>2026-07-06 20:42:20</v>
+      </c>
+      <c r="N779" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O779" s="1">
+        <v>0</v>
+      </c>
+      <c r="P779" t="str">
+        <v/>
+      </c>
+      <c r="Q779" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R779" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="str">
+        <v>T260706-00028</v>
+      </c>
+      <c r="B780" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C780" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D780" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E780" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F780">
+        <v>1</v>
+      </c>
+      <c r="G780" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H780" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I780" t="str">
+        <v>2026-07-07 08:00</v>
+      </c>
+      <c r="J780" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K780">
+        <v>1</v>
+      </c>
+      <c r="L780" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M780" t="str">
+        <v>2026-07-06 20:41:21</v>
+      </c>
+      <c r="N780" s="1">
+        <v>170000</v>
+      </c>
+      <c r="O780" s="1">
+        <v>0</v>
+      </c>
+      <c r="P780" t="str">
+        <v/>
+      </c>
+      <c r="Q780" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R780" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="str">
+        <v>T260706-00027</v>
+      </c>
+      <c r="B781" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C781" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D781" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E781" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F781">
+        <v>1</v>
+      </c>
+      <c r="G781" t="str">
+        <v>속초ACP</v>
+      </c>
+      <c r="H781" t="str">
+        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
+      </c>
+      <c r="I781" t="str">
+        <v>2026-07-07 08:00</v>
+      </c>
+      <c r="J781" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K781">
+        <v>1</v>
+      </c>
+      <c r="L781" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M781" t="str">
+        <v>2026-07-06 20:40:49</v>
+      </c>
+      <c r="N781" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O781" s="1">
+        <v>0</v>
+      </c>
+      <c r="P781" t="str">
+        <v/>
+      </c>
+      <c r="Q781" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R781" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="str">
+        <v>T260706-00026</v>
+      </c>
+      <c r="B782" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C782" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D782" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E782" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F782">
+        <v>3</v>
+      </c>
+      <c r="G782" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H782" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I782" t="str">
+        <v>2026-07-07 07:00</v>
+      </c>
+      <c r="J782" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K782">
+        <v>1</v>
+      </c>
+      <c r="L782" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M782" t="str">
+        <v>2026-07-06 20:40:12</v>
+      </c>
+      <c r="N782" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O782" s="1">
+        <v>0</v>
+      </c>
+      <c r="P782" t="str">
+        <v/>
+      </c>
+      <c r="Q782" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R782" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="str">
+        <v>T260706-00025</v>
+      </c>
+      <c r="B783" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C783" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D783" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E783" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F783">
+        <v>0</v>
+      </c>
+      <c r="G783" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H783" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I783" t="str">
+        <v>2026-07-06 22:00</v>
+      </c>
+      <c r="J783" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K783">
+        <v>1</v>
+      </c>
+      <c r="L783" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M783" t="str">
+        <v>2026-07-06 20:39:25</v>
+      </c>
+      <c r="N783" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O783" s="1">
+        <v>0</v>
+      </c>
+      <c r="P783" t="str">
+        <v/>
+      </c>
+      <c r="Q783" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R783" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="str">
+        <v>T260706-00024</v>
+      </c>
+      <c r="B784" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C784" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D784" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E784" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F784">
+        <v>0</v>
+      </c>
+      <c r="G784" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H784" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I784" t="str">
+        <v>2026-07-07 07:00</v>
+      </c>
+      <c r="J784" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K784">
+        <v>1</v>
+      </c>
+      <c r="L784" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M784" t="str">
+        <v>2026-07-06 20:39:07</v>
+      </c>
+      <c r="N784" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O784" s="1">
+        <v>0</v>
+      </c>
+      <c r="P784" t="str">
+        <v/>
+      </c>
+      <c r="Q784" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R784" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="str">
+        <v>T260706-00023</v>
+      </c>
+      <c r="B785" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C785" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D785" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E785" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F785">
+        <v>0</v>
+      </c>
+      <c r="G785" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H785" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I785" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J785" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K785">
+        <v>1</v>
+      </c>
+      <c r="L785" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M785" t="str">
+        <v>2026-07-06 20:38:47</v>
+      </c>
+      <c r="N785" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O785" s="1">
+        <v>0</v>
+      </c>
+      <c r="P785" t="str">
+        <v/>
+      </c>
+      <c r="Q785" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R785" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="str">
+        <v>T260706-00022</v>
+      </c>
+      <c r="B786" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C786" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D786" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E786" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F786">
+        <v>0</v>
+      </c>
+      <c r="G786" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H786" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I786" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J786" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K786">
+        <v>1</v>
+      </c>
+      <c r="L786" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M786" t="str">
+        <v>2026-07-06 20:38:33</v>
+      </c>
+      <c r="N786" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O786" s="1">
+        <v>0</v>
+      </c>
+      <c r="P786" t="str">
+        <v/>
+      </c>
+      <c r="Q786" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R786" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="str">
+        <v>T260706-00021</v>
+      </c>
+      <c r="B787" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C787" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D787" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E787" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F787">
+        <v>0</v>
+      </c>
+      <c r="G787" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="H787" t="str">
+        <v>충청남도 아산시 음봉면 월암로 265-16 가동 천안FDC</v>
+      </c>
+      <c r="I787" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J787" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K787">
+        <v>1</v>
+      </c>
+      <c r="L787" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M787" t="str">
+        <v>2026-07-06 20:38:16</v>
+      </c>
+      <c r="N787" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O787" s="1">
+        <v>0</v>
+      </c>
+      <c r="P787" t="str">
+        <v/>
+      </c>
+      <c r="Q787" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R787" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="str">
+        <v>T260706-00020</v>
+      </c>
+      <c r="B788" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C788" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D788" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E788" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F788">
+        <v>1</v>
+      </c>
+      <c r="G788" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H788" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I788" t="str">
+        <v>2026-07-06 23:00</v>
+      </c>
+      <c r="J788" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K788">
+        <v>1</v>
+      </c>
+      <c r="L788" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M788" t="str">
+        <v>2026-07-06 20:37:59</v>
+      </c>
+      <c r="N788" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O788" s="1">
+        <v>0</v>
+      </c>
+      <c r="P788" t="str">
+        <v/>
+      </c>
+      <c r="Q788" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R788" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="str">
+        <v>T260706-00019</v>
+      </c>
+      <c r="B789" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C789" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D789" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E789" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F789">
+        <v>0</v>
+      </c>
+      <c r="G789" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H789" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I789" t="str">
+        <v>2026-07-06 22:00</v>
+      </c>
+      <c r="J789" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K789">
+        <v>1</v>
+      </c>
+      <c r="L789" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M789" t="str">
+        <v>2026-07-06 20:37:38</v>
+      </c>
+      <c r="N789" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O789" s="1">
+        <v>0</v>
+      </c>
+      <c r="P789" t="str">
+        <v/>
+      </c>
+      <c r="Q789" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R789" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="str">
+        <v>T260706-00018</v>
+      </c>
+      <c r="B790" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C790" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D790" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E790" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F790">
+        <v>1</v>
+      </c>
+      <c r="G790" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H790" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I790" t="str">
+        <v>2026-07-06 22:00</v>
+      </c>
+      <c r="J790" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K790">
+        <v>1</v>
+      </c>
+      <c r="L790" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M790" t="str">
+        <v>2026-07-06 20:37:22</v>
+      </c>
+      <c r="N790" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O790" s="1">
+        <v>0</v>
+      </c>
+      <c r="P790" t="str">
+        <v/>
+      </c>
+      <c r="Q790" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R790" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="str">
+        <v>T260706-00017</v>
+      </c>
+      <c r="B791" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C791" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D791" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E791" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F791">
+        <v>0</v>
+      </c>
+      <c r="G791" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H791" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I791" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J791" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K791">
+        <v>1</v>
+      </c>
+      <c r="L791" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M791" t="str">
+        <v>2026-07-06 20:36:54</v>
+      </c>
+      <c r="N791" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O791" s="1">
+        <v>0</v>
+      </c>
+      <c r="P791" t="str">
+        <v/>
+      </c>
+      <c r="Q791" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R791" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="str">
+        <v>T260706-00016</v>
+      </c>
+      <c r="B792" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C792" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D792" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E792" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F792">
+        <v>1</v>
+      </c>
+      <c r="G792" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H792" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I792" t="str">
+        <v>2026-07-06 22:00</v>
+      </c>
+      <c r="J792" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K792">
+        <v>1</v>
+      </c>
+      <c r="L792" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M792" t="str">
+        <v>2026-07-06 20:35:29</v>
+      </c>
+      <c r="N792" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O792" s="1">
+        <v>0</v>
+      </c>
+      <c r="P792" t="str">
+        <v/>
+      </c>
+      <c r="Q792" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R792" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="str">
+        <v>T260706-00015</v>
+      </c>
+      <c r="B793" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C793" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D793" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E793" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F793">
+        <v>0</v>
+      </c>
+      <c r="G793" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H793" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I793" t="str">
+        <v>2026-07-06 23:00</v>
+      </c>
+      <c r="J793" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K793">
+        <v>1</v>
+      </c>
+      <c r="L793" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M793" t="str">
+        <v>2026-07-06 20:35:06</v>
+      </c>
+      <c r="N793" s="1">
+        <v>480000</v>
+      </c>
+      <c r="O793" s="1">
+        <v>0</v>
+      </c>
+      <c r="P793" t="str">
+        <v/>
+      </c>
+      <c r="Q793" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R793" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="str">
+        <v>T260706-00014</v>
+      </c>
+      <c r="B794" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C794" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D794" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E794" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F794">
+        <v>0</v>
+      </c>
+      <c r="G794" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H794" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I794" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J794" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K794">
+        <v>1</v>
+      </c>
+      <c r="L794" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M794" t="str">
+        <v>2026-07-06 20:34:46</v>
+      </c>
+      <c r="N794" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O794" s="1">
+        <v>0</v>
+      </c>
+      <c r="P794" t="str">
+        <v/>
+      </c>
+      <c r="Q794" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R794" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="str">
+        <v>T260706-00013</v>
+      </c>
+      <c r="B795" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C795" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D795" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E795" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F795">
+        <v>0</v>
+      </c>
+      <c r="G795" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H795" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I795" t="str">
+        <v>2026-07-07 06:00</v>
+      </c>
+      <c r="J795" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K795">
+        <v>1</v>
+      </c>
+      <c r="L795" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M795" t="str">
+        <v>2026-07-06 20:34:27</v>
+      </c>
+      <c r="N795" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O795" s="1">
+        <v>0</v>
+      </c>
+      <c r="P795" t="str">
+        <v/>
+      </c>
+      <c r="Q795" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R795" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="str">
+        <v>T260706-00012</v>
+      </c>
+      <c r="B796" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C796" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D796" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E796" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F796">
+        <v>0</v>
+      </c>
+      <c r="G796" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H796" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I796" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J796" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K796">
+        <v>1</v>
+      </c>
+      <c r="L796" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M796" t="str">
+        <v>2026-07-06 20:33:52</v>
+      </c>
+      <c r="N796" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O796" s="1">
+        <v>0</v>
+      </c>
+      <c r="P796" t="str">
+        <v/>
+      </c>
+      <c r="Q796" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R796" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="str">
+        <v>T260706-00011</v>
+      </c>
+      <c r="B797" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C797" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D797" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E797" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F797">
+        <v>0</v>
+      </c>
+      <c r="G797" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H797" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I797" t="str">
+        <v>2026-07-06 23:00</v>
+      </c>
+      <c r="J797" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K797">
+        <v>1</v>
+      </c>
+      <c r="L797" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M797" t="str">
+        <v>2026-07-06 20:33:32</v>
+      </c>
+      <c r="N797" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O797" s="1">
+        <v>0</v>
+      </c>
+      <c r="P797" t="str">
+        <v/>
+      </c>
+      <c r="Q797" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R797" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="str">
+        <v>T260706-00010</v>
+      </c>
+      <c r="B798" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C798" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D798" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E798" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F798">
+        <v>0</v>
+      </c>
+      <c r="G798" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H798" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I798" t="str">
+        <v>2026-07-06 21:00</v>
+      </c>
+      <c r="J798" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K798">
+        <v>1</v>
+      </c>
+      <c r="L798" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M798" t="str">
+        <v>2026-07-06 20:33:02</v>
+      </c>
+      <c r="N798" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O798" s="1">
+        <v>0</v>
+      </c>
+      <c r="P798" t="str">
+        <v/>
+      </c>
+      <c r="Q798" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R798" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="str">
+        <v>T260706-00009</v>
+      </c>
+      <c r="B799" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C799" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D799" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E799" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F799">
+        <v>1</v>
+      </c>
+      <c r="G799" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H799" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="I799" t="str">
+        <v>2026-07-06 23:00</v>
+      </c>
+      <c r="J799" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K799">
+        <v>1</v>
+      </c>
+      <c r="L799" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M799" t="str">
+        <v>2026-07-06 20:32:45</v>
+      </c>
+      <c r="N799" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O799" s="1">
+        <v>0</v>
+      </c>
+      <c r="P799" t="str">
+        <v/>
+      </c>
+      <c r="Q799" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R799" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="str">
+        <v>T260706-00008</v>
+      </c>
+      <c r="B800" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C800" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D800" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E800" t="str">
+        <v>2026-07-06 19:00</v>
+      </c>
+      <c r="F800">
+        <v>1</v>
+      </c>
+      <c r="G800" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="H800" t="str">
+        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="I800" t="str">
+        <v>2026-07-06 23:00</v>
+      </c>
+      <c r="J800" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K800">
+        <v>1</v>
+      </c>
+      <c r="L800" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M800" t="str">
+        <v>2026-07-06 20:32:23</v>
+      </c>
+      <c r="N800" s="1">
+        <v>330000</v>
+      </c>
+      <c r="O800" s="1">
+        <v>0</v>
+      </c>
+      <c r="P800" t="str">
+        <v/>
+      </c>
+      <c r="Q800" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R800" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="str">
+        <v>T260706-00007</v>
+      </c>
+      <c r="B801" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C801" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D801" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E801" t="str">
+        <v>2026-07-06 17:30</v>
+      </c>
+      <c r="F801">
+        <v>0</v>
+      </c>
+      <c r="G801" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H801" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I801" t="str">
+        <v>2026-07-06 18:30</v>
+      </c>
+      <c r="J801" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K801">
+        <v>1</v>
+      </c>
+      <c r="L801" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M801" t="str">
+        <v>2026-07-06 20:29:06</v>
+      </c>
+      <c r="N801" s="1">
+        <v>130000</v>
+      </c>
+      <c r="O801" s="1">
+        <v>0</v>
+      </c>
+      <c r="P801" t="str">
+        <v/>
+      </c>
+      <c r="Q801" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R801" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="str">
+        <v>T260706-00006</v>
+      </c>
+      <c r="B802" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C802" t="str">
+        <v>라꾸스토리</v>
+      </c>
+      <c r="D802" t="str">
+        <v>충북 옥천군 군서면 동평리 130 라꾸스토리</v>
+      </c>
+      <c r="E802" t="str">
+        <v>2026-07-06 13:30</v>
+      </c>
+      <c r="F802">
+        <v>0</v>
+      </c>
+      <c r="G802" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H802" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I802" t="str">
+        <v>2026-07-06 15:30</v>
+      </c>
+      <c r="J802" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K802">
+        <v>1</v>
+      </c>
+      <c r="L802" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M802" t="str">
+        <v>2026-07-06 20:28:33</v>
+      </c>
+      <c r="N802" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O802" s="1">
+        <v>0</v>
+      </c>
+      <c r="P802" t="str">
+        <v>거래처비용청구</v>
+      </c>
+      <c r="Q802" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R802" t="str">
+        <v>라꾸스토리</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="str">
+        <v>T260706-00005</v>
+      </c>
+      <c r="B803" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C803" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="D803" t="str">
+        <v>강원특별자치도 강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="E803" t="str">
+        <v>2026-07-06 08:00</v>
+      </c>
+      <c r="F803">
+        <v>0</v>
+      </c>
+      <c r="G803" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="H803" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="I803" t="str">
+        <v>2026-07-06 11:30</v>
+      </c>
+      <c r="J803" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K803">
+        <v>1</v>
+      </c>
+      <c r="L803" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M803" t="str">
+        <v>2026-07-06 20:27:47</v>
+      </c>
+      <c r="N803" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O803" s="1">
+        <v>0</v>
+      </c>
+      <c r="P803" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="Q803" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R803" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="str">
+        <v>T260706-00004</v>
+      </c>
+      <c r="B804" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C804" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D804" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E804" t="str">
+        <v>2026-07-06 13:30</v>
+      </c>
+      <c r="F804">
+        <v>0</v>
+      </c>
+      <c r="G804" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H804" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I804" t="str">
+        <v>2026-07-06 15:30</v>
+      </c>
+      <c r="J804" t="str">
+        <v>1.5톤 윙바디</v>
+      </c>
+      <c r="K804">
+        <v>1</v>
+      </c>
+      <c r="L804" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M804" t="str">
+        <v>2026-07-06 20:26:56</v>
+      </c>
+      <c r="N804" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O804" s="1">
+        <v>0</v>
+      </c>
+      <c r="P804" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q804" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R804" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="str">
+        <v>T260706-00003</v>
+      </c>
+      <c r="B805" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C805" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D805" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E805" t="str">
+        <v>2026-07-06 10:00</v>
+      </c>
+      <c r="F805">
+        <v>0</v>
+      </c>
+      <c r="G805" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H805" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I805" t="str">
+        <v>2026-07-06 13:30</v>
+      </c>
+      <c r="J805" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K805">
+        <v>1</v>
+      </c>
+      <c r="L805" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M805" t="str">
+        <v>2026-07-06 20:25:59</v>
+      </c>
+      <c r="N805" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O805" s="1">
+        <v>0</v>
+      </c>
+      <c r="P805" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q805" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R805" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="str">
+        <v>T260706-00002</v>
+      </c>
+      <c r="B806" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C806" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D806" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E806" t="str">
+        <v>2026-07-06 16:30</v>
+      </c>
+      <c r="F806">
+        <v>0</v>
+      </c>
+      <c r="G806" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H806" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I806" t="str">
+        <v>2026-07-06 18:00</v>
+      </c>
+      <c r="J806" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K806">
+        <v>1</v>
+      </c>
+      <c r="L806" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M806" t="str">
+        <v>2026-07-06 15:56:39</v>
+      </c>
+      <c r="N806" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O806" s="1">
+        <v>0</v>
+      </c>
+      <c r="P806" t="str">
+        <v>20260706/경동택배_남이가마258 영업소_파렛트 출하</v>
+      </c>
+      <c r="Q806" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R806" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="str">
+        <v>T260706-00001</v>
+      </c>
+      <c r="B807" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C807" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D807" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E807" t="str">
+        <v>2026-07-06 09:00</v>
+      </c>
+      <c r="F807">
+        <v>0</v>
+      </c>
+      <c r="G807" t="str">
+        <v>세상담기(14대 서울 벌크 출하)</v>
+      </c>
+      <c r="H807" t="str">
+        <v>서울 서대문구 이화여대길 50-8 2층 문 앞</v>
+      </c>
+      <c r="I807" t="str">
+        <v>2026-07-06 11:50</v>
+      </c>
+      <c r="J807" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K807">
+        <v>1</v>
+      </c>
+      <c r="L807" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M807" t="str">
+        <v>2026-07-06 10:32:22</v>
+      </c>
+      <c r="N807" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O807" s="1">
+        <v>0</v>
+      </c>
+      <c r="P807" t="str">
+        <v>20260706/세상담기_서울 벌크_출하(14대 2층 운반 건)</v>
+      </c>
+      <c r="Q807" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R807" t="str">
+        <v>세상담기</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="str">
+        <v>T260703-00034</v>
+      </c>
+      <c r="B808" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C808" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D808" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E808" t="str">
+        <v>2026-07-03 19:01</v>
+      </c>
+      <c r="F808">
+        <v>0</v>
+      </c>
+      <c r="G808" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H808" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I808" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J808" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K808">
+        <v>1</v>
+      </c>
+      <c r="L808" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M808" t="str">
+        <v>2026-07-03 20:43:25</v>
+      </c>
+      <c r="N808" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O808" s="1">
+        <v>0</v>
+      </c>
+      <c r="P808" t="str">
+        <v/>
+      </c>
+      <c r="Q808" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R808" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="str">
+        <v>T260703-00033</v>
+      </c>
+      <c r="B809" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C809" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D809" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E809" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F809">
+        <v>1</v>
+      </c>
+      <c r="G809" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H809" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I809" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J809" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K809">
+        <v>1</v>
+      </c>
+      <c r="L809" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M809" t="str">
+        <v>2026-07-03 20:42:58</v>
+      </c>
+      <c r="N809" s="1">
+        <v>170000</v>
+      </c>
+      <c r="O809" s="1">
+        <v>0</v>
+      </c>
+      <c r="P809" t="str">
+        <v/>
+      </c>
+      <c r="Q809" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R809" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="str">
+        <v>T260703-00032</v>
+      </c>
+      <c r="B810" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C810" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D810" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E810" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F810">
+        <v>1</v>
+      </c>
+      <c r="G810" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H810" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I810" t="str">
+        <v>2026-07-04 08:00</v>
+      </c>
+      <c r="J810" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K810">
+        <v>1</v>
+      </c>
+      <c r="L810" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M810" t="str">
+        <v>2026-07-03 20:42:34</v>
+      </c>
+      <c r="N810" s="1">
+        <v>170000</v>
+      </c>
+      <c r="O810" s="1">
+        <v>0</v>
+      </c>
+      <c r="P810" t="str">
+        <v/>
+      </c>
+      <c r="Q810" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R810" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="str">
+        <v>T260703-00031</v>
+      </c>
+      <c r="B811" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C811" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D811" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E811" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F811">
+        <v>0</v>
+      </c>
+      <c r="G811" t="str">
+        <v>시흥ACP</v>
+      </c>
+      <c r="H811" t="str">
+        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
+      </c>
+      <c r="I811" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J811" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K811">
+        <v>1</v>
+      </c>
+      <c r="L811" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M811" t="str">
+        <v>2026-07-03 20:41:59</v>
+      </c>
+      <c r="N811" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O811" s="1">
+        <v>0</v>
+      </c>
+      <c r="P811" t="str">
+        <v/>
+      </c>
+      <c r="Q811" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R811" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="str">
+        <v>T260703-00030</v>
+      </c>
+      <c r="B812" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C812" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D812" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E812" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F812">
+        <v>3</v>
+      </c>
+      <c r="G812" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H812" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I812" t="str">
+        <v>2026-07-04 08:00</v>
+      </c>
+      <c r="J812" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K812">
+        <v>1</v>
+      </c>
+      <c r="L812" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M812" t="str">
+        <v>2026-07-03 20:41:34</v>
+      </c>
+      <c r="N812" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O812" s="1">
+        <v>0</v>
+      </c>
+      <c r="P812" t="str">
+        <v/>
+      </c>
+      <c r="Q812" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R812" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="str">
+        <v>T260703-00029</v>
+      </c>
+      <c r="B813" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C813" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D813" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E813" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F813">
+        <v>0</v>
+      </c>
+      <c r="G813" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H813" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I813" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J813" t="str">
+        <v>1톤 기타차량</v>
+      </c>
+      <c r="K813">
+        <v>1</v>
+      </c>
+      <c r="L813" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M813" t="str">
+        <v>2026-07-03 20:40:56</v>
+      </c>
+      <c r="N813" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O813" s="1">
+        <v>0</v>
+      </c>
+      <c r="P813" t="str">
+        <v/>
+      </c>
+      <c r="Q813" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R813" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="str">
+        <v>T260703-00028</v>
+      </c>
+      <c r="B814" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C814" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D814" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E814" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F814">
+        <v>0</v>
+      </c>
+      <c r="G814" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H814" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I814" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J814" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K814">
+        <v>1</v>
+      </c>
+      <c r="L814" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M814" t="str">
+        <v>2026-07-03 20:40:32</v>
+      </c>
+      <c r="N814" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O814" s="1">
+        <v>0</v>
+      </c>
+      <c r="P814" t="str">
+        <v/>
+      </c>
+      <c r="Q814" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R814" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="str">
+        <v>T260703-00027</v>
+      </c>
+      <c r="B815" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C815" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D815" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E815" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F815">
+        <v>3</v>
+      </c>
+      <c r="G815" t="str">
+        <v>인제ACP</v>
+      </c>
+      <c r="H815" t="str">
+        <v>강원특별자치도 속초시 만천6길 13 인제ACP</v>
+      </c>
+      <c r="I815" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J815" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K815">
+        <v>1</v>
+      </c>
+      <c r="L815" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M815" t="str">
+        <v>2026-07-03 20:40:07</v>
+      </c>
+      <c r="N815" s="1">
+        <v>390000</v>
+      </c>
+      <c r="O815" s="1">
+        <v>0</v>
+      </c>
+      <c r="P815" t="str">
+        <v/>
+      </c>
+      <c r="Q815" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R815" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="str">
+        <v>T260703-00026</v>
+      </c>
+      <c r="B816" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C816" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D816" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E816" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F816">
+        <v>0</v>
+      </c>
+      <c r="G816" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H816" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I816" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J816" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K816">
+        <v>1</v>
+      </c>
+      <c r="L816" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M816" t="str">
+        <v>2026-07-03 20:39:21</v>
+      </c>
+      <c r="N816" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O816" s="1">
+        <v>0</v>
+      </c>
+      <c r="P816" t="str">
+        <v/>
+      </c>
+      <c r="Q816" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R816" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="str">
+        <v>T260703-00025</v>
+      </c>
+      <c r="B817" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C817" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D817" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E817" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F817">
+        <v>1</v>
+      </c>
+      <c r="G817" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H817" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I817" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J817" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K817">
+        <v>1</v>
+      </c>
+      <c r="L817" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M817" t="str">
+        <v>2026-07-03 20:39:06</v>
+      </c>
+      <c r="N817" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O817" s="1">
+        <v>0</v>
+      </c>
+      <c r="P817" t="str">
+        <v/>
+      </c>
+      <c r="Q817" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R817" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="str">
+        <v>T260703-00024</v>
+      </c>
+      <c r="B818" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C818" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D818" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E818" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F818">
+        <v>1</v>
+      </c>
+      <c r="G818" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H818" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I818" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J818" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K818">
+        <v>1</v>
+      </c>
+      <c r="L818" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M818" t="str">
+        <v>2026-07-03 20:38:48</v>
+      </c>
+      <c r="N818" s="1">
+        <v>530000</v>
+      </c>
+      <c r="O818" s="1">
+        <v>0</v>
+      </c>
+      <c r="P818" t="str">
+        <v/>
+      </c>
+      <c r="Q818" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R818" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="str">
+        <v>T260703-00023</v>
+      </c>
+      <c r="B819" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C819" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D819" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E819" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F819">
+        <v>0</v>
+      </c>
+      <c r="G819" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H819" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I819" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J819" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K819">
+        <v>1</v>
+      </c>
+      <c r="L819" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M819" t="str">
+        <v>2026-07-03 20:38:28</v>
+      </c>
+      <c r="N819" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O819" s="1">
+        <v>0</v>
+      </c>
+      <c r="P819" t="str">
+        <v/>
+      </c>
+      <c r="Q819" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R819" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="str">
+        <v>T260703-00022</v>
+      </c>
+      <c r="B820" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C820" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D820" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E820" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F820">
+        <v>0</v>
+      </c>
+      <c r="G820" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H820" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I820" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J820" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K820">
+        <v>1</v>
+      </c>
+      <c r="L820" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M820" t="str">
+        <v>2026-07-03 20:38:14</v>
+      </c>
+      <c r="N820" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O820" s="1">
+        <v>0</v>
+      </c>
+      <c r="P820" t="str">
+        <v/>
+      </c>
+      <c r="Q820" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R820" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="str">
+        <v>T260703-00021</v>
+      </c>
+      <c r="B821" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C821" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D821" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E821" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F821">
+        <v>1</v>
+      </c>
+      <c r="G821" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H821" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I821" t="str">
+        <v>2026-07-03 22:00</v>
+      </c>
+      <c r="J821" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K821">
+        <v>1</v>
+      </c>
+      <c r="L821" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M821" t="str">
+        <v>2026-07-03 20:37:59</v>
+      </c>
+      <c r="N821" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O821" s="1">
+        <v>0</v>
+      </c>
+      <c r="P821" t="str">
+        <v/>
+      </c>
+      <c r="Q821" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R821" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="str">
+        <v>T260703-00020</v>
+      </c>
+      <c r="B822" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C822" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D822" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E822" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F822">
+        <v>0</v>
+      </c>
+      <c r="G822" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H822" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I822" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J822" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K822">
+        <v>1</v>
+      </c>
+      <c r="L822" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M822" t="str">
+        <v>2026-07-03 20:37:40</v>
+      </c>
+      <c r="N822" s="1">
+        <v>490000</v>
+      </c>
+      <c r="O822" s="1">
+        <v>0</v>
+      </c>
+      <c r="P822" t="str">
+        <v/>
+      </c>
+      <c r="Q822" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R822" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="str">
+        <v>T260703-00019</v>
+      </c>
+      <c r="B823" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C823" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D823" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E823" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F823">
+        <v>0</v>
+      </c>
+      <c r="G823" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H823" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I823" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J823" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K823">
+        <v>1</v>
+      </c>
+      <c r="L823" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M823" t="str">
+        <v>2026-07-03 20:37:26</v>
+      </c>
+      <c r="N823" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O823" s="1">
+        <v>0</v>
+      </c>
+      <c r="P823" t="str">
+        <v/>
+      </c>
+      <c r="Q823" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R823" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="str">
+        <v>T260703-00018</v>
+      </c>
+      <c r="B824" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C824" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D824" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E824" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F824">
+        <v>0</v>
+      </c>
+      <c r="G824" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H824" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I824" t="str">
+        <v>2026-07-03 20:00</v>
+      </c>
+      <c r="J824" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K824">
+        <v>1</v>
+      </c>
+      <c r="L824" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M824" t="str">
+        <v>2026-07-03 20:37:11</v>
+      </c>
+      <c r="N824" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O824" s="1">
+        <v>0</v>
+      </c>
+      <c r="P824" t="str">
+        <v/>
+      </c>
+      <c r="Q824" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R824" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="str">
+        <v>T260703-00017</v>
+      </c>
+      <c r="B825" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C825" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D825" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E825" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F825">
+        <v>0</v>
+      </c>
+      <c r="G825" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H825" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I825" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J825" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K825">
+        <v>1</v>
+      </c>
+      <c r="L825" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M825" t="str">
+        <v>2026-07-03 20:36:55</v>
+      </c>
+      <c r="N825" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O825" s="1">
+        <v>0</v>
+      </c>
+      <c r="P825" t="str">
+        <v/>
+      </c>
+      <c r="Q825" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R825" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="str">
+        <v>T260703-00016</v>
+      </c>
+      <c r="B826" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C826" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D826" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E826" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F826">
+        <v>0</v>
+      </c>
+      <c r="G826" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H826" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I826" t="str">
+        <v>2026-07-03 21:00</v>
+      </c>
+      <c r="J826" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K826">
+        <v>1</v>
+      </c>
+      <c r="L826" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M826" t="str">
+        <v>2026-07-03 20:36:37</v>
+      </c>
+      <c r="N826" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O826" s="1">
+        <v>0</v>
+      </c>
+      <c r="P826" t="str">
+        <v/>
+      </c>
+      <c r="Q826" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R826" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="str">
+        <v>T260703-00015</v>
+      </c>
+      <c r="B827" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C827" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D827" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E827" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F827">
+        <v>0</v>
+      </c>
+      <c r="G827" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H827" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I827" t="str">
+        <v>2026-07-04 07:00</v>
+      </c>
+      <c r="J827" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K827">
+        <v>1</v>
+      </c>
+      <c r="L827" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M827" t="str">
+        <v>2026-07-03 20:36:15</v>
+      </c>
+      <c r="N827" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O827" s="1">
+        <v>0</v>
+      </c>
+      <c r="P827" t="str">
+        <v/>
+      </c>
+      <c r="Q827" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R827" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="str">
+        <v>T260703-00014</v>
+      </c>
+      <c r="B828" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C828" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D828" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E828" t="str">
+        <v>2026-07-03 19:00</v>
+      </c>
+      <c r="F828">
+        <v>1</v>
+      </c>
+      <c r="G828" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H828" t="str">
+        <v>경산시 해오름길114-2 경산FDC</v>
+      </c>
+      <c r="I828" t="str">
+        <v>2026-07-03 23:00</v>
+      </c>
+      <c r="J828" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K828">
+        <v>1</v>
+      </c>
+      <c r="L828" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M828" t="str">
+        <v>2026-07-03 20:35:55</v>
+      </c>
+      <c r="N828" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O828" s="1">
+        <v>0</v>
+      </c>
+      <c r="P828" t="str">
+        <v/>
+      </c>
+      <c r="Q828" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R828" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="str">
+        <v>T260703-00013</v>
+      </c>
+      <c r="B829" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C829" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D829" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E829" t="str">
+        <v>2026-07-03 17:30</v>
+      </c>
+      <c r="F829">
+        <v>0</v>
+      </c>
+      <c r="G829" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H829" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I829" t="str">
+        <v>2026-07-03 18:30</v>
+      </c>
+      <c r="J829" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K829">
+        <v>1</v>
+      </c>
+      <c r="L829" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M829" t="str">
+        <v>2026-07-03 20:31:55</v>
+      </c>
+      <c r="N829" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O829" s="1">
+        <v>0</v>
+      </c>
+      <c r="P829" t="str">
+        <v/>
+      </c>
+      <c r="Q829" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R829" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="str">
+        <v>T260703-00012</v>
+      </c>
+      <c r="B830" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C830" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="D830" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="E830" t="str">
+        <v>2026-07-03 08:30</v>
+      </c>
+      <c r="F830">
+        <v>0</v>
+      </c>
+      <c r="G830" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="H830" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="I830" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="J830" t="str">
+        <v>3.5톤 카고</v>
+      </c>
+      <c r="K830">
+        <v>1</v>
+      </c>
+      <c r="L830" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M830" t="str">
+        <v>2026-07-03 20:31:21</v>
+      </c>
+      <c r="N830" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O830" s="1">
+        <v>0</v>
+      </c>
+      <c r="P830" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="Q830" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R830" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="str">
+        <v>T260703-00011</v>
+      </c>
+      <c r="B831" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C831" t="str">
+        <v>샤오미</v>
+      </c>
+      <c r="D831" t="str">
+        <v>경기 이천시 대월면 부필리 309 샤오미</v>
+      </c>
+      <c r="E831" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="F831">
+        <v>0</v>
+      </c>
+      <c r="G831" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H831" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I831" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="J831" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K831">
+        <v>1</v>
+      </c>
+      <c r="L831" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M831" t="str">
+        <v>2026-07-03 20:30:39</v>
+      </c>
+      <c r="N831" s="1">
+        <v>80000</v>
+      </c>
+      <c r="O831" s="1">
+        <v>0</v>
+      </c>
+      <c r="P831" t="str">
+        <v>거래처비용청구(1대)</v>
+      </c>
+      <c r="Q831" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R831" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="str">
+        <v>T260703-00010</v>
+      </c>
+      <c r="B832" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C832" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D832" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E832" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="F832">
+        <v>0</v>
+      </c>
+      <c r="G832" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H832" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I832" t="str">
+        <v>2026-07-03 15:30</v>
+      </c>
+      <c r="J832" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K832">
+        <v>1</v>
+      </c>
+      <c r="L832" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M832" t="str">
+        <v>2026-07-03 20:29:47</v>
+      </c>
+      <c r="N832" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O832" s="1">
+        <v>0</v>
+      </c>
+      <c r="P832" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q832" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R832" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="str">
+        <v>T260703-00009</v>
+      </c>
+      <c r="B833" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C833" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D833" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E833" t="str">
+        <v>2026-07-03 10:00</v>
+      </c>
+      <c r="F833">
+        <v>0</v>
+      </c>
+      <c r="G833" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H833" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I833" t="str">
+        <v>2026-07-03 13:30</v>
+      </c>
+      <c r="J833" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K833">
+        <v>1</v>
+      </c>
+      <c r="L833" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M833" t="str">
+        <v>2026-07-03 20:29:05</v>
+      </c>
+      <c r="N833" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O833" s="1">
+        <v>0</v>
+      </c>
+      <c r="P833" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q833" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R833" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="str">
+        <v>T260703-00008</v>
+      </c>
+      <c r="B834" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C834" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D834" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E834" t="str">
+        <v>2026-07-03 16:30</v>
+      </c>
+      <c r="F834">
+        <v>0</v>
+      </c>
+      <c r="G834" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H834" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I834" t="str">
+        <v>2026-07-03 18:00</v>
+      </c>
+      <c r="J834" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K834">
+        <v>1</v>
+      </c>
+      <c r="L834" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M834" t="str">
+        <v>2026-07-03 18:39:34</v>
+      </c>
+      <c r="N834" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O834" s="1">
+        <v>0</v>
+      </c>
+      <c r="P834" t="str">
+        <v>20260703/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q834" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R834" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="str">
+        <v>T260703-00007</v>
+      </c>
+      <c r="B835" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C835" t="str">
+        <v>청주ARC(공파렛트 이동)</v>
+      </c>
+      <c r="D835" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(공파렛트 이동)</v>
+      </c>
+      <c r="E835" t="str">
+        <v>2026-07-03 11:40</v>
+      </c>
+      <c r="F835">
+        <v>0</v>
+      </c>
+      <c r="G835" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H835" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="I835" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="J835" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K835">
+        <v>1</v>
+      </c>
+      <c r="L835" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M835" t="str">
+        <v>2026-07-03 11:28:01</v>
+      </c>
+      <c r="N835" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O835" s="1">
+        <v>0</v>
+      </c>
+      <c r="P835" t="str">
+        <v>20260703청주-&gt; 안성FC/공파렛트이동</v>
+      </c>
+      <c r="Q835" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R835" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="str">
+        <v>T260703-00006</v>
+      </c>
+      <c r="B836" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C836" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D836" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E836" t="str">
+        <v>2026-07-03 11:55</v>
+      </c>
+      <c r="F836">
+        <v>0</v>
+      </c>
+      <c r="G836" t="str">
+        <v>하이얼(서울 벌크 출하)</v>
+      </c>
+      <c r="H836" t="str">
+        <v>서울 강남구 선릉로92길 38 도파민</v>
+      </c>
+      <c r="I836" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="J836" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K836">
+        <v>1</v>
+      </c>
+      <c r="L836" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M836" t="str">
+        <v>2026-07-03 11:26:22</v>
+      </c>
+      <c r="N836" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O836" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P836" t="str">
+        <v>20260703/하이얼_서울_벌크_출하</v>
+      </c>
+      <c r="Q836" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R836" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="str">
+        <v>T260703-00005</v>
+      </c>
+      <c r="B837" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C837" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D837" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E837" t="str">
+        <v>2026-07-03 11:00</v>
+      </c>
+      <c r="F837">
+        <v>0</v>
+      </c>
+      <c r="G837" t="str">
+        <v>파주 하이마트 물류</v>
+      </c>
+      <c r="H837" t="str">
+        <v>경기 파주시 탄현면 월롱산로 296 파주 하이마트 물류</v>
+      </c>
+      <c r="I837" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J837" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K837">
+        <v>1</v>
+      </c>
+      <c r="L837" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M837" t="str">
+        <v>2026-07-03 11:22:28</v>
+      </c>
+      <c r="N837" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O837" s="1">
+        <v>0</v>
+      </c>
+      <c r="P837" t="str">
+        <v>일코전자 파주 하이마트 물류</v>
+      </c>
+      <c r="Q837" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R837" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="str">
+        <v>T260703-00004</v>
+      </c>
+      <c r="B838" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C838" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D838" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지  안성FC</v>
+      </c>
+      <c r="E838" t="str">
+        <v>2026-07-03 09:30</v>
+      </c>
+      <c r="F838">
+        <v>0</v>
+      </c>
+      <c r="G838" t="str">
+        <v>TCL다코넷</v>
+      </c>
+      <c r="H838" t="str">
+        <v>경기 평택시 포승읍 희곡리 847 평택 켄달스퀘어 3층, 다코넷 37번 도크</v>
+      </c>
+      <c r="I838" t="str">
+        <v>2026-07-03 11:30</v>
+      </c>
+      <c r="J838" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K838">
+        <v>1</v>
+      </c>
+      <c r="L838" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M838" t="str">
+        <v>2026-07-03 11:21:17</v>
+      </c>
+      <c r="N838" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O838" s="1">
+        <v>0</v>
+      </c>
+      <c r="P838" t="str">
+        <v>TCL 다코넷</v>
+      </c>
+      <c r="Q838" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R838" t="str">
+        <v>TCL</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="str">
+        <v>T260703-00003</v>
+      </c>
+      <c r="B839" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C839" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D839" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E839" t="str">
+        <v>2026-07-03 13:00</v>
+      </c>
+      <c r="F839">
+        <v>0</v>
+      </c>
+      <c r="G839" t="str">
+        <v>이천 하이마트 물류</v>
+      </c>
+      <c r="H839" t="str">
+        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 물류</v>
+      </c>
+      <c r="I839" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J839" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K839">
+        <v>1</v>
+      </c>
+      <c r="L839" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M839" t="str">
+        <v>2026-07-03 11:19:40</v>
+      </c>
+      <c r="N839" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O839" s="1">
+        <v>0</v>
+      </c>
+      <c r="P839" t="str">
+        <v>일코전자 이천 하이마트 물류</v>
+      </c>
+      <c r="Q839" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R839" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="str">
+        <v>T260703-00002</v>
+      </c>
+      <c r="B840" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C840" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D840" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E840" t="str">
+        <v>2026-07-03 10:00</v>
+      </c>
+      <c r="F840">
+        <v>0</v>
+      </c>
+      <c r="G840" t="str">
+        <v>화성 하이마트 물류</v>
+      </c>
+      <c r="H840" t="str">
+        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 물류</v>
+      </c>
+      <c r="I840" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J840" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K840">
+        <v>1</v>
+      </c>
+      <c r="L840" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M840" t="str">
+        <v>2026-07-03 11:18:03</v>
+      </c>
+      <c r="N840" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O840" s="1">
+        <v>0</v>
+      </c>
+      <c r="P840" t="str">
+        <v>일코전자 화성 하이마트 물류</v>
+      </c>
+      <c r="Q840" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R840" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="str">
+        <v>T260703-00001</v>
+      </c>
+      <c r="B841" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C841" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D841" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E841" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="F841">
+        <v>0</v>
+      </c>
+      <c r="G841" t="str">
+        <v>인천 하이마트 물류</v>
+      </c>
+      <c r="H841" t="str">
+        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
+      </c>
+      <c r="I841" t="str">
+        <v>2026-07-03 15:00</v>
+      </c>
+      <c r="J841" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K841">
+        <v>1</v>
+      </c>
+      <c r="L841" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M841" t="str">
+        <v>2026-07-03 11:16:52</v>
+      </c>
+      <c r="N841" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O841" s="1">
+        <v>0</v>
+      </c>
+      <c r="P841" t="str">
+        <v>일코전자 인천 하이마트 물류</v>
+      </c>
+      <c r="Q841" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R841" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="str">
+        <v>T260702-00027</v>
+      </c>
+      <c r="B842" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C842" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D842" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E842" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F842">
+        <v>1</v>
+      </c>
+      <c r="G842" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H842" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I842" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J842" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K842">
+        <v>1</v>
+      </c>
+      <c r="L842" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M842" t="str">
+        <v>2026-07-02 20:54:21</v>
+      </c>
+      <c r="N842" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O842" s="1">
+        <v>0</v>
+      </c>
+      <c r="P842" t="str">
+        <v/>
+      </c>
+      <c r="Q842" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R842" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="str">
+        <v>T260702-00026</v>
+      </c>
+      <c r="B843" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C843" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D843" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E843" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F843">
+        <v>1</v>
+      </c>
+      <c r="G843" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H843" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I843" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J843" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K843">
+        <v>1</v>
+      </c>
+      <c r="L843" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M843" t="str">
+        <v>2026-07-02 20:53:56</v>
+      </c>
+      <c r="N843" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O843" s="1">
+        <v>0</v>
+      </c>
+      <c r="P843" t="str">
+        <v/>
+      </c>
+      <c r="Q843" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R843" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="str">
+        <v>T260702-00025</v>
+      </c>
+      <c r="B844" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C844" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D844" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E844" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F844">
+        <v>3</v>
+      </c>
+      <c r="G844" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H844" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I844" t="str">
+        <v>2026-07-03 08:00</v>
+      </c>
+      <c r="J844" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K844">
+        <v>1</v>
+      </c>
+      <c r="L844" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M844" t="str">
+        <v>2026-07-02 20:53:28</v>
+      </c>
+      <c r="N844" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O844" s="1">
+        <v>0</v>
+      </c>
+      <c r="P844" t="str">
+        <v/>
+      </c>
+      <c r="Q844" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R844" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="str">
+        <v>T260702-00024</v>
+      </c>
+      <c r="B845" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C845" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D845" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E845" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F845">
+        <v>0</v>
+      </c>
+      <c r="G845" t="str">
+        <v>용인ACP</v>
+      </c>
+      <c r="H845" t="str">
+        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
+      </c>
+      <c r="I845" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J845" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K845">
+        <v>1</v>
+      </c>
+      <c r="L845" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M845" t="str">
+        <v>2026-07-02 20:52:18</v>
+      </c>
+      <c r="N845" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O845" s="1">
+        <v>0</v>
+      </c>
+      <c r="P845" t="str">
+        <v/>
+      </c>
+      <c r="Q845" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R845" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="str">
+        <v>T260702-00023</v>
+      </c>
+      <c r="B846" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C846" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D846" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E846" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F846">
+        <v>1</v>
+      </c>
+      <c r="G846" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H846" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I846" t="str">
+        <v>2026-07-03 07:00</v>
+      </c>
+      <c r="J846" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K846">
+        <v>1</v>
+      </c>
+      <c r="L846" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M846" t="str">
+        <v>2026-07-02 20:51:59</v>
+      </c>
+      <c r="N846" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O846" s="1">
+        <v>0</v>
+      </c>
+      <c r="P846" t="str">
+        <v/>
+      </c>
+      <c r="Q846" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R846" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="str">
+        <v>T260702-00022</v>
+      </c>
+      <c r="B847" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C847" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D847" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E847" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F847">
+        <v>0</v>
+      </c>
+      <c r="G847" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H847" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I847" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J847" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K847">
+        <v>1</v>
+      </c>
+      <c r="L847" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M847" t="str">
+        <v>2026-07-02 20:51:32</v>
+      </c>
+      <c r="N847" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O847" s="1">
+        <v>0</v>
+      </c>
+      <c r="P847" t="str">
+        <v/>
+      </c>
+      <c r="Q847" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R847" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="str">
+        <v>T260702-00021</v>
+      </c>
+      <c r="B848" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C848" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D848" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E848" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F848">
+        <v>1</v>
+      </c>
+      <c r="G848" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H848" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I848" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J848" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K848">
+        <v>1</v>
+      </c>
+      <c r="L848" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M848" t="str">
+        <v>2026-07-02 20:51:14</v>
+      </c>
+      <c r="N848" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O848" s="1">
+        <v>0</v>
+      </c>
+      <c r="P848" t="str">
+        <v/>
+      </c>
+      <c r="Q848" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R848" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="str">
+        <v>T260702-00020</v>
+      </c>
+      <c r="B849" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C849" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D849" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E849" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F849">
+        <v>0</v>
+      </c>
+      <c r="G849" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H849" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I849" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J849" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K849">
+        <v>1</v>
+      </c>
+      <c r="L849" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M849" t="str">
+        <v>2026-07-02 20:50:54</v>
+      </c>
+      <c r="N849" s="1">
+        <v>280000</v>
+      </c>
+      <c r="O849" s="1">
+        <v>0</v>
+      </c>
+      <c r="P849" t="str">
+        <v/>
+      </c>
+      <c r="Q849" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R849" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="str">
+        <v>T260702-00019</v>
+      </c>
+      <c r="B850" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C850" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D850" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E850" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F850">
+        <v>0</v>
+      </c>
+      <c r="G850" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H850" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I850" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J850" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K850">
+        <v>1</v>
+      </c>
+      <c r="L850" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M850" t="str">
+        <v>2026-07-02 20:50:36</v>
+      </c>
+      <c r="N850" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O850" s="1">
+        <v>0</v>
+      </c>
+      <c r="P850" t="str">
+        <v/>
+      </c>
+      <c r="Q850" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R850" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="str">
+        <v>T260702-00018</v>
+      </c>
+      <c r="B851" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C851" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D851" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E851" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F851">
+        <v>1</v>
+      </c>
+      <c r="G851" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H851" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I851" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J851" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K851">
+        <v>1</v>
+      </c>
+      <c r="L851" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M851" t="str">
+        <v>2026-07-02 20:50:19</v>
+      </c>
+      <c r="N851" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O851" s="1">
+        <v>0</v>
+      </c>
+      <c r="P851" t="str">
+        <v/>
+      </c>
+      <c r="Q851" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R851" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="str">
+        <v>T260702-00017</v>
+      </c>
+      <c r="B852" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C852" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D852" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E852" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F852">
+        <v>1</v>
+      </c>
+      <c r="G852" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H852" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I852" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J852" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K852">
+        <v>1</v>
+      </c>
+      <c r="L852" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M852" t="str">
+        <v>2026-07-02 20:49:56</v>
+      </c>
+      <c r="N852" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O852" s="1">
+        <v>0</v>
+      </c>
+      <c r="P852" t="str">
+        <v/>
+      </c>
+      <c r="Q852" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R852" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="str">
+        <v>T260702-00016</v>
+      </c>
+      <c r="B853" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C853" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D853" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E853" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F853">
+        <v>0</v>
+      </c>
+      <c r="G853" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H853" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I853" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J853" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K853">
+        <v>1</v>
+      </c>
+      <c r="L853" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M853" t="str">
+        <v>2026-07-02 20:49:25</v>
+      </c>
+      <c r="N853" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O853" s="1">
+        <v>0</v>
+      </c>
+      <c r="P853" t="str">
+        <v/>
+      </c>
+      <c r="Q853" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R853" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="str">
+        <v>T260702-00015</v>
+      </c>
+      <c r="B854" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C854" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D854" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E854" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F854">
+        <v>1</v>
+      </c>
+      <c r="G854" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H854" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I854" t="str">
+        <v>2026-07-02 22:00</v>
+      </c>
+      <c r="J854" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K854">
+        <v>1</v>
+      </c>
+      <c r="L854" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M854" t="str">
+        <v>2026-07-02 20:48:50</v>
+      </c>
+      <c r="N854" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O854" s="1">
+        <v>0</v>
+      </c>
+      <c r="P854" t="str">
+        <v/>
+      </c>
+      <c r="Q854" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R854" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="str">
+        <v>T260702-00014</v>
+      </c>
+      <c r="B855" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C855" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D855" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E855" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F855">
+        <v>0</v>
+      </c>
+      <c r="G855" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H855" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I855" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J855" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K855">
+        <v>1</v>
+      </c>
+      <c r="L855" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M855" t="str">
+        <v>2026-07-02 20:48:25</v>
+      </c>
+      <c r="N855" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O855" s="1">
+        <v>0</v>
+      </c>
+      <c r="P855" t="str">
+        <v/>
+      </c>
+      <c r="Q855" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R855" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="str">
+        <v>T260702-00013</v>
+      </c>
+      <c r="B856" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C856" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D856" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E856" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F856">
+        <v>0</v>
+      </c>
+      <c r="G856" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H856" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I856" t="str">
+        <v>2026-07-02 21:00</v>
+      </c>
+      <c r="J856" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K856">
+        <v>1</v>
+      </c>
+      <c r="L856" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M856" t="str">
+        <v>2026-07-02 20:48:09</v>
+      </c>
+      <c r="N856" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O856" s="1">
+        <v>0</v>
+      </c>
+      <c r="P856" t="str">
+        <v/>
+      </c>
+      <c r="Q856" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R856" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="str">
+        <v>T260702-00012</v>
+      </c>
+      <c r="B857" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C857" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D857" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E857" t="str">
+        <v>2026-07-02 19:00</v>
+      </c>
+      <c r="F857">
+        <v>2</v>
+      </c>
+      <c r="G857" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H857" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I857" t="str">
+        <v>2026-07-02 23:00</v>
+      </c>
+      <c r="J857" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K857">
+        <v>1</v>
+      </c>
+      <c r="L857" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M857" t="str">
+        <v>2026-07-02 20:47:49</v>
+      </c>
+      <c r="N857" s="1">
+        <v>680000</v>
+      </c>
+      <c r="O857" s="1">
+        <v>0</v>
+      </c>
+      <c r="P857" t="str">
+        <v/>
+      </c>
+      <c r="Q857" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R857" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="str">
+        <v>T260702-00011</v>
+      </c>
+      <c r="B858" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C858" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D858" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E858" t="str">
+        <v>2026-07-02 17:50</v>
+      </c>
+      <c r="F858">
+        <v>0</v>
+      </c>
+      <c r="G858" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H858" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I858" t="str">
+        <v>2026-07-02 18:50</v>
+      </c>
+      <c r="J858" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K858">
+        <v>1</v>
+      </c>
+      <c r="L858" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M858" t="str">
+        <v>2026-07-02 20:44:59</v>
+      </c>
+      <c r="N858" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O858" s="1">
+        <v>0</v>
+      </c>
+      <c r="P858" t="str">
+        <v/>
+      </c>
+      <c r="Q858" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R858" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="str">
+        <v>T260702-00010</v>
+      </c>
+      <c r="B859" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C859" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D859" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E859" t="str">
+        <v>2026-07-02 13:30</v>
+      </c>
+      <c r="F859">
+        <v>0</v>
+      </c>
+      <c r="G859" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H859" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I859" t="str">
+        <v>2026-07-02 15:40</v>
+      </c>
+      <c r="J859" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K859">
+        <v>1</v>
+      </c>
+      <c r="L859" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M859" t="str">
+        <v>2026-07-02 20:44:26</v>
+      </c>
+      <c r="N859" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O859" s="1">
+        <v>0</v>
+      </c>
+      <c r="P859" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q859" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R859" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="str">
+        <v>T260702-00009</v>
+      </c>
+      <c r="B860" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C860" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D860" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E860" t="str">
+        <v>2026-07-02 10:00</v>
+      </c>
+      <c r="F860">
+        <v>0</v>
+      </c>
+      <c r="G860" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H860" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I860" t="str">
+        <v>2026-07-02 13:40</v>
+      </c>
+      <c r="J860" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K860">
+        <v>1</v>
+      </c>
+      <c r="L860" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M860" t="str">
+        <v>2026-07-02 20:43:37</v>
+      </c>
+      <c r="N860" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O860" s="1">
+        <v>0</v>
+      </c>
+      <c r="P860" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q860" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R860" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="str">
+        <v>T260702-00008</v>
+      </c>
+      <c r="B861" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C861" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D861" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E861" t="str">
+        <v>2026-07-02 17:00</v>
+      </c>
+      <c r="F861">
+        <v>0</v>
+      </c>
+      <c r="G861" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="H861" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="I861" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J861" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K861">
+        <v>1</v>
+      </c>
+      <c r="L861" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M861" t="str">
+        <v>2026-07-02 16:38:23</v>
+      </c>
+      <c r="N861" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O861" s="1">
+        <v>0</v>
+      </c>
+      <c r="P861" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="Q861" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R861" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="str">
+        <v>T260702-00007</v>
+      </c>
+      <c r="B862" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C862" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D862" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E862" t="str">
+        <v>2026-07-02 16:30</v>
+      </c>
+      <c r="F862">
+        <v>0</v>
+      </c>
+      <c r="G862" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H862" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I862" t="str">
+        <v>2026-07-02 18:00</v>
+      </c>
+      <c r="J862" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K862">
+        <v>1</v>
+      </c>
+      <c r="L862" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M862" t="str">
+        <v>2026-07-02 16:34:35</v>
+      </c>
+      <c r="N862" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O862" s="1">
+        <v>0</v>
+      </c>
+      <c r="P862" t="str">
+        <v>20260702/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q862" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R862" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="str">
+        <v>T260702-00006</v>
+      </c>
+      <c r="B863" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C863" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D863" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E863" t="str">
+        <v>2026-07-02 16:00</v>
+      </c>
+      <c r="F863">
+        <v>0</v>
+      </c>
+      <c r="G863" t="str">
+        <v>광주 하이마트 물류</v>
+      </c>
+      <c r="H863" t="str">
+        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
+      </c>
+      <c r="I863" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J863" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K863">
+        <v>1</v>
+      </c>
+      <c r="L863" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M863" t="str">
+        <v>2026-07-02 15:30:55</v>
+      </c>
+      <c r="N863" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O863" s="1">
+        <v>0</v>
+      </c>
+      <c r="P863" t="str">
+        <v>일코 광주 하이마트 물류</v>
+      </c>
+      <c r="Q863" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R863" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="str">
+        <v>T260702-00005</v>
+      </c>
+      <c r="B864" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C864" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D864" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E864" t="str">
+        <v>2026-07-02 14:30</v>
+      </c>
+      <c r="F864">
+        <v>0</v>
+      </c>
+      <c r="G864" t="str">
+        <v>마산 하이마트 물류</v>
+      </c>
+      <c r="H864" t="str">
+        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
+      </c>
+      <c r="I864" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J864" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K864">
+        <v>1</v>
+      </c>
+      <c r="L864" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M864" t="str">
+        <v>2026-07-02 13:44:41</v>
+      </c>
+      <c r="N864" s="1">
+        <v>380000</v>
+      </c>
+      <c r="O864" s="1">
+        <v>0</v>
+      </c>
+      <c r="P864" t="str">
+        <v>일코 마산 하이마트 물류</v>
+      </c>
+      <c r="Q864" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R864" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="str">
+        <v>T260702-00004</v>
+      </c>
+      <c r="B865" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C865" t="str">
+        <v>강릉 하이마트 물류</v>
+      </c>
+      <c r="D865" t="str">
+        <v>강원특별자치도 강릉시 연곡면 동해대로 4100-36 강릉 하이마트 물류</v>
+      </c>
+      <c r="E865" t="str">
+        <v>2026-07-02 13:30</v>
+      </c>
+      <c r="F865">
+        <v>0</v>
+      </c>
+      <c r="G865" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H865" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I865" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J865" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K865">
+        <v>1</v>
+      </c>
+      <c r="L865" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M865" t="str">
+        <v>2026-07-02 12:00:10</v>
+      </c>
+      <c r="N865" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O865" s="1">
+        <v>0</v>
+      </c>
+      <c r="P865" t="str">
+        <v>일코전자 강릉 하이마트 물류</v>
+      </c>
+      <c r="Q865" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R865" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="str">
+        <v>T260702-00003</v>
+      </c>
+      <c r="B866" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C866" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D866" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E866" t="str">
+        <v>2026-07-02 14:30</v>
+      </c>
+      <c r="F866">
+        <v>0</v>
+      </c>
+      <c r="G866" t="str">
+        <v>대구 하이마트 물류</v>
+      </c>
+      <c r="H866" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="I866" t="str">
+        <v>2026-07-03 09:00</v>
+      </c>
+      <c r="J866" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K866">
+        <v>1</v>
+      </c>
+      <c r="L866" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M866" t="str">
+        <v>2026-07-02 11:59:32</v>
+      </c>
+      <c r="N866" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O866" s="1">
+        <v>0</v>
+      </c>
+      <c r="P866" t="str">
+        <v>일코전자 대구 하이마트 물류</v>
+      </c>
+      <c r="Q866" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R866" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="str">
+        <v>T260702-00002</v>
+      </c>
+      <c r="B867" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C867" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D867" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E867" t="str">
+        <v>2026-07-02 09:30</v>
+      </c>
+      <c r="F867">
+        <v>1</v>
+      </c>
+      <c r="G867" t="str">
+        <v>하이얼(대구2착)</v>
+      </c>
+      <c r="H867" t="str">
+        <v>대구 남구 양지로 25 대명자이 아파트</v>
+      </c>
+      <c r="I867" t="str">
+        <v>2026-07-02 15:00</v>
+      </c>
+      <c r="J867" t="str">
+        <v>1.5톤 윙바디</v>
+      </c>
+      <c r="K867">
+        <v>1</v>
+      </c>
+      <c r="L867" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M867" t="str">
+        <v>2026-07-02 09:20:07</v>
+      </c>
+      <c r="N867" s="1">
+        <v>220000</v>
+      </c>
+      <c r="O867" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P867" t="str">
+        <v>20260702/하이얼_대구 착지 2곳_벌크_출하</v>
+      </c>
+      <c r="Q867" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R867" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="str">
+        <v>T260702-00001</v>
+      </c>
+      <c r="B868" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C868" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D868" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E868" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="F868">
+        <v>0</v>
+      </c>
+      <c r="G868" t="str">
+        <v>로지스밸리인천포트(Logisvalley)</v>
+      </c>
+      <c r="H868" t="str">
+        <v>인천 연수구 인천타워대로599번길 60 로지스밸리인천포트(Logisvalley) 1층 13번(HTC)</v>
+      </c>
+      <c r="I868" t="str">
+        <v>2026-07-02 11:00</v>
+      </c>
+      <c r="J868" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K868">
+        <v>1</v>
+      </c>
+      <c r="L868" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M868" t="str">
+        <v>2026-07-02 09:17:29</v>
+      </c>
+      <c r="N868" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O868" s="1">
+        <v>0</v>
+      </c>
+      <c r="P868" t="str">
+        <v>패스트레인 출하</v>
+      </c>
+      <c r="Q868" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R868" t="str">
+        <v>패스트레인코리아</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="str">
+        <v>T260701-00026</v>
+      </c>
+      <c r="B869" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C869" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D869" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E869" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F869">
+        <v>1</v>
+      </c>
+      <c r="G869" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H869" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I869" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J869" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K869">
+        <v>1</v>
+      </c>
+      <c r="L869" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M869" t="str">
+        <v>2026-07-01 19:47:13</v>
+      </c>
+      <c r="N869" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O869" s="1">
+        <v>0</v>
+      </c>
+      <c r="P869" t="str">
+        <v/>
+      </c>
+      <c r="Q869" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R869" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="str">
+        <v>T260701-00025</v>
+      </c>
+      <c r="B870" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C870" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D870" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E870" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F870">
+        <v>2</v>
+      </c>
+      <c r="G870" t="str">
+        <v>원주ACP</v>
+      </c>
+      <c r="H870" t="str">
+        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
+      </c>
+      <c r="I870" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J870" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K870">
+        <v>1</v>
+      </c>
+      <c r="L870" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M870" t="str">
+        <v>2026-07-01 19:46:48</v>
+      </c>
+      <c r="N870" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O870" s="1">
+        <v>0</v>
+      </c>
+      <c r="P870" t="str">
+        <v/>
+      </c>
+      <c r="Q870" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R870" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="str">
+        <v>T260701-00024</v>
+      </c>
+      <c r="B871" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C871" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D871" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E871" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F871">
+        <v>1</v>
+      </c>
+      <c r="G871" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H871" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I871" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J871" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K871">
+        <v>1</v>
+      </c>
+      <c r="L871" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M871" t="str">
+        <v>2026-07-01 19:46:12</v>
+      </c>
+      <c r="N871" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O871" s="1">
+        <v>0</v>
+      </c>
+      <c r="P871" t="str">
+        <v/>
+      </c>
+      <c r="Q871" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R871" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="str">
+        <v>T260701-00023</v>
+      </c>
+      <c r="B872" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C872" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D872" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E872" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F872">
+        <v>3</v>
+      </c>
+      <c r="G872" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H872" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I872" t="str">
+        <v>2026-07-02 07:00</v>
+      </c>
+      <c r="J872" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K872">
+        <v>1</v>
+      </c>
+      <c r="L872" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M872" t="str">
+        <v>2026-07-01 19:45:40</v>
+      </c>
+      <c r="N872" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O872" s="1">
+        <v>0</v>
+      </c>
+      <c r="P872" t="str">
+        <v/>
+      </c>
+      <c r="Q872" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R872" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="str">
+        <v>T260701-00022</v>
+      </c>
+      <c r="B873" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C873" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D873" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E873" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F873">
+        <v>0</v>
+      </c>
+      <c r="G873" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H873" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I873" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J873" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K873">
+        <v>1</v>
+      </c>
+      <c r="L873" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M873" t="str">
+        <v>2026-07-01 19:44:56</v>
+      </c>
+      <c r="N873" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O873" s="1">
+        <v>0</v>
+      </c>
+      <c r="P873" t="str">
+        <v/>
+      </c>
+      <c r="Q873" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R873" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="str">
+        <v>T260701-00021</v>
+      </c>
+      <c r="B874" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C874" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D874" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E874" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F874">
+        <v>1</v>
+      </c>
+      <c r="G874" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H874" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I874" t="str">
+        <v>2026-07-02 08:00</v>
+      </c>
+      <c r="J874" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K874">
+        <v>1</v>
+      </c>
+      <c r="L874" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M874" t="str">
+        <v>2026-07-01 19:44:37</v>
+      </c>
+      <c r="N874" s="1">
+        <v>190000</v>
+      </c>
+      <c r="O874" s="1">
+        <v>0</v>
+      </c>
+      <c r="P874" t="str">
+        <v/>
+      </c>
+      <c r="Q874" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R874" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="str">
+        <v>T260701-00020</v>
+      </c>
+      <c r="B875" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C875" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D875" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E875" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F875">
+        <v>2</v>
+      </c>
+      <c r="G875" t="str">
+        <v>속초ACP</v>
+      </c>
+      <c r="H875" t="str">
+        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
+      </c>
+      <c r="I875" t="str">
+        <v>2026-07-02 06:00</v>
+      </c>
+      <c r="J875" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K875">
+        <v>1</v>
+      </c>
+      <c r="L875" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M875" t="str">
+        <v>2026-07-01 19:44:05</v>
+      </c>
+      <c r="N875" s="1">
+        <v>320000</v>
+      </c>
+      <c r="O875" s="1">
+        <v>0</v>
+      </c>
+      <c r="P875" t="str">
+        <v/>
+      </c>
+      <c r="Q875" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R875" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="str">
+        <v>T260701-00019</v>
+      </c>
+      <c r="B876" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C876" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D876" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E876" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F876">
+        <v>0</v>
+      </c>
+      <c r="G876" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H876" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I876" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J876" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K876">
+        <v>1</v>
+      </c>
+      <c r="L876" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M876" t="str">
+        <v>2026-07-01 19:43:22</v>
+      </c>
+      <c r="N876" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O876" s="1">
+        <v>0</v>
+      </c>
+      <c r="P876" t="str">
+        <v/>
+      </c>
+      <c r="Q876" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R876" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="str">
+        <v>T260701-00018</v>
+      </c>
+      <c r="B877" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C877" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D877" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E877" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F877">
+        <v>1</v>
+      </c>
+      <c r="G877" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H877" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I877" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J877" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K877">
+        <v>1</v>
+      </c>
+      <c r="L877" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M877" t="str">
+        <v>2026-07-01 19:43:03</v>
+      </c>
+      <c r="N877" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O877" s="1">
+        <v>0</v>
+      </c>
+      <c r="P877" t="str">
+        <v/>
+      </c>
+      <c r="Q877" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R877" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="str">
+        <v>T260701-00017</v>
+      </c>
+      <c r="B878" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C878" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D878" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E878" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F878">
+        <v>0</v>
+      </c>
+      <c r="G878" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H878" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I878" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J878" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K878">
+        <v>1</v>
+      </c>
+      <c r="L878" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M878" t="str">
+        <v>2026-07-01 19:42:39</v>
+      </c>
+      <c r="N878" s="1">
+        <v>310000</v>
+      </c>
+      <c r="O878" s="1">
+        <v>0</v>
+      </c>
+      <c r="P878" t="str">
+        <v/>
+      </c>
+      <c r="Q878" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R878" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="str">
+        <v>T260701-00016</v>
+      </c>
+      <c r="B879" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C879" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D879" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E879" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F879">
+        <v>0</v>
+      </c>
+      <c r="G879" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H879" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I879" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J879" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K879">
+        <v>1</v>
+      </c>
+      <c r="L879" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M879" t="str">
+        <v>2026-07-01 19:42:17</v>
+      </c>
+      <c r="N879" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O879" s="1">
+        <v>0</v>
+      </c>
+      <c r="P879" t="str">
+        <v/>
+      </c>
+      <c r="Q879" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R879" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="str">
+        <v>T260701-00015</v>
+      </c>
+      <c r="B880" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C880" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D880" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E880" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F880">
+        <v>1</v>
+      </c>
+      <c r="G880" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H880" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I880" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J880" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K880">
+        <v>1</v>
+      </c>
+      <c r="L880" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M880" t="str">
+        <v>2026-07-01 19:42:02</v>
+      </c>
+      <c r="N880" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O880" s="1">
+        <v>0</v>
+      </c>
+      <c r="P880" t="str">
+        <v/>
+      </c>
+      <c r="Q880" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R880" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="str">
+        <v>T260701-00014</v>
+      </c>
+      <c r="B881" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C881" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D881" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E881" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F881">
+        <v>1</v>
+      </c>
+      <c r="G881" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H881" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I881" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J881" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K881">
+        <v>1</v>
+      </c>
+      <c r="L881" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M881" t="str">
+        <v>2026-07-01 19:41:41</v>
+      </c>
+      <c r="N881" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O881" s="1">
+        <v>0</v>
+      </c>
+      <c r="P881" t="str">
+        <v/>
+      </c>
+      <c r="Q881" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R881" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="str">
+        <v>T260701-00013</v>
+      </c>
+      <c r="B882" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C882" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D882" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E882" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F882">
+        <v>1</v>
+      </c>
+      <c r="G882" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H882" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I882" t="str">
+        <v>2026-07-01 22:00</v>
+      </c>
+      <c r="J882" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K882">
+        <v>1</v>
+      </c>
+      <c r="L882" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M882" t="str">
+        <v>2026-07-01 19:41:08</v>
+      </c>
+      <c r="N882" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O882" s="1">
+        <v>0</v>
+      </c>
+      <c r="P882" t="str">
+        <v/>
+      </c>
+      <c r="Q882" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R882" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="str">
+        <v>T260701-00012</v>
+      </c>
+      <c r="B883" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C883" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D883" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E883" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F883">
+        <v>1</v>
+      </c>
+      <c r="G883" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H883" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I883" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J883" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K883">
+        <v>1</v>
+      </c>
+      <c r="L883" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M883" t="str">
+        <v>2026-07-01 19:40:45</v>
+      </c>
+      <c r="N883" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O883" s="1">
+        <v>0</v>
+      </c>
+      <c r="P883" t="str">
+        <v/>
+      </c>
+      <c r="Q883" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R883" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="str">
+        <v>T260701-00011</v>
+      </c>
+      <c r="B884" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C884" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D884" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E884" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F884">
+        <v>0</v>
+      </c>
+      <c r="G884" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H884" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I884" t="str">
+        <v>2026-07-01 21:00</v>
+      </c>
+      <c r="J884" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K884">
+        <v>1</v>
+      </c>
+      <c r="L884" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M884" t="str">
+        <v>2026-07-01 19:40:21</v>
+      </c>
+      <c r="N884" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O884" s="1">
+        <v>0</v>
+      </c>
+      <c r="P884" t="str">
+        <v/>
+      </c>
+      <c r="Q884" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R884" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="str">
+        <v>T260701-00010</v>
+      </c>
+      <c r="B885" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C885" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D885" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E885" t="str">
+        <v>2026-07-01 19:00</v>
+      </c>
+      <c r="F885">
+        <v>1</v>
+      </c>
+      <c r="G885" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H885" t="str">
+        <v>경산시 해오름길114-2 경산FDC</v>
+      </c>
+      <c r="I885" t="str">
+        <v>2026-07-01 23:00</v>
+      </c>
+      <c r="J885" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K885">
+        <v>1</v>
+      </c>
+      <c r="L885" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M885" t="str">
+        <v>2026-07-01 19:40:04</v>
+      </c>
+      <c r="N885" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O885" s="1">
+        <v>0</v>
+      </c>
+      <c r="P885" t="str">
+        <v/>
+      </c>
+      <c r="Q885" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R885" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="str">
+        <v>T260701-00009</v>
+      </c>
+      <c r="B886" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C886" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D886" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E886" t="str">
+        <v>2026-07-01 17:30</v>
+      </c>
+      <c r="F886">
+        <v>0</v>
+      </c>
+      <c r="G886" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H886" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I886" t="str">
+        <v>2026-07-01 18:30</v>
+      </c>
+      <c r="J886" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K886">
+        <v>1</v>
+      </c>
+      <c r="L886" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M886" t="str">
+        <v>2026-07-01 19:31:35</v>
+      </c>
+      <c r="N886" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O886" s="1">
+        <v>0</v>
+      </c>
+      <c r="P886" t="str">
+        <v/>
+      </c>
+      <c r="Q886" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R886" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="str">
+        <v>T260701-00008</v>
+      </c>
+      <c r="B887" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C887" t="str">
+        <v>듀오백(화성)</v>
+      </c>
+      <c r="D887" t="str">
+        <v>경기 화성시 마도면 마도공단로6길 7 듀오백(화성)</v>
+      </c>
+      <c r="E887" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="F887">
+        <v>0</v>
+      </c>
+      <c r="G887" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H887" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I887" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="J887" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K887">
+        <v>1</v>
+      </c>
+      <c r="L887" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M887" t="str">
+        <v>2026-07-01 19:31:02</v>
+      </c>
+      <c r="N887" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O887" s="1">
+        <v>0</v>
+      </c>
+      <c r="P887" t="str">
+        <v>듀오백(화성) 외주사입고</v>
+      </c>
+      <c r="Q887" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R887" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="str">
+        <v>T260701-00007</v>
+      </c>
+      <c r="B888" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C888" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D888" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E888" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F888">
+        <v>0</v>
+      </c>
+      <c r="G888" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H888" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I888" t="str">
+        <v>2026-07-01 13:30</v>
+      </c>
+      <c r="J888" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K888">
+        <v>1</v>
+      </c>
+      <c r="L888" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M888" t="str">
+        <v>2026-07-01 19:29:27</v>
+      </c>
+      <c r="N888" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O888" s="1">
+        <v>0</v>
+      </c>
+      <c r="P888" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q888" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R888" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="str">
+        <v>T260701-00006</v>
+      </c>
+      <c r="B889" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C889" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D889" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E889" t="str">
+        <v>2026-07-01 16:30</v>
+      </c>
+      <c r="F889">
+        <v>0</v>
+      </c>
+      <c r="G889" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H889" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I889" t="str">
+        <v>2026-07-01 18:00</v>
+      </c>
+      <c r="J889" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K889">
+        <v>1</v>
+      </c>
+      <c r="L889" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M889" t="str">
+        <v>2026-07-01 16:09:24</v>
+      </c>
+      <c r="N889" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O889" s="1">
+        <v>0</v>
+      </c>
+      <c r="P889" t="str">
+        <v>20260701/경동택배_남이가마258 영업소_파렛트출하</v>
+      </c>
+      <c r="Q889" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R889" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="str">
+        <v>T260701-00005</v>
+      </c>
+      <c r="B890" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C890" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D890" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E890" t="str">
+        <v>2026-07-01 15:30</v>
+      </c>
+      <c r="F890">
+        <v>0</v>
+      </c>
+      <c r="G890" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H890" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I890" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J890" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K890">
+        <v>1</v>
+      </c>
+      <c r="L890" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M890" t="str">
+        <v>2026-07-01 14:58:37</v>
+      </c>
+      <c r="N890" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O890" s="1">
+        <v>0</v>
+      </c>
+      <c r="P890" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q890" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R890" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="str">
+        <v>T260701-00004</v>
+      </c>
+      <c r="B891" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C891" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D891" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E891" t="str">
+        <v>2026-07-01 15:20</v>
+      </c>
+      <c r="F891">
+        <v>0</v>
+      </c>
+      <c r="G891" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H891" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I891" t="str">
+        <v>2026-07-02 09:00</v>
+      </c>
+      <c r="J891" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K891">
+        <v>1</v>
+      </c>
+      <c r="L891" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M891" t="str">
+        <v>2026-07-01 14:53:20</v>
+      </c>
+      <c r="N891" s="1">
+        <v>440000</v>
+      </c>
+      <c r="O891" s="1">
+        <v>0</v>
+      </c>
+      <c r="P891" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q891" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R891" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="str">
+        <v>T260701-00003</v>
+      </c>
+      <c r="B892" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C892" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D892" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E892" t="str">
+        <v>2026-07-01 10:00</v>
+      </c>
+      <c r="F892">
+        <v>0</v>
+      </c>
+      <c r="G892" t="str">
+        <v>하이얼(이천다코넷)</v>
+      </c>
+      <c r="H892" t="str">
+        <v>경기 이천시 마장면 덕평로 787 다코넷 이천</v>
+      </c>
+      <c r="I892" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J892" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K892">
+        <v>1</v>
+      </c>
+      <c r="L892" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M892" t="str">
+        <v>2026-07-01 10:15:38</v>
+      </c>
+      <c r="N892" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O892" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P892" t="str">
+        <v>20260701/하이얼_이천다코넷_ 파렛트_출하</v>
+      </c>
+      <c r="Q892" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R892" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="str">
+        <v>T260701-00002</v>
+      </c>
+      <c r="B893" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C893" t="str">
+        <v>청주ARC(디지탈태양)</v>
+      </c>
+      <c r="D893" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주ARC(디지탈태양)</v>
+      </c>
+      <c r="E893" t="str">
+        <v>2026-07-01 08:30</v>
+      </c>
+      <c r="F893">
+        <v>0</v>
+      </c>
+      <c r="G893" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H893" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="I893" t="str">
+        <v>2026-07-01 10:30</v>
+      </c>
+      <c r="J893" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K893">
+        <v>1</v>
+      </c>
+      <c r="L893" t="str">
+        <v>신소라</v>
+      </c>
+      <c r="M893" t="str">
+        <v>2026-07-01 10:13:39</v>
+      </c>
+      <c r="N893" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O893" s="1">
+        <v>0</v>
+      </c>
+      <c r="P893" t="str">
+        <v>20260701_디지탈태양 청주→안성FC 재고 이동 1호차</v>
+      </c>
+      <c r="Q893" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R893" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="str">
+        <v>T260701-00001</v>
+      </c>
+      <c r="B894" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C894" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D894" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E894" t="str">
+        <v>2026-07-01 09:00</v>
+      </c>
+      <c r="F894">
+        <v>0</v>
+      </c>
+      <c r="G894" t="str">
+        <v>현대클러스터 한강미사3차</v>
+      </c>
+      <c r="H894" t="str">
+        <v>경기 하남시 미사강변한강로 165 현대클러스터 한강미사3차</v>
+      </c>
+      <c r="I894" t="str">
+        <v>2026-07-01 11:00</v>
+      </c>
+      <c r="J894" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K894">
+        <v>1</v>
+      </c>
+      <c r="L894" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M894" t="str">
+        <v>2026-07-01 09:07:09</v>
+      </c>
+      <c r="N894" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O894" s="1">
+        <v>0</v>
+      </c>
+      <c r="P894" t="str">
+        <v>스마트윈드 출하</v>
+      </c>
+      <c r="Q894" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R894" t="str">
+        <v>스마트윈드</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R746"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R894"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260807-00043</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260807-00042</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260807-00041</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260807-00040</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260807-00039</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260807-00038</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260807-00037</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260807-00036</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260807-00035</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260807-00034</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260807-00033</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260807-00032</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260807-00031</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260807-00030</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260807-00029</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260807-00028</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260807-00027</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260807-00026</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260807-00025</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260807-00024</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260807-00023</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1616,7 +1616,7 @@
         <v>T260807-00022</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>안성FC</v>
@@ -1672,7 +1672,7 @@
         <v>T260807-00021</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>안성FC</v>
@@ -1728,7 +1728,7 @@
         <v>T260807-00020</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>안성FC</v>
@@ -1784,7 +1784,7 @@
         <v>T260807-00019</v>
       </c>
       <c r="B26" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C26" t="str">
         <v>안성FC</v>
@@ -1840,7 +1840,7 @@
         <v>T260807-00018</v>
       </c>
       <c r="B27" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C27" t="str">
         <v>안성FC</v>
@@ -1896,7 +1896,7 @@
         <v>T260807-00017</v>
       </c>
       <c r="B28" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C28" t="str">
         <v>안성FC</v>
@@ -1952,7 +1952,7 @@
         <v>T260807-00016</v>
       </c>
       <c r="B29" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C29" t="str">
         <v>안성FC</v>
@@ -2008,7 +2008,7 @@
         <v>T260807-00015</v>
       </c>
       <c r="B30" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C30" t="str">
         <v>안성FC</v>
@@ -2064,7 +2064,7 @@
         <v>T260807-00014</v>
       </c>
       <c r="B31" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C31" t="str">
         <v>인천FDC</v>
@@ -2120,7 +2120,7 @@
         <v>T260807-00013</v>
       </c>
       <c r="B32" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C32" t="str">
         <v>샤오미</v>
@@ -2176,7 +2176,7 @@
         <v>T260807-00012</v>
       </c>
       <c r="B33" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C33" t="str">
         <v>아이베</v>
@@ -2232,7 +2232,7 @@
         <v>T260807-00011</v>
       </c>
       <c r="B34" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C34" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -1336,7 +1336,7 @@
         <v>T260811-00012</v>
       </c>
       <c r="B18" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1372,16 +1372,16 @@
         <v>2026-08-11 19:08:29</v>
       </c>
       <c r="N18" s="1">
-        <v/>
+        <v>200000</v>
       </c>
       <c r="O18" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P18" t="str">
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R18" t="str">
         <v>(주)위니온로지스</v>
@@ -1392,7 +1392,7 @@
         <v>T260811-00011</v>
       </c>
       <c r="B19" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1428,16 +1428,16 @@
         <v>2026-08-11 19:08:15</v>
       </c>
       <c r="N19" s="1">
-        <v/>
+        <v>520000</v>
       </c>
       <c r="O19" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P19" t="str">
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R19" t="str">
         <v>(주)위니온로지스</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260811-00028</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260811-00027</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260811-00026</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260811-00025</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260811-00024</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260811-00023</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260811-00022</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260811-00021</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260811-00020</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260811-00019</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260811-00018</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260811-00017</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260811-00016</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260811-00015</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260811-00014</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260811-00013</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260811-00012</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260811-00011</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260811-00010</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260811-00009</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>남양주FDC</v>
@@ -1560,7 +1560,7 @@
         <v>T260811-00008</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>화성FDC</v>
@@ -1616,7 +1616,7 @@
         <v>T260811-00007</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>용인FDSYS</v>
@@ -1672,7 +1672,7 @@
         <v>T260811-00006</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>용인FDSYS</v>
@@ -1728,7 +1728,7 @@
         <v>T260811-00005</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>아이베</v>
@@ -1784,7 +1784,7 @@
         <v>T260811-00004</v>
       </c>
       <c r="B26" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C26" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -776,7 +776,7 @@
         <v>T260812-00026</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260812-00025</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260812-00024</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260812-00023</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260812-00022</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260812-00021</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260812-00020</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260812-00019</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260812-00018</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260812-00017</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260812-00016</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260812-00015</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260812-00014</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260812-00013</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260812-00012</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1616,7 +1616,7 @@
         <v>T260812-00011</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>안성FC</v>
@@ -1672,7 +1672,7 @@
         <v>T260812-00010</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>안성FC</v>
@@ -1728,7 +1728,7 @@
         <v>T260812-00009</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>안성FC</v>
@@ -1784,7 +1784,7 @@
         <v>T260812-00008</v>
       </c>
       <c r="B26" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C26" t="str">
         <v>안성FC</v>
@@ -1840,7 +1840,7 @@
         <v>T260812-00007</v>
       </c>
       <c r="B27" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C27" t="str">
         <v>안성FC</v>
@@ -1896,7 +1896,7 @@
         <v>T260812-00006</v>
       </c>
       <c r="B28" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C28" t="str">
         <v>안성FC</v>
@@ -1952,7 +1952,7 @@
         <v>T260812-00005</v>
       </c>
       <c r="B29" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C29" t="str">
         <v>안성FC</v>
@@ -2008,7 +2008,7 @@
         <v>T260812-00004</v>
       </c>
       <c r="B30" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C30" t="str">
         <v>곤지암FDC</v>
@@ -2064,7 +2064,7 @@
         <v>T260812-00003</v>
       </c>
       <c r="B31" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C31" t="str">
         <v>샤오미 집하장</v>
@@ -2120,7 +2120,7 @@
         <v>T260812-00002</v>
       </c>
       <c r="B32" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C32" t="str">
         <v>아이베</v>
@@ -2176,7 +2176,7 @@
         <v>T260812-00001</v>
       </c>
       <c r="B33" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C33" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -832,7 +832,7 @@
         <v>T260813-00028</v>
       </c>
       <c r="B9" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -868,16 +868,16 @@
         <v>2026-08-13 18:29:08</v>
       </c>
       <c r="N9" s="1">
-        <v/>
+        <v>240000</v>
       </c>
       <c r="O9" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P9" t="str">
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R9" t="str">
         <v>(주)위니온로지스</v>
@@ -888,7 +888,7 @@
         <v>T260813-00027</v>
       </c>
       <c r="B10" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -924,16 +924,16 @@
         <v>2026-08-13 18:28:48</v>
       </c>
       <c r="N10" s="1">
-        <v/>
+        <v>350000</v>
       </c>
       <c r="O10" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P10" t="str">
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R10" t="str">
         <v>(주)위니온로지스</v>
@@ -944,7 +944,7 @@
         <v>T260813-00026</v>
       </c>
       <c r="B11" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -980,16 +980,16 @@
         <v>2026-08-13 18:28:21</v>
       </c>
       <c r="N11" s="1">
-        <v/>
+        <v>240000</v>
       </c>
       <c r="O11" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P11" t="str">
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R11" t="str">
         <v>(주)위니온로지스</v>
@@ -1000,7 +1000,7 @@
         <v>T260813-00025</v>
       </c>
       <c r="B12" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1036,16 +1036,16 @@
         <v>2026-08-13 18:28:04</v>
       </c>
       <c r="N12" s="1">
-        <v/>
+        <v>260000</v>
       </c>
       <c r="O12" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P12" t="str">
         <v/>
       </c>
       <c r="Q12" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R12" t="str">
         <v>(주)위니온로지스</v>
@@ -1056,7 +1056,7 @@
         <v>T260813-00024</v>
       </c>
       <c r="B13" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1092,16 +1092,16 @@
         <v>2026-08-13 18:27:35</v>
       </c>
       <c r="N13" s="1">
-        <v/>
+        <v>290000</v>
       </c>
       <c r="O13" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P13" t="str">
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R13" t="str">
         <v>(주)위니온로지스</v>
@@ -1112,7 +1112,7 @@
         <v>T260813-00023</v>
       </c>
       <c r="B14" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1148,16 +1148,16 @@
         <v>2026-08-13 18:27:10</v>
       </c>
       <c r="N14" s="1">
-        <v/>
+        <v>590000</v>
       </c>
       <c r="O14" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P14" t="str">
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R14" t="str">
         <v>(주)위니온로지스</v>
@@ -1168,7 +1168,7 @@
         <v>T260813-00022</v>
       </c>
       <c r="B15" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1204,16 +1204,16 @@
         <v>2026-08-13 18:24:20</v>
       </c>
       <c r="N15" s="1">
-        <v/>
+        <v>250000</v>
       </c>
       <c r="O15" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P15" t="str">
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R15" t="str">
         <v>(주)위니온로지스</v>
@@ -1224,7 +1224,7 @@
         <v>T260813-00021</v>
       </c>
       <c r="B16" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1260,16 +1260,16 @@
         <v>2026-08-13 18:24:03</v>
       </c>
       <c r="N16" s="1">
-        <v/>
+        <v>260000</v>
       </c>
       <c r="O16" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P16" t="str">
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R16" t="str">
         <v>(주)위니온로지스</v>
@@ -1280,7 +1280,7 @@
         <v>T260813-00020</v>
       </c>
       <c r="B17" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1316,16 +1316,16 @@
         <v>2026-08-13 18:23:45</v>
       </c>
       <c r="N17" s="1">
-        <v/>
+        <v>520000</v>
       </c>
       <c r="O17" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P17" t="str">
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R17" t="str">
         <v>(주)위니온로지스</v>
@@ -1336,7 +1336,7 @@
         <v>T260813-00019</v>
       </c>
       <c r="B18" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1372,16 +1372,16 @@
         <v>2026-08-13 18:23:23</v>
       </c>
       <c r="N18" s="1">
-        <v/>
+        <v>200000</v>
       </c>
       <c r="O18" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P18" t="str">
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R18" t="str">
         <v>(주)위니온로지스</v>
@@ -1392,7 +1392,7 @@
         <v>T260813-00018</v>
       </c>
       <c r="B19" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1428,16 +1428,16 @@
         <v>2026-08-13 18:23:08</v>
       </c>
       <c r="N19" s="1">
-        <v/>
+        <v>520000</v>
       </c>
       <c r="O19" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P19" t="str">
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R19" t="str">
         <v>(주)위니온로지스</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260814-00029</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260814-00028</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260814-00027</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260814-00026</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260814-00025</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260814-00024</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260814-00023</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260814-00022</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260814-00021</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260814-00020</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260814-00019</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260814-00018</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260814-00017</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260814-00016</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260814-00015</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260814-00014</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260814-00013</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260818-00032</v>
       </c>
       <c r="B2" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -476,16 +476,16 @@
         <v>2026-08-18 19:48:09</v>
       </c>
       <c r="N2" s="1">
-        <v/>
+        <v>130000</v>
       </c>
       <c r="O2" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P2" t="str">
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R2" t="str">
         <v>(주)위니온로지스</v>
@@ -496,7 +496,7 @@
         <v>T260818-00031</v>
       </c>
       <c r="B3" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -532,16 +532,16 @@
         <v>2026-08-18 19:47:49</v>
       </c>
       <c r="N3" s="1">
-        <v/>
+        <v>80000</v>
       </c>
       <c r="O3" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P3" t="str">
         <v/>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R3" t="str">
         <v>(주)위니온로지스</v>
@@ -552,7 +552,7 @@
         <v>T260818-00030</v>
       </c>
       <c r="B4" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -588,16 +588,16 @@
         <v>2026-08-18 19:47:30</v>
       </c>
       <c r="N4" s="1">
-        <v/>
+        <v>240000</v>
       </c>
       <c r="O4" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P4" t="str">
         <v/>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R4" t="str">
         <v>(주)위니온로지스</v>
@@ -608,7 +608,7 @@
         <v>T260818-00029</v>
       </c>
       <c r="B5" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -644,16 +644,16 @@
         <v>2026-08-18 19:46:19</v>
       </c>
       <c r="N5" s="1">
-        <v/>
+        <v>350000</v>
       </c>
       <c r="O5" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P5" t="str">
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R5" t="str">
         <v>(주)위니온로지스</v>
@@ -664,7 +664,7 @@
         <v>T260818-00028</v>
       </c>
       <c r="B6" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -700,16 +700,16 @@
         <v>2026-08-18 19:45:39</v>
       </c>
       <c r="N6" s="1">
-        <v/>
+        <v>170000</v>
       </c>
       <c r="O6" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P6" t="str">
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R6" t="str">
         <v>(주)위니온로지스</v>
@@ -720,7 +720,7 @@
         <v>T260818-00027</v>
       </c>
       <c r="B7" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -744,7 +744,7 @@
         <v>2026-08-19 07:00</v>
       </c>
       <c r="J7" t="str">
-        <v>1.5톤 카고</v>
+        <v>1톤 카고</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -756,16 +756,16 @@
         <v>2026-08-18 19:45:10</v>
       </c>
       <c r="N7" s="1">
-        <v/>
+        <v>240000</v>
       </c>
       <c r="O7" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P7" t="str">
         <v/>
       </c>
       <c r="Q7" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R7" t="str">
         <v>(주)위니온로지스</v>
@@ -776,7 +776,7 @@
         <v>T260818-00026</v>
       </c>
       <c r="B8" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -812,16 +812,16 @@
         <v>2026-08-18 19:44:01</v>
       </c>
       <c r="N8" s="1">
-        <v/>
+        <v>240000</v>
       </c>
       <c r="O8" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P8" t="str">
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R8" t="str">
         <v>(주)위니온로지스</v>
@@ -832,7 +832,7 @@
         <v>T260818-00025</v>
       </c>
       <c r="B9" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -868,16 +868,16 @@
         <v>2026-08-18 19:43:29</v>
       </c>
       <c r="N9" s="1">
-        <v/>
+        <v>350000</v>
       </c>
       <c r="O9" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P9" t="str">
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R9" t="str">
         <v>(주)위니온로지스</v>
@@ -888,7 +888,7 @@
         <v>T260818-00024</v>
       </c>
       <c r="B10" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -924,19 +924,19 @@
         <v>2026-08-18 19:43:06</v>
       </c>
       <c r="N10" s="1">
-        <v/>
+        <v>590000</v>
       </c>
       <c r="O10" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P10" t="str">
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R10" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
     </row>
     <row r="11">
@@ -944,7 +944,7 @@
         <v>T260818-00023</v>
       </c>
       <c r="B11" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -980,19 +980,19 @@
         <v>2026-08-18 19:42:33</v>
       </c>
       <c r="N11" s="1">
-        <v/>
+        <v>260000</v>
       </c>
       <c r="O11" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P11" t="str">
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R11" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
     </row>
     <row r="12">
@@ -1000,7 +1000,7 @@
         <v>T260818-00022</v>
       </c>
       <c r="B12" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1024,7 +1024,7 @@
         <v>2026-08-18 22:00</v>
       </c>
       <c r="J12" t="str">
-        <v>11톤 윙바디</v>
+        <v>5톤 윙바디</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1036,19 +1036,19 @@
         <v>2026-08-18 19:42:15</v>
       </c>
       <c r="N12" s="1">
-        <v/>
+        <v>290000</v>
       </c>
       <c r="O12" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P12" t="str">
         <v/>
       </c>
       <c r="Q12" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R12" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
     </row>
     <row r="13">
@@ -1056,7 +1056,7 @@
         <v>T260818-00021</v>
       </c>
       <c r="B13" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1092,19 +1092,19 @@
         <v>2026-08-18 19:41:54</v>
       </c>
       <c r="N13" s="1">
-        <v/>
+        <v>490000</v>
       </c>
       <c r="O13" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P13" t="str">
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R13" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
     </row>
     <row r="14">
@@ -1112,7 +1112,7 @@
         <v>T260818-00020</v>
       </c>
       <c r="B14" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1148,19 +1148,19 @@
         <v>2026-08-18 19:41:20</v>
       </c>
       <c r="N14" s="1">
-        <v/>
+        <v>250000</v>
       </c>
       <c r="O14" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P14" t="str">
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R14" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
     </row>
     <row r="15">
@@ -1168,7 +1168,7 @@
         <v>T260818-00019</v>
       </c>
       <c r="B15" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1204,19 +1204,19 @@
         <v>2026-08-18 19:41:05</v>
       </c>
       <c r="N15" s="1">
-        <v/>
+        <v>260000</v>
       </c>
       <c r="O15" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P15" t="str">
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R15" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
     </row>
     <row r="16">
@@ -1224,7 +1224,7 @@
         <v>T260818-00018</v>
       </c>
       <c r="B16" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1260,19 +1260,19 @@
         <v>2026-08-18 19:40:46</v>
       </c>
       <c r="N16" s="1">
-        <v/>
+        <v>520000</v>
       </c>
       <c r="O16" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P16" t="str">
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R16" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
     </row>
     <row r="17">
@@ -1280,7 +1280,7 @@
         <v>T260818-00017</v>
       </c>
       <c r="B17" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1316,19 +1316,19 @@
         <v>2026-08-18 19:40:24</v>
       </c>
       <c r="N17" s="1">
-        <v/>
+        <v>150000</v>
       </c>
       <c r="O17" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P17" t="str">
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R17" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
     </row>
     <row r="18">
@@ -1336,7 +1336,7 @@
         <v>T260818-00016</v>
       </c>
       <c r="B18" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1372,19 +1372,19 @@
         <v>2026-08-18 19:39:56</v>
       </c>
       <c r="N18" s="1">
-        <v/>
+        <v>200000</v>
       </c>
       <c r="O18" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P18" t="str">
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R18" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
     </row>
     <row r="19">
@@ -1392,7 +1392,7 @@
         <v>T260818-00015</v>
       </c>
       <c r="B19" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1428,19 +1428,19 @@
         <v>2026-08-18 19:39:41</v>
       </c>
       <c r="N19" s="1">
-        <v/>
+        <v>520000</v>
       </c>
       <c r="O19" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P19" t="str">
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="R19" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
     </row>
     <row r="20">

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -776,7 +776,7 @@
         <v>T260818-00032</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260818-00031</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260818-00030</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260818-00029</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260818-00028</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260818-00027</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260818-00026</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260818-00025</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260818-00024</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260818-00023</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260818-00022</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260818-00021</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260818-00020</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260818-00019</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260818-00018</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1616,7 +1616,7 @@
         <v>T260818-00017</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>안성FC</v>
@@ -1672,7 +1672,7 @@
         <v>T260818-00016</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>안성FC</v>
@@ -1728,7 +1728,7 @@
         <v>T260818-00015</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>안성FC</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260819-00031</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260819-00030</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260819-00029</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260819-00027</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260819-00026</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260819-00025</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260819-00024</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260819-00023</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260819-00022</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260819-00021</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260819-00020</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260819-00019</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260819-00018</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260819-00017</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260819-00016</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260819-00015</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260819-00014</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260819-00013</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260819-00012</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>라꾸스토리</v>
@@ -1504,7 +1504,7 @@
         <v>T260819-00011</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>전주FDC</v>
@@ -1560,7 +1560,7 @@
         <v>T260819-00010</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>아이베</v>
@@ -1616,7 +1616,7 @@
         <v>T260819-00009</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -832,7 +832,7 @@
         <v>T260820-00021</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260820-00020</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260820-00019</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260820-00018</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260820-00017</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260820-00016</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260820-00015</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260820-00014</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260820-00013</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260820-00012</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260820-00011</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260820-00010</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260820-00009</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260820-00008</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>원주FDC(신규)</v>
@@ -1616,7 +1616,7 @@
         <v>T260820-00007</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>샤오미 집하장</v>
@@ -1672,7 +1672,7 @@
         <v>T260820-00006</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>아이베</v>
@@ -1728,7 +1728,7 @@
         <v>T260820-00005</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260821-00038</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260821-00037</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260821-00036</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260821-00035</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260821-00034</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260821-00033</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260821-00032</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260821-00031</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260821-00030</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260821-00029</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260821-00028</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260821-00027</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260821-00026</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260821-00025</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260821-00024</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260821-00023</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260821-00022</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -496,7 +496,7 @@
         <v>T260824-00027</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260824-00026</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260824-00025</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260824-00024</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260824-00023</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260824-00022</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260824-00021</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260824-00020</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260824-00019</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260824-00018</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260824-00017</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260824-00016</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260824-00015</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260824-00014</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260824-00013</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260824-00012</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260824-00011</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260824-00010</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260824-00009</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260824-00008</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1728,7 +1728,7 @@
         <v>T260824-00005</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>안성FC</v>
@@ -1784,7 +1784,7 @@
         <v>T260824-00004</v>
       </c>
       <c r="B26" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C26" t="str">
         <v>남양주FDC</v>
@@ -1840,7 +1840,7 @@
         <v>T260824-00003</v>
       </c>
       <c r="B27" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C27" t="str">
         <v>샤오미 집하장</v>
@@ -1896,7 +1896,7 @@
         <v>T260824-00002</v>
       </c>
       <c r="B28" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C28" t="str">
         <v>아이베</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260825-00021</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260825-00020</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260825-00018</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260825-00017</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260825-00016</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260825-00015</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260825-00014</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260825-00013</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260825-00012</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260825-00011</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260825-00010</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260825-00009</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260825-00008</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260825-00007</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260825-00006</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>샤오미 집하장</v>
@@ -1280,7 +1280,7 @@
         <v>T260825-00005</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>아이베</v>
@@ -1336,7 +1336,7 @@
         <v>T260825-00004</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260826-00010</v>
       </c>
       <c r="B2" t="str">
-        <v>접수</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -476,7 +476,7 @@
         <v>2026-08-26 16:13:08</v>
       </c>
       <c r="N2" s="1">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -485,7 +485,7 @@
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
       <c r="R2" t="str">
         <v>(주)위니온로지스</v>
@@ -496,7 +496,7 @@
         <v>T260826-00009</v>
       </c>
       <c r="B3" t="str">
-        <v>접수</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>청주ARC</v>
@@ -532,7 +532,7 @@
         <v>2026-08-26 14:42:58</v>
       </c>
       <c r="N3" s="1">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>운송장 : 260717300013 / ILD-501UWB, 260811650030 / ILW-301BHW, 260716480013 / ILKR-120HMS 샘플용으로 사용 필요하여 거래처로 출하</v>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
       <c r="R3" t="str">
         <v>일코전자</v>
@@ -552,7 +552,7 @@
         <v>T260826-00008</v>
       </c>
       <c r="B4" t="str">
-        <v>접수</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>하이마트 마산</v>
@@ -588,7 +588,7 @@
         <v>2026-08-26 14:42:14</v>
       </c>
       <c r="N4" s="1">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="O4" s="1">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v/>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
       <c r="R4" t="str">
         <v>일코전자</v>
@@ -664,7 +664,7 @@
         <v>T260826-00006</v>
       </c>
       <c r="B6" t="str">
-        <v>접수</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>하이마트 광주</v>
@@ -700,7 +700,7 @@
         <v>2026-08-26 14:40:39</v>
       </c>
       <c r="N6" s="1">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
       <c r="R6" t="str">
         <v>일코전자</v>
@@ -720,7 +720,7 @@
         <v>T260826-00005</v>
       </c>
       <c r="B7" t="str">
-        <v>접수</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>하이마트 이천</v>
@@ -756,7 +756,7 @@
         <v>2026-08-26 14:39:40</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -765,7 +765,7 @@
         <v/>
       </c>
       <c r="Q7" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
       <c r="R7" t="str">
         <v>일코전자</v>
@@ -776,7 +776,7 @@
         <v>T260826-00004</v>
       </c>
       <c r="B8" t="str">
-        <v>접수</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>하이마트 공주</v>
@@ -812,7 +812,7 @@
         <v>2026-08-26 14:38:56</v>
       </c>
       <c r="N8" s="1">
-        <v>0</v>
+        <v>170000</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
       <c r="R8" t="str">
         <v>일코전자</v>
@@ -832,7 +832,7 @@
         <v>T260826-00003</v>
       </c>
       <c r="B9" t="str">
-        <v>접수</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>하이마트 화성</v>
@@ -868,7 +868,7 @@
         <v>2026-08-26 14:38:06</v>
       </c>
       <c r="N9" s="1">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
       <c r="R9" t="str">
         <v>일코전자</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260828-00033</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260828-00032</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260828-00031</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260828-00030</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260828-00029</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260828-00028</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260828-00027</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260828-00026</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260828-00025</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260828-00024</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260828-00023</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260828-00022</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260828-00021</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260828-00020</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260828-00019</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260828-00018</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260828-00014</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1616,7 +1616,7 @@
         <v>T260828-00012</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>샤오미 집하장</v>
@@ -1672,7 +1672,7 @@
         <v>T260828-00011</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>아이베</v>
@@ -1728,7 +1728,7 @@
         <v>T260828-00010</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R734"/>
+  <dimension ref="A1:R678"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38347,3145 +38347,9 @@
         <v>(주)위니온로지스</v>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="str">
-        <v>T260804-00025</v>
-      </c>
-      <c r="B679" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C679" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D679" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E679" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F679">
-        <v>0</v>
-      </c>
-      <c r="G679" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H679" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I679" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J679" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K679">
-        <v>1</v>
-      </c>
-      <c r="L679" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M679" t="str">
-        <v>2026-08-04 20:32:35</v>
-      </c>
-      <c r="N679" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O679" s="1">
-        <v>0</v>
-      </c>
-      <c r="P679" t="str">
-        <v/>
-      </c>
-      <c r="Q679" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R679" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="str">
-        <v>T260804-00024</v>
-      </c>
-      <c r="B680" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C680" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D680" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E680" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F680">
-        <v>0</v>
-      </c>
-      <c r="G680" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H680" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I680" t="str">
-        <v>2026-08-05 08:00</v>
-      </c>
-      <c r="J680" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K680">
-        <v>1</v>
-      </c>
-      <c r="L680" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M680" t="str">
-        <v>2026-08-04 20:32:12</v>
-      </c>
-      <c r="N680" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O680" s="1">
-        <v>0</v>
-      </c>
-      <c r="P680" t="str">
-        <v/>
-      </c>
-      <c r="Q680" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R680" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="str">
-        <v>T260804-00023</v>
-      </c>
-      <c r="B681" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C681" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D681" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E681" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F681">
-        <v>1</v>
-      </c>
-      <c r="G681" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H681" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I681" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J681" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K681">
-        <v>1</v>
-      </c>
-      <c r="L681" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M681" t="str">
-        <v>2026-08-04 20:31:26</v>
-      </c>
-      <c r="N681" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O681" s="1">
-        <v>0</v>
-      </c>
-      <c r="P681" t="str">
-        <v/>
-      </c>
-      <c r="Q681" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R681" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="str">
-        <v>T260804-00022</v>
-      </c>
-      <c r="B682" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C682" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D682" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E682" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F682">
-        <v>0</v>
-      </c>
-      <c r="G682" t="str">
-        <v>안성ACP</v>
-      </c>
-      <c r="H682" t="str">
-        <v>경기 안성시 대덕면 중앙로 96-15 안성ACP</v>
-      </c>
-      <c r="I682" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J682" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K682">
-        <v>1</v>
-      </c>
-      <c r="L682" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M682" t="str">
-        <v>2026-08-04 20:30:56</v>
-      </c>
-      <c r="N682" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O682" s="1">
-        <v>0</v>
-      </c>
-      <c r="P682" t="str">
-        <v/>
-      </c>
-      <c r="Q682" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R682" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="str">
-        <v>T260804-00021</v>
-      </c>
-      <c r="B683" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C683" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D683" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E683" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F683">
-        <v>0</v>
-      </c>
-      <c r="G683" t="str">
-        <v>시흥ACP</v>
-      </c>
-      <c r="H683" t="str">
-        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
-      </c>
-      <c r="I683" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J683" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K683">
-        <v>1</v>
-      </c>
-      <c r="L683" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M683" t="str">
-        <v>2026-08-04 20:30:28</v>
-      </c>
-      <c r="N683" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O683" s="1">
-        <v>0</v>
-      </c>
-      <c r="P683" t="str">
-        <v/>
-      </c>
-      <c r="Q683" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R683" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="str">
-        <v>T260804-00020</v>
-      </c>
-      <c r="B684" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C684" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D684" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E684" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F684">
-        <v>0</v>
-      </c>
-      <c r="G684" t="str">
-        <v>부산ACP</v>
-      </c>
-      <c r="H684" t="str">
-        <v>부산 강서구 상덕로97번길 47 부산ACP</v>
-      </c>
-      <c r="I684" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J684" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K684">
-        <v>1</v>
-      </c>
-      <c r="L684" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M684" t="str">
-        <v>2026-08-04 20:29:48</v>
-      </c>
-      <c r="N684" s="1">
-        <v>450000</v>
-      </c>
-      <c r="O684" s="1">
-        <v>0</v>
-      </c>
-      <c r="P684" t="str">
-        <v/>
-      </c>
-      <c r="Q684" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R684" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="str">
-        <v>T260804-00019</v>
-      </c>
-      <c r="B685" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C685" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D685" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E685" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F685">
-        <v>0</v>
-      </c>
-      <c r="G685" t="str">
-        <v>대전중구ACP</v>
-      </c>
-      <c r="H685" t="str">
-        <v>대전 중구 보문산로77번길 8 대전중구ACP</v>
-      </c>
-      <c r="I685" t="str">
-        <v>2026-08-05 06:00</v>
-      </c>
-      <c r="J685" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K685">
-        <v>1</v>
-      </c>
-      <c r="L685" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M685" t="str">
-        <v>2026-08-04 20:14:33</v>
-      </c>
-      <c r="N685" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O685" s="1">
-        <v>0</v>
-      </c>
-      <c r="P685" t="str">
-        <v/>
-      </c>
-      <c r="Q685" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R685" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="str">
-        <v>T260804-00018</v>
-      </c>
-      <c r="B686" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C686" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D686" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E686" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F686">
-        <v>0</v>
-      </c>
-      <c r="G686" t="str">
-        <v>대전대덕ACP</v>
-      </c>
-      <c r="H686" t="str">
-        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
-      </c>
-      <c r="I686" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J686" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K686">
-        <v>1</v>
-      </c>
-      <c r="L686" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M686" t="str">
-        <v>2026-08-04 20:14:11</v>
-      </c>
-      <c r="N686" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O686" s="1">
-        <v>0</v>
-      </c>
-      <c r="P686" t="str">
-        <v/>
-      </c>
-      <c r="Q686" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R686" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="str">
-        <v>T260804-00017</v>
-      </c>
-      <c r="B687" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C687" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D687" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E687" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F687">
-        <v>1</v>
-      </c>
-      <c r="G687" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H687" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I687" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J687" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K687">
-        <v>1</v>
-      </c>
-      <c r="L687" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M687" t="str">
-        <v>2026-08-04 20:13:47</v>
-      </c>
-      <c r="N687" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O687" s="1">
-        <v>0</v>
-      </c>
-      <c r="P687" t="str">
-        <v/>
-      </c>
-      <c r="Q687" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R687" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="str">
-        <v>T260804-00016</v>
-      </c>
-      <c r="B688" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C688" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D688" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E688" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F688">
-        <v>0</v>
-      </c>
-      <c r="G688" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="H688" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="I688" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J688" t="str">
-        <v>2.5톤 카고</v>
-      </c>
-      <c r="K688">
-        <v>1</v>
-      </c>
-      <c r="L688" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M688" t="str">
-        <v>2026-08-04 20:13:22</v>
-      </c>
-      <c r="N688" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O688" s="1">
-        <v>0</v>
-      </c>
-      <c r="P688" t="str">
-        <v/>
-      </c>
-      <c r="Q688" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R688" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="str">
-        <v>T260804-00015</v>
-      </c>
-      <c r="B689" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C689" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D689" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E689" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F689">
-        <v>0</v>
-      </c>
-      <c r="G689" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H689" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I689" t="str">
-        <v>2026-08-04 21:00</v>
-      </c>
-      <c r="J689" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K689">
-        <v>1</v>
-      </c>
-      <c r="L689" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M689" t="str">
-        <v>2026-08-04 20:11:31</v>
-      </c>
-      <c r="N689" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O689" s="1">
-        <v>0</v>
-      </c>
-      <c r="P689" t="str">
-        <v/>
-      </c>
-      <c r="Q689" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R689" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="str">
-        <v>T260804-00014</v>
-      </c>
-      <c r="B690" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C690" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D690" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E690" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F690">
-        <v>1</v>
-      </c>
-      <c r="G690" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H690" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I690" t="str">
-        <v>2026-08-04 22:00</v>
-      </c>
-      <c r="J690" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K690">
-        <v>1</v>
-      </c>
-      <c r="L690" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M690" t="str">
-        <v>2026-08-04 20:11:15</v>
-      </c>
-      <c r="N690" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O690" s="1">
-        <v>0</v>
-      </c>
-      <c r="P690" t="str">
-        <v/>
-      </c>
-      <c r="Q690" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R690" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="str">
-        <v>T260804-00013</v>
-      </c>
-      <c r="B691" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C691" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D691" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E691" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F691">
-        <v>0</v>
-      </c>
-      <c r="G691" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H691" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I691" t="str">
-        <v>2026-08-04 23:00</v>
-      </c>
-      <c r="J691" t="str">
-        <v>5톤 카고</v>
-      </c>
-      <c r="K691">
-        <v>1</v>
-      </c>
-      <c r="L691" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M691" t="str">
-        <v>2026-08-04 20:10:56</v>
-      </c>
-      <c r="N691" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O691" s="1">
-        <v>0</v>
-      </c>
-      <c r="P691" t="str">
-        <v/>
-      </c>
-      <c r="Q691" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R691" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="str">
-        <v>T260804-00012</v>
-      </c>
-      <c r="B692" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C692" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D692" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E692" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F692">
-        <v>0</v>
-      </c>
-      <c r="G692" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H692" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I692" t="str">
-        <v>2026-08-04 21:00</v>
-      </c>
-      <c r="J692" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K692">
-        <v>1</v>
-      </c>
-      <c r="L692" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M692" t="str">
-        <v>2026-08-04 20:10:40</v>
-      </c>
-      <c r="N692" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O692" s="1">
-        <v>0</v>
-      </c>
-      <c r="P692" t="str">
-        <v/>
-      </c>
-      <c r="Q692" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R692" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="str">
-        <v>T260804-00011</v>
-      </c>
-      <c r="B693" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C693" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D693" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E693" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F693">
-        <v>1</v>
-      </c>
-      <c r="G693" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H693" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I693" t="str">
-        <v>2026-08-04 22:00</v>
-      </c>
-      <c r="J693" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K693">
-        <v>1</v>
-      </c>
-      <c r="L693" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M693" t="str">
-        <v>2026-08-04 20:10:24</v>
-      </c>
-      <c r="N693" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O693" s="1">
-        <v>0</v>
-      </c>
-      <c r="P693" t="str">
-        <v/>
-      </c>
-      <c r="Q693" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R693" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="str">
-        <v>T260804-00010</v>
-      </c>
-      <c r="B694" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C694" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D694" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E694" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F694">
-        <v>1</v>
-      </c>
-      <c r="G694" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H694" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I694" t="str">
-        <v>2026-08-04 23:00</v>
-      </c>
-      <c r="J694" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K694">
-        <v>1</v>
-      </c>
-      <c r="L694" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M694" t="str">
-        <v>2026-08-04 20:07:49</v>
-      </c>
-      <c r="N694" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O694" s="1">
-        <v>0</v>
-      </c>
-      <c r="P694" t="str">
-        <v/>
-      </c>
-      <c r="Q694" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R694" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="str">
-        <v>T260804-00009</v>
-      </c>
-      <c r="B695" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C695" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D695" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E695" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F695">
-        <v>1</v>
-      </c>
-      <c r="G695" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H695" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I695" t="str">
-        <v>2026-08-04 22:00</v>
-      </c>
-      <c r="J695" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K695">
-        <v>1</v>
-      </c>
-      <c r="L695" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M695" t="str">
-        <v>2026-08-04 20:07:16</v>
-      </c>
-      <c r="N695" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O695" s="1">
-        <v>0</v>
-      </c>
-      <c r="P695" t="str">
-        <v/>
-      </c>
-      <c r="Q695" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R695" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="str">
-        <v>T260804-00008</v>
-      </c>
-      <c r="B696" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C696" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D696" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E696" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F696">
-        <v>1</v>
-      </c>
-      <c r="G696" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H696" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I696" t="str">
-        <v>2026-08-04 23:00</v>
-      </c>
-      <c r="J696" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K696">
-        <v>1</v>
-      </c>
-      <c r="L696" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M696" t="str">
-        <v>2026-08-04 20:06:56</v>
-      </c>
-      <c r="N696" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O696" s="1">
-        <v>0</v>
-      </c>
-      <c r="P696" t="str">
-        <v/>
-      </c>
-      <c r="Q696" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R696" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="str">
-        <v>T260804-00007</v>
-      </c>
-      <c r="B697" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C697" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D697" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E697" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F697">
-        <v>0</v>
-      </c>
-      <c r="G697" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H697" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I697" t="str">
-        <v>2026-08-04 21:00</v>
-      </c>
-      <c r="J697" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K697">
-        <v>1</v>
-      </c>
-      <c r="L697" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M697" t="str">
-        <v>2026-08-04 20:06:32</v>
-      </c>
-      <c r="N697" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O697" s="1">
-        <v>0</v>
-      </c>
-      <c r="P697" t="str">
-        <v/>
-      </c>
-      <c r="Q697" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R697" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="str">
-        <v>T260804-00006</v>
-      </c>
-      <c r="B698" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C698" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D698" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E698" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F698">
-        <v>0</v>
-      </c>
-      <c r="G698" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H698" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I698" t="str">
-        <v>2026-08-04 21:00</v>
-      </c>
-      <c r="J698" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K698">
-        <v>1</v>
-      </c>
-      <c r="L698" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M698" t="str">
-        <v>2026-08-04 20:06:08</v>
-      </c>
-      <c r="N698" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O698" s="1">
-        <v>0</v>
-      </c>
-      <c r="P698" t="str">
-        <v/>
-      </c>
-      <c r="Q698" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R698" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="str">
-        <v>T260804-00005</v>
-      </c>
-      <c r="B699" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C699" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D699" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E699" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F699">
-        <v>1</v>
-      </c>
-      <c r="G699" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H699" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="I699" t="str">
-        <v>2026-08-04 23:00</v>
-      </c>
-      <c r="J699" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K699">
-        <v>1</v>
-      </c>
-      <c r="L699" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M699" t="str">
-        <v>2026-08-04 20:05:49</v>
-      </c>
-      <c r="N699" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O699" s="1">
-        <v>0</v>
-      </c>
-      <c r="P699" t="str">
-        <v/>
-      </c>
-      <c r="Q699" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R699" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="str">
-        <v>T260804-00004</v>
-      </c>
-      <c r="B700" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C700" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D700" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E700" t="str">
-        <v>2026-08-04 17:00</v>
-      </c>
-      <c r="F700">
-        <v>0</v>
-      </c>
-      <c r="G700" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H700" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I700" t="str">
-        <v>2026-08-04 18:00</v>
-      </c>
-      <c r="J700" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K700">
-        <v>1</v>
-      </c>
-      <c r="L700" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M700" t="str">
-        <v>2026-08-04 20:00:36</v>
-      </c>
-      <c r="N700" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O700" s="1">
-        <v>0</v>
-      </c>
-      <c r="P700" t="str">
-        <v/>
-      </c>
-      <c r="Q700" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R700" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="str">
-        <v>T260804-00003</v>
-      </c>
-      <c r="B701" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C701" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D701" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E701" t="str">
-        <v>2026-08-04 15:00</v>
-      </c>
-      <c r="F701">
-        <v>0</v>
-      </c>
-      <c r="G701" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H701" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I701" t="str">
-        <v>2026-08-04 16:00</v>
-      </c>
-      <c r="J701" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K701">
-        <v>1</v>
-      </c>
-      <c r="L701" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M701" t="str">
-        <v>2026-08-04 20:00:02</v>
-      </c>
-      <c r="N701" s="1">
-        <v>70000</v>
-      </c>
-      <c r="O701" s="1">
-        <v>0</v>
-      </c>
-      <c r="P701" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="Q701" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R701" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="str">
-        <v>T260804-00002</v>
-      </c>
-      <c r="B702" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C702" t="str">
-        <v>샤오미</v>
-      </c>
-      <c r="D702" t="str">
-        <v>경기 이천시 대월면 부필리 309 샤오미</v>
-      </c>
-      <c r="E702" t="str">
-        <v>2026-08-04 14:00</v>
-      </c>
-      <c r="F702">
-        <v>0</v>
-      </c>
-      <c r="G702" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H702" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I702" t="str">
-        <v>2026-08-04 15:00</v>
-      </c>
-      <c r="J702" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K702">
-        <v>1</v>
-      </c>
-      <c r="L702" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M702" t="str">
-        <v>2026-08-04 19:59:20</v>
-      </c>
-      <c r="N702" s="1">
-        <v>80000</v>
-      </c>
-      <c r="O702" s="1">
-        <v>0</v>
-      </c>
-      <c r="P702" t="str">
-        <v>거래처비용청구(3대)</v>
-      </c>
-      <c r="Q702" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R702" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="str">
-        <v>T260804-00001</v>
-      </c>
-      <c r="B703" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C703" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D703" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E703" t="str">
-        <v>2026-08-04 16:30</v>
-      </c>
-      <c r="F703">
-        <v>0</v>
-      </c>
-      <c r="G703" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H703" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I703" t="str">
-        <v>2026-08-04 18:00</v>
-      </c>
-      <c r="J703" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K703">
-        <v>1</v>
-      </c>
-      <c r="L703" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="M703" t="str">
-        <v>2026-08-04 15:46:27</v>
-      </c>
-      <c r="N703" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O703" s="1">
-        <v>0</v>
-      </c>
-      <c r="P703" t="str">
-        <v/>
-      </c>
-      <c r="Q703" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R703" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="str">
-        <v>T260803-00031</v>
-      </c>
-      <c r="B704" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C704" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D704" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E704" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F704">
-        <v>0</v>
-      </c>
-      <c r="G704" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H704" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I704" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J704" t="str">
-        <v>2.5톤 카고</v>
-      </c>
-      <c r="K704">
-        <v>1</v>
-      </c>
-      <c r="L704" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M704" t="str">
-        <v>2026-08-03 23:48:09</v>
-      </c>
-      <c r="N704" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O704" s="1">
-        <v>0</v>
-      </c>
-      <c r="P704" t="str">
-        <v/>
-      </c>
-      <c r="Q704" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R704" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="str">
-        <v>T260803-00030</v>
-      </c>
-      <c r="B705" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C705" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D705" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E705" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F705">
-        <v>0</v>
-      </c>
-      <c r="G705" t="str">
-        <v>춘천ACP</v>
-      </c>
-      <c r="H705" t="str">
-        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
-      </c>
-      <c r="I705" t="str">
-        <v>2026-08-04 08:00</v>
-      </c>
-      <c r="J705" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K705">
-        <v>1</v>
-      </c>
-      <c r="L705" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M705" t="str">
-        <v>2026-08-03 23:47:48</v>
-      </c>
-      <c r="N705" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O705" s="1">
-        <v>0</v>
-      </c>
-      <c r="P705" t="str">
-        <v/>
-      </c>
-      <c r="Q705" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R705" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="str">
-        <v>T260803-00029</v>
-      </c>
-      <c r="B706" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C706" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D706" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E706" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F706">
-        <v>0</v>
-      </c>
-      <c r="G706" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H706" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I706" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J706" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K706">
-        <v>1</v>
-      </c>
-      <c r="L706" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M706" t="str">
-        <v>2026-08-03 23:46:49</v>
-      </c>
-      <c r="N706" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O706" s="1">
-        <v>0</v>
-      </c>
-      <c r="P706" t="str">
-        <v/>
-      </c>
-      <c r="Q706" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R706" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="str">
-        <v>T260803-00028</v>
-      </c>
-      <c r="B707" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C707" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D707" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E707" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F707">
-        <v>1</v>
-      </c>
-      <c r="G707" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H707" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I707" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J707" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K707">
-        <v>1</v>
-      </c>
-      <c r="L707" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M707" t="str">
-        <v>2026-08-03 23:46:26</v>
-      </c>
-      <c r="N707" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O707" s="1">
-        <v>0</v>
-      </c>
-      <c r="P707" t="str">
-        <v/>
-      </c>
-      <c r="Q707" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R707" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="str">
-        <v>T260803-00027</v>
-      </c>
-      <c r="B708" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C708" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D708" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E708" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F708">
-        <v>0</v>
-      </c>
-      <c r="G708" t="str">
-        <v>안성ACP</v>
-      </c>
-      <c r="H708" t="str">
-        <v>경기 안성시 대덕면 중앙로 96-15 안성ACP</v>
-      </c>
-      <c r="I708" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J708" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K708">
-        <v>1</v>
-      </c>
-      <c r="L708" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M708" t="str">
-        <v>2026-08-03 23:45:59</v>
-      </c>
-      <c r="N708" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O708" s="1">
-        <v>0</v>
-      </c>
-      <c r="P708" t="str">
-        <v/>
-      </c>
-      <c r="Q708" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R708" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="str">
-        <v>T260803-00026</v>
-      </c>
-      <c r="B709" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C709" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D709" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E709" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F709">
-        <v>0</v>
-      </c>
-      <c r="G709" t="str">
-        <v>시흥ACP</v>
-      </c>
-      <c r="H709" t="str">
-        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
-      </c>
-      <c r="I709" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J709" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K709">
-        <v>1</v>
-      </c>
-      <c r="L709" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M709" t="str">
-        <v>2026-08-03 23:45:40</v>
-      </c>
-      <c r="N709" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O709" s="1">
-        <v>0</v>
-      </c>
-      <c r="P709" t="str">
-        <v/>
-      </c>
-      <c r="Q709" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R709" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="str">
-        <v>T260803-00025</v>
-      </c>
-      <c r="B710" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C710" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D710" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E710" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F710">
-        <v>2</v>
-      </c>
-      <c r="G710" t="str">
-        <v>속초ACP</v>
-      </c>
-      <c r="H710" t="str">
-        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
-      </c>
-      <c r="I710" t="str">
-        <v>2026-08-04 06:00</v>
-      </c>
-      <c r="J710" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K710">
-        <v>1</v>
-      </c>
-      <c r="L710" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M710" t="str">
-        <v>2026-08-03 23:45:13</v>
-      </c>
-      <c r="N710" s="1">
-        <v>330000</v>
-      </c>
-      <c r="O710" s="1">
-        <v>0</v>
-      </c>
-      <c r="P710" t="str">
-        <v/>
-      </c>
-      <c r="Q710" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R710" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="str">
-        <v>T260803-00024</v>
-      </c>
-      <c r="B711" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C711" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D711" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E711" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F711">
-        <v>0</v>
-      </c>
-      <c r="G711" t="str">
-        <v>서산ACP</v>
-      </c>
-      <c r="H711" t="str">
-        <v>충남 서산시 덕지천로 328-3 서산ACP</v>
-      </c>
-      <c r="I711" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J711" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K711">
-        <v>1</v>
-      </c>
-      <c r="L711" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M711" t="str">
-        <v>2026-08-03 23:44:40</v>
-      </c>
-      <c r="N711" s="1">
-        <v>130000</v>
-      </c>
-      <c r="O711" s="1">
-        <v>0</v>
-      </c>
-      <c r="P711" t="str">
-        <v/>
-      </c>
-      <c r="Q711" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R711" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="str">
-        <v>T260803-00023</v>
-      </c>
-      <c r="B712" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C712" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D712" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E712" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F712">
-        <v>0</v>
-      </c>
-      <c r="G712" t="str">
-        <v>부산ACP</v>
-      </c>
-      <c r="H712" t="str">
-        <v>부산 강서구 상덕로97번길 47 부산ACP</v>
-      </c>
-      <c r="I712" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J712" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K712">
-        <v>1</v>
-      </c>
-      <c r="L712" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M712" t="str">
-        <v>2026-08-03 23:44:17</v>
-      </c>
-      <c r="N712" s="1">
-        <v>450000</v>
-      </c>
-      <c r="O712" s="1">
-        <v>0</v>
-      </c>
-      <c r="P712" t="str">
-        <v/>
-      </c>
-      <c r="Q712" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R712" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="str">
-        <v>T260803-00022</v>
-      </c>
-      <c r="B713" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C713" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D713" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E713" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F713">
-        <v>0</v>
-      </c>
-      <c r="G713" t="str">
-        <v>대전중구ACP</v>
-      </c>
-      <c r="H713" t="str">
-        <v>대전 중구 보문산로77번길 8 대전중구ACP</v>
-      </c>
-      <c r="I713" t="str">
-        <v>2026-08-04 06:00</v>
-      </c>
-      <c r="J713" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K713">
-        <v>1</v>
-      </c>
-      <c r="L713" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M713" t="str">
-        <v>2026-08-03 23:43:56</v>
-      </c>
-      <c r="N713" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O713" s="1">
-        <v>0</v>
-      </c>
-      <c r="P713" t="str">
-        <v/>
-      </c>
-      <c r="Q713" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R713" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="str">
-        <v>T260803-00021</v>
-      </c>
-      <c r="B714" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C714" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D714" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E714" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F714">
-        <v>2</v>
-      </c>
-      <c r="G714" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H714" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I714" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J714" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K714">
-        <v>1</v>
-      </c>
-      <c r="L714" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M714" t="str">
-        <v>2026-08-03 23:43:37</v>
-      </c>
-      <c r="N714" s="1">
-        <v>320000</v>
-      </c>
-      <c r="O714" s="1">
-        <v>0</v>
-      </c>
-      <c r="P714" t="str">
-        <v/>
-      </c>
-      <c r="Q714" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R714" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="str">
-        <v>T260803-00020</v>
-      </c>
-      <c r="B715" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C715" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D715" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E715" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F715">
-        <v>0</v>
-      </c>
-      <c r="G715" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H715" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I715" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J715" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K715">
-        <v>1</v>
-      </c>
-      <c r="L715" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M715" t="str">
-        <v>2026-08-03 23:35:31</v>
-      </c>
-      <c r="N715" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O715" s="1">
-        <v>0</v>
-      </c>
-      <c r="P715" t="str">
-        <v/>
-      </c>
-      <c r="Q715" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R715" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="str">
-        <v>T260803-00019</v>
-      </c>
-      <c r="B716" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C716" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D716" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E716" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F716">
-        <v>0</v>
-      </c>
-      <c r="G716" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="H716" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="I716" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J716" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K716">
-        <v>1</v>
-      </c>
-      <c r="L716" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M716" t="str">
-        <v>2026-08-03 23:34:40</v>
-      </c>
-      <c r="N716" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O716" s="1">
-        <v>0</v>
-      </c>
-      <c r="P716" t="str">
-        <v/>
-      </c>
-      <c r="Q716" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R716" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="str">
-        <v>T260803-00018</v>
-      </c>
-      <c r="B717" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C717" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D717" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E717" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F717">
-        <v>0</v>
-      </c>
-      <c r="G717" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H717" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I717" t="str">
-        <v>2026-08-03 21:00</v>
-      </c>
-      <c r="J717" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K717">
-        <v>1</v>
-      </c>
-      <c r="L717" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M717" t="str">
-        <v>2026-08-03 23:33:48</v>
-      </c>
-      <c r="N717" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O717" s="1">
-        <v>0</v>
-      </c>
-      <c r="P717" t="str">
-        <v/>
-      </c>
-      <c r="Q717" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R717" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="str">
-        <v>T260803-00017</v>
-      </c>
-      <c r="B718" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C718" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D718" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E718" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F718">
-        <v>1</v>
-      </c>
-      <c r="G718" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H718" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I718" t="str">
-        <v>2026-08-03 22:00</v>
-      </c>
-      <c r="J718" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K718">
-        <v>1</v>
-      </c>
-      <c r="L718" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M718" t="str">
-        <v>2026-08-03 23:33:33</v>
-      </c>
-      <c r="N718" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O718" s="1">
-        <v>0</v>
-      </c>
-      <c r="P718" t="str">
-        <v/>
-      </c>
-      <c r="Q718" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R718" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="str">
-        <v>T260803-00016</v>
-      </c>
-      <c r="B719" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C719" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D719" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E719" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F719">
-        <v>1</v>
-      </c>
-      <c r="G719" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H719" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I719" t="str">
-        <v>2026-08-03 23:00</v>
-      </c>
-      <c r="J719" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K719">
-        <v>1</v>
-      </c>
-      <c r="L719" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M719" t="str">
-        <v>2026-08-03 23:33:14</v>
-      </c>
-      <c r="N719" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O719" s="1">
-        <v>0</v>
-      </c>
-      <c r="P719" t="str">
-        <v/>
-      </c>
-      <c r="Q719" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R719" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="str">
-        <v>T260803-00015</v>
-      </c>
-      <c r="B720" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C720" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D720" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E720" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F720">
-        <v>0</v>
-      </c>
-      <c r="G720" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="H720" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="I720" t="str">
-        <v>2026-08-03 22:00</v>
-      </c>
-      <c r="J720" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K720">
-        <v>1</v>
-      </c>
-      <c r="L720" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M720" t="str">
-        <v>2026-08-03 23:32:56</v>
-      </c>
-      <c r="N720" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O720" s="1">
-        <v>0</v>
-      </c>
-      <c r="P720" t="str">
-        <v/>
-      </c>
-      <c r="Q720" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R720" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="str">
-        <v>T260803-00014</v>
-      </c>
-      <c r="B721" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C721" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D721" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E721" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F721">
-        <v>0</v>
-      </c>
-      <c r="G721" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H721" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I721" t="str">
-        <v>2026-08-03 21:00</v>
-      </c>
-      <c r="J721" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K721">
-        <v>1</v>
-      </c>
-      <c r="L721" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M721" t="str">
-        <v>2026-08-03 23:32:42</v>
-      </c>
-      <c r="N721" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O721" s="1">
-        <v>0</v>
-      </c>
-      <c r="P721" t="str">
-        <v/>
-      </c>
-      <c r="Q721" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R721" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="str">
-        <v>T260803-00013</v>
-      </c>
-      <c r="B722" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C722" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D722" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E722" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F722">
-        <v>1</v>
-      </c>
-      <c r="G722" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H722" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I722" t="str">
-        <v>2026-08-03 22:00</v>
-      </c>
-      <c r="J722" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K722">
-        <v>1</v>
-      </c>
-      <c r="L722" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M722" t="str">
-        <v>2026-08-03 23:32:24</v>
-      </c>
-      <c r="N722" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O722" s="1">
-        <v>0</v>
-      </c>
-      <c r="P722" t="str">
-        <v/>
-      </c>
-      <c r="Q722" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R722" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="str">
-        <v>T260803-00012</v>
-      </c>
-      <c r="B723" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C723" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D723" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E723" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F723">
-        <v>0</v>
-      </c>
-      <c r="G723" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H723" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I723" t="str">
-        <v>2026-08-03 23:00</v>
-      </c>
-      <c r="J723" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K723">
-        <v>1</v>
-      </c>
-      <c r="L723" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M723" t="str">
-        <v>2026-08-03 23:32:00</v>
-      </c>
-      <c r="N723" s="1">
-        <v>490000</v>
-      </c>
-      <c r="O723" s="1">
-        <v>0</v>
-      </c>
-      <c r="P723" t="str">
-        <v/>
-      </c>
-      <c r="Q723" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R723" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="str">
-        <v>T260803-00011</v>
-      </c>
-      <c r="B724" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C724" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D724" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E724" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F724">
-        <v>0</v>
-      </c>
-      <c r="G724" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H724" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I724" t="str">
-        <v>2026-08-03 21:00</v>
-      </c>
-      <c r="J724" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K724">
-        <v>1</v>
-      </c>
-      <c r="L724" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M724" t="str">
-        <v>2026-08-03 23:31:43</v>
-      </c>
-      <c r="N724" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O724" s="1">
-        <v>0</v>
-      </c>
-      <c r="P724" t="str">
-        <v/>
-      </c>
-      <c r="Q724" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R724" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="str">
-        <v>T260803-00010</v>
-      </c>
-      <c r="B725" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C725" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D725" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E725" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F725">
-        <v>1</v>
-      </c>
-      <c r="G725" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H725" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I725" t="str">
-        <v>2026-08-03 22:00</v>
-      </c>
-      <c r="J725" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K725">
-        <v>1</v>
-      </c>
-      <c r="L725" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M725" t="str">
-        <v>2026-08-03 23:31:28</v>
-      </c>
-      <c r="N725" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O725" s="1">
-        <v>0</v>
-      </c>
-      <c r="P725" t="str">
-        <v/>
-      </c>
-      <c r="Q725" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R725" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="str">
-        <v>T260803-00009</v>
-      </c>
-      <c r="B726" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C726" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D726" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E726" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F726">
-        <v>0</v>
-      </c>
-      <c r="G726" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H726" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I726" t="str">
-        <v>2026-08-03 23:00</v>
-      </c>
-      <c r="J726" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K726">
-        <v>1</v>
-      </c>
-      <c r="L726" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M726" t="str">
-        <v>2026-08-03 23:31:08</v>
-      </c>
-      <c r="N726" s="1">
-        <v>420000</v>
-      </c>
-      <c r="O726" s="1">
-        <v>0</v>
-      </c>
-      <c r="P726" t="str">
-        <v/>
-      </c>
-      <c r="Q726" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R726" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="str">
-        <v>T260803-00008</v>
-      </c>
-      <c r="B727" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C727" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D727" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E727" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F727">
-        <v>1</v>
-      </c>
-      <c r="G727" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H727" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="I727" t="str">
-        <v>2026-08-03 23:00</v>
-      </c>
-      <c r="J727" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K727">
-        <v>1</v>
-      </c>
-      <c r="L727" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M727" t="str">
-        <v>2026-08-03 23:30:52</v>
-      </c>
-      <c r="N727" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O727" s="1">
-        <v>0</v>
-      </c>
-      <c r="P727" t="str">
-        <v/>
-      </c>
-      <c r="Q727" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R727" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="str">
-        <v>T260803-00007</v>
-      </c>
-      <c r="B728" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C728" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D728" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E728" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F728">
-        <v>0</v>
-      </c>
-      <c r="G728" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H728" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I728" t="str">
-        <v>2026-08-03 21:00</v>
-      </c>
-      <c r="J728" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K728">
-        <v>1</v>
-      </c>
-      <c r="L728" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M728" t="str">
-        <v>2026-08-03 22:51:56</v>
-      </c>
-      <c r="N728" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O728" s="1">
-        <v>0</v>
-      </c>
-      <c r="P728" t="str">
-        <v/>
-      </c>
-      <c r="Q728" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R728" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="str">
-        <v>T260803-00006</v>
-      </c>
-      <c r="B729" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C729" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D729" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E729" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F729">
-        <v>1</v>
-      </c>
-      <c r="G729" t="str">
-        <v>강릉FDC</v>
-      </c>
-      <c r="H729" t="str">
-        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
-      </c>
-      <c r="I729" t="str">
-        <v>2026-08-03 23:00</v>
-      </c>
-      <c r="J729" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K729">
-        <v>1</v>
-      </c>
-      <c r="L729" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M729" t="str">
-        <v>2026-08-03 22:51:37</v>
-      </c>
-      <c r="N729" s="1">
-        <v>310000</v>
-      </c>
-      <c r="O729" s="1">
-        <v>0</v>
-      </c>
-      <c r="P729" t="str">
-        <v/>
-      </c>
-      <c r="Q729" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R729" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="str">
-        <v>T260803-00005</v>
-      </c>
-      <c r="B730" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C730" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D730" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E730" t="str">
-        <v>2026-08-03 17:50</v>
-      </c>
-      <c r="F730">
-        <v>0</v>
-      </c>
-      <c r="G730" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H730" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I730" t="str">
-        <v>2026-08-03 18:50</v>
-      </c>
-      <c r="J730" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K730">
-        <v>1</v>
-      </c>
-      <c r="L730" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M730" t="str">
-        <v>2026-08-03 22:47:04</v>
-      </c>
-      <c r="N730" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O730" s="1">
-        <v>0</v>
-      </c>
-      <c r="P730" t="str">
-        <v/>
-      </c>
-      <c r="Q730" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R730" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="str">
-        <v>T260803-00004</v>
-      </c>
-      <c r="B731" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C731" t="str">
-        <v>샤오미</v>
-      </c>
-      <c r="D731" t="str">
-        <v>경기 이천시 대월면 부필리 309 샤오미</v>
-      </c>
-      <c r="E731" t="str">
-        <v>2026-08-03 13:50</v>
-      </c>
-      <c r="F731">
-        <v>0</v>
-      </c>
-      <c r="G731" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H731" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I731" t="str">
-        <v>2026-08-03 14:50</v>
-      </c>
-      <c r="J731" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K731">
-        <v>1</v>
-      </c>
-      <c r="L731" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M731" t="str">
-        <v>2026-08-03 22:46:33</v>
-      </c>
-      <c r="N731" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O731" s="1">
-        <v>0</v>
-      </c>
-      <c r="P731" t="str">
-        <v>샤오미 외주사입고(11대)</v>
-      </c>
-      <c r="Q731" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R731" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="str">
-        <v>T260803-00003</v>
-      </c>
-      <c r="B732" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C732" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D732" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E732" t="str">
-        <v>2026-08-03 14:50</v>
-      </c>
-      <c r="F732">
-        <v>0</v>
-      </c>
-      <c r="G732" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H732" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I732" t="str">
-        <v>2026-08-03 15:50</v>
-      </c>
-      <c r="J732" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K732">
-        <v>1</v>
-      </c>
-      <c r="L732" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M732" t="str">
-        <v>2026-08-03 22:45:46</v>
-      </c>
-      <c r="N732" s="1">
-        <v>70000</v>
-      </c>
-      <c r="O732" s="1">
-        <v>0</v>
-      </c>
-      <c r="P732" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="Q732" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R732" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="str">
-        <v>T260803-00002</v>
-      </c>
-      <c r="B733" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C733" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D733" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E733" t="str">
-        <v>2026-08-03 10:00</v>
-      </c>
-      <c r="F733">
-        <v>0</v>
-      </c>
-      <c r="G733" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H733" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I733" t="str">
-        <v>2026-08-03 13:50</v>
-      </c>
-      <c r="J733" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K733">
-        <v>1</v>
-      </c>
-      <c r="L733" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M733" t="str">
-        <v>2026-08-03 22:45:01</v>
-      </c>
-      <c r="N733" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O733" s="1">
-        <v>0</v>
-      </c>
-      <c r="P733" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q733" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R733" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="str">
-        <v>T260803-00001</v>
-      </c>
-      <c r="B734" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C734" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D734" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E734" t="str">
-        <v>2026-08-03 16:30</v>
-      </c>
-      <c r="F734">
-        <v>0</v>
-      </c>
-      <c r="G734" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H734" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I734" t="str">
-        <v>2026-08-03 18:00</v>
-      </c>
-      <c r="J734" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K734">
-        <v>1</v>
-      </c>
-      <c r="L734" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="M734" t="str">
-        <v>2026-08-03 15:39:18</v>
-      </c>
-      <c r="N734" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O734" s="1">
-        <v>0</v>
-      </c>
-      <c r="P734" t="str">
-        <v/>
-      </c>
-      <c r="Q734" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R734" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R734"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R678"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R678"/>
+  <dimension ref="A1:R734"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38347,9 +38347,3145 @@
         <v>(주)위니온로지스</v>
       </c>
     </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>T260804-00025</v>
+      </c>
+      <c r="B679" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C679" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D679" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E679" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F679">
+        <v>0</v>
+      </c>
+      <c r="G679" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H679" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I679" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J679" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K679">
+        <v>1</v>
+      </c>
+      <c r="L679" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M679" t="str">
+        <v>2026-08-04 20:32:35</v>
+      </c>
+      <c r="N679" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O679" s="1">
+        <v>0</v>
+      </c>
+      <c r="P679" t="str">
+        <v/>
+      </c>
+      <c r="Q679" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R679" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>T260804-00024</v>
+      </c>
+      <c r="B680" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C680" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D680" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E680" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F680">
+        <v>0</v>
+      </c>
+      <c r="G680" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H680" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I680" t="str">
+        <v>2026-08-05 08:00</v>
+      </c>
+      <c r="J680" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K680">
+        <v>1</v>
+      </c>
+      <c r="L680" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M680" t="str">
+        <v>2026-08-04 20:32:12</v>
+      </c>
+      <c r="N680" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O680" s="1">
+        <v>0</v>
+      </c>
+      <c r="P680" t="str">
+        <v/>
+      </c>
+      <c r="Q680" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R680" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>T260804-00023</v>
+      </c>
+      <c r="B681" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C681" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D681" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E681" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F681">
+        <v>1</v>
+      </c>
+      <c r="G681" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H681" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I681" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J681" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K681">
+        <v>1</v>
+      </c>
+      <c r="L681" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M681" t="str">
+        <v>2026-08-04 20:31:26</v>
+      </c>
+      <c r="N681" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O681" s="1">
+        <v>0</v>
+      </c>
+      <c r="P681" t="str">
+        <v/>
+      </c>
+      <c r="Q681" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R681" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>T260804-00022</v>
+      </c>
+      <c r="B682" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C682" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D682" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E682" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F682">
+        <v>0</v>
+      </c>
+      <c r="G682" t="str">
+        <v>안성ACP</v>
+      </c>
+      <c r="H682" t="str">
+        <v>경기 안성시 대덕면 중앙로 96-15 안성ACP</v>
+      </c>
+      <c r="I682" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J682" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K682">
+        <v>1</v>
+      </c>
+      <c r="L682" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M682" t="str">
+        <v>2026-08-04 20:30:56</v>
+      </c>
+      <c r="N682" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O682" s="1">
+        <v>0</v>
+      </c>
+      <c r="P682" t="str">
+        <v/>
+      </c>
+      <c r="Q682" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R682" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>T260804-00021</v>
+      </c>
+      <c r="B683" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C683" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D683" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E683" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F683">
+        <v>0</v>
+      </c>
+      <c r="G683" t="str">
+        <v>시흥ACP</v>
+      </c>
+      <c r="H683" t="str">
+        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
+      </c>
+      <c r="I683" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J683" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K683">
+        <v>1</v>
+      </c>
+      <c r="L683" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M683" t="str">
+        <v>2026-08-04 20:30:28</v>
+      </c>
+      <c r="N683" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O683" s="1">
+        <v>0</v>
+      </c>
+      <c r="P683" t="str">
+        <v/>
+      </c>
+      <c r="Q683" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R683" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>T260804-00020</v>
+      </c>
+      <c r="B684" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C684" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D684" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E684" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F684">
+        <v>0</v>
+      </c>
+      <c r="G684" t="str">
+        <v>부산ACP</v>
+      </c>
+      <c r="H684" t="str">
+        <v>부산 강서구 상덕로97번길 47 부산ACP</v>
+      </c>
+      <c r="I684" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J684" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K684">
+        <v>1</v>
+      </c>
+      <c r="L684" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M684" t="str">
+        <v>2026-08-04 20:29:48</v>
+      </c>
+      <c r="N684" s="1">
+        <v>450000</v>
+      </c>
+      <c r="O684" s="1">
+        <v>0</v>
+      </c>
+      <c r="P684" t="str">
+        <v/>
+      </c>
+      <c r="Q684" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R684" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>T260804-00019</v>
+      </c>
+      <c r="B685" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C685" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D685" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E685" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F685">
+        <v>0</v>
+      </c>
+      <c r="G685" t="str">
+        <v>대전중구ACP</v>
+      </c>
+      <c r="H685" t="str">
+        <v>대전 중구 보문산로77번길 8 대전중구ACP</v>
+      </c>
+      <c r="I685" t="str">
+        <v>2026-08-05 06:00</v>
+      </c>
+      <c r="J685" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K685">
+        <v>1</v>
+      </c>
+      <c r="L685" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M685" t="str">
+        <v>2026-08-04 20:14:33</v>
+      </c>
+      <c r="N685" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O685" s="1">
+        <v>0</v>
+      </c>
+      <c r="P685" t="str">
+        <v/>
+      </c>
+      <c r="Q685" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R685" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>T260804-00018</v>
+      </c>
+      <c r="B686" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C686" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D686" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E686" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F686">
+        <v>0</v>
+      </c>
+      <c r="G686" t="str">
+        <v>대전대덕ACP</v>
+      </c>
+      <c r="H686" t="str">
+        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
+      </c>
+      <c r="I686" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J686" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K686">
+        <v>1</v>
+      </c>
+      <c r="L686" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M686" t="str">
+        <v>2026-08-04 20:14:11</v>
+      </c>
+      <c r="N686" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O686" s="1">
+        <v>0</v>
+      </c>
+      <c r="P686" t="str">
+        <v/>
+      </c>
+      <c r="Q686" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R686" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>T260804-00017</v>
+      </c>
+      <c r="B687" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C687" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D687" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E687" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F687">
+        <v>1</v>
+      </c>
+      <c r="G687" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H687" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I687" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J687" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K687">
+        <v>1</v>
+      </c>
+      <c r="L687" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M687" t="str">
+        <v>2026-08-04 20:13:47</v>
+      </c>
+      <c r="N687" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O687" s="1">
+        <v>0</v>
+      </c>
+      <c r="P687" t="str">
+        <v/>
+      </c>
+      <c r="Q687" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R687" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>T260804-00016</v>
+      </c>
+      <c r="B688" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C688" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D688" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E688" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F688">
+        <v>0</v>
+      </c>
+      <c r="G688" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H688" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I688" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J688" t="str">
+        <v>2.5톤 카고</v>
+      </c>
+      <c r="K688">
+        <v>1</v>
+      </c>
+      <c r="L688" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M688" t="str">
+        <v>2026-08-04 20:13:22</v>
+      </c>
+      <c r="N688" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O688" s="1">
+        <v>0</v>
+      </c>
+      <c r="P688" t="str">
+        <v/>
+      </c>
+      <c r="Q688" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R688" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>T260804-00015</v>
+      </c>
+      <c r="B689" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C689" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D689" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E689" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F689">
+        <v>0</v>
+      </c>
+      <c r="G689" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H689" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I689" t="str">
+        <v>2026-08-04 21:00</v>
+      </c>
+      <c r="J689" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K689">
+        <v>1</v>
+      </c>
+      <c r="L689" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M689" t="str">
+        <v>2026-08-04 20:11:31</v>
+      </c>
+      <c r="N689" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O689" s="1">
+        <v>0</v>
+      </c>
+      <c r="P689" t="str">
+        <v/>
+      </c>
+      <c r="Q689" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R689" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>T260804-00014</v>
+      </c>
+      <c r="B690" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C690" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D690" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E690" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F690">
+        <v>1</v>
+      </c>
+      <c r="G690" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H690" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I690" t="str">
+        <v>2026-08-04 22:00</v>
+      </c>
+      <c r="J690" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K690">
+        <v>1</v>
+      </c>
+      <c r="L690" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M690" t="str">
+        <v>2026-08-04 20:11:15</v>
+      </c>
+      <c r="N690" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O690" s="1">
+        <v>0</v>
+      </c>
+      <c r="P690" t="str">
+        <v/>
+      </c>
+      <c r="Q690" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R690" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>T260804-00013</v>
+      </c>
+      <c r="B691" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C691" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D691" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E691" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F691">
+        <v>0</v>
+      </c>
+      <c r="G691" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H691" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I691" t="str">
+        <v>2026-08-04 23:00</v>
+      </c>
+      <c r="J691" t="str">
+        <v>5톤 카고</v>
+      </c>
+      <c r="K691">
+        <v>1</v>
+      </c>
+      <c r="L691" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M691" t="str">
+        <v>2026-08-04 20:10:56</v>
+      </c>
+      <c r="N691" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O691" s="1">
+        <v>0</v>
+      </c>
+      <c r="P691" t="str">
+        <v/>
+      </c>
+      <c r="Q691" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R691" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>T260804-00012</v>
+      </c>
+      <c r="B692" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C692" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D692" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E692" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F692">
+        <v>0</v>
+      </c>
+      <c r="G692" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H692" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I692" t="str">
+        <v>2026-08-04 21:00</v>
+      </c>
+      <c r="J692" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K692">
+        <v>1</v>
+      </c>
+      <c r="L692" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M692" t="str">
+        <v>2026-08-04 20:10:40</v>
+      </c>
+      <c r="N692" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O692" s="1">
+        <v>0</v>
+      </c>
+      <c r="P692" t="str">
+        <v/>
+      </c>
+      <c r="Q692" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R692" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
+        <v>T260804-00011</v>
+      </c>
+      <c r="B693" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C693" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D693" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E693" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F693">
+        <v>1</v>
+      </c>
+      <c r="G693" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H693" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I693" t="str">
+        <v>2026-08-04 22:00</v>
+      </c>
+      <c r="J693" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K693">
+        <v>1</v>
+      </c>
+      <c r="L693" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M693" t="str">
+        <v>2026-08-04 20:10:24</v>
+      </c>
+      <c r="N693" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O693" s="1">
+        <v>0</v>
+      </c>
+      <c r="P693" t="str">
+        <v/>
+      </c>
+      <c r="Q693" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R693" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>T260804-00010</v>
+      </c>
+      <c r="B694" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C694" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D694" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E694" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F694">
+        <v>1</v>
+      </c>
+      <c r="G694" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H694" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I694" t="str">
+        <v>2026-08-04 23:00</v>
+      </c>
+      <c r="J694" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K694">
+        <v>1</v>
+      </c>
+      <c r="L694" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M694" t="str">
+        <v>2026-08-04 20:07:49</v>
+      </c>
+      <c r="N694" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O694" s="1">
+        <v>0</v>
+      </c>
+      <c r="P694" t="str">
+        <v/>
+      </c>
+      <c r="Q694" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R694" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>T260804-00009</v>
+      </c>
+      <c r="B695" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C695" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D695" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E695" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F695">
+        <v>1</v>
+      </c>
+      <c r="G695" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H695" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I695" t="str">
+        <v>2026-08-04 22:00</v>
+      </c>
+      <c r="J695" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K695">
+        <v>1</v>
+      </c>
+      <c r="L695" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M695" t="str">
+        <v>2026-08-04 20:07:16</v>
+      </c>
+      <c r="N695" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O695" s="1">
+        <v>0</v>
+      </c>
+      <c r="P695" t="str">
+        <v/>
+      </c>
+      <c r="Q695" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R695" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>T260804-00008</v>
+      </c>
+      <c r="B696" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C696" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D696" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E696" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F696">
+        <v>1</v>
+      </c>
+      <c r="G696" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H696" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I696" t="str">
+        <v>2026-08-04 23:00</v>
+      </c>
+      <c r="J696" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K696">
+        <v>1</v>
+      </c>
+      <c r="L696" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M696" t="str">
+        <v>2026-08-04 20:06:56</v>
+      </c>
+      <c r="N696" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O696" s="1">
+        <v>0</v>
+      </c>
+      <c r="P696" t="str">
+        <v/>
+      </c>
+      <c r="Q696" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R696" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>T260804-00007</v>
+      </c>
+      <c r="B697" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C697" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D697" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E697" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F697">
+        <v>0</v>
+      </c>
+      <c r="G697" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H697" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I697" t="str">
+        <v>2026-08-04 21:00</v>
+      </c>
+      <c r="J697" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K697">
+        <v>1</v>
+      </c>
+      <c r="L697" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M697" t="str">
+        <v>2026-08-04 20:06:32</v>
+      </c>
+      <c r="N697" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O697" s="1">
+        <v>0</v>
+      </c>
+      <c r="P697" t="str">
+        <v/>
+      </c>
+      <c r="Q697" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R697" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>T260804-00006</v>
+      </c>
+      <c r="B698" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C698" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D698" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E698" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F698">
+        <v>0</v>
+      </c>
+      <c r="G698" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H698" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I698" t="str">
+        <v>2026-08-04 21:00</v>
+      </c>
+      <c r="J698" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K698">
+        <v>1</v>
+      </c>
+      <c r="L698" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M698" t="str">
+        <v>2026-08-04 20:06:08</v>
+      </c>
+      <c r="N698" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O698" s="1">
+        <v>0</v>
+      </c>
+      <c r="P698" t="str">
+        <v/>
+      </c>
+      <c r="Q698" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R698" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>T260804-00005</v>
+      </c>
+      <c r="B699" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C699" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D699" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E699" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F699">
+        <v>1</v>
+      </c>
+      <c r="G699" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H699" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="I699" t="str">
+        <v>2026-08-04 23:00</v>
+      </c>
+      <c r="J699" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K699">
+        <v>1</v>
+      </c>
+      <c r="L699" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M699" t="str">
+        <v>2026-08-04 20:05:49</v>
+      </c>
+      <c r="N699" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O699" s="1">
+        <v>0</v>
+      </c>
+      <c r="P699" t="str">
+        <v/>
+      </c>
+      <c r="Q699" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R699" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
+        <v>T260804-00004</v>
+      </c>
+      <c r="B700" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C700" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D700" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E700" t="str">
+        <v>2026-08-04 17:00</v>
+      </c>
+      <c r="F700">
+        <v>0</v>
+      </c>
+      <c r="G700" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H700" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I700" t="str">
+        <v>2026-08-04 18:00</v>
+      </c>
+      <c r="J700" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K700">
+        <v>1</v>
+      </c>
+      <c r="L700" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M700" t="str">
+        <v>2026-08-04 20:00:36</v>
+      </c>
+      <c r="N700" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O700" s="1">
+        <v>0</v>
+      </c>
+      <c r="P700" t="str">
+        <v/>
+      </c>
+      <c r="Q700" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R700" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>T260804-00003</v>
+      </c>
+      <c r="B701" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C701" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D701" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E701" t="str">
+        <v>2026-08-04 15:00</v>
+      </c>
+      <c r="F701">
+        <v>0</v>
+      </c>
+      <c r="G701" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H701" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I701" t="str">
+        <v>2026-08-04 16:00</v>
+      </c>
+      <c r="J701" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K701">
+        <v>1</v>
+      </c>
+      <c r="L701" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M701" t="str">
+        <v>2026-08-04 20:00:02</v>
+      </c>
+      <c r="N701" s="1">
+        <v>70000</v>
+      </c>
+      <c r="O701" s="1">
+        <v>0</v>
+      </c>
+      <c r="P701" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="Q701" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R701" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>T260804-00002</v>
+      </c>
+      <c r="B702" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C702" t="str">
+        <v>샤오미</v>
+      </c>
+      <c r="D702" t="str">
+        <v>경기 이천시 대월면 부필리 309 샤오미</v>
+      </c>
+      <c r="E702" t="str">
+        <v>2026-08-04 14:00</v>
+      </c>
+      <c r="F702">
+        <v>0</v>
+      </c>
+      <c r="G702" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H702" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I702" t="str">
+        <v>2026-08-04 15:00</v>
+      </c>
+      <c r="J702" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K702">
+        <v>1</v>
+      </c>
+      <c r="L702" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M702" t="str">
+        <v>2026-08-04 19:59:20</v>
+      </c>
+      <c r="N702" s="1">
+        <v>80000</v>
+      </c>
+      <c r="O702" s="1">
+        <v>0</v>
+      </c>
+      <c r="P702" t="str">
+        <v>거래처비용청구(3대)</v>
+      </c>
+      <c r="Q702" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R702" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>T260804-00001</v>
+      </c>
+      <c r="B703" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C703" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D703" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E703" t="str">
+        <v>2026-08-04 16:30</v>
+      </c>
+      <c r="F703">
+        <v>0</v>
+      </c>
+      <c r="G703" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H703" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I703" t="str">
+        <v>2026-08-04 18:00</v>
+      </c>
+      <c r="J703" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K703">
+        <v>1</v>
+      </c>
+      <c r="L703" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="M703" t="str">
+        <v>2026-08-04 15:46:27</v>
+      </c>
+      <c r="N703" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O703" s="1">
+        <v>0</v>
+      </c>
+      <c r="P703" t="str">
+        <v/>
+      </c>
+      <c r="Q703" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R703" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>T260803-00031</v>
+      </c>
+      <c r="B704" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C704" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D704" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E704" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F704">
+        <v>0</v>
+      </c>
+      <c r="G704" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H704" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I704" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J704" t="str">
+        <v>2.5톤 카고</v>
+      </c>
+      <c r="K704">
+        <v>1</v>
+      </c>
+      <c r="L704" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M704" t="str">
+        <v>2026-08-03 23:48:09</v>
+      </c>
+      <c r="N704" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O704" s="1">
+        <v>0</v>
+      </c>
+      <c r="P704" t="str">
+        <v/>
+      </c>
+      <c r="Q704" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R704" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
+        <v>T260803-00030</v>
+      </c>
+      <c r="B705" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C705" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D705" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E705" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F705">
+        <v>0</v>
+      </c>
+      <c r="G705" t="str">
+        <v>춘천ACP</v>
+      </c>
+      <c r="H705" t="str">
+        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
+      </c>
+      <c r="I705" t="str">
+        <v>2026-08-04 08:00</v>
+      </c>
+      <c r="J705" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K705">
+        <v>1</v>
+      </c>
+      <c r="L705" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M705" t="str">
+        <v>2026-08-03 23:47:48</v>
+      </c>
+      <c r="N705" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O705" s="1">
+        <v>0</v>
+      </c>
+      <c r="P705" t="str">
+        <v/>
+      </c>
+      <c r="Q705" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R705" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
+        <v>T260803-00029</v>
+      </c>
+      <c r="B706" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C706" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D706" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E706" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F706">
+        <v>0</v>
+      </c>
+      <c r="G706" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H706" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I706" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J706" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K706">
+        <v>1</v>
+      </c>
+      <c r="L706" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M706" t="str">
+        <v>2026-08-03 23:46:49</v>
+      </c>
+      <c r="N706" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O706" s="1">
+        <v>0</v>
+      </c>
+      <c r="P706" t="str">
+        <v/>
+      </c>
+      <c r="Q706" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R706" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
+        <v>T260803-00028</v>
+      </c>
+      <c r="B707" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C707" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D707" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E707" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F707">
+        <v>1</v>
+      </c>
+      <c r="G707" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H707" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I707" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J707" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K707">
+        <v>1</v>
+      </c>
+      <c r="L707" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M707" t="str">
+        <v>2026-08-03 23:46:26</v>
+      </c>
+      <c r="N707" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O707" s="1">
+        <v>0</v>
+      </c>
+      <c r="P707" t="str">
+        <v/>
+      </c>
+      <c r="Q707" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R707" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="str">
+        <v>T260803-00027</v>
+      </c>
+      <c r="B708" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C708" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D708" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E708" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F708">
+        <v>0</v>
+      </c>
+      <c r="G708" t="str">
+        <v>안성ACP</v>
+      </c>
+      <c r="H708" t="str">
+        <v>경기 안성시 대덕면 중앙로 96-15 안성ACP</v>
+      </c>
+      <c r="I708" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J708" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K708">
+        <v>1</v>
+      </c>
+      <c r="L708" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M708" t="str">
+        <v>2026-08-03 23:45:59</v>
+      </c>
+      <c r="N708" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O708" s="1">
+        <v>0</v>
+      </c>
+      <c r="P708" t="str">
+        <v/>
+      </c>
+      <c r="Q708" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R708" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="str">
+        <v>T260803-00026</v>
+      </c>
+      <c r="B709" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C709" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D709" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E709" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F709">
+        <v>0</v>
+      </c>
+      <c r="G709" t="str">
+        <v>시흥ACP</v>
+      </c>
+      <c r="H709" t="str">
+        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
+      </c>
+      <c r="I709" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J709" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K709">
+        <v>1</v>
+      </c>
+      <c r="L709" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M709" t="str">
+        <v>2026-08-03 23:45:40</v>
+      </c>
+      <c r="N709" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O709" s="1">
+        <v>0</v>
+      </c>
+      <c r="P709" t="str">
+        <v/>
+      </c>
+      <c r="Q709" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R709" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="str">
+        <v>T260803-00025</v>
+      </c>
+      <c r="B710" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C710" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D710" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E710" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F710">
+        <v>2</v>
+      </c>
+      <c r="G710" t="str">
+        <v>속초ACP</v>
+      </c>
+      <c r="H710" t="str">
+        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
+      </c>
+      <c r="I710" t="str">
+        <v>2026-08-04 06:00</v>
+      </c>
+      <c r="J710" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K710">
+        <v>1</v>
+      </c>
+      <c r="L710" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M710" t="str">
+        <v>2026-08-03 23:45:13</v>
+      </c>
+      <c r="N710" s="1">
+        <v>330000</v>
+      </c>
+      <c r="O710" s="1">
+        <v>0</v>
+      </c>
+      <c r="P710" t="str">
+        <v/>
+      </c>
+      <c r="Q710" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R710" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="str">
+        <v>T260803-00024</v>
+      </c>
+      <c r="B711" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C711" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D711" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E711" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F711">
+        <v>0</v>
+      </c>
+      <c r="G711" t="str">
+        <v>서산ACP</v>
+      </c>
+      <c r="H711" t="str">
+        <v>충남 서산시 덕지천로 328-3 서산ACP</v>
+      </c>
+      <c r="I711" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J711" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K711">
+        <v>1</v>
+      </c>
+      <c r="L711" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M711" t="str">
+        <v>2026-08-03 23:44:40</v>
+      </c>
+      <c r="N711" s="1">
+        <v>130000</v>
+      </c>
+      <c r="O711" s="1">
+        <v>0</v>
+      </c>
+      <c r="P711" t="str">
+        <v/>
+      </c>
+      <c r="Q711" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R711" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="str">
+        <v>T260803-00023</v>
+      </c>
+      <c r="B712" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C712" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D712" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E712" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F712">
+        <v>0</v>
+      </c>
+      <c r="G712" t="str">
+        <v>부산ACP</v>
+      </c>
+      <c r="H712" t="str">
+        <v>부산 강서구 상덕로97번길 47 부산ACP</v>
+      </c>
+      <c r="I712" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J712" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K712">
+        <v>1</v>
+      </c>
+      <c r="L712" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M712" t="str">
+        <v>2026-08-03 23:44:17</v>
+      </c>
+      <c r="N712" s="1">
+        <v>450000</v>
+      </c>
+      <c r="O712" s="1">
+        <v>0</v>
+      </c>
+      <c r="P712" t="str">
+        <v/>
+      </c>
+      <c r="Q712" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R712" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="str">
+        <v>T260803-00022</v>
+      </c>
+      <c r="B713" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C713" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D713" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E713" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F713">
+        <v>0</v>
+      </c>
+      <c r="G713" t="str">
+        <v>대전중구ACP</v>
+      </c>
+      <c r="H713" t="str">
+        <v>대전 중구 보문산로77번길 8 대전중구ACP</v>
+      </c>
+      <c r="I713" t="str">
+        <v>2026-08-04 06:00</v>
+      </c>
+      <c r="J713" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K713">
+        <v>1</v>
+      </c>
+      <c r="L713" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M713" t="str">
+        <v>2026-08-03 23:43:56</v>
+      </c>
+      <c r="N713" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O713" s="1">
+        <v>0</v>
+      </c>
+      <c r="P713" t="str">
+        <v/>
+      </c>
+      <c r="Q713" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R713" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="str">
+        <v>T260803-00021</v>
+      </c>
+      <c r="B714" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C714" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D714" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E714" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F714">
+        <v>2</v>
+      </c>
+      <c r="G714" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H714" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I714" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J714" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K714">
+        <v>1</v>
+      </c>
+      <c r="L714" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M714" t="str">
+        <v>2026-08-03 23:43:37</v>
+      </c>
+      <c r="N714" s="1">
+        <v>320000</v>
+      </c>
+      <c r="O714" s="1">
+        <v>0</v>
+      </c>
+      <c r="P714" t="str">
+        <v/>
+      </c>
+      <c r="Q714" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R714" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="str">
+        <v>T260803-00020</v>
+      </c>
+      <c r="B715" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C715" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D715" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E715" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F715">
+        <v>0</v>
+      </c>
+      <c r="G715" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H715" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I715" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J715" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K715">
+        <v>1</v>
+      </c>
+      <c r="L715" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M715" t="str">
+        <v>2026-08-03 23:35:31</v>
+      </c>
+      <c r="N715" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O715" s="1">
+        <v>0</v>
+      </c>
+      <c r="P715" t="str">
+        <v/>
+      </c>
+      <c r="Q715" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R715" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="str">
+        <v>T260803-00019</v>
+      </c>
+      <c r="B716" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C716" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D716" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E716" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F716">
+        <v>0</v>
+      </c>
+      <c r="G716" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H716" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I716" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J716" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K716">
+        <v>1</v>
+      </c>
+      <c r="L716" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M716" t="str">
+        <v>2026-08-03 23:34:40</v>
+      </c>
+      <c r="N716" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O716" s="1">
+        <v>0</v>
+      </c>
+      <c r="P716" t="str">
+        <v/>
+      </c>
+      <c r="Q716" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R716" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="str">
+        <v>T260803-00018</v>
+      </c>
+      <c r="B717" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C717" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D717" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E717" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F717">
+        <v>0</v>
+      </c>
+      <c r="G717" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H717" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I717" t="str">
+        <v>2026-08-03 21:00</v>
+      </c>
+      <c r="J717" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K717">
+        <v>1</v>
+      </c>
+      <c r="L717" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M717" t="str">
+        <v>2026-08-03 23:33:48</v>
+      </c>
+      <c r="N717" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O717" s="1">
+        <v>0</v>
+      </c>
+      <c r="P717" t="str">
+        <v/>
+      </c>
+      <c r="Q717" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R717" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="str">
+        <v>T260803-00017</v>
+      </c>
+      <c r="B718" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C718" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D718" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E718" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F718">
+        <v>1</v>
+      </c>
+      <c r="G718" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H718" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I718" t="str">
+        <v>2026-08-03 22:00</v>
+      </c>
+      <c r="J718" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K718">
+        <v>1</v>
+      </c>
+      <c r="L718" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M718" t="str">
+        <v>2026-08-03 23:33:33</v>
+      </c>
+      <c r="N718" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O718" s="1">
+        <v>0</v>
+      </c>
+      <c r="P718" t="str">
+        <v/>
+      </c>
+      <c r="Q718" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R718" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="str">
+        <v>T260803-00016</v>
+      </c>
+      <c r="B719" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C719" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D719" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E719" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F719">
+        <v>1</v>
+      </c>
+      <c r="G719" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H719" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I719" t="str">
+        <v>2026-08-03 23:00</v>
+      </c>
+      <c r="J719" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K719">
+        <v>1</v>
+      </c>
+      <c r="L719" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M719" t="str">
+        <v>2026-08-03 23:33:14</v>
+      </c>
+      <c r="N719" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O719" s="1">
+        <v>0</v>
+      </c>
+      <c r="P719" t="str">
+        <v/>
+      </c>
+      <c r="Q719" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R719" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="str">
+        <v>T260803-00015</v>
+      </c>
+      <c r="B720" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C720" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D720" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E720" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F720">
+        <v>0</v>
+      </c>
+      <c r="G720" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H720" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I720" t="str">
+        <v>2026-08-03 22:00</v>
+      </c>
+      <c r="J720" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K720">
+        <v>1</v>
+      </c>
+      <c r="L720" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M720" t="str">
+        <v>2026-08-03 23:32:56</v>
+      </c>
+      <c r="N720" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O720" s="1">
+        <v>0</v>
+      </c>
+      <c r="P720" t="str">
+        <v/>
+      </c>
+      <c r="Q720" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R720" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="str">
+        <v>T260803-00014</v>
+      </c>
+      <c r="B721" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C721" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D721" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E721" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F721">
+        <v>0</v>
+      </c>
+      <c r="G721" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H721" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I721" t="str">
+        <v>2026-08-03 21:00</v>
+      </c>
+      <c r="J721" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K721">
+        <v>1</v>
+      </c>
+      <c r="L721" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M721" t="str">
+        <v>2026-08-03 23:32:42</v>
+      </c>
+      <c r="N721" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O721" s="1">
+        <v>0</v>
+      </c>
+      <c r="P721" t="str">
+        <v/>
+      </c>
+      <c r="Q721" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R721" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="str">
+        <v>T260803-00013</v>
+      </c>
+      <c r="B722" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C722" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D722" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E722" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F722">
+        <v>1</v>
+      </c>
+      <c r="G722" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H722" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I722" t="str">
+        <v>2026-08-03 22:00</v>
+      </c>
+      <c r="J722" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K722">
+        <v>1</v>
+      </c>
+      <c r="L722" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M722" t="str">
+        <v>2026-08-03 23:32:24</v>
+      </c>
+      <c r="N722" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O722" s="1">
+        <v>0</v>
+      </c>
+      <c r="P722" t="str">
+        <v/>
+      </c>
+      <c r="Q722" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R722" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="str">
+        <v>T260803-00012</v>
+      </c>
+      <c r="B723" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C723" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D723" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E723" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F723">
+        <v>0</v>
+      </c>
+      <c r="G723" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H723" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I723" t="str">
+        <v>2026-08-03 23:00</v>
+      </c>
+      <c r="J723" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K723">
+        <v>1</v>
+      </c>
+      <c r="L723" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M723" t="str">
+        <v>2026-08-03 23:32:00</v>
+      </c>
+      <c r="N723" s="1">
+        <v>490000</v>
+      </c>
+      <c r="O723" s="1">
+        <v>0</v>
+      </c>
+      <c r="P723" t="str">
+        <v/>
+      </c>
+      <c r="Q723" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R723" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="str">
+        <v>T260803-00011</v>
+      </c>
+      <c r="B724" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C724" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D724" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E724" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F724">
+        <v>0</v>
+      </c>
+      <c r="G724" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H724" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I724" t="str">
+        <v>2026-08-03 21:00</v>
+      </c>
+      <c r="J724" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K724">
+        <v>1</v>
+      </c>
+      <c r="L724" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M724" t="str">
+        <v>2026-08-03 23:31:43</v>
+      </c>
+      <c r="N724" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O724" s="1">
+        <v>0</v>
+      </c>
+      <c r="P724" t="str">
+        <v/>
+      </c>
+      <c r="Q724" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R724" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="str">
+        <v>T260803-00010</v>
+      </c>
+      <c r="B725" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C725" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D725" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E725" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F725">
+        <v>1</v>
+      </c>
+      <c r="G725" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H725" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I725" t="str">
+        <v>2026-08-03 22:00</v>
+      </c>
+      <c r="J725" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K725">
+        <v>1</v>
+      </c>
+      <c r="L725" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M725" t="str">
+        <v>2026-08-03 23:31:28</v>
+      </c>
+      <c r="N725" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O725" s="1">
+        <v>0</v>
+      </c>
+      <c r="P725" t="str">
+        <v/>
+      </c>
+      <c r="Q725" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R725" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="str">
+        <v>T260803-00009</v>
+      </c>
+      <c r="B726" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C726" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D726" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E726" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F726">
+        <v>0</v>
+      </c>
+      <c r="G726" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H726" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I726" t="str">
+        <v>2026-08-03 23:00</v>
+      </c>
+      <c r="J726" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K726">
+        <v>1</v>
+      </c>
+      <c r="L726" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M726" t="str">
+        <v>2026-08-03 23:31:08</v>
+      </c>
+      <c r="N726" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O726" s="1">
+        <v>0</v>
+      </c>
+      <c r="P726" t="str">
+        <v/>
+      </c>
+      <c r="Q726" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R726" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="str">
+        <v>T260803-00008</v>
+      </c>
+      <c r="B727" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C727" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D727" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E727" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F727">
+        <v>1</v>
+      </c>
+      <c r="G727" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H727" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="I727" t="str">
+        <v>2026-08-03 23:00</v>
+      </c>
+      <c r="J727" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K727">
+        <v>1</v>
+      </c>
+      <c r="L727" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M727" t="str">
+        <v>2026-08-03 23:30:52</v>
+      </c>
+      <c r="N727" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O727" s="1">
+        <v>0</v>
+      </c>
+      <c r="P727" t="str">
+        <v/>
+      </c>
+      <c r="Q727" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R727" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="str">
+        <v>T260803-00007</v>
+      </c>
+      <c r="B728" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C728" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D728" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E728" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F728">
+        <v>0</v>
+      </c>
+      <c r="G728" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H728" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I728" t="str">
+        <v>2026-08-03 21:00</v>
+      </c>
+      <c r="J728" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K728">
+        <v>1</v>
+      </c>
+      <c r="L728" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M728" t="str">
+        <v>2026-08-03 22:51:56</v>
+      </c>
+      <c r="N728" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O728" s="1">
+        <v>0</v>
+      </c>
+      <c r="P728" t="str">
+        <v/>
+      </c>
+      <c r="Q728" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R728" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="str">
+        <v>T260803-00006</v>
+      </c>
+      <c r="B729" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C729" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D729" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E729" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F729">
+        <v>1</v>
+      </c>
+      <c r="G729" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="H729" t="str">
+        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="I729" t="str">
+        <v>2026-08-03 23:00</v>
+      </c>
+      <c r="J729" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K729">
+        <v>1</v>
+      </c>
+      <c r="L729" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M729" t="str">
+        <v>2026-08-03 22:51:37</v>
+      </c>
+      <c r="N729" s="1">
+        <v>310000</v>
+      </c>
+      <c r="O729" s="1">
+        <v>0</v>
+      </c>
+      <c r="P729" t="str">
+        <v/>
+      </c>
+      <c r="Q729" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R729" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="str">
+        <v>T260803-00005</v>
+      </c>
+      <c r="B730" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C730" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D730" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E730" t="str">
+        <v>2026-08-03 17:50</v>
+      </c>
+      <c r="F730">
+        <v>0</v>
+      </c>
+      <c r="G730" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H730" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I730" t="str">
+        <v>2026-08-03 18:50</v>
+      </c>
+      <c r="J730" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K730">
+        <v>1</v>
+      </c>
+      <c r="L730" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M730" t="str">
+        <v>2026-08-03 22:47:04</v>
+      </c>
+      <c r="N730" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O730" s="1">
+        <v>0</v>
+      </c>
+      <c r="P730" t="str">
+        <v/>
+      </c>
+      <c r="Q730" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R730" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="str">
+        <v>T260803-00004</v>
+      </c>
+      <c r="B731" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C731" t="str">
+        <v>샤오미</v>
+      </c>
+      <c r="D731" t="str">
+        <v>경기 이천시 대월면 부필리 309 샤오미</v>
+      </c>
+      <c r="E731" t="str">
+        <v>2026-08-03 13:50</v>
+      </c>
+      <c r="F731">
+        <v>0</v>
+      </c>
+      <c r="G731" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H731" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I731" t="str">
+        <v>2026-08-03 14:50</v>
+      </c>
+      <c r="J731" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K731">
+        <v>1</v>
+      </c>
+      <c r="L731" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M731" t="str">
+        <v>2026-08-03 22:46:33</v>
+      </c>
+      <c r="N731" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O731" s="1">
+        <v>0</v>
+      </c>
+      <c r="P731" t="str">
+        <v>샤오미 외주사입고(11대)</v>
+      </c>
+      <c r="Q731" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R731" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="str">
+        <v>T260803-00003</v>
+      </c>
+      <c r="B732" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C732" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D732" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E732" t="str">
+        <v>2026-08-03 14:50</v>
+      </c>
+      <c r="F732">
+        <v>0</v>
+      </c>
+      <c r="G732" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H732" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I732" t="str">
+        <v>2026-08-03 15:50</v>
+      </c>
+      <c r="J732" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K732">
+        <v>1</v>
+      </c>
+      <c r="L732" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M732" t="str">
+        <v>2026-08-03 22:45:46</v>
+      </c>
+      <c r="N732" s="1">
+        <v>70000</v>
+      </c>
+      <c r="O732" s="1">
+        <v>0</v>
+      </c>
+      <c r="P732" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="Q732" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R732" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="str">
+        <v>T260803-00002</v>
+      </c>
+      <c r="B733" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C733" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D733" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E733" t="str">
+        <v>2026-08-03 10:00</v>
+      </c>
+      <c r="F733">
+        <v>0</v>
+      </c>
+      <c r="G733" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H733" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I733" t="str">
+        <v>2026-08-03 13:50</v>
+      </c>
+      <c r="J733" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K733">
+        <v>1</v>
+      </c>
+      <c r="L733" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M733" t="str">
+        <v>2026-08-03 22:45:01</v>
+      </c>
+      <c r="N733" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O733" s="1">
+        <v>0</v>
+      </c>
+      <c r="P733" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q733" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R733" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="str">
+        <v>T260803-00001</v>
+      </c>
+      <c r="B734" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C734" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D734" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E734" t="str">
+        <v>2026-08-03 16:30</v>
+      </c>
+      <c r="F734">
+        <v>0</v>
+      </c>
+      <c r="G734" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H734" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I734" t="str">
+        <v>2026-08-03 18:00</v>
+      </c>
+      <c r="J734" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K734">
+        <v>1</v>
+      </c>
+      <c r="L734" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="M734" t="str">
+        <v>2026-08-03 15:39:18</v>
+      </c>
+      <c r="N734" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O734" s="1">
+        <v>0</v>
+      </c>
+      <c r="P734" t="str">
+        <v/>
+      </c>
+      <c r="Q734" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R734" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R678"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R734"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R734"/>
+  <dimension ref="A1:R632"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -35771,5721 +35771,9 @@
         <v>일코전자</v>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="str">
-        <v>T260805-00046</v>
-      </c>
-      <c r="B633" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C633" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D633" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E633" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F633">
-        <v>0</v>
-      </c>
-      <c r="G633" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H633" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I633" t="str">
-        <v>2026-08-06 07:00</v>
-      </c>
-      <c r="J633" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K633">
-        <v>1</v>
-      </c>
-      <c r="L633" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M633" t="str">
-        <v>2026-08-05 20:55:08</v>
-      </c>
-      <c r="N633" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O633" s="1">
-        <v>0</v>
-      </c>
-      <c r="P633" t="str">
-        <v/>
-      </c>
-      <c r="Q633" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R633" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="str">
-        <v>T260805-00045</v>
-      </c>
-      <c r="B634" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C634" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D634" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E634" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F634">
-        <v>0</v>
-      </c>
-      <c r="G634" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H634" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I634" t="str">
-        <v>2026-08-06 08:00</v>
-      </c>
-      <c r="J634" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K634">
-        <v>1</v>
-      </c>
-      <c r="L634" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M634" t="str">
-        <v>2026-08-05 20:54:48</v>
-      </c>
-      <c r="N634" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O634" s="1">
-        <v>0</v>
-      </c>
-      <c r="P634" t="str">
-        <v/>
-      </c>
-      <c r="Q634" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R634" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="str">
-        <v>T260805-00044</v>
-      </c>
-      <c r="B635" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C635" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D635" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E635" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F635">
-        <v>0</v>
-      </c>
-      <c r="G635" t="str">
-        <v>용인ACP</v>
-      </c>
-      <c r="H635" t="str">
-        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
-      </c>
-      <c r="I635" t="str">
-        <v>2026-08-06 06:00</v>
-      </c>
-      <c r="J635" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K635">
-        <v>1</v>
-      </c>
-      <c r="L635" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M635" t="str">
-        <v>2026-08-05 20:54:28</v>
-      </c>
-      <c r="N635" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O635" s="1">
-        <v>0</v>
-      </c>
-      <c r="P635" t="str">
-        <v/>
-      </c>
-      <c r="Q635" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R635" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="str">
-        <v>T260805-00043</v>
-      </c>
-      <c r="B636" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C636" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D636" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E636" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F636">
-        <v>1</v>
-      </c>
-      <c r="G636" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H636" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I636" t="str">
-        <v>2026-08-06 07:00</v>
-      </c>
-      <c r="J636" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K636">
-        <v>1</v>
-      </c>
-      <c r="L636" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M636" t="str">
-        <v>2026-08-05 20:54:08</v>
-      </c>
-      <c r="N636" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O636" s="1">
-        <v>0</v>
-      </c>
-      <c r="P636" t="str">
-        <v/>
-      </c>
-      <c r="Q636" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R636" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="str">
-        <v>T260805-00042</v>
-      </c>
-      <c r="B637" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C637" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D637" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E637" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F637">
-        <v>0</v>
-      </c>
-      <c r="G637" t="str">
-        <v>시흥ACP</v>
-      </c>
-      <c r="H637" t="str">
-        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
-      </c>
-      <c r="I637" t="str">
-        <v>2026-08-06 07:00</v>
-      </c>
-      <c r="J637" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K637">
-        <v>1</v>
-      </c>
-      <c r="L637" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M637" t="str">
-        <v>2026-08-05 20:49:31</v>
-      </c>
-      <c r="N637" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O637" s="1">
-        <v>0</v>
-      </c>
-      <c r="P637" t="str">
-        <v/>
-      </c>
-      <c r="Q637" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R637" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="str">
-        <v>T260805-00041</v>
-      </c>
-      <c r="B638" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C638" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D638" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E638" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F638">
-        <v>1</v>
-      </c>
-      <c r="G638" t="str">
-        <v>속초ACP</v>
-      </c>
-      <c r="H638" t="str">
-        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
-      </c>
-      <c r="I638" t="str">
-        <v>2026-08-06 06:00</v>
-      </c>
-      <c r="J638" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K638">
-        <v>1</v>
-      </c>
-      <c r="L638" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M638" t="str">
-        <v>2026-08-05 20:48:08</v>
-      </c>
-      <c r="N638" s="1">
-        <v>270000</v>
-      </c>
-      <c r="O638" s="1">
-        <v>0</v>
-      </c>
-      <c r="P638" t="str">
-        <v/>
-      </c>
-      <c r="Q638" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R638" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="str">
-        <v>T260805-00040</v>
-      </c>
-      <c r="B639" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C639" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D639" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E639" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F639">
-        <v>0</v>
-      </c>
-      <c r="G639" t="str">
-        <v>서산ACP</v>
-      </c>
-      <c r="H639" t="str">
-        <v>충남 서산시 덕지천로 328-3 서산ACP</v>
-      </c>
-      <c r="I639" t="str">
-        <v>2026-08-06 07:00</v>
-      </c>
-      <c r="J639" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K639">
-        <v>1</v>
-      </c>
-      <c r="L639" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M639" t="str">
-        <v>2026-08-05 20:47:41</v>
-      </c>
-      <c r="N639" s="1">
-        <v>130000</v>
-      </c>
-      <c r="O639" s="1">
-        <v>0</v>
-      </c>
-      <c r="P639" t="str">
-        <v/>
-      </c>
-      <c r="Q639" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R639" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="str">
-        <v>T260805-00039</v>
-      </c>
-      <c r="B640" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C640" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D640" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E640" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F640">
-        <v>1</v>
-      </c>
-      <c r="G640" t="str">
-        <v>대전대덕ACP</v>
-      </c>
-      <c r="H640" t="str">
-        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
-      </c>
-      <c r="I640" t="str">
-        <v>2026-08-06 07:00</v>
-      </c>
-      <c r="J640" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K640">
-        <v>1</v>
-      </c>
-      <c r="L640" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M640" t="str">
-        <v>2026-08-05 20:47:22</v>
-      </c>
-      <c r="N640" s="1">
-        <v>220000</v>
-      </c>
-      <c r="O640" s="1">
-        <v>0</v>
-      </c>
-      <c r="P640" t="str">
-        <v/>
-      </c>
-      <c r="Q640" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R640" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="str">
-        <v>T260805-00038</v>
-      </c>
-      <c r="B641" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C641" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D641" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E641" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F641">
-        <v>1</v>
-      </c>
-      <c r="G641" t="str">
-        <v>원주ACP</v>
-      </c>
-      <c r="H641" t="str">
-        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
-      </c>
-      <c r="I641" t="str">
-        <v>2026-08-05 22:00</v>
-      </c>
-      <c r="J641" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K641">
-        <v>1</v>
-      </c>
-      <c r="L641" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M641" t="str">
-        <v>2026-08-05 20:45:34</v>
-      </c>
-      <c r="N641" s="1">
-        <v>170000</v>
-      </c>
-      <c r="O641" s="1">
-        <v>0</v>
-      </c>
-      <c r="P641" t="str">
-        <v/>
-      </c>
-      <c r="Q641" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R641" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="str">
-        <v>T260805-00037</v>
-      </c>
-      <c r="B642" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C642" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D642" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E642" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F642">
-        <v>1</v>
-      </c>
-      <c r="G642" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H642" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I642" t="str">
-        <v>2026-08-06 07:00</v>
-      </c>
-      <c r="J642" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K642">
-        <v>1</v>
-      </c>
-      <c r="L642" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M642" t="str">
-        <v>2026-08-05 20:44:44</v>
-      </c>
-      <c r="N642" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O642" s="1">
-        <v>0</v>
-      </c>
-      <c r="P642" t="str">
-        <v/>
-      </c>
-      <c r="Q642" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R642" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" t="str">
-        <v>T260805-00036</v>
-      </c>
-      <c r="B643" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C643" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D643" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E643" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F643">
-        <v>0</v>
-      </c>
-      <c r="G643" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H643" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I643" t="str">
-        <v>2026-08-06 08:00</v>
-      </c>
-      <c r="J643" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K643">
-        <v>1</v>
-      </c>
-      <c r="L643" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M643" t="str">
-        <v>2026-08-05 20:43:06</v>
-      </c>
-      <c r="N643" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O643" s="1">
-        <v>0</v>
-      </c>
-      <c r="P643" t="str">
-        <v/>
-      </c>
-      <c r="Q643" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R643" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="str">
-        <v>T260805-00035</v>
-      </c>
-      <c r="B644" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C644" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D644" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E644" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F644">
-        <v>0</v>
-      </c>
-      <c r="G644" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="H644" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="I644" t="str">
-        <v>2026-08-06 07:00</v>
-      </c>
-      <c r="J644" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K644">
-        <v>1</v>
-      </c>
-      <c r="L644" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M644" t="str">
-        <v>2026-08-05 20:42:44</v>
-      </c>
-      <c r="N644" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O644" s="1">
-        <v>0</v>
-      </c>
-      <c r="P644" t="str">
-        <v/>
-      </c>
-      <c r="Q644" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R644" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="str">
-        <v>T260805-00034</v>
-      </c>
-      <c r="B645" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C645" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D645" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E645" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F645">
-        <v>0</v>
-      </c>
-      <c r="G645" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H645" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I645" t="str">
-        <v>2026-08-05 21:00</v>
-      </c>
-      <c r="J645" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K645">
-        <v>1</v>
-      </c>
-      <c r="L645" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M645" t="str">
-        <v>2026-08-05 20:41:24</v>
-      </c>
-      <c r="N645" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O645" s="1">
-        <v>0</v>
-      </c>
-      <c r="P645" t="str">
-        <v/>
-      </c>
-      <c r="Q645" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R645" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="str">
-        <v>T260805-00033</v>
-      </c>
-      <c r="B646" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C646" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D646" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E646" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F646">
-        <v>1</v>
-      </c>
-      <c r="G646" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H646" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I646" t="str">
-        <v>2026-08-05 22:00</v>
-      </c>
-      <c r="J646" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K646">
-        <v>1</v>
-      </c>
-      <c r="L646" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M646" t="str">
-        <v>2026-08-05 20:41:08</v>
-      </c>
-      <c r="N646" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O646" s="1">
-        <v>0</v>
-      </c>
-      <c r="P646" t="str">
-        <v/>
-      </c>
-      <c r="Q646" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R646" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="str">
-        <v>T260805-00032</v>
-      </c>
-      <c r="B647" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C647" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D647" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E647" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F647">
-        <v>1</v>
-      </c>
-      <c r="G647" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H647" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I647" t="str">
-        <v>2026-08-05 22:00</v>
-      </c>
-      <c r="J647" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K647">
-        <v>1</v>
-      </c>
-      <c r="L647" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M647" t="str">
-        <v>2026-08-05 20:40:46</v>
-      </c>
-      <c r="N647" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O647" s="1">
-        <v>0</v>
-      </c>
-      <c r="P647" t="str">
-        <v/>
-      </c>
-      <c r="Q647" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R647" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="str">
-        <v>T260805-00031</v>
-      </c>
-      <c r="B648" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C648" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D648" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E648" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F648">
-        <v>0</v>
-      </c>
-      <c r="G648" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H648" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I648" t="str">
-        <v>2026-08-05 21:00</v>
-      </c>
-      <c r="J648" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K648">
-        <v>1</v>
-      </c>
-      <c r="L648" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M648" t="str">
-        <v>2026-08-05 20:40:24</v>
-      </c>
-      <c r="N648" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O648" s="1">
-        <v>0</v>
-      </c>
-      <c r="P648" t="str">
-        <v/>
-      </c>
-      <c r="Q648" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R648" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="str">
-        <v>T260805-00030</v>
-      </c>
-      <c r="B649" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C649" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D649" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E649" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F649">
-        <v>1</v>
-      </c>
-      <c r="G649" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H649" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I649" t="str">
-        <v>2026-08-05 22:00</v>
-      </c>
-      <c r="J649" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K649">
-        <v>1</v>
-      </c>
-      <c r="L649" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M649" t="str">
-        <v>2026-08-05 20:40:08</v>
-      </c>
-      <c r="N649" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O649" s="1">
-        <v>0</v>
-      </c>
-      <c r="P649" t="str">
-        <v/>
-      </c>
-      <c r="Q649" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R649" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="str">
-        <v>T260805-00029</v>
-      </c>
-      <c r="B650" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C650" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D650" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E650" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F650">
-        <v>0</v>
-      </c>
-      <c r="G650" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H650" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I650" t="str">
-        <v>2026-08-05 23:00</v>
-      </c>
-      <c r="J650" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K650">
-        <v>1</v>
-      </c>
-      <c r="L650" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M650" t="str">
-        <v>2026-08-05 20:39:22</v>
-      </c>
-      <c r="N650" s="1">
-        <v>490000</v>
-      </c>
-      <c r="O650" s="1">
-        <v>0</v>
-      </c>
-      <c r="P650" t="str">
-        <v/>
-      </c>
-      <c r="Q650" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R650" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="str">
-        <v>T260805-00028</v>
-      </c>
-      <c r="B651" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C651" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D651" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E651" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F651">
-        <v>0</v>
-      </c>
-      <c r="G651" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H651" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I651" t="str">
-        <v>2026-08-05 21:00</v>
-      </c>
-      <c r="J651" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K651">
-        <v>1</v>
-      </c>
-      <c r="L651" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M651" t="str">
-        <v>2026-08-05 20:39:04</v>
-      </c>
-      <c r="N651" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O651" s="1">
-        <v>0</v>
-      </c>
-      <c r="P651" t="str">
-        <v/>
-      </c>
-      <c r="Q651" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R651" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="str">
-        <v>T260805-00027</v>
-      </c>
-      <c r="B652" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C652" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D652" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E652" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F652">
-        <v>0</v>
-      </c>
-      <c r="G652" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H652" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I652" t="str">
-        <v>2026-08-05 21:00</v>
-      </c>
-      <c r="J652" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K652">
-        <v>1</v>
-      </c>
-      <c r="L652" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M652" t="str">
-        <v>2026-08-05 20:38:50</v>
-      </c>
-      <c r="N652" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O652" s="1">
-        <v>0</v>
-      </c>
-      <c r="P652" t="str">
-        <v/>
-      </c>
-      <c r="Q652" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R652" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="str">
-        <v>T260805-00026</v>
-      </c>
-      <c r="B653" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C653" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D653" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E653" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F653">
-        <v>1</v>
-      </c>
-      <c r="G653" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H653" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I653" t="str">
-        <v>2026-08-05 23:00</v>
-      </c>
-      <c r="J653" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K653">
-        <v>1</v>
-      </c>
-      <c r="L653" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M653" t="str">
-        <v>2026-08-05 20:38:02</v>
-      </c>
-      <c r="N653" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O653" s="1">
-        <v>0</v>
-      </c>
-      <c r="P653" t="str">
-        <v/>
-      </c>
-      <c r="Q653" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R653" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" t="str">
-        <v>T260805-00025</v>
-      </c>
-      <c r="B654" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C654" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D654" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E654" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F654">
-        <v>0</v>
-      </c>
-      <c r="G654" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H654" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I654" t="str">
-        <v>2026-08-05 21:00</v>
-      </c>
-      <c r="J654" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K654">
-        <v>1</v>
-      </c>
-      <c r="L654" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M654" t="str">
-        <v>2026-08-05 20:37:42</v>
-      </c>
-      <c r="N654" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O654" s="1">
-        <v>0</v>
-      </c>
-      <c r="P654" t="str">
-        <v/>
-      </c>
-      <c r="Q654" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R654" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="str">
-        <v>T260805-00024</v>
-      </c>
-      <c r="B655" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C655" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D655" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E655" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F655">
-        <v>1</v>
-      </c>
-      <c r="G655" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H655" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="I655" t="str">
-        <v>2026-08-05 23:00</v>
-      </c>
-      <c r="J655" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K655">
-        <v>1</v>
-      </c>
-      <c r="L655" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M655" t="str">
-        <v>2026-08-05 20:37:26</v>
-      </c>
-      <c r="N655" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O655" s="1">
-        <v>0</v>
-      </c>
-      <c r="P655" t="str">
-        <v/>
-      </c>
-      <c r="Q655" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R655" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" t="str">
-        <v>T260805-00023</v>
-      </c>
-      <c r="B656" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C656" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D656" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E656" t="str">
-        <v>2026-08-05 19:00</v>
-      </c>
-      <c r="F656">
-        <v>1</v>
-      </c>
-      <c r="G656" t="str">
-        <v>강릉FDC</v>
-      </c>
-      <c r="H656" t="str">
-        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
-      </c>
-      <c r="I656" t="str">
-        <v>2026-08-05 23:00</v>
-      </c>
-      <c r="J656" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K656">
-        <v>1</v>
-      </c>
-      <c r="L656" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M656" t="str">
-        <v>2026-08-05 20:37:05</v>
-      </c>
-      <c r="N656" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O656" s="1">
-        <v>0</v>
-      </c>
-      <c r="P656" t="str">
-        <v/>
-      </c>
-      <c r="Q656" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R656" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="str">
-        <v>T260805-00022</v>
-      </c>
-      <c r="B657" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C657" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D657" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E657" t="str">
-        <v>2026-08-05 17:30</v>
-      </c>
-      <c r="F657">
-        <v>0</v>
-      </c>
-      <c r="G657" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H657" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I657" t="str">
-        <v>2026-08-05 18:30</v>
-      </c>
-      <c r="J657" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K657">
-        <v>1</v>
-      </c>
-      <c r="L657" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M657" t="str">
-        <v>2026-08-05 20:32:13</v>
-      </c>
-      <c r="N657" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O657" s="1">
-        <v>0</v>
-      </c>
-      <c r="P657" t="str">
-        <v/>
-      </c>
-      <c r="Q657" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R657" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" t="str">
-        <v>T260805-00021</v>
-      </c>
-      <c r="B658" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C658" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="D658" t="str">
-        <v>경기 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="E658" t="str">
-        <v>2026-08-05 21:30</v>
-      </c>
-      <c r="F658">
-        <v>0</v>
-      </c>
-      <c r="G658" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H658" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I658" t="str">
-        <v>2026-08-05 23:30</v>
-      </c>
-      <c r="J658" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K658">
-        <v>1</v>
-      </c>
-      <c r="L658" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M658" t="str">
-        <v>2026-08-05 20:31:41</v>
-      </c>
-      <c r="N658" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O658" s="1">
-        <v>0</v>
-      </c>
-      <c r="P658" t="str">
-        <v>공파렛이동</v>
-      </c>
-      <c r="Q658" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R658" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="str">
-        <v>T260805-00020</v>
-      </c>
-      <c r="B659" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C659" t="str">
-        <v>샤오미</v>
-      </c>
-      <c r="D659" t="str">
-        <v>경기 이천시 대월면 부필리 309 샤오미</v>
-      </c>
-      <c r="E659" t="str">
-        <v>2026-08-05 14:30</v>
-      </c>
-      <c r="F659">
-        <v>0</v>
-      </c>
-      <c r="G659" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H659" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I659" t="str">
-        <v>2026-08-05 15:30</v>
-      </c>
-      <c r="J659" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K659">
-        <v>1</v>
-      </c>
-      <c r="L659" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M659" t="str">
-        <v>2026-08-05 20:30:39</v>
-      </c>
-      <c r="N659" s="1">
-        <v>80000</v>
-      </c>
-      <c r="O659" s="1">
-        <v>0</v>
-      </c>
-      <c r="P659" t="str">
-        <v>거래처비용청구(2대)</v>
-      </c>
-      <c r="Q659" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R659" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="str">
-        <v>T260805-00019</v>
-      </c>
-      <c r="B660" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C660" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D660" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E660" t="str">
-        <v>2026-08-05 14:30</v>
-      </c>
-      <c r="F660">
-        <v>0</v>
-      </c>
-      <c r="G660" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H660" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I660" t="str">
-        <v>2026-08-05 15:30</v>
-      </c>
-      <c r="J660" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K660">
-        <v>1</v>
-      </c>
-      <c r="L660" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M660" t="str">
-        <v>2026-08-05 20:29:36</v>
-      </c>
-      <c r="N660" s="1">
-        <v>70000</v>
-      </c>
-      <c r="O660" s="1">
-        <v>0</v>
-      </c>
-      <c r="P660" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="Q660" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R660" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="str">
-        <v>T260805-00018</v>
-      </c>
-      <c r="B661" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C661" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D661" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E661" t="str">
-        <v>2026-08-05 10:30</v>
-      </c>
-      <c r="F661">
-        <v>0</v>
-      </c>
-      <c r="G661" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H661" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I661" t="str">
-        <v>2026-08-05 13:30</v>
-      </c>
-      <c r="J661" t="str">
-        <v>1.5톤 윙바디</v>
-      </c>
-      <c r="K661">
-        <v>1</v>
-      </c>
-      <c r="L661" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M661" t="str">
-        <v>2026-08-05 20:28:50</v>
-      </c>
-      <c r="N661" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O661" s="1">
-        <v>0</v>
-      </c>
-      <c r="P661" t="str">
-        <v>듀오백외주사입고</v>
-      </c>
-      <c r="Q661" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R661" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="str">
-        <v>T260805-00017</v>
-      </c>
-      <c r="B662" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C662" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D662" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E662" t="str">
-        <v>2026-08-05 18:00</v>
-      </c>
-      <c r="F662">
-        <v>0</v>
-      </c>
-      <c r="G662" t="str">
-        <v>인천 하이마트 물류</v>
-      </c>
-      <c r="H662" t="str">
-        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
-      </c>
-      <c r="I662" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J662" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K662">
-        <v>1</v>
-      </c>
-      <c r="L662" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M662" t="str">
-        <v>2026-08-05 17:06:03</v>
-      </c>
-      <c r="N662" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O662" s="1">
-        <v>0</v>
-      </c>
-      <c r="P662" t="str">
-        <v>일코전자 인천 하이마트 물류</v>
-      </c>
-      <c r="Q662" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R662" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="str">
-        <v>T260805-00016</v>
-      </c>
-      <c r="B663" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C663" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D663" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E663" t="str">
-        <v>2026-08-05 17:30</v>
-      </c>
-      <c r="F663">
-        <v>0</v>
-      </c>
-      <c r="G663" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="H663" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="I663" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J663" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K663">
-        <v>1</v>
-      </c>
-      <c r="L663" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M663" t="str">
-        <v>2026-08-05 17:05:09</v>
-      </c>
-      <c r="N663" s="1">
-        <v>220000</v>
-      </c>
-      <c r="O663" s="1">
-        <v>0</v>
-      </c>
-      <c r="P663" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="Q663" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R663" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="str">
-        <v>T260805-00015</v>
-      </c>
-      <c r="B664" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C664" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D664" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E664" t="str">
-        <v>2026-08-05 16:40</v>
-      </c>
-      <c r="F664">
-        <v>0</v>
-      </c>
-      <c r="G664" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="H664" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="I664" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J664" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K664">
-        <v>1</v>
-      </c>
-      <c r="L664" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M664" t="str">
-        <v>2026-08-05 16:12:42</v>
-      </c>
-      <c r="N664" s="1">
-        <v>220000</v>
-      </c>
-      <c r="O664" s="1">
-        <v>0</v>
-      </c>
-      <c r="P664" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="Q664" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R664" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="str">
-        <v>T260805-00014</v>
-      </c>
-      <c r="B665" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C665" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D665" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E665" t="str">
-        <v>2026-08-05 17:30</v>
-      </c>
-      <c r="F665">
-        <v>0</v>
-      </c>
-      <c r="G665" t="str">
-        <v>마산 하이마트 물류</v>
-      </c>
-      <c r="H665" t="str">
-        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
-      </c>
-      <c r="I665" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J665" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K665">
-        <v>1</v>
-      </c>
-      <c r="L665" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M665" t="str">
-        <v>2026-08-05 16:05:16</v>
-      </c>
-      <c r="N665" s="1">
-        <v>460000</v>
-      </c>
-      <c r="O665" s="1">
-        <v>0</v>
-      </c>
-      <c r="P665" t="str">
-        <v>일코 마산 하이마트 물류</v>
-      </c>
-      <c r="Q665" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R665" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="str">
-        <v>T260805-00013</v>
-      </c>
-      <c r="B666" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C666" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D666" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E666" t="str">
-        <v>2026-08-05 16:30</v>
-      </c>
-      <c r="F666">
-        <v>0</v>
-      </c>
-      <c r="G666" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H666" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I666" t="str">
-        <v>2026-08-05 18:00</v>
-      </c>
-      <c r="J666" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K666">
-        <v>1</v>
-      </c>
-      <c r="L666" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="M666" t="str">
-        <v>2026-08-05 15:59:59</v>
-      </c>
-      <c r="N666" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O666" s="1">
-        <v>0</v>
-      </c>
-      <c r="P666" t="str">
-        <v/>
-      </c>
-      <c r="Q666" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R666" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="str">
-        <v>T260805-00012</v>
-      </c>
-      <c r="B667" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C667" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D667" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E667" t="str">
-        <v>2026-08-05 16:00</v>
-      </c>
-      <c r="F667">
-        <v>0</v>
-      </c>
-      <c r="G667" t="str">
-        <v>대구 하이마트 물류</v>
-      </c>
-      <c r="H667" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="I667" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J667" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K667">
-        <v>1</v>
-      </c>
-      <c r="L667" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M667" t="str">
-        <v>2026-08-05 15:15:47</v>
-      </c>
-      <c r="N667" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O667" s="1">
-        <v>0</v>
-      </c>
-      <c r="P667" t="str">
-        <v>일코전자 대구 하이마트 물류</v>
-      </c>
-      <c r="Q667" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R667" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="str">
-        <v>T260805-00011</v>
-      </c>
-      <c r="B668" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C668" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D668" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E668" t="str">
-        <v>2026-08-05 15:20</v>
-      </c>
-      <c r="F668">
-        <v>0</v>
-      </c>
-      <c r="G668" t="str">
-        <v>파주 하이마트 물류</v>
-      </c>
-      <c r="H668" t="str">
-        <v>경기 파주시 탄현면 월롱산로 296 파주 하이마트 물류</v>
-      </c>
-      <c r="I668" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J668" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K668">
-        <v>1</v>
-      </c>
-      <c r="L668" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M668" t="str">
-        <v>2026-08-05 15:00:25</v>
-      </c>
-      <c r="N668" s="1">
-        <v>280000</v>
-      </c>
-      <c r="O668" s="1">
-        <v>0</v>
-      </c>
-      <c r="P668" t="str">
-        <v>일코전자 파주 하이마트 물류</v>
-      </c>
-      <c r="Q668" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R668" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="str">
-        <v>T260805-00010</v>
-      </c>
-      <c r="B669" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C669" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D669" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E669" t="str">
-        <v>2026-08-05 14:30</v>
-      </c>
-      <c r="F669">
-        <v>0</v>
-      </c>
-      <c r="G669" t="str">
-        <v>마산 하이마트 물류</v>
-      </c>
-      <c r="H669" t="str">
-        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
-      </c>
-      <c r="I669" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J669" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K669">
-        <v>1</v>
-      </c>
-      <c r="L669" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M669" t="str">
-        <v>2026-08-05 14:27:45</v>
-      </c>
-      <c r="N669" s="1">
-        <v>440000</v>
-      </c>
-      <c r="O669" s="1">
-        <v>0</v>
-      </c>
-      <c r="P669" t="str">
-        <v>일코 마산 하이마트 물류</v>
-      </c>
-      <c r="Q669" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R669" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="str">
-        <v>T260805-00009</v>
-      </c>
-      <c r="B670" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C670" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D670" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E670" t="str">
-        <v>2026-08-05 02:30</v>
-      </c>
-      <c r="F670">
-        <v>0</v>
-      </c>
-      <c r="G670" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="H670" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="I670" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J670" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K670">
-        <v>1</v>
-      </c>
-      <c r="L670" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M670" t="str">
-        <v>2026-08-05 14:27:13</v>
-      </c>
-      <c r="N670" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O670" s="1">
-        <v>0</v>
-      </c>
-      <c r="P670" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="Q670" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R670" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="str">
-        <v>T260805-00008</v>
-      </c>
-      <c r="B671" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C671" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D671" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E671" t="str">
-        <v>2026-08-05 15:30</v>
-      </c>
-      <c r="F671">
-        <v>0</v>
-      </c>
-      <c r="G671" t="str">
-        <v>광주 하이마트 물류</v>
-      </c>
-      <c r="H671" t="str">
-        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
-      </c>
-      <c r="I671" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J671" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K671">
-        <v>1</v>
-      </c>
-      <c r="L671" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M671" t="str">
-        <v>2026-08-05 13:23:42</v>
-      </c>
-      <c r="N671" s="1">
-        <v>400000</v>
-      </c>
-      <c r="O671" s="1">
-        <v>0</v>
-      </c>
-      <c r="P671" t="str">
-        <v>일코 광주 하이마트 물류</v>
-      </c>
-      <c r="Q671" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R671" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="str">
-        <v>T260805-00007</v>
-      </c>
-      <c r="B672" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C672" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="D672" t="str">
-        <v>광주 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="E672" t="str">
-        <v>2026-08-02 07:00</v>
-      </c>
-      <c r="F672">
-        <v>0</v>
-      </c>
-      <c r="G672" t="str">
-        <v>진주FDC</v>
-      </c>
-      <c r="H672" t="str">
-        <v>경남 진주시 지수면 승산리 163-1 진주FDC</v>
-      </c>
-      <c r="I672" t="str">
-        <v>2026-08-02 10:00</v>
-      </c>
-      <c r="J672" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K672">
-        <v>1</v>
-      </c>
-      <c r="L672" t="str">
-        <v>임서혁</v>
-      </c>
-      <c r="M672" t="str">
-        <v>2026-08-05 11:05:41</v>
-      </c>
-      <c r="N672" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O672" s="1">
-        <v>0</v>
-      </c>
-      <c r="P672" t="str">
-        <v>광주fdcㅡ진주fdc 에어컨파렛</v>
-      </c>
-      <c r="Q672" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R672" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="str">
-        <v>T260805-00006</v>
-      </c>
-      <c r="B673" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C673" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="D673" t="str">
-        <v>경남 창원시 의창구 동읍 노연리 30-4 창원FDC</v>
-      </c>
-      <c r="E673" t="str">
-        <v>2026-08-04 13:00</v>
-      </c>
-      <c r="F673">
-        <v>0</v>
-      </c>
-      <c r="G673" t="str">
-        <v>진주FDC</v>
-      </c>
-      <c r="H673" t="str">
-        <v>경남 진주시 지수면 승산리 163-1 진주FDC</v>
-      </c>
-      <c r="I673" t="str">
-        <v>2026-08-05 15:00</v>
-      </c>
-      <c r="J673" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K673">
-        <v>1</v>
-      </c>
-      <c r="L673" t="str">
-        <v>임서혁</v>
-      </c>
-      <c r="M673" t="str">
-        <v>2026-08-05 11:04:27</v>
-      </c>
-      <c r="N673" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O673" s="1">
-        <v>0</v>
-      </c>
-      <c r="P673" t="str">
-        <v>창원fdcㅡ진주fdc 1톤카고 에어컨</v>
-      </c>
-      <c r="Q673" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R673" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="str">
-        <v>T260805-00005</v>
-      </c>
-      <c r="B674" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C674" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D674" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E674" t="str">
-        <v>2026-08-05 15:00</v>
-      </c>
-      <c r="F674">
-        <v>0</v>
-      </c>
-      <c r="G674" t="str">
-        <v>대구 하이마트 물류</v>
-      </c>
-      <c r="H674" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="I674" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J674" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K674">
-        <v>1</v>
-      </c>
-      <c r="L674" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M674" t="str">
-        <v>2026-08-05 10:17:17</v>
-      </c>
-      <c r="N674" s="1">
-        <v>340000</v>
-      </c>
-      <c r="O674" s="1">
-        <v>0</v>
-      </c>
-      <c r="P674" t="str">
-        <v>일코전자 대구 하이마트 물류</v>
-      </c>
-      <c r="Q674" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R674" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="str">
-        <v>T260805-00004</v>
-      </c>
-      <c r="B675" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C675" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D675" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E675" t="str">
-        <v>2026-08-05 15:00</v>
-      </c>
-      <c r="F675">
-        <v>0</v>
-      </c>
-      <c r="G675" t="str">
-        <v>광주 하이마트 물류</v>
-      </c>
-      <c r="H675" t="str">
-        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
-      </c>
-      <c r="I675" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J675" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K675">
-        <v>1</v>
-      </c>
-      <c r="L675" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M675" t="str">
-        <v>2026-08-05 09:11:17</v>
-      </c>
-      <c r="N675" s="1">
-        <v>380000</v>
-      </c>
-      <c r="O675" s="1">
-        <v>0</v>
-      </c>
-      <c r="P675" t="str">
-        <v>일코 광주 하이마트 물류</v>
-      </c>
-      <c r="Q675" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R675" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="str">
-        <v>T260805-00003</v>
-      </c>
-      <c r="B676" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C676" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D676" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E676" t="str">
-        <v>2026-08-05 14:00</v>
-      </c>
-      <c r="F676">
-        <v>0</v>
-      </c>
-      <c r="G676" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H676" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I676" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J676" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="K676">
-        <v>1</v>
-      </c>
-      <c r="L676" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M676" t="str">
-        <v>2026-08-05 09:10:38</v>
-      </c>
-      <c r="N676" s="1">
-        <v>380000</v>
-      </c>
-      <c r="O676" s="1">
-        <v>0</v>
-      </c>
-      <c r="P676" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q676" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R676" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="str">
-        <v>T260805-00002</v>
-      </c>
-      <c r="B677" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C677" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D677" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E677" t="str">
-        <v>2026-08-05 11:00</v>
-      </c>
-      <c r="F677">
-        <v>0</v>
-      </c>
-      <c r="G677" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="H677" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="I677" t="str">
-        <v>2026-08-06 09:00</v>
-      </c>
-      <c r="J677" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K677">
-        <v>1</v>
-      </c>
-      <c r="L677" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M677" t="str">
-        <v>2026-08-05 09:09:57</v>
-      </c>
-      <c r="N677" s="1">
-        <v>440000</v>
-      </c>
-      <c r="O677" s="1">
-        <v>0</v>
-      </c>
-      <c r="P677" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="Q677" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R677" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="str">
-        <v>T260805-00001</v>
-      </c>
-      <c r="B678" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C678" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D678" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E678" t="str">
-        <v>2026-08-05 09:00</v>
-      </c>
-      <c r="F678">
-        <v>0</v>
-      </c>
-      <c r="G678" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H678" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I678" t="str">
-        <v>2026-08-05 10:00</v>
-      </c>
-      <c r="J678" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K678">
-        <v>1</v>
-      </c>
-      <c r="L678" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="M678" t="str">
-        <v>2026-08-05 09:05:10</v>
-      </c>
-      <c r="N678" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O678" s="1">
-        <v>0</v>
-      </c>
-      <c r="P678" t="str">
-        <v/>
-      </c>
-      <c r="Q678" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R678" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="str">
-        <v>T260804-00025</v>
-      </c>
-      <c r="B679" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C679" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D679" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E679" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F679">
-        <v>0</v>
-      </c>
-      <c r="G679" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H679" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I679" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J679" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K679">
-        <v>1</v>
-      </c>
-      <c r="L679" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M679" t="str">
-        <v>2026-08-04 20:32:35</v>
-      </c>
-      <c r="N679" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O679" s="1">
-        <v>0</v>
-      </c>
-      <c r="P679" t="str">
-        <v/>
-      </c>
-      <c r="Q679" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R679" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="str">
-        <v>T260804-00024</v>
-      </c>
-      <c r="B680" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C680" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D680" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E680" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F680">
-        <v>0</v>
-      </c>
-      <c r="G680" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H680" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I680" t="str">
-        <v>2026-08-05 08:00</v>
-      </c>
-      <c r="J680" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K680">
-        <v>1</v>
-      </c>
-      <c r="L680" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M680" t="str">
-        <v>2026-08-04 20:32:12</v>
-      </c>
-      <c r="N680" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O680" s="1">
-        <v>0</v>
-      </c>
-      <c r="P680" t="str">
-        <v/>
-      </c>
-      <c r="Q680" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R680" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="str">
-        <v>T260804-00023</v>
-      </c>
-      <c r="B681" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C681" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D681" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E681" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F681">
-        <v>1</v>
-      </c>
-      <c r="G681" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H681" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I681" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J681" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K681">
-        <v>1</v>
-      </c>
-      <c r="L681" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M681" t="str">
-        <v>2026-08-04 20:31:26</v>
-      </c>
-      <c r="N681" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O681" s="1">
-        <v>0</v>
-      </c>
-      <c r="P681" t="str">
-        <v/>
-      </c>
-      <c r="Q681" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R681" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="str">
-        <v>T260804-00022</v>
-      </c>
-      <c r="B682" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C682" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D682" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E682" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F682">
-        <v>0</v>
-      </c>
-      <c r="G682" t="str">
-        <v>안성ACP</v>
-      </c>
-      <c r="H682" t="str">
-        <v>경기 안성시 대덕면 중앙로 96-15 안성ACP</v>
-      </c>
-      <c r="I682" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J682" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K682">
-        <v>1</v>
-      </c>
-      <c r="L682" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M682" t="str">
-        <v>2026-08-04 20:30:56</v>
-      </c>
-      <c r="N682" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O682" s="1">
-        <v>0</v>
-      </c>
-      <c r="P682" t="str">
-        <v/>
-      </c>
-      <c r="Q682" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R682" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="str">
-        <v>T260804-00021</v>
-      </c>
-      <c r="B683" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C683" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D683" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E683" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F683">
-        <v>0</v>
-      </c>
-      <c r="G683" t="str">
-        <v>시흥ACP</v>
-      </c>
-      <c r="H683" t="str">
-        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
-      </c>
-      <c r="I683" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J683" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K683">
-        <v>1</v>
-      </c>
-      <c r="L683" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M683" t="str">
-        <v>2026-08-04 20:30:28</v>
-      </c>
-      <c r="N683" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O683" s="1">
-        <v>0</v>
-      </c>
-      <c r="P683" t="str">
-        <v/>
-      </c>
-      <c r="Q683" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R683" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="str">
-        <v>T260804-00020</v>
-      </c>
-      <c r="B684" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C684" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D684" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E684" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F684">
-        <v>0</v>
-      </c>
-      <c r="G684" t="str">
-        <v>부산ACP</v>
-      </c>
-      <c r="H684" t="str">
-        <v>부산 강서구 상덕로97번길 47 부산ACP</v>
-      </c>
-      <c r="I684" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J684" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K684">
-        <v>1</v>
-      </c>
-      <c r="L684" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M684" t="str">
-        <v>2026-08-04 20:29:48</v>
-      </c>
-      <c r="N684" s="1">
-        <v>450000</v>
-      </c>
-      <c r="O684" s="1">
-        <v>0</v>
-      </c>
-      <c r="P684" t="str">
-        <v/>
-      </c>
-      <c r="Q684" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R684" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="str">
-        <v>T260804-00019</v>
-      </c>
-      <c r="B685" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C685" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D685" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E685" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F685">
-        <v>0</v>
-      </c>
-      <c r="G685" t="str">
-        <v>대전중구ACP</v>
-      </c>
-      <c r="H685" t="str">
-        <v>대전 중구 보문산로77번길 8 대전중구ACP</v>
-      </c>
-      <c r="I685" t="str">
-        <v>2026-08-05 06:00</v>
-      </c>
-      <c r="J685" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K685">
-        <v>1</v>
-      </c>
-      <c r="L685" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M685" t="str">
-        <v>2026-08-04 20:14:33</v>
-      </c>
-      <c r="N685" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O685" s="1">
-        <v>0</v>
-      </c>
-      <c r="P685" t="str">
-        <v/>
-      </c>
-      <c r="Q685" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R685" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="str">
-        <v>T260804-00018</v>
-      </c>
-      <c r="B686" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C686" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D686" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E686" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F686">
-        <v>0</v>
-      </c>
-      <c r="G686" t="str">
-        <v>대전대덕ACP</v>
-      </c>
-      <c r="H686" t="str">
-        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
-      </c>
-      <c r="I686" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J686" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K686">
-        <v>1</v>
-      </c>
-      <c r="L686" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M686" t="str">
-        <v>2026-08-04 20:14:11</v>
-      </c>
-      <c r="N686" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O686" s="1">
-        <v>0</v>
-      </c>
-      <c r="P686" t="str">
-        <v/>
-      </c>
-      <c r="Q686" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R686" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="str">
-        <v>T260804-00017</v>
-      </c>
-      <c r="B687" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C687" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D687" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E687" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F687">
-        <v>1</v>
-      </c>
-      <c r="G687" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H687" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I687" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J687" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K687">
-        <v>1</v>
-      </c>
-      <c r="L687" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M687" t="str">
-        <v>2026-08-04 20:13:47</v>
-      </c>
-      <c r="N687" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O687" s="1">
-        <v>0</v>
-      </c>
-      <c r="P687" t="str">
-        <v/>
-      </c>
-      <c r="Q687" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R687" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="str">
-        <v>T260804-00016</v>
-      </c>
-      <c r="B688" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C688" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D688" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E688" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F688">
-        <v>0</v>
-      </c>
-      <c r="G688" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="H688" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="I688" t="str">
-        <v>2026-08-05 07:00</v>
-      </c>
-      <c r="J688" t="str">
-        <v>2.5톤 카고</v>
-      </c>
-      <c r="K688">
-        <v>1</v>
-      </c>
-      <c r="L688" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M688" t="str">
-        <v>2026-08-04 20:13:22</v>
-      </c>
-      <c r="N688" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O688" s="1">
-        <v>0</v>
-      </c>
-      <c r="P688" t="str">
-        <v/>
-      </c>
-      <c r="Q688" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R688" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="str">
-        <v>T260804-00015</v>
-      </c>
-      <c r="B689" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C689" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D689" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E689" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F689">
-        <v>0</v>
-      </c>
-      <c r="G689" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H689" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I689" t="str">
-        <v>2026-08-04 21:00</v>
-      </c>
-      <c r="J689" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K689">
-        <v>1</v>
-      </c>
-      <c r="L689" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M689" t="str">
-        <v>2026-08-04 20:11:31</v>
-      </c>
-      <c r="N689" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O689" s="1">
-        <v>0</v>
-      </c>
-      <c r="P689" t="str">
-        <v/>
-      </c>
-      <c r="Q689" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R689" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="str">
-        <v>T260804-00014</v>
-      </c>
-      <c r="B690" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C690" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D690" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E690" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F690">
-        <v>1</v>
-      </c>
-      <c r="G690" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H690" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I690" t="str">
-        <v>2026-08-04 22:00</v>
-      </c>
-      <c r="J690" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K690">
-        <v>1</v>
-      </c>
-      <c r="L690" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M690" t="str">
-        <v>2026-08-04 20:11:15</v>
-      </c>
-      <c r="N690" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O690" s="1">
-        <v>0</v>
-      </c>
-      <c r="P690" t="str">
-        <v/>
-      </c>
-      <c r="Q690" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R690" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="str">
-        <v>T260804-00013</v>
-      </c>
-      <c r="B691" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C691" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D691" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E691" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F691">
-        <v>0</v>
-      </c>
-      <c r="G691" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H691" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I691" t="str">
-        <v>2026-08-04 23:00</v>
-      </c>
-      <c r="J691" t="str">
-        <v>5톤 카고</v>
-      </c>
-      <c r="K691">
-        <v>1</v>
-      </c>
-      <c r="L691" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M691" t="str">
-        <v>2026-08-04 20:10:56</v>
-      </c>
-      <c r="N691" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O691" s="1">
-        <v>0</v>
-      </c>
-      <c r="P691" t="str">
-        <v/>
-      </c>
-      <c r="Q691" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R691" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="str">
-        <v>T260804-00012</v>
-      </c>
-      <c r="B692" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C692" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D692" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E692" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F692">
-        <v>0</v>
-      </c>
-      <c r="G692" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H692" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I692" t="str">
-        <v>2026-08-04 21:00</v>
-      </c>
-      <c r="J692" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K692">
-        <v>1</v>
-      </c>
-      <c r="L692" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M692" t="str">
-        <v>2026-08-04 20:10:40</v>
-      </c>
-      <c r="N692" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O692" s="1">
-        <v>0</v>
-      </c>
-      <c r="P692" t="str">
-        <v/>
-      </c>
-      <c r="Q692" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R692" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="str">
-        <v>T260804-00011</v>
-      </c>
-      <c r="B693" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C693" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D693" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E693" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F693">
-        <v>1</v>
-      </c>
-      <c r="G693" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H693" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I693" t="str">
-        <v>2026-08-04 22:00</v>
-      </c>
-      <c r="J693" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K693">
-        <v>1</v>
-      </c>
-      <c r="L693" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M693" t="str">
-        <v>2026-08-04 20:10:24</v>
-      </c>
-      <c r="N693" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O693" s="1">
-        <v>0</v>
-      </c>
-      <c r="P693" t="str">
-        <v/>
-      </c>
-      <c r="Q693" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R693" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="str">
-        <v>T260804-00010</v>
-      </c>
-      <c r="B694" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C694" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D694" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E694" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F694">
-        <v>1</v>
-      </c>
-      <c r="G694" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H694" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I694" t="str">
-        <v>2026-08-04 23:00</v>
-      </c>
-      <c r="J694" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K694">
-        <v>1</v>
-      </c>
-      <c r="L694" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M694" t="str">
-        <v>2026-08-04 20:07:49</v>
-      </c>
-      <c r="N694" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O694" s="1">
-        <v>0</v>
-      </c>
-      <c r="P694" t="str">
-        <v/>
-      </c>
-      <c r="Q694" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R694" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="str">
-        <v>T260804-00009</v>
-      </c>
-      <c r="B695" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C695" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D695" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E695" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F695">
-        <v>1</v>
-      </c>
-      <c r="G695" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H695" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I695" t="str">
-        <v>2026-08-04 22:00</v>
-      </c>
-      <c r="J695" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K695">
-        <v>1</v>
-      </c>
-      <c r="L695" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M695" t="str">
-        <v>2026-08-04 20:07:16</v>
-      </c>
-      <c r="N695" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O695" s="1">
-        <v>0</v>
-      </c>
-      <c r="P695" t="str">
-        <v/>
-      </c>
-      <c r="Q695" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R695" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="str">
-        <v>T260804-00008</v>
-      </c>
-      <c r="B696" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C696" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D696" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E696" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F696">
-        <v>1</v>
-      </c>
-      <c r="G696" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H696" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I696" t="str">
-        <v>2026-08-04 23:00</v>
-      </c>
-      <c r="J696" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K696">
-        <v>1</v>
-      </c>
-      <c r="L696" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M696" t="str">
-        <v>2026-08-04 20:06:56</v>
-      </c>
-      <c r="N696" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O696" s="1">
-        <v>0</v>
-      </c>
-      <c r="P696" t="str">
-        <v/>
-      </c>
-      <c r="Q696" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R696" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="str">
-        <v>T260804-00007</v>
-      </c>
-      <c r="B697" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C697" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D697" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E697" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F697">
-        <v>0</v>
-      </c>
-      <c r="G697" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H697" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I697" t="str">
-        <v>2026-08-04 21:00</v>
-      </c>
-      <c r="J697" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K697">
-        <v>1</v>
-      </c>
-      <c r="L697" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M697" t="str">
-        <v>2026-08-04 20:06:32</v>
-      </c>
-      <c r="N697" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O697" s="1">
-        <v>0</v>
-      </c>
-      <c r="P697" t="str">
-        <v/>
-      </c>
-      <c r="Q697" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R697" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="str">
-        <v>T260804-00006</v>
-      </c>
-      <c r="B698" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C698" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D698" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E698" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F698">
-        <v>0</v>
-      </c>
-      <c r="G698" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H698" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I698" t="str">
-        <v>2026-08-04 21:00</v>
-      </c>
-      <c r="J698" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K698">
-        <v>1</v>
-      </c>
-      <c r="L698" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M698" t="str">
-        <v>2026-08-04 20:06:08</v>
-      </c>
-      <c r="N698" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O698" s="1">
-        <v>0</v>
-      </c>
-      <c r="P698" t="str">
-        <v/>
-      </c>
-      <c r="Q698" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R698" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="str">
-        <v>T260804-00005</v>
-      </c>
-      <c r="B699" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C699" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D699" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E699" t="str">
-        <v>2026-08-04 19:00</v>
-      </c>
-      <c r="F699">
-        <v>1</v>
-      </c>
-      <c r="G699" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H699" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="I699" t="str">
-        <v>2026-08-04 23:00</v>
-      </c>
-      <c r="J699" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K699">
-        <v>1</v>
-      </c>
-      <c r="L699" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M699" t="str">
-        <v>2026-08-04 20:05:49</v>
-      </c>
-      <c r="N699" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O699" s="1">
-        <v>0</v>
-      </c>
-      <c r="P699" t="str">
-        <v/>
-      </c>
-      <c r="Q699" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R699" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="str">
-        <v>T260804-00004</v>
-      </c>
-      <c r="B700" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C700" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D700" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E700" t="str">
-        <v>2026-08-04 17:00</v>
-      </c>
-      <c r="F700">
-        <v>0</v>
-      </c>
-      <c r="G700" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H700" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I700" t="str">
-        <v>2026-08-04 18:00</v>
-      </c>
-      <c r="J700" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K700">
-        <v>1</v>
-      </c>
-      <c r="L700" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M700" t="str">
-        <v>2026-08-04 20:00:36</v>
-      </c>
-      <c r="N700" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O700" s="1">
-        <v>0</v>
-      </c>
-      <c r="P700" t="str">
-        <v/>
-      </c>
-      <c r="Q700" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R700" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="str">
-        <v>T260804-00003</v>
-      </c>
-      <c r="B701" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C701" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D701" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E701" t="str">
-        <v>2026-08-04 15:00</v>
-      </c>
-      <c r="F701">
-        <v>0</v>
-      </c>
-      <c r="G701" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H701" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I701" t="str">
-        <v>2026-08-04 16:00</v>
-      </c>
-      <c r="J701" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K701">
-        <v>1</v>
-      </c>
-      <c r="L701" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M701" t="str">
-        <v>2026-08-04 20:00:02</v>
-      </c>
-      <c r="N701" s="1">
-        <v>70000</v>
-      </c>
-      <c r="O701" s="1">
-        <v>0</v>
-      </c>
-      <c r="P701" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="Q701" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R701" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="str">
-        <v>T260804-00002</v>
-      </c>
-      <c r="B702" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C702" t="str">
-        <v>샤오미</v>
-      </c>
-      <c r="D702" t="str">
-        <v>경기 이천시 대월면 부필리 309 샤오미</v>
-      </c>
-      <c r="E702" t="str">
-        <v>2026-08-04 14:00</v>
-      </c>
-      <c r="F702">
-        <v>0</v>
-      </c>
-      <c r="G702" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H702" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I702" t="str">
-        <v>2026-08-04 15:00</v>
-      </c>
-      <c r="J702" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K702">
-        <v>1</v>
-      </c>
-      <c r="L702" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M702" t="str">
-        <v>2026-08-04 19:59:20</v>
-      </c>
-      <c r="N702" s="1">
-        <v>80000</v>
-      </c>
-      <c r="O702" s="1">
-        <v>0</v>
-      </c>
-      <c r="P702" t="str">
-        <v>거래처비용청구(3대)</v>
-      </c>
-      <c r="Q702" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R702" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="str">
-        <v>T260804-00001</v>
-      </c>
-      <c r="B703" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C703" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D703" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E703" t="str">
-        <v>2026-08-04 16:30</v>
-      </c>
-      <c r="F703">
-        <v>0</v>
-      </c>
-      <c r="G703" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H703" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I703" t="str">
-        <v>2026-08-04 18:00</v>
-      </c>
-      <c r="J703" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K703">
-        <v>1</v>
-      </c>
-      <c r="L703" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="M703" t="str">
-        <v>2026-08-04 15:46:27</v>
-      </c>
-      <c r="N703" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O703" s="1">
-        <v>0</v>
-      </c>
-      <c r="P703" t="str">
-        <v/>
-      </c>
-      <c r="Q703" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R703" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="str">
-        <v>T260803-00031</v>
-      </c>
-      <c r="B704" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C704" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D704" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E704" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F704">
-        <v>0</v>
-      </c>
-      <c r="G704" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H704" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I704" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J704" t="str">
-        <v>2.5톤 카고</v>
-      </c>
-      <c r="K704">
-        <v>1</v>
-      </c>
-      <c r="L704" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M704" t="str">
-        <v>2026-08-03 23:48:09</v>
-      </c>
-      <c r="N704" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O704" s="1">
-        <v>0</v>
-      </c>
-      <c r="P704" t="str">
-        <v/>
-      </c>
-      <c r="Q704" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R704" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="str">
-        <v>T260803-00030</v>
-      </c>
-      <c r="B705" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C705" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D705" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E705" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F705">
-        <v>0</v>
-      </c>
-      <c r="G705" t="str">
-        <v>춘천ACP</v>
-      </c>
-      <c r="H705" t="str">
-        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
-      </c>
-      <c r="I705" t="str">
-        <v>2026-08-04 08:00</v>
-      </c>
-      <c r="J705" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K705">
-        <v>1</v>
-      </c>
-      <c r="L705" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M705" t="str">
-        <v>2026-08-03 23:47:48</v>
-      </c>
-      <c r="N705" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O705" s="1">
-        <v>0</v>
-      </c>
-      <c r="P705" t="str">
-        <v/>
-      </c>
-      <c r="Q705" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R705" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="str">
-        <v>T260803-00029</v>
-      </c>
-      <c r="B706" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C706" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D706" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E706" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F706">
-        <v>0</v>
-      </c>
-      <c r="G706" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H706" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I706" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J706" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K706">
-        <v>1</v>
-      </c>
-      <c r="L706" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M706" t="str">
-        <v>2026-08-03 23:46:49</v>
-      </c>
-      <c r="N706" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O706" s="1">
-        <v>0</v>
-      </c>
-      <c r="P706" t="str">
-        <v/>
-      </c>
-      <c r="Q706" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R706" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="str">
-        <v>T260803-00028</v>
-      </c>
-      <c r="B707" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C707" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D707" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E707" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F707">
-        <v>1</v>
-      </c>
-      <c r="G707" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H707" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I707" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J707" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K707">
-        <v>1</v>
-      </c>
-      <c r="L707" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M707" t="str">
-        <v>2026-08-03 23:46:26</v>
-      </c>
-      <c r="N707" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O707" s="1">
-        <v>0</v>
-      </c>
-      <c r="P707" t="str">
-        <v/>
-      </c>
-      <c r="Q707" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R707" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="str">
-        <v>T260803-00027</v>
-      </c>
-      <c r="B708" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C708" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D708" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E708" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F708">
-        <v>0</v>
-      </c>
-      <c r="G708" t="str">
-        <v>안성ACP</v>
-      </c>
-      <c r="H708" t="str">
-        <v>경기 안성시 대덕면 중앙로 96-15 안성ACP</v>
-      </c>
-      <c r="I708" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J708" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K708">
-        <v>1</v>
-      </c>
-      <c r="L708" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M708" t="str">
-        <v>2026-08-03 23:45:59</v>
-      </c>
-      <c r="N708" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O708" s="1">
-        <v>0</v>
-      </c>
-      <c r="P708" t="str">
-        <v/>
-      </c>
-      <c r="Q708" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R708" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="str">
-        <v>T260803-00026</v>
-      </c>
-      <c r="B709" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C709" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D709" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E709" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F709">
-        <v>0</v>
-      </c>
-      <c r="G709" t="str">
-        <v>시흥ACP</v>
-      </c>
-      <c r="H709" t="str">
-        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
-      </c>
-      <c r="I709" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J709" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K709">
-        <v>1</v>
-      </c>
-      <c r="L709" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M709" t="str">
-        <v>2026-08-03 23:45:40</v>
-      </c>
-      <c r="N709" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O709" s="1">
-        <v>0</v>
-      </c>
-      <c r="P709" t="str">
-        <v/>
-      </c>
-      <c r="Q709" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R709" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="str">
-        <v>T260803-00025</v>
-      </c>
-      <c r="B710" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C710" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D710" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E710" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F710">
-        <v>2</v>
-      </c>
-      <c r="G710" t="str">
-        <v>속초ACP</v>
-      </c>
-      <c r="H710" t="str">
-        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
-      </c>
-      <c r="I710" t="str">
-        <v>2026-08-04 06:00</v>
-      </c>
-      <c r="J710" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K710">
-        <v>1</v>
-      </c>
-      <c r="L710" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M710" t="str">
-        <v>2026-08-03 23:45:13</v>
-      </c>
-      <c r="N710" s="1">
-        <v>330000</v>
-      </c>
-      <c r="O710" s="1">
-        <v>0</v>
-      </c>
-      <c r="P710" t="str">
-        <v/>
-      </c>
-      <c r="Q710" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R710" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="str">
-        <v>T260803-00024</v>
-      </c>
-      <c r="B711" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C711" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D711" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E711" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F711">
-        <v>0</v>
-      </c>
-      <c r="G711" t="str">
-        <v>서산ACP</v>
-      </c>
-      <c r="H711" t="str">
-        <v>충남 서산시 덕지천로 328-3 서산ACP</v>
-      </c>
-      <c r="I711" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J711" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K711">
-        <v>1</v>
-      </c>
-      <c r="L711" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M711" t="str">
-        <v>2026-08-03 23:44:40</v>
-      </c>
-      <c r="N711" s="1">
-        <v>130000</v>
-      </c>
-      <c r="O711" s="1">
-        <v>0</v>
-      </c>
-      <c r="P711" t="str">
-        <v/>
-      </c>
-      <c r="Q711" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R711" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="str">
-        <v>T260803-00023</v>
-      </c>
-      <c r="B712" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C712" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D712" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E712" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F712">
-        <v>0</v>
-      </c>
-      <c r="G712" t="str">
-        <v>부산ACP</v>
-      </c>
-      <c r="H712" t="str">
-        <v>부산 강서구 상덕로97번길 47 부산ACP</v>
-      </c>
-      <c r="I712" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J712" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K712">
-        <v>1</v>
-      </c>
-      <c r="L712" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M712" t="str">
-        <v>2026-08-03 23:44:17</v>
-      </c>
-      <c r="N712" s="1">
-        <v>450000</v>
-      </c>
-      <c r="O712" s="1">
-        <v>0</v>
-      </c>
-      <c r="P712" t="str">
-        <v/>
-      </c>
-      <c r="Q712" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R712" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="str">
-        <v>T260803-00022</v>
-      </c>
-      <c r="B713" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C713" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D713" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E713" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F713">
-        <v>0</v>
-      </c>
-      <c r="G713" t="str">
-        <v>대전중구ACP</v>
-      </c>
-      <c r="H713" t="str">
-        <v>대전 중구 보문산로77번길 8 대전중구ACP</v>
-      </c>
-      <c r="I713" t="str">
-        <v>2026-08-04 06:00</v>
-      </c>
-      <c r="J713" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K713">
-        <v>1</v>
-      </c>
-      <c r="L713" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M713" t="str">
-        <v>2026-08-03 23:43:56</v>
-      </c>
-      <c r="N713" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O713" s="1">
-        <v>0</v>
-      </c>
-      <c r="P713" t="str">
-        <v/>
-      </c>
-      <c r="Q713" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R713" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="str">
-        <v>T260803-00021</v>
-      </c>
-      <c r="B714" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C714" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D714" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E714" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F714">
-        <v>2</v>
-      </c>
-      <c r="G714" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H714" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I714" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J714" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K714">
-        <v>1</v>
-      </c>
-      <c r="L714" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M714" t="str">
-        <v>2026-08-03 23:43:37</v>
-      </c>
-      <c r="N714" s="1">
-        <v>320000</v>
-      </c>
-      <c r="O714" s="1">
-        <v>0</v>
-      </c>
-      <c r="P714" t="str">
-        <v/>
-      </c>
-      <c r="Q714" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R714" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="str">
-        <v>T260803-00020</v>
-      </c>
-      <c r="B715" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C715" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D715" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E715" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F715">
-        <v>0</v>
-      </c>
-      <c r="G715" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="H715" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="I715" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J715" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K715">
-        <v>1</v>
-      </c>
-      <c r="L715" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M715" t="str">
-        <v>2026-08-03 23:35:31</v>
-      </c>
-      <c r="N715" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O715" s="1">
-        <v>0</v>
-      </c>
-      <c r="P715" t="str">
-        <v/>
-      </c>
-      <c r="Q715" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R715" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="str">
-        <v>T260803-00019</v>
-      </c>
-      <c r="B716" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C716" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D716" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E716" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F716">
-        <v>0</v>
-      </c>
-      <c r="G716" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="H716" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="I716" t="str">
-        <v>2026-08-04 07:00</v>
-      </c>
-      <c r="J716" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K716">
-        <v>1</v>
-      </c>
-      <c r="L716" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M716" t="str">
-        <v>2026-08-03 23:34:40</v>
-      </c>
-      <c r="N716" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O716" s="1">
-        <v>0</v>
-      </c>
-      <c r="P716" t="str">
-        <v/>
-      </c>
-      <c r="Q716" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R716" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="str">
-        <v>T260803-00018</v>
-      </c>
-      <c r="B717" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C717" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D717" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E717" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F717">
-        <v>0</v>
-      </c>
-      <c r="G717" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H717" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I717" t="str">
-        <v>2026-08-03 21:00</v>
-      </c>
-      <c r="J717" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K717">
-        <v>1</v>
-      </c>
-      <c r="L717" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M717" t="str">
-        <v>2026-08-03 23:33:48</v>
-      </c>
-      <c r="N717" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O717" s="1">
-        <v>0</v>
-      </c>
-      <c r="P717" t="str">
-        <v/>
-      </c>
-      <c r="Q717" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R717" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="str">
-        <v>T260803-00017</v>
-      </c>
-      <c r="B718" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C718" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D718" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E718" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F718">
-        <v>1</v>
-      </c>
-      <c r="G718" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H718" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I718" t="str">
-        <v>2026-08-03 22:00</v>
-      </c>
-      <c r="J718" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K718">
-        <v>1</v>
-      </c>
-      <c r="L718" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M718" t="str">
-        <v>2026-08-03 23:33:33</v>
-      </c>
-      <c r="N718" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O718" s="1">
-        <v>0</v>
-      </c>
-      <c r="P718" t="str">
-        <v/>
-      </c>
-      <c r="Q718" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R718" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="str">
-        <v>T260803-00016</v>
-      </c>
-      <c r="B719" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C719" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D719" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E719" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F719">
-        <v>1</v>
-      </c>
-      <c r="G719" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H719" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I719" t="str">
-        <v>2026-08-03 23:00</v>
-      </c>
-      <c r="J719" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K719">
-        <v>1</v>
-      </c>
-      <c r="L719" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M719" t="str">
-        <v>2026-08-03 23:33:14</v>
-      </c>
-      <c r="N719" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O719" s="1">
-        <v>0</v>
-      </c>
-      <c r="P719" t="str">
-        <v/>
-      </c>
-      <c r="Q719" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R719" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="str">
-        <v>T260803-00015</v>
-      </c>
-      <c r="B720" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C720" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D720" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E720" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F720">
-        <v>0</v>
-      </c>
-      <c r="G720" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="H720" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="I720" t="str">
-        <v>2026-08-03 22:00</v>
-      </c>
-      <c r="J720" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K720">
-        <v>1</v>
-      </c>
-      <c r="L720" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M720" t="str">
-        <v>2026-08-03 23:32:56</v>
-      </c>
-      <c r="N720" s="1">
-        <v>230000</v>
-      </c>
-      <c r="O720" s="1">
-        <v>0</v>
-      </c>
-      <c r="P720" t="str">
-        <v/>
-      </c>
-      <c r="Q720" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R720" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="str">
-        <v>T260803-00014</v>
-      </c>
-      <c r="B721" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C721" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D721" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E721" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F721">
-        <v>0</v>
-      </c>
-      <c r="G721" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H721" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I721" t="str">
-        <v>2026-08-03 21:00</v>
-      </c>
-      <c r="J721" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K721">
-        <v>1</v>
-      </c>
-      <c r="L721" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M721" t="str">
-        <v>2026-08-03 23:32:42</v>
-      </c>
-      <c r="N721" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O721" s="1">
-        <v>0</v>
-      </c>
-      <c r="P721" t="str">
-        <v/>
-      </c>
-      <c r="Q721" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R721" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="str">
-        <v>T260803-00013</v>
-      </c>
-      <c r="B722" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C722" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D722" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E722" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F722">
-        <v>1</v>
-      </c>
-      <c r="G722" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H722" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I722" t="str">
-        <v>2026-08-03 22:00</v>
-      </c>
-      <c r="J722" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K722">
-        <v>1</v>
-      </c>
-      <c r="L722" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M722" t="str">
-        <v>2026-08-03 23:32:24</v>
-      </c>
-      <c r="N722" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O722" s="1">
-        <v>0</v>
-      </c>
-      <c r="P722" t="str">
-        <v/>
-      </c>
-      <c r="Q722" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R722" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="str">
-        <v>T260803-00012</v>
-      </c>
-      <c r="B723" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C723" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D723" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E723" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F723">
-        <v>0</v>
-      </c>
-      <c r="G723" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H723" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I723" t="str">
-        <v>2026-08-03 23:00</v>
-      </c>
-      <c r="J723" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K723">
-        <v>1</v>
-      </c>
-      <c r="L723" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M723" t="str">
-        <v>2026-08-03 23:32:00</v>
-      </c>
-      <c r="N723" s="1">
-        <v>490000</v>
-      </c>
-      <c r="O723" s="1">
-        <v>0</v>
-      </c>
-      <c r="P723" t="str">
-        <v/>
-      </c>
-      <c r="Q723" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R723" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="str">
-        <v>T260803-00011</v>
-      </c>
-      <c r="B724" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C724" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D724" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E724" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F724">
-        <v>0</v>
-      </c>
-      <c r="G724" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="H724" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="I724" t="str">
-        <v>2026-08-03 21:00</v>
-      </c>
-      <c r="J724" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K724">
-        <v>1</v>
-      </c>
-      <c r="L724" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M724" t="str">
-        <v>2026-08-03 23:31:43</v>
-      </c>
-      <c r="N724" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O724" s="1">
-        <v>0</v>
-      </c>
-      <c r="P724" t="str">
-        <v/>
-      </c>
-      <c r="Q724" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R724" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="str">
-        <v>T260803-00010</v>
-      </c>
-      <c r="B725" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C725" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D725" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E725" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F725">
-        <v>1</v>
-      </c>
-      <c r="G725" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H725" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I725" t="str">
-        <v>2026-08-03 22:00</v>
-      </c>
-      <c r="J725" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K725">
-        <v>1</v>
-      </c>
-      <c r="L725" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M725" t="str">
-        <v>2026-08-03 23:31:28</v>
-      </c>
-      <c r="N725" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O725" s="1">
-        <v>0</v>
-      </c>
-      <c r="P725" t="str">
-        <v/>
-      </c>
-      <c r="Q725" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R725" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="str">
-        <v>T260803-00009</v>
-      </c>
-      <c r="B726" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C726" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D726" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E726" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F726">
-        <v>0</v>
-      </c>
-      <c r="G726" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H726" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I726" t="str">
-        <v>2026-08-03 23:00</v>
-      </c>
-      <c r="J726" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K726">
-        <v>1</v>
-      </c>
-      <c r="L726" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M726" t="str">
-        <v>2026-08-03 23:31:08</v>
-      </c>
-      <c r="N726" s="1">
-        <v>420000</v>
-      </c>
-      <c r="O726" s="1">
-        <v>0</v>
-      </c>
-      <c r="P726" t="str">
-        <v/>
-      </c>
-      <c r="Q726" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R726" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="str">
-        <v>T260803-00008</v>
-      </c>
-      <c r="B727" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C727" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D727" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E727" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F727">
-        <v>1</v>
-      </c>
-      <c r="G727" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H727" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="I727" t="str">
-        <v>2026-08-03 23:00</v>
-      </c>
-      <c r="J727" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K727">
-        <v>1</v>
-      </c>
-      <c r="L727" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M727" t="str">
-        <v>2026-08-03 23:30:52</v>
-      </c>
-      <c r="N727" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O727" s="1">
-        <v>0</v>
-      </c>
-      <c r="P727" t="str">
-        <v/>
-      </c>
-      <c r="Q727" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R727" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="str">
-        <v>T260803-00007</v>
-      </c>
-      <c r="B728" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C728" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D728" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E728" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F728">
-        <v>0</v>
-      </c>
-      <c r="G728" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H728" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I728" t="str">
-        <v>2026-08-03 21:00</v>
-      </c>
-      <c r="J728" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K728">
-        <v>1</v>
-      </c>
-      <c r="L728" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M728" t="str">
-        <v>2026-08-03 22:51:56</v>
-      </c>
-      <c r="N728" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O728" s="1">
-        <v>0</v>
-      </c>
-      <c r="P728" t="str">
-        <v/>
-      </c>
-      <c r="Q728" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R728" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="str">
-        <v>T260803-00006</v>
-      </c>
-      <c r="B729" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C729" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D729" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E729" t="str">
-        <v>2026-08-03 19:00</v>
-      </c>
-      <c r="F729">
-        <v>1</v>
-      </c>
-      <c r="G729" t="str">
-        <v>강릉FDC</v>
-      </c>
-      <c r="H729" t="str">
-        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
-      </c>
-      <c r="I729" t="str">
-        <v>2026-08-03 23:00</v>
-      </c>
-      <c r="J729" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K729">
-        <v>1</v>
-      </c>
-      <c r="L729" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M729" t="str">
-        <v>2026-08-03 22:51:37</v>
-      </c>
-      <c r="N729" s="1">
-        <v>310000</v>
-      </c>
-      <c r="O729" s="1">
-        <v>0</v>
-      </c>
-      <c r="P729" t="str">
-        <v/>
-      </c>
-      <c r="Q729" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R729" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="str">
-        <v>T260803-00005</v>
-      </c>
-      <c r="B730" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C730" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D730" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E730" t="str">
-        <v>2026-08-03 17:50</v>
-      </c>
-      <c r="F730">
-        <v>0</v>
-      </c>
-      <c r="G730" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H730" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I730" t="str">
-        <v>2026-08-03 18:50</v>
-      </c>
-      <c r="J730" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K730">
-        <v>1</v>
-      </c>
-      <c r="L730" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M730" t="str">
-        <v>2026-08-03 22:47:04</v>
-      </c>
-      <c r="N730" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O730" s="1">
-        <v>0</v>
-      </c>
-      <c r="P730" t="str">
-        <v/>
-      </c>
-      <c r="Q730" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R730" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="str">
-        <v>T260803-00004</v>
-      </c>
-      <c r="B731" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C731" t="str">
-        <v>샤오미</v>
-      </c>
-      <c r="D731" t="str">
-        <v>경기 이천시 대월면 부필리 309 샤오미</v>
-      </c>
-      <c r="E731" t="str">
-        <v>2026-08-03 13:50</v>
-      </c>
-      <c r="F731">
-        <v>0</v>
-      </c>
-      <c r="G731" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H731" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I731" t="str">
-        <v>2026-08-03 14:50</v>
-      </c>
-      <c r="J731" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K731">
-        <v>1</v>
-      </c>
-      <c r="L731" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M731" t="str">
-        <v>2026-08-03 22:46:33</v>
-      </c>
-      <c r="N731" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O731" s="1">
-        <v>0</v>
-      </c>
-      <c r="P731" t="str">
-        <v>샤오미 외주사입고(11대)</v>
-      </c>
-      <c r="Q731" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R731" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="str">
-        <v>T260803-00003</v>
-      </c>
-      <c r="B732" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C732" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D732" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E732" t="str">
-        <v>2026-08-03 14:50</v>
-      </c>
-      <c r="F732">
-        <v>0</v>
-      </c>
-      <c r="G732" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H732" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I732" t="str">
-        <v>2026-08-03 15:50</v>
-      </c>
-      <c r="J732" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K732">
-        <v>1</v>
-      </c>
-      <c r="L732" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M732" t="str">
-        <v>2026-08-03 22:45:46</v>
-      </c>
-      <c r="N732" s="1">
-        <v>70000</v>
-      </c>
-      <c r="O732" s="1">
-        <v>0</v>
-      </c>
-      <c r="P732" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="Q732" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R732" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="str">
-        <v>T260803-00002</v>
-      </c>
-      <c r="B733" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C733" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D733" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E733" t="str">
-        <v>2026-08-03 10:00</v>
-      </c>
-      <c r="F733">
-        <v>0</v>
-      </c>
-      <c r="G733" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H733" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I733" t="str">
-        <v>2026-08-03 13:50</v>
-      </c>
-      <c r="J733" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K733">
-        <v>1</v>
-      </c>
-      <c r="L733" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M733" t="str">
-        <v>2026-08-03 22:45:01</v>
-      </c>
-      <c r="N733" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O733" s="1">
-        <v>0</v>
-      </c>
-      <c r="P733" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q733" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R733" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="str">
-        <v>T260803-00001</v>
-      </c>
-      <c r="B734" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C734" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D734" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E734" t="str">
-        <v>2026-08-03 16:30</v>
-      </c>
-      <c r="F734">
-        <v>0</v>
-      </c>
-      <c r="G734" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="H734" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I734" t="str">
-        <v>2026-08-03 18:00</v>
-      </c>
-      <c r="J734" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K734">
-        <v>1</v>
-      </c>
-      <c r="L734" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="M734" t="str">
-        <v>2026-08-03 15:39:18</v>
-      </c>
-      <c r="N734" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O734" s="1">
-        <v>0</v>
-      </c>
-      <c r="P734" t="str">
-        <v/>
-      </c>
-      <c r="Q734" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R734" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R734"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R632"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R632"/>
+  <dimension ref="A1:R734"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,7 +440,7 @@
         <v>T260904-00030</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260904-00029</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260904-00028</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260904-00027</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260904-00026</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260904-00025</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260904-00024</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260904-00023</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260904-00022</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260904-00021</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260904-00020</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260904-00019</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260904-00018</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260904-00017</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260904-00016</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260904-00015</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260904-00014</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>화성FDC</v>
@@ -1392,7 +1392,7 @@
         <v>T260904-00013</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>샤오미 집하장</v>
@@ -1448,7 +1448,7 @@
         <v>T260904-00012</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>아이베</v>
@@ -1504,7 +1504,7 @@
         <v>T260904-00011</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>듀오백</v>
@@ -35771,9 +35771,5721 @@
         <v>일코전자</v>
       </c>
     </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>T260805-00046</v>
+      </c>
+      <c r="B633" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C633" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D633" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E633" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F633">
+        <v>0</v>
+      </c>
+      <c r="G633" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H633" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I633" t="str">
+        <v>2026-08-06 07:00</v>
+      </c>
+      <c r="J633" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K633">
+        <v>1</v>
+      </c>
+      <c r="L633" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M633" t="str">
+        <v>2026-08-05 20:55:08</v>
+      </c>
+      <c r="N633" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O633" s="1">
+        <v>0</v>
+      </c>
+      <c r="P633" t="str">
+        <v/>
+      </c>
+      <c r="Q633" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R633" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>T260805-00045</v>
+      </c>
+      <c r="B634" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C634" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D634" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E634" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F634">
+        <v>0</v>
+      </c>
+      <c r="G634" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H634" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I634" t="str">
+        <v>2026-08-06 08:00</v>
+      </c>
+      <c r="J634" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K634">
+        <v>1</v>
+      </c>
+      <c r="L634" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M634" t="str">
+        <v>2026-08-05 20:54:48</v>
+      </c>
+      <c r="N634" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O634" s="1">
+        <v>0</v>
+      </c>
+      <c r="P634" t="str">
+        <v/>
+      </c>
+      <c r="Q634" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R634" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>T260805-00044</v>
+      </c>
+      <c r="B635" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C635" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D635" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E635" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F635">
+        <v>0</v>
+      </c>
+      <c r="G635" t="str">
+        <v>용인ACP</v>
+      </c>
+      <c r="H635" t="str">
+        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
+      </c>
+      <c r="I635" t="str">
+        <v>2026-08-06 06:00</v>
+      </c>
+      <c r="J635" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K635">
+        <v>1</v>
+      </c>
+      <c r="L635" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M635" t="str">
+        <v>2026-08-05 20:54:28</v>
+      </c>
+      <c r="N635" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O635" s="1">
+        <v>0</v>
+      </c>
+      <c r="P635" t="str">
+        <v/>
+      </c>
+      <c r="Q635" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R635" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>T260805-00043</v>
+      </c>
+      <c r="B636" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C636" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D636" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E636" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F636">
+        <v>1</v>
+      </c>
+      <c r="G636" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H636" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I636" t="str">
+        <v>2026-08-06 07:00</v>
+      </c>
+      <c r="J636" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K636">
+        <v>1</v>
+      </c>
+      <c r="L636" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M636" t="str">
+        <v>2026-08-05 20:54:08</v>
+      </c>
+      <c r="N636" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O636" s="1">
+        <v>0</v>
+      </c>
+      <c r="P636" t="str">
+        <v/>
+      </c>
+      <c r="Q636" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R636" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>T260805-00042</v>
+      </c>
+      <c r="B637" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C637" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D637" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E637" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F637">
+        <v>0</v>
+      </c>
+      <c r="G637" t="str">
+        <v>시흥ACP</v>
+      </c>
+      <c r="H637" t="str">
+        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
+      </c>
+      <c r="I637" t="str">
+        <v>2026-08-06 07:00</v>
+      </c>
+      <c r="J637" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K637">
+        <v>1</v>
+      </c>
+      <c r="L637" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M637" t="str">
+        <v>2026-08-05 20:49:31</v>
+      </c>
+      <c r="N637" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O637" s="1">
+        <v>0</v>
+      </c>
+      <c r="P637" t="str">
+        <v/>
+      </c>
+      <c r="Q637" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R637" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>T260805-00041</v>
+      </c>
+      <c r="B638" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C638" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D638" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E638" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F638">
+        <v>1</v>
+      </c>
+      <c r="G638" t="str">
+        <v>속초ACP</v>
+      </c>
+      <c r="H638" t="str">
+        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
+      </c>
+      <c r="I638" t="str">
+        <v>2026-08-06 06:00</v>
+      </c>
+      <c r="J638" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K638">
+        <v>1</v>
+      </c>
+      <c r="L638" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M638" t="str">
+        <v>2026-08-05 20:48:08</v>
+      </c>
+      <c r="N638" s="1">
+        <v>270000</v>
+      </c>
+      <c r="O638" s="1">
+        <v>0</v>
+      </c>
+      <c r="P638" t="str">
+        <v/>
+      </c>
+      <c r="Q638" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R638" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>T260805-00040</v>
+      </c>
+      <c r="B639" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C639" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D639" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E639" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F639">
+        <v>0</v>
+      </c>
+      <c r="G639" t="str">
+        <v>서산ACP</v>
+      </c>
+      <c r="H639" t="str">
+        <v>충남 서산시 덕지천로 328-3 서산ACP</v>
+      </c>
+      <c r="I639" t="str">
+        <v>2026-08-06 07:00</v>
+      </c>
+      <c r="J639" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K639">
+        <v>1</v>
+      </c>
+      <c r="L639" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M639" t="str">
+        <v>2026-08-05 20:47:41</v>
+      </c>
+      <c r="N639" s="1">
+        <v>130000</v>
+      </c>
+      <c r="O639" s="1">
+        <v>0</v>
+      </c>
+      <c r="P639" t="str">
+        <v/>
+      </c>
+      <c r="Q639" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R639" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>T260805-00039</v>
+      </c>
+      <c r="B640" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C640" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D640" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E640" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F640">
+        <v>1</v>
+      </c>
+      <c r="G640" t="str">
+        <v>대전대덕ACP</v>
+      </c>
+      <c r="H640" t="str">
+        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
+      </c>
+      <c r="I640" t="str">
+        <v>2026-08-06 07:00</v>
+      </c>
+      <c r="J640" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K640">
+        <v>1</v>
+      </c>
+      <c r="L640" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M640" t="str">
+        <v>2026-08-05 20:47:22</v>
+      </c>
+      <c r="N640" s="1">
+        <v>220000</v>
+      </c>
+      <c r="O640" s="1">
+        <v>0</v>
+      </c>
+      <c r="P640" t="str">
+        <v/>
+      </c>
+      <c r="Q640" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R640" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>T260805-00038</v>
+      </c>
+      <c r="B641" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C641" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D641" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E641" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F641">
+        <v>1</v>
+      </c>
+      <c r="G641" t="str">
+        <v>원주ACP</v>
+      </c>
+      <c r="H641" t="str">
+        <v>강원특별자치도 원주시 단구동 683-3 원주ACP</v>
+      </c>
+      <c r="I641" t="str">
+        <v>2026-08-05 22:00</v>
+      </c>
+      <c r="J641" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K641">
+        <v>1</v>
+      </c>
+      <c r="L641" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M641" t="str">
+        <v>2026-08-05 20:45:34</v>
+      </c>
+      <c r="N641" s="1">
+        <v>170000</v>
+      </c>
+      <c r="O641" s="1">
+        <v>0</v>
+      </c>
+      <c r="P641" t="str">
+        <v/>
+      </c>
+      <c r="Q641" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R641" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>T260805-00037</v>
+      </c>
+      <c r="B642" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C642" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D642" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E642" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F642">
+        <v>1</v>
+      </c>
+      <c r="G642" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H642" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I642" t="str">
+        <v>2026-08-06 07:00</v>
+      </c>
+      <c r="J642" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K642">
+        <v>1</v>
+      </c>
+      <c r="L642" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M642" t="str">
+        <v>2026-08-05 20:44:44</v>
+      </c>
+      <c r="N642" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O642" s="1">
+        <v>0</v>
+      </c>
+      <c r="P642" t="str">
+        <v/>
+      </c>
+      <c r="Q642" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R642" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>T260805-00036</v>
+      </c>
+      <c r="B643" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C643" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D643" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E643" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F643">
+        <v>0</v>
+      </c>
+      <c r="G643" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H643" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I643" t="str">
+        <v>2026-08-06 08:00</v>
+      </c>
+      <c r="J643" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K643">
+        <v>1</v>
+      </c>
+      <c r="L643" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M643" t="str">
+        <v>2026-08-05 20:43:06</v>
+      </c>
+      <c r="N643" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O643" s="1">
+        <v>0</v>
+      </c>
+      <c r="P643" t="str">
+        <v/>
+      </c>
+      <c r="Q643" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R643" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>T260805-00035</v>
+      </c>
+      <c r="B644" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C644" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D644" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E644" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F644">
+        <v>0</v>
+      </c>
+      <c r="G644" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H644" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I644" t="str">
+        <v>2026-08-06 07:00</v>
+      </c>
+      <c r="J644" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K644">
+        <v>1</v>
+      </c>
+      <c r="L644" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M644" t="str">
+        <v>2026-08-05 20:42:44</v>
+      </c>
+      <c r="N644" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O644" s="1">
+        <v>0</v>
+      </c>
+      <c r="P644" t="str">
+        <v/>
+      </c>
+      <c r="Q644" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R644" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>T260805-00034</v>
+      </c>
+      <c r="B645" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C645" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D645" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E645" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F645">
+        <v>0</v>
+      </c>
+      <c r="G645" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H645" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I645" t="str">
+        <v>2026-08-05 21:00</v>
+      </c>
+      <c r="J645" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K645">
+        <v>1</v>
+      </c>
+      <c r="L645" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M645" t="str">
+        <v>2026-08-05 20:41:24</v>
+      </c>
+      <c r="N645" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O645" s="1">
+        <v>0</v>
+      </c>
+      <c r="P645" t="str">
+        <v/>
+      </c>
+      <c r="Q645" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R645" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>T260805-00033</v>
+      </c>
+      <c r="B646" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C646" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D646" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E646" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F646">
+        <v>1</v>
+      </c>
+      <c r="G646" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H646" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I646" t="str">
+        <v>2026-08-05 22:00</v>
+      </c>
+      <c r="J646" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K646">
+        <v>1</v>
+      </c>
+      <c r="L646" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M646" t="str">
+        <v>2026-08-05 20:41:08</v>
+      </c>
+      <c r="N646" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O646" s="1">
+        <v>0</v>
+      </c>
+      <c r="P646" t="str">
+        <v/>
+      </c>
+      <c r="Q646" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R646" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>T260805-00032</v>
+      </c>
+      <c r="B647" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C647" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D647" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E647" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F647">
+        <v>1</v>
+      </c>
+      <c r="G647" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H647" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I647" t="str">
+        <v>2026-08-05 22:00</v>
+      </c>
+      <c r="J647" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K647">
+        <v>1</v>
+      </c>
+      <c r="L647" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M647" t="str">
+        <v>2026-08-05 20:40:46</v>
+      </c>
+      <c r="N647" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O647" s="1">
+        <v>0</v>
+      </c>
+      <c r="P647" t="str">
+        <v/>
+      </c>
+      <c r="Q647" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R647" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>T260805-00031</v>
+      </c>
+      <c r="B648" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C648" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D648" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E648" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F648">
+        <v>0</v>
+      </c>
+      <c r="G648" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H648" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I648" t="str">
+        <v>2026-08-05 21:00</v>
+      </c>
+      <c r="J648" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K648">
+        <v>1</v>
+      </c>
+      <c r="L648" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M648" t="str">
+        <v>2026-08-05 20:40:24</v>
+      </c>
+      <c r="N648" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O648" s="1">
+        <v>0</v>
+      </c>
+      <c r="P648" t="str">
+        <v/>
+      </c>
+      <c r="Q648" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R648" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>T260805-00030</v>
+      </c>
+      <c r="B649" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C649" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D649" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E649" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F649">
+        <v>1</v>
+      </c>
+      <c r="G649" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H649" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I649" t="str">
+        <v>2026-08-05 22:00</v>
+      </c>
+      <c r="J649" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K649">
+        <v>1</v>
+      </c>
+      <c r="L649" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M649" t="str">
+        <v>2026-08-05 20:40:08</v>
+      </c>
+      <c r="N649" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O649" s="1">
+        <v>0</v>
+      </c>
+      <c r="P649" t="str">
+        <v/>
+      </c>
+      <c r="Q649" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R649" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
+        <v>T260805-00029</v>
+      </c>
+      <c r="B650" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C650" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D650" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E650" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F650">
+        <v>0</v>
+      </c>
+      <c r="G650" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H650" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I650" t="str">
+        <v>2026-08-05 23:00</v>
+      </c>
+      <c r="J650" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K650">
+        <v>1</v>
+      </c>
+      <c r="L650" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M650" t="str">
+        <v>2026-08-05 20:39:22</v>
+      </c>
+      <c r="N650" s="1">
+        <v>490000</v>
+      </c>
+      <c r="O650" s="1">
+        <v>0</v>
+      </c>
+      <c r="P650" t="str">
+        <v/>
+      </c>
+      <c r="Q650" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R650" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>T260805-00028</v>
+      </c>
+      <c r="B651" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C651" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D651" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E651" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F651">
+        <v>0</v>
+      </c>
+      <c r="G651" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H651" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I651" t="str">
+        <v>2026-08-05 21:00</v>
+      </c>
+      <c r="J651" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K651">
+        <v>1</v>
+      </c>
+      <c r="L651" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M651" t="str">
+        <v>2026-08-05 20:39:04</v>
+      </c>
+      <c r="N651" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O651" s="1">
+        <v>0</v>
+      </c>
+      <c r="P651" t="str">
+        <v/>
+      </c>
+      <c r="Q651" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R651" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>T260805-00027</v>
+      </c>
+      <c r="B652" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C652" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D652" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E652" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F652">
+        <v>0</v>
+      </c>
+      <c r="G652" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H652" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I652" t="str">
+        <v>2026-08-05 21:00</v>
+      </c>
+      <c r="J652" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K652">
+        <v>1</v>
+      </c>
+      <c r="L652" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M652" t="str">
+        <v>2026-08-05 20:38:50</v>
+      </c>
+      <c r="N652" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O652" s="1">
+        <v>0</v>
+      </c>
+      <c r="P652" t="str">
+        <v/>
+      </c>
+      <c r="Q652" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R652" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>T260805-00026</v>
+      </c>
+      <c r="B653" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C653" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D653" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E653" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F653">
+        <v>1</v>
+      </c>
+      <c r="G653" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H653" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I653" t="str">
+        <v>2026-08-05 23:00</v>
+      </c>
+      <c r="J653" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K653">
+        <v>1</v>
+      </c>
+      <c r="L653" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M653" t="str">
+        <v>2026-08-05 20:38:02</v>
+      </c>
+      <c r="N653" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O653" s="1">
+        <v>0</v>
+      </c>
+      <c r="P653" t="str">
+        <v/>
+      </c>
+      <c r="Q653" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R653" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>T260805-00025</v>
+      </c>
+      <c r="B654" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C654" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D654" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E654" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F654">
+        <v>0</v>
+      </c>
+      <c r="G654" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H654" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I654" t="str">
+        <v>2026-08-05 21:00</v>
+      </c>
+      <c r="J654" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K654">
+        <v>1</v>
+      </c>
+      <c r="L654" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M654" t="str">
+        <v>2026-08-05 20:37:42</v>
+      </c>
+      <c r="N654" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O654" s="1">
+        <v>0</v>
+      </c>
+      <c r="P654" t="str">
+        <v/>
+      </c>
+      <c r="Q654" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R654" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>T260805-00024</v>
+      </c>
+      <c r="B655" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C655" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D655" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E655" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F655">
+        <v>1</v>
+      </c>
+      <c r="G655" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H655" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="I655" t="str">
+        <v>2026-08-05 23:00</v>
+      </c>
+      <c r="J655" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K655">
+        <v>1</v>
+      </c>
+      <c r="L655" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M655" t="str">
+        <v>2026-08-05 20:37:26</v>
+      </c>
+      <c r="N655" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O655" s="1">
+        <v>0</v>
+      </c>
+      <c r="P655" t="str">
+        <v/>
+      </c>
+      <c r="Q655" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R655" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>T260805-00023</v>
+      </c>
+      <c r="B656" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C656" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D656" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E656" t="str">
+        <v>2026-08-05 19:00</v>
+      </c>
+      <c r="F656">
+        <v>1</v>
+      </c>
+      <c r="G656" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="H656" t="str">
+        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="I656" t="str">
+        <v>2026-08-05 23:00</v>
+      </c>
+      <c r="J656" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K656">
+        <v>1</v>
+      </c>
+      <c r="L656" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M656" t="str">
+        <v>2026-08-05 20:37:05</v>
+      </c>
+      <c r="N656" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O656" s="1">
+        <v>0</v>
+      </c>
+      <c r="P656" t="str">
+        <v/>
+      </c>
+      <c r="Q656" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R656" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>T260805-00022</v>
+      </c>
+      <c r="B657" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C657" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D657" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E657" t="str">
+        <v>2026-08-05 17:30</v>
+      </c>
+      <c r="F657">
+        <v>0</v>
+      </c>
+      <c r="G657" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H657" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I657" t="str">
+        <v>2026-08-05 18:30</v>
+      </c>
+      <c r="J657" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K657">
+        <v>1</v>
+      </c>
+      <c r="L657" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M657" t="str">
+        <v>2026-08-05 20:32:13</v>
+      </c>
+      <c r="N657" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O657" s="1">
+        <v>0</v>
+      </c>
+      <c r="P657" t="str">
+        <v/>
+      </c>
+      <c r="Q657" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R657" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
+        <v>T260805-00021</v>
+      </c>
+      <c r="B658" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C658" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="D658" t="str">
+        <v>경기 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="E658" t="str">
+        <v>2026-08-05 21:30</v>
+      </c>
+      <c r="F658">
+        <v>0</v>
+      </c>
+      <c r="G658" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H658" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I658" t="str">
+        <v>2026-08-05 23:30</v>
+      </c>
+      <c r="J658" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K658">
+        <v>1</v>
+      </c>
+      <c r="L658" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M658" t="str">
+        <v>2026-08-05 20:31:41</v>
+      </c>
+      <c r="N658" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O658" s="1">
+        <v>0</v>
+      </c>
+      <c r="P658" t="str">
+        <v>공파렛이동</v>
+      </c>
+      <c r="Q658" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R658" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
+        <v>T260805-00020</v>
+      </c>
+      <c r="B659" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C659" t="str">
+        <v>샤오미</v>
+      </c>
+      <c r="D659" t="str">
+        <v>경기 이천시 대월면 부필리 309 샤오미</v>
+      </c>
+      <c r="E659" t="str">
+        <v>2026-08-05 14:30</v>
+      </c>
+      <c r="F659">
+        <v>0</v>
+      </c>
+      <c r="G659" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H659" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I659" t="str">
+        <v>2026-08-05 15:30</v>
+      </c>
+      <c r="J659" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K659">
+        <v>1</v>
+      </c>
+      <c r="L659" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M659" t="str">
+        <v>2026-08-05 20:30:39</v>
+      </c>
+      <c r="N659" s="1">
+        <v>80000</v>
+      </c>
+      <c r="O659" s="1">
+        <v>0</v>
+      </c>
+      <c r="P659" t="str">
+        <v>거래처비용청구(2대)</v>
+      </c>
+      <c r="Q659" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R659" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>T260805-00019</v>
+      </c>
+      <c r="B660" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C660" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D660" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E660" t="str">
+        <v>2026-08-05 14:30</v>
+      </c>
+      <c r="F660">
+        <v>0</v>
+      </c>
+      <c r="G660" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H660" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I660" t="str">
+        <v>2026-08-05 15:30</v>
+      </c>
+      <c r="J660" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K660">
+        <v>1</v>
+      </c>
+      <c r="L660" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M660" t="str">
+        <v>2026-08-05 20:29:36</v>
+      </c>
+      <c r="N660" s="1">
+        <v>70000</v>
+      </c>
+      <c r="O660" s="1">
+        <v>0</v>
+      </c>
+      <c r="P660" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="Q660" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R660" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>T260805-00018</v>
+      </c>
+      <c r="B661" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C661" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D661" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E661" t="str">
+        <v>2026-08-05 10:30</v>
+      </c>
+      <c r="F661">
+        <v>0</v>
+      </c>
+      <c r="G661" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H661" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I661" t="str">
+        <v>2026-08-05 13:30</v>
+      </c>
+      <c r="J661" t="str">
+        <v>1.5톤 윙바디</v>
+      </c>
+      <c r="K661">
+        <v>1</v>
+      </c>
+      <c r="L661" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M661" t="str">
+        <v>2026-08-05 20:28:50</v>
+      </c>
+      <c r="N661" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O661" s="1">
+        <v>0</v>
+      </c>
+      <c r="P661" t="str">
+        <v>듀오백외주사입고</v>
+      </c>
+      <c r="Q661" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R661" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>T260805-00017</v>
+      </c>
+      <c r="B662" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C662" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D662" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E662" t="str">
+        <v>2026-08-05 18:00</v>
+      </c>
+      <c r="F662">
+        <v>0</v>
+      </c>
+      <c r="G662" t="str">
+        <v>인천 하이마트 물류</v>
+      </c>
+      <c r="H662" t="str">
+        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
+      </c>
+      <c r="I662" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J662" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K662">
+        <v>1</v>
+      </c>
+      <c r="L662" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M662" t="str">
+        <v>2026-08-05 17:06:03</v>
+      </c>
+      <c r="N662" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O662" s="1">
+        <v>0</v>
+      </c>
+      <c r="P662" t="str">
+        <v>일코전자 인천 하이마트 물류</v>
+      </c>
+      <c r="Q662" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R662" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>T260805-00016</v>
+      </c>
+      <c r="B663" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C663" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D663" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E663" t="str">
+        <v>2026-08-05 17:30</v>
+      </c>
+      <c r="F663">
+        <v>0</v>
+      </c>
+      <c r="G663" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="H663" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="I663" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J663" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K663">
+        <v>1</v>
+      </c>
+      <c r="L663" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M663" t="str">
+        <v>2026-08-05 17:05:09</v>
+      </c>
+      <c r="N663" s="1">
+        <v>220000</v>
+      </c>
+      <c r="O663" s="1">
+        <v>0</v>
+      </c>
+      <c r="P663" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="Q663" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R663" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>T260805-00015</v>
+      </c>
+      <c r="B664" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C664" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D664" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E664" t="str">
+        <v>2026-08-05 16:40</v>
+      </c>
+      <c r="F664">
+        <v>0</v>
+      </c>
+      <c r="G664" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="H664" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="I664" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J664" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K664">
+        <v>1</v>
+      </c>
+      <c r="L664" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M664" t="str">
+        <v>2026-08-05 16:12:42</v>
+      </c>
+      <c r="N664" s="1">
+        <v>220000</v>
+      </c>
+      <c r="O664" s="1">
+        <v>0</v>
+      </c>
+      <c r="P664" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="Q664" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R664" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>T260805-00014</v>
+      </c>
+      <c r="B665" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C665" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D665" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E665" t="str">
+        <v>2026-08-05 17:30</v>
+      </c>
+      <c r="F665">
+        <v>0</v>
+      </c>
+      <c r="G665" t="str">
+        <v>마산 하이마트 물류</v>
+      </c>
+      <c r="H665" t="str">
+        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
+      </c>
+      <c r="I665" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J665" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K665">
+        <v>1</v>
+      </c>
+      <c r="L665" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M665" t="str">
+        <v>2026-08-05 16:05:16</v>
+      </c>
+      <c r="N665" s="1">
+        <v>460000</v>
+      </c>
+      <c r="O665" s="1">
+        <v>0</v>
+      </c>
+      <c r="P665" t="str">
+        <v>일코 마산 하이마트 물류</v>
+      </c>
+      <c r="Q665" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R665" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>T260805-00013</v>
+      </c>
+      <c r="B666" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C666" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D666" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E666" t="str">
+        <v>2026-08-05 16:30</v>
+      </c>
+      <c r="F666">
+        <v>0</v>
+      </c>
+      <c r="G666" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H666" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I666" t="str">
+        <v>2026-08-05 18:00</v>
+      </c>
+      <c r="J666" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K666">
+        <v>1</v>
+      </c>
+      <c r="L666" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="M666" t="str">
+        <v>2026-08-05 15:59:59</v>
+      </c>
+      <c r="N666" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O666" s="1">
+        <v>0</v>
+      </c>
+      <c r="P666" t="str">
+        <v/>
+      </c>
+      <c r="Q666" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R666" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>T260805-00012</v>
+      </c>
+      <c r="B667" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C667" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D667" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E667" t="str">
+        <v>2026-08-05 16:00</v>
+      </c>
+      <c r="F667">
+        <v>0</v>
+      </c>
+      <c r="G667" t="str">
+        <v>대구 하이마트 물류</v>
+      </c>
+      <c r="H667" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="I667" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J667" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K667">
+        <v>1</v>
+      </c>
+      <c r="L667" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M667" t="str">
+        <v>2026-08-05 15:15:47</v>
+      </c>
+      <c r="N667" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O667" s="1">
+        <v>0</v>
+      </c>
+      <c r="P667" t="str">
+        <v>일코전자 대구 하이마트 물류</v>
+      </c>
+      <c r="Q667" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R667" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>T260805-00011</v>
+      </c>
+      <c r="B668" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C668" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D668" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E668" t="str">
+        <v>2026-08-05 15:20</v>
+      </c>
+      <c r="F668">
+        <v>0</v>
+      </c>
+      <c r="G668" t="str">
+        <v>파주 하이마트 물류</v>
+      </c>
+      <c r="H668" t="str">
+        <v>경기 파주시 탄현면 월롱산로 296 파주 하이마트 물류</v>
+      </c>
+      <c r="I668" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J668" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K668">
+        <v>1</v>
+      </c>
+      <c r="L668" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M668" t="str">
+        <v>2026-08-05 15:00:25</v>
+      </c>
+      <c r="N668" s="1">
+        <v>280000</v>
+      </c>
+      <c r="O668" s="1">
+        <v>0</v>
+      </c>
+      <c r="P668" t="str">
+        <v>일코전자 파주 하이마트 물류</v>
+      </c>
+      <c r="Q668" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R668" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>T260805-00010</v>
+      </c>
+      <c r="B669" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C669" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D669" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E669" t="str">
+        <v>2026-08-05 14:30</v>
+      </c>
+      <c r="F669">
+        <v>0</v>
+      </c>
+      <c r="G669" t="str">
+        <v>마산 하이마트 물류</v>
+      </c>
+      <c r="H669" t="str">
+        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
+      </c>
+      <c r="I669" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J669" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K669">
+        <v>1</v>
+      </c>
+      <c r="L669" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M669" t="str">
+        <v>2026-08-05 14:27:45</v>
+      </c>
+      <c r="N669" s="1">
+        <v>440000</v>
+      </c>
+      <c r="O669" s="1">
+        <v>0</v>
+      </c>
+      <c r="P669" t="str">
+        <v>일코 마산 하이마트 물류</v>
+      </c>
+      <c r="Q669" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R669" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
+        <v>T260805-00009</v>
+      </c>
+      <c r="B670" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C670" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D670" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E670" t="str">
+        <v>2026-08-05 02:30</v>
+      </c>
+      <c r="F670">
+        <v>0</v>
+      </c>
+      <c r="G670" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="H670" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="I670" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J670" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K670">
+        <v>1</v>
+      </c>
+      <c r="L670" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M670" t="str">
+        <v>2026-08-05 14:27:13</v>
+      </c>
+      <c r="N670" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O670" s="1">
+        <v>0</v>
+      </c>
+      <c r="P670" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="Q670" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R670" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>T260805-00008</v>
+      </c>
+      <c r="B671" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C671" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D671" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E671" t="str">
+        <v>2026-08-05 15:30</v>
+      </c>
+      <c r="F671">
+        <v>0</v>
+      </c>
+      <c r="G671" t="str">
+        <v>광주 하이마트 물류</v>
+      </c>
+      <c r="H671" t="str">
+        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
+      </c>
+      <c r="I671" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J671" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K671">
+        <v>1</v>
+      </c>
+      <c r="L671" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M671" t="str">
+        <v>2026-08-05 13:23:42</v>
+      </c>
+      <c r="N671" s="1">
+        <v>400000</v>
+      </c>
+      <c r="O671" s="1">
+        <v>0</v>
+      </c>
+      <c r="P671" t="str">
+        <v>일코 광주 하이마트 물류</v>
+      </c>
+      <c r="Q671" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R671" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>T260805-00007</v>
+      </c>
+      <c r="B672" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C672" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="D672" t="str">
+        <v>광주 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="E672" t="str">
+        <v>2026-08-02 07:00</v>
+      </c>
+      <c r="F672">
+        <v>0</v>
+      </c>
+      <c r="G672" t="str">
+        <v>진주FDC</v>
+      </c>
+      <c r="H672" t="str">
+        <v>경남 진주시 지수면 승산리 163-1 진주FDC</v>
+      </c>
+      <c r="I672" t="str">
+        <v>2026-08-02 10:00</v>
+      </c>
+      <c r="J672" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K672">
+        <v>1</v>
+      </c>
+      <c r="L672" t="str">
+        <v>임서혁</v>
+      </c>
+      <c r="M672" t="str">
+        <v>2026-08-05 11:05:41</v>
+      </c>
+      <c r="N672" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O672" s="1">
+        <v>0</v>
+      </c>
+      <c r="P672" t="str">
+        <v>광주fdcㅡ진주fdc 에어컨파렛</v>
+      </c>
+      <c r="Q672" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R672" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>T260805-00006</v>
+      </c>
+      <c r="B673" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C673" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="D673" t="str">
+        <v>경남 창원시 의창구 동읍 노연리 30-4 창원FDC</v>
+      </c>
+      <c r="E673" t="str">
+        <v>2026-08-04 13:00</v>
+      </c>
+      <c r="F673">
+        <v>0</v>
+      </c>
+      <c r="G673" t="str">
+        <v>진주FDC</v>
+      </c>
+      <c r="H673" t="str">
+        <v>경남 진주시 지수면 승산리 163-1 진주FDC</v>
+      </c>
+      <c r="I673" t="str">
+        <v>2026-08-05 15:00</v>
+      </c>
+      <c r="J673" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K673">
+        <v>1</v>
+      </c>
+      <c r="L673" t="str">
+        <v>임서혁</v>
+      </c>
+      <c r="M673" t="str">
+        <v>2026-08-05 11:04:27</v>
+      </c>
+      <c r="N673" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O673" s="1">
+        <v>0</v>
+      </c>
+      <c r="P673" t="str">
+        <v>창원fdcㅡ진주fdc 1톤카고 에어컨</v>
+      </c>
+      <c r="Q673" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R673" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>T260805-00005</v>
+      </c>
+      <c r="B674" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C674" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D674" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E674" t="str">
+        <v>2026-08-05 15:00</v>
+      </c>
+      <c r="F674">
+        <v>0</v>
+      </c>
+      <c r="G674" t="str">
+        <v>대구 하이마트 물류</v>
+      </c>
+      <c r="H674" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="I674" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J674" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K674">
+        <v>1</v>
+      </c>
+      <c r="L674" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M674" t="str">
+        <v>2026-08-05 10:17:17</v>
+      </c>
+      <c r="N674" s="1">
+        <v>340000</v>
+      </c>
+      <c r="O674" s="1">
+        <v>0</v>
+      </c>
+      <c r="P674" t="str">
+        <v>일코전자 대구 하이마트 물류</v>
+      </c>
+      <c r="Q674" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R674" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>T260805-00004</v>
+      </c>
+      <c r="B675" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C675" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D675" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E675" t="str">
+        <v>2026-08-05 15:00</v>
+      </c>
+      <c r="F675">
+        <v>0</v>
+      </c>
+      <c r="G675" t="str">
+        <v>광주 하이마트 물류</v>
+      </c>
+      <c r="H675" t="str">
+        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
+      </c>
+      <c r="I675" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J675" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K675">
+        <v>1</v>
+      </c>
+      <c r="L675" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M675" t="str">
+        <v>2026-08-05 09:11:17</v>
+      </c>
+      <c r="N675" s="1">
+        <v>380000</v>
+      </c>
+      <c r="O675" s="1">
+        <v>0</v>
+      </c>
+      <c r="P675" t="str">
+        <v>일코 광주 하이마트 물류</v>
+      </c>
+      <c r="Q675" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R675" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>T260805-00003</v>
+      </c>
+      <c r="B676" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C676" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D676" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E676" t="str">
+        <v>2026-08-05 14:00</v>
+      </c>
+      <c r="F676">
+        <v>0</v>
+      </c>
+      <c r="G676" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H676" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I676" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J676" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="K676">
+        <v>1</v>
+      </c>
+      <c r="L676" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M676" t="str">
+        <v>2026-08-05 09:10:38</v>
+      </c>
+      <c r="N676" s="1">
+        <v>380000</v>
+      </c>
+      <c r="O676" s="1">
+        <v>0</v>
+      </c>
+      <c r="P676" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q676" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R676" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>T260805-00002</v>
+      </c>
+      <c r="B677" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C677" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D677" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E677" t="str">
+        <v>2026-08-05 11:00</v>
+      </c>
+      <c r="F677">
+        <v>0</v>
+      </c>
+      <c r="G677" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="H677" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="I677" t="str">
+        <v>2026-08-06 09:00</v>
+      </c>
+      <c r="J677" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K677">
+        <v>1</v>
+      </c>
+      <c r="L677" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="M677" t="str">
+        <v>2026-08-05 09:09:57</v>
+      </c>
+      <c r="N677" s="1">
+        <v>440000</v>
+      </c>
+      <c r="O677" s="1">
+        <v>0</v>
+      </c>
+      <c r="P677" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="Q677" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R677" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>T260805-00001</v>
+      </c>
+      <c r="B678" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C678" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D678" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E678" t="str">
+        <v>2026-08-05 09:00</v>
+      </c>
+      <c r="F678">
+        <v>0</v>
+      </c>
+      <c r="G678" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H678" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I678" t="str">
+        <v>2026-08-05 10:00</v>
+      </c>
+      <c r="J678" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K678">
+        <v>1</v>
+      </c>
+      <c r="L678" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="M678" t="str">
+        <v>2026-08-05 09:05:10</v>
+      </c>
+      <c r="N678" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O678" s="1">
+        <v>0</v>
+      </c>
+      <c r="P678" t="str">
+        <v/>
+      </c>
+      <c r="Q678" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R678" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>T260804-00025</v>
+      </c>
+      <c r="B679" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C679" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D679" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E679" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F679">
+        <v>0</v>
+      </c>
+      <c r="G679" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H679" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I679" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J679" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K679">
+        <v>1</v>
+      </c>
+      <c r="L679" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M679" t="str">
+        <v>2026-08-04 20:32:35</v>
+      </c>
+      <c r="N679" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O679" s="1">
+        <v>0</v>
+      </c>
+      <c r="P679" t="str">
+        <v/>
+      </c>
+      <c r="Q679" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R679" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>T260804-00024</v>
+      </c>
+      <c r="B680" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C680" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D680" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E680" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F680">
+        <v>0</v>
+      </c>
+      <c r="G680" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H680" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I680" t="str">
+        <v>2026-08-05 08:00</v>
+      </c>
+      <c r="J680" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K680">
+        <v>1</v>
+      </c>
+      <c r="L680" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M680" t="str">
+        <v>2026-08-04 20:32:12</v>
+      </c>
+      <c r="N680" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O680" s="1">
+        <v>0</v>
+      </c>
+      <c r="P680" t="str">
+        <v/>
+      </c>
+      <c r="Q680" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R680" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>T260804-00023</v>
+      </c>
+      <c r="B681" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C681" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D681" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E681" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F681">
+        <v>1</v>
+      </c>
+      <c r="G681" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H681" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I681" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J681" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K681">
+        <v>1</v>
+      </c>
+      <c r="L681" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M681" t="str">
+        <v>2026-08-04 20:31:26</v>
+      </c>
+      <c r="N681" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O681" s="1">
+        <v>0</v>
+      </c>
+      <c r="P681" t="str">
+        <v/>
+      </c>
+      <c r="Q681" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R681" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>T260804-00022</v>
+      </c>
+      <c r="B682" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C682" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D682" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E682" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F682">
+        <v>0</v>
+      </c>
+      <c r="G682" t="str">
+        <v>안성ACP</v>
+      </c>
+      <c r="H682" t="str">
+        <v>경기 안성시 대덕면 중앙로 96-15 안성ACP</v>
+      </c>
+      <c r="I682" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J682" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K682">
+        <v>1</v>
+      </c>
+      <c r="L682" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M682" t="str">
+        <v>2026-08-04 20:30:56</v>
+      </c>
+      <c r="N682" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O682" s="1">
+        <v>0</v>
+      </c>
+      <c r="P682" t="str">
+        <v/>
+      </c>
+      <c r="Q682" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R682" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>T260804-00021</v>
+      </c>
+      <c r="B683" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C683" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D683" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E683" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F683">
+        <v>0</v>
+      </c>
+      <c r="G683" t="str">
+        <v>시흥ACP</v>
+      </c>
+      <c r="H683" t="str">
+        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
+      </c>
+      <c r="I683" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J683" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K683">
+        <v>1</v>
+      </c>
+      <c r="L683" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M683" t="str">
+        <v>2026-08-04 20:30:28</v>
+      </c>
+      <c r="N683" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O683" s="1">
+        <v>0</v>
+      </c>
+      <c r="P683" t="str">
+        <v/>
+      </c>
+      <c r="Q683" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R683" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>T260804-00020</v>
+      </c>
+      <c r="B684" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C684" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D684" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E684" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F684">
+        <v>0</v>
+      </c>
+      <c r="G684" t="str">
+        <v>부산ACP</v>
+      </c>
+      <c r="H684" t="str">
+        <v>부산 강서구 상덕로97번길 47 부산ACP</v>
+      </c>
+      <c r="I684" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J684" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K684">
+        <v>1</v>
+      </c>
+      <c r="L684" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M684" t="str">
+        <v>2026-08-04 20:29:48</v>
+      </c>
+      <c r="N684" s="1">
+        <v>450000</v>
+      </c>
+      <c r="O684" s="1">
+        <v>0</v>
+      </c>
+      <c r="P684" t="str">
+        <v/>
+      </c>
+      <c r="Q684" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R684" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>T260804-00019</v>
+      </c>
+      <c r="B685" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C685" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D685" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E685" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F685">
+        <v>0</v>
+      </c>
+      <c r="G685" t="str">
+        <v>대전중구ACP</v>
+      </c>
+      <c r="H685" t="str">
+        <v>대전 중구 보문산로77번길 8 대전중구ACP</v>
+      </c>
+      <c r="I685" t="str">
+        <v>2026-08-05 06:00</v>
+      </c>
+      <c r="J685" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K685">
+        <v>1</v>
+      </c>
+      <c r="L685" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M685" t="str">
+        <v>2026-08-04 20:14:33</v>
+      </c>
+      <c r="N685" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O685" s="1">
+        <v>0</v>
+      </c>
+      <c r="P685" t="str">
+        <v/>
+      </c>
+      <c r="Q685" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R685" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>T260804-00018</v>
+      </c>
+      <c r="B686" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C686" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D686" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E686" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F686">
+        <v>0</v>
+      </c>
+      <c r="G686" t="str">
+        <v>대전대덕ACP</v>
+      </c>
+      <c r="H686" t="str">
+        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
+      </c>
+      <c r="I686" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J686" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K686">
+        <v>1</v>
+      </c>
+      <c r="L686" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M686" t="str">
+        <v>2026-08-04 20:14:11</v>
+      </c>
+      <c r="N686" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O686" s="1">
+        <v>0</v>
+      </c>
+      <c r="P686" t="str">
+        <v/>
+      </c>
+      <c r="Q686" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R686" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>T260804-00017</v>
+      </c>
+      <c r="B687" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C687" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D687" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E687" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F687">
+        <v>1</v>
+      </c>
+      <c r="G687" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H687" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I687" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J687" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K687">
+        <v>1</v>
+      </c>
+      <c r="L687" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M687" t="str">
+        <v>2026-08-04 20:13:47</v>
+      </c>
+      <c r="N687" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O687" s="1">
+        <v>0</v>
+      </c>
+      <c r="P687" t="str">
+        <v/>
+      </c>
+      <c r="Q687" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R687" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>T260804-00016</v>
+      </c>
+      <c r="B688" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C688" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D688" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E688" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F688">
+        <v>0</v>
+      </c>
+      <c r="G688" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H688" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I688" t="str">
+        <v>2026-08-05 07:00</v>
+      </c>
+      <c r="J688" t="str">
+        <v>2.5톤 카고</v>
+      </c>
+      <c r="K688">
+        <v>1</v>
+      </c>
+      <c r="L688" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M688" t="str">
+        <v>2026-08-04 20:13:22</v>
+      </c>
+      <c r="N688" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O688" s="1">
+        <v>0</v>
+      </c>
+      <c r="P688" t="str">
+        <v/>
+      </c>
+      <c r="Q688" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R688" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>T260804-00015</v>
+      </c>
+      <c r="B689" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C689" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D689" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E689" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F689">
+        <v>0</v>
+      </c>
+      <c r="G689" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H689" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I689" t="str">
+        <v>2026-08-04 21:00</v>
+      </c>
+      <c r="J689" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K689">
+        <v>1</v>
+      </c>
+      <c r="L689" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M689" t="str">
+        <v>2026-08-04 20:11:31</v>
+      </c>
+      <c r="N689" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O689" s="1">
+        <v>0</v>
+      </c>
+      <c r="P689" t="str">
+        <v/>
+      </c>
+      <c r="Q689" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R689" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>T260804-00014</v>
+      </c>
+      <c r="B690" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C690" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D690" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E690" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F690">
+        <v>1</v>
+      </c>
+      <c r="G690" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H690" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I690" t="str">
+        <v>2026-08-04 22:00</v>
+      </c>
+      <c r="J690" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K690">
+        <v>1</v>
+      </c>
+      <c r="L690" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M690" t="str">
+        <v>2026-08-04 20:11:15</v>
+      </c>
+      <c r="N690" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O690" s="1">
+        <v>0</v>
+      </c>
+      <c r="P690" t="str">
+        <v/>
+      </c>
+      <c r="Q690" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R690" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>T260804-00013</v>
+      </c>
+      <c r="B691" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C691" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D691" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E691" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F691">
+        <v>0</v>
+      </c>
+      <c r="G691" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H691" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I691" t="str">
+        <v>2026-08-04 23:00</v>
+      </c>
+      <c r="J691" t="str">
+        <v>5톤 카고</v>
+      </c>
+      <c r="K691">
+        <v>1</v>
+      </c>
+      <c r="L691" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M691" t="str">
+        <v>2026-08-04 20:10:56</v>
+      </c>
+      <c r="N691" s="1">
+        <v>360000</v>
+      </c>
+      <c r="O691" s="1">
+        <v>0</v>
+      </c>
+      <c r="P691" t="str">
+        <v/>
+      </c>
+      <c r="Q691" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R691" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>T260804-00012</v>
+      </c>
+      <c r="B692" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C692" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D692" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E692" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F692">
+        <v>0</v>
+      </c>
+      <c r="G692" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H692" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I692" t="str">
+        <v>2026-08-04 21:00</v>
+      </c>
+      <c r="J692" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K692">
+        <v>1</v>
+      </c>
+      <c r="L692" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M692" t="str">
+        <v>2026-08-04 20:10:40</v>
+      </c>
+      <c r="N692" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O692" s="1">
+        <v>0</v>
+      </c>
+      <c r="P692" t="str">
+        <v/>
+      </c>
+      <c r="Q692" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R692" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
+        <v>T260804-00011</v>
+      </c>
+      <c r="B693" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C693" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D693" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E693" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F693">
+        <v>1</v>
+      </c>
+      <c r="G693" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H693" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I693" t="str">
+        <v>2026-08-04 22:00</v>
+      </c>
+      <c r="J693" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K693">
+        <v>1</v>
+      </c>
+      <c r="L693" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M693" t="str">
+        <v>2026-08-04 20:10:24</v>
+      </c>
+      <c r="N693" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O693" s="1">
+        <v>0</v>
+      </c>
+      <c r="P693" t="str">
+        <v/>
+      </c>
+      <c r="Q693" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R693" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>T260804-00010</v>
+      </c>
+      <c r="B694" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C694" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D694" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E694" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F694">
+        <v>1</v>
+      </c>
+      <c r="G694" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H694" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I694" t="str">
+        <v>2026-08-04 23:00</v>
+      </c>
+      <c r="J694" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K694">
+        <v>1</v>
+      </c>
+      <c r="L694" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M694" t="str">
+        <v>2026-08-04 20:07:49</v>
+      </c>
+      <c r="N694" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O694" s="1">
+        <v>0</v>
+      </c>
+      <c r="P694" t="str">
+        <v/>
+      </c>
+      <c r="Q694" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R694" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>T260804-00009</v>
+      </c>
+      <c r="B695" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C695" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D695" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E695" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F695">
+        <v>1</v>
+      </c>
+      <c r="G695" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H695" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I695" t="str">
+        <v>2026-08-04 22:00</v>
+      </c>
+      <c r="J695" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K695">
+        <v>1</v>
+      </c>
+      <c r="L695" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M695" t="str">
+        <v>2026-08-04 20:07:16</v>
+      </c>
+      <c r="N695" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O695" s="1">
+        <v>0</v>
+      </c>
+      <c r="P695" t="str">
+        <v/>
+      </c>
+      <c r="Q695" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R695" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>T260804-00008</v>
+      </c>
+      <c r="B696" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C696" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D696" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E696" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F696">
+        <v>1</v>
+      </c>
+      <c r="G696" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H696" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I696" t="str">
+        <v>2026-08-04 23:00</v>
+      </c>
+      <c r="J696" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K696">
+        <v>1</v>
+      </c>
+      <c r="L696" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M696" t="str">
+        <v>2026-08-04 20:06:56</v>
+      </c>
+      <c r="N696" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O696" s="1">
+        <v>0</v>
+      </c>
+      <c r="P696" t="str">
+        <v/>
+      </c>
+      <c r="Q696" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R696" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>T260804-00007</v>
+      </c>
+      <c r="B697" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C697" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D697" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E697" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F697">
+        <v>0</v>
+      </c>
+      <c r="G697" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H697" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I697" t="str">
+        <v>2026-08-04 21:00</v>
+      </c>
+      <c r="J697" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K697">
+        <v>1</v>
+      </c>
+      <c r="L697" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M697" t="str">
+        <v>2026-08-04 20:06:32</v>
+      </c>
+      <c r="N697" s="1">
+        <v>90000</v>
+      </c>
+      <c r="O697" s="1">
+        <v>0</v>
+      </c>
+      <c r="P697" t="str">
+        <v/>
+      </c>
+      <c r="Q697" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R697" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>T260804-00006</v>
+      </c>
+      <c r="B698" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C698" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D698" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E698" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F698">
+        <v>0</v>
+      </c>
+      <c r="G698" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H698" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I698" t="str">
+        <v>2026-08-04 21:00</v>
+      </c>
+      <c r="J698" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K698">
+        <v>1</v>
+      </c>
+      <c r="L698" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M698" t="str">
+        <v>2026-08-04 20:06:08</v>
+      </c>
+      <c r="N698" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O698" s="1">
+        <v>0</v>
+      </c>
+      <c r="P698" t="str">
+        <v/>
+      </c>
+      <c r="Q698" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R698" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>T260804-00005</v>
+      </c>
+      <c r="B699" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C699" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D699" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E699" t="str">
+        <v>2026-08-04 19:00</v>
+      </c>
+      <c r="F699">
+        <v>1</v>
+      </c>
+      <c r="G699" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H699" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="I699" t="str">
+        <v>2026-08-04 23:00</v>
+      </c>
+      <c r="J699" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K699">
+        <v>1</v>
+      </c>
+      <c r="L699" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M699" t="str">
+        <v>2026-08-04 20:05:49</v>
+      </c>
+      <c r="N699" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O699" s="1">
+        <v>0</v>
+      </c>
+      <c r="P699" t="str">
+        <v/>
+      </c>
+      <c r="Q699" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R699" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
+        <v>T260804-00004</v>
+      </c>
+      <c r="B700" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C700" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D700" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E700" t="str">
+        <v>2026-08-04 17:00</v>
+      </c>
+      <c r="F700">
+        <v>0</v>
+      </c>
+      <c r="G700" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H700" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I700" t="str">
+        <v>2026-08-04 18:00</v>
+      </c>
+      <c r="J700" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K700">
+        <v>1</v>
+      </c>
+      <c r="L700" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M700" t="str">
+        <v>2026-08-04 20:00:36</v>
+      </c>
+      <c r="N700" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O700" s="1">
+        <v>0</v>
+      </c>
+      <c r="P700" t="str">
+        <v/>
+      </c>
+      <c r="Q700" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R700" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>T260804-00003</v>
+      </c>
+      <c r="B701" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C701" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D701" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E701" t="str">
+        <v>2026-08-04 15:00</v>
+      </c>
+      <c r="F701">
+        <v>0</v>
+      </c>
+      <c r="G701" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H701" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I701" t="str">
+        <v>2026-08-04 16:00</v>
+      </c>
+      <c r="J701" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K701">
+        <v>1</v>
+      </c>
+      <c r="L701" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M701" t="str">
+        <v>2026-08-04 20:00:02</v>
+      </c>
+      <c r="N701" s="1">
+        <v>70000</v>
+      </c>
+      <c r="O701" s="1">
+        <v>0</v>
+      </c>
+      <c r="P701" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="Q701" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R701" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>T260804-00002</v>
+      </c>
+      <c r="B702" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C702" t="str">
+        <v>샤오미</v>
+      </c>
+      <c r="D702" t="str">
+        <v>경기 이천시 대월면 부필리 309 샤오미</v>
+      </c>
+      <c r="E702" t="str">
+        <v>2026-08-04 14:00</v>
+      </c>
+      <c r="F702">
+        <v>0</v>
+      </c>
+      <c r="G702" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H702" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I702" t="str">
+        <v>2026-08-04 15:00</v>
+      </c>
+      <c r="J702" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K702">
+        <v>1</v>
+      </c>
+      <c r="L702" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M702" t="str">
+        <v>2026-08-04 19:59:20</v>
+      </c>
+      <c r="N702" s="1">
+        <v>80000</v>
+      </c>
+      <c r="O702" s="1">
+        <v>0</v>
+      </c>
+      <c r="P702" t="str">
+        <v>거래처비용청구(3대)</v>
+      </c>
+      <c r="Q702" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R702" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>T260804-00001</v>
+      </c>
+      <c r="B703" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C703" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D703" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E703" t="str">
+        <v>2026-08-04 16:30</v>
+      </c>
+      <c r="F703">
+        <v>0</v>
+      </c>
+      <c r="G703" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H703" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I703" t="str">
+        <v>2026-08-04 18:00</v>
+      </c>
+      <c r="J703" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K703">
+        <v>1</v>
+      </c>
+      <c r="L703" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="M703" t="str">
+        <v>2026-08-04 15:46:27</v>
+      </c>
+      <c r="N703" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O703" s="1">
+        <v>0</v>
+      </c>
+      <c r="P703" t="str">
+        <v/>
+      </c>
+      <c r="Q703" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R703" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>T260803-00031</v>
+      </c>
+      <c r="B704" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C704" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D704" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E704" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F704">
+        <v>0</v>
+      </c>
+      <c r="G704" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="H704" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="I704" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J704" t="str">
+        <v>2.5톤 카고</v>
+      </c>
+      <c r="K704">
+        <v>1</v>
+      </c>
+      <c r="L704" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M704" t="str">
+        <v>2026-08-03 23:48:09</v>
+      </c>
+      <c r="N704" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O704" s="1">
+        <v>0</v>
+      </c>
+      <c r="P704" t="str">
+        <v/>
+      </c>
+      <c r="Q704" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R704" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
+        <v>T260803-00030</v>
+      </c>
+      <c r="B705" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C705" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D705" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E705" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F705">
+        <v>0</v>
+      </c>
+      <c r="G705" t="str">
+        <v>춘천ACP</v>
+      </c>
+      <c r="H705" t="str">
+        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
+      </c>
+      <c r="I705" t="str">
+        <v>2026-08-04 08:00</v>
+      </c>
+      <c r="J705" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K705">
+        <v>1</v>
+      </c>
+      <c r="L705" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M705" t="str">
+        <v>2026-08-03 23:47:48</v>
+      </c>
+      <c r="N705" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O705" s="1">
+        <v>0</v>
+      </c>
+      <c r="P705" t="str">
+        <v/>
+      </c>
+      <c r="Q705" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R705" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
+        <v>T260803-00029</v>
+      </c>
+      <c r="B706" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C706" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D706" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E706" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F706">
+        <v>0</v>
+      </c>
+      <c r="G706" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="H706" t="str">
+        <v>인천 부평구 안남로433번길 19 인천ACP</v>
+      </c>
+      <c r="I706" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J706" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K706">
+        <v>1</v>
+      </c>
+      <c r="L706" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M706" t="str">
+        <v>2026-08-03 23:46:49</v>
+      </c>
+      <c r="N706" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O706" s="1">
+        <v>0</v>
+      </c>
+      <c r="P706" t="str">
+        <v/>
+      </c>
+      <c r="Q706" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R706" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
+        <v>T260803-00028</v>
+      </c>
+      <c r="B707" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C707" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D707" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E707" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F707">
+        <v>1</v>
+      </c>
+      <c r="G707" t="str">
+        <v>화성ACP</v>
+      </c>
+      <c r="H707" t="str">
+        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
+      </c>
+      <c r="I707" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J707" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K707">
+        <v>1</v>
+      </c>
+      <c r="L707" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M707" t="str">
+        <v>2026-08-03 23:46:26</v>
+      </c>
+      <c r="N707" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O707" s="1">
+        <v>0</v>
+      </c>
+      <c r="P707" t="str">
+        <v/>
+      </c>
+      <c r="Q707" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R707" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="str">
+        <v>T260803-00027</v>
+      </c>
+      <c r="B708" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C708" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D708" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E708" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F708">
+        <v>0</v>
+      </c>
+      <c r="G708" t="str">
+        <v>안성ACP</v>
+      </c>
+      <c r="H708" t="str">
+        <v>경기 안성시 대덕면 중앙로 96-15 안성ACP</v>
+      </c>
+      <c r="I708" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J708" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K708">
+        <v>1</v>
+      </c>
+      <c r="L708" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M708" t="str">
+        <v>2026-08-03 23:45:59</v>
+      </c>
+      <c r="N708" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O708" s="1">
+        <v>0</v>
+      </c>
+      <c r="P708" t="str">
+        <v/>
+      </c>
+      <c r="Q708" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R708" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="str">
+        <v>T260803-00026</v>
+      </c>
+      <c r="B709" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C709" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D709" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E709" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F709">
+        <v>0</v>
+      </c>
+      <c r="G709" t="str">
+        <v>시흥ACP</v>
+      </c>
+      <c r="H709" t="str">
+        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
+      </c>
+      <c r="I709" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J709" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K709">
+        <v>1</v>
+      </c>
+      <c r="L709" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M709" t="str">
+        <v>2026-08-03 23:45:40</v>
+      </c>
+      <c r="N709" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O709" s="1">
+        <v>0</v>
+      </c>
+      <c r="P709" t="str">
+        <v/>
+      </c>
+      <c r="Q709" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R709" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="str">
+        <v>T260803-00025</v>
+      </c>
+      <c r="B710" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C710" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D710" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E710" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F710">
+        <v>2</v>
+      </c>
+      <c r="G710" t="str">
+        <v>속초ACP</v>
+      </c>
+      <c r="H710" t="str">
+        <v>강원특별자치도 속초시 번영로 169 속초ACP</v>
+      </c>
+      <c r="I710" t="str">
+        <v>2026-08-04 06:00</v>
+      </c>
+      <c r="J710" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K710">
+        <v>1</v>
+      </c>
+      <c r="L710" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M710" t="str">
+        <v>2026-08-03 23:45:13</v>
+      </c>
+      <c r="N710" s="1">
+        <v>330000</v>
+      </c>
+      <c r="O710" s="1">
+        <v>0</v>
+      </c>
+      <c r="P710" t="str">
+        <v/>
+      </c>
+      <c r="Q710" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R710" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="str">
+        <v>T260803-00024</v>
+      </c>
+      <c r="B711" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C711" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D711" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E711" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F711">
+        <v>0</v>
+      </c>
+      <c r="G711" t="str">
+        <v>서산ACP</v>
+      </c>
+      <c r="H711" t="str">
+        <v>충남 서산시 덕지천로 328-3 서산ACP</v>
+      </c>
+      <c r="I711" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J711" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K711">
+        <v>1</v>
+      </c>
+      <c r="L711" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M711" t="str">
+        <v>2026-08-03 23:44:40</v>
+      </c>
+      <c r="N711" s="1">
+        <v>130000</v>
+      </c>
+      <c r="O711" s="1">
+        <v>0</v>
+      </c>
+      <c r="P711" t="str">
+        <v/>
+      </c>
+      <c r="Q711" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R711" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="str">
+        <v>T260803-00023</v>
+      </c>
+      <c r="B712" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C712" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D712" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E712" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F712">
+        <v>0</v>
+      </c>
+      <c r="G712" t="str">
+        <v>부산ACP</v>
+      </c>
+      <c r="H712" t="str">
+        <v>부산 강서구 상덕로97번길 47 부산ACP</v>
+      </c>
+      <c r="I712" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J712" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K712">
+        <v>1</v>
+      </c>
+      <c r="L712" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M712" t="str">
+        <v>2026-08-03 23:44:17</v>
+      </c>
+      <c r="N712" s="1">
+        <v>450000</v>
+      </c>
+      <c r="O712" s="1">
+        <v>0</v>
+      </c>
+      <c r="P712" t="str">
+        <v/>
+      </c>
+      <c r="Q712" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R712" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="str">
+        <v>T260803-00022</v>
+      </c>
+      <c r="B713" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C713" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D713" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E713" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F713">
+        <v>0</v>
+      </c>
+      <c r="G713" t="str">
+        <v>대전중구ACP</v>
+      </c>
+      <c r="H713" t="str">
+        <v>대전 중구 보문산로77번길 8 대전중구ACP</v>
+      </c>
+      <c r="I713" t="str">
+        <v>2026-08-04 06:00</v>
+      </c>
+      <c r="J713" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K713">
+        <v>1</v>
+      </c>
+      <c r="L713" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M713" t="str">
+        <v>2026-08-03 23:43:56</v>
+      </c>
+      <c r="N713" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O713" s="1">
+        <v>0</v>
+      </c>
+      <c r="P713" t="str">
+        <v/>
+      </c>
+      <c r="Q713" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R713" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="str">
+        <v>T260803-00021</v>
+      </c>
+      <c r="B714" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C714" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D714" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E714" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F714">
+        <v>2</v>
+      </c>
+      <c r="G714" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="H714" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="I714" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J714" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K714">
+        <v>1</v>
+      </c>
+      <c r="L714" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M714" t="str">
+        <v>2026-08-03 23:43:37</v>
+      </c>
+      <c r="N714" s="1">
+        <v>320000</v>
+      </c>
+      <c r="O714" s="1">
+        <v>0</v>
+      </c>
+      <c r="P714" t="str">
+        <v/>
+      </c>
+      <c r="Q714" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R714" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="str">
+        <v>T260803-00020</v>
+      </c>
+      <c r="B715" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C715" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D715" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E715" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F715">
+        <v>0</v>
+      </c>
+      <c r="G715" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="H715" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="I715" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J715" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K715">
+        <v>1</v>
+      </c>
+      <c r="L715" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M715" t="str">
+        <v>2026-08-03 23:35:31</v>
+      </c>
+      <c r="N715" s="1">
+        <v>180000</v>
+      </c>
+      <c r="O715" s="1">
+        <v>0</v>
+      </c>
+      <c r="P715" t="str">
+        <v/>
+      </c>
+      <c r="Q715" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R715" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="str">
+        <v>T260803-00019</v>
+      </c>
+      <c r="B716" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C716" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D716" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E716" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F716">
+        <v>0</v>
+      </c>
+      <c r="G716" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="H716" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="I716" t="str">
+        <v>2026-08-04 07:00</v>
+      </c>
+      <c r="J716" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="K716">
+        <v>1</v>
+      </c>
+      <c r="L716" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M716" t="str">
+        <v>2026-08-03 23:34:40</v>
+      </c>
+      <c r="N716" s="1">
+        <v>140000</v>
+      </c>
+      <c r="O716" s="1">
+        <v>0</v>
+      </c>
+      <c r="P716" t="str">
+        <v/>
+      </c>
+      <c r="Q716" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R716" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="str">
+        <v>T260803-00018</v>
+      </c>
+      <c r="B717" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C717" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D717" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E717" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F717">
+        <v>0</v>
+      </c>
+      <c r="G717" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="H717" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="I717" t="str">
+        <v>2026-08-03 21:00</v>
+      </c>
+      <c r="J717" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K717">
+        <v>1</v>
+      </c>
+      <c r="L717" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M717" t="str">
+        <v>2026-08-03 23:33:48</v>
+      </c>
+      <c r="N717" s="1">
+        <v>240000</v>
+      </c>
+      <c r="O717" s="1">
+        <v>0</v>
+      </c>
+      <c r="P717" t="str">
+        <v/>
+      </c>
+      <c r="Q717" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R717" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="str">
+        <v>T260803-00017</v>
+      </c>
+      <c r="B718" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C718" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D718" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E718" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F718">
+        <v>1</v>
+      </c>
+      <c r="G718" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="H718" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="I718" t="str">
+        <v>2026-08-03 22:00</v>
+      </c>
+      <c r="J718" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K718">
+        <v>1</v>
+      </c>
+      <c r="L718" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M718" t="str">
+        <v>2026-08-03 23:33:33</v>
+      </c>
+      <c r="N718" s="1">
+        <v>350000</v>
+      </c>
+      <c r="O718" s="1">
+        <v>0</v>
+      </c>
+      <c r="P718" t="str">
+        <v/>
+      </c>
+      <c r="Q718" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R718" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="str">
+        <v>T260803-00016</v>
+      </c>
+      <c r="B719" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C719" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D719" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E719" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F719">
+        <v>1</v>
+      </c>
+      <c r="G719" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="H719" t="str">
+        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
+      </c>
+      <c r="I719" t="str">
+        <v>2026-08-03 23:00</v>
+      </c>
+      <c r="J719" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K719">
+        <v>1</v>
+      </c>
+      <c r="L719" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M719" t="str">
+        <v>2026-08-03 23:33:14</v>
+      </c>
+      <c r="N719" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O719" s="1">
+        <v>0</v>
+      </c>
+      <c r="P719" t="str">
+        <v/>
+      </c>
+      <c r="Q719" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R719" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="str">
+        <v>T260803-00015</v>
+      </c>
+      <c r="B720" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C720" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D720" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E720" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F720">
+        <v>0</v>
+      </c>
+      <c r="G720" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="H720" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="I720" t="str">
+        <v>2026-08-03 22:00</v>
+      </c>
+      <c r="J720" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K720">
+        <v>1</v>
+      </c>
+      <c r="L720" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M720" t="str">
+        <v>2026-08-03 23:32:56</v>
+      </c>
+      <c r="N720" s="1">
+        <v>230000</v>
+      </c>
+      <c r="O720" s="1">
+        <v>0</v>
+      </c>
+      <c r="P720" t="str">
+        <v/>
+      </c>
+      <c r="Q720" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R720" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="str">
+        <v>T260803-00014</v>
+      </c>
+      <c r="B721" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C721" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D721" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E721" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F721">
+        <v>0</v>
+      </c>
+      <c r="G721" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="H721" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="I721" t="str">
+        <v>2026-08-03 21:00</v>
+      </c>
+      <c r="J721" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K721">
+        <v>1</v>
+      </c>
+      <c r="L721" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M721" t="str">
+        <v>2026-08-03 23:32:42</v>
+      </c>
+      <c r="N721" s="1">
+        <v>260000</v>
+      </c>
+      <c r="O721" s="1">
+        <v>0</v>
+      </c>
+      <c r="P721" t="str">
+        <v/>
+      </c>
+      <c r="Q721" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R721" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="str">
+        <v>T260803-00013</v>
+      </c>
+      <c r="B722" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C722" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D722" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E722" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F722">
+        <v>1</v>
+      </c>
+      <c r="G722" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="H722" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="I722" t="str">
+        <v>2026-08-03 22:00</v>
+      </c>
+      <c r="J722" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="K722">
+        <v>1</v>
+      </c>
+      <c r="L722" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M722" t="str">
+        <v>2026-08-03 23:32:24</v>
+      </c>
+      <c r="N722" s="1">
+        <v>290000</v>
+      </c>
+      <c r="O722" s="1">
+        <v>0</v>
+      </c>
+      <c r="P722" t="str">
+        <v/>
+      </c>
+      <c r="Q722" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R722" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="str">
+        <v>T260803-00012</v>
+      </c>
+      <c r="B723" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C723" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D723" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E723" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F723">
+        <v>0</v>
+      </c>
+      <c r="G723" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="H723" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="I723" t="str">
+        <v>2026-08-03 23:00</v>
+      </c>
+      <c r="J723" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K723">
+        <v>1</v>
+      </c>
+      <c r="L723" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M723" t="str">
+        <v>2026-08-03 23:32:00</v>
+      </c>
+      <c r="N723" s="1">
+        <v>490000</v>
+      </c>
+      <c r="O723" s="1">
+        <v>0</v>
+      </c>
+      <c r="P723" t="str">
+        <v/>
+      </c>
+      <c r="Q723" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R723" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="str">
+        <v>T260803-00011</v>
+      </c>
+      <c r="B724" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C724" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D724" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E724" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F724">
+        <v>0</v>
+      </c>
+      <c r="G724" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="H724" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="I724" t="str">
+        <v>2026-08-03 21:00</v>
+      </c>
+      <c r="J724" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K724">
+        <v>1</v>
+      </c>
+      <c r="L724" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M724" t="str">
+        <v>2026-08-03 23:31:43</v>
+      </c>
+      <c r="N724" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O724" s="1">
+        <v>0</v>
+      </c>
+      <c r="P724" t="str">
+        <v/>
+      </c>
+      <c r="Q724" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R724" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="str">
+        <v>T260803-00010</v>
+      </c>
+      <c r="B725" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C725" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D725" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E725" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F725">
+        <v>1</v>
+      </c>
+      <c r="G725" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="H725" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="I725" t="str">
+        <v>2026-08-03 22:00</v>
+      </c>
+      <c r="J725" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K725">
+        <v>1</v>
+      </c>
+      <c r="L725" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M725" t="str">
+        <v>2026-08-03 23:31:28</v>
+      </c>
+      <c r="N725" s="1">
+        <v>370000</v>
+      </c>
+      <c r="O725" s="1">
+        <v>0</v>
+      </c>
+      <c r="P725" t="str">
+        <v/>
+      </c>
+      <c r="Q725" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R725" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="str">
+        <v>T260803-00009</v>
+      </c>
+      <c r="B726" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C726" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D726" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E726" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F726">
+        <v>0</v>
+      </c>
+      <c r="G726" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="H726" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="I726" t="str">
+        <v>2026-08-03 23:00</v>
+      </c>
+      <c r="J726" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K726">
+        <v>1</v>
+      </c>
+      <c r="L726" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M726" t="str">
+        <v>2026-08-03 23:31:08</v>
+      </c>
+      <c r="N726" s="1">
+        <v>420000</v>
+      </c>
+      <c r="O726" s="1">
+        <v>0</v>
+      </c>
+      <c r="P726" t="str">
+        <v/>
+      </c>
+      <c r="Q726" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R726" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="str">
+        <v>T260803-00008</v>
+      </c>
+      <c r="B727" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C727" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D727" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E727" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F727">
+        <v>1</v>
+      </c>
+      <c r="G727" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="H727" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="I727" t="str">
+        <v>2026-08-03 23:00</v>
+      </c>
+      <c r="J727" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K727">
+        <v>1</v>
+      </c>
+      <c r="L727" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M727" t="str">
+        <v>2026-08-03 23:30:52</v>
+      </c>
+      <c r="N727" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O727" s="1">
+        <v>0</v>
+      </c>
+      <c r="P727" t="str">
+        <v/>
+      </c>
+      <c r="Q727" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R727" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="str">
+        <v>T260803-00007</v>
+      </c>
+      <c r="B728" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C728" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D728" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E728" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F728">
+        <v>0</v>
+      </c>
+      <c r="G728" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="H728" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="I728" t="str">
+        <v>2026-08-03 21:00</v>
+      </c>
+      <c r="J728" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="K728">
+        <v>1</v>
+      </c>
+      <c r="L728" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M728" t="str">
+        <v>2026-08-03 22:51:56</v>
+      </c>
+      <c r="N728" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O728" s="1">
+        <v>0</v>
+      </c>
+      <c r="P728" t="str">
+        <v/>
+      </c>
+      <c r="Q728" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R728" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="str">
+        <v>T260803-00006</v>
+      </c>
+      <c r="B729" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C729" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D729" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E729" t="str">
+        <v>2026-08-03 19:00</v>
+      </c>
+      <c r="F729">
+        <v>1</v>
+      </c>
+      <c r="G729" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="H729" t="str">
+        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="I729" t="str">
+        <v>2026-08-03 23:00</v>
+      </c>
+      <c r="J729" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="K729">
+        <v>1</v>
+      </c>
+      <c r="L729" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M729" t="str">
+        <v>2026-08-03 22:51:37</v>
+      </c>
+      <c r="N729" s="1">
+        <v>310000</v>
+      </c>
+      <c r="O729" s="1">
+        <v>0</v>
+      </c>
+      <c r="P729" t="str">
+        <v/>
+      </c>
+      <c r="Q729" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R729" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="str">
+        <v>T260803-00005</v>
+      </c>
+      <c r="B730" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C730" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D730" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E730" t="str">
+        <v>2026-08-03 17:50</v>
+      </c>
+      <c r="F730">
+        <v>0</v>
+      </c>
+      <c r="G730" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="H730" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="I730" t="str">
+        <v>2026-08-03 18:50</v>
+      </c>
+      <c r="J730" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="K730">
+        <v>1</v>
+      </c>
+      <c r="L730" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M730" t="str">
+        <v>2026-08-03 22:47:04</v>
+      </c>
+      <c r="N730" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O730" s="1">
+        <v>0</v>
+      </c>
+      <c r="P730" t="str">
+        <v/>
+      </c>
+      <c r="Q730" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R730" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="str">
+        <v>T260803-00004</v>
+      </c>
+      <c r="B731" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C731" t="str">
+        <v>샤오미</v>
+      </c>
+      <c r="D731" t="str">
+        <v>경기 이천시 대월면 부필리 309 샤오미</v>
+      </c>
+      <c r="E731" t="str">
+        <v>2026-08-03 13:50</v>
+      </c>
+      <c r="F731">
+        <v>0</v>
+      </c>
+      <c r="G731" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H731" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I731" t="str">
+        <v>2026-08-03 14:50</v>
+      </c>
+      <c r="J731" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K731">
+        <v>1</v>
+      </c>
+      <c r="L731" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M731" t="str">
+        <v>2026-08-03 22:46:33</v>
+      </c>
+      <c r="N731" s="1">
+        <v>120000</v>
+      </c>
+      <c r="O731" s="1">
+        <v>0</v>
+      </c>
+      <c r="P731" t="str">
+        <v>샤오미 외주사입고(11대)</v>
+      </c>
+      <c r="Q731" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R731" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="str">
+        <v>T260803-00003</v>
+      </c>
+      <c r="B732" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C732" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D732" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E732" t="str">
+        <v>2026-08-03 14:50</v>
+      </c>
+      <c r="F732">
+        <v>0</v>
+      </c>
+      <c r="G732" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H732" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I732" t="str">
+        <v>2026-08-03 15:50</v>
+      </c>
+      <c r="J732" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K732">
+        <v>1</v>
+      </c>
+      <c r="L732" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M732" t="str">
+        <v>2026-08-03 22:45:46</v>
+      </c>
+      <c r="N732" s="1">
+        <v>70000</v>
+      </c>
+      <c r="O732" s="1">
+        <v>0</v>
+      </c>
+      <c r="P732" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="Q732" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R732" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="str">
+        <v>T260803-00002</v>
+      </c>
+      <c r="B733" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C733" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D733" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E733" t="str">
+        <v>2026-08-03 10:00</v>
+      </c>
+      <c r="F733">
+        <v>0</v>
+      </c>
+      <c r="G733" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="H733" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="I733" t="str">
+        <v>2026-08-03 13:50</v>
+      </c>
+      <c r="J733" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="K733">
+        <v>1</v>
+      </c>
+      <c r="L733" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="M733" t="str">
+        <v>2026-08-03 22:45:01</v>
+      </c>
+      <c r="N733" s="1">
+        <v>160000</v>
+      </c>
+      <c r="O733" s="1">
+        <v>0</v>
+      </c>
+      <c r="P733" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="Q733" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="R733" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="str">
+        <v>T260803-00001</v>
+      </c>
+      <c r="B734" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C734" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D734" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E734" t="str">
+        <v>2026-08-03 16:30</v>
+      </c>
+      <c r="F734">
+        <v>0</v>
+      </c>
+      <c r="G734" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="H734" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I734" t="str">
+        <v>2026-08-03 18:00</v>
+      </c>
+      <c r="J734" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="K734">
+        <v>1</v>
+      </c>
+      <c r="L734" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="M734" t="str">
+        <v>2026-08-03 15:39:18</v>
+      </c>
+      <c r="N734" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O734" s="1">
+        <v>0</v>
+      </c>
+      <c r="P734" t="str">
+        <v/>
+      </c>
+      <c r="Q734" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="R734" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R632"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R734"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -720,7 +720,7 @@
         <v>T260909-00024</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260909-00023</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260909-00022</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260909-00021</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260909-00020</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260909-00019</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260909-00018</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260909-00017</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260909-00016</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260909-00015</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260909-00014</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260909-00013</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>안성FC</v>
@@ -1392,7 +1392,7 @@
         <v>T260909-00012</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>안성FC</v>
@@ -1448,7 +1448,7 @@
         <v>T260909-00011</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>안성FC</v>
@@ -1504,7 +1504,7 @@
         <v>T260909-00010</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>안성FC</v>
@@ -1560,7 +1560,7 @@
         <v>T260909-00009</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>안성FC</v>
@@ -1616,7 +1616,7 @@
         <v>T260909-00008</v>
       </c>
       <c r="B23" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C23" t="str">
         <v>안성FC</v>
@@ -1672,7 +1672,7 @@
         <v>T260909-00007</v>
       </c>
       <c r="B24" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C24" t="str">
         <v>샤오미 집하장</v>
@@ -1728,7 +1728,7 @@
         <v>T260909-00006</v>
       </c>
       <c r="B25" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C25" t="str">
         <v>아이베</v>
@@ -1784,7 +1784,7 @@
         <v>T260909-00005</v>
       </c>
       <c r="B26" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C26" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R637"/>
+  <dimension ref="A1:R609"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -34483,1577 +34483,9 @@
         <v>(주)위니온로지스</v>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="str">
-        <v>T260811-00028</v>
-      </c>
-      <c r="B610" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C610" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D610" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E610" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F610">
-        <v>0</v>
-      </c>
-      <c r="G610" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="H610" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="I610" t="str">
-        <v>2026-08-12 07:00</v>
-      </c>
-      <c r="J610" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K610">
-        <v>1</v>
-      </c>
-      <c r="L610" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M610" t="str">
-        <v>2026-08-11 19:14:28</v>
-      </c>
-      <c r="N610" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O610" s="1">
-        <v>0</v>
-      </c>
-      <c r="P610" t="str">
-        <v/>
-      </c>
-      <c r="Q610" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R610" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="str">
-        <v>T260811-00027</v>
-      </c>
-      <c r="B611" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C611" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D611" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E611" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F611">
-        <v>0</v>
-      </c>
-      <c r="G611" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="H611" t="str">
-        <v>인천 부평구 안남로433번길 19 인천ACP</v>
-      </c>
-      <c r="I611" t="str">
-        <v>2026-08-12 08:00</v>
-      </c>
-      <c r="J611" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K611">
-        <v>1</v>
-      </c>
-      <c r="L611" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M611" t="str">
-        <v>2026-08-11 19:13:34</v>
-      </c>
-      <c r="N611" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O611" s="1">
-        <v>0</v>
-      </c>
-      <c r="P611" t="str">
-        <v/>
-      </c>
-      <c r="Q611" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R611" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="str">
-        <v>T260811-00026</v>
-      </c>
-      <c r="B612" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C612" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D612" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E612" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F612">
-        <v>1</v>
-      </c>
-      <c r="G612" t="str">
-        <v>화성ACP</v>
-      </c>
-      <c r="H612" t="str">
-        <v>경기 화성시 효행구 비봉면 구포동길37번길 19 화성ACP</v>
-      </c>
-      <c r="I612" t="str">
-        <v>2026-08-12 07:00</v>
-      </c>
-      <c r="J612" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K612">
-        <v>1</v>
-      </c>
-      <c r="L612" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M612" t="str">
-        <v>2026-08-11 19:13:08</v>
-      </c>
-      <c r="N612" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O612" s="1">
-        <v>0</v>
-      </c>
-      <c r="P612" t="str">
-        <v/>
-      </c>
-      <c r="Q612" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R612" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="str">
-        <v>T260811-00025</v>
-      </c>
-      <c r="B613" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C613" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D613" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E613" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F613">
-        <v>0</v>
-      </c>
-      <c r="G613" t="str">
-        <v>시흥ACP</v>
-      </c>
-      <c r="H613" t="str">
-        <v>경기 시흥시 미산동 138-3 시흥ACP</v>
-      </c>
-      <c r="I613" t="str">
-        <v>2026-08-12 07:00</v>
-      </c>
-      <c r="J613" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K613">
-        <v>1</v>
-      </c>
-      <c r="L613" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M613" t="str">
-        <v>2026-08-11 19:12:43</v>
-      </c>
-      <c r="N613" s="1">
-        <v>140000</v>
-      </c>
-      <c r="O613" s="1">
-        <v>0</v>
-      </c>
-      <c r="P613" t="str">
-        <v/>
-      </c>
-      <c r="Q613" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R613" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="str">
-        <v>T260811-00024</v>
-      </c>
-      <c r="B614" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C614" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D614" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E614" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F614">
-        <v>0</v>
-      </c>
-      <c r="G614" t="str">
-        <v>대전중구ACP</v>
-      </c>
-      <c r="H614" t="str">
-        <v>대전 중구 보문산로77번길 8 대전중구ACP</v>
-      </c>
-      <c r="I614" t="str">
-        <v>2026-08-12 06:00</v>
-      </c>
-      <c r="J614" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="K614">
-        <v>1</v>
-      </c>
-      <c r="L614" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M614" t="str">
-        <v>2026-08-11 19:12:26</v>
-      </c>
-      <c r="N614" s="1">
-        <v>160000</v>
-      </c>
-      <c r="O614" s="1">
-        <v>0</v>
-      </c>
-      <c r="P614" t="str">
-        <v/>
-      </c>
-      <c r="Q614" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R614" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="str">
-        <v>T260811-00023</v>
-      </c>
-      <c r="B615" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C615" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D615" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E615" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F615">
-        <v>2</v>
-      </c>
-      <c r="G615" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="H615" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="I615" t="str">
-        <v>2026-08-12 07:00</v>
-      </c>
-      <c r="J615" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="K615">
-        <v>1</v>
-      </c>
-      <c r="L615" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M615" t="str">
-        <v>2026-08-11 19:12:09</v>
-      </c>
-      <c r="N615" s="1">
-        <v>320000</v>
-      </c>
-      <c r="O615" s="1">
-        <v>0</v>
-      </c>
-      <c r="P615" t="str">
-        <v/>
-      </c>
-      <c r="Q615" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R615" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="str">
-        <v>T260811-00022</v>
-      </c>
-      <c r="B616" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C616" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D616" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E616" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F616">
-        <v>0</v>
-      </c>
-      <c r="G616" t="str">
-        <v>용인ACP</v>
-      </c>
-      <c r="H616" t="str">
-        <v>경기 용인시 기흥구 신정로191번길 12 용인ACP</v>
-      </c>
-      <c r="I616" t="str">
-        <v>2026-08-11 21:00</v>
-      </c>
-      <c r="J616" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K616">
-        <v>1</v>
-      </c>
-      <c r="L616" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M616" t="str">
-        <v>2026-08-11 19:11:36</v>
-      </c>
-      <c r="N616" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O616" s="1">
-        <v>0</v>
-      </c>
-      <c r="P616" t="str">
-        <v/>
-      </c>
-      <c r="Q616" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R616" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="str">
-        <v>T260811-00021</v>
-      </c>
-      <c r="B617" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C617" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D617" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E617" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F617">
-        <v>0</v>
-      </c>
-      <c r="G617" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="H617" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="I617" t="str">
-        <v>2026-08-12 06:30</v>
-      </c>
-      <c r="J617" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K617">
-        <v>1</v>
-      </c>
-      <c r="L617" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M617" t="str">
-        <v>2026-08-11 19:11:20</v>
-      </c>
-      <c r="N617" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O617" s="1">
-        <v>0</v>
-      </c>
-      <c r="P617" t="str">
-        <v/>
-      </c>
-      <c r="Q617" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R617" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="str">
-        <v>T260811-00020</v>
-      </c>
-      <c r="B618" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C618" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D618" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E618" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F618">
-        <v>0</v>
-      </c>
-      <c r="G618" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="H618" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="I618" t="str">
-        <v>2026-08-11 21:00</v>
-      </c>
-      <c r="J618" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K618">
-        <v>1</v>
-      </c>
-      <c r="L618" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M618" t="str">
-        <v>2026-08-11 19:11:01</v>
-      </c>
-      <c r="N618" s="1">
-        <v>240000</v>
-      </c>
-      <c r="O618" s="1">
-        <v>0</v>
-      </c>
-      <c r="P618" t="str">
-        <v/>
-      </c>
-      <c r="Q618" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R618" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="str">
-        <v>T260811-00019</v>
-      </c>
-      <c r="B619" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C619" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D619" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E619" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F619">
-        <v>1</v>
-      </c>
-      <c r="G619" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="H619" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="I619" t="str">
-        <v>2026-08-11 22:00</v>
-      </c>
-      <c r="J619" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K619">
-        <v>1</v>
-      </c>
-      <c r="L619" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M619" t="str">
-        <v>2026-08-11 19:10:46</v>
-      </c>
-      <c r="N619" s="1">
-        <v>350000</v>
-      </c>
-      <c r="O619" s="1">
-        <v>0</v>
-      </c>
-      <c r="P619" t="str">
-        <v/>
-      </c>
-      <c r="Q619" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R619" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="str">
-        <v>T260811-00018</v>
-      </c>
-      <c r="B620" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C620" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D620" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E620" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F620">
-        <v>0</v>
-      </c>
-      <c r="G620" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="H620" t="str">
-        <v>창원시 의창구 동읍 노연리30-4 창원FDC</v>
-      </c>
-      <c r="I620" t="str">
-        <v>2026-08-11 23:00</v>
-      </c>
-      <c r="J620" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K620">
-        <v>1</v>
-      </c>
-      <c r="L620" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M620" t="str">
-        <v>2026-08-11 19:10:27</v>
-      </c>
-      <c r="N620" s="1">
-        <v>360000</v>
-      </c>
-      <c r="O620" s="1">
-        <v>0</v>
-      </c>
-      <c r="P620" t="str">
-        <v/>
-      </c>
-      <c r="Q620" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R620" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="str">
-        <v>T260811-00017</v>
-      </c>
-      <c r="B621" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C621" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D621" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E621" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F621">
-        <v>0</v>
-      </c>
-      <c r="G621" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="H621" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="I621" t="str">
-        <v>2026-08-11 21:00</v>
-      </c>
-      <c r="J621" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K621">
-        <v>1</v>
-      </c>
-      <c r="L621" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M621" t="str">
-        <v>2026-08-11 19:10:10</v>
-      </c>
-      <c r="N621" s="1">
-        <v>260000</v>
-      </c>
-      <c r="O621" s="1">
-        <v>0</v>
-      </c>
-      <c r="P621" t="str">
-        <v/>
-      </c>
-      <c r="Q621" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R621" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="str">
-        <v>T260811-00016</v>
-      </c>
-      <c r="B622" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C622" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D622" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E622" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F622">
-        <v>1</v>
-      </c>
-      <c r="G622" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="H622" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="I622" t="str">
-        <v>2026-08-11 22:00</v>
-      </c>
-      <c r="J622" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K622">
-        <v>1</v>
-      </c>
-      <c r="L622" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M622" t="str">
-        <v>2026-08-11 19:09:56</v>
-      </c>
-      <c r="N622" s="1">
-        <v>290000</v>
-      </c>
-      <c r="O622" s="1">
-        <v>0</v>
-      </c>
-      <c r="P622" t="str">
-        <v/>
-      </c>
-      <c r="Q622" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R622" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="str">
-        <v>T260811-00015</v>
-      </c>
-      <c r="B623" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C623" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D623" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E623" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F623">
-        <v>1</v>
-      </c>
-      <c r="G623" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="H623" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="I623" t="str">
-        <v>2026-08-11 23:00</v>
-      </c>
-      <c r="J623" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K623">
-        <v>1</v>
-      </c>
-      <c r="L623" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M623" t="str">
-        <v>2026-08-11 19:09:37</v>
-      </c>
-      <c r="N623" s="1">
-        <v>590000</v>
-      </c>
-      <c r="O623" s="1">
-        <v>0</v>
-      </c>
-      <c r="P623" t="str">
-        <v/>
-      </c>
-      <c r="Q623" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R623" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="str">
-        <v>T260811-00014</v>
-      </c>
-      <c r="B624" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C624" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D624" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E624" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F624">
-        <v>1</v>
-      </c>
-      <c r="G624" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="H624" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="I624" t="str">
-        <v>2026-08-11 22:00</v>
-      </c>
-      <c r="J624" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K624">
-        <v>1</v>
-      </c>
-      <c r="L624" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M624" t="str">
-        <v>2026-08-11 19:09:13</v>
-      </c>
-      <c r="N624" s="1">
-        <v>370000</v>
-      </c>
-      <c r="O624" s="1">
-        <v>0</v>
-      </c>
-      <c r="P624" t="str">
-        <v/>
-      </c>
-      <c r="Q624" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R624" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="str">
-        <v>T260811-00013</v>
-      </c>
-      <c r="B625" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C625" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D625" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E625" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F625">
-        <v>1</v>
-      </c>
-      <c r="G625" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="H625" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="I625" t="str">
-        <v>2026-08-11 23:00</v>
-      </c>
-      <c r="J625" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K625">
-        <v>1</v>
-      </c>
-      <c r="L625" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M625" t="str">
-        <v>2026-08-11 19:08:54</v>
-      </c>
-      <c r="N625" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O625" s="1">
-        <v>0</v>
-      </c>
-      <c r="P625" t="str">
-        <v/>
-      </c>
-      <c r="Q625" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R625" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="str">
-        <v>T260811-00012</v>
-      </c>
-      <c r="B626" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C626" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D626" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E626" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F626">
-        <v>0</v>
-      </c>
-      <c r="G626" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="H626" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="I626" t="str">
-        <v>2026-08-11 21:00</v>
-      </c>
-      <c r="J626" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K626">
-        <v>1</v>
-      </c>
-      <c r="L626" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M626" t="str">
-        <v>2026-08-11 19:08:29</v>
-      </c>
-      <c r="N626" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O626" s="1">
-        <v>0</v>
-      </c>
-      <c r="P626" t="str">
-        <v/>
-      </c>
-      <c r="Q626" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R626" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="str">
-        <v>T260811-00011</v>
-      </c>
-      <c r="B627" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C627" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D627" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E627" t="str">
-        <v>2026-08-11 19:00</v>
-      </c>
-      <c r="F627">
-        <v>1</v>
-      </c>
-      <c r="G627" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="H627" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="I627" t="str">
-        <v>2026-08-11 23:00</v>
-      </c>
-      <c r="J627" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K627">
-        <v>1</v>
-      </c>
-      <c r="L627" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M627" t="str">
-        <v>2026-08-11 19:08:15</v>
-      </c>
-      <c r="N627" s="1">
-        <v>520000</v>
-      </c>
-      <c r="O627" s="1">
-        <v>0</v>
-      </c>
-      <c r="P627" t="str">
-        <v/>
-      </c>
-      <c r="Q627" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R627" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="str">
-        <v>T260811-00010</v>
-      </c>
-      <c r="B628" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C628" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D628" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E628" t="str">
-        <v>2026-08-11 17:00</v>
-      </c>
-      <c r="F628">
-        <v>0</v>
-      </c>
-      <c r="G628" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="H628" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="I628" t="str">
-        <v>2026-08-11 18:00</v>
-      </c>
-      <c r="J628" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="K628">
-        <v>1</v>
-      </c>
-      <c r="L628" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M628" t="str">
-        <v>2026-08-11 19:04:09</v>
-      </c>
-      <c r="N628" s="1">
-        <v>100000</v>
-      </c>
-      <c r="O628" s="1">
-        <v>0</v>
-      </c>
-      <c r="P628" t="str">
-        <v/>
-      </c>
-      <c r="Q628" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R628" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="str">
-        <v>T260811-00009</v>
-      </c>
-      <c r="B629" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C629" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="D629" t="str">
-        <v>경기 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="E629" t="str">
-        <v>2026-08-11 08:00</v>
-      </c>
-      <c r="F629">
-        <v>0</v>
-      </c>
-      <c r="G629" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="H629" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="I629" t="str">
-        <v>2026-08-11 11:00</v>
-      </c>
-      <c r="J629" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K629">
-        <v>1</v>
-      </c>
-      <c r="L629" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M629" t="str">
-        <v>2026-08-11 19:03:32</v>
-      </c>
-      <c r="N629" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O629" s="1">
-        <v>0</v>
-      </c>
-      <c r="P629" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="Q629" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R629" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="str">
-        <v>T260811-00008</v>
-      </c>
-      <c r="B630" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C630" t="str">
-        <v>화성FDC</v>
-      </c>
-      <c r="D630" t="str">
-        <v>경기 화성시 장안면 3.1만세로 506-21 화성FDC</v>
-      </c>
-      <c r="E630" t="str">
-        <v>2026-08-11 22:00</v>
-      </c>
-      <c r="F630">
-        <v>0</v>
-      </c>
-      <c r="G630" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H630" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I630" t="str">
-        <v>2026-08-11 23:30</v>
-      </c>
-      <c r="J630" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K630">
-        <v>1</v>
-      </c>
-      <c r="L630" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M630" t="str">
-        <v>2026-08-11 19:02:42</v>
-      </c>
-      <c r="N630" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O630" s="1">
-        <v>0</v>
-      </c>
-      <c r="P630" t="str">
-        <v>공파렛이동</v>
-      </c>
-      <c r="Q630" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R630" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="str">
-        <v>T260811-00007</v>
-      </c>
-      <c r="B631" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C631" t="str">
-        <v>용인FDSYS</v>
-      </c>
-      <c r="D631" t="str">
-        <v>경기 용인시 처인구 원삼면 맹리 659-19 용인FDSYS</v>
-      </c>
-      <c r="E631" t="str">
-        <v>2026-08-11 09:00</v>
-      </c>
-      <c r="F631">
-        <v>0</v>
-      </c>
-      <c r="G631" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H631" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I631" t="str">
-        <v>2026-08-11 10:00</v>
-      </c>
-      <c r="J631" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="K631">
-        <v>1</v>
-      </c>
-      <c r="L631" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M631" t="str">
-        <v>2026-08-11 19:01:45</v>
-      </c>
-      <c r="N631" s="1">
-        <v>120000</v>
-      </c>
-      <c r="O631" s="1">
-        <v>0</v>
-      </c>
-      <c r="P631" t="str">
-        <v>거래처비용청구</v>
-      </c>
-      <c r="Q631" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R631" t="str">
-        <v>오텍캐리어</v>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="str">
-        <v>T260811-00006</v>
-      </c>
-      <c r="B632" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C632" t="str">
-        <v>용인FDSYS</v>
-      </c>
-      <c r="D632" t="str">
-        <v>경기 용인시 처인구 원삼면 맹리 659-19 용인FDSYS</v>
-      </c>
-      <c r="E632" t="str">
-        <v>2026-08-11 09:00</v>
-      </c>
-      <c r="F632">
-        <v>0</v>
-      </c>
-      <c r="G632" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H632" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I632" t="str">
-        <v>2026-08-11 12:00</v>
-      </c>
-      <c r="J632" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K632">
-        <v>1</v>
-      </c>
-      <c r="L632" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M632" t="str">
-        <v>2026-08-11 19:00:44</v>
-      </c>
-      <c r="N632" s="1">
-        <v>300000</v>
-      </c>
-      <c r="O632" s="1">
-        <v>0</v>
-      </c>
-      <c r="P632" t="str">
-        <v>거래처비용청구(2회전)</v>
-      </c>
-      <c r="Q632" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R632" t="str">
-        <v>오텍캐리어</v>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="str">
-        <v>T260811-00005</v>
-      </c>
-      <c r="B633" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C633" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D633" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E633" t="str">
-        <v>2026-08-11 14:00</v>
-      </c>
-      <c r="F633">
-        <v>0</v>
-      </c>
-      <c r="G633" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H633" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I633" t="str">
-        <v>2026-08-11 15:00</v>
-      </c>
-      <c r="J633" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K633">
-        <v>1</v>
-      </c>
-      <c r="L633" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M633" t="str">
-        <v>2026-08-11 18:59:25</v>
-      </c>
-      <c r="N633" s="1">
-        <v>70000</v>
-      </c>
-      <c r="O633" s="1">
-        <v>0</v>
-      </c>
-      <c r="P633" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="Q633" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R633" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="str">
-        <v>T260811-00004</v>
-      </c>
-      <c r="B634" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C634" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D634" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E634" t="str">
-        <v>2026-08-11 10:00</v>
-      </c>
-      <c r="F634">
-        <v>0</v>
-      </c>
-      <c r="G634" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H634" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I634" t="str">
-        <v>2026-08-11 13:00</v>
-      </c>
-      <c r="J634" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="K634">
-        <v>1</v>
-      </c>
-      <c r="L634" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="M634" t="str">
-        <v>2026-08-11 18:58:35</v>
-      </c>
-      <c r="N634" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O634" s="1">
-        <v>0</v>
-      </c>
-      <c r="P634" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="Q634" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="R634" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="str">
-        <v>T260811-00003</v>
-      </c>
-      <c r="B635" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C635" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D635" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E635" t="str">
-        <v>2026-08-11 21:00</v>
-      </c>
-      <c r="F635">
-        <v>0</v>
-      </c>
-      <c r="G635" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="H635" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="I635" t="str">
-        <v>2026-08-11 22:00</v>
-      </c>
-      <c r="J635" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="K635">
-        <v>1</v>
-      </c>
-      <c r="L635" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="M635" t="str">
-        <v>2026-08-11 15:49:47</v>
-      </c>
-      <c r="N635" s="1">
-        <v>180000</v>
-      </c>
-      <c r="O635" s="1">
-        <v>0</v>
-      </c>
-      <c r="P635" t="str">
-        <v xml:space="preserve">디지털태양제품 </v>
-      </c>
-      <c r="Q635" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R635" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="str">
-        <v>T260811-00002</v>
-      </c>
-      <c r="B636" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C636" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D636" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E636" t="str">
-        <v>2026-08-11 11:40</v>
-      </c>
-      <c r="F636">
-        <v>0</v>
-      </c>
-      <c r="G636" t="str">
-        <v>일코전자 박스출하</v>
-      </c>
-      <c r="H636" t="str">
-        <v>인천 남동구 호구포로 803 롯데캐슬 2303동 402호</v>
-      </c>
-      <c r="I636" t="str">
-        <v>2026-08-11 13:50</v>
-      </c>
-      <c r="J636" t="str">
-        <v>1톤 기타차량</v>
-      </c>
-      <c r="K636">
-        <v>1</v>
-      </c>
-      <c r="L636" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M636" t="str">
-        <v>2026-08-11 11:23:44</v>
-      </c>
-      <c r="N636" s="1">
-        <v>90000</v>
-      </c>
-      <c r="O636" s="1">
-        <v>0</v>
-      </c>
-      <c r="P636" t="str">
-        <v>일코전자 박스 출하</v>
-      </c>
-      <c r="Q636" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R636" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="str">
-        <v>T260811-00001</v>
-      </c>
-      <c r="B637" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C637" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D637" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E637" t="str">
-        <v>2026-08-11 10:30</v>
-      </c>
-      <c r="F637">
-        <v>0</v>
-      </c>
-      <c r="G637" t="str">
-        <v>의정부 이마트</v>
-      </c>
-      <c r="H637" t="str">
-        <v>경기 의정부시 민락로 210 의정부 이마트 1층</v>
-      </c>
-      <c r="I637" t="str">
-        <v>2026-08-11 13:00</v>
-      </c>
-      <c r="J637" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="K637">
-        <v>1</v>
-      </c>
-      <c r="L637" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="M637" t="str">
-        <v>2026-08-11 10:22:39</v>
-      </c>
-      <c r="N637" s="1">
-        <v>210000</v>
-      </c>
-      <c r="O637" s="1">
-        <v>0</v>
-      </c>
-      <c r="P637" t="str">
-        <v>마이디어 이마트 출하</v>
-      </c>
-      <c r="Q637" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="R637" t="str">
-        <v>마이디어</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R637"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R609"/>
   </ignoredErrors>
 </worksheet>
 </file>